--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
   <si>
     <t>DÍA</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>AGOSTO</t>
+  </si>
+  <si>
+    <t>1.185.93</t>
   </si>
 </sst>
 </file>
@@ -1633,7 +1636,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1704,6 +1707,9 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="956">
     <cellStyle name="=C:\WINNT\SYSTEM32\COMMAND.COM" xfId="936"/>
@@ -2982,7 +2988,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2990,7 +2996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H116"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5232,6 +5238,26 @@
         <v>80</v>
       </c>
     </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="22">
+        <v>46276</v>
+      </c>
+      <c r="B117" s="18">
+        <v>108</v>
+      </c>
+      <c r="C117" s="21"/>
+      <c r="D117" s="18">
+        <v>60</v>
+      </c>
+      <c r="E117" s="21"/>
+      <c r="F117" s="18">
+        <v>100</v>
+      </c>
+      <c r="G117" s="21"/>
+      <c r="H117" s="18">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5240,7 +5266,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5269,14 +5295,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B2" s="25">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C27" si="0">+((B3-B4)/B4)</f>
-        <v>0.64045278098882874</v>
+        <f t="shared" ref="C2:C28" si="0">+((B3-B4)/B4)</f>
+        <v>18.560573043109468</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -5287,14 +5313,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B3" s="25">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <v>0.64045278098882874</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -5305,14 +5331,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B4" s="25">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C4" s="31">
         <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <v>-0.82640880552358198</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -5323,14 +5349,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B5" s="25">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <v>2.4737529624349173</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -5341,14 +5367,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B6" s="25">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <v>-0.97953700801723442</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5359,14 +5385,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B7" s="25">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <v>80.163058476193896</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -5377,14 +5403,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B8" s="25">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C8" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <v>-0.77463732472189939</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -5395,1113 +5421,1120 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B9" s="25">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C9" s="31">
         <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <v>-0.99727371031195</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B10" s="25">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C10" s="31">
         <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <v>1028.4103166122507</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B11" s="25">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C11" s="31">
         <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <v>-0.98760095272084658</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B12" s="25">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C12" s="31">
         <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <v>98.812318362183703</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B13" s="25">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C13" s="31">
         <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <v>-0.9864837734804992</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="26">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B14" s="25">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C14" s="31">
         <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <v>74.639780601233326</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="26">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B15" s="25">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C15" s="31">
         <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="26">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B16" s="25">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C16" s="31">
         <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="26">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B17" s="25">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C17" s="31">
         <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="26">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B18" s="25">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C18" s="31">
         <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="26">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B19" s="25">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C19" s="31">
         <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="26">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B20" s="25">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C20" s="31">
         <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="26">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B21" s="25">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C21" s="31">
         <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="26">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B22" s="25">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C22" s="31">
         <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="26">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B23" s="25">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C23" s="31">
         <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="26">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B24" s="25">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C24" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="26">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B25" s="25">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C25" s="31">
         <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="26">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B26" s="25">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C26" s="31">
         <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="26">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B27" s="25">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C27" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="26">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B28" s="25">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C28" s="31">
-        <f t="shared" ref="C28:C71" si="1">+((B29-B30)/B30)</f>
-        <v>75.11816589074563</v>
+        <f t="shared" si="0"/>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="26">
+        <v>46239</v>
+      </c>
+      <c r="B29" s="25">
+        <v>2.8086933300000001</v>
+      </c>
+      <c r="C29" s="31">
+        <f t="shared" ref="C29:C72" si="1">+((B30-B31)/B31)</f>
+        <v>75.11816589074563</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="26">
         <v>46238</v>
       </c>
-      <c r="B29" s="25">
+      <c r="B30" s="25">
         <v>499.27660521000001</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C30" s="31">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="26">
+    <row r="31" spans="1:3">
+      <c r="A31" s="26">
         <v>46237</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B31" s="25">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="26">
+    <row r="32" spans="1:3">
+      <c r="A32" s="26">
         <v>46234</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B32" s="25">
         <v>19481.20894855</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="26">
+    <row r="33" spans="1:3">
+      <c r="A33" s="26">
         <v>46233</v>
       </c>
-      <c r="B32">
+      <c r="B33">
         <v>466.33578662999997</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="26">
+    <row r="34" spans="1:3">
+      <c r="A34" s="26">
         <v>46232</v>
       </c>
-      <c r="B33" s="25">
+      <c r="B34" s="25">
         <v>101.55832515</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C34" s="31">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="26">
+    <row r="35" spans="1:3">
+      <c r="A35" s="26">
         <v>46231</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B35" s="25">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C35" s="31">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="26">
+    <row r="36" spans="1:3">
+      <c r="A36" s="26">
         <v>46108</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B36" s="25">
         <v>223.50959897000001</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C36" s="31">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="26">
+    <row r="37" spans="1:3">
+      <c r="A37" s="26">
         <v>46226</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B37" s="25">
         <v>28677.412251940001</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C37" s="31">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="26">
+    <row r="38" spans="1:3">
+      <c r="A38" s="26">
         <v>46225</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B38" s="25">
         <v>858.25054019000004</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C38" s="31">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="26">
+    <row r="39" spans="1:3">
+      <c r="A39" s="26">
         <v>46224</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B39" s="25">
         <v>20.063323860000001</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C39" s="31">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="26">
+    <row r="40" spans="1:3">
+      <c r="A40" s="26">
         <v>46220</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B40" s="25">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C40" s="31">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="26">
+    <row r="41" spans="1:3">
+      <c r="A41" s="26">
         <v>46219</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B41" s="25">
         <v>16578.913830919999</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C41" s="31">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="26">
+    <row r="42" spans="1:3">
+      <c r="A42" s="26">
         <v>46218</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B42" s="25">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C42" s="31">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="26">
+    <row r="43" spans="1:3">
+      <c r="A43" s="26">
         <v>46217</v>
       </c>
-      <c r="B42" s="25">
+      <c r="B43" s="25">
         <v>38833.478919130001</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C43" s="31">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="26">
+    <row r="44" spans="1:3">
+      <c r="A44" s="26">
         <v>46216</v>
       </c>
-      <c r="B43" s="25">
+      <c r="B44" s="25">
         <v>52315.97026473</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C44" s="31">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="26">
+    <row r="45" spans="1:3">
+      <c r="A45" s="26">
         <v>46213</v>
       </c>
-      <c r="B44" s="25">
+      <c r="B45" s="25">
         <v>64626.363040830001</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C45" s="31">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="26">
+    <row r="46" spans="1:3">
+      <c r="A46" s="26">
         <v>46212</v>
       </c>
-      <c r="B45" s="25">
+      <c r="B46" s="25">
         <v>28200.29395617</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C46" s="31">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="26">
+    <row r="47" spans="1:3">
+      <c r="A47" s="26">
         <v>46211</v>
       </c>
-      <c r="B46" s="25">
+      <c r="B47" s="25">
         <v>7705.0577555</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C47" s="31">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="26">
+    <row r="48" spans="1:3">
+      <c r="A48" s="26">
         <v>46210</v>
       </c>
-      <c r="B47" s="25">
+      <c r="B48" s="25">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C48" s="31">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="26">
+    <row r="49" spans="1:3">
+      <c r="A49" s="26">
         <v>46209</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B49" s="25">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C49" s="31">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="26">
+    <row r="50" spans="1:3">
+      <c r="A50" s="26">
         <v>46206</v>
       </c>
-      <c r="B49" s="25">
+      <c r="B50" s="25">
         <v>17125.195337590001</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C50" s="31">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="26">
+    <row r="51" spans="1:3">
+      <c r="A51" s="26">
         <v>46205</v>
       </c>
-      <c r="B50" s="25">
+      <c r="B51" s="25">
         <v>28151.370695969999</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C51" s="31">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="26">
+    <row r="52" spans="1:3">
+      <c r="A52" s="26">
         <v>46204</v>
       </c>
-      <c r="B51" s="25">
+      <c r="B52" s="25">
         <v>989.47411254999997</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C52" s="31">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="26">
+    <row r="53" spans="1:3">
+      <c r="A53" s="26">
         <v>46203</v>
       </c>
-      <c r="B52" s="25">
+      <c r="B53" s="25">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C53" s="31">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="26">
+    <row r="54" spans="1:3">
+      <c r="A54" s="26">
         <v>46198</v>
       </c>
-      <c r="B53" s="25">
+      <c r="B54" s="25">
         <v>31666.069450710002</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C54" s="31">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="26">
+    <row r="55" spans="1:3">
+      <c r="A55" s="26">
         <v>46196</v>
       </c>
-      <c r="B54" s="25">
+      <c r="B55" s="25">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C55" s="31">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="26">
+    <row r="56" spans="1:3">
+      <c r="A56" s="26">
         <v>46195</v>
       </c>
-      <c r="B55" s="25">
+      <c r="B56" s="25">
         <v>1716.30170335</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C56" s="31">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="26">
+    <row r="57" spans="1:3">
+      <c r="A57" s="26">
         <v>46192</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B57" s="25">
         <v>16.43890412</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C57" s="31">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="26">
+    <row r="58" spans="1:3">
+      <c r="A58" s="26">
         <v>46191</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B58" s="25">
         <v>269.81083503999997</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C58" s="31">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="26">
+    <row r="59" spans="1:3">
+      <c r="A59" s="26">
         <v>46190</v>
       </c>
-      <c r="B58" s="25">
+      <c r="B59" s="25">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C59" s="31">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="26">
+    <row r="60" spans="1:3">
+      <c r="A60" s="26">
         <v>46189</v>
       </c>
-      <c r="B59" s="25">
+      <c r="B60" s="25">
         <v>1206.260808</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C60" s="31">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="26">
+    <row r="61" spans="1:3">
+      <c r="A61" s="26">
         <v>46188</v>
       </c>
-      <c r="B60" s="25">
+      <c r="B61" s="25">
         <v>8.42</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C61" s="31">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="26">
+    <row r="62" spans="1:3">
+      <c r="A62" s="26">
         <v>46185</v>
       </c>
-      <c r="B61" s="25">
+      <c r="B62" s="25">
         <v>19.156653639999998</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C62" s="31">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="26">
+    <row r="63" spans="1:3">
+      <c r="A63" s="26">
         <v>46184</v>
       </c>
-      <c r="B62" s="25">
+      <c r="B63" s="25">
         <v>12.711483429999999</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C63" s="31">
         <f t="shared" si="1"/>
         <v>5.2639483520141219</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="26">
+    <row r="64" spans="1:3">
+      <c r="A64" s="26">
         <v>46183</v>
       </c>
-      <c r="B63" s="25">
+      <c r="B64" s="25">
         <v>22562.357509739999</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C64" s="31">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="26">
+    <row r="65" spans="1:3">
+      <c r="A65" s="26">
         <v>46182</v>
       </c>
-      <c r="B64" s="25">
+      <c r="B65" s="25">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C65" s="31">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="26">
+    <row r="66" spans="1:3">
+      <c r="A66" s="26">
         <v>46178</v>
       </c>
-      <c r="B65" s="25">
+      <c r="B66" s="25">
         <v>58292.928576159997</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C66" s="31">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="26">
+    <row r="67" spans="1:3">
+      <c r="A67" s="26">
         <v>46177</v>
       </c>
-      <c r="B66" s="25">
+      <c r="B67" s="25">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C67" s="31">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="26">
+    <row r="68" spans="1:3">
+      <c r="A68" s="26">
         <v>46176</v>
       </c>
-      <c r="B67" s="25">
+      <c r="B68" s="25">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C68" s="31">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="26">
+    <row r="69" spans="1:3">
+      <c r="A69" s="26">
         <v>46175</v>
       </c>
-      <c r="B68" s="25">
+      <c r="B69" s="25">
         <v>29863.561946620001</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C69" s="31">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="26">
+    <row r="70" spans="1:3">
+      <c r="A70" s="26">
         <v>46174</v>
       </c>
-      <c r="B69" s="25">
+      <c r="B70" s="25">
         <v>55.287064620000002</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C70" s="31">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="26">
+    <row r="71" spans="1:3">
+      <c r="A71" s="26">
         <v>46171</v>
       </c>
-      <c r="B70" s="25">
+      <c r="B71" s="25">
         <v>33469.1560455</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C71" s="31">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="26">
+    <row r="72" spans="1:3">
+      <c r="A72" s="26">
         <v>45074</v>
       </c>
-      <c r="B71" s="25">
+      <c r="B72" s="25">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C72" s="31">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="26">
-        <v>46169</v>
-      </c>
-      <c r="B72" s="25">
-        <v>21.673895040000001</v>
-      </c>
-      <c r="C72" s="31">
-        <f>+((B73-B74)/B74)</f>
-        <v>-0.31892665326814518</v>
-      </c>
-    </row>
     <row r="73" spans="1:3">
       <c r="A73" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B73" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C73" s="31">
         <f>+((B74-B75)/B75)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B74" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C74" s="31">
         <f>+((B75-B76)/B76)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B75" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C75" s="31">
-        <f>+((B80-B81)/B81)</f>
-        <v>82.182099964255912</v>
+        <f>+((B76-B77)/B77)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B76" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C76" s="31">
-        <f t="shared" ref="C76:C99" si="2">+((B81-B82)/B82)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B81-B82)/B82)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="26">
+        <v>46163</v>
+      </c>
+      <c r="B77" s="25">
+        <v>55.256117230000001</v>
+      </c>
+      <c r="C77" s="31">
+        <f t="shared" ref="C77:C100" si="2">+((B82-B83)/B83)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="26">
         <v>46162</v>
       </c>
-      <c r="B77" s="25">
+      <c r="B78" s="25">
         <v>20356.468143580001</v>
       </c>
-      <c r="C77" s="31">
+      <c r="C78" s="31">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="26">
+    <row r="79" spans="1:3">
+      <c r="A79" s="26">
         <v>46161</v>
       </c>
-      <c r="B78" s="25">
+      <c r="B79" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C78" s="31">
+      <c r="C79" s="31">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="26">
+    <row r="80" spans="1:3">
+      <c r="A80" s="26">
         <v>46157</v>
       </c>
-      <c r="B79" s="25">
+      <c r="B80" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C79" s="31">
+      <c r="C80" s="31">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="26">
+    <row r="81" spans="1:3">
+      <c r="A81" s="26">
         <v>46156</v>
       </c>
-      <c r="B80" s="25">
+      <c r="B81" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C80" s="31">
+      <c r="C81" s="31">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="26">
+    <row r="82" spans="1:3">
+      <c r="A82" s="26">
         <v>46155</v>
       </c>
-      <c r="B81" s="25">
+      <c r="B82" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C81" s="31">
+      <c r="C82" s="31">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="26">
+    <row r="83" spans="1:3">
+      <c r="A83" s="26">
         <v>46154</v>
       </c>
-      <c r="B82" s="25">
+      <c r="B83" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C82" s="31">
+      <c r="C83" s="31">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="26">
+    <row r="84" spans="1:3">
+      <c r="A84" s="26">
         <v>46153</v>
       </c>
-      <c r="B83" s="25">
+      <c r="B84" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C83" s="31">
+      <c r="C84" s="31">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="26">
+    <row r="85" spans="1:3">
+      <c r="A85" s="26">
         <v>46150</v>
       </c>
-      <c r="B84" s="25">
+      <c r="B85" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C85" s="31">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46149</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C85" s="31">
+      <c r="C86" s="31">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="19">
+    <row r="87" spans="1:3">
+      <c r="A87" s="19">
         <v>46148</v>
       </c>
-      <c r="B86" s="17">
+      <c r="B87" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C86" s="31">
+      <c r="C87" s="31">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="19">
+    <row r="88" spans="1:3">
+      <c r="A88" s="19">
         <v>46147</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B88" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C87" s="31">
+      <c r="C88" s="31">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="19">
+    <row r="89" spans="1:3">
+      <c r="A89" s="19">
         <v>46146</v>
       </c>
-      <c r="B88" s="17">
+      <c r="B89" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C89" s="31">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="20">
+    <row r="90" spans="1:3">
+      <c r="A90" s="20">
         <v>46142</v>
       </c>
-      <c r="B89" s="17">
+      <c r="B90" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C89" s="31">
+      <c r="C90" s="31">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="20">
+    <row r="91" spans="1:3">
+      <c r="A91" s="20">
         <v>46141</v>
       </c>
-      <c r="B90" s="17">
+      <c r="B91" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C90" s="31">
+      <c r="C91" s="31">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="20">
+    <row r="92" spans="1:3">
+      <c r="A92" s="20">
         <v>46140</v>
       </c>
-      <c r="B91" s="17">
+      <c r="B92" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C91" s="31">
+      <c r="C92" s="31">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="20">
+    <row r="93" spans="1:3">
+      <c r="A93" s="20">
         <v>46139</v>
       </c>
-      <c r="B92" s="17">
+      <c r="B93" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C92" s="31">
+      <c r="C93" s="31">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="20">
+    <row r="94" spans="1:3">
+      <c r="A94" s="20">
         <v>46136</v>
       </c>
-      <c r="B93" s="17">
+      <c r="B94" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C93" s="31">
+      <c r="C94" s="31">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="20">
+    <row r="95" spans="1:3">
+      <c r="A95" s="20">
         <v>46135</v>
       </c>
-      <c r="B94" s="17">
+      <c r="B95" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C94" s="31">
+      <c r="C95" s="31">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="20">
+    <row r="96" spans="1:3">
+      <c r="A96" s="20">
         <v>46134</v>
       </c>
-      <c r="B95" s="17">
+      <c r="B96" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C95" s="31">
+      <c r="C96" s="31">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="20">
+    <row r="97" spans="1:3">
+      <c r="A97" s="20">
         <v>46133</v>
       </c>
-      <c r="B96" s="17">
+      <c r="B97" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C96" s="31">
+      <c r="C97" s="31">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="20">
+    <row r="98" spans="1:3">
+      <c r="A98" s="20">
         <v>46132</v>
       </c>
-      <c r="B97" s="17">
+      <c r="B98" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C97" s="31">
+      <c r="C98" s="31">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="20">
+    <row r="99" spans="1:3">
+      <c r="A99" s="20">
         <v>46129</v>
       </c>
-      <c r="B98" s="17">
+      <c r="B99" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C98" s="31">
+      <c r="C99" s="31">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="20">
+    <row r="100" spans="1:3">
+      <c r="A100" s="20">
         <v>46128</v>
       </c>
-      <c r="B99" s="17">
+      <c r="B100" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C99" s="31">
+      <c r="C100" s="31">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="20">
-        <v>46127</v>
-      </c>
-      <c r="B100" s="17">
-        <v>15.79809785</v>
-      </c>
-      <c r="C100" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="101" spans="1:3">
       <c r="A101" s="20">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B101" s="17">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C101" s="16">
         <v>0</v>
@@ -6509,10 +6542,10 @@
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B102" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C102" s="16">
         <v>0</v>
@@ -6520,10 +6553,10 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B103" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C103" s="16">
         <v>0</v>
@@ -6531,10 +6564,10 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B104" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C104" s="16">
         <v>0</v>
@@ -6542,10 +6575,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B105" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C105" s="16">
         <v>0</v>
@@ -6553,41 +6586,52 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B106" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C106" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B107" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B108" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B109" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B110" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="20">
         <v>46111</v>
       </c>
-      <c r="B110" s="17">
+      <c r="B111" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7009,7 +7053,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -7650,6 +7694,32 @@
         <v>3.2456431709609603</v>
       </c>
     </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="26">
+        <v>46269</v>
+      </c>
+      <c r="B25" s="18">
+        <v>79934788.226620004</v>
+      </c>
+      <c r="C25" s="18">
+        <v>2449226669.3992906</v>
+      </c>
+      <c r="D25" s="18">
+        <v>220761212.62711993</v>
+      </c>
+      <c r="E25" s="18">
+        <v>2749922670.2530308</v>
+      </c>
+      <c r="F25" s="18">
+        <v>2498658.4271799996</v>
+      </c>
+      <c r="G25" s="18">
+        <v>2752421328.6802111</v>
+      </c>
+      <c r="H25" s="28">
+        <v>3.0254778175788317</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7657,7 +7727,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9258,7 +9328,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="32">
-        <f t="shared" ref="E76:E98" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E99" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="33">
@@ -9725,6 +9795,27 @@
       </c>
       <c r="F98" s="33">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" s="26">
+        <v>46275</v>
+      </c>
+      <c r="B99" s="27">
+        <v>12855</v>
+      </c>
+      <c r="C99" s="25">
+        <v>3</v>
+      </c>
+      <c r="D99" s="27">
+        <v>12858</v>
+      </c>
+      <c r="E99" s="32">
+        <f t="shared" si="4"/>
+        <v>-3.3330749554298118E-3</v>
+      </c>
+      <c r="F99" s="33">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2988,7 +2988,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2996,7 +2996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5258,6 +5258,26 @@
         <v>80</v>
       </c>
     </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="22">
+        <v>46280</v>
+      </c>
+      <c r="B118" s="18">
+        <v>2571.288</v>
+      </c>
+      <c r="C118" s="21"/>
+      <c r="D118" s="18">
+        <v>100</v>
+      </c>
+      <c r="E118" s="21"/>
+      <c r="F118" s="18">
+        <v>150</v>
+      </c>
+      <c r="G118" s="21"/>
+      <c r="H118" s="18">
+        <v>110.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5266,7 +5286,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5295,14 +5315,14 @@
     </row>
     <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="26">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B2" s="25">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C2" s="31">
-        <f t="shared" ref="C2:C28" si="0">+((B3-B4)/B4)</f>
-        <v>18.560573043109468</v>
+        <f t="shared" ref="C2:C29" si="0">+((B3-B4)/B4)</f>
+        <v>-0.67806849277578529</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>8</v>
@@ -5313,14 +5333,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="26">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B3" s="25">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C3" s="31">
         <f t="shared" si="0"/>
-        <v>0.64045278098882874</v>
+        <v>18.560573043109468</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>9</v>
@@ -5331,14 +5351,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="26">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B4" s="25">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C4" s="31">
         <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <v>0.64045278098882874</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>10</v>
@@ -5349,14 +5369,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="26">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B5" s="25">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C5" s="31">
         <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <v>-0.82640880552358198</v>
       </c>
       <c r="D5" s="25" t="s">
         <v>30</v>
@@ -5367,14 +5387,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="26">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B6" s="25">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C6" s="31">
         <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <v>2.4737529624349173</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5385,14 +5405,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="26">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B7" s="25">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C7" s="31">
         <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <v>-0.97953700801723442</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -5403,14 +5423,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B8" s="25">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C8" s="31">
         <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <v>80.163058476193896</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -5421,14 +5441,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="26">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B9" s="25">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C9" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <v>-0.77463732472189939</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -5439,1113 +5459,1114 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="26">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B10" s="25">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C10" s="31">
         <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <v>-0.99727371031195</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="26">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B11" s="25">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C11" s="31">
         <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <v>1028.4103166122507</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="26">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B12" s="25">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C12" s="31">
         <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <v>-0.98760095272084658</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="26">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B13" s="25">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C13" s="31">
         <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <v>98.812318362183703</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="26">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B14" s="25">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C14" s="31">
         <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <v>-0.9864837734804992</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="26">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="25">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C15" s="31">
         <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <v>74.639780601233326</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="26">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B16" s="25">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C16" s="31">
         <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="26">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B17" s="25">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C17" s="31">
         <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="26">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B18" s="25">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C18" s="31">
         <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="26">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B19" s="25">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C19" s="31">
         <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="26">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B20" s="25">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C20" s="31">
         <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="26">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B21" s="25">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C21" s="31">
         <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="26">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B22" s="25">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C22" s="31">
         <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="26">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B23" s="25">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C23" s="31">
         <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="26">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B24" s="25">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C24" s="31">
         <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="26">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B25" s="25">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C25" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="26">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B26" s="25">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C26" s="31">
         <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="26">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B27" s="25">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C27" s="31">
         <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="26">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B28" s="25">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C28" s="31">
         <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="26">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B29" s="25">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C29" s="31">
-        <f t="shared" ref="C29:C72" si="1">+((B30-B31)/B31)</f>
-        <v>75.11816589074563</v>
+        <f t="shared" si="0"/>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="26">
+        <v>46239</v>
+      </c>
+      <c r="B30" s="25">
+        <v>2.8086933300000001</v>
+      </c>
+      <c r="C30" s="31">
+        <f t="shared" ref="C30:C73" si="1">+((B31-B32)/B32)</f>
+        <v>75.11816589074563</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="26">
         <v>46238</v>
       </c>
-      <c r="B30" s="25">
+      <c r="B31" s="25">
         <v>499.27660521000001</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C31" s="31">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="26">
+    <row r="32" spans="1:3">
+      <c r="A32" s="26">
         <v>46237</v>
       </c>
-      <c r="B31" s="25">
+      <c r="B32" s="25">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C32" s="31">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="26">
+    <row r="33" spans="1:3">
+      <c r="A33" s="26">
         <v>46234</v>
       </c>
-      <c r="B32" s="25">
+      <c r="B33" s="25">
         <v>19481.20894855</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C33" s="31">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="26">
+    <row r="34" spans="1:3">
+      <c r="A34" s="26">
         <v>46233</v>
       </c>
-      <c r="B33">
+      <c r="B34">
         <v>466.33578662999997</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C34" s="31">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="26">
+    <row r="35" spans="1:3">
+      <c r="A35" s="26">
         <v>46232</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B35" s="25">
         <v>101.55832515</v>
       </c>
-      <c r="C34" s="31">
+      <c r="C35" s="31">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="26">
+    <row r="36" spans="1:3">
+      <c r="A36" s="26">
         <v>46231</v>
       </c>
-      <c r="B35" s="25">
+      <c r="B36" s="25">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C36" s="31">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="26">
+    <row r="37" spans="1:3">
+      <c r="A37" s="26">
         <v>46108</v>
       </c>
-      <c r="B36" s="25">
+      <c r="B37" s="25">
         <v>223.50959897000001</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C37" s="31">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="26">
+    <row r="38" spans="1:3">
+      <c r="A38" s="26">
         <v>46226</v>
       </c>
-      <c r="B37" s="25">
+      <c r="B38" s="25">
         <v>28677.412251940001</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C38" s="31">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="26">
+    <row r="39" spans="1:3">
+      <c r="A39" s="26">
         <v>46225</v>
       </c>
-      <c r="B38" s="25">
+      <c r="B39" s="25">
         <v>858.25054019000004</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C39" s="31">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="26">
+    <row r="40" spans="1:3">
+      <c r="A40" s="26">
         <v>46224</v>
       </c>
-      <c r="B39" s="25">
+      <c r="B40" s="25">
         <v>20.063323860000001</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C40" s="31">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="26">
+    <row r="41" spans="1:3">
+      <c r="A41" s="26">
         <v>46220</v>
       </c>
-      <c r="B40" s="25">
+      <c r="B41" s="25">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C41" s="31">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="26">
+    <row r="42" spans="1:3">
+      <c r="A42" s="26">
         <v>46219</v>
       </c>
-      <c r="B41" s="25">
+      <c r="B42" s="25">
         <v>16578.913830919999</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C42" s="31">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="26">
+    <row r="43" spans="1:3">
+      <c r="A43" s="26">
         <v>46218</v>
       </c>
-      <c r="B42" s="25">
+      <c r="B43" s="25">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C43" s="31">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="26">
+    <row r="44" spans="1:3">
+      <c r="A44" s="26">
         <v>46217</v>
       </c>
-      <c r="B43" s="25">
+      <c r="B44" s="25">
         <v>38833.478919130001</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C44" s="31">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="26">
+    <row r="45" spans="1:3">
+      <c r="A45" s="26">
         <v>46216</v>
       </c>
-      <c r="B44" s="25">
+      <c r="B45" s="25">
         <v>52315.97026473</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C45" s="31">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="26">
+    <row r="46" spans="1:3">
+      <c r="A46" s="26">
         <v>46213</v>
       </c>
-      <c r="B45" s="25">
+      <c r="B46" s="25">
         <v>64626.363040830001</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C46" s="31">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="26">
+    <row r="47" spans="1:3">
+      <c r="A47" s="26">
         <v>46212</v>
       </c>
-      <c r="B46" s="25">
+      <c r="B47" s="25">
         <v>28200.29395617</v>
       </c>
-      <c r="C46" s="31">
+      <c r="C47" s="31">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="26">
+    <row r="48" spans="1:3">
+      <c r="A48" s="26">
         <v>46211</v>
       </c>
-      <c r="B47" s="25">
+      <c r="B48" s="25">
         <v>7705.0577555</v>
       </c>
-      <c r="C47" s="31">
+      <c r="C48" s="31">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="26">
+    <row r="49" spans="1:3">
+      <c r="A49" s="26">
         <v>46210</v>
       </c>
-      <c r="B48" s="25">
+      <c r="B49" s="25">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C48" s="31">
+      <c r="C49" s="31">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="26">
+    <row r="50" spans="1:3">
+      <c r="A50" s="26">
         <v>46209</v>
       </c>
-      <c r="B49" s="25">
+      <c r="B50" s="25">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C49" s="31">
+      <c r="C50" s="31">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="26">
+    <row r="51" spans="1:3">
+      <c r="A51" s="26">
         <v>46206</v>
       </c>
-      <c r="B50" s="25">
+      <c r="B51" s="25">
         <v>17125.195337590001</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C51" s="31">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="26">
+    <row r="52" spans="1:3">
+      <c r="A52" s="26">
         <v>46205</v>
       </c>
-      <c r="B51" s="25">
+      <c r="B52" s="25">
         <v>28151.370695969999</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C52" s="31">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="26">
+    <row r="53" spans="1:3">
+      <c r="A53" s="26">
         <v>46204</v>
       </c>
-      <c r="B52" s="25">
+      <c r="B53" s="25">
         <v>989.47411254999997</v>
       </c>
-      <c r="C52" s="31">
+      <c r="C53" s="31">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="26">
+    <row r="54" spans="1:3">
+      <c r="A54" s="26">
         <v>46203</v>
       </c>
-      <c r="B53" s="25">
+      <c r="B54" s="25">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C54" s="31">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="26">
+    <row r="55" spans="1:3">
+      <c r="A55" s="26">
         <v>46198</v>
       </c>
-      <c r="B54" s="25">
+      <c r="B55" s="25">
         <v>31666.069450710002</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C55" s="31">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="26">
+    <row r="56" spans="1:3">
+      <c r="A56" s="26">
         <v>46196</v>
       </c>
-      <c r="B55" s="25">
+      <c r="B56" s="25">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C55" s="31">
+      <c r="C56" s="31">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="26">
+    <row r="57" spans="1:3">
+      <c r="A57" s="26">
         <v>46195</v>
       </c>
-      <c r="B56" s="25">
+      <c r="B57" s="25">
         <v>1716.30170335</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C57" s="31">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="26">
+    <row r="58" spans="1:3">
+      <c r="A58" s="26">
         <v>46192</v>
       </c>
-      <c r="B57" s="25">
+      <c r="B58" s="25">
         <v>16.43890412</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C58" s="31">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="26">
+    <row r="59" spans="1:3">
+      <c r="A59" s="26">
         <v>46191</v>
       </c>
-      <c r="B58" s="25">
+      <c r="B59" s="25">
         <v>269.81083503999997</v>
       </c>
-      <c r="C58" s="31">
+      <c r="C59" s="31">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="26">
+    <row r="60" spans="1:3">
+      <c r="A60" s="26">
         <v>46190</v>
       </c>
-      <c r="B59" s="25">
+      <c r="B60" s="25">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C60" s="31">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="26">
+    <row r="61" spans="1:3">
+      <c r="A61" s="26">
         <v>46189</v>
       </c>
-      <c r="B60" s="25">
+      <c r="B61" s="25">
         <v>1206.260808</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C61" s="31">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="26">
+    <row r="62" spans="1:3">
+      <c r="A62" s="26">
         <v>46188</v>
       </c>
-      <c r="B61" s="25">
+      <c r="B62" s="25">
         <v>8.42</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C62" s="31">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="26">
+    <row r="63" spans="1:3">
+      <c r="A63" s="26">
         <v>46185</v>
       </c>
-      <c r="B62" s="25">
+      <c r="B63" s="25">
         <v>19.156653639999998</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C63" s="31">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="26">
+    <row r="64" spans="1:3">
+      <c r="A64" s="26">
         <v>46184</v>
       </c>
-      <c r="B63" s="25">
+      <c r="B64" s="25">
         <v>12.711483429999999</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C64" s="31">
         <f t="shared" si="1"/>
         <v>5.2639483520141219</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="26">
+    <row r="65" spans="1:3">
+      <c r="A65" s="26">
         <v>46183</v>
       </c>
-      <c r="B64" s="25">
+      <c r="B65" s="25">
         <v>22562.357509739999</v>
       </c>
-      <c r="C64" s="31">
+      <c r="C65" s="31">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="26">
+    <row r="66" spans="1:3">
+      <c r="A66" s="26">
         <v>46182</v>
       </c>
-      <c r="B65" s="25">
+      <c r="B66" s="25">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C66" s="31">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="26">
+    <row r="67" spans="1:3">
+      <c r="A67" s="26">
         <v>46178</v>
       </c>
-      <c r="B66" s="25">
+      <c r="B67" s="25">
         <v>58292.928576159997</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C67" s="31">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="26">
+    <row r="68" spans="1:3">
+      <c r="A68" s="26">
         <v>46177</v>
       </c>
-      <c r="B67" s="25">
+      <c r="B68" s="25">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C67" s="31">
+      <c r="C68" s="31">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="26">
+    <row r="69" spans="1:3">
+      <c r="A69" s="26">
         <v>46176</v>
       </c>
-      <c r="B68" s="25">
+      <c r="B69" s="25">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C69" s="31">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="26">
+    <row r="70" spans="1:3">
+      <c r="A70" s="26">
         <v>46175</v>
       </c>
-      <c r="B69" s="25">
+      <c r="B70" s="25">
         <v>29863.561946620001</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C70" s="31">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="26">
+    <row r="71" spans="1:3">
+      <c r="A71" s="26">
         <v>46174</v>
       </c>
-      <c r="B70" s="25">
+      <c r="B71" s="25">
         <v>55.287064620000002</v>
       </c>
-      <c r="C70" s="31">
+      <c r="C71" s="31">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="26">
+    <row r="72" spans="1:3">
+      <c r="A72" s="26">
         <v>46171</v>
       </c>
-      <c r="B71" s="25">
+      <c r="B72" s="25">
         <v>33469.1560455</v>
       </c>
-      <c r="C71" s="31">
+      <c r="C72" s="31">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="26">
+    <row r="73" spans="1:3">
+      <c r="A73" s="26">
         <v>45074</v>
       </c>
-      <c r="B72" s="25">
+      <c r="B73" s="25">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C72" s="31">
+      <c r="C73" s="31">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="26">
-        <v>46169</v>
-      </c>
-      <c r="B73" s="25">
-        <v>21.673895040000001</v>
-      </c>
-      <c r="C73" s="31">
-        <f>+((B74-B75)/B75)</f>
-        <v>-0.31892665326814518</v>
-      </c>
-    </row>
     <row r="74" spans="1:3">
       <c r="A74" s="26">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B74" s="25">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C74" s="31">
         <f>+((B75-B76)/B76)</f>
-        <v>-0.78753584478722383</v>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="26">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B75" s="25">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C75" s="31">
         <f>+((B76-B77)/B77)</f>
-        <v>1063.8095709311931</v>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="26">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B76" s="25">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C76" s="31">
-        <f>+((B81-B82)/B82)</f>
-        <v>82.182099964255912</v>
+        <f>+((B77-B78)/B78)</f>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="26">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B77" s="25">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C77" s="31">
-        <f t="shared" ref="C77:C100" si="2">+((B82-B83)/B83)</f>
-        <v>-0.96342609797465562</v>
+        <f>+((B82-B83)/B83)</f>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="26">
+        <v>46163</v>
+      </c>
+      <c r="B78" s="25">
+        <v>55.256117230000001</v>
+      </c>
+      <c r="C78" s="31">
+        <f t="shared" ref="C78:C101" si="2">+((B83-B84)/B84)</f>
+        <v>-0.96342609797465562</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="26">
         <v>46162</v>
       </c>
-      <c r="B78" s="25">
+      <c r="B79" s="25">
         <v>20356.468143580001</v>
       </c>
-      <c r="C78" s="31">
+      <c r="C79" s="31">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="26">
+    <row r="80" spans="1:3">
+      <c r="A80" s="26">
         <v>46161</v>
       </c>
-      <c r="B79" s="25">
+      <c r="B80" s="25">
         <v>72301.933723569993</v>
       </c>
-      <c r="C79" s="31">
+      <c r="C80" s="31">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="26">
+    <row r="81" spans="1:3">
+      <c r="A81" s="26">
         <v>46157</v>
       </c>
-      <c r="B80" s="25">
+      <c r="B81" s="25">
         <v>74209.813271849998</v>
       </c>
-      <c r="C80" s="31">
+      <c r="C81" s="31">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="26">
+    <row r="82" spans="1:3">
+      <c r="A82" s="26">
         <v>46156</v>
       </c>
-      <c r="B81" s="25">
+      <c r="B82" s="25">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C81" s="31">
+      <c r="C82" s="31">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="26">
+    <row r="83" spans="1:3">
+      <c r="A83" s="26">
         <v>46155</v>
       </c>
-      <c r="B82" s="25">
+      <c r="B83" s="25">
         <v>24.614867159999999</v>
       </c>
-      <c r="C82" s="31">
+      <c r="C83" s="31">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="26">
+    <row r="84" spans="1:3">
+      <c r="A84" s="26">
         <v>46154</v>
       </c>
-      <c r="B83" s="25">
+      <c r="B84" s="25">
         <v>673.01725538999995</v>
       </c>
-      <c r="C83" s="31">
+      <c r="C84" s="31">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="26">
+    <row r="85" spans="1:3">
+      <c r="A85" s="26">
         <v>46153</v>
       </c>
-      <c r="B84" s="25">
+      <c r="B85" s="25">
         <v>16068.49495319</v>
       </c>
-      <c r="C84" s="31">
+      <c r="C85" s="31">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="26">
+    <row r="86" spans="1:3">
+      <c r="A86" s="26">
         <v>46150</v>
       </c>
-      <c r="B85" s="25">
+      <c r="B86" s="25">
         <v>23652.710333340001</v>
       </c>
-      <c r="C85" s="31">
+      <c r="C86" s="31">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46149</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>131.99794839</v>
       </c>
-      <c r="C86" s="31">
+      <c r="C87" s="31">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="19">
+    <row r="88" spans="1:3">
+      <c r="A88" s="19">
         <v>46148</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B88" s="17">
         <v>745.52443231999996</v>
       </c>
-      <c r="C87" s="31">
+      <c r="C88" s="31">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="19">
+    <row r="89" spans="1:3">
+      <c r="A89" s="19">
         <v>46147</v>
       </c>
-      <c r="B88" s="17">
+      <c r="B89" s="17">
         <v>84317.802960360001</v>
       </c>
-      <c r="C88" s="31">
+      <c r="C89" s="31">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="19">
+    <row r="90" spans="1:3">
+      <c r="A90" s="19">
         <v>46146</v>
       </c>
-      <c r="B89" s="17">
+      <c r="B90" s="17">
         <v>49567.396050169998</v>
       </c>
-      <c r="C89" s="31">
+      <c r="C90" s="31">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="20">
+    <row r="91" spans="1:3">
+      <c r="A91" s="20">
         <v>46142</v>
       </c>
-      <c r="B90" s="17">
+      <c r="B91" s="17">
         <v>87352.396084139997</v>
       </c>
-      <c r="C90" s="31">
+      <c r="C91" s="31">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="20">
+    <row r="92" spans="1:3">
+      <c r="A92" s="20">
         <v>46141</v>
       </c>
-      <c r="B91" s="17">
+      <c r="B92" s="17">
         <v>28385.438679769999</v>
       </c>
-      <c r="C91" s="31">
+      <c r="C92" s="31">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="20">
+    <row r="93" spans="1:3">
+      <c r="A93" s="20">
         <v>46140</v>
       </c>
-      <c r="B92" s="17">
+      <c r="B93" s="17">
         <v>70324.097718699995</v>
       </c>
-      <c r="C92" s="31">
+      <c r="C93" s="31">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="20">
+    <row r="94" spans="1:3">
+      <c r="A94" s="20">
         <v>46139</v>
       </c>
-      <c r="B93" s="17">
+      <c r="B94" s="17">
         <v>40338.944788629997</v>
       </c>
-      <c r="C93" s="31">
+      <c r="C94" s="31">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="20">
+    <row r="95" spans="1:3">
+      <c r="A95" s="20">
         <v>46136</v>
       </c>
-      <c r="B94" s="17">
+      <c r="B95" s="17">
         <v>60973.651931649998</v>
       </c>
-      <c r="C94" s="31">
+      <c r="C95" s="31">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="20">
+    <row r="96" spans="1:3">
+      <c r="A96" s="20">
         <v>46135</v>
       </c>
-      <c r="B95" s="17">
+      <c r="B96" s="17">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C95" s="31">
+      <c r="C96" s="31">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="20">
+    <row r="97" spans="1:3">
+      <c r="A97" s="20">
         <v>46134</v>
       </c>
-      <c r="B96" s="17">
+      <c r="B97" s="17">
         <v>17251.00486529</v>
       </c>
-      <c r="C96" s="31">
+      <c r="C97" s="31">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="20">
+    <row r="98" spans="1:3">
+      <c r="A98" s="20">
         <v>46133</v>
       </c>
-      <c r="B97" s="17">
+      <c r="B98" s="17">
         <v>47981.781644150004</v>
       </c>
-      <c r="C97" s="31">
+      <c r="C98" s="31">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="20">
+    <row r="99" spans="1:3">
+      <c r="A99" s="20">
         <v>46132</v>
       </c>
-      <c r="B98" s="17">
+      <c r="B99" s="17">
         <v>51339.49161813</v>
       </c>
-      <c r="C98" s="31">
+      <c r="C99" s="31">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="20">
+    <row r="100" spans="1:3">
+      <c r="A100" s="20">
         <v>46129</v>
       </c>
-      <c r="B99" s="17">
+      <c r="B100" s="17">
         <v>17216.492596060001</v>
       </c>
-      <c r="C99" s="31">
+      <c r="C100" s="31">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="20">
+    <row r="101" spans="1:3">
+      <c r="A101" s="20">
         <v>46128</v>
       </c>
-      <c r="B100" s="17">
+      <c r="B101" s="17">
         <v>18.890111640000001</v>
       </c>
-      <c r="C100" s="31">
+      <c r="C101" s="31">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="20">
-        <v>46127</v>
-      </c>
-      <c r="B101" s="17">
-        <v>15.79809785</v>
-      </c>
-      <c r="C101" s="16">
-        <v>0</v>
-      </c>
-    </row>
     <row r="102" spans="1:3">
       <c r="A102" s="20">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B102" s="17">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C102" s="16">
         <v>0</v>
@@ -6553,10 +6574,10 @@
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="20">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B103" s="17">
-        <v>2475.4322626600001</v>
+        <v>16.215898760000002</v>
       </c>
       <c r="C103" s="16">
         <v>0</v>
@@ -6564,10 +6585,10 @@
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="20">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B104" s="17">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C104" s="16">
         <v>0</v>
@@ -6575,10 +6596,10 @@
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="20">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B105" s="17">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C105" s="16">
         <v>0</v>
@@ -6586,10 +6607,10 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="20">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B106" s="17">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C106" s="16">
         <v>0</v>
@@ -6597,41 +6618,52 @@
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="20">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B107" s="17">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C107" s="16">
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="20">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B108" s="17">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="20">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B109" s="17">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="20">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B110" s="17">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="20">
+        <v>46112</v>
+      </c>
+      <c r="B111" s="17">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="20">
         <v>46111</v>
       </c>
-      <c r="B111" s="17">
+      <c r="B112" s="17">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7727,7 +7759,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9328,7 +9360,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="32">
-        <f t="shared" ref="E76:E99" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E100" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="33">
@@ -9816,6 +9848,27 @@
       </c>
       <c r="F99" s="33">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" s="26">
+        <v>46276</v>
+      </c>
+      <c r="B100" s="27">
+        <v>13098</v>
+      </c>
+      <c r="C100" s="25">
+        <v>3</v>
+      </c>
+      <c r="D100" s="27">
+        <v>13101</v>
+      </c>
+      <c r="E100" s="32">
+        <f t="shared" si="4"/>
+        <v>1.8898740083994399E-2</v>
+      </c>
+      <c r="F100" s="33">
+        <v>1.89</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -1636,7 +1636,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1668,9 +1668,6 @@
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1710,6 +1707,10 @@
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="956">
     <cellStyle name="=C:\WINNT\SYSTEM32\COMMAND.COM" xfId="936"/>
@@ -2996,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -3563,1719 +3564,1739 @@
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="22">
+      <c r="A33" s="21">
         <v>46149</v>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="17">
         <v>32505.648000000001</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="18">
+      <c r="C33" s="20"/>
+      <c r="D33" s="17">
         <v>150</v>
       </c>
-      <c r="E33" s="21"/>
-      <c r="F33" s="18">
+      <c r="E33" s="20"/>
+      <c r="F33" s="17">
         <v>300</v>
       </c>
-      <c r="G33" s="21"/>
-      <c r="H33" s="18">
+      <c r="G33" s="20"/>
+      <c r="H33" s="17">
         <v>243.9</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="22">
+      <c r="A34" s="21">
         <v>46150</v>
       </c>
-      <c r="B34" s="18">
+      <c r="B34" s="17">
         <v>8103.3360000000002</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="18">
+      <c r="C34" s="20"/>
+      <c r="D34" s="17">
         <v>100</v>
       </c>
-      <c r="E34" s="21"/>
-      <c r="F34" s="18">
+      <c r="E34" s="20"/>
+      <c r="F34" s="17">
         <v>100</v>
       </c>
-      <c r="G34" s="21"/>
-      <c r="H34" s="18">
+      <c r="G34" s="20"/>
+      <c r="H34" s="17">
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="22">
+      <c r="A35" s="21">
         <v>46153</v>
       </c>
-      <c r="B35" s="18">
+      <c r="B35" s="17">
         <v>30219.955319000001</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="18">
+      <c r="C35" s="20"/>
+      <c r="D35" s="17">
         <v>100</v>
       </c>
-      <c r="E35" s="21"/>
-      <c r="F35" s="18">
+      <c r="E35" s="20"/>
+      <c r="F35" s="17">
         <v>110.06</v>
       </c>
-      <c r="G35" s="21"/>
-      <c r="H35" s="18">
+      <c r="G35" s="20"/>
+      <c r="H35" s="17">
         <v>109.71</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="22">
+      <c r="A36" s="21">
         <v>46154</v>
       </c>
-      <c r="B36" s="18">
-        <v>0</v>
-      </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="18">
-        <v>0</v>
-      </c>
-      <c r="E36" s="21"/>
-      <c r="F36" s="18">
-        <v>0</v>
-      </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="18">
+      <c r="B36" s="17">
+        <v>0</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="17">
+        <v>0</v>
+      </c>
+      <c r="E36" s="20"/>
+      <c r="F36" s="17">
+        <v>0</v>
+      </c>
+      <c r="G36" s="20"/>
+      <c r="H36" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="22">
+      <c r="A37" s="21">
         <v>46155</v>
       </c>
-      <c r="B37" s="18">
+      <c r="B37" s="17">
         <v>200</v>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="18">
+      <c r="C37" s="20"/>
+      <c r="D37" s="17">
         <v>100</v>
       </c>
-      <c r="E37" s="21"/>
-      <c r="F37" s="18">
+      <c r="E37" s="20"/>
+      <c r="F37" s="17">
         <v>100</v>
       </c>
-      <c r="G37" s="21"/>
-      <c r="H37" s="18">
+      <c r="G37" s="20"/>
+      <c r="H37" s="17">
         <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="22">
+      <c r="A38" s="21">
         <v>46156</v>
       </c>
-      <c r="B38" s="18">
-        <v>0</v>
-      </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="18">
-        <v>0</v>
-      </c>
-      <c r="E38" s="21"/>
-      <c r="F38" s="18">
-        <v>0</v>
-      </c>
-      <c r="G38" s="21"/>
-      <c r="H38" s="18">
+      <c r="B38" s="17">
+        <v>0</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="D38" s="17">
+        <v>0</v>
+      </c>
+      <c r="E38" s="20"/>
+      <c r="F38" s="17">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20"/>
+      <c r="H38" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="22">
+      <c r="A39" s="21">
         <v>46157</v>
       </c>
-      <c r="B39" s="18">
-        <v>0</v>
-      </c>
-      <c r="C39" s="29"/>
-      <c r="D39" s="18">
-        <v>0</v>
-      </c>
-      <c r="E39" s="30"/>
-      <c r="F39" s="18">
-        <v>0</v>
-      </c>
-      <c r="G39" s="30"/>
-      <c r="H39" s="18">
+      <c r="B39" s="17">
+        <v>0</v>
+      </c>
+      <c r="C39" s="28"/>
+      <c r="D39" s="17">
+        <v>0</v>
+      </c>
+      <c r="E39" s="29"/>
+      <c r="F39" s="17">
+        <v>0</v>
+      </c>
+      <c r="G39" s="29"/>
+      <c r="H39" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="22">
+      <c r="A40" s="21">
         <v>46161</v>
       </c>
-      <c r="B40" s="18">
-        <v>0</v>
-      </c>
-      <c r="D40" s="18">
-        <v>0</v>
-      </c>
-      <c r="E40" s="30"/>
-      <c r="F40" s="18">
-        <v>0</v>
-      </c>
-      <c r="G40" s="30"/>
-      <c r="H40" s="18">
+      <c r="B40" s="17">
+        <v>0</v>
+      </c>
+      <c r="D40" s="17">
+        <v>0</v>
+      </c>
+      <c r="E40" s="29"/>
+      <c r="F40" s="17">
+        <v>0</v>
+      </c>
+      <c r="G40" s="29"/>
+      <c r="H40" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="22">
+      <c r="A41" s="21">
         <v>46162</v>
       </c>
-      <c r="B41" s="18">
-        <v>0</v>
-      </c>
-      <c r="C41" s="25"/>
-      <c r="D41" s="18">
-        <v>0</v>
-      </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="18">
-        <v>0</v>
-      </c>
-      <c r="G41" s="25"/>
-      <c r="H41" s="18">
+      <c r="B41" s="17">
+        <v>0</v>
+      </c>
+      <c r="C41" s="24"/>
+      <c r="D41" s="17">
+        <v>0</v>
+      </c>
+      <c r="E41" s="24"/>
+      <c r="F41" s="17">
+        <v>0</v>
+      </c>
+      <c r="G41" s="24"/>
+      <c r="H41" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="22">
+      <c r="A42" s="21">
         <v>46163</v>
       </c>
-      <c r="B42" s="18">
+      <c r="B42" s="17">
         <v>5006.6000000000004</v>
       </c>
-      <c r="C42" s="21"/>
-      <c r="D42" s="18">
+      <c r="C42" s="20"/>
+      <c r="D42" s="17">
         <v>120</v>
       </c>
-      <c r="E42" s="21"/>
-      <c r="F42" s="18">
+      <c r="E42" s="20"/>
+      <c r="F42" s="17">
         <v>120</v>
       </c>
-      <c r="G42" s="21"/>
-      <c r="H42" s="18">
+      <c r="G42" s="20"/>
+      <c r="H42" s="17">
         <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="22">
+      <c r="A43" s="21">
         <v>46164</v>
       </c>
-      <c r="B43" s="18">
-        <v>0</v>
-      </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="18">
-        <v>0</v>
-      </c>
-      <c r="E43" s="21"/>
-      <c r="F43" s="18">
-        <v>0</v>
-      </c>
-      <c r="G43" s="21"/>
-      <c r="H43" s="18">
+      <c r="B43" s="17">
+        <v>0</v>
+      </c>
+      <c r="C43" s="20"/>
+      <c r="D43" s="17">
+        <v>0</v>
+      </c>
+      <c r="E43" s="20"/>
+      <c r="F43" s="17">
+        <v>0</v>
+      </c>
+      <c r="G43" s="20"/>
+      <c r="H43" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="22">
+      <c r="A44" s="21">
         <v>46167</v>
       </c>
-      <c r="B44" s="18">
-        <v>0</v>
-      </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="18">
-        <v>0</v>
-      </c>
-      <c r="E44" s="21"/>
-      <c r="F44" s="18">
-        <v>0</v>
-      </c>
-      <c r="G44" s="21"/>
-      <c r="H44" s="18">
+      <c r="B44" s="17">
+        <v>0</v>
+      </c>
+      <c r="C44" s="20"/>
+      <c r="D44" s="17">
+        <v>0</v>
+      </c>
+      <c r="E44" s="20"/>
+      <c r="F44" s="17">
+        <v>0</v>
+      </c>
+      <c r="G44" s="20"/>
+      <c r="H44" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="22">
+      <c r="A45" s="21">
         <v>46168</v>
       </c>
-      <c r="B45" s="18">
-        <v>0</v>
-      </c>
-      <c r="C45" s="21"/>
-      <c r="D45" s="18">
-        <v>0</v>
-      </c>
-      <c r="E45" s="21"/>
-      <c r="F45" s="18">
-        <v>0</v>
-      </c>
-      <c r="G45" s="21"/>
-      <c r="H45" s="18">
+      <c r="B45" s="17">
+        <v>0</v>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="17">
+        <v>0</v>
+      </c>
+      <c r="E45" s="20"/>
+      <c r="F45" s="17">
+        <v>0</v>
+      </c>
+      <c r="G45" s="20"/>
+      <c r="H45" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="22">
+      <c r="A46" s="21">
         <v>46169</v>
       </c>
-      <c r="B46" s="18">
+      <c r="B46" s="17">
         <v>51256.235569999997</v>
       </c>
-      <c r="C46" s="21"/>
-      <c r="D46" s="18">
+      <c r="C46" s="20"/>
+      <c r="D46" s="17">
         <v>250</v>
       </c>
-      <c r="E46" s="21"/>
-      <c r="F46" s="18">
+      <c r="E46" s="20"/>
+      <c r="F46" s="17">
         <v>300.02</v>
       </c>
-      <c r="G46" s="21"/>
-      <c r="H46" s="18">
+      <c r="G46" s="20"/>
+      <c r="H46" s="17">
         <v>273.24</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="22">
+      <c r="A47" s="21">
         <v>46170</v>
       </c>
-      <c r="B47" s="18">
+      <c r="B47" s="17">
         <v>38032.045118000002</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="18">
+      <c r="C47" s="20"/>
+      <c r="D47" s="17">
         <v>300</v>
       </c>
-      <c r="E47" s="21"/>
-      <c r="F47" s="18">
+      <c r="E47" s="20"/>
+      <c r="F47" s="17">
         <v>330</v>
       </c>
-      <c r="G47" s="21"/>
-      <c r="H47" s="18">
+      <c r="G47" s="20"/>
+      <c r="H47" s="17">
         <v>311.49</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="22">
+      <c r="A48" s="21">
         <v>46171</v>
       </c>
-      <c r="B48" s="18">
+      <c r="B48" s="17">
         <v>45546.404509</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="18">
+      <c r="C48" s="20"/>
+      <c r="D48" s="17">
         <v>100</v>
       </c>
-      <c r="E48" s="21"/>
-      <c r="F48" s="18">
+      <c r="E48" s="20"/>
+      <c r="F48" s="17">
         <v>120</v>
       </c>
-      <c r="G48" s="21"/>
-      <c r="H48" s="18">
+      <c r="G48" s="20"/>
+      <c r="H48" s="17">
         <v>107.95</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="22">
+      <c r="A49" s="21">
         <v>46174</v>
       </c>
-      <c r="B49" s="18">
-        <v>0</v>
-      </c>
-      <c r="C49" s="21"/>
-      <c r="D49" s="18">
-        <v>0</v>
-      </c>
-      <c r="E49" s="21"/>
-      <c r="F49" s="18">
-        <v>0</v>
-      </c>
-      <c r="G49" s="21"/>
-      <c r="H49" s="18">
+      <c r="B49" s="17">
+        <v>0</v>
+      </c>
+      <c r="C49" s="20"/>
+      <c r="D49" s="17">
+        <v>0</v>
+      </c>
+      <c r="E49" s="20"/>
+      <c r="F49" s="17">
+        <v>0</v>
+      </c>
+      <c r="G49" s="20"/>
+      <c r="H49" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="22">
+      <c r="A50" s="21">
         <v>46175</v>
       </c>
-      <c r="B50" s="18">
-        <v>0</v>
-      </c>
-      <c r="C50" s="21"/>
-      <c r="D50" s="18">
-        <v>0</v>
-      </c>
-      <c r="E50" s="21"/>
-      <c r="F50" s="18">
-        <v>0</v>
-      </c>
-      <c r="G50" s="21"/>
-      <c r="H50" s="18">
+      <c r="B50" s="17">
+        <v>0</v>
+      </c>
+      <c r="C50" s="20"/>
+      <c r="D50" s="17">
+        <v>0</v>
+      </c>
+      <c r="E50" s="20"/>
+      <c r="F50" s="17">
+        <v>0</v>
+      </c>
+      <c r="G50" s="20"/>
+      <c r="H50" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="22">
+      <c r="A51" s="21">
         <v>46176</v>
       </c>
-      <c r="B51" s="18">
-        <v>0</v>
-      </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="18">
-        <v>0</v>
-      </c>
-      <c r="E51" s="21"/>
-      <c r="F51" s="18">
-        <v>0</v>
-      </c>
-      <c r="G51" s="21"/>
-      <c r="H51" s="18">
+      <c r="B51" s="17">
+        <v>0</v>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="17">
+        <v>0</v>
+      </c>
+      <c r="E51" s="20"/>
+      <c r="F51" s="17">
+        <v>0</v>
+      </c>
+      <c r="G51" s="20"/>
+      <c r="H51" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="22">
+      <c r="A52" s="21">
         <v>46177</v>
       </c>
-      <c r="B52" s="18">
+      <c r="B52" s="17">
         <v>200</v>
       </c>
-      <c r="C52" s="21"/>
-      <c r="D52" s="18">
+      <c r="C52" s="20"/>
+      <c r="D52" s="17">
         <v>150</v>
       </c>
-      <c r="E52" s="21"/>
-      <c r="F52" s="18">
+      <c r="E52" s="20"/>
+      <c r="F52" s="17">
         <v>150</v>
       </c>
-      <c r="G52" s="21"/>
-      <c r="H52" s="18">
+      <c r="G52" s="20"/>
+      <c r="H52" s="17">
         <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="22">
+      <c r="A53" s="21">
         <v>46178</v>
       </c>
-      <c r="B53" s="18">
+      <c r="B53" s="17">
         <v>10878.022664</v>
       </c>
-      <c r="C53" s="21"/>
-      <c r="D53" s="18">
+      <c r="C53" s="20"/>
+      <c r="D53" s="17">
         <v>50</v>
       </c>
-      <c r="E53" s="21"/>
-      <c r="F53" s="18">
+      <c r="E53" s="20"/>
+      <c r="F53" s="17">
         <v>50</v>
       </c>
-      <c r="G53" s="21"/>
-      <c r="H53" s="18">
+      <c r="G53" s="20"/>
+      <c r="H53" s="17">
         <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="22">
+      <c r="A54" s="21">
         <v>46182</v>
       </c>
-      <c r="B54" s="18">
-        <v>0</v>
-      </c>
-      <c r="C54" s="21"/>
-      <c r="D54" s="18">
-        <v>0</v>
-      </c>
-      <c r="E54" s="21"/>
-      <c r="F54" s="18">
-        <v>0</v>
-      </c>
-      <c r="G54" s="21"/>
-      <c r="H54" s="18">
+      <c r="B54" s="17">
+        <v>0</v>
+      </c>
+      <c r="C54" s="20"/>
+      <c r="D54" s="17">
+        <v>0</v>
+      </c>
+      <c r="E54" s="20"/>
+      <c r="F54" s="17">
+        <v>0</v>
+      </c>
+      <c r="G54" s="20"/>
+      <c r="H54" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="22">
+      <c r="A55" s="21">
         <v>46183</v>
       </c>
-      <c r="B55" s="18">
+      <c r="B55" s="17">
         <v>67565.465119999993</v>
       </c>
-      <c r="C55" s="21"/>
-      <c r="D55" s="18">
+      <c r="C55" s="20"/>
+      <c r="D55" s="17">
         <v>250</v>
       </c>
-      <c r="E55" s="21"/>
-      <c r="F55" s="18">
+      <c r="E55" s="20"/>
+      <c r="F55" s="17">
         <v>320</v>
       </c>
-      <c r="G55" s="21"/>
-      <c r="H55" s="18">
+      <c r="G55" s="20"/>
+      <c r="H55" s="17">
         <v>294.99</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="22">
+      <c r="A56" s="21">
         <v>46184</v>
       </c>
-      <c r="B56" s="18">
-        <v>0</v>
-      </c>
-      <c r="C56" s="21"/>
-      <c r="D56" s="18">
-        <v>0</v>
-      </c>
-      <c r="E56" s="21"/>
-      <c r="F56" s="18">
-        <v>0</v>
-      </c>
-      <c r="G56" s="21"/>
-      <c r="H56" s="18">
+      <c r="B56" s="17">
+        <v>0</v>
+      </c>
+      <c r="C56" s="20"/>
+      <c r="D56" s="17">
+        <v>0</v>
+      </c>
+      <c r="E56" s="20"/>
+      <c r="F56" s="17">
+        <v>0</v>
+      </c>
+      <c r="G56" s="20"/>
+      <c r="H56" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="22">
+      <c r="A57" s="21">
         <v>46185</v>
       </c>
-      <c r="B57" s="18">
+      <c r="B57" s="17">
         <v>40962.766997999999</v>
       </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="18">
+      <c r="C57" s="20"/>
+      <c r="D57" s="17">
         <v>110</v>
       </c>
-      <c r="E57" s="21"/>
-      <c r="F57" s="18">
+      <c r="E57" s="20"/>
+      <c r="F57" s="17">
         <v>120</v>
       </c>
-      <c r="G57" s="21"/>
-      <c r="H57" s="18">
+      <c r="G57" s="20"/>
+      <c r="H57" s="17">
         <v>110.87</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="22">
+      <c r="A58" s="21">
         <v>46188</v>
       </c>
-      <c r="B58" s="18">
+      <c r="B58" s="17">
         <v>13248.755665999999</v>
       </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="18">
+      <c r="C58" s="20"/>
+      <c r="D58" s="17">
         <v>290</v>
       </c>
-      <c r="E58" s="21"/>
-      <c r="F58" s="18">
+      <c r="E58" s="20"/>
+      <c r="F58" s="17">
         <v>330</v>
       </c>
-      <c r="G58" s="21"/>
-      <c r="H58" s="18">
+      <c r="G58" s="20"/>
+      <c r="H58" s="17">
         <v>300.5</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="22">
+      <c r="A59" s="21">
         <v>46189</v>
       </c>
-      <c r="B59" s="18">
+      <c r="B59" s="17">
         <v>15884.312540000001</v>
       </c>
-      <c r="C59" s="21"/>
-      <c r="D59" s="18">
+      <c r="C59" s="20"/>
+      <c r="D59" s="17">
         <v>335</v>
       </c>
-      <c r="E59" s="21"/>
-      <c r="F59" s="18">
+      <c r="E59" s="20"/>
+      <c r="F59" s="17">
         <v>340</v>
       </c>
-      <c r="G59" s="21"/>
-      <c r="H59" s="18">
+      <c r="G59" s="20"/>
+      <c r="H59" s="17">
         <v>335.1</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="22">
+      <c r="A60" s="21">
         <v>46190</v>
       </c>
-      <c r="B60" s="18">
+      <c r="B60" s="17">
         <v>51428.024998000001</v>
       </c>
-      <c r="C60" s="21"/>
-      <c r="D60" s="18">
+      <c r="C60" s="20"/>
+      <c r="D60" s="17">
         <v>300</v>
       </c>
-      <c r="E60" s="21"/>
-      <c r="F60" s="18">
+      <c r="E60" s="20"/>
+      <c r="F60" s="17">
         <v>340</v>
       </c>
-      <c r="G60" s="21"/>
-      <c r="H60" s="18">
+      <c r="G60" s="20"/>
+      <c r="H60" s="17">
         <v>314.18</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="22">
+      <c r="A61" s="21">
         <v>46191</v>
       </c>
-      <c r="B61" s="18">
+      <c r="B61" s="17">
         <v>21477.350433</v>
       </c>
-      <c r="C61" s="21"/>
-      <c r="D61" s="18">
+      <c r="C61" s="20"/>
+      <c r="D61" s="17">
         <v>350</v>
       </c>
-      <c r="E61" s="21"/>
-      <c r="F61" s="18">
+      <c r="E61" s="20"/>
+      <c r="F61" s="17">
         <v>390</v>
       </c>
-      <c r="G61" s="21"/>
-      <c r="H61" s="18">
+      <c r="G61" s="20"/>
+      <c r="H61" s="17">
         <v>354.17</v>
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="22">
+      <c r="A62" s="21">
         <v>46192</v>
       </c>
-      <c r="B62" s="18">
+      <c r="B62" s="17">
         <v>19544.702092</v>
       </c>
-      <c r="C62" s="21"/>
-      <c r="D62" s="18">
+      <c r="C62" s="20"/>
+      <c r="D62" s="17">
         <v>120</v>
       </c>
-      <c r="E62" s="21"/>
-      <c r="F62" s="18">
+      <c r="E62" s="20"/>
+      <c r="F62" s="17">
         <v>125.02</v>
       </c>
-      <c r="G62" s="21"/>
-      <c r="H62" s="18">
+      <c r="G62" s="20"/>
+      <c r="H62" s="17">
         <v>121.88</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="22">
+      <c r="A63" s="21">
         <v>46195</v>
       </c>
-      <c r="B63" s="18">
+      <c r="B63" s="17">
         <v>1676.4307650000001</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="18">
+      <c r="C63" s="20"/>
+      <c r="D63" s="17">
         <v>350</v>
       </c>
-      <c r="E63" s="21"/>
-      <c r="F63" s="18">
+      <c r="E63" s="20"/>
+      <c r="F63" s="17">
         <v>360</v>
       </c>
-      <c r="G63" s="21"/>
-      <c r="H63" s="18">
+      <c r="G63" s="20"/>
+      <c r="H63" s="17">
         <v>351.2</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="22">
+      <c r="A64" s="21">
         <v>46196</v>
       </c>
-      <c r="B64" s="18">
+      <c r="B64" s="17">
         <v>4776.4754999999996</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="18">
+      <c r="C64" s="20"/>
+      <c r="D64" s="17">
         <v>140</v>
       </c>
-      <c r="E64" s="21"/>
-      <c r="F64" s="18">
+      <c r="E64" s="20"/>
+      <c r="F64" s="17">
         <v>350</v>
       </c>
-      <c r="G64" s="21"/>
-      <c r="H64" s="18">
+      <c r="G64" s="20"/>
+      <c r="H64" s="17">
         <v>184.42</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="22">
+      <c r="A65" s="21">
         <v>46198</v>
       </c>
-      <c r="B65" s="18">
+      <c r="B65" s="17">
         <v>1740</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="18">
+      <c r="C65" s="20"/>
+      <c r="D65" s="17">
         <v>120</v>
       </c>
-      <c r="E65" s="21"/>
-      <c r="F65" s="18">
+      <c r="E65" s="20"/>
+      <c r="F65" s="17">
         <v>300</v>
       </c>
-      <c r="G65" s="21"/>
-      <c r="H65" s="18">
+      <c r="G65" s="20"/>
+      <c r="H65" s="17">
         <v>282.06896551724139</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="22">
+      <c r="A66" s="21">
         <v>46203</v>
       </c>
-      <c r="B66" s="18">
+      <c r="B66" s="17">
         <v>1904.22222222</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="18">
+      <c r="C66" s="20"/>
+      <c r="D66" s="17">
         <v>0.01</v>
       </c>
-      <c r="E66" s="21"/>
-      <c r="F66" s="18">
+      <c r="E66" s="20"/>
+      <c r="F66" s="17">
         <v>0.01</v>
       </c>
-      <c r="G66" s="21"/>
-      <c r="H66" s="18">
+      <c r="G66" s="20"/>
+      <c r="H66" s="17">
         <v>0.01</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="22">
+      <c r="A67" s="21">
         <v>46204</v>
       </c>
-      <c r="B67" s="18">
-        <v>0</v>
-      </c>
-      <c r="C67" s="21"/>
-      <c r="D67" s="18">
-        <v>0</v>
-      </c>
-      <c r="E67" s="21"/>
-      <c r="F67" s="18">
-        <v>0</v>
-      </c>
-      <c r="G67" s="21"/>
-      <c r="H67" s="18">
+      <c r="B67" s="17">
+        <v>0</v>
+      </c>
+      <c r="C67" s="20"/>
+      <c r="D67" s="17">
+        <v>0</v>
+      </c>
+      <c r="E67" s="20"/>
+      <c r="F67" s="17">
+        <v>0</v>
+      </c>
+      <c r="G67" s="20"/>
+      <c r="H67" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="22">
+      <c r="A68" s="21">
         <v>46205</v>
       </c>
-      <c r="B68" s="18">
+      <c r="B68" s="17">
         <v>2461.9</v>
       </c>
-      <c r="C68" s="21"/>
-      <c r="D68" s="18">
+      <c r="C68" s="20"/>
+      <c r="D68" s="17">
         <v>110</v>
       </c>
-      <c r="E68" s="21"/>
-      <c r="F68" s="18">
+      <c r="E68" s="20"/>
+      <c r="F68" s="17">
         <v>135</v>
       </c>
-      <c r="G68" s="21"/>
-      <c r="H68" s="18">
+      <c r="G68" s="20"/>
+      <c r="H68" s="17">
         <v>131.66</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="22">
+      <c r="A69" s="21">
         <v>46206</v>
       </c>
-      <c r="B69" s="18">
+      <c r="B69" s="17">
         <v>279.5</v>
       </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="18">
+      <c r="C69" s="20"/>
+      <c r="D69" s="17">
         <v>5</v>
       </c>
-      <c r="E69" s="21"/>
-      <c r="F69" s="18">
+      <c r="E69" s="20"/>
+      <c r="F69" s="17">
         <v>60</v>
       </c>
-      <c r="G69" s="21"/>
-      <c r="H69" s="18">
+      <c r="G69" s="20"/>
+      <c r="H69" s="17">
         <v>54.19</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="22">
+      <c r="A70" s="21">
         <v>46209</v>
       </c>
-      <c r="B70" s="18">
-        <v>0</v>
-      </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="18">
-        <v>0</v>
-      </c>
-      <c r="E70" s="21"/>
-      <c r="F70" s="18">
-        <v>0</v>
-      </c>
-      <c r="G70" s="21"/>
-      <c r="H70" s="18">
+      <c r="B70" s="17">
+        <v>0</v>
+      </c>
+      <c r="C70" s="20"/>
+      <c r="D70" s="17">
+        <v>0</v>
+      </c>
+      <c r="E70" s="20"/>
+      <c r="F70" s="17">
+        <v>0</v>
+      </c>
+      <c r="G70" s="20"/>
+      <c r="H70" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="22">
+      <c r="A71" s="21">
         <v>46210</v>
       </c>
-      <c r="B71" s="18">
-        <v>0</v>
-      </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="18">
-        <v>0</v>
-      </c>
-      <c r="E71" s="21"/>
-      <c r="F71" s="18">
-        <v>0</v>
-      </c>
-      <c r="G71" s="21"/>
-      <c r="H71" s="18">
+      <c r="B71" s="17">
+        <v>0</v>
+      </c>
+      <c r="C71" s="20"/>
+      <c r="D71" s="17">
+        <v>0</v>
+      </c>
+      <c r="E71" s="20"/>
+      <c r="F71" s="17">
+        <v>0</v>
+      </c>
+      <c r="G71" s="20"/>
+      <c r="H71" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="22">
+      <c r="A72" s="21">
         <v>46211</v>
       </c>
-      <c r="B72" s="18">
-        <v>0</v>
-      </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="18">
-        <v>0</v>
-      </c>
-      <c r="E72" s="21"/>
-      <c r="F72" s="18">
-        <v>0</v>
-      </c>
-      <c r="G72" s="21"/>
-      <c r="H72" s="18">
+      <c r="B72" s="17">
+        <v>0</v>
+      </c>
+      <c r="C72" s="20"/>
+      <c r="D72" s="17">
+        <v>0</v>
+      </c>
+      <c r="E72" s="20"/>
+      <c r="F72" s="17">
+        <v>0</v>
+      </c>
+      <c r="G72" s="20"/>
+      <c r="H72" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="22">
+      <c r="A73" s="21">
         <v>46212</v>
       </c>
-      <c r="B73" s="18">
+      <c r="B73" s="17">
         <v>3000</v>
       </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="18">
+      <c r="C73" s="20"/>
+      <c r="D73" s="17">
         <v>1</v>
       </c>
-      <c r="E73" s="21"/>
-      <c r="F73" s="18">
+      <c r="E73" s="20"/>
+      <c r="F73" s="17">
         <v>1</v>
       </c>
-      <c r="G73" s="21"/>
-      <c r="H73" s="18">
+      <c r="G73" s="20"/>
+      <c r="H73" s="17">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="22">
+      <c r="A74" s="21">
         <v>46213</v>
       </c>
-      <c r="B74" s="18">
-        <v>0</v>
-      </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="18">
-        <v>0</v>
-      </c>
-      <c r="E74" s="21"/>
-      <c r="F74" s="18">
-        <v>0</v>
-      </c>
-      <c r="G74" s="21"/>
-      <c r="H74" s="18">
+      <c r="B74" s="17">
+        <v>0</v>
+      </c>
+      <c r="C74" s="20"/>
+      <c r="D74" s="17">
+        <v>0</v>
+      </c>
+      <c r="E74" s="20"/>
+      <c r="F74" s="17">
+        <v>0</v>
+      </c>
+      <c r="G74" s="20"/>
+      <c r="H74" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="22">
+      <c r="A75" s="21">
         <v>46216</v>
       </c>
-      <c r="B75" s="18">
-        <v>0</v>
-      </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="18">
-        <v>0</v>
-      </c>
-      <c r="E75" s="21"/>
-      <c r="F75" s="18">
-        <v>0</v>
-      </c>
-      <c r="G75" s="21"/>
-      <c r="H75" s="18">
+      <c r="B75" s="17">
+        <v>0</v>
+      </c>
+      <c r="C75" s="20"/>
+      <c r="D75" s="17">
+        <v>0</v>
+      </c>
+      <c r="E75" s="20"/>
+      <c r="F75" s="17">
+        <v>0</v>
+      </c>
+      <c r="G75" s="20"/>
+      <c r="H75" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="22">
+      <c r="A76" s="21">
         <v>46217</v>
       </c>
-      <c r="B76" s="18">
-        <v>0</v>
-      </c>
-      <c r="C76" s="21"/>
-      <c r="D76" s="18">
-        <v>0</v>
-      </c>
-      <c r="E76" s="21"/>
-      <c r="F76" s="18">
-        <v>0</v>
-      </c>
-      <c r="G76" s="21"/>
-      <c r="H76" s="18">
+      <c r="B76" s="17">
+        <v>0</v>
+      </c>
+      <c r="C76" s="20"/>
+      <c r="D76" s="17">
+        <v>0</v>
+      </c>
+      <c r="E76" s="20"/>
+      <c r="F76" s="17">
+        <v>0</v>
+      </c>
+      <c r="G76" s="20"/>
+      <c r="H76" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="22">
+      <c r="A77" s="21">
         <v>46218</v>
       </c>
-      <c r="B77" s="18">
+      <c r="B77" s="17">
         <v>217.41</v>
       </c>
-      <c r="C77" s="21"/>
-      <c r="D77" s="18">
+      <c r="C77" s="20"/>
+      <c r="D77" s="17">
         <v>50</v>
       </c>
-      <c r="E77" s="21"/>
-      <c r="F77" s="18">
+      <c r="E77" s="20"/>
+      <c r="F77" s="17">
         <v>200</v>
       </c>
-      <c r="G77" s="21"/>
-      <c r="H77" s="18">
+      <c r="G77" s="20"/>
+      <c r="H77" s="17">
         <v>165.7</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="22">
+      <c r="A78" s="21">
         <v>46219</v>
       </c>
-      <c r="B78" s="18">
+      <c r="B78" s="17">
         <v>517.9</v>
       </c>
-      <c r="C78" s="21"/>
-      <c r="D78" s="18">
+      <c r="C78" s="20"/>
+      <c r="D78" s="17">
         <v>50</v>
       </c>
-      <c r="E78" s="21"/>
-      <c r="F78" s="18">
+      <c r="E78" s="20"/>
+      <c r="F78" s="17">
         <v>120</v>
       </c>
-      <c r="G78" s="21"/>
-      <c r="H78" s="18">
+      <c r="G78" s="20"/>
+      <c r="H78" s="17">
         <v>119.03</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="22">
+      <c r="A79" s="21">
         <v>46190</v>
       </c>
-      <c r="B79" s="18">
+      <c r="B79" s="17">
         <v>31613.569407999999</v>
       </c>
-      <c r="C79" s="21"/>
-      <c r="D79" s="18">
+      <c r="C79" s="20"/>
+      <c r="D79" s="17">
         <v>25</v>
       </c>
-      <c r="E79" s="21"/>
-      <c r="F79" s="18">
+      <c r="E79" s="20"/>
+      <c r="F79" s="17">
         <v>85</v>
       </c>
-      <c r="G79" s="21"/>
-      <c r="H79" s="18">
+      <c r="G79" s="20"/>
+      <c r="H79" s="17">
         <v>80.14</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="22">
+      <c r="A80" s="21">
         <v>46224</v>
       </c>
-      <c r="B80" s="18">
+      <c r="B80" s="17">
         <v>880</v>
       </c>
-      <c r="C80" s="21"/>
-      <c r="D80" s="18">
+      <c r="C80" s="20"/>
+      <c r="D80" s="17">
         <v>150</v>
       </c>
-      <c r="E80" s="21"/>
-      <c r="F80" s="18">
+      <c r="E80" s="20"/>
+      <c r="F80" s="17">
         <v>200</v>
       </c>
-      <c r="G80" s="21"/>
-      <c r="H80" s="18">
+      <c r="G80" s="20"/>
+      <c r="H80" s="17">
         <v>184.77</v>
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="22">
+      <c r="A81" s="21">
         <v>46225</v>
       </c>
-      <c r="B81" s="18">
-        <v>0</v>
-      </c>
-      <c r="C81" s="21"/>
-      <c r="D81" s="18">
-        <v>0</v>
-      </c>
-      <c r="E81" s="21"/>
-      <c r="F81" s="18">
-        <v>0</v>
-      </c>
-      <c r="G81" s="21"/>
-      <c r="H81" s="18">
+      <c r="B81" s="17">
+        <v>0</v>
+      </c>
+      <c r="C81" s="20"/>
+      <c r="D81" s="17">
+        <v>0</v>
+      </c>
+      <c r="E81" s="20"/>
+      <c r="F81" s="17">
+        <v>0</v>
+      </c>
+      <c r="G81" s="20"/>
+      <c r="H81" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="22">
+      <c r="A82" s="21">
         <v>46226</v>
       </c>
-      <c r="B82" s="18">
-        <v>0</v>
-      </c>
-      <c r="C82" s="21"/>
-      <c r="D82" s="18">
-        <v>0</v>
-      </c>
-      <c r="E82" s="21"/>
-      <c r="F82" s="18">
-        <v>0</v>
-      </c>
-      <c r="G82" s="21"/>
-      <c r="H82" s="18">
+      <c r="B82" s="17">
+        <v>0</v>
+      </c>
+      <c r="C82" s="20"/>
+      <c r="D82" s="17">
+        <v>0</v>
+      </c>
+      <c r="E82" s="20"/>
+      <c r="F82" s="17">
+        <v>0</v>
+      </c>
+      <c r="G82" s="20"/>
+      <c r="H82" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="22">
+      <c r="A83" s="21">
         <v>46230</v>
       </c>
-      <c r="B83" s="18">
-        <v>0</v>
-      </c>
-      <c r="C83" s="21"/>
-      <c r="D83" s="18">
-        <v>0</v>
-      </c>
-      <c r="E83" s="21"/>
-      <c r="F83" s="18">
-        <v>0</v>
-      </c>
-      <c r="G83" s="21"/>
-      <c r="H83" s="18">
+      <c r="B83" s="17">
+        <v>0</v>
+      </c>
+      <c r="C83" s="20"/>
+      <c r="D83" s="17">
+        <v>0</v>
+      </c>
+      <c r="E83" s="20"/>
+      <c r="F83" s="17">
+        <v>0</v>
+      </c>
+      <c r="G83" s="20"/>
+      <c r="H83" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="22">
+      <c r="A84" s="21">
         <v>46231</v>
       </c>
-      <c r="B84" s="18">
+      <c r="B84" s="17">
         <v>230</v>
       </c>
-      <c r="C84" s="21"/>
-      <c r="D84" s="18">
+      <c r="C84" s="20"/>
+      <c r="D84" s="17">
         <v>90</v>
       </c>
-      <c r="E84" s="21"/>
-      <c r="F84" s="18">
+      <c r="E84" s="20"/>
+      <c r="F84" s="17">
         <v>100</v>
       </c>
-      <c r="G84" s="21"/>
-      <c r="H84" s="18">
+      <c r="G84" s="20"/>
+      <c r="H84" s="17">
         <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="22">
+      <c r="A85" s="21">
         <v>46232</v>
       </c>
-      <c r="B85" s="18">
+      <c r="B85" s="17">
         <v>20</v>
       </c>
-      <c r="C85" s="21"/>
-      <c r="D85" s="18">
+      <c r="C85" s="20"/>
+      <c r="D85" s="17">
         <v>100</v>
       </c>
-      <c r="E85" s="21"/>
-      <c r="F85" s="18">
+      <c r="E85" s="20"/>
+      <c r="F85" s="17">
         <v>100</v>
       </c>
-      <c r="G85" s="21"/>
-      <c r="H85" s="18">
+      <c r="G85" s="20"/>
+      <c r="H85" s="17">
         <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="22">
+      <c r="A86" s="21">
         <v>46233</v>
       </c>
-      <c r="B86" s="18">
+      <c r="B86" s="17">
         <v>280</v>
       </c>
-      <c r="C86" s="21"/>
-      <c r="D86" s="18">
+      <c r="C86" s="20"/>
+      <c r="D86" s="17">
         <v>40</v>
       </c>
-      <c r="E86" s="21"/>
-      <c r="F86" s="18">
+      <c r="E86" s="20"/>
+      <c r="F86" s="17">
         <v>100</v>
       </c>
-      <c r="G86" s="21"/>
-      <c r="H86" s="18">
+      <c r="G86" s="20"/>
+      <c r="H86" s="17">
         <v>66.430000000000007</v>
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="22">
+      <c r="A87" s="21">
         <v>46234</v>
       </c>
-      <c r="B87" s="18">
+      <c r="B87" s="17">
         <v>60</v>
       </c>
-      <c r="C87" s="21"/>
-      <c r="D87" s="18">
+      <c r="C87" s="20"/>
+      <c r="D87" s="17">
         <v>40</v>
       </c>
-      <c r="E87" s="21"/>
-      <c r="F87" s="18">
+      <c r="E87" s="20"/>
+      <c r="F87" s="17">
         <v>40</v>
       </c>
-      <c r="G87" s="21"/>
-      <c r="H87" s="18">
+      <c r="G87" s="20"/>
+      <c r="H87" s="17">
         <v>40</v>
       </c>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="22">
+      <c r="A88" s="21">
         <v>46237</v>
       </c>
-      <c r="B88" s="18">
+      <c r="B88" s="17">
         <v>1500</v>
       </c>
-      <c r="C88" s="21"/>
-      <c r="D88" s="18">
+      <c r="C88" s="20"/>
+      <c r="D88" s="17">
         <v>110</v>
       </c>
-      <c r="E88" s="21"/>
-      <c r="F88" s="18">
+      <c r="E88" s="20"/>
+      <c r="F88" s="17">
         <v>110</v>
       </c>
-      <c r="G88" s="21"/>
-      <c r="H88" s="18">
+      <c r="G88" s="20"/>
+      <c r="H88" s="17">
         <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="22">
+      <c r="A89" s="21">
         <v>46238</v>
       </c>
-      <c r="B89" s="18">
-        <v>0</v>
-      </c>
-      <c r="C89" s="21"/>
-      <c r="D89" s="18">
-        <v>0</v>
-      </c>
-      <c r="E89" s="21"/>
-      <c r="F89" s="18">
-        <v>0</v>
-      </c>
-      <c r="G89" s="21"/>
-      <c r="H89" s="18">
+      <c r="B89" s="17">
+        <v>0</v>
+      </c>
+      <c r="C89" s="20"/>
+      <c r="D89" s="17">
+        <v>0</v>
+      </c>
+      <c r="E89" s="20"/>
+      <c r="F89" s="17">
+        <v>0</v>
+      </c>
+      <c r="G89" s="20"/>
+      <c r="H89" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="22">
+      <c r="A90" s="21">
         <v>46239</v>
       </c>
-      <c r="B90" s="18">
-        <v>0</v>
-      </c>
-      <c r="C90" s="21"/>
-      <c r="D90" s="18">
-        <v>0</v>
-      </c>
-      <c r="E90" s="21"/>
-      <c r="F90" s="18">
-        <v>0</v>
-      </c>
-      <c r="G90" s="21"/>
-      <c r="H90" s="18">
+      <c r="B90" s="17">
+        <v>0</v>
+      </c>
+      <c r="C90" s="20"/>
+      <c r="D90" s="17">
+        <v>0</v>
+      </c>
+      <c r="E90" s="20"/>
+      <c r="F90" s="17">
+        <v>0</v>
+      </c>
+      <c r="G90" s="20"/>
+      <c r="H90" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="22">
+      <c r="A91" s="21">
         <v>46240</v>
       </c>
-      <c r="B91" s="18">
-        <v>0</v>
-      </c>
-      <c r="C91" s="21"/>
-      <c r="D91" s="18">
-        <v>0</v>
-      </c>
-      <c r="E91" s="21"/>
-      <c r="F91" s="18">
-        <v>0</v>
-      </c>
-      <c r="G91" s="21"/>
-      <c r="H91" s="18">
+      <c r="B91" s="17">
+        <v>0</v>
+      </c>
+      <c r="C91" s="20"/>
+      <c r="D91" s="17">
+        <v>0</v>
+      </c>
+      <c r="E91" s="20"/>
+      <c r="F91" s="17">
+        <v>0</v>
+      </c>
+      <c r="G91" s="20"/>
+      <c r="H91" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="22">
+      <c r="A92" s="21">
         <v>46241</v>
       </c>
-      <c r="B92" s="18">
+      <c r="B92" s="17">
         <v>100</v>
       </c>
-      <c r="C92" s="21"/>
-      <c r="D92" s="18">
+      <c r="C92" s="20"/>
+      <c r="D92" s="17">
         <v>90</v>
       </c>
-      <c r="E92" s="21"/>
-      <c r="F92" s="18">
+      <c r="E92" s="20"/>
+      <c r="F92" s="17">
         <v>100</v>
       </c>
-      <c r="G92" s="21"/>
-      <c r="H92" s="18">
+      <c r="G92" s="20"/>
+      <c r="H92" s="17">
         <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="22">
+      <c r="A93" s="21">
         <v>46244</v>
       </c>
-      <c r="B93" s="18">
-        <v>0</v>
-      </c>
-      <c r="C93" s="21"/>
-      <c r="D93" s="18">
-        <v>0</v>
-      </c>
-      <c r="E93" s="21"/>
-      <c r="F93" s="18">
-        <v>0</v>
-      </c>
-      <c r="G93" s="21"/>
-      <c r="H93" s="18">
+      <c r="B93" s="17">
+        <v>0</v>
+      </c>
+      <c r="C93" s="20"/>
+      <c r="D93" s="17">
+        <v>0</v>
+      </c>
+      <c r="E93" s="20"/>
+      <c r="F93" s="17">
+        <v>0</v>
+      </c>
+      <c r="G93" s="20"/>
+      <c r="H93" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="22">
+      <c r="A94" s="21">
         <v>46245</v>
       </c>
-      <c r="B94" s="18">
+      <c r="B94" s="17">
         <v>100</v>
       </c>
-      <c r="D94" s="18">
+      <c r="D94" s="17">
         <v>90</v>
       </c>
-      <c r="F94" s="18">
+      <c r="F94" s="17">
         <v>100</v>
       </c>
-      <c r="H94" s="18">
+      <c r="H94" s="17">
         <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="22">
+      <c r="A95" s="21">
         <v>46246</v>
       </c>
-      <c r="B95" s="18">
+      <c r="B95" s="17">
         <v>2710.8615399999999</v>
       </c>
-      <c r="C95" s="21"/>
-      <c r="D95" s="18">
+      <c r="C95" s="20"/>
+      <c r="D95" s="17">
         <v>90</v>
       </c>
-      <c r="E95" s="21"/>
-      <c r="F95" s="18">
+      <c r="E95" s="20"/>
+      <c r="F95" s="17">
         <v>160</v>
       </c>
-      <c r="G95" s="21"/>
-      <c r="H95" s="18">
+      <c r="G95" s="20"/>
+      <c r="H95" s="17">
         <v>143.79</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="22">
+      <c r="A96" s="21">
         <v>46247</v>
       </c>
-      <c r="B96" s="18">
+      <c r="B96" s="17">
         <v>480</v>
       </c>
-      <c r="C96" s="21"/>
-      <c r="D96" s="18">
+      <c r="C96" s="20"/>
+      <c r="D96" s="17">
         <v>90</v>
       </c>
-      <c r="E96" s="21"/>
-      <c r="F96" s="18">
+      <c r="E96" s="20"/>
+      <c r="F96" s="17">
         <v>100</v>
       </c>
-      <c r="G96" s="21"/>
-      <c r="H96" s="18">
+      <c r="G96" s="20"/>
+      <c r="H96" s="17">
         <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="22">
+      <c r="A97" s="21">
         <v>46248</v>
       </c>
-      <c r="B97" s="18">
+      <c r="B97" s="17">
         <v>4514.1648089999999</v>
       </c>
-      <c r="C97" s="21"/>
-      <c r="D97" s="18">
+      <c r="C97" s="20"/>
+      <c r="D97" s="17">
         <v>70</v>
       </c>
-      <c r="E97" s="21"/>
-      <c r="F97" s="18">
+      <c r="E97" s="20"/>
+      <c r="F97" s="17">
         <v>70</v>
       </c>
-      <c r="G97" s="21"/>
-      <c r="H97" s="18">
+      <c r="G97" s="20"/>
+      <c r="H97" s="17">
         <v>70</v>
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="22">
+      <c r="A98" s="21">
         <v>46251</v>
       </c>
-      <c r="B98" s="18">
-        <v>0</v>
-      </c>
-      <c r="C98" s="21"/>
-      <c r="D98" s="18">
-        <v>0</v>
-      </c>
-      <c r="E98" s="21"/>
-      <c r="F98" s="18">
-        <v>0</v>
-      </c>
-      <c r="G98" s="21"/>
-      <c r="H98" s="18">
+      <c r="B98" s="17">
+        <v>0</v>
+      </c>
+      <c r="C98" s="20"/>
+      <c r="D98" s="17">
+        <v>0</v>
+      </c>
+      <c r="E98" s="20"/>
+      <c r="F98" s="17">
+        <v>0</v>
+      </c>
+      <c r="G98" s="20"/>
+      <c r="H98" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="22">
+      <c r="A99" s="21">
         <v>46252</v>
       </c>
-      <c r="B99" s="18">
+      <c r="B99" s="17">
         <v>120</v>
       </c>
-      <c r="C99" s="21"/>
-      <c r="D99" s="18">
+      <c r="C99" s="20"/>
+      <c r="D99" s="17">
         <v>90</v>
       </c>
-      <c r="E99" s="21"/>
-      <c r="F99" s="18">
+      <c r="E99" s="20"/>
+      <c r="F99" s="17">
         <v>100</v>
       </c>
-      <c r="G99" s="21"/>
-      <c r="H99" s="18">
+      <c r="G99" s="20"/>
+      <c r="H99" s="17">
         <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="22">
+      <c r="A100" s="21">
         <v>46253</v>
       </c>
-      <c r="B100" s="18">
-        <v>0</v>
-      </c>
-      <c r="C100" s="21"/>
-      <c r="D100" s="18">
-        <v>0</v>
-      </c>
-      <c r="E100" s="21"/>
-      <c r="F100" s="18">
-        <v>0</v>
-      </c>
-      <c r="G100" s="21"/>
-      <c r="H100" s="18">
+      <c r="B100" s="17">
+        <v>0</v>
+      </c>
+      <c r="C100" s="20"/>
+      <c r="D100" s="17">
+        <v>0</v>
+      </c>
+      <c r="E100" s="20"/>
+      <c r="F100" s="17">
+        <v>0</v>
+      </c>
+      <c r="G100" s="20"/>
+      <c r="H100" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="22">
+      <c r="A101" s="21">
         <v>46254</v>
       </c>
-      <c r="B101" s="18">
-        <v>0</v>
-      </c>
-      <c r="C101" s="21"/>
-      <c r="D101" s="18">
-        <v>0</v>
-      </c>
-      <c r="E101" s="21"/>
-      <c r="F101" s="18">
-        <v>0</v>
-      </c>
-      <c r="G101" s="21"/>
-      <c r="H101" s="18">
+      <c r="B101" s="17">
+        <v>0</v>
+      </c>
+      <c r="C101" s="20"/>
+      <c r="D101" s="17">
+        <v>0</v>
+      </c>
+      <c r="E101" s="20"/>
+      <c r="F101" s="17">
+        <v>0</v>
+      </c>
+      <c r="G101" s="20"/>
+      <c r="H101" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="22">
+      <c r="A102" s="21">
         <v>46255</v>
       </c>
-      <c r="B102" s="18">
-        <v>0</v>
-      </c>
-      <c r="C102" s="21"/>
-      <c r="D102" s="18">
-        <v>0</v>
-      </c>
-      <c r="E102" s="21"/>
-      <c r="F102" s="18">
-        <v>0</v>
-      </c>
-      <c r="G102" s="21"/>
-      <c r="H102" s="18">
+      <c r="B102" s="17">
+        <v>0</v>
+      </c>
+      <c r="C102" s="20"/>
+      <c r="D102" s="17">
+        <v>0</v>
+      </c>
+      <c r="E102" s="20"/>
+      <c r="F102" s="17">
+        <v>0</v>
+      </c>
+      <c r="G102" s="20"/>
+      <c r="H102" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="22">
+      <c r="A103" s="21">
         <v>46256</v>
       </c>
-      <c r="B103" s="18">
+      <c r="B103" s="17">
         <v>60</v>
       </c>
-      <c r="C103" s="21"/>
-      <c r="D103" s="18">
+      <c r="C103" s="20"/>
+      <c r="D103" s="17">
         <v>90</v>
       </c>
-      <c r="E103" s="21"/>
-      <c r="F103" s="18">
+      <c r="E103" s="20"/>
+      <c r="F103" s="17">
         <v>100</v>
       </c>
-      <c r="G103" s="21"/>
-      <c r="H103" s="18">
+      <c r="G103" s="20"/>
+      <c r="H103" s="17">
         <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="22">
+      <c r="A104" s="21">
         <v>46259</v>
       </c>
-      <c r="B104" s="18">
+      <c r="B104" s="17">
         <v>53</v>
       </c>
-      <c r="C104" s="21"/>
-      <c r="D104" s="18">
+      <c r="C104" s="20"/>
+      <c r="D104" s="17">
         <v>250</v>
       </c>
-      <c r="E104" s="21"/>
-      <c r="F104" s="18">
+      <c r="E104" s="20"/>
+      <c r="F104" s="17">
         <v>250</v>
       </c>
-      <c r="G104" s="21"/>
-      <c r="H104" s="18">
+      <c r="G104" s="20"/>
+      <c r="H104" s="17">
         <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="22">
+      <c r="A105" s="21">
         <v>46260</v>
       </c>
-      <c r="B105" s="18">
+      <c r="B105" s="17">
         <v>266</v>
       </c>
-      <c r="C105" s="21"/>
-      <c r="D105" s="18">
+      <c r="C105" s="20"/>
+      <c r="D105" s="17">
         <v>120</v>
       </c>
-      <c r="E105" s="21"/>
-      <c r="F105" s="18">
+      <c r="E105" s="20"/>
+      <c r="F105" s="17">
         <v>250</v>
       </c>
-      <c r="G105" s="21"/>
-      <c r="H105" s="18">
+      <c r="G105" s="20"/>
+      <c r="H105" s="17">
         <v>183.16</v>
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="22">
+      <c r="A106" s="21">
         <v>46261</v>
       </c>
-      <c r="B106" s="18">
+      <c r="B106" s="17">
         <v>175</v>
       </c>
-      <c r="C106" s="21"/>
-      <c r="D106" s="18">
+      <c r="C106" s="20"/>
+      <c r="D106" s="17">
         <v>90</v>
       </c>
-      <c r="E106" s="21"/>
-      <c r="F106" s="18">
+      <c r="E106" s="20"/>
+      <c r="F106" s="17">
         <v>100</v>
       </c>
-      <c r="G106" s="21"/>
-      <c r="H106" s="18">
+      <c r="G106" s="20"/>
+      <c r="H106" s="17">
         <v>96</v>
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="22">
+      <c r="A107" s="21">
         <v>46262</v>
       </c>
-      <c r="B107" s="18">
+      <c r="B107" s="17">
         <v>800</v>
       </c>
-      <c r="C107" s="21"/>
-      <c r="D107" s="18">
+      <c r="C107" s="20"/>
+      <c r="D107" s="17">
         <v>50</v>
       </c>
-      <c r="E107" s="21"/>
-      <c r="F107" s="18">
+      <c r="E107" s="20"/>
+      <c r="F107" s="17">
         <v>500</v>
       </c>
-      <c r="G107" s="21"/>
-      <c r="H107" s="18">
+      <c r="G107" s="20"/>
+      <c r="H107" s="17">
         <v>275</v>
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="22">
+      <c r="A108" s="21">
         <v>46265</v>
       </c>
-      <c r="B108" s="18">
+      <c r="B108" s="17">
         <v>60</v>
       </c>
-      <c r="C108" s="21"/>
-      <c r="D108" s="18">
+      <c r="C108" s="20"/>
+      <c r="D108" s="17">
         <v>40</v>
       </c>
-      <c r="E108" s="21"/>
-      <c r="F108" s="18">
+      <c r="E108" s="20"/>
+      <c r="F108" s="17">
         <v>40</v>
       </c>
-      <c r="G108" s="21"/>
-      <c r="H108" s="18">
+      <c r="G108" s="20"/>
+      <c r="H108" s="17">
         <v>40</v>
       </c>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="22">
+      <c r="A109" s="21">
         <v>46266</v>
       </c>
-      <c r="B109" s="18">
-        <v>0</v>
-      </c>
-      <c r="C109" s="21"/>
-      <c r="D109" s="18">
-        <v>0</v>
-      </c>
-      <c r="E109" s="21"/>
-      <c r="F109" s="18">
-        <v>0</v>
-      </c>
-      <c r="G109" s="21"/>
-      <c r="H109" s="18">
+      <c r="B109" s="17">
+        <v>0</v>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="17">
+        <v>0</v>
+      </c>
+      <c r="E109" s="20"/>
+      <c r="F109" s="17">
+        <v>0</v>
+      </c>
+      <c r="G109" s="20"/>
+      <c r="H109" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="22">
+      <c r="A110" s="21">
         <v>46267</v>
       </c>
-      <c r="B110" s="18">
+      <c r="B110" s="17">
         <v>700</v>
       </c>
-      <c r="C110" s="21"/>
-      <c r="D110" s="18">
+      <c r="C110" s="20"/>
+      <c r="D110" s="17">
         <v>90</v>
       </c>
-      <c r="E110" s="21"/>
-      <c r="F110" s="18">
+      <c r="E110" s="20"/>
+      <c r="F110" s="17">
         <v>100</v>
       </c>
-      <c r="G110" s="21"/>
-      <c r="H110" s="18">
+      <c r="G110" s="20"/>
+      <c r="H110" s="17">
         <v>95</v>
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="22">
+      <c r="A111" s="21">
         <v>46268</v>
       </c>
-      <c r="B111" s="18">
+      <c r="B111" s="17">
         <v>420</v>
       </c>
-      <c r="C111" s="21"/>
-      <c r="D111" s="18">
+      <c r="C111" s="20"/>
+      <c r="D111" s="17">
         <v>80</v>
       </c>
-      <c r="E111" s="21"/>
-      <c r="F111" s="18">
+      <c r="E111" s="20"/>
+      <c r="F111" s="17">
         <v>100</v>
       </c>
-      <c r="G111" s="21"/>
-      <c r="H111" s="18">
+      <c r="G111" s="20"/>
+      <c r="H111" s="17">
         <v>91.19</v>
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="22">
+      <c r="A112" s="21">
         <v>46269</v>
       </c>
-      <c r="B112" s="18">
+      <c r="B112" s="17">
         <v>604</v>
       </c>
-      <c r="C112" s="21"/>
-      <c r="D112" s="18">
+      <c r="C112" s="20"/>
+      <c r="D112" s="17">
         <v>20</v>
       </c>
-      <c r="E112" s="21"/>
-      <c r="F112" s="18">
+      <c r="E112" s="20"/>
+      <c r="F112" s="17">
         <v>30</v>
       </c>
-      <c r="G112" s="21"/>
-      <c r="H112" s="18">
+      <c r="G112" s="20"/>
+      <c r="H112" s="17">
         <v>26.75</v>
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="22">
+      <c r="A113" s="21">
         <v>46272</v>
       </c>
-      <c r="B113" s="18">
+      <c r="B113" s="17">
         <v>1389.4680000000001</v>
       </c>
-      <c r="C113" s="21"/>
-      <c r="D113" s="18">
+      <c r="C113" s="20"/>
+      <c r="D113" s="17">
         <v>90</v>
       </c>
-      <c r="E113" s="21"/>
-      <c r="F113" s="18">
+      <c r="E113" s="20"/>
+      <c r="F113" s="17">
         <v>300</v>
       </c>
-      <c r="G113" s="21"/>
-      <c r="H113" s="18">
+      <c r="G113" s="20"/>
+      <c r="H113" s="17">
         <v>171.07</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="22">
+      <c r="A114" s="21">
         <v>46273</v>
       </c>
-      <c r="B114" s="18">
+      <c r="B114" s="17">
         <v>1000</v>
       </c>
-      <c r="C114" s="21"/>
-      <c r="D114" s="18">
+      <c r="C114" s="20"/>
+      <c r="D114" s="17">
         <v>90</v>
       </c>
-      <c r="E114" s="21"/>
-      <c r="F114" s="18">
+      <c r="E114" s="20"/>
+      <c r="F114" s="17">
         <v>100</v>
       </c>
-      <c r="G114" s="21"/>
-      <c r="H114" s="18">
+      <c r="G114" s="20"/>
+      <c r="H114" s="17">
         <v>95</v>
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="22">
+      <c r="A115" s="21">
         <v>47370</v>
       </c>
-      <c r="B115" s="18">
+      <c r="B115" s="17">
         <v>386</v>
       </c>
-      <c r="C115" s="21"/>
-      <c r="D115" s="18">
+      <c r="C115" s="20"/>
+      <c r="D115" s="17">
         <v>60</v>
       </c>
-      <c r="E115" s="21"/>
-      <c r="F115" s="18">
+      <c r="E115" s="20"/>
+      <c r="F115" s="17">
         <v>100</v>
       </c>
-      <c r="G115" s="21"/>
-      <c r="H115" s="18">
+      <c r="G115" s="20"/>
+      <c r="H115" s="17">
         <v>80</v>
       </c>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="22">
+      <c r="A116" s="21">
         <v>46275</v>
       </c>
-      <c r="B116" s="18">
+      <c r="B116" s="17">
         <v>300</v>
       </c>
-      <c r="C116" s="21"/>
-      <c r="D116" s="18">
+      <c r="C116" s="20"/>
+      <c r="D116" s="17">
         <v>60</v>
       </c>
-      <c r="E116" s="21"/>
-      <c r="F116" s="18">
+      <c r="E116" s="20"/>
+      <c r="F116" s="17">
         <v>100</v>
       </c>
-      <c r="G116" s="21"/>
-      <c r="H116" s="18">
+      <c r="G116" s="20"/>
+      <c r="H116" s="17">
         <v>80</v>
       </c>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="22">
+      <c r="A117" s="21">
         <v>46276</v>
       </c>
-      <c r="B117" s="18">
+      <c r="B117" s="17">
         <v>108</v>
       </c>
-      <c r="C117" s="21"/>
-      <c r="D117" s="18">
+      <c r="C117" s="20"/>
+      <c r="D117" s="17">
         <v>60</v>
       </c>
-      <c r="E117" s="21"/>
-      <c r="F117" s="18">
+      <c r="E117" s="20"/>
+      <c r="F117" s="17">
         <v>100</v>
       </c>
-      <c r="G117" s="21"/>
-      <c r="H117" s="18">
+      <c r="G117" s="20"/>
+      <c r="H117" s="17">
         <v>80</v>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="22">
+      <c r="A118" s="21">
         <v>46280</v>
       </c>
-      <c r="B118" s="18">
+      <c r="B118" s="17">
         <v>2571.288</v>
       </c>
-      <c r="C118" s="21"/>
-      <c r="D118" s="18">
+      <c r="C118" s="20"/>
+      <c r="D118" s="17">
         <v>100</v>
       </c>
-      <c r="E118" s="21"/>
-      <c r="F118" s="18">
+      <c r="E118" s="20"/>
+      <c r="F118" s="17">
         <v>150</v>
       </c>
-      <c r="G118" s="21"/>
-      <c r="H118" s="18">
+      <c r="G118" s="20"/>
+      <c r="H118" s="17">
         <v>110.92</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="21">
+        <v>46281</v>
+      </c>
+      <c r="B119" s="17">
+        <v>10800</v>
+      </c>
+      <c r="C119" s="20"/>
+      <c r="D119" s="17">
+        <v>200</v>
+      </c>
+      <c r="E119" s="20"/>
+      <c r="F119" s="17">
+        <v>200</v>
+      </c>
+      <c r="G119" s="20"/>
+      <c r="H119" s="17">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -5286,7 +5307,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5313,18 +5334,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="25" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="26">
-        <v>46280</v>
-      </c>
-      <c r="B2" s="25">
-        <v>50.214025489999997</v>
-      </c>
-      <c r="C2" s="31">
-        <f t="shared" ref="C2:C29" si="0">+((B3-B4)/B4)</f>
-        <v>-0.67806849277578529</v>
-      </c>
-      <c r="D2" s="25" t="s">
+    <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="25">
+        <v>46281</v>
+      </c>
+      <c r="B2" s="24">
+        <v>2804.9294905100001</v>
+      </c>
+      <c r="C2" s="30">
+        <f t="shared" ref="C2:C65" si="0">+(B2-B3)/B3</f>
+        <v>54.85948274687906</v>
+      </c>
+      <c r="D2" s="24" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5">
@@ -5332,1338 +5353,1362 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A3" s="26">
+      <c r="A3" s="25">
+        <v>46280</v>
+      </c>
+      <c r="B3" s="24">
+        <v>50.214025489999997</v>
+      </c>
+      <c r="C3" s="30">
+        <f t="shared" si="0"/>
+        <v>0.37097114686342592</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>68497.757342013356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="25">
         <v>46276</v>
       </c>
-      <c r="B3" s="25">
+      <c r="B4" s="24">
         <v>36.626609979999998</v>
       </c>
-      <c r="C3" s="31">
+      <c r="C4" s="30">
+        <f t="shared" si="0"/>
+        <v>-0.67806849277578529</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
+        <v>85928.931135131905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="25">
+        <v>46275</v>
+      </c>
+      <c r="B5" s="24">
+        <v>113.77143633999999</v>
+      </c>
+      <c r="C5" s="30">
         <f t="shared" si="0"/>
         <v>18.560573043109468</v>
       </c>
-      <c r="D3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5">
-        <v>68497.757342013356</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="26">
-        <v>46275</v>
-      </c>
-      <c r="B4" s="25">
-        <v>113.77143633999999</v>
-      </c>
-      <c r="C4" s="31">
+      <c r="D5" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="6">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="25">
+        <v>46274</v>
+      </c>
+      <c r="B6" s="24">
+        <v>5.8163651999999999</v>
+      </c>
+      <c r="C6" s="30">
         <f t="shared" si="0"/>
         <v>0.64045278098882874</v>
       </c>
-      <c r="D4" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6">
-        <v>85928.931135131905</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="26">
-        <v>46274</v>
-      </c>
-      <c r="B5" s="25">
-        <v>5.8163651999999999</v>
-      </c>
-      <c r="C5" s="31">
+      <c r="D6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="6">
+        <v>24565.759999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="25">
+        <v>46273</v>
+      </c>
+      <c r="B7" s="24">
+        <v>3.5455852600000002</v>
+      </c>
+      <c r="C7" s="30">
         <f t="shared" si="0"/>
         <v>-0.82640880552358198</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="6">
-        <v>22227.4775024345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="26">
-        <v>46273</v>
-      </c>
-      <c r="B6" s="25">
-        <v>3.5455852600000002</v>
-      </c>
-      <c r="C6" s="31">
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="25">
+        <v>46272</v>
+      </c>
+      <c r="B8" s="24">
+        <v>20.42491424</v>
+      </c>
+      <c r="C8" s="30">
         <f t="shared" si="0"/>
         <v>2.4737529624349173</v>
       </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="6">
-        <v>24565.759999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="26">
-        <v>46272</v>
-      </c>
-      <c r="B7" s="25">
-        <v>20.42491424</v>
-      </c>
-      <c r="C7" s="31">
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="34">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="25">
+        <v>46269</v>
+      </c>
+      <c r="B9" s="24">
+        <v>5.8797831800000004</v>
+      </c>
+      <c r="C9" s="30">
         <f t="shared" si="0"/>
         <v>-0.97953700801723442</v>
       </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="26">
-        <v>46269</v>
-      </c>
-      <c r="B8" s="25">
-        <v>5.8797831800000004</v>
-      </c>
-      <c r="C8" s="31">
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25">
+        <v>46268</v>
+      </c>
+      <c r="B10" s="24">
+        <v>287.33741307000003</v>
+      </c>
+      <c r="C10" s="30">
         <f t="shared" si="0"/>
         <v>80.163058476193896</v>
       </c>
-      <c r="D8" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="35">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="26">
-        <v>46268</v>
-      </c>
-      <c r="B9" s="25">
-        <v>287.33741307000003</v>
-      </c>
-      <c r="C9" s="31">
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="25">
+        <v>46267</v>
+      </c>
+      <c r="B11" s="24">
+        <v>3.5402487100000002</v>
+      </c>
+      <c r="C11" s="30">
         <f t="shared" si="0"/>
         <v>-0.77463732472189939</v>
       </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="26">
-        <v>46267</v>
-      </c>
-      <c r="B10" s="25">
-        <v>3.5402487100000002</v>
-      </c>
-      <c r="C10" s="31">
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="25">
+        <v>46266</v>
+      </c>
+      <c r="B12" s="24">
+        <v>15.709117340000001</v>
+      </c>
+      <c r="C12" s="30">
         <f t="shared" si="0"/>
         <v>-0.99727371031195</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="26">
-        <v>46266</v>
-      </c>
-      <c r="B11" s="25">
-        <v>15.709117340000001</v>
-      </c>
-      <c r="C11" s="31">
+      <c r="E12" s="37"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="25">
+        <v>46265</v>
+      </c>
+      <c r="B13" s="24">
+        <v>5762.0866222900004</v>
+      </c>
+      <c r="C13" s="30">
         <f t="shared" si="0"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="26">
-        <v>46265</v>
-      </c>
-      <c r="B12" s="25">
-        <v>5762.0866222900004</v>
-      </c>
-      <c r="C12" s="31">
+    <row r="14" spans="1:5">
+      <c r="A14" s="25">
+        <v>46262</v>
+      </c>
+      <c r="B14" s="24">
+        <v>5.5974634500000002</v>
+      </c>
+      <c r="C14" s="30">
         <f t="shared" si="0"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="26">
-        <v>46262</v>
-      </c>
-      <c r="B13" s="25">
-        <v>5.5974634500000002</v>
-      </c>
-      <c r="C13" s="31">
+    <row r="15" spans="1:5">
+      <c r="A15" s="25">
+        <v>46261</v>
+      </c>
+      <c r="B15" s="24">
+        <v>451.44302815999998</v>
+      </c>
+      <c r="C15" s="30">
         <f t="shared" si="0"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="26">
-        <v>46261</v>
-      </c>
-      <c r="B14" s="25">
-        <v>451.44302815999998</v>
-      </c>
-      <c r="C14" s="31">
+    <row r="16" spans="1:5">
+      <c r="A16" s="25">
+        <v>46260</v>
+      </c>
+      <c r="B16" s="24">
+        <v>4.5229189700000001</v>
+      </c>
+      <c r="C16" s="30">
         <f t="shared" si="0"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="26">
-        <v>46260</v>
-      </c>
-      <c r="B15" s="25">
-        <v>4.5229189700000001</v>
-      </c>
-      <c r="C15" s="31">
+    <row r="17" spans="1:5">
+      <c r="A17" s="25">
+        <v>46259</v>
+      </c>
+      <c r="B17" s="24">
+        <v>334.62882287999997</v>
+      </c>
+      <c r="C17" s="30">
         <f t="shared" si="0"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="26">
-        <v>46259</v>
-      </c>
-      <c r="B16" s="25">
-        <v>334.62882287999997</v>
-      </c>
-      <c r="C16" s="31">
+    <row r="18" spans="1:5">
+      <c r="A18" s="25">
+        <v>46256</v>
+      </c>
+      <c r="B18" s="24">
+        <v>4.4239792900000001</v>
+      </c>
+      <c r="C18" s="30">
         <f t="shared" si="0"/>
         <v>-0.96494750708048294</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="26">
-        <v>46256</v>
-      </c>
-      <c r="B17" s="25">
-        <v>4.4239792900000001</v>
-      </c>
-      <c r="C17" s="31">
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="25">
+        <v>46255</v>
+      </c>
+      <c r="B19" s="24">
+        <v>126.21011864</v>
+      </c>
+      <c r="C19" s="30">
         <f t="shared" si="0"/>
         <v>71.190985743560688</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="26">
-        <v>46255</v>
-      </c>
-      <c r="B18" s="25">
-        <v>126.21011864</v>
-      </c>
-      <c r="C18" s="31">
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="25">
+        <v>46254</v>
+      </c>
+      <c r="B20" s="24">
+        <v>1.7482808599999999</v>
+      </c>
+      <c r="C20" s="30">
         <f t="shared" si="0"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="26">
-        <v>46254</v>
-      </c>
-      <c r="B19" s="25">
-        <v>1.7482808599999999</v>
-      </c>
-      <c r="C19" s="31">
+    <row r="21" spans="1:5">
+      <c r="A21" s="25">
+        <v>46253</v>
+      </c>
+      <c r="B21" s="24">
+        <v>1.8562879000000001</v>
+      </c>
+      <c r="C21" s="30">
         <f t="shared" si="0"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="26">
-        <v>46253</v>
-      </c>
-      <c r="B20" s="25">
-        <v>1.8562879000000001</v>
-      </c>
-      <c r="C20" s="31">
+    <row r="22" spans="1:5">
+      <c r="A22" s="25">
+        <v>46252</v>
+      </c>
+      <c r="B22" s="24">
+        <v>1.8511089700000001</v>
+      </c>
+      <c r="C22" s="30">
         <f t="shared" si="0"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="26">
-        <v>46252</v>
-      </c>
-      <c r="B21" s="25">
-        <v>1.8511089700000001</v>
-      </c>
-      <c r="C21" s="31">
+    <row r="23" spans="1:5">
+      <c r="A23" s="25">
+        <v>46251</v>
+      </c>
+      <c r="B23" s="24">
+        <v>12.53018157</v>
+      </c>
+      <c r="C23" s="30">
         <f t="shared" si="0"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="26">
-        <v>46251</v>
-      </c>
-      <c r="B22" s="25">
-        <v>12.53018157</v>
-      </c>
-      <c r="C22" s="31">
+    <row r="24" spans="1:5">
+      <c r="A24" s="25">
+        <v>46248</v>
+      </c>
+      <c r="B24" s="24">
+        <v>4.3130696300000002</v>
+      </c>
+      <c r="C24" s="30">
         <f t="shared" si="0"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="26">
-        <v>46248</v>
-      </c>
-      <c r="B23" s="25">
-        <v>4.3130696300000002</v>
-      </c>
-      <c r="C23" s="31">
+    <row r="25" spans="1:5">
+      <c r="A25" s="25">
+        <v>46247</v>
+      </c>
+      <c r="B25" s="24">
+        <v>2.5727404300000001</v>
+      </c>
+      <c r="C25" s="30">
         <f t="shared" si="0"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="26">
-        <v>46247</v>
-      </c>
-      <c r="B24" s="25">
-        <v>2.5727404300000001</v>
-      </c>
-      <c r="C24" s="31">
+    <row r="26" spans="1:5">
+      <c r="A26" s="25">
+        <v>46246</v>
+      </c>
+      <c r="B26" s="24">
+        <v>2.3826061100000002</v>
+      </c>
+      <c r="C26" s="30">
         <f t="shared" si="0"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="26">
-        <v>46246</v>
-      </c>
-      <c r="B25" s="25">
-        <v>2.3826061100000002</v>
-      </c>
-      <c r="C25" s="31">
+    <row r="27" spans="1:5">
+      <c r="A27" s="25">
+        <v>46245</v>
+      </c>
+      <c r="B27" s="24">
+        <v>2048.0748137999999</v>
+      </c>
+      <c r="C27" s="30">
         <f t="shared" si="0"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="26">
-        <v>46245</v>
-      </c>
-      <c r="B26" s="25">
-        <v>2048.0748137999999</v>
-      </c>
-      <c r="C26" s="31">
+    <row r="28" spans="1:5">
+      <c r="A28" s="25">
+        <v>46244</v>
+      </c>
+      <c r="B28" s="24">
+        <v>4.14256738</v>
+      </c>
+      <c r="C28" s="30">
         <f t="shared" si="0"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="26">
-        <v>46244</v>
-      </c>
-      <c r="B27" s="25">
-        <v>4.14256738</v>
-      </c>
-      <c r="C27" s="31">
+    <row r="29" spans="1:5">
+      <c r="A29" s="25">
+        <v>46241</v>
+      </c>
+      <c r="B29" s="24">
+        <v>15624.152913600001</v>
+      </c>
+      <c r="C29" s="30">
         <f t="shared" si="0"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="26">
-        <v>46241</v>
-      </c>
-      <c r="B28" s="25">
-        <v>15624.152913600001</v>
-      </c>
-      <c r="C28" s="31">
+    <row r="30" spans="1:5">
+      <c r="A30" s="25">
+        <v>46240</v>
+      </c>
+      <c r="B30" s="24">
+        <v>3.2564743699999998</v>
+      </c>
+      <c r="C30" s="30">
         <f t="shared" si="0"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="26">
-        <v>46240</v>
-      </c>
-      <c r="B29" s="25">
-        <v>3.2564743699999998</v>
-      </c>
-      <c r="C29" s="31">
+    <row r="31" spans="1:5">
+      <c r="A31" s="25">
+        <v>46239</v>
+      </c>
+      <c r="B31" s="24">
+        <v>2.8086933300000001</v>
+      </c>
+      <c r="C31" s="30">
         <f t="shared" si="0"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="26">
-        <v>46239</v>
-      </c>
-      <c r="B30" s="25">
-        <v>2.8086933300000001</v>
-      </c>
-      <c r="C30" s="31">
-        <f t="shared" ref="C30:C73" si="1">+((B31-B32)/B32)</f>
+    <row r="32" spans="1:5">
+      <c r="A32" s="25">
+        <v>46238</v>
+      </c>
+      <c r="B32" s="24">
+        <v>499.27660521000001</v>
+      </c>
+      <c r="C32" s="30">
+        <f t="shared" si="0"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="26">
-        <v>46238</v>
-      </c>
-      <c r="B31" s="25">
-        <v>499.27660521000001</v>
-      </c>
-      <c r="C31" s="31">
-        <f t="shared" si="1"/>
+    <row r="33" spans="1:3">
+      <c r="A33" s="25">
+        <v>46237</v>
+      </c>
+      <c r="B33" s="24">
+        <v>6.5592306300000001</v>
+      </c>
+      <c r="C33" s="30">
+        <f t="shared" si="0"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="26">
-        <v>46237</v>
-      </c>
-      <c r="B32" s="25">
-        <v>6.5592306300000001</v>
-      </c>
-      <c r="C32" s="31">
-        <f t="shared" si="1"/>
+    <row r="34" spans="1:3">
+      <c r="A34" s="25">
+        <v>46234</v>
+      </c>
+      <c r="B34" s="24">
+        <v>19481.20894855</v>
+      </c>
+      <c r="C34" s="30">
+        <f t="shared" si="0"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="26">
-        <v>46234</v>
-      </c>
-      <c r="B33" s="25">
-        <v>19481.20894855</v>
-      </c>
-      <c r="C33" s="31">
-        <f t="shared" si="1"/>
+    <row r="35" spans="1:3">
+      <c r="A35" s="25">
+        <v>46233</v>
+      </c>
+      <c r="B35">
+        <v>466.33578662999997</v>
+      </c>
+      <c r="C35" s="30">
+        <f t="shared" si="0"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="26">
-        <v>46233</v>
-      </c>
-      <c r="B34">
-        <v>466.33578662999997</v>
-      </c>
-      <c r="C34" s="31">
-        <f t="shared" si="1"/>
+    <row r="36" spans="1:3">
+      <c r="A36" s="25">
+        <v>46232</v>
+      </c>
+      <c r="B36" s="24">
+        <v>101.55832515</v>
+      </c>
+      <c r="C36" s="30">
+        <f t="shared" si="0"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="26">
-        <v>46232</v>
-      </c>
-      <c r="B35" s="25">
-        <v>101.55832515</v>
-      </c>
-      <c r="C35" s="31">
-        <f t="shared" si="1"/>
+    <row r="37" spans="1:3">
+      <c r="A37" s="25">
+        <v>46231</v>
+      </c>
+      <c r="B37" s="24">
+        <v>4.3645205499999999</v>
+      </c>
+      <c r="C37" s="30">
+        <f t="shared" si="0"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="26">
-        <v>46231</v>
-      </c>
-      <c r="B36" s="25">
-        <v>4.3645205499999999</v>
-      </c>
-      <c r="C36" s="31">
-        <f t="shared" si="1"/>
+    <row r="38" spans="1:3">
+      <c r="A38" s="25">
+        <v>46108</v>
+      </c>
+      <c r="B38" s="24">
+        <v>223.50959897000001</v>
+      </c>
+      <c r="C38" s="30">
+        <f t="shared" si="0"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="26">
-        <v>46108</v>
-      </c>
-      <c r="B37" s="25">
-        <v>223.50959897000001</v>
-      </c>
-      <c r="C37" s="31">
-        <f t="shared" si="1"/>
+    <row r="39" spans="1:3">
+      <c r="A39" s="25">
+        <v>46226</v>
+      </c>
+      <c r="B39" s="24">
+        <v>28677.412251940001</v>
+      </c>
+      <c r="C39" s="30">
+        <f t="shared" si="0"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="26">
-        <v>46226</v>
-      </c>
-      <c r="B38" s="25">
-        <v>28677.412251940001</v>
-      </c>
-      <c r="C38" s="31">
-        <f t="shared" si="1"/>
+    <row r="40" spans="1:3">
+      <c r="A40" s="25">
+        <v>46225</v>
+      </c>
+      <c r="B40" s="24">
+        <v>858.25054019000004</v>
+      </c>
+      <c r="C40" s="30">
+        <f t="shared" si="0"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="26">
-        <v>46225</v>
-      </c>
-      <c r="B39" s="25">
-        <v>858.25054019000004</v>
-      </c>
-      <c r="C39" s="31">
-        <f t="shared" si="1"/>
+    <row r="41" spans="1:3">
+      <c r="A41" s="25">
+        <v>46224</v>
+      </c>
+      <c r="B41" s="24">
+        <v>20.063323860000001</v>
+      </c>
+      <c r="C41" s="30">
+        <f t="shared" si="0"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="26">
-        <v>46224</v>
-      </c>
-      <c r="B40" s="25">
-        <v>20.063323860000001</v>
-      </c>
-      <c r="C40" s="31">
-        <f t="shared" si="1"/>
+    <row r="42" spans="1:3">
+      <c r="A42" s="25">
+        <v>46220</v>
+      </c>
+      <c r="B42" s="24">
+        <v>7544.8528890099997</v>
+      </c>
+      <c r="C42" s="30">
+        <f t="shared" si="0"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="26">
-        <v>46220</v>
-      </c>
-      <c r="B41" s="25">
-        <v>7544.8528890099997</v>
-      </c>
-      <c r="C41" s="31">
-        <f t="shared" si="1"/>
+    <row r="43" spans="1:3">
+      <c r="A43" s="25">
+        <v>46219</v>
+      </c>
+      <c r="B43" s="24">
+        <v>16578.913830919999</v>
+      </c>
+      <c r="C43" s="30">
+        <f t="shared" si="0"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="26">
-        <v>46219</v>
-      </c>
-      <c r="B42" s="25">
-        <v>16578.913830919999</v>
-      </c>
-      <c r="C42" s="31">
-        <f t="shared" si="1"/>
+    <row r="44" spans="1:3">
+      <c r="A44" s="25">
+        <v>46218</v>
+      </c>
+      <c r="B44" s="24">
+        <v>7891.6954687400003</v>
+      </c>
+      <c r="C44" s="30">
+        <f t="shared" si="0"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="26">
-        <v>46218</v>
-      </c>
-      <c r="B43" s="25">
-        <v>7891.6954687400003</v>
-      </c>
-      <c r="C43" s="31">
-        <f t="shared" si="1"/>
+    <row r="45" spans="1:3">
+      <c r="A45" s="25">
+        <v>46217</v>
+      </c>
+      <c r="B45" s="24">
+        <v>38833.478919130001</v>
+      </c>
+      <c r="C45" s="30">
+        <f t="shared" si="0"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="26">
-        <v>46217</v>
-      </c>
-      <c r="B44" s="25">
-        <v>38833.478919130001</v>
-      </c>
-      <c r="C44" s="31">
-        <f t="shared" si="1"/>
+    <row r="46" spans="1:3">
+      <c r="A46" s="25">
+        <v>46216</v>
+      </c>
+      <c r="B46" s="24">
+        <v>52315.97026473</v>
+      </c>
+      <c r="C46" s="30">
+        <f t="shared" si="0"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="26">
-        <v>46216</v>
-      </c>
-      <c r="B45" s="25">
-        <v>52315.97026473</v>
-      </c>
-      <c r="C45" s="31">
-        <f t="shared" si="1"/>
+    <row r="47" spans="1:3">
+      <c r="A47" s="25">
+        <v>46213</v>
+      </c>
+      <c r="B47" s="24">
+        <v>64626.363040830001</v>
+      </c>
+      <c r="C47" s="30">
+        <f t="shared" si="0"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="26">
-        <v>46213</v>
-      </c>
-      <c r="B46" s="25">
-        <v>64626.363040830001</v>
-      </c>
-      <c r="C46" s="31">
-        <f t="shared" si="1"/>
+    <row r="48" spans="1:3">
+      <c r="A48" s="25">
+        <v>46212</v>
+      </c>
+      <c r="B48" s="24">
+        <v>28200.29395617</v>
+      </c>
+      <c r="C48" s="30">
+        <f t="shared" si="0"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="26">
-        <v>46212</v>
-      </c>
-      <c r="B47" s="25">
-        <v>28200.29395617</v>
-      </c>
-      <c r="C47" s="31">
-        <f t="shared" si="1"/>
+    <row r="49" spans="1:3">
+      <c r="A49" s="25">
+        <v>46211</v>
+      </c>
+      <c r="B49" s="24">
+        <v>7705.0577555</v>
+      </c>
+      <c r="C49" s="30">
+        <f t="shared" si="0"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="26">
-        <v>46211</v>
-      </c>
-      <c r="B48" s="25">
-        <v>7705.0577555</v>
-      </c>
-      <c r="C48" s="31">
-        <f t="shared" si="1"/>
+    <row r="50" spans="1:3">
+      <c r="A50" s="25">
+        <v>46210</v>
+      </c>
+      <c r="B50" s="24">
+        <v>4185.2572516800001</v>
+      </c>
+      <c r="C50" s="30">
+        <f t="shared" si="0"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="26">
-        <v>46210</v>
-      </c>
-      <c r="B49" s="25">
-        <v>4185.2572516800001</v>
-      </c>
-      <c r="C49" s="31">
-        <f t="shared" si="1"/>
+    <row r="51" spans="1:3">
+      <c r="A51" s="25">
+        <v>46209</v>
+      </c>
+      <c r="B51" s="24">
+        <v>9017.3713134900008</v>
+      </c>
+      <c r="C51" s="30">
+        <f t="shared" si="0"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="26">
-        <v>46209</v>
-      </c>
-      <c r="B50" s="25">
-        <v>9017.3713134900008</v>
-      </c>
-      <c r="C50" s="31">
-        <f t="shared" si="1"/>
+    <row r="52" spans="1:3">
+      <c r="A52" s="25">
+        <v>46206</v>
+      </c>
+      <c r="B52" s="24">
+        <v>17125.195337590001</v>
+      </c>
+      <c r="C52" s="30">
+        <f t="shared" si="0"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="26">
-        <v>46206</v>
-      </c>
-      <c r="B51" s="25">
-        <v>17125.195337590001</v>
-      </c>
-      <c r="C51" s="31">
-        <f t="shared" si="1"/>
+    <row r="53" spans="1:3">
+      <c r="A53" s="25">
+        <v>46205</v>
+      </c>
+      <c r="B53" s="24">
+        <v>28151.370695969999</v>
+      </c>
+      <c r="C53" s="30">
+        <f t="shared" si="0"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="26">
-        <v>46205</v>
-      </c>
-      <c r="B52" s="25">
-        <v>28151.370695969999</v>
-      </c>
-      <c r="C52" s="31">
-        <f t="shared" si="1"/>
+    <row r="54" spans="1:3">
+      <c r="A54" s="25">
+        <v>46204</v>
+      </c>
+      <c r="B54" s="24">
+        <v>989.47411254999997</v>
+      </c>
+      <c r="C54" s="30">
+        <f t="shared" si="0"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="26">
-        <v>46204</v>
-      </c>
-      <c r="B53" s="25">
-        <v>989.47411254999997</v>
-      </c>
-      <c r="C53" s="31">
-        <f t="shared" si="1"/>
+    <row r="55" spans="1:3">
+      <c r="A55" s="25">
+        <v>46203</v>
+      </c>
+      <c r="B55" s="24">
+        <v>5688.5275189000004</v>
+      </c>
+      <c r="C55" s="30">
+        <f t="shared" si="0"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="26">
-        <v>46203</v>
-      </c>
-      <c r="B54" s="25">
-        <v>5688.5275189000004</v>
-      </c>
-      <c r="C54" s="31">
-        <f t="shared" si="1"/>
+    <row r="56" spans="1:3">
+      <c r="A56" s="25">
+        <v>46198</v>
+      </c>
+      <c r="B56" s="24">
+        <v>31666.069450710002</v>
+      </c>
+      <c r="C56" s="30">
+        <f t="shared" si="0"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="26">
-        <v>46198</v>
-      </c>
-      <c r="B55" s="25">
-        <v>31666.069450710002</v>
-      </c>
-      <c r="C55" s="31">
-        <f t="shared" si="1"/>
+    <row r="57" spans="1:3">
+      <c r="A57" s="25">
+        <v>46196</v>
+      </c>
+      <c r="B57" s="24">
+        <v>2417.8997009200002</v>
+      </c>
+      <c r="C57" s="30">
+        <f t="shared" si="0"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="26">
-        <v>46196</v>
-      </c>
-      <c r="B56" s="25">
-        <v>2417.8997009200002</v>
-      </c>
-      <c r="C56" s="31">
-        <f t="shared" si="1"/>
+    <row r="58" spans="1:3">
+      <c r="A58" s="25">
+        <v>46195</v>
+      </c>
+      <c r="B58" s="24">
+        <v>1716.30170335</v>
+      </c>
+      <c r="C58" s="30">
+        <f t="shared" si="0"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="26">
-        <v>46195</v>
-      </c>
-      <c r="B57" s="25">
-        <v>1716.30170335</v>
-      </c>
-      <c r="C57" s="31">
-        <f t="shared" si="1"/>
+    <row r="59" spans="1:3">
+      <c r="A59" s="25">
+        <v>46192</v>
+      </c>
+      <c r="B59" s="24">
+        <v>16.43890412</v>
+      </c>
+      <c r="C59" s="30">
+        <f t="shared" si="0"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="26">
-        <v>46192</v>
-      </c>
-      <c r="B58" s="25">
-        <v>16.43890412</v>
-      </c>
-      <c r="C58" s="31">
-        <f t="shared" si="1"/>
+    <row r="60" spans="1:3">
+      <c r="A60" s="25">
+        <v>46191</v>
+      </c>
+      <c r="B60" s="24">
+        <v>269.81083503999997</v>
+      </c>
+      <c r="C60" s="30">
+        <f t="shared" si="0"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="26">
-        <v>46191</v>
-      </c>
-      <c r="B59" s="25">
-        <v>269.81083503999997</v>
-      </c>
-      <c r="C59" s="31">
-        <f t="shared" si="1"/>
+    <row r="61" spans="1:3">
+      <c r="A61" s="25">
+        <v>46190</v>
+      </c>
+      <c r="B61" s="24">
+        <v>2298.2133896800001</v>
+      </c>
+      <c r="C61" s="30">
+        <f t="shared" si="0"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="26">
-        <v>46190</v>
-      </c>
-      <c r="B60" s="25">
-        <v>2298.2133896800001</v>
-      </c>
-      <c r="C60" s="31">
-        <f t="shared" si="1"/>
+    <row r="62" spans="1:3">
+      <c r="A62" s="25">
+        <v>46189</v>
+      </c>
+      <c r="B62" s="24">
+        <v>1206.260808</v>
+      </c>
+      <c r="C62" s="30">
+        <f t="shared" si="0"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="26">
-        <v>46189</v>
-      </c>
-      <c r="B61" s="25">
-        <v>1206.260808</v>
-      </c>
-      <c r="C61" s="31">
-        <f t="shared" si="1"/>
+    <row r="63" spans="1:3">
+      <c r="A63" s="25">
+        <v>46188</v>
+      </c>
+      <c r="B63" s="24">
+        <v>8.42</v>
+      </c>
+      <c r="C63" s="30">
+        <f t="shared" si="0"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="26">
-        <v>46188</v>
-      </c>
-      <c r="B62" s="25">
-        <v>8.42</v>
-      </c>
-      <c r="C62" s="31">
-        <f t="shared" si="1"/>
+    <row r="64" spans="1:3">
+      <c r="A64" s="25">
+        <v>46185</v>
+      </c>
+      <c r="B64" s="24">
+        <v>19.156653639999998</v>
+      </c>
+      <c r="C64" s="30">
+        <f t="shared" si="0"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="26">
-        <v>46185</v>
-      </c>
-      <c r="B63" s="25">
-        <v>19.156653639999998</v>
-      </c>
-      <c r="C63" s="31">
-        <f t="shared" si="1"/>
+    <row r="65" spans="1:3">
+      <c r="A65" s="25">
+        <v>46184</v>
+      </c>
+      <c r="B65" s="24">
+        <v>12.711483429999999</v>
+      </c>
+      <c r="C65" s="30">
+        <f t="shared" si="0"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="26">
-        <v>46184</v>
-      </c>
-      <c r="B64" s="25">
-        <v>12.711483429999999</v>
-      </c>
-      <c r="C64" s="31">
-        <f t="shared" si="1"/>
+    <row r="66" spans="1:3">
+      <c r="A66" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B66" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C66" s="30">
+        <f t="shared" ref="C66:C107" si="1">+(B66-B67)/B67</f>
         <v>5.2639483520141219</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="26">
-        <v>46183</v>
-      </c>
-      <c r="B65" s="25">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C65" s="31">
+    <row r="67" spans="1:3">
+      <c r="A67" s="25">
+        <v>46182</v>
+      </c>
+      <c r="B67" s="24">
+        <v>3601.9386242999999</v>
+      </c>
+      <c r="C67" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="26">
-        <v>46182</v>
-      </c>
-      <c r="B66" s="25">
-        <v>3601.9386242999999</v>
-      </c>
-      <c r="C66" s="31">
+    <row r="68" spans="1:3">
+      <c r="A68" s="25">
+        <v>46178</v>
+      </c>
+      <c r="B68" s="24">
+        <v>58292.928576159997</v>
+      </c>
+      <c r="C68" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="26">
-        <v>46178</v>
-      </c>
-      <c r="B67" s="25">
-        <v>58292.928576159997</v>
-      </c>
-      <c r="C67" s="31">
+    <row r="69" spans="1:3">
+      <c r="A69" s="25">
+        <v>46177</v>
+      </c>
+      <c r="B69" s="24">
+        <v>9350.0363108799993</v>
+      </c>
+      <c r="C69" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="26">
-        <v>46177</v>
-      </c>
-      <c r="B68" s="25">
-        <v>9350.0363108799993</v>
-      </c>
-      <c r="C68" s="31">
+    <row r="70" spans="1:3">
+      <c r="A70" s="25">
+        <v>46176</v>
+      </c>
+      <c r="B70" s="24">
+        <v>3300.6863896099999</v>
+      </c>
+      <c r="C70" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="26">
-        <v>46176</v>
-      </c>
-      <c r="B69" s="25">
-        <v>3300.6863896099999</v>
-      </c>
-      <c r="C69" s="31">
+    <row r="71" spans="1:3">
+      <c r="A71" s="25">
+        <v>46175</v>
+      </c>
+      <c r="B71" s="24">
+        <v>29863.561946620001</v>
+      </c>
+      <c r="C71" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="26">
-        <v>46175</v>
-      </c>
-      <c r="B70" s="25">
-        <v>29863.561946620001</v>
-      </c>
-      <c r="C70" s="31">
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
+        <v>46174</v>
+      </c>
+      <c r="B72" s="24">
+        <v>55.287064620000002</v>
+      </c>
+      <c r="C72" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="26">
-        <v>46174</v>
-      </c>
-      <c r="B71" s="25">
-        <v>55.287064620000002</v>
-      </c>
-      <c r="C71" s="31">
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
+        <v>46171</v>
+      </c>
+      <c r="B73" s="24">
+        <v>33469.1560455</v>
+      </c>
+      <c r="C73" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="26">
-        <v>46171</v>
-      </c>
-      <c r="B72" s="25">
-        <v>33469.1560455</v>
-      </c>
-      <c r="C72" s="31">
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
+        <v>45074</v>
+      </c>
+      <c r="B74" s="24">
+        <v>9253.9873366299998</v>
+      </c>
+      <c r="C74" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="26">
-        <v>45074</v>
-      </c>
-      <c r="B73" s="25">
-        <v>9253.9873366299998</v>
-      </c>
-      <c r="C73" s="31">
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
+        <v>46169</v>
+      </c>
+      <c r="B75" s="24">
+        <v>21.673895040000001</v>
+      </c>
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="26">
-        <v>46169</v>
-      </c>
-      <c r="B74" s="25">
-        <v>21.673895040000001</v>
-      </c>
-      <c r="C74" s="31">
-        <f>+((B75-B76)/B76)</f>
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
+        <v>46168</v>
+      </c>
+      <c r="B76" s="24">
+        <v>8513.9651106900001</v>
+      </c>
+      <c r="C76" s="30">
+        <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="26">
-        <v>46168</v>
-      </c>
-      <c r="B75" s="25">
-        <v>8513.9651106900001</v>
-      </c>
-      <c r="C75" s="31">
-        <f>+((B76-B77)/B77)</f>
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
+        <v>46167</v>
+      </c>
+      <c r="B77" s="24">
+        <v>12500.80501835</v>
+      </c>
+      <c r="C77" s="30">
+        <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="26">
-        <v>46167</v>
-      </c>
-      <c r="B76" s="25">
-        <v>12500.80501835</v>
-      </c>
-      <c r="C76" s="31">
-        <f>+((B77-B78)/B78)</f>
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
+        <v>46164</v>
+      </c>
+      <c r="B78" s="24">
+        <v>58837.242479</v>
+      </c>
+      <c r="C78" s="30">
+        <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="26">
-        <v>46164</v>
-      </c>
-      <c r="B77" s="25">
-        <v>58837.242479</v>
-      </c>
-      <c r="C77" s="31">
-        <f>+((B82-B83)/B83)</f>
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
+        <v>46163</v>
+      </c>
+      <c r="B79" s="24">
+        <v>55.256117230000001</v>
+      </c>
+      <c r="C79" s="30">
+        <f t="shared" si="1"/>
+        <v>-0.99728557445032884</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
+        <v>46162</v>
+      </c>
+      <c r="B80" s="24">
+        <v>20356.468143580001</v>
+      </c>
+      <c r="C80" s="30">
+        <f t="shared" si="1"/>
+        <v>-0.71845195425328001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
+        <v>46161</v>
+      </c>
+      <c r="B81" s="24">
+        <v>72301.933723569993</v>
+      </c>
+      <c r="C81" s="30">
+        <f t="shared" si="1"/>
+        <v>-2.5709262214296945E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
+        <v>46157</v>
+      </c>
+      <c r="B82" s="24">
+        <v>74209.813271849998</v>
+      </c>
+      <c r="C82" s="30">
+        <f t="shared" si="1"/>
+        <v>35.243819791014161</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
+        <v>46156</v>
+      </c>
+      <c r="B83" s="24">
+        <v>2047.5163407099999</v>
+      </c>
+      <c r="C83" s="30">
+        <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="26">
-        <v>46163</v>
-      </c>
-      <c r="B78" s="25">
-        <v>55.256117230000001</v>
-      </c>
-      <c r="C78" s="31">
-        <f t="shared" ref="C78:C101" si="2">+((B83-B84)/B84)</f>
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
+        <v>46155</v>
+      </c>
+      <c r="B84" s="24">
+        <v>24.614867159999999</v>
+      </c>
+      <c r="C84" s="30">
+        <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="26">
-        <v>46162</v>
-      </c>
-      <c r="B79" s="25">
-        <v>20356.468143580001</v>
-      </c>
-      <c r="C79" s="31">
-        <f t="shared" si="2"/>
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
+        <v>46154</v>
+      </c>
+      <c r="B85" s="24">
+        <v>673.01725538999995</v>
+      </c>
+      <c r="C85" s="30">
+        <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="26">
-        <v>46161</v>
-      </c>
-      <c r="B80" s="25">
-        <v>72301.933723569993</v>
-      </c>
-      <c r="C80" s="31">
-        <f t="shared" si="2"/>
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
+        <v>46153</v>
+      </c>
+      <c r="B86" s="24">
+        <v>16068.49495319</v>
+      </c>
+      <c r="C86" s="30">
+        <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="26">
-        <v>46157</v>
-      </c>
-      <c r="B81" s="25">
-        <v>74209.813271849998</v>
-      </c>
-      <c r="C81" s="31">
-        <f t="shared" si="2"/>
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
+        <v>46150</v>
+      </c>
+      <c r="B87" s="24">
+        <v>23652.710333340001</v>
+      </c>
+      <c r="C87" s="30">
+        <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="26">
-        <v>46156</v>
-      </c>
-      <c r="B82" s="25">
-        <v>2047.5163407099999</v>
-      </c>
-      <c r="C82" s="31">
-        <f t="shared" si="2"/>
+    <row r="88" spans="1:3">
+      <c r="A88" s="23">
+        <v>46149</v>
+      </c>
+      <c r="B88" s="22">
+        <v>131.99794839</v>
+      </c>
+      <c r="C88" s="30">
+        <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="26">
-        <v>46155</v>
-      </c>
-      <c r="B83" s="25">
-        <v>24.614867159999999</v>
-      </c>
-      <c r="C83" s="31">
-        <f t="shared" si="2"/>
+    <row r="89" spans="1:3">
+      <c r="A89" s="18">
+        <v>46148</v>
+      </c>
+      <c r="B89" s="16">
+        <v>745.52443231999996</v>
+      </c>
+      <c r="C89" s="30">
+        <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="26">
-        <v>46154</v>
-      </c>
-      <c r="B84" s="25">
-        <v>673.01725538999995</v>
-      </c>
-      <c r="C84" s="31">
-        <f t="shared" si="2"/>
+    <row r="90" spans="1:3">
+      <c r="A90" s="18">
+        <v>46147</v>
+      </c>
+      <c r="B90" s="16">
+        <v>84317.802960360001</v>
+      </c>
+      <c r="C90" s="30">
+        <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="26">
-        <v>46153</v>
-      </c>
-      <c r="B85" s="25">
-        <v>16068.49495319</v>
-      </c>
-      <c r="C85" s="31">
-        <f t="shared" si="2"/>
+    <row r="91" spans="1:3">
+      <c r="A91" s="18">
+        <v>46146</v>
+      </c>
+      <c r="B91" s="16">
+        <v>49567.396050169998</v>
+      </c>
+      <c r="C91" s="30">
+        <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="26">
-        <v>46150</v>
-      </c>
-      <c r="B86" s="25">
-        <v>23652.710333340001</v>
-      </c>
-      <c r="C86" s="31">
-        <f t="shared" si="2"/>
+    <row r="92" spans="1:3">
+      <c r="A92" s="19">
+        <v>46142</v>
+      </c>
+      <c r="B92" s="16">
+        <v>87352.396084139997</v>
+      </c>
+      <c r="C92" s="30">
+        <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
-        <v>46149</v>
-      </c>
-      <c r="B87" s="23">
-        <v>131.99794839</v>
-      </c>
-      <c r="C87" s="31">
-        <f t="shared" si="2"/>
+    <row r="93" spans="1:3">
+      <c r="A93" s="19">
+        <v>46141</v>
+      </c>
+      <c r="B93" s="16">
+        <v>28385.438679769999</v>
+      </c>
+      <c r="C93" s="30">
+        <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="19">
-        <v>46148</v>
-      </c>
-      <c r="B88" s="17">
-        <v>745.52443231999996</v>
-      </c>
-      <c r="C88" s="31">
-        <f t="shared" si="2"/>
+    <row r="94" spans="1:3">
+      <c r="A94" s="19">
+        <v>46140</v>
+      </c>
+      <c r="B94" s="16">
+        <v>70324.097718699995</v>
+      </c>
+      <c r="C94" s="30">
+        <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="19">
-        <v>46147</v>
-      </c>
-      <c r="B89" s="17">
-        <v>84317.802960360001</v>
-      </c>
-      <c r="C89" s="31">
-        <f t="shared" si="2"/>
+    <row r="95" spans="1:3">
+      <c r="A95" s="19">
+        <v>46139</v>
+      </c>
+      <c r="B95" s="16">
+        <v>40338.944788629997</v>
+      </c>
+      <c r="C95" s="30">
+        <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="19">
-        <v>46146</v>
-      </c>
-      <c r="B90" s="17">
-        <v>49567.396050169998</v>
-      </c>
-      <c r="C90" s="31">
-        <f t="shared" si="2"/>
+    <row r="96" spans="1:3">
+      <c r="A96" s="19">
+        <v>46136</v>
+      </c>
+      <c r="B96" s="16">
+        <v>60973.651931649998</v>
+      </c>
+      <c r="C96" s="30">
+        <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="20">
-        <v>46142</v>
-      </c>
-      <c r="B91" s="17">
-        <v>87352.396084139997</v>
-      </c>
-      <c r="C91" s="31">
-        <f t="shared" si="2"/>
+    <row r="97" spans="1:4">
+      <c r="A97" s="19">
+        <v>46135</v>
+      </c>
+      <c r="B97" s="16">
+        <v>4652.1817311200002</v>
+      </c>
+      <c r="C97" s="30">
+        <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="20">
-        <v>46141</v>
-      </c>
-      <c r="B92" s="17">
-        <v>28385.438679769999</v>
-      </c>
-      <c r="C92" s="31">
-        <f t="shared" si="2"/>
+    <row r="98" spans="1:4">
+      <c r="A98" s="19">
+        <v>46134</v>
+      </c>
+      <c r="B98" s="16">
+        <v>17251.00486529</v>
+      </c>
+      <c r="C98" s="30">
+        <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="20">
-        <v>46140</v>
-      </c>
-      <c r="B93" s="17">
-        <v>70324.097718699995</v>
-      </c>
-      <c r="C93" s="31">
-        <f t="shared" si="2"/>
+    <row r="99" spans="1:4">
+      <c r="A99" s="19">
+        <v>46133</v>
+      </c>
+      <c r="B99" s="16">
+        <v>47981.781644150004</v>
+      </c>
+      <c r="C99" s="30">
+        <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="20">
-        <v>46139</v>
-      </c>
-      <c r="B94" s="17">
-        <v>40338.944788629997</v>
-      </c>
-      <c r="C94" s="31">
-        <f t="shared" si="2"/>
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
+        <v>46132</v>
+      </c>
+      <c r="B100" s="16">
+        <v>51339.49161813</v>
+      </c>
+      <c r="C100" s="30">
+        <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="20">
-        <v>46136</v>
-      </c>
-      <c r="B95" s="17">
-        <v>60973.651931649998</v>
-      </c>
-      <c r="C95" s="31">
-        <f t="shared" si="2"/>
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
+        <v>46129</v>
+      </c>
+      <c r="B101" s="16">
+        <v>17216.492596060001</v>
+      </c>
+      <c r="C101" s="30">
+        <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="20">
-        <v>46135</v>
-      </c>
-      <c r="B96" s="17">
-        <v>4652.1817311200002</v>
-      </c>
-      <c r="C96" s="31">
-        <f t="shared" si="2"/>
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
+        <v>46128</v>
+      </c>
+      <c r="B102" s="16">
+        <v>18.890111640000001</v>
+      </c>
+      <c r="C102" s="30">
+        <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="20">
-        <v>46134</v>
-      </c>
-      <c r="B97" s="17">
-        <v>17251.00486529</v>
-      </c>
-      <c r="C97" s="31">
-        <f t="shared" si="2"/>
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
+        <v>46127</v>
+      </c>
+      <c r="B103" s="39">
+        <v>15.79809785</v>
+      </c>
+      <c r="C103" s="30">
+        <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
-    </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="20">
-        <v>46133</v>
-      </c>
-      <c r="B98" s="17">
-        <v>47981.781644150004</v>
-      </c>
-      <c r="C98" s="31">
-        <f t="shared" si="2"/>
+      <c r="D103" s="37"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
+        <v>46126</v>
+      </c>
+      <c r="B104" s="39">
+        <v>16.215898760000002</v>
+      </c>
+      <c r="C104" s="30">
+        <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="20">
-        <v>46132</v>
-      </c>
-      <c r="B99" s="17">
-        <v>51339.49161813</v>
-      </c>
-      <c r="C99" s="31">
-        <f t="shared" si="2"/>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
+        <v>46125</v>
+      </c>
+      <c r="B105" s="16">
+        <v>2475.4322626600001</v>
+      </c>
+      <c r="C105" s="30">
+        <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
-      <c r="A100" s="20">
-        <v>46129</v>
-      </c>
-      <c r="B100" s="17">
-        <v>17216.492596060001</v>
-      </c>
-      <c r="C100" s="31">
-        <f t="shared" si="2"/>
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
+        <v>46122</v>
+      </c>
+      <c r="B106" s="16">
+        <v>7956.2858669899997</v>
+      </c>
+      <c r="C106" s="30">
+        <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
-      <c r="A101" s="20">
-        <v>46128</v>
-      </c>
-      <c r="B101" s="17">
-        <v>18.890111640000001</v>
-      </c>
-      <c r="C101" s="31">
-        <f t="shared" si="2"/>
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
+        <v>46121</v>
+      </c>
+      <c r="B107" s="16">
+        <v>41.536584740000002</v>
+      </c>
+      <c r="C107" s="30">
+        <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="102" spans="1:3">
-      <c r="A102" s="20">
-        <v>46127</v>
-      </c>
-      <c r="B102" s="17">
-        <v>15.79809785</v>
-      </c>
-      <c r="C102" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3">
-      <c r="A103" s="20">
-        <v>46126</v>
-      </c>
-      <c r="B103" s="17">
-        <v>16.215898760000002</v>
-      </c>
-      <c r="C103" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3">
-      <c r="A104" s="20">
-        <v>46125</v>
-      </c>
-      <c r="B104" s="17">
-        <v>2475.4322626600001</v>
-      </c>
-      <c r="C104" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3">
-      <c r="A105" s="20">
-        <v>46122</v>
-      </c>
-      <c r="B105" s="17">
-        <v>7956.2858669899997</v>
-      </c>
-      <c r="C105" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3">
-      <c r="A106" s="20">
-        <v>46121</v>
-      </c>
-      <c r="B106" s="17">
-        <v>41.536584740000002</v>
-      </c>
-      <c r="C106" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
-      <c r="A107" s="20">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46120</v>
       </c>
-      <c r="B107" s="17">
+      <c r="B108" s="16">
         <v>580.56056466999996</v>
       </c>
-      <c r="C107" s="16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3">
-      <c r="A108" s="20">
+      <c r="C108" s="30">
+        <f>+(B108-B109)/B109</f>
+        <v>3.9632497533121036</v>
+      </c>
+      <c r="D108" s="36"/>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46119</v>
       </c>
-      <c r="B108" s="17">
+      <c r="B109" s="16">
         <v>116.97186189</v>
       </c>
     </row>
-    <row r="109" spans="1:3">
-      <c r="A109" s="20">
+    <row r="110" spans="1:4">
+      <c r="A110" s="19">
         <v>46118</v>
       </c>
-      <c r="B109" s="17">
+      <c r="B110" s="16">
         <v>6972.36861443</v>
       </c>
-    </row>
-    <row r="110" spans="1:3">
-      <c r="A110" s="20">
+      <c r="D110" s="36"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="19">
         <v>46113</v>
       </c>
-      <c r="B110" s="17">
+      <c r="B111" s="16">
         <v>540.00852741999995</v>
       </c>
     </row>
-    <row r="111" spans="1:3">
-      <c r="A111" s="20">
+    <row r="112" spans="1:4">
+      <c r="A112" s="19">
         <v>46112</v>
       </c>
-      <c r="B111" s="17">
+      <c r="B112" s="16">
         <v>5262.3389565099997</v>
       </c>
     </row>
-    <row r="112" spans="1:3">
-      <c r="A112" s="20">
+    <row r="113" spans="1:2">
+      <c r="A113" s="19">
         <v>46111</v>
       </c>
-      <c r="B112" s="17">
+      <c r="B113" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -6702,7 +6747,7 @@
       <c r="A2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="17">
         <v>98931.490865999993</v>
       </c>
       <c r="C2" s="1">
@@ -6716,16 +6761,16 @@
       <c r="A3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="17">
         <v>251306.31</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C3" s="17">
         <v>13226.65</v>
       </c>
       <c r="D3">
         <v>188.96</v>
       </c>
-      <c r="G3" s="34" t="s">
+      <c r="G3" s="33" t="s">
         <v>33</v>
       </c>
     </row>
@@ -6733,33 +6778,33 @@
       <c r="A4" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <v>254788.61</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="17">
         <v>13409.93</v>
       </c>
       <c r="D4" s="7">
         <v>245.29</v>
       </c>
-      <c r="G4" s="34" t="s">
+      <c r="G4" s="33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>40192.65</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="17">
         <v>1826.94</v>
       </c>
       <c r="D5" s="7">
         <v>81.88</v>
       </c>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="33" t="s">
         <v>35</v>
       </c>
     </row>
@@ -6767,7 +6812,7 @@
       <c r="A6" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <v>10939.03</v>
       </c>
       <c r="C6" s="7">
@@ -6785,7 +6830,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -6959,10 +7004,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1">
-      <c r="A16" s="26">
+      <c r="A16" s="25">
         <v>46136</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="17">
         <v>1206629034.17156</v>
       </c>
       <c r="C16" s="4">
@@ -6970,11 +7015,11 @@
         <v>12.607640378286277</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" thickBot="1">
-      <c r="A17" s="26">
+    <row r="17" spans="1:5" ht="15" thickBot="1">
+      <c r="A17" s="25">
         <v>46164</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="17">
         <v>1440966613.4014599</v>
       </c>
       <c r="C17" s="4">
@@ -6982,11 +7027,11 @@
         <v>19.42084705352627</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" thickBot="1">
-      <c r="A18" s="26">
+    <row r="18" spans="1:5" ht="15" thickBot="1">
+      <c r="A18" s="25">
         <v>46171</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <v>1452167458.20135</v>
       </c>
       <c r="C18" s="4">
@@ -6994,11 +7039,11 @@
         <v>0.77731466473397282</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" thickBot="1">
-      <c r="A19" s="26">
+    <row r="19" spans="1:5" ht="15" thickBot="1">
+      <c r="A19" s="25">
         <v>46178</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="17">
         <v>1583302878.3216901</v>
       </c>
       <c r="C19" s="4">
@@ -7006,11 +7051,11 @@
         <v>9.0303235608077888</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" thickBot="1">
-      <c r="A20" s="26">
+    <row r="20" spans="1:5" ht="15" thickBot="1">
+      <c r="A20" s="25">
         <v>46185</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="17">
         <v>1491369041.2082701</v>
       </c>
       <c r="C20" s="4">
@@ -7018,11 +7063,11 @@
         <v>-5.8064592929225514</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" thickBot="1">
-      <c r="A21" s="26">
+    <row r="21" spans="1:5" ht="15" thickBot="1">
+      <c r="A21" s="25">
         <v>46192</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="17">
         <v>1486232648.3692801</v>
       </c>
       <c r="C21" s="4">
@@ -7030,11 +7075,11 @@
         <v>-0.34440790287751955</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" thickBot="1">
-      <c r="A22" s="26">
+    <row r="22" spans="1:5" ht="15" thickBot="1">
+      <c r="A22" s="25">
         <v>46199</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="17">
         <v>1396607027.6049099</v>
       </c>
       <c r="C22" s="4">
@@ -7042,11 +7087,11 @@
         <v>-6.0303897147400827</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" thickBot="1">
-      <c r="A23" s="26">
+    <row r="23" spans="1:5" ht="15" thickBot="1">
+      <c r="A23" s="25">
         <v>46227</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="17">
         <v>1468051657.5950301</v>
       </c>
       <c r="C23" s="4">
@@ -7054,11 +7099,11 @@
         <v>5.1155857430162772</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" thickBot="1">
-      <c r="A24" s="26">
+    <row r="24" spans="1:5" ht="15" thickBot="1">
+      <c r="A24" s="25">
         <v>46255</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="17">
         <v>1588746455.7100201</v>
       </c>
       <c r="C24" s="4">
@@ -7066,17 +7111,21 @@
         <v>8.2214271882443732</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" thickBot="1">
-      <c r="A25" s="26">
+    <row r="25" spans="1:5" ht="15" thickBot="1">
+      <c r="A25" s="25">
         <v>46262</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="17">
         <v>1616236987.2485399</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="0"/>
         <v>1.730328425893116</v>
       </c>
+      <c r="E25" s="38"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="E26" s="38"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7259,496 +7308,496 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="26">
+      <c r="A7" s="25">
         <v>46143</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="17">
         <v>56289349.634710021</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="17">
         <v>1572208957.4513197</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>131632832.49728999</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>1760131139.5833197</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <v>1480052.1803799996</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <v>1761611191.7636998</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="27">
         <v>9.2253839605925378</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="26">
+      <c r="A8" s="25">
         <v>46150</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="17">
         <v>56976115.061530016</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="17">
         <v>1583444536.3055906</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>120943453.33754002</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>1761364104.7046607</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>1443633.0552200002</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <v>1762807737.7598805</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <v>6.7923387508850297E-2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="26">
+      <c r="A9" s="25">
         <v>46157</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="17">
         <v>57191389.678870022</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="17">
         <v>1736713788.0136802</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>154232219.13352999</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="17">
         <v>1948137396.8260801</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <v>1517284.0840200002</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <v>1949654680.9101</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="27">
         <v>10.599394315551303</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="26">
+      <c r="A10" s="25">
         <v>46164</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="17">
         <v>59297253.722750016</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="17">
         <v>1756395281.4472902</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>146574089.18363994</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>1962266624.3536801</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <v>1598030.6558000003</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <v>1963864655.0094802</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="27">
         <v>0.72884568936828487</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="26">
+      <c r="A11" s="25">
         <v>46202</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="17">
         <v>61835356.210640013</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="17">
         <v>1886607672.3299406</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>163572012.59929004</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>2112015041.1398706</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>1706770.0237499999</v>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <v>2113721811.1636207</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="27">
         <v>7.6307272892701832</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="26">
+      <c r="A12" s="25">
         <v>46178</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="17">
         <v>63931654.937720016</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <v>1957457867.6445699</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <v>149657684.68581003</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="17">
         <v>2171047207.2680998</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <v>1753411.3252600001</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <v>2172800618.5933599</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="27">
         <v>2.7950133796091023</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="26">
+      <c r="A13" s="25">
         <v>46185</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="17">
         <v>63611606.013210006</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <v>1879421568.1788502</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <v>133033132.39342</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="17">
         <v>2076066306.5854802</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <v>1714526.8965600003</v>
       </c>
-      <c r="G13" s="18">
+      <c r="G13" s="17">
         <v>2077780833.4820399</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="27">
         <v>-4.3731479224649092</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="26">
+      <c r="A14" s="25">
         <v>46192</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="17">
         <v>65860434.967950001</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>1914988346.0565095</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <v>162309932.49878004</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="17">
         <v>2143158713.5232396</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <v>1705432.2701800002</v>
       </c>
-      <c r="G14" s="18">
+      <c r="G14" s="17">
         <v>2144864145.7934194</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="27">
         <v>3.2286038657387337</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="26">
+      <c r="A15" s="25">
         <v>46199</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="17">
         <v>66643069.210480012</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="17">
         <v>1865343448.3990905</v>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="17">
         <v>172370820.8464765</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="17">
         <v>2104357338.4560471</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="17">
         <v>1885890.7660000003</v>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="17">
         <v>2106243229.2220471</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="27">
         <v>-1.8006229740525441</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="26">
+      <c r="A16" s="25">
         <v>46206</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="17">
         <v>68376322.198670015</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="17">
         <v>1874824600.7037601</v>
       </c>
-      <c r="D16" s="18">
+      <c r="D16" s="17">
         <v>187900609.12325659</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <v>2131101532.0256867</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="17">
         <v>2089309.7912699997</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="17">
         <v>2133190841.8169568</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="27">
         <v>1.2794159867691519</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="26">
+      <c r="A17" s="25">
         <v>46213</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="17">
         <v>68487199.928740025</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="17">
         <v>1899748731.1160312</v>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="17">
         <v>162301220.45412648</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>2130537151.4988976</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>2464039.5699600005</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="17">
         <v>2133001191.0688577</v>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="27">
         <v>-8.8904726375744758E-3</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="26">
+      <c r="A18" s="25">
         <v>46220</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="17">
         <v>69757899.158520013</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <v>2038826282.5316811</v>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="17">
         <v>217968687.7986365</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <v>2326552869.4888377</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <v>2029339.0808599996</v>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="17">
         <v>2328582208.5696979</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="27">
         <v>9.1692877772296697</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="26">
+      <c r="A19" s="25">
         <v>46227</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="17">
         <v>71935096.137300014</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <v>2094704967.8231509</v>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="17">
         <v>222110560.74773642</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <v>2388750624.7081876</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <v>2133572.8824000005</v>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="17">
         <v>2390884197.5905876</v>
       </c>
-      <c r="H19" s="28">
+      <c r="H19" s="27">
         <v>2.6755331545351737</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="26">
+      <c r="A20" s="25">
         <v>46234</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="17">
         <v>73562982.041420013</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="17">
         <v>2158280622.777401</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="17">
         <v>232842453.77054653</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="17">
         <v>2464686058.5893674</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="17">
         <v>2259648.3903599996</v>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="17">
         <v>2466945706.9797273</v>
       </c>
-      <c r="H20" s="28">
+      <c r="H20" s="27">
         <v>3.1813129831127327</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="26">
+      <c r="A21" s="25">
         <v>46241</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="17">
         <v>74588465.34969002</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="17">
         <v>2167193538.7617316</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="17">
         <v>198439181.48875651</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="17">
         <v>2440221185.6001782</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="17">
         <v>2971243.6223900001</v>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="17">
         <v>2443192429.222568</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="27">
         <v>-0.96286179667246508</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="26">
+      <c r="A22" s="25">
         <v>46248</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="17">
         <v>74239926.334400013</v>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="17">
         <v>2163040890.6203313</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="17">
         <v>208734334.00143653</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="17">
         <v>2446015150.9561682</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="17">
         <v>2159689.0630499991</v>
       </c>
-      <c r="G22" s="18">
+      <c r="G22" s="17">
         <v>2448174840.0192175</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="27">
         <v>0.2039303469123297</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="26">
+      <c r="A23" s="25">
         <v>46255</v>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="17">
         <v>76026162.824400008</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="17">
         <v>2297157294.4069014</v>
       </c>
-      <c r="D23" s="18">
+      <c r="D23" s="17">
         <v>212317214.11852658</v>
       </c>
-      <c r="E23" s="18">
+      <c r="E23" s="17">
         <v>2585500671.3498278</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="17">
         <v>2182911.8923299997</v>
       </c>
-      <c r="G23" s="18">
+      <c r="G23" s="17">
         <v>2587683583.2421579</v>
       </c>
-      <c r="H23" s="28">
+      <c r="H23" s="27">
         <v>5.6984795751697845</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="26">
+      <c r="A24" s="25">
         <v>46262</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="17">
         <v>78436320.980450019</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <v>2368853653.2673907</v>
       </c>
-      <c r="D24" s="18">
+      <c r="D24" s="17">
         <v>221939034.59143993</v>
       </c>
-      <c r="E24" s="18">
+      <c r="E24" s="17">
         <v>2669229008.8392806</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="17">
         <v>2363869.91811</v>
       </c>
-      <c r="G24" s="18">
+      <c r="G24" s="17">
         <v>2671592878.7573905</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="27">
         <v>3.2456431709609603</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="26">
+      <c r="A25" s="25">
         <v>46269</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="17">
         <v>79934788.226620004</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="17">
         <v>2449226669.3992906</v>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="17">
         <v>220761212.62711993</v>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="17">
         <v>2749922670.2530308</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="17">
         <v>2498658.4271799996</v>
       </c>
-      <c r="G25" s="18">
+      <c r="G25" s="17">
         <v>2752421328.6802111</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="27">
         <v>3.0254778175788317</v>
       </c>
     </row>
@@ -7759,7 +7808,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -7803,11 +7852,11 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2" s="32" t="e">
+      <c r="E2" s="31" t="e">
         <f t="shared" ref="E2:E17" si="0">+((D2-D1)/D1)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="F2" s="33">
+      <c r="F2" s="32">
         <v>-0.03</v>
       </c>
     </row>
@@ -7824,11 +7873,11 @@
       <c r="D3">
         <v>13741</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="31">
         <f t="shared" si="0"/>
         <v>4.8691139433717466E-2</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="32">
         <v>0.05</v>
       </c>
     </row>
@@ -7845,11 +7894,11 @@
       <c r="D4">
         <v>13589</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="31">
         <f t="shared" si="0"/>
         <v>-1.1061785896222982E-2</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="32">
         <v>-0.01</v>
       </c>
     </row>
@@ -7866,11 +7915,11 @@
       <c r="D5">
         <v>13674</v>
       </c>
-      <c r="E5" s="32">
+      <c r="E5" s="31">
         <f t="shared" si="0"/>
         <v>6.2550592390904405E-3</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="32">
         <v>0.01</v>
       </c>
     </row>
@@ -7887,11 +7936,11 @@
       <c r="D6">
         <v>13484</v>
       </c>
-      <c r="E6" s="32">
+      <c r="E6" s="31">
         <f t="shared" si="0"/>
         <v>-1.3894983179757204E-2</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="32">
         <v>-0.01</v>
       </c>
     </row>
@@ -7908,11 +7957,11 @@
       <c r="D7">
         <v>13460</v>
       </c>
-      <c r="E7" s="32">
+      <c r="E7" s="31">
         <f t="shared" si="0"/>
         <v>-1.7798872738059924E-3</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="32">
         <v>-0.01</v>
       </c>
     </row>
@@ -7929,11 +7978,11 @@
       <c r="D8">
         <v>13253</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="31">
         <f t="shared" si="0"/>
         <v>-1.5378900445765229E-2</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="32">
         <v>-0.01</v>
       </c>
     </row>
@@ -7950,11 +7999,11 @@
       <c r="D9">
         <v>13187</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="31">
         <f t="shared" si="0"/>
         <v>-4.9800045272768434E-3</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="32">
         <v>-0.01</v>
       </c>
     </row>
@@ -7971,11 +8020,11 @@
       <c r="D10">
         <v>13280</v>
       </c>
-      <c r="E10" s="32">
+      <c r="E10" s="31">
         <f t="shared" si="0"/>
         <v>7.0524000909987106E-3</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="32">
         <v>-0.01</v>
       </c>
       <c r="G10" s="7"/>
@@ -7993,11 +8042,11 @@
       <c r="D11">
         <v>14061</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="31">
         <f t="shared" si="0"/>
         <v>5.8810240963855419E-2</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="32">
         <v>-0.01</v>
       </c>
     </row>
@@ -8014,1862 +8063,1886 @@
       <c r="D12" s="12">
         <v>13872</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="31">
         <f t="shared" si="0"/>
         <v>-1.3441433752933647E-2</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="32">
         <v>-0.01</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="26">
+      <c r="A13" s="25">
         <v>46148</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="26">
         <v>13411</v>
       </c>
-      <c r="C13" s="25">
-        <v>3</v>
-      </c>
-      <c r="D13" s="27">
+      <c r="C13" s="24">
+        <v>3</v>
+      </c>
+      <c r="D13" s="26">
         <v>13414</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="31">
         <f t="shared" si="0"/>
         <v>-3.3016147635524795E-2</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="32">
         <v>-0.123456</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="26">
+      <c r="A14" s="25">
         <v>46149</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="26">
         <v>13460</v>
       </c>
-      <c r="C14" s="25">
-        <v>3</v>
-      </c>
-      <c r="D14" s="27">
+      <c r="C14" s="24">
+        <v>3</v>
+      </c>
+      <c r="D14" s="26">
         <v>13463</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="31">
         <f t="shared" si="0"/>
         <v>3.6528999552706129E-3</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="32">
         <v>0.37123455999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="26">
+      <c r="A15" s="25">
         <v>46150</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="26">
         <v>13398</v>
       </c>
-      <c r="C15" s="25">
-        <v>3</v>
-      </c>
-      <c r="D15" s="27">
+      <c r="C15" s="24">
+        <v>3</v>
+      </c>
+      <c r="D15" s="26">
         <v>13401</v>
       </c>
-      <c r="E15" s="32">
+      <c r="E15" s="31">
         <f t="shared" si="0"/>
         <v>-4.6052142910198322E-3</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="32">
         <v>-0.46123456000000002</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="26">
+      <c r="A16" s="25">
         <v>46153</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="26">
         <v>13309</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
-      <c r="D16" s="27">
+      <c r="D16" s="26">
         <v>13312</v>
       </c>
-      <c r="E16" s="32">
+      <c r="E16" s="31">
         <f t="shared" si="0"/>
         <v>-6.6412954257144986E-3</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="32">
         <v>-0.66123456000000003</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="26">
+      <c r="A17" s="25">
         <v>46154</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="26">
         <v>13300</v>
       </c>
-      <c r="C17" s="25">
-        <v>3</v>
-      </c>
-      <c r="D17" s="27">
+      <c r="C17" s="24">
+        <v>3</v>
+      </c>
+      <c r="D17" s="26">
         <v>13303</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="31">
         <f t="shared" si="0"/>
         <v>-6.7608173076923075E-4</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="32">
         <v>-7.1234560000000002E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="26">
+      <c r="A18" s="25">
         <v>46155</v>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="26">
         <v>13277</v>
       </c>
-      <c r="C18" s="25">
-        <v>3</v>
-      </c>
-      <c r="D18" s="27">
+      <c r="C18" s="24">
+        <v>3</v>
+      </c>
+      <c r="D18" s="26">
         <v>13280</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="31">
         <f>+((D18-D17)/D17)</f>
         <v>-1.7289333233105315E-3</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="32">
         <v>-0.17123456000000001</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="26">
+      <c r="A19" s="25">
         <v>46156</v>
       </c>
-      <c r="B19" s="27">
+      <c r="B19" s="26">
         <v>13282</v>
       </c>
-      <c r="C19" s="25">
-        <v>3</v>
-      </c>
-      <c r="D19" s="27">
+      <c r="C19" s="24">
+        <v>3</v>
+      </c>
+      <c r="D19" s="26">
         <f t="shared" ref="D19" si="1">SUM(B19+C19)</f>
         <v>13285</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="31">
         <f>+((D19-D18)/D18)</f>
         <v>3.7650602409638556E-4</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="32">
         <v>4.1234560000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="26">
+      <c r="A20" s="25">
         <v>46157</v>
       </c>
-      <c r="B20" s="27">
+      <c r="B20" s="26">
         <v>13015</v>
       </c>
-      <c r="C20" s="25">
-        <v>3</v>
-      </c>
-      <c r="D20" s="27">
+      <c r="C20" s="24">
+        <v>3</v>
+      </c>
+      <c r="D20" s="26">
         <v>13018</v>
       </c>
-      <c r="E20" s="32">
+      <c r="E20" s="31">
         <f>+((D20-D19)/D19)</f>
         <v>-2.0097854723372225E-2</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="32">
         <v>-2.0112345600000001</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="26">
+      <c r="A21" s="25">
         <v>46161</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="26">
         <v>12992</v>
       </c>
-      <c r="C21" s="25">
-        <v>3</v>
-      </c>
-      <c r="D21" s="27">
+      <c r="C21" s="24">
+        <v>3</v>
+      </c>
+      <c r="D21" s="26">
         <v>12995</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="31">
         <f>+((D21-D20)/D20)</f>
         <v>-1.7667844522968198E-3</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="32">
         <v>-0.18123455999999999</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="26">
+      <c r="A22" s="25">
         <v>46162</v>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="26">
         <v>12888</v>
       </c>
-      <c r="C22" s="25">
-        <v>3</v>
-      </c>
-      <c r="D22" s="27">
+      <c r="C22" s="24">
+        <v>3</v>
+      </c>
+      <c r="D22" s="26">
         <v>12891</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="31">
         <f>+((D22-D21)/D21)</f>
         <v>-8.0030781069642173E-3</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="32">
         <v>-0.80123456000000004</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="26">
+      <c r="A23" s="25">
         <v>46163</v>
       </c>
-      <c r="B23" s="27">
+      <c r="B23" s="26">
         <v>14686</v>
       </c>
-      <c r="C23" s="25">
-        <v>3</v>
-      </c>
-      <c r="D23" s="27">
+      <c r="C23" s="24">
+        <v>3</v>
+      </c>
+      <c r="D23" s="26">
         <v>14689</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="31">
         <f t="shared" ref="E23:E24" si="2">+((D23-D22)/D22)</f>
         <v>0.13947715460398727</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="32">
         <v>13.95123456</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="26">
+      <c r="A24" s="25">
         <v>46164</v>
       </c>
-      <c r="B24" s="27">
+      <c r="B24" s="26">
         <v>14649</v>
       </c>
-      <c r="C24" s="25">
-        <v>3</v>
-      </c>
-      <c r="D24" s="27">
+      <c r="C24" s="24">
+        <v>3</v>
+      </c>
+      <c r="D24" s="26">
         <v>14652</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="31">
         <f t="shared" si="2"/>
         <v>-2.5188916876574307E-3</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="32">
         <v>-0.25123456</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="26">
+      <c r="A25" s="25">
         <v>46167</v>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="26">
         <v>12949</v>
       </c>
-      <c r="C25" s="25">
-        <v>3</v>
-      </c>
-      <c r="D25" s="27">
+      <c r="C25" s="24">
+        <v>3</v>
+      </c>
+      <c r="D25" s="26">
         <v>12952</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="31">
         <f t="shared" ref="E25:E75" si="3">+((D25-D24)/D24)</f>
         <v>-0.11602511602511603</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="32">
         <v>-11.60123456</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="26">
+      <c r="A26" s="25">
         <v>46168</v>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="26">
         <v>12961</v>
       </c>
-      <c r="C26" s="25">
-        <v>3</v>
-      </c>
-      <c r="D26" s="27">
+      <c r="C26" s="24">
+        <v>3</v>
+      </c>
+      <c r="D26" s="26">
         <v>12964</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="31">
         <f t="shared" si="3"/>
         <v>9.2649783817171094E-4</v>
       </c>
-      <c r="F26" s="33">
+      <c r="F26" s="32">
         <v>9.1234560000000006E-2</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="26">
+      <c r="A27" s="25">
         <v>46169</v>
       </c>
-      <c r="B27" s="27">
+      <c r="B27" s="26">
         <v>12914</v>
       </c>
-      <c r="C27" s="25">
-        <v>3</v>
-      </c>
-      <c r="D27" s="27">
+      <c r="C27" s="24">
+        <v>3</v>
+      </c>
+      <c r="D27" s="26">
         <v>12917</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="31">
         <f t="shared" si="3"/>
         <v>-3.625424251774144E-3</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="32">
         <v>-0.36</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="26">
+      <c r="A28" s="25">
         <v>46170</v>
       </c>
-      <c r="B28" s="27">
+      <c r="B28" s="26">
         <v>12758</v>
       </c>
-      <c r="C28" s="25">
-        <v>3</v>
-      </c>
-      <c r="D28" s="27">
+      <c r="C28" s="24">
+        <v>3</v>
+      </c>
+      <c r="D28" s="26">
         <v>12761</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="31">
         <f t="shared" si="3"/>
         <v>-1.2077107687543547E-2</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="32">
         <v>-1.21</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="26">
+      <c r="A29" s="25">
         <v>46171</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="26">
         <v>12968</v>
       </c>
-      <c r="C29" s="25">
-        <v>3</v>
-      </c>
-      <c r="D29" s="27">
+      <c r="C29" s="24">
+        <v>3</v>
+      </c>
+      <c r="D29" s="26">
         <v>12971</v>
       </c>
-      <c r="E29" s="32">
+      <c r="E29" s="31">
         <f t="shared" si="3"/>
         <v>1.6456390565002744E-2</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="32">
         <v>1.65</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="26">
+      <c r="A30" s="25">
         <v>46174</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>12916</v>
       </c>
-      <c r="C30" s="25">
-        <v>3</v>
-      </c>
-      <c r="D30" s="27">
+      <c r="C30" s="24">
+        <v>3</v>
+      </c>
+      <c r="D30" s="26">
         <v>12919</v>
       </c>
-      <c r="E30" s="32">
+      <c r="E30" s="31">
         <f t="shared" si="3"/>
         <v>-4.0089430267519852E-3</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="32">
         <v>-0.4</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="26">
+      <c r="A31" s="25">
         <v>46175</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="26">
         <v>12982</v>
       </c>
-      <c r="C31" s="25">
-        <v>3</v>
-      </c>
-      <c r="D31" s="27">
+      <c r="C31" s="24">
+        <v>3</v>
+      </c>
+      <c r="D31" s="26">
         <v>12985</v>
       </c>
-      <c r="E31" s="32">
+      <c r="E31" s="31">
         <f t="shared" si="3"/>
         <v>5.1087545475656014E-3</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="32">
         <v>0.51</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="26">
+      <c r="A32" s="25">
         <v>46176</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>12852</v>
       </c>
-      <c r="C32" s="25">
-        <v>3</v>
-      </c>
-      <c r="D32" s="27">
+      <c r="C32" s="24">
+        <v>3</v>
+      </c>
+      <c r="D32" s="26">
         <v>12855</v>
       </c>
-      <c r="E32" s="32">
+      <c r="E32" s="31">
         <f t="shared" si="3"/>
         <v>-1.0011551790527531E-2</v>
       </c>
-      <c r="F32" s="33">
+      <c r="F32" s="32">
         <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="26">
+      <c r="A33" s="25">
         <v>46177</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="26">
         <v>12861</v>
       </c>
-      <c r="C33" s="25">
-        <v>3</v>
-      </c>
-      <c r="D33" s="27">
+      <c r="C33" s="24">
+        <v>3</v>
+      </c>
+      <c r="D33" s="26">
         <v>12864</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="31">
         <f t="shared" si="3"/>
         <v>7.0011668611435238E-4</v>
       </c>
-      <c r="F33" s="33">
+      <c r="F33" s="32">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="26">
+      <c r="A34" s="25">
         <v>46178</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>12861</v>
       </c>
-      <c r="C34" s="25">
-        <v>3</v>
-      </c>
-      <c r="D34" s="27">
+      <c r="C34" s="24">
+        <v>3</v>
+      </c>
+      <c r="D34" s="26">
         <v>12864</v>
       </c>
-      <c r="E34" s="32">
+      <c r="E34" s="31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="32">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="26">
+      <c r="A35" s="25">
         <v>46182</v>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="26">
         <v>12645</v>
       </c>
-      <c r="C35" s="25">
-        <v>3</v>
-      </c>
-      <c r="D35" s="27">
+      <c r="C35" s="24">
+        <v>3</v>
+      </c>
+      <c r="D35" s="26">
         <v>12648</v>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="31">
         <f t="shared" si="3"/>
         <v>-1.6791044776119403E-2</v>
       </c>
-      <c r="F35" s="33">
+      <c r="F35" s="32">
         <v>-1.68</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="26">
+      <c r="A36" s="25">
         <v>46183</v>
       </c>
-      <c r="B36" s="27">
+      <c r="B36" s="26">
         <v>12401</v>
       </c>
-      <c r="C36" s="25">
-        <v>3</v>
-      </c>
-      <c r="D36" s="27">
+      <c r="C36" s="24">
+        <v>3</v>
+      </c>
+      <c r="D36" s="26">
         <v>12404</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="31">
         <f t="shared" si="3"/>
         <v>-1.9291587602783048E-2</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F36" s="32">
         <v>-1.93</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="26">
+      <c r="A37" s="25">
         <v>46184</v>
       </c>
-      <c r="B37" s="27">
+      <c r="B37" s="26">
         <v>12260</v>
       </c>
-      <c r="C37" s="25">
-        <v>3</v>
-      </c>
-      <c r="D37" s="27">
+      <c r="C37" s="24">
+        <v>3</v>
+      </c>
+      <c r="D37" s="26">
         <v>12263</v>
       </c>
-      <c r="E37" s="32">
+      <c r="E37" s="31">
         <f t="shared" si="3"/>
         <v>-1.1367300870686875E-2</v>
       </c>
-      <c r="F37" s="33">
+      <c r="F37" s="32">
         <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="26">
+      <c r="A38" s="25">
         <v>46185</v>
       </c>
-      <c r="B38" s="27">
+      <c r="B38" s="26">
         <v>13444</v>
       </c>
-      <c r="C38" s="25">
-        <v>3</v>
-      </c>
-      <c r="D38" s="27">
+      <c r="C38" s="24">
+        <v>3</v>
+      </c>
+      <c r="D38" s="26">
         <v>13447</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="31">
         <f t="shared" si="3"/>
         <v>9.6550599363940309E-2</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="32">
         <v>9.66</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="26">
+      <c r="A39" s="25">
         <v>46188</v>
       </c>
-      <c r="B39" s="27">
+      <c r="B39" s="26">
         <v>13557</v>
       </c>
-      <c r="C39" s="25">
-        <v>3</v>
-      </c>
-      <c r="D39" s="27">
+      <c r="C39" s="24">
+        <v>3</v>
+      </c>
+      <c r="D39" s="26">
         <v>13560</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="31">
         <f t="shared" si="3"/>
         <v>8.4033613445378148E-3</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="32">
         <v>0.84</v>
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="26">
+      <c r="A40" s="25">
         <v>46189</v>
       </c>
-      <c r="B40" s="27">
+      <c r="B40" s="26">
         <v>13566</v>
       </c>
-      <c r="C40" s="25">
-        <v>3</v>
-      </c>
-      <c r="D40" s="27">
+      <c r="C40" s="24">
+        <v>3</v>
+      </c>
+      <c r="D40" s="26">
         <v>13569</v>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="31">
         <f t="shared" si="3"/>
         <v>6.6371681415929203E-4</v>
       </c>
-      <c r="F40" s="33">
+      <c r="F40" s="32">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="26">
+      <c r="A41" s="25">
         <v>46190</v>
       </c>
-      <c r="B41" s="27">
+      <c r="B41" s="26">
         <v>13567</v>
       </c>
-      <c r="C41" s="25">
-        <v>3</v>
-      </c>
-      <c r="D41" s="27">
+      <c r="C41" s="24">
+        <v>3</v>
+      </c>
+      <c r="D41" s="26">
         <v>13570</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="31">
         <f t="shared" si="3"/>
         <v>7.3697398481833586E-5</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="32">
         <v>0.01</v>
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="26">
+      <c r="A42" s="25">
         <v>46191</v>
       </c>
-      <c r="B42" s="27">
+      <c r="B42" s="26">
         <v>13443</v>
       </c>
-      <c r="C42" s="25">
-        <v>3</v>
-      </c>
-      <c r="D42" s="27">
+      <c r="C42" s="24">
+        <v>3</v>
+      </c>
+      <c r="D42" s="26">
         <v>13446</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="31">
         <f t="shared" si="3"/>
         <v>-9.1378039793662495E-3</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="32">
         <v>-0.91</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="26">
+      <c r="A43" s="25">
         <v>46192</v>
       </c>
-      <c r="B43" s="27">
+      <c r="B43" s="26">
         <v>12812</v>
       </c>
-      <c r="C43" s="25">
-        <v>3</v>
-      </c>
-      <c r="D43" s="27">
+      <c r="C43" s="24">
+        <v>3</v>
+      </c>
+      <c r="D43" s="26">
         <v>12815</v>
       </c>
-      <c r="E43" s="32">
+      <c r="E43" s="31">
         <f t="shared" si="3"/>
         <v>-4.6928454558976644E-2</v>
       </c>
-      <c r="F43" s="33">
+      <c r="F43" s="32">
         <v>-4.6900000000000004</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="26">
+      <c r="A44" s="25">
         <v>46195</v>
       </c>
-      <c r="B44" s="27">
+      <c r="B44" s="26">
         <v>14632</v>
       </c>
-      <c r="C44" s="25">
-        <v>3</v>
-      </c>
-      <c r="D44" s="27">
+      <c r="C44" s="24">
+        <v>3</v>
+      </c>
+      <c r="D44" s="26">
         <v>14635</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="31">
         <f t="shared" si="3"/>
         <v>0.14202106905969566</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="32">
         <v>14.2</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="26">
+      <c r="A45" s="25">
         <v>46196</v>
       </c>
-      <c r="B45" s="27">
+      <c r="B45" s="26">
         <v>14497</v>
       </c>
-      <c r="C45" s="25">
-        <v>3</v>
-      </c>
-      <c r="D45" s="27">
+      <c r="C45" s="24">
+        <v>3</v>
+      </c>
+      <c r="D45" s="26">
         <v>14500</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="31">
         <f t="shared" si="3"/>
         <v>-9.2244619063887937E-3</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="32">
         <v>-0.92</v>
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="26">
+      <c r="A46" s="25">
         <v>46198</v>
       </c>
-      <c r="B46" s="27">
+      <c r="B46" s="26">
         <v>14307</v>
       </c>
-      <c r="C46" s="25">
-        <v>3</v>
-      </c>
-      <c r="D46" s="27">
+      <c r="C46" s="24">
+        <v>3</v>
+      </c>
+      <c r="D46" s="26">
         <v>14310</v>
       </c>
-      <c r="E46" s="32">
+      <c r="E46" s="31">
         <f t="shared" si="3"/>
         <v>-1.3103448275862069E-2</v>
       </c>
-      <c r="F46" s="33">
+      <c r="F46" s="32">
         <v>-1.31</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="26">
+      <c r="A47" s="25">
         <v>46199</v>
       </c>
-      <c r="B47" s="27">
+      <c r="B47" s="26">
         <v>13995</v>
       </c>
-      <c r="C47" s="25">
-        <v>3</v>
-      </c>
-      <c r="D47" s="27">
+      <c r="C47" s="24">
+        <v>3</v>
+      </c>
+      <c r="D47" s="26">
         <v>13998</v>
       </c>
-      <c r="E47" s="32">
+      <c r="E47" s="31">
         <f t="shared" si="3"/>
         <v>-2.180293501048218E-2</v>
       </c>
-      <c r="F47" s="33">
+      <c r="F47" s="32">
         <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="26">
+      <c r="A48" s="25">
         <v>46203</v>
       </c>
-      <c r="B48" s="27">
+      <c r="B48" s="26">
         <v>13908</v>
       </c>
-      <c r="C48" s="25">
-        <v>3</v>
-      </c>
-      <c r="D48" s="27">
+      <c r="C48" s="24">
+        <v>3</v>
+      </c>
+      <c r="D48" s="26">
         <v>13911</v>
       </c>
-      <c r="E48" s="32">
+      <c r="E48" s="31">
         <f t="shared" si="3"/>
         <v>-6.2151735962280323E-3</v>
       </c>
-      <c r="F48" s="33">
+      <c r="F48" s="32">
         <v>-0.62</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="26">
+      <c r="A49" s="25">
         <v>46204</v>
       </c>
-      <c r="B49" s="27">
+      <c r="B49" s="26">
         <v>13749</v>
       </c>
-      <c r="C49" s="25">
-        <v>3</v>
-      </c>
-      <c r="D49" s="27">
+      <c r="C49" s="24">
+        <v>3</v>
+      </c>
+      <c r="D49" s="26">
         <v>13752</v>
       </c>
-      <c r="E49" s="32">
+      <c r="E49" s="31">
         <f t="shared" si="3"/>
         <v>-1.1429803752426138E-2</v>
       </c>
-      <c r="F49" s="33">
+      <c r="F49" s="32">
         <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="26">
+      <c r="A50" s="25">
         <v>46205</v>
       </c>
-      <c r="B50" s="27">
+      <c r="B50" s="26">
         <v>13869</v>
       </c>
-      <c r="C50" s="25">
-        <v>3</v>
-      </c>
-      <c r="D50" s="27">
+      <c r="C50" s="24">
+        <v>3</v>
+      </c>
+      <c r="D50" s="26">
         <v>13872</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="31">
         <f t="shared" si="3"/>
         <v>8.7260034904013961E-3</v>
       </c>
-      <c r="F50" s="33">
+      <c r="F50" s="32">
         <v>0.87</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="26">
+      <c r="A51" s="25">
         <v>46206</v>
       </c>
-      <c r="B51" s="27">
+      <c r="B51" s="26">
         <v>13495</v>
       </c>
-      <c r="C51" s="25">
-        <v>3</v>
-      </c>
-      <c r="D51" s="27">
+      <c r="C51" s="24">
+        <v>3</v>
+      </c>
+      <c r="D51" s="26">
         <v>13498</v>
       </c>
-      <c r="E51" s="32">
+      <c r="E51" s="31">
         <f t="shared" si="3"/>
         <v>-2.6960784313725492E-2</v>
       </c>
-      <c r="F51" s="33">
+      <c r="F51" s="32">
         <v>-2.7</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="26">
+      <c r="A52" s="25">
         <v>46209</v>
       </c>
-      <c r="B52" s="27">
+      <c r="B52" s="26">
         <v>13393</v>
       </c>
-      <c r="C52" s="25">
-        <v>3</v>
-      </c>
-      <c r="D52" s="27">
+      <c r="C52" s="24">
+        <v>3</v>
+      </c>
+      <c r="D52" s="26">
         <v>13396</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52" s="31">
         <f t="shared" si="3"/>
         <v>-7.556675062972292E-3</v>
       </c>
-      <c r="F52" s="33">
+      <c r="F52" s="32">
         <v>-0.76</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="26">
+      <c r="A53" s="25">
         <v>46210</v>
       </c>
-      <c r="B53" s="27">
+      <c r="B53" s="26">
         <v>13475</v>
       </c>
-      <c r="C53" s="25">
-        <v>3</v>
-      </c>
-      <c r="D53" s="27">
+      <c r="C53" s="24">
+        <v>3</v>
+      </c>
+      <c r="D53" s="26">
         <v>13478</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="31">
         <f t="shared" si="3"/>
         <v>6.1212302179755153E-3</v>
       </c>
-      <c r="F53" s="33">
+      <c r="F53" s="32">
         <v>0.61</v>
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="26">
+      <c r="A54" s="25">
         <v>46211</v>
       </c>
-      <c r="B54" s="27">
+      <c r="B54" s="26">
         <v>13365</v>
       </c>
-      <c r="C54" s="25">
-        <v>3</v>
-      </c>
-      <c r="D54" s="27">
+      <c r="C54" s="24">
+        <v>3</v>
+      </c>
+      <c r="D54" s="26">
         <v>13368</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="31">
         <f t="shared" si="3"/>
         <v>-8.1614482860958605E-3</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="32">
         <v>-0.82</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="26">
+      <c r="A55" s="25">
         <v>46212</v>
       </c>
-      <c r="B55" s="27">
+      <c r="B55" s="26">
         <v>13447</v>
       </c>
-      <c r="C55" s="25">
-        <v>3</v>
-      </c>
-      <c r="D55" s="27">
+      <c r="C55" s="24">
+        <v>3</v>
+      </c>
+      <c r="D55" s="26">
         <v>13450</v>
       </c>
-      <c r="E55" s="32">
+      <c r="E55" s="31">
         <f t="shared" si="3"/>
         <v>6.1340514661879118E-3</v>
       </c>
-      <c r="F55" s="33">
+      <c r="F55" s="32">
         <v>0.61</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="26">
+      <c r="A56" s="25">
         <v>46213</v>
       </c>
-      <c r="B56" s="27">
+      <c r="B56" s="26">
         <v>13286</v>
       </c>
-      <c r="C56" s="25">
-        <v>3</v>
-      </c>
-      <c r="D56" s="27">
+      <c r="C56" s="24">
+        <v>3</v>
+      </c>
+      <c r="D56" s="26">
         <v>13289</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="31">
         <f t="shared" si="3"/>
         <v>-1.1970260223048328E-2</v>
       </c>
-      <c r="F56" s="33">
+      <c r="F56" s="32">
         <v>-1.2</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="26">
+      <c r="A57" s="25">
         <v>46216</v>
       </c>
-      <c r="B57" s="27">
+      <c r="B57" s="26">
         <v>13313</v>
       </c>
-      <c r="C57" s="25">
-        <v>3</v>
-      </c>
-      <c r="D57" s="27">
+      <c r="C57" s="24">
+        <v>3</v>
+      </c>
+      <c r="D57" s="26">
         <v>13316</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="31">
         <f t="shared" si="3"/>
         <v>2.0317555873278653E-3</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="32">
         <v>0.2</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="26">
+      <c r="A58" s="25">
         <v>46217</v>
       </c>
-      <c r="B58" s="27">
+      <c r="B58" s="26">
         <v>13191</v>
       </c>
-      <c r="C58" s="25">
-        <v>3</v>
-      </c>
-      <c r="D58" s="27">
+      <c r="C58" s="24">
+        <v>3</v>
+      </c>
+      <c r="D58" s="26">
         <v>13194</v>
       </c>
-      <c r="E58" s="32">
+      <c r="E58" s="31">
         <f t="shared" si="3"/>
         <v>-9.1619104836287175E-3</v>
       </c>
-      <c r="F58" s="33">
+      <c r="F58" s="32">
         <v>-0.92</v>
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="26">
+      <c r="A59" s="25">
         <v>46218</v>
       </c>
-      <c r="B59" s="27">
+      <c r="B59" s="26">
         <v>13192</v>
       </c>
-      <c r="C59" s="25">
-        <v>3</v>
-      </c>
-      <c r="D59" s="27">
+      <c r="C59" s="24">
+        <v>3</v>
+      </c>
+      <c r="D59" s="26">
         <v>13195</v>
       </c>
-      <c r="E59" s="32">
+      <c r="E59" s="31">
         <f t="shared" si="3"/>
         <v>7.5792026678793393E-5</v>
       </c>
-      <c r="F59" s="33">
+      <c r="F59" s="32">
         <v>0.01</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="26">
+      <c r="A60" s="25">
         <v>46219</v>
       </c>
-      <c r="B60" s="27">
+      <c r="B60" s="26">
         <v>13206</v>
       </c>
-      <c r="C60" s="25">
-        <v>3</v>
-      </c>
-      <c r="D60" s="27">
+      <c r="C60" s="24">
+        <v>3</v>
+      </c>
+      <c r="D60" s="26">
         <v>13209</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60" s="31">
         <f t="shared" si="3"/>
         <v>1.0610079575596816E-3</v>
       </c>
-      <c r="F60" s="33">
+      <c r="F60" s="32">
         <v>0.11</v>
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="26">
+      <c r="A61" s="25">
         <v>46220</v>
       </c>
-      <c r="B61" s="27">
+      <c r="B61" s="26">
         <v>13769</v>
       </c>
-      <c r="C61" s="25">
-        <v>3</v>
-      </c>
-      <c r="D61" s="27">
+      <c r="C61" s="24">
+        <v>3</v>
+      </c>
+      <c r="D61" s="26">
         <v>13772</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="31">
         <f t="shared" si="3"/>
         <v>4.2622454387160266E-2</v>
       </c>
-      <c r="F61" s="33">
+      <c r="F61" s="32">
         <v>4.26</v>
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="26">
+      <c r="A62" s="25">
         <v>46223</v>
       </c>
-      <c r="B62" s="27">
+      <c r="B62" s="26">
         <v>13591</v>
       </c>
-      <c r="C62" s="25">
-        <v>3</v>
-      </c>
-      <c r="D62" s="27">
+      <c r="C62" s="24">
+        <v>3</v>
+      </c>
+      <c r="D62" s="26">
         <v>13594</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="31">
         <f t="shared" si="3"/>
         <v>-1.2924774905605577E-2</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="32">
         <v>-1.26</v>
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="26">
+      <c r="A63" s="25">
         <v>46224</v>
       </c>
-      <c r="B63" s="27">
+      <c r="B63" s="26">
         <v>13510</v>
       </c>
-      <c r="C63" s="25">
-        <v>3</v>
-      </c>
-      <c r="D63" s="27">
+      <c r="C63" s="24">
+        <v>3</v>
+      </c>
+      <c r="D63" s="26">
         <v>13513</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="31">
         <f t="shared" si="3"/>
         <v>-5.9585111078416944E-3</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="32">
         <v>-0.6</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="26">
+      <c r="A64" s="25">
         <v>46225</v>
       </c>
-      <c r="B64" s="27">
+      <c r="B64" s="26">
         <v>13589</v>
       </c>
-      <c r="C64" s="25">
-        <v>3</v>
-      </c>
-      <c r="D64" s="27">
+      <c r="C64" s="24">
+        <v>3</v>
+      </c>
+      <c r="D64" s="26">
         <v>13592</v>
       </c>
-      <c r="E64" s="32">
+      <c r="E64" s="31">
         <f t="shared" si="3"/>
         <v>5.8462221564419452E-3</v>
       </c>
-      <c r="F64" s="33">
+      <c r="F64" s="32">
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="26">
+      <c r="A65" s="25">
         <v>46226</v>
       </c>
-      <c r="B65" s="27">
+      <c r="B65" s="26">
         <v>13361</v>
       </c>
-      <c r="C65" s="25">
-        <v>3</v>
-      </c>
-      <c r="D65" s="27">
+      <c r="C65" s="24">
+        <v>3</v>
+      </c>
+      <c r="D65" s="26">
         <v>13364</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="31">
         <f t="shared" si="3"/>
         <v>-1.6774573278399058E-2</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="32">
         <v>-1.58</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="26">
+      <c r="A66" s="25">
         <v>46230</v>
       </c>
-      <c r="B66" s="27">
+      <c r="B66" s="26">
         <v>13208</v>
       </c>
-      <c r="C66" s="25">
-        <v>3</v>
-      </c>
-      <c r="D66" s="27">
+      <c r="C66" s="24">
+        <v>3</v>
+      </c>
+      <c r="D66" s="26">
         <v>13211</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="31">
         <f t="shared" si="3"/>
         <v>-1.1448668063454055E-2</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="32">
         <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="26">
+      <c r="A67" s="25">
         <v>46231</v>
       </c>
-      <c r="B67" s="27">
+      <c r="B67" s="26">
         <v>13105</v>
       </c>
-      <c r="C67" s="25">
-        <v>3</v>
-      </c>
-      <c r="D67" s="27">
+      <c r="C67" s="24">
+        <v>3</v>
+      </c>
+      <c r="D67" s="26">
         <v>13108</v>
       </c>
-      <c r="E67" s="32">
+      <c r="E67" s="31">
         <f t="shared" si="3"/>
         <v>-7.7965331920369389E-3</v>
       </c>
-      <c r="F67" s="33">
+      <c r="F67" s="32">
         <v>-0.78</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="26">
+      <c r="A68" s="25">
         <v>46232</v>
       </c>
-      <c r="B68" s="27">
+      <c r="B68" s="26">
         <v>12971</v>
       </c>
-      <c r="C68" s="25">
-        <v>3</v>
-      </c>
-      <c r="D68" s="27">
+      <c r="C68" s="24">
+        <v>3</v>
+      </c>
+      <c r="D68" s="26">
         <v>12974</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="31">
         <f t="shared" si="3"/>
         <v>-1.0222764723832774E-2</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="32">
         <v>-1.02</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="26">
+      <c r="A69" s="25">
         <v>46233</v>
       </c>
-      <c r="B69" s="27">
+      <c r="B69" s="26">
         <v>13004</v>
       </c>
-      <c r="C69" s="25">
-        <v>3</v>
-      </c>
-      <c r="D69" s="27">
+      <c r="C69" s="24">
+        <v>3</v>
+      </c>
+      <c r="D69" s="26">
         <v>13007</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="31">
         <f t="shared" si="3"/>
         <v>2.5435486357330045E-3</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="32">
         <v>0.25</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="26">
+      <c r="A70" s="25">
         <v>46234</v>
       </c>
-      <c r="B70" s="27">
+      <c r="B70" s="26">
         <v>12822</v>
       </c>
-      <c r="C70" s="25">
-        <v>3</v>
-      </c>
-      <c r="D70" s="27">
+      <c r="C70" s="24">
+        <v>3</v>
+      </c>
+      <c r="D70" s="26">
         <v>12825</v>
       </c>
-      <c r="E70" s="32">
+      <c r="E70" s="31">
         <f t="shared" si="3"/>
         <v>-1.3992465595448604E-2</v>
       </c>
-      <c r="F70" s="33">
+      <c r="F70" s="32">
         <v>-1.4</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="26">
+      <c r="A71" s="25">
         <v>46237</v>
       </c>
-      <c r="B71" s="27">
+      <c r="B71" s="26">
         <v>13167</v>
       </c>
-      <c r="C71" s="25">
-        <v>3</v>
-      </c>
-      <c r="D71" s="27">
+      <c r="C71" s="24">
+        <v>3</v>
+      </c>
+      <c r="D71" s="26">
         <v>13170</v>
       </c>
-      <c r="E71" s="32">
+      <c r="E71" s="31">
         <f t="shared" si="3"/>
         <v>2.6900584795321637E-2</v>
       </c>
-      <c r="F71" s="33">
+      <c r="F71" s="32">
         <v>2.69</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="26">
+      <c r="A72" s="25">
         <v>46238</v>
       </c>
-      <c r="B72" s="27">
+      <c r="B72" s="26">
         <v>13114</v>
       </c>
-      <c r="C72" s="25">
-        <v>3</v>
-      </c>
-      <c r="D72" s="27">
+      <c r="C72" s="24">
+        <v>3</v>
+      </c>
+      <c r="D72" s="26">
         <v>13117</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="31">
         <f t="shared" si="3"/>
         <v>-4.0242976461655278E-3</v>
       </c>
-      <c r="F72" s="33">
+      <c r="F72" s="32">
         <v>-4.4000000000000004</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="26">
+      <c r="A73" s="25">
         <v>46239</v>
       </c>
-      <c r="B73" s="27">
+      <c r="B73" s="26">
         <v>13146</v>
       </c>
-      <c r="C73" s="25">
-        <v>3</v>
-      </c>
-      <c r="D73" s="27">
+      <c r="C73" s="24">
+        <v>3</v>
+      </c>
+      <c r="D73" s="26">
         <v>13149</v>
       </c>
-      <c r="E73" s="32">
+      <c r="E73" s="31">
         <f t="shared" si="3"/>
         <v>2.4395822215445605E-3</v>
       </c>
-      <c r="F73" s="33">
+      <c r="F73" s="32">
         <v>0.24</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="26">
+      <c r="A74" s="25">
         <v>46240</v>
       </c>
-      <c r="B74" s="27">
+      <c r="B74" s="26">
         <v>13234</v>
       </c>
-      <c r="C74" s="25">
-        <v>3</v>
-      </c>
-      <c r="D74" s="27">
+      <c r="C74" s="24">
+        <v>3</v>
+      </c>
+      <c r="D74" s="26">
         <v>13237</v>
       </c>
-      <c r="E74" s="32">
+      <c r="E74" s="31">
         <f t="shared" si="3"/>
         <v>6.6925241463229139E-3</v>
       </c>
-      <c r="F74" s="33">
+      <c r="F74" s="32">
         <v>0.67</v>
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="26">
+      <c r="A75" s="25">
         <v>46241</v>
       </c>
-      <c r="B75" s="27">
+      <c r="B75" s="26">
         <v>13266</v>
       </c>
-      <c r="C75" s="25">
-        <v>3</v>
-      </c>
-      <c r="D75" s="27">
+      <c r="C75" s="24">
+        <v>3</v>
+      </c>
+      <c r="D75" s="26">
         <v>13269</v>
       </c>
-      <c r="E75" s="32">
+      <c r="E75" s="31">
         <f t="shared" si="3"/>
         <v>2.4174661932462038E-3</v>
       </c>
-      <c r="F75" s="33">
+      <c r="F75" s="32">
         <v>0.24</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="26">
+      <c r="A76" s="25">
         <v>46244</v>
       </c>
-      <c r="B76" s="27">
+      <c r="B76" s="26">
         <v>13237</v>
       </c>
-      <c r="C76" s="25">
-        <v>3</v>
-      </c>
-      <c r="D76" s="27">
+      <c r="C76" s="24">
+        <v>3</v>
+      </c>
+      <c r="D76" s="26">
         <v>13240</v>
       </c>
-      <c r="E76" s="32">
-        <f t="shared" ref="E76:E100" si="4">+((D76-D75)/D75)</f>
+      <c r="E76" s="31">
+        <f t="shared" ref="E76:E101" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
-      <c r="F76" s="33">
+      <c r="F76" s="32">
         <v>0.22</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="26">
+      <c r="A77" s="25">
         <v>46245</v>
       </c>
-      <c r="B77" s="27">
+      <c r="B77" s="26">
         <v>13220</v>
       </c>
-      <c r="C77" s="25">
-        <v>3</v>
-      </c>
-      <c r="D77" s="27">
+      <c r="C77" s="24">
+        <v>3</v>
+      </c>
+      <c r="D77" s="26">
         <v>13223</v>
       </c>
-      <c r="E77" s="32">
+      <c r="E77" s="31">
         <f t="shared" si="4"/>
         <v>-1.2839879154078551E-3</v>
       </c>
-      <c r="F77" s="33">
+      <c r="F77" s="32">
         <v>-0.13</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="26">
+      <c r="A78" s="25">
         <v>46246</v>
       </c>
-      <c r="B78" s="27">
+      <c r="B78" s="26">
         <v>13231</v>
       </c>
-      <c r="C78" s="25">
-        <v>3</v>
-      </c>
-      <c r="D78" s="27">
+      <c r="C78" s="24">
+        <v>3</v>
+      </c>
+      <c r="D78" s="26">
         <v>13234</v>
       </c>
-      <c r="E78" s="32">
+      <c r="E78" s="31">
         <f t="shared" si="4"/>
         <v>8.3188383876578692E-4</v>
       </c>
-      <c r="F78" s="33">
+      <c r="F78" s="32">
         <v>0.08</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="26">
+      <c r="A79" s="25">
         <v>46247</v>
       </c>
-      <c r="B79" s="27">
+      <c r="B79" s="26">
         <v>13147</v>
       </c>
-      <c r="C79" s="25">
-        <v>3</v>
-      </c>
-      <c r="D79" s="27">
+      <c r="C79" s="24">
+        <v>3</v>
+      </c>
+      <c r="D79" s="26">
         <v>13150</v>
       </c>
-      <c r="E79" s="32">
+      <c r="E79" s="31">
         <f t="shared" si="4"/>
         <v>-6.3472872903128303E-3</v>
       </c>
-      <c r="F79" s="33">
+      <c r="F79" s="32">
         <v>-0.63</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="26">
+      <c r="A80" s="25">
         <v>46248</v>
       </c>
-      <c r="B80" s="27">
+      <c r="B80" s="26">
         <v>13019</v>
       </c>
-      <c r="C80" s="25">
-        <v>3</v>
-      </c>
-      <c r="D80" s="27">
+      <c r="C80" s="24">
+        <v>3</v>
+      </c>
+      <c r="D80" s="26">
         <v>13022</v>
       </c>
-      <c r="E80" s="32">
+      <c r="E80" s="31">
         <f t="shared" si="4"/>
         <v>-9.7338403041825096E-3</v>
       </c>
-      <c r="F80" s="33">
+      <c r="F80" s="32">
         <v>-97</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="26">
+      <c r="A81" s="25">
         <v>46251</v>
       </c>
-      <c r="B81" s="27">
+      <c r="B81" s="26">
         <v>13022</v>
       </c>
-      <c r="C81" s="25">
-        <v>3</v>
-      </c>
-      <c r="D81" s="27">
+      <c r="C81" s="24">
+        <v>3</v>
+      </c>
+      <c r="D81" s="26">
         <v>13025</v>
       </c>
-      <c r="E81" s="32">
+      <c r="E81" s="31">
         <f t="shared" si="4"/>
         <v>2.3037935800952235E-4</v>
       </c>
-      <c r="F81" s="33">
+      <c r="F81" s="32">
         <v>0.02</v>
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="26">
+      <c r="A82" s="25">
         <v>46252</v>
       </c>
-      <c r="B82" s="27">
+      <c r="B82" s="26">
         <v>13431</v>
       </c>
-      <c r="C82" s="25">
-        <v>3</v>
-      </c>
-      <c r="D82" s="27">
+      <c r="C82" s="24">
+        <v>3</v>
+      </c>
+      <c r="D82" s="26">
         <v>13434</v>
       </c>
-      <c r="E82" s="32">
+      <c r="E82" s="31">
         <f t="shared" si="4"/>
         <v>3.1401151631477928E-2</v>
       </c>
-      <c r="F82" s="33">
+      <c r="F82" s="32">
         <v>3.14</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="26">
+      <c r="A83" s="25">
         <v>46253</v>
       </c>
-      <c r="B83" s="27">
+      <c r="B83" s="26">
         <v>13323</v>
       </c>
-      <c r="C83" s="25">
-        <v>3</v>
-      </c>
-      <c r="D83" s="27">
+      <c r="C83" s="24">
+        <v>3</v>
+      </c>
+      <c r="D83" s="26">
         <v>13326</v>
       </c>
-      <c r="E83" s="32">
+      <c r="E83" s="31">
         <f t="shared" si="4"/>
         <v>-8.0393032603841008E-3</v>
       </c>
-      <c r="F83" s="33">
+      <c r="F83" s="32">
         <v>-0.8</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="26">
+      <c r="A84" s="25">
         <v>46254</v>
       </c>
-      <c r="B84" s="27">
+      <c r="B84" s="26">
         <v>13436</v>
       </c>
-      <c r="C84" s="25">
-        <v>3</v>
-      </c>
-      <c r="D84" s="27">
+      <c r="C84" s="24">
+        <v>3</v>
+      </c>
+      <c r="D84" s="26">
         <v>13439</v>
       </c>
-      <c r="E84" s="32">
+      <c r="E84" s="31">
         <f t="shared" si="4"/>
         <v>8.4796638150983032E-3</v>
       </c>
-      <c r="F84" s="33">
+      <c r="F84" s="32">
         <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="26">
+      <c r="A85" s="25">
         <v>46255</v>
       </c>
-      <c r="B85" s="27">
+      <c r="B85" s="26">
         <v>13379</v>
       </c>
-      <c r="C85" s="25">
-        <v>3</v>
-      </c>
-      <c r="D85" s="27">
+      <c r="C85" s="24">
+        <v>3</v>
+      </c>
+      <c r="D85" s="26">
         <v>13382</v>
       </c>
-      <c r="E85" s="32">
+      <c r="E85" s="31">
         <f t="shared" si="4"/>
         <v>-4.2413870079619021E-3</v>
       </c>
-      <c r="F85" s="33">
+      <c r="F85" s="32">
         <v>-0.42</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="26">
+      <c r="A86" s="25">
         <v>46258</v>
       </c>
-      <c r="B86" s="27">
+      <c r="B86" s="26">
         <v>13352</v>
       </c>
-      <c r="C86" s="25">
-        <v>3</v>
-      </c>
-      <c r="D86" s="27">
+      <c r="C86" s="24">
+        <v>3</v>
+      </c>
+      <c r="D86" s="26">
         <v>13355</v>
       </c>
-      <c r="E86" s="32">
+      <c r="E86" s="31">
         <f t="shared" si="4"/>
         <v>-2.01763562995068E-3</v>
       </c>
-      <c r="F86" s="33">
+      <c r="F86" s="32">
         <v>-0.20300000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="26">
+      <c r="A87" s="25">
         <v>46259</v>
       </c>
-      <c r="B87" s="27">
+      <c r="B87" s="26">
         <v>13205</v>
       </c>
-      <c r="C87" s="25">
-        <v>3</v>
-      </c>
-      <c r="D87" s="27">
+      <c r="C87" s="24">
+        <v>3</v>
+      </c>
+      <c r="D87" s="26">
         <v>13208</v>
       </c>
-      <c r="E87" s="32">
+      <c r="E87" s="31">
         <f t="shared" si="4"/>
         <v>-1.1007113440658928E-2</v>
       </c>
-      <c r="F87" s="33">
+      <c r="F87" s="32">
         <v>-1.1000000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="26">
+      <c r="A88" s="25">
         <v>46260</v>
       </c>
-      <c r="B88" s="27">
+      <c r="B88" s="26">
         <v>13147</v>
       </c>
-      <c r="C88" s="25">
-        <v>3</v>
-      </c>
-      <c r="D88" s="27">
+      <c r="C88" s="24">
+        <v>3</v>
+      </c>
+      <c r="D88" s="26">
         <v>13150</v>
       </c>
-      <c r="E88" s="32">
+      <c r="E88" s="31">
         <f t="shared" si="4"/>
         <v>-4.3912780133252578E-3</v>
       </c>
-      <c r="F88" s="33">
+      <c r="F88" s="32">
         <v>-4.4400000000000004</v>
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="26">
+      <c r="A89" s="25">
         <v>46261</v>
       </c>
-      <c r="B89" s="27">
+      <c r="B89" s="26">
         <v>13053</v>
       </c>
-      <c r="C89" s="25">
-        <v>3</v>
-      </c>
-      <c r="D89" s="27">
+      <c r="C89" s="24">
+        <v>3</v>
+      </c>
+      <c r="D89" s="26">
         <v>13056</v>
       </c>
-      <c r="E89" s="32">
+      <c r="E89" s="31">
         <f t="shared" si="4"/>
         <v>-7.1482889733840305E-3</v>
       </c>
-      <c r="F89" s="33">
+      <c r="F89" s="32">
         <v>-0.71</v>
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="26">
+      <c r="A90" s="25">
         <v>46262</v>
       </c>
-      <c r="B90" s="27">
+      <c r="B90" s="26">
         <v>13360</v>
       </c>
-      <c r="C90" s="25">
-        <v>3</v>
-      </c>
-      <c r="D90" s="27">
+      <c r="C90" s="24">
+        <v>3</v>
+      </c>
+      <c r="D90" s="26">
         <v>13363</v>
       </c>
-      <c r="E90" s="32">
+      <c r="E90" s="31">
         <f t="shared" si="4"/>
         <v>2.3514093137254902E-2</v>
       </c>
-      <c r="F90" s="33">
+      <c r="F90" s="32">
         <v>2.35</v>
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="26">
+      <c r="A91" s="25">
         <v>46265</v>
       </c>
-      <c r="B91" s="27">
+      <c r="B91" s="26">
         <v>13285</v>
       </c>
-      <c r="C91" s="25">
-        <v>3</v>
-      </c>
-      <c r="D91" s="27">
+      <c r="C91" s="24">
+        <v>3</v>
+      </c>
+      <c r="D91" s="26">
         <v>13288</v>
       </c>
-      <c r="E91" s="32">
+      <c r="E91" s="31">
         <f t="shared" si="4"/>
         <v>-5.612512160443014E-3</v>
       </c>
-      <c r="F91" s="33">
+      <c r="F91" s="32">
         <v>-0.56000000000000005</v>
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="26">
+      <c r="A92" s="25">
         <v>46266</v>
       </c>
-      <c r="B92" s="27">
+      <c r="B92" s="26">
         <v>12895</v>
       </c>
-      <c r="C92" s="25">
-        <v>3</v>
-      </c>
-      <c r="D92" s="27">
+      <c r="C92" s="24">
+        <v>3</v>
+      </c>
+      <c r="D92" s="26">
         <v>12898</v>
       </c>
-      <c r="E92" s="32">
+      <c r="E92" s="31">
         <f t="shared" si="4"/>
         <v>-2.9349789283564118E-2</v>
       </c>
-      <c r="F92" s="33">
+      <c r="F92" s="32">
         <v>-2.93</v>
       </c>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="26">
+      <c r="A93" s="25">
         <v>46267</v>
       </c>
-      <c r="B93" s="27">
+      <c r="B93" s="26">
         <v>12709</v>
       </c>
-      <c r="C93" s="25">
-        <v>3</v>
-      </c>
-      <c r="D93" s="27">
+      <c r="C93" s="24">
+        <v>3</v>
+      </c>
+      <c r="D93" s="26">
         <v>12712</v>
       </c>
-      <c r="E93" s="32">
+      <c r="E93" s="31">
         <f t="shared" si="4"/>
         <v>-1.4420840440378353E-2</v>
       </c>
-      <c r="F93" s="33">
+      <c r="F93" s="32">
         <v>-1.44</v>
       </c>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="26">
+      <c r="A94" s="25">
         <v>46268</v>
       </c>
-      <c r="B94" s="27">
+      <c r="B94" s="26">
         <v>12864</v>
       </c>
-      <c r="C94" s="25">
-        <v>3</v>
-      </c>
-      <c r="D94" s="27">
+      <c r="C94" s="24">
+        <v>3</v>
+      </c>
+      <c r="D94" s="26">
         <v>12867</v>
       </c>
-      <c r="E94" s="32">
+      <c r="E94" s="31">
         <f t="shared" si="4"/>
         <v>1.2193203272498426E-2</v>
       </c>
-      <c r="F94" s="33">
+      <c r="F94" s="32">
         <v>1.22</v>
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="26">
+      <c r="A95" s="25">
         <v>46269</v>
       </c>
-      <c r="B95" s="27">
+      <c r="B95" s="26">
         <v>12801</v>
       </c>
-      <c r="C95" s="25">
-        <v>3</v>
-      </c>
-      <c r="D95" s="27">
+      <c r="C95" s="24">
+        <v>3</v>
+      </c>
+      <c r="D95" s="26">
         <v>12804</v>
       </c>
-      <c r="E95" s="32">
+      <c r="E95" s="31">
         <f t="shared" si="4"/>
         <v>-4.8962462112380504E-3</v>
       </c>
-      <c r="F95" s="33">
+      <c r="F95" s="32">
         <v>-0.49</v>
       </c>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="26">
+      <c r="A96" s="25">
         <v>46272</v>
       </c>
-      <c r="B96" s="27">
+      <c r="B96" s="26">
         <v>12979</v>
       </c>
-      <c r="C96" s="25">
-        <v>3</v>
-      </c>
-      <c r="D96" s="27">
+      <c r="C96" s="24">
+        <v>3</v>
+      </c>
+      <c r="D96" s="26">
         <v>12982</v>
       </c>
-      <c r="E96" s="32">
+      <c r="E96" s="31">
         <f t="shared" si="4"/>
         <v>1.3901905654482974E-2</v>
       </c>
-      <c r="F96" s="33">
+      <c r="F96" s="32">
         <v>1.39</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="26">
+      <c r="A97" s="25">
         <v>46273</v>
       </c>
-      <c r="B97" s="27">
+      <c r="B97" s="26">
         <v>12912</v>
       </c>
-      <c r="C97" s="25">
-        <v>3</v>
-      </c>
-      <c r="D97" s="27">
+      <c r="C97" s="24">
+        <v>3</v>
+      </c>
+      <c r="D97" s="26">
         <v>12915</v>
       </c>
-      <c r="E97" s="32">
+      <c r="E97" s="31">
         <f t="shared" si="4"/>
         <v>-5.1609921429671855E-3</v>
       </c>
-      <c r="F97" s="33">
+      <c r="F97" s="32">
         <v>-0.52</v>
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="26">
+      <c r="A98" s="25">
         <v>46274</v>
       </c>
-      <c r="B98" s="27">
+      <c r="B98" s="26">
         <v>12898</v>
       </c>
-      <c r="C98" s="25">
-        <v>3</v>
-      </c>
-      <c r="D98" s="27">
+      <c r="C98" s="24">
+        <v>3</v>
+      </c>
+      <c r="D98" s="26">
         <v>12901</v>
       </c>
-      <c r="E98" s="32">
+      <c r="E98" s="31">
         <f t="shared" si="4"/>
         <v>-1.0840108401084011E-3</v>
       </c>
-      <c r="F98" s="33">
+      <c r="F98" s="32">
         <v>-0.11</v>
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="26">
+      <c r="A99" s="25">
         <v>46275</v>
       </c>
-      <c r="B99" s="27">
+      <c r="B99" s="26">
         <v>12855</v>
       </c>
-      <c r="C99" s="25">
-        <v>3</v>
-      </c>
-      <c r="D99" s="27">
+      <c r="C99" s="24">
+        <v>3</v>
+      </c>
+      <c r="D99" s="26">
         <v>12858</v>
       </c>
-      <c r="E99" s="32">
+      <c r="E99" s="31">
         <f t="shared" si="4"/>
         <v>-3.3330749554298118E-3</v>
       </c>
-      <c r="F99" s="33">
+      <c r="F99" s="32">
         <v>-0.33</v>
       </c>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="26">
+      <c r="A100" s="25">
         <v>46276</v>
       </c>
-      <c r="B100" s="27">
+      <c r="B100" s="26">
         <v>13098</v>
       </c>
-      <c r="C100" s="25">
-        <v>3</v>
-      </c>
-      <c r="D100" s="27">
+      <c r="C100" s="24">
+        <v>3</v>
+      </c>
+      <c r="D100" s="26">
         <v>13101</v>
       </c>
-      <c r="E100" s="32">
+      <c r="E100" s="31">
         <f t="shared" si="4"/>
         <v>1.8898740083994399E-2</v>
       </c>
-      <c r="F100" s="33">
+      <c r="F100" s="32">
         <v>1.89</v>
       </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" s="25">
+        <v>46280</v>
+      </c>
+      <c r="B101" s="26">
+        <v>12938</v>
+      </c>
+      <c r="C101" s="24">
+        <v>3</v>
+      </c>
+      <c r="D101" s="26">
+        <v>12941</v>
+      </c>
+      <c r="E101" s="31">
+        <f t="shared" si="4"/>
+        <v>-1.2212808182581482E-2</v>
+      </c>
+      <c r="F101" s="32">
+        <v>-1.22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="E103" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2989,7 +2989,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5299,6 +5299,26 @@
         <v>200</v>
       </c>
     </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="21">
+        <v>46282</v>
+      </c>
+      <c r="B120" s="17">
+        <v>3168.1590000000001</v>
+      </c>
+      <c r="C120" s="20"/>
+      <c r="D120" s="17">
+        <v>90</v>
+      </c>
+      <c r="E120" s="20"/>
+      <c r="F120" s="17">
+        <v>250</v>
+      </c>
+      <c r="G120" s="20"/>
+      <c r="H120" s="17">
+        <v>247.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5307,7 +5327,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5336,14 +5356,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B2" s="24">
-        <v>2804.9294905100001</v>
+        <v>82707.40661228</v>
       </c>
       <c r="C2" s="30">
-        <f t="shared" ref="C2:C65" si="0">+(B2-B3)/B3</f>
-        <v>54.85948274687906</v>
+        <f t="shared" ref="C2:C66" si="0">+(B2-B3)/B3</f>
+        <v>28.486447660130633</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5354,14 +5374,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="25">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B3" s="24">
-        <v>50.214025489999997</v>
+        <v>2804.9294905100001</v>
       </c>
       <c r="C3" s="30">
         <f t="shared" si="0"/>
-        <v>0.37097114686342592</v>
+        <v>54.85948274687906</v>
       </c>
       <c r="D3" s="24" t="s">
         <v>9</v>
@@ -5372,14 +5392,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="25">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B4" s="24">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C4" s="30">
         <f t="shared" si="0"/>
-        <v>-0.67806849277578529</v>
+        <v>0.37097114686342592</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>10</v>
@@ -5390,14 +5410,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="25">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B5" s="24">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C5" s="30">
         <f t="shared" si="0"/>
-        <v>18.560573043109468</v>
+        <v>-0.67806849277578529</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>30</v>
@@ -5408,14 +5428,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="25">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B6" s="24">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C6" s="30">
         <f t="shared" si="0"/>
-        <v>0.64045278098882874</v>
+        <v>18.560573043109468</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5426,14 +5446,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="25">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B7" s="24">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C7" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <v>0.64045278098882874</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -5444,14 +5464,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="25">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B8" s="24">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C8" s="30">
         <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <v>-0.82640880552358198</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -5462,14 +5482,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="25">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B9" s="24">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C9" s="30">
         <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <v>2.4737529624349173</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -5480,1235 +5500,1247 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="25">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B10" s="24">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C10" s="30">
         <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <v>-0.97953700801723442</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="25">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B11" s="24">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C11" s="30">
         <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <v>80.163058476193896</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B12" s="24">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C12" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <v>-0.77463732472189939</v>
       </c>
       <c r="E12" s="37"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="25">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B13" s="24">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C13" s="30">
         <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <v>-0.99727371031195</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="25">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B14" s="24">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C14" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <v>1028.4103166122507</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="25">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B15" s="24">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C15" s="30">
         <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <v>-0.98760095272084658</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="25">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="24">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C16" s="30">
         <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <v>98.812318362183703</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B17" s="24">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C17" s="30">
         <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <v>-0.9864837734804992</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B18" s="24">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C18" s="30">
         <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <v>74.639780601233326</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B19" s="24">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C19" s="30">
         <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <v>-0.96494750708048294</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B20" s="24">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C20" s="30">
         <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="25">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B21" s="24">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C21" s="30">
         <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="25">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B22" s="24">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C22" s="30">
         <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="25">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B23" s="24">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C23" s="30">
         <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="25">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B24" s="24">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C24" s="30">
         <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="25">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B25" s="24">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C25" s="30">
         <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="25">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B26" s="24">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C26" s="30">
         <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="25">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B27" s="24">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C27" s="30">
         <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="25">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B28" s="24">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C28" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="25">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B29" s="24">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C29" s="30">
         <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="25">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B30" s="24">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C30" s="30">
         <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="25">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B31" s="24">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C31" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="25">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B32" s="24">
-        <v>499.27660521000001</v>
+        <v>2.8086933300000001</v>
       </c>
       <c r="C32" s="30">
         <f t="shared" si="0"/>
-        <v>75.11816589074563</v>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="25">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B33" s="24">
-        <v>6.5592306300000001</v>
+        <v>499.27660521000001</v>
       </c>
       <c r="C33" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99966330474421161</v>
+        <v>75.11816589074563</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="25">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B34" s="24">
-        <v>19481.20894855</v>
+        <v>6.5592306300000001</v>
       </c>
       <c r="C34" s="30">
         <f t="shared" si="0"/>
-        <v>40.77506746658235</v>
+        <v>-0.99966330474421161</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="25">
-        <v>46233</v>
-      </c>
-      <c r="B35">
-        <v>466.33578662999997</v>
+        <v>46234</v>
+      </c>
+      <c r="B35" s="24">
+        <v>19481.20894855</v>
       </c>
       <c r="C35" s="30">
         <f t="shared" si="0"/>
-        <v>3.5918026507549188</v>
+        <v>40.77506746658235</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="25">
-        <v>46232</v>
-      </c>
-      <c r="B36" s="24">
-        <v>101.55832515</v>
+        <v>46233</v>
+      </c>
+      <c r="B36">
+        <v>466.33578662999997</v>
       </c>
       <c r="C36" s="30">
         <f t="shared" si="0"/>
-        <v>22.269067927747528</v>
+        <v>3.5918026507549188</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="25">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B37" s="24">
-        <v>4.3645205499999999</v>
+        <v>101.55832515</v>
       </c>
       <c r="C37" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98047278251084946</v>
+        <v>22.269067927747528</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="25">
-        <v>46108</v>
+        <v>46231</v>
       </c>
       <c r="B38" s="24">
-        <v>223.50959897000001</v>
+        <v>4.3645205499999999</v>
       </c>
       <c r="C38" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99220607504587943</v>
+        <v>-0.98047278251084946</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="25">
-        <v>46226</v>
+        <v>46108</v>
       </c>
       <c r="B39" s="24">
-        <v>28677.412251940001</v>
+        <v>223.50959897000001</v>
       </c>
       <c r="C39" s="30">
         <f t="shared" si="0"/>
-        <v>32.413800410299046</v>
+        <v>-0.99220607504587943</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="25">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B40" s="24">
-        <v>858.25054019000004</v>
+        <v>28677.412251940001</v>
       </c>
       <c r="C40" s="30">
         <f t="shared" si="0"/>
-        <v>41.77708649767068</v>
+        <v>32.413800410299046</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="25">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B41" s="24">
-        <v>20.063323860000001</v>
+        <v>858.25054019000004</v>
       </c>
       <c r="C41" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99734079323279778</v>
+        <v>41.77708649767068</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="25">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B42" s="24">
-        <v>7544.8528890099997</v>
+        <v>20.063323860000001</v>
       </c>
       <c r="C42" s="30">
         <f t="shared" si="0"/>
-        <v>-0.54491271467140989</v>
+        <v>-0.99734079323279778</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="25">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B43" s="24">
-        <v>16578.913830919999</v>
+        <v>7544.8528890099997</v>
       </c>
       <c r="C43" s="30">
         <f t="shared" si="0"/>
-        <v>1.1008050673763534</v>
+        <v>-0.54491271467140989</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="25">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B44" s="24">
-        <v>7891.6954687400003</v>
+        <v>16578.913830919999</v>
       </c>
       <c r="C44" s="30">
         <f t="shared" si="0"/>
-        <v>-0.79678113606112111</v>
+        <v>1.1008050673763534</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="25">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B45" s="24">
-        <v>38833.478919130001</v>
+        <v>7891.6954687400003</v>
       </c>
       <c r="C45" s="30">
         <f t="shared" si="0"/>
-        <v>-0.25771272667553924</v>
+        <v>-0.79678113606112111</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="25">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B46" s="24">
-        <v>52315.97026473</v>
+        <v>38833.478919130001</v>
       </c>
       <c r="C46" s="30">
         <f t="shared" si="0"/>
-        <v>-0.19048561913228002</v>
+        <v>-0.25771272667553924</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="25">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B47" s="24">
-        <v>64626.363040830001</v>
+        <v>52315.97026473</v>
       </c>
       <c r="C47" s="30">
         <f t="shared" si="0"/>
-        <v>1.2916911129109088</v>
+        <v>-0.19048561913228002</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="25">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B48" s="24">
-        <v>28200.29395617</v>
+        <v>64626.363040830001</v>
       </c>
       <c r="C48" s="30">
         <f t="shared" si="0"/>
-        <v>2.65997178100841</v>
+        <v>1.2916911129109088</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="25">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B49" s="24">
-        <v>7705.0577555</v>
+        <v>28200.29395617</v>
       </c>
       <c r="C49" s="30">
         <f t="shared" si="0"/>
-        <v>0.84099979813836301</v>
+        <v>2.65997178100841</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="25">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B50" s="24">
-        <v>4185.2572516800001</v>
+        <v>7705.0577555</v>
       </c>
       <c r="C50" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5358672604044985</v>
+        <v>0.84099979813836301</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="25">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B51" s="24">
-        <v>9017.3713134900008</v>
+        <v>4185.2572516800001</v>
       </c>
       <c r="C51" s="30">
         <f t="shared" si="0"/>
-        <v>-0.47344417767330416</v>
+        <v>-0.5358672604044985</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="25">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B52" s="24">
-        <v>17125.195337590001</v>
+        <v>9017.3713134900008</v>
       </c>
       <c r="C52" s="30">
         <f t="shared" si="0"/>
-        <v>-0.39167454677290181</v>
+        <v>-0.47344417767330416</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="25">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B53" s="24">
-        <v>28151.370695969999</v>
+        <v>17125.195337590001</v>
       </c>
       <c r="C53" s="30">
         <f t="shared" si="0"/>
-        <v>27.450841046685248</v>
+        <v>-0.39167454677290181</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="25">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B54" s="24">
-        <v>989.47411254999997</v>
+        <v>28151.370695969999</v>
       </c>
       <c r="C54" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82605795449481512</v>
+        <v>27.450841046685248</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="25">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B55" s="24">
-        <v>5688.5275189000004</v>
+        <v>989.47411254999997</v>
       </c>
       <c r="C55" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82035890094428965</v>
+        <v>-0.82605795449481512</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="25">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B56" s="24">
-        <v>31666.069450710002</v>
+        <v>5688.5275189000004</v>
       </c>
       <c r="C56" s="30">
         <f t="shared" si="0"/>
-        <v>12.096519032059602</v>
+        <v>-0.82035890094428965</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="25">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B57" s="24">
-        <v>2417.8997009200002</v>
+        <v>31666.069450710002</v>
       </c>
       <c r="C57" s="30">
         <f t="shared" si="0"/>
-        <v>0.40878477030033311</v>
+        <v>12.096519032059602</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="25">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B58" s="24">
-        <v>1716.30170335</v>
+        <v>2417.8997009200002</v>
       </c>
       <c r="C58" s="30">
         <f t="shared" si="0"/>
-        <v>103.40487339188886</v>
+        <v>0.40878477030033311</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="25">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B59" s="24">
-        <v>16.43890412</v>
+        <v>1716.30170335</v>
       </c>
       <c r="C59" s="30">
         <f t="shared" si="0"/>
-        <v>-0.93907248343987781</v>
+        <v>103.40487339188886</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="25">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B60" s="24">
-        <v>269.81083503999997</v>
+        <v>16.43890412</v>
       </c>
       <c r="C60" s="30">
         <f t="shared" si="0"/>
-        <v>-0.88259974628484428</v>
+        <v>-0.93907248343987781</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="25">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B61" s="24">
-        <v>2298.2133896800001</v>
+        <v>269.81083503999997</v>
       </c>
       <c r="C61" s="30">
         <f t="shared" si="0"/>
-        <v>0.90523755264044037</v>
+        <v>-0.88259974628484428</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="25">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B62" s="24">
-        <v>1206.260808</v>
+        <v>2298.2133896800001</v>
       </c>
       <c r="C62" s="30">
         <f t="shared" si="0"/>
-        <v>142.26137862232778</v>
+        <v>0.90523755264044037</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="25">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B63" s="24">
-        <v>8.42</v>
+        <v>1206.260808</v>
       </c>
       <c r="C63" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5604660313731078</v>
+        <v>142.26137862232778</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="25">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B64" s="24">
-        <v>19.156653639999998</v>
+        <v>8.42</v>
       </c>
       <c r="C64" s="30">
         <f t="shared" si="0"/>
-        <v>0.50703525245440206</v>
+        <v>-0.5604660313731078</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="25">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B65" s="24">
-        <v>12.711483429999999</v>
+        <v>19.156653639999998</v>
       </c>
       <c r="C65" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99943660659465605</v>
+        <v>0.50703525245440206</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="25">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B66" s="24">
-        <v>22562.357509739999</v>
+        <v>12.711483429999999</v>
       </c>
       <c r="C66" s="30">
-        <f t="shared" ref="C66:C107" si="1">+(B66-B67)/B67</f>
-        <v>5.2639483520141219</v>
+        <f t="shared" si="0"/>
+        <v>-0.99943660659465605</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B67" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C67" s="30">
+        <f t="shared" ref="C67:C108" si="1">+(B67-B68)/B68</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="25">
         <v>46182</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B68" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C67" s="30">
+      <c r="C68" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="25">
+    <row r="69" spans="1:3">
+      <c r="A69" s="25">
         <v>46178</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B69" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C69" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="25">
+    <row r="70" spans="1:3">
+      <c r="A70" s="25">
         <v>46177</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B70" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C70" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="25">
+    <row r="71" spans="1:3">
+      <c r="A71" s="25">
         <v>46176</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B71" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C71" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="25">
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
         <v>46175</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
         <v>46174</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
         <v>46171</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
         <v>45074</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>46169</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>46168</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>46167</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>46164</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>46163</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>46162</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>46161</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>46157</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46156</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46155</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46154</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46153</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46150</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="23">
+    <row r="89" spans="1:3">
+      <c r="A89" s="23">
         <v>46149</v>
       </c>
-      <c r="B88" s="22">
+      <c r="B89" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="18">
+    <row r="90" spans="1:3">
+      <c r="A90" s="18">
         <v>46148</v>
       </c>
-      <c r="B89" s="16">
+      <c r="B90" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="18">
+    <row r="91" spans="1:3">
+      <c r="A91" s="18">
         <v>46147</v>
       </c>
-      <c r="B90" s="16">
+      <c r="B91" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="18">
+    <row r="92" spans="1:3">
+      <c r="A92" s="18">
         <v>46146</v>
       </c>
-      <c r="B91" s="16">
+      <c r="B92" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="19">
+    <row r="93" spans="1:3">
+      <c r="A93" s="19">
         <v>46142</v>
       </c>
-      <c r="B92" s="16">
+      <c r="B93" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="19">
+    <row r="94" spans="1:3">
+      <c r="A94" s="19">
         <v>46141</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B94" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="19">
+    <row r="95" spans="1:3">
+      <c r="A95" s="19">
         <v>46140</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B95" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="19">
+    <row r="96" spans="1:3">
+      <c r="A96" s="19">
         <v>46139</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B96" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="19">
+    <row r="97" spans="1:4">
+      <c r="A97" s="19">
         <v>46136</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B97" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="19">
+    <row r="98" spans="1:4">
+      <c r="A98" s="19">
         <v>46135</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="19">
+    <row r="99" spans="1:4">
+      <c r="A99" s="19">
         <v>46134</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="19">
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
         <v>46133</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46132</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46129</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46128</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+      <c r="D103" s="37"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46127</v>
       </c>
-      <c r="B103" s="39">
+      <c r="B104" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
-      <c r="D103" s="37"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46126</v>
       </c>
-      <c r="B104" s="39">
+      <c r="B105" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46125</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B106" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46122</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46121</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B108" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
-        <v>46120</v>
-      </c>
-      <c r="B108" s="16">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C108" s="30">
-        <f>+(B108-B109)/B109</f>
-        <v>3.9632497533121036</v>
-      </c>
       <c r="D108" s="36"/>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="19">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B109" s="16">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C109" s="30">
+        <f>+(B109-B110)/B110</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B110" s="16">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
       <c r="D110" s="36"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B111" s="16">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B112" s="16">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="19">
+        <v>46112</v>
+      </c>
+      <c r="B113" s="16">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="19">
         <v>46111</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B114" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -9409,7 +9441,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:E101" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E102" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -9939,6 +9971,27 @@
       </c>
       <c r="F101" s="32">
         <v>-1.22</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" s="25">
+        <v>46281</v>
+      </c>
+      <c r="B102" s="26">
+        <v>12985</v>
+      </c>
+      <c r="C102" s="24">
+        <v>3</v>
+      </c>
+      <c r="D102" s="26">
+        <v>12988</v>
+      </c>
+      <c r="E102" s="31">
+        <f t="shared" si="4"/>
+        <v>3.6318677072869174E-3</v>
+      </c>
+      <c r="F102" s="32">
+        <v>0.36</v>
       </c>
     </row>
     <row r="103" spans="1:6">

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2989,7 +2989,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H120"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5319,6 +5319,26 @@
         <v>247.55</v>
       </c>
     </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="21">
+        <v>46283</v>
+      </c>
+      <c r="B121" s="17">
+        <v>820</v>
+      </c>
+      <c r="C121" s="20"/>
+      <c r="D121" s="17">
+        <v>25</v>
+      </c>
+      <c r="E121" s="20"/>
+      <c r="F121" s="17">
+        <v>30</v>
+      </c>
+      <c r="G121" s="20"/>
+      <c r="H121" s="17">
+        <v>27.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5327,7 +5347,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5356,14 +5376,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B2" s="24">
-        <v>82707.40661228</v>
+        <v>109462.8853239</v>
       </c>
       <c r="C2" s="30">
-        <f t="shared" ref="C2:C66" si="0">+(B2-B3)/B3</f>
-        <v>28.486447660130633</v>
+        <f t="shared" ref="C2:C67" si="0">+(B2-B3)/B3</f>
+        <v>0.32349555871151542</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5374,14 +5394,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="25">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B3" s="24">
-        <v>2804.9294905100001</v>
+        <v>82707.40661228</v>
       </c>
       <c r="C3" s="30">
         <f t="shared" si="0"/>
-        <v>54.85948274687906</v>
+        <v>28.486447660130633</v>
       </c>
       <c r="D3" s="24" t="s">
         <v>9</v>
@@ -5392,14 +5412,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="25">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B4" s="24">
-        <v>50.214025489999997</v>
+        <v>2804.9294905100001</v>
       </c>
       <c r="C4" s="30">
         <f t="shared" si="0"/>
-        <v>0.37097114686342592</v>
+        <v>54.85948274687906</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>10</v>
@@ -5410,14 +5430,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="25">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B5" s="24">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C5" s="30">
         <f t="shared" si="0"/>
-        <v>-0.67806849277578529</v>
+        <v>0.37097114686342592</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>30</v>
@@ -5428,14 +5448,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="25">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B6" s="24">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C6" s="30">
         <f t="shared" si="0"/>
-        <v>18.560573043109468</v>
+        <v>-0.67806849277578529</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5446,14 +5466,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="25">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B7" s="24">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C7" s="30">
         <f t="shared" si="0"/>
-        <v>0.64045278098882874</v>
+        <v>18.560573043109468</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -5464,14 +5484,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="25">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B8" s="24">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C8" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <v>0.64045278098882874</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -5482,14 +5502,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="25">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B9" s="24">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C9" s="30">
         <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <v>-0.82640880552358198</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -5500,1247 +5520,1259 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="25">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B10" s="24">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C10" s="30">
         <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <v>2.4737529624349173</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="25">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B11" s="24">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C11" s="30">
         <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <v>-0.97953700801723442</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B12" s="24">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C12" s="30">
         <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <v>80.163058476193896</v>
       </c>
       <c r="E12" s="37"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="25">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B13" s="24">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C13" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <v>-0.77463732472189939</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="25">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B14" s="24">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C14" s="30">
         <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <v>-0.99727371031195</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="25">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B15" s="24">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C15" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <v>1028.4103166122507</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="25">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B16" s="24">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C16" s="30">
         <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <v>-0.98760095272084658</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B17" s="24">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C17" s="30">
         <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <v>98.812318362183703</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B18" s="24">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C18" s="30">
         <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <v>-0.9864837734804992</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B19" s="24">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C19" s="30">
         <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <v>74.639780601233326</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B20" s="24">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C20" s="30">
         <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="25">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B21" s="24">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C21" s="30">
         <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="25">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B22" s="24">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C22" s="30">
         <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="25">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B23" s="24">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C23" s="30">
         <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="25">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B24" s="24">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C24" s="30">
         <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="25">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B25" s="24">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C25" s="30">
         <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="25">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B26" s="24">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C26" s="30">
         <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="25">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B27" s="24">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C27" s="30">
         <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="25">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B28" s="24">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C28" s="30">
         <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="25">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B29" s="24">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C29" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="25">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B30" s="24">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C30" s="30">
         <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="25">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B31" s="24">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C31" s="30">
         <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="25">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B32" s="24">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C32" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="25">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B33" s="24">
-        <v>499.27660521000001</v>
+        <v>2.8086933300000001</v>
       </c>
       <c r="C33" s="30">
         <f t="shared" si="0"/>
-        <v>75.11816589074563</v>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="25">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B34" s="24">
-        <v>6.5592306300000001</v>
+        <v>499.27660521000001</v>
       </c>
       <c r="C34" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99966330474421161</v>
+        <v>75.11816589074563</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="25">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B35" s="24">
-        <v>19481.20894855</v>
+        <v>6.5592306300000001</v>
       </c>
       <c r="C35" s="30">
         <f t="shared" si="0"/>
-        <v>40.77506746658235</v>
+        <v>-0.99966330474421161</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="25">
-        <v>46233</v>
-      </c>
-      <c r="B36">
-        <v>466.33578662999997</v>
+        <v>46234</v>
+      </c>
+      <c r="B36" s="24">
+        <v>19481.20894855</v>
       </c>
       <c r="C36" s="30">
         <f t="shared" si="0"/>
-        <v>3.5918026507549188</v>
+        <v>40.77506746658235</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="25">
-        <v>46232</v>
-      </c>
-      <c r="B37" s="24">
-        <v>101.55832515</v>
+        <v>46233</v>
+      </c>
+      <c r="B37">
+        <v>466.33578662999997</v>
       </c>
       <c r="C37" s="30">
         <f t="shared" si="0"/>
-        <v>22.269067927747528</v>
+        <v>3.5918026507549188</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="25">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B38" s="24">
-        <v>4.3645205499999999</v>
+        <v>101.55832515</v>
       </c>
       <c r="C38" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98047278251084946</v>
+        <v>22.269067927747528</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="25">
-        <v>46108</v>
+        <v>46231</v>
       </c>
       <c r="B39" s="24">
-        <v>223.50959897000001</v>
+        <v>4.3645205499999999</v>
       </c>
       <c r="C39" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99220607504587943</v>
+        <v>-0.98047278251084946</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="25">
-        <v>46226</v>
+        <v>46108</v>
       </c>
       <c r="B40" s="24">
-        <v>28677.412251940001</v>
+        <v>223.50959897000001</v>
       </c>
       <c r="C40" s="30">
         <f t="shared" si="0"/>
-        <v>32.413800410299046</v>
+        <v>-0.99220607504587943</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="25">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B41" s="24">
-        <v>858.25054019000004</v>
+        <v>28677.412251940001</v>
       </c>
       <c r="C41" s="30">
         <f t="shared" si="0"/>
-        <v>41.77708649767068</v>
+        <v>32.413800410299046</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="25">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B42" s="24">
-        <v>20.063323860000001</v>
+        <v>858.25054019000004</v>
       </c>
       <c r="C42" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99734079323279778</v>
+        <v>41.77708649767068</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="25">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B43" s="24">
-        <v>7544.8528890099997</v>
+        <v>20.063323860000001</v>
       </c>
       <c r="C43" s="30">
         <f t="shared" si="0"/>
-        <v>-0.54491271467140989</v>
+        <v>-0.99734079323279778</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="25">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B44" s="24">
-        <v>16578.913830919999</v>
+        <v>7544.8528890099997</v>
       </c>
       <c r="C44" s="30">
         <f t="shared" si="0"/>
-        <v>1.1008050673763534</v>
+        <v>-0.54491271467140989</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="25">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B45" s="24">
-        <v>7891.6954687400003</v>
+        <v>16578.913830919999</v>
       </c>
       <c r="C45" s="30">
         <f t="shared" si="0"/>
-        <v>-0.79678113606112111</v>
+        <v>1.1008050673763534</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="25">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B46" s="24">
-        <v>38833.478919130001</v>
+        <v>7891.6954687400003</v>
       </c>
       <c r="C46" s="30">
         <f t="shared" si="0"/>
-        <v>-0.25771272667553924</v>
+        <v>-0.79678113606112111</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="25">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B47" s="24">
-        <v>52315.97026473</v>
+        <v>38833.478919130001</v>
       </c>
       <c r="C47" s="30">
         <f t="shared" si="0"/>
-        <v>-0.19048561913228002</v>
+        <v>-0.25771272667553924</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="25">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B48" s="24">
-        <v>64626.363040830001</v>
+        <v>52315.97026473</v>
       </c>
       <c r="C48" s="30">
         <f t="shared" si="0"/>
-        <v>1.2916911129109088</v>
+        <v>-0.19048561913228002</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="25">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B49" s="24">
-        <v>28200.29395617</v>
+        <v>64626.363040830001</v>
       </c>
       <c r="C49" s="30">
         <f t="shared" si="0"/>
-        <v>2.65997178100841</v>
+        <v>1.2916911129109088</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="25">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B50" s="24">
-        <v>7705.0577555</v>
+        <v>28200.29395617</v>
       </c>
       <c r="C50" s="30">
         <f t="shared" si="0"/>
-        <v>0.84099979813836301</v>
+        <v>2.65997178100841</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="25">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B51" s="24">
-        <v>4185.2572516800001</v>
+        <v>7705.0577555</v>
       </c>
       <c r="C51" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5358672604044985</v>
+        <v>0.84099979813836301</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="25">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B52" s="24">
-        <v>9017.3713134900008</v>
+        <v>4185.2572516800001</v>
       </c>
       <c r="C52" s="30">
         <f t="shared" si="0"/>
-        <v>-0.47344417767330416</v>
+        <v>-0.5358672604044985</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="25">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B53" s="24">
-        <v>17125.195337590001</v>
+        <v>9017.3713134900008</v>
       </c>
       <c r="C53" s="30">
         <f t="shared" si="0"/>
-        <v>-0.39167454677290181</v>
+        <v>-0.47344417767330416</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="25">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B54" s="24">
-        <v>28151.370695969999</v>
+        <v>17125.195337590001</v>
       </c>
       <c r="C54" s="30">
         <f t="shared" si="0"/>
-        <v>27.450841046685248</v>
+        <v>-0.39167454677290181</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="25">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B55" s="24">
-        <v>989.47411254999997</v>
+        <v>28151.370695969999</v>
       </c>
       <c r="C55" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82605795449481512</v>
+        <v>27.450841046685248</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="25">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B56" s="24">
-        <v>5688.5275189000004</v>
+        <v>989.47411254999997</v>
       </c>
       <c r="C56" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82035890094428965</v>
+        <v>-0.82605795449481512</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="25">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B57" s="24">
-        <v>31666.069450710002</v>
+        <v>5688.5275189000004</v>
       </c>
       <c r="C57" s="30">
         <f t="shared" si="0"/>
-        <v>12.096519032059602</v>
+        <v>-0.82035890094428965</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="25">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B58" s="24">
-        <v>2417.8997009200002</v>
+        <v>31666.069450710002</v>
       </c>
       <c r="C58" s="30">
         <f t="shared" si="0"/>
-        <v>0.40878477030033311</v>
+        <v>12.096519032059602</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="25">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B59" s="24">
-        <v>1716.30170335</v>
+        <v>2417.8997009200002</v>
       </c>
       <c r="C59" s="30">
         <f t="shared" si="0"/>
-        <v>103.40487339188886</v>
+        <v>0.40878477030033311</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="25">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B60" s="24">
-        <v>16.43890412</v>
+        <v>1716.30170335</v>
       </c>
       <c r="C60" s="30">
         <f t="shared" si="0"/>
-        <v>-0.93907248343987781</v>
+        <v>103.40487339188886</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="25">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B61" s="24">
-        <v>269.81083503999997</v>
+        <v>16.43890412</v>
       </c>
       <c r="C61" s="30">
         <f t="shared" si="0"/>
-        <v>-0.88259974628484428</v>
+        <v>-0.93907248343987781</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="25">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B62" s="24">
-        <v>2298.2133896800001</v>
+        <v>269.81083503999997</v>
       </c>
       <c r="C62" s="30">
         <f t="shared" si="0"/>
-        <v>0.90523755264044037</v>
+        <v>-0.88259974628484428</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="25">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B63" s="24">
-        <v>1206.260808</v>
+        <v>2298.2133896800001</v>
       </c>
       <c r="C63" s="30">
         <f t="shared" si="0"/>
-        <v>142.26137862232778</v>
+        <v>0.90523755264044037</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="25">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B64" s="24">
-        <v>8.42</v>
+        <v>1206.260808</v>
       </c>
       <c r="C64" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5604660313731078</v>
+        <v>142.26137862232778</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="25">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B65" s="24">
-        <v>19.156653639999998</v>
+        <v>8.42</v>
       </c>
       <c r="C65" s="30">
         <f t="shared" si="0"/>
-        <v>0.50703525245440206</v>
+        <v>-0.5604660313731078</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="25">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B66" s="24">
-        <v>12.711483429999999</v>
+        <v>19.156653639999998</v>
       </c>
       <c r="C66" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99943660659465605</v>
+        <v>0.50703525245440206</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="25">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B67" s="24">
-        <v>22562.357509739999</v>
+        <v>12.711483429999999</v>
       </c>
       <c r="C67" s="30">
-        <f t="shared" ref="C67:C108" si="1">+(B67-B68)/B68</f>
-        <v>5.2639483520141219</v>
+        <f t="shared" si="0"/>
+        <v>-0.99943660659465605</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B68" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C68" s="30">
+        <f t="shared" ref="C68:C109" si="1">+(B68-B69)/B69</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="25">
         <v>46182</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B69" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C69" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="25">
+    <row r="70" spans="1:3">
+      <c r="A70" s="25">
         <v>46178</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B70" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C70" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="25">
+    <row r="71" spans="1:3">
+      <c r="A71" s="25">
         <v>46177</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B71" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C71" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="25">
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
         <v>46176</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
         <v>46175</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
         <v>46174</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
         <v>46171</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>45074</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>46169</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>46168</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>46167</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>46164</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>46163</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>46162</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>46161</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46157</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46156</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46155</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46154</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46153</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="25">
         <v>46150</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="23">
+    <row r="90" spans="1:3">
+      <c r="A90" s="23">
         <v>46149</v>
       </c>
-      <c r="B89" s="22">
+      <c r="B90" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="18">
+    <row r="91" spans="1:3">
+      <c r="A91" s="18">
         <v>46148</v>
       </c>
-      <c r="B90" s="16">
+      <c r="B91" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="18">
+    <row r="92" spans="1:3">
+      <c r="A92" s="18">
         <v>46147</v>
       </c>
-      <c r="B91" s="16">
+      <c r="B92" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="18">
+    <row r="93" spans="1:3">
+      <c r="A93" s="18">
         <v>46146</v>
       </c>
-      <c r="B92" s="16">
+      <c r="B93" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="19">
+    <row r="94" spans="1:3">
+      <c r="A94" s="19">
         <v>46142</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B94" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="19">
+    <row r="95" spans="1:3">
+      <c r="A95" s="19">
         <v>46141</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B95" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="19">
+    <row r="96" spans="1:3">
+      <c r="A96" s="19">
         <v>46140</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B96" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="19">
+    <row r="97" spans="1:4">
+      <c r="A97" s="19">
         <v>46139</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B97" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="19">
+    <row r="98" spans="1:4">
+      <c r="A98" s="19">
         <v>46136</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="19">
+    <row r="99" spans="1:4">
+      <c r="A99" s="19">
         <v>46135</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="19">
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
         <v>46134</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46133</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46132</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46129</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+      <c r="D103" s="37"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46128</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
-      <c r="D103" s="37"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46127</v>
       </c>
-      <c r="B104" s="39">
+      <c r="B105" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46126</v>
       </c>
-      <c r="B105" s="39">
+      <c r="B106" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46125</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46122</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B108" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+      <c r="D108" s="36"/>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46121</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B109" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
-      <c r="D108" s="36"/>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
-        <v>46120</v>
-      </c>
-      <c r="B109" s="16">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C109" s="30">
-        <f>+(B109-B110)/B110</f>
-        <v>3.9632497533121036</v>
-      </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="19">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B110" s="16">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C110" s="30">
+        <f>+(B110-B111)/B111</f>
+        <v>3.9632497533121036</v>
       </c>
       <c r="D110" s="36"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B111" s="16">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B112" s="16">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="19">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B113" s="16">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="19">
+        <v>46112</v>
+      </c>
+      <c r="B114" s="16">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="19">
         <v>46111</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B115" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7166,7 +7198,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -7833,6 +7865,32 @@
         <v>3.0254778175788317</v>
       </c>
     </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B26" s="17">
+        <v>79385922.735550016</v>
+      </c>
+      <c r="C26" s="17">
+        <v>2467050597.1357689</v>
+      </c>
+      <c r="D26" s="17">
+        <v>198171308.14264002</v>
+      </c>
+      <c r="E26" s="17">
+        <v>2744607828.0139589</v>
+      </c>
+      <c r="F26" s="17">
+        <v>2520693.33421</v>
+      </c>
+      <c r="G26" s="17">
+        <v>2747128521.3481688</v>
+      </c>
+      <c r="H26" s="27">
+        <v>-0.19229640741738052</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7844,7 +7902,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="2" width="7.375" customWidth="1"/>
+    <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.875" style="14" customWidth="1"/>
@@ -9441,7 +9499,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:E102" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E103" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -9995,7 +10053,25 @@
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="E103" s="31"/>
+      <c r="A103" s="25">
+        <v>46282</v>
+      </c>
+      <c r="B103" s="26">
+        <v>12914</v>
+      </c>
+      <c r="C103" s="24">
+        <v>3</v>
+      </c>
+      <c r="D103" s="26">
+        <v>12917</v>
+      </c>
+      <c r="E103" s="31">
+        <f t="shared" si="4"/>
+        <v>-5.4665845395749924E-3</v>
+      </c>
+      <c r="F103" s="32">
+        <v>-0.55000000000000004</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2989,7 +2989,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5339,6 +5339,26 @@
         <v>27.5</v>
       </c>
     </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="21">
+        <v>46286</v>
+      </c>
+      <c r="B122" s="17">
+        <v>20888.307000000001</v>
+      </c>
+      <c r="C122" s="20"/>
+      <c r="D122" s="17">
+        <v>1</v>
+      </c>
+      <c r="E122" s="20"/>
+      <c r="F122" s="17">
+        <v>100</v>
+      </c>
+      <c r="G122" s="20"/>
+      <c r="H122" s="17">
+        <v>23.39</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5347,7 +5367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5376,14 +5396,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B2" s="24">
-        <v>109462.8853239</v>
+        <v>137505.15153979001</v>
       </c>
       <c r="C2" s="30">
-        <f t="shared" ref="C2:C67" si="0">+(B2-B3)/B3</f>
-        <v>0.32349555871151542</v>
+        <f t="shared" ref="C2:C68" si="0">+(B2-B3)/B3</f>
+        <v>0.25618058698994745</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5394,14 +5414,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="25">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B3" s="24">
-        <v>82707.40661228</v>
+        <v>109462.8853239</v>
       </c>
       <c r="C3" s="30">
         <f t="shared" si="0"/>
-        <v>28.486447660130633</v>
+        <v>0.32349555871151542</v>
       </c>
       <c r="D3" s="24" t="s">
         <v>9</v>
@@ -5412,14 +5432,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="25">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B4" s="24">
-        <v>2804.9294905100001</v>
+        <v>82707.40661228</v>
       </c>
       <c r="C4" s="30">
         <f t="shared" si="0"/>
-        <v>54.85948274687906</v>
+        <v>28.486447660130633</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>10</v>
@@ -5430,14 +5450,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="25">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B5" s="24">
-        <v>50.214025489999997</v>
+        <v>2804.9294905100001</v>
       </c>
       <c r="C5" s="30">
         <f t="shared" si="0"/>
-        <v>0.37097114686342592</v>
+        <v>54.85948274687906</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>30</v>
@@ -5448,14 +5468,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="25">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B6" s="24">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C6" s="30">
         <f t="shared" si="0"/>
-        <v>-0.67806849277578529</v>
+        <v>0.37097114686342592</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5466,14 +5486,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="25">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B7" s="24">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C7" s="30">
         <f t="shared" si="0"/>
-        <v>18.560573043109468</v>
+        <v>-0.67806849277578529</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -5484,14 +5504,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="25">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B8" s="24">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C8" s="30">
         <f t="shared" si="0"/>
-        <v>0.64045278098882874</v>
+        <v>18.560573043109468</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -5502,14 +5522,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="25">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B9" s="24">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C9" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <v>0.64045278098882874</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -5520,1259 +5540,1271 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="25">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B10" s="24">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C10" s="30">
         <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <v>-0.82640880552358198</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="25">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B11" s="24">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C11" s="30">
         <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <v>2.4737529624349173</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B12" s="24">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C12" s="30">
         <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <v>-0.97953700801723442</v>
       </c>
       <c r="E12" s="37"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="25">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B13" s="24">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C13" s="30">
         <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <v>80.163058476193896</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="25">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B14" s="24">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C14" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <v>-0.77463732472189939</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="25">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B15" s="24">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C15" s="30">
         <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <v>-0.99727371031195</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="25">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B16" s="24">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C16" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <v>1028.4103166122507</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="24">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C17" s="30">
         <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <v>-0.98760095272084658</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B18" s="24">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C18" s="30">
         <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <v>98.812318362183703</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B19" s="24">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C19" s="30">
         <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <v>-0.9864837734804992</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B20" s="24">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C20" s="30">
         <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <v>74.639780601233326</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="25">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B21" s="24">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C21" s="30">
         <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="25">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B22" s="24">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C22" s="30">
         <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="25">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B23" s="24">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C23" s="30">
         <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="25">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B24" s="24">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C24" s="30">
         <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="25">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B25" s="24">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C25" s="30">
         <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="25">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B26" s="24">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C26" s="30">
         <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="25">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B27" s="24">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C27" s="30">
         <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="25">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B28" s="24">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C28" s="30">
         <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="25">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B29" s="24">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C29" s="30">
         <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="25">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B30" s="24">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C30" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="25">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B31" s="24">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C31" s="30">
         <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="25">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B32" s="24">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C32" s="30">
         <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="25">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B33" s="24">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C33" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="25">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B34" s="24">
-        <v>499.27660521000001</v>
+        <v>2.8086933300000001</v>
       </c>
       <c r="C34" s="30">
         <f t="shared" si="0"/>
-        <v>75.11816589074563</v>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="25">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B35" s="24">
-        <v>6.5592306300000001</v>
+        <v>499.27660521000001</v>
       </c>
       <c r="C35" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99966330474421161</v>
+        <v>75.11816589074563</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="25">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B36" s="24">
-        <v>19481.20894855</v>
+        <v>6.5592306300000001</v>
       </c>
       <c r="C36" s="30">
         <f t="shared" si="0"/>
-        <v>40.77506746658235</v>
+        <v>-0.99966330474421161</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="25">
-        <v>46233</v>
-      </c>
-      <c r="B37">
-        <v>466.33578662999997</v>
+        <v>46234</v>
+      </c>
+      <c r="B37" s="24">
+        <v>19481.20894855</v>
       </c>
       <c r="C37" s="30">
         <f t="shared" si="0"/>
-        <v>3.5918026507549188</v>
+        <v>40.77506746658235</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="25">
-        <v>46232</v>
-      </c>
-      <c r="B38" s="24">
-        <v>101.55832515</v>
+        <v>46233</v>
+      </c>
+      <c r="B38">
+        <v>466.33578662999997</v>
       </c>
       <c r="C38" s="30">
         <f t="shared" si="0"/>
-        <v>22.269067927747528</v>
+        <v>3.5918026507549188</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="25">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B39" s="24">
-        <v>4.3645205499999999</v>
+        <v>101.55832515</v>
       </c>
       <c r="C39" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98047278251084946</v>
+        <v>22.269067927747528</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="25">
-        <v>46108</v>
+        <v>46231</v>
       </c>
       <c r="B40" s="24">
-        <v>223.50959897000001</v>
+        <v>4.3645205499999999</v>
       </c>
       <c r="C40" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99220607504587943</v>
+        <v>-0.98047278251084946</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="25">
-        <v>46226</v>
+        <v>46108</v>
       </c>
       <c r="B41" s="24">
-        <v>28677.412251940001</v>
+        <v>223.50959897000001</v>
       </c>
       <c r="C41" s="30">
         <f t="shared" si="0"/>
-        <v>32.413800410299046</v>
+        <v>-0.99220607504587943</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="25">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B42" s="24">
-        <v>858.25054019000004</v>
+        <v>28677.412251940001</v>
       </c>
       <c r="C42" s="30">
         <f t="shared" si="0"/>
-        <v>41.77708649767068</v>
+        <v>32.413800410299046</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="25">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B43" s="24">
-        <v>20.063323860000001</v>
+        <v>858.25054019000004</v>
       </c>
       <c r="C43" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99734079323279778</v>
+        <v>41.77708649767068</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="25">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B44" s="24">
-        <v>7544.8528890099997</v>
+        <v>20.063323860000001</v>
       </c>
       <c r="C44" s="30">
         <f t="shared" si="0"/>
-        <v>-0.54491271467140989</v>
+        <v>-0.99734079323279778</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="25">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B45" s="24">
-        <v>16578.913830919999</v>
+        <v>7544.8528890099997</v>
       </c>
       <c r="C45" s="30">
         <f t="shared" si="0"/>
-        <v>1.1008050673763534</v>
+        <v>-0.54491271467140989</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="25">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B46" s="24">
-        <v>7891.6954687400003</v>
+        <v>16578.913830919999</v>
       </c>
       <c r="C46" s="30">
         <f t="shared" si="0"/>
-        <v>-0.79678113606112111</v>
+        <v>1.1008050673763534</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="25">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B47" s="24">
-        <v>38833.478919130001</v>
+        <v>7891.6954687400003</v>
       </c>
       <c r="C47" s="30">
         <f t="shared" si="0"/>
-        <v>-0.25771272667553924</v>
+        <v>-0.79678113606112111</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="25">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B48" s="24">
-        <v>52315.97026473</v>
+        <v>38833.478919130001</v>
       </c>
       <c r="C48" s="30">
         <f t="shared" si="0"/>
-        <v>-0.19048561913228002</v>
+        <v>-0.25771272667553924</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="25">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B49" s="24">
-        <v>64626.363040830001</v>
+        <v>52315.97026473</v>
       </c>
       <c r="C49" s="30">
         <f t="shared" si="0"/>
-        <v>1.2916911129109088</v>
+        <v>-0.19048561913228002</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="25">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B50" s="24">
-        <v>28200.29395617</v>
+        <v>64626.363040830001</v>
       </c>
       <c r="C50" s="30">
         <f t="shared" si="0"/>
-        <v>2.65997178100841</v>
+        <v>1.2916911129109088</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="25">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B51" s="24">
-        <v>7705.0577555</v>
+        <v>28200.29395617</v>
       </c>
       <c r="C51" s="30">
         <f t="shared" si="0"/>
-        <v>0.84099979813836301</v>
+        <v>2.65997178100841</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="25">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B52" s="24">
-        <v>4185.2572516800001</v>
+        <v>7705.0577555</v>
       </c>
       <c r="C52" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5358672604044985</v>
+        <v>0.84099979813836301</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="25">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B53" s="24">
-        <v>9017.3713134900008</v>
+        <v>4185.2572516800001</v>
       </c>
       <c r="C53" s="30">
         <f t="shared" si="0"/>
-        <v>-0.47344417767330416</v>
+        <v>-0.5358672604044985</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="25">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B54" s="24">
-        <v>17125.195337590001</v>
+        <v>9017.3713134900008</v>
       </c>
       <c r="C54" s="30">
         <f t="shared" si="0"/>
-        <v>-0.39167454677290181</v>
+        <v>-0.47344417767330416</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="25">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B55" s="24">
-        <v>28151.370695969999</v>
+        <v>17125.195337590001</v>
       </c>
       <c r="C55" s="30">
         <f t="shared" si="0"/>
-        <v>27.450841046685248</v>
+        <v>-0.39167454677290181</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="25">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B56" s="24">
-        <v>989.47411254999997</v>
+        <v>28151.370695969999</v>
       </c>
       <c r="C56" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82605795449481512</v>
+        <v>27.450841046685248</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="25">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B57" s="24">
-        <v>5688.5275189000004</v>
+        <v>989.47411254999997</v>
       </c>
       <c r="C57" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82035890094428965</v>
+        <v>-0.82605795449481512</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="25">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B58" s="24">
-        <v>31666.069450710002</v>
+        <v>5688.5275189000004</v>
       </c>
       <c r="C58" s="30">
         <f t="shared" si="0"/>
-        <v>12.096519032059602</v>
+        <v>-0.82035890094428965</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="25">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B59" s="24">
-        <v>2417.8997009200002</v>
+        <v>31666.069450710002</v>
       </c>
       <c r="C59" s="30">
         <f t="shared" si="0"/>
-        <v>0.40878477030033311</v>
+        <v>12.096519032059602</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="25">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B60" s="24">
-        <v>1716.30170335</v>
+        <v>2417.8997009200002</v>
       </c>
       <c r="C60" s="30">
         <f t="shared" si="0"/>
-        <v>103.40487339188886</v>
+        <v>0.40878477030033311</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="25">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B61" s="24">
-        <v>16.43890412</v>
+        <v>1716.30170335</v>
       </c>
       <c r="C61" s="30">
         <f t="shared" si="0"/>
-        <v>-0.93907248343987781</v>
+        <v>103.40487339188886</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="25">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B62" s="24">
-        <v>269.81083503999997</v>
+        <v>16.43890412</v>
       </c>
       <c r="C62" s="30">
         <f t="shared" si="0"/>
-        <v>-0.88259974628484428</v>
+        <v>-0.93907248343987781</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="25">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B63" s="24">
-        <v>2298.2133896800001</v>
+        <v>269.81083503999997</v>
       </c>
       <c r="C63" s="30">
         <f t="shared" si="0"/>
-        <v>0.90523755264044037</v>
+        <v>-0.88259974628484428</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="25">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B64" s="24">
-        <v>1206.260808</v>
+        <v>2298.2133896800001</v>
       </c>
       <c r="C64" s="30">
         <f t="shared" si="0"/>
-        <v>142.26137862232778</v>
+        <v>0.90523755264044037</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="25">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B65" s="24">
-        <v>8.42</v>
+        <v>1206.260808</v>
       </c>
       <c r="C65" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5604660313731078</v>
+        <v>142.26137862232778</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="25">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B66" s="24">
-        <v>19.156653639999998</v>
+        <v>8.42</v>
       </c>
       <c r="C66" s="30">
         <f t="shared" si="0"/>
-        <v>0.50703525245440206</v>
+        <v>-0.5604660313731078</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="25">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B67" s="24">
-        <v>12.711483429999999</v>
+        <v>19.156653639999998</v>
       </c>
       <c r="C67" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99943660659465605</v>
+        <v>0.50703525245440206</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="25">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B68" s="24">
-        <v>22562.357509739999</v>
+        <v>12.711483429999999</v>
       </c>
       <c r="C68" s="30">
-        <f t="shared" ref="C68:C109" si="1">+(B68-B69)/B69</f>
-        <v>5.2639483520141219</v>
+        <f t="shared" si="0"/>
+        <v>-0.99943660659465605</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B69" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C69" s="30">
+        <f t="shared" ref="C69:C110" si="1">+(B69-B70)/B70</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="25">
         <v>46182</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B70" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C70" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="25">
+    <row r="71" spans="1:3">
+      <c r="A71" s="25">
         <v>46178</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B71" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C71" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="25">
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
         <v>46177</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
         <v>46176</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
         <v>46175</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
         <v>46174</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>46171</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>45074</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>46169</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>46168</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>46167</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>46164</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>46163</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>46162</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46161</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46157</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46156</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46155</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46154</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="25">
         <v>46153</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="25">
+    <row r="90" spans="1:3">
+      <c r="A90" s="25">
         <v>46150</v>
       </c>
-      <c r="B89" s="24">
+      <c r="B90" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="23">
+    <row r="91" spans="1:3">
+      <c r="A91" s="23">
         <v>46149</v>
       </c>
-      <c r="B90" s="22">
+      <c r="B91" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="18">
+    <row r="92" spans="1:3">
+      <c r="A92" s="18">
         <v>46148</v>
       </c>
-      <c r="B91" s="16">
+      <c r="B92" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="18">
+    <row r="93" spans="1:3">
+      <c r="A93" s="18">
         <v>46147</v>
       </c>
-      <c r="B92" s="16">
+      <c r="B93" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="18">
+    <row r="94" spans="1:3">
+      <c r="A94" s="18">
         <v>46146</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B94" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="19">
+    <row r="95" spans="1:3">
+      <c r="A95" s="19">
         <v>46142</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B95" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="19">
+    <row r="96" spans="1:3">
+      <c r="A96" s="19">
         <v>46141</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B96" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="19">
+    <row r="97" spans="1:4">
+      <c r="A97" s="19">
         <v>46140</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B97" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="19">
+    <row r="98" spans="1:4">
+      <c r="A98" s="19">
         <v>46139</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="19">
+    <row r="99" spans="1:4">
+      <c r="A99" s="19">
         <v>46136</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="19">
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
         <v>46135</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46134</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46133</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46132</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+      <c r="D103" s="37"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46129</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
-      <c r="D103" s="37"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46128</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B105" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46127</v>
       </c>
-      <c r="B105" s="39">
+      <c r="B106" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46126</v>
       </c>
-      <c r="B106" s="39">
+      <c r="B107" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46125</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B108" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+      <c r="D108" s="36"/>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46122</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B109" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
-      <c r="D108" s="36"/>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="19">
         <v>46121</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B110" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C110" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="19">
-        <v>46120</v>
-      </c>
-      <c r="B110" s="16">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C110" s="30">
-        <f>+(B110-B111)/B111</f>
-        <v>3.9632497533121036</v>
-      </c>
       <c r="D110" s="36"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="19">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B111" s="16">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C111" s="30">
+        <f>+(B111-B112)/B112</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B112" s="16">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="19">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B113" s="16">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="19">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B114" s="16">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="19">
+        <v>46112</v>
+      </c>
+      <c r="B115" s="16">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="19">
         <v>46111</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B116" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7898,7 +7930,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9499,7 +9531,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:E103" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E104" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -10071,6 +10103,27 @@
       </c>
       <c r="F103" s="32">
         <v>-0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" s="25">
+        <v>46283</v>
+      </c>
+      <c r="B104" s="26">
+        <v>13335</v>
+      </c>
+      <c r="C104" s="24">
+        <v>3</v>
+      </c>
+      <c r="D104" s="26">
+        <v>13338</v>
+      </c>
+      <c r="E104" s="31">
+        <f t="shared" si="4"/>
+        <v>3.2592707284973294E-2</v>
+      </c>
+      <c r="F104" s="32">
+        <v>3.26</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2989,7 +2989,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5359,6 +5359,26 @@
         <v>23.39</v>
       </c>
     </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="21">
+        <v>46287</v>
+      </c>
+      <c r="B123" s="17">
+        <v>17245.765071999998</v>
+      </c>
+      <c r="C123" s="20"/>
+      <c r="D123" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="E123" s="20"/>
+      <c r="F123" s="17">
+        <v>100</v>
+      </c>
+      <c r="G123" s="20"/>
+      <c r="H123" s="17">
+        <v>4.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5367,7 +5387,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5396,14 +5416,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B2" s="24">
-        <v>137505.15153979001</v>
+        <v>146837.85895197999</v>
       </c>
       <c r="C2" s="30">
-        <f t="shared" ref="C2:C68" si="0">+(B2-B3)/B3</f>
-        <v>0.25618058698994745</v>
+        <f t="shared" ref="C2:C69" si="0">+(B2-B3)/B3</f>
+        <v>6.7871692861553368E-2</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5414,14 +5434,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="25">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B3" s="24">
-        <v>109462.8853239</v>
+        <v>137505.15153979001</v>
       </c>
       <c r="C3" s="30">
         <f t="shared" si="0"/>
-        <v>0.32349555871151542</v>
+        <v>0.25618058698994745</v>
       </c>
       <c r="D3" s="24" t="s">
         <v>9</v>
@@ -5432,14 +5452,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="25">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B4" s="24">
-        <v>82707.40661228</v>
+        <v>109462.8853239</v>
       </c>
       <c r="C4" s="30">
         <f t="shared" si="0"/>
-        <v>28.486447660130633</v>
+        <v>0.32349555871151542</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>10</v>
@@ -5450,14 +5470,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="25">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B5" s="24">
-        <v>2804.9294905100001</v>
+        <v>82707.40661228</v>
       </c>
       <c r="C5" s="30">
         <f t="shared" si="0"/>
-        <v>54.85948274687906</v>
+        <v>28.486447660130633</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>30</v>
@@ -5468,14 +5488,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="25">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B6" s="24">
-        <v>50.214025489999997</v>
+        <v>2804.9294905100001</v>
       </c>
       <c r="C6" s="30">
         <f t="shared" si="0"/>
-        <v>0.37097114686342592</v>
+        <v>54.85948274687906</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5486,14 +5506,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="25">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B7" s="24">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C7" s="30">
         <f t="shared" si="0"/>
-        <v>-0.67806849277578529</v>
+        <v>0.37097114686342592</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -5504,14 +5524,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="25">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B8" s="24">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C8" s="30">
         <f t="shared" si="0"/>
-        <v>18.560573043109468</v>
+        <v>-0.67806849277578529</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -5522,14 +5542,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="25">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B9" s="24">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C9" s="30">
         <f t="shared" si="0"/>
-        <v>0.64045278098882874</v>
+        <v>18.560573043109468</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -5540,1271 +5560,1283 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="25">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B10" s="24">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C10" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <v>0.64045278098882874</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="25">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B11" s="24">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C11" s="30">
         <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <v>-0.82640880552358198</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B12" s="24">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C12" s="30">
         <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <v>2.4737529624349173</v>
       </c>
       <c r="E12" s="37"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="25">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B13" s="24">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C13" s="30">
         <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <v>-0.97953700801723442</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="25">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B14" s="24">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C14" s="30">
         <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <v>80.163058476193896</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="25">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B15" s="24">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C15" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <v>-0.77463732472189939</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="25">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B16" s="24">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C16" s="30">
         <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <v>-0.99727371031195</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B17" s="24">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C17" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <v>1028.4103166122507</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B18" s="24">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C18" s="30">
         <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <v>-0.98760095272084658</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B19" s="24">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C19" s="30">
         <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <v>98.812318362183703</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B20" s="24">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C20" s="30">
         <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <v>-0.9864837734804992</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="25">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B21" s="24">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C21" s="30">
         <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <v>74.639780601233326</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="25">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B22" s="24">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C22" s="30">
         <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="25">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B23" s="24">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C23" s="30">
         <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="25">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B24" s="24">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C24" s="30">
         <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="25">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B25" s="24">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C25" s="30">
         <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="25">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B26" s="24">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C26" s="30">
         <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="25">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B27" s="24">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C27" s="30">
         <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="25">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B28" s="24">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C28" s="30">
         <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="25">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B29" s="24">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C29" s="30">
         <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="25">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B30" s="24">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C30" s="30">
         <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="25">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B31" s="24">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C31" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="25">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B32" s="24">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C32" s="30">
         <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="25">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B33" s="24">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C33" s="30">
         <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="25">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B34" s="24">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C34" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="25">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B35" s="24">
-        <v>499.27660521000001</v>
+        <v>2.8086933300000001</v>
       </c>
       <c r="C35" s="30">
         <f t="shared" si="0"/>
-        <v>75.11816589074563</v>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="25">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B36" s="24">
-        <v>6.5592306300000001</v>
+        <v>499.27660521000001</v>
       </c>
       <c r="C36" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99966330474421161</v>
+        <v>75.11816589074563</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="25">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B37" s="24">
-        <v>19481.20894855</v>
+        <v>6.5592306300000001</v>
       </c>
       <c r="C37" s="30">
         <f t="shared" si="0"/>
-        <v>40.77506746658235</v>
+        <v>-0.99966330474421161</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="25">
-        <v>46233</v>
-      </c>
-      <c r="B38">
-        <v>466.33578662999997</v>
+        <v>46234</v>
+      </c>
+      <c r="B38" s="24">
+        <v>19481.20894855</v>
       </c>
       <c r="C38" s="30">
         <f t="shared" si="0"/>
-        <v>3.5918026507549188</v>
+        <v>40.77506746658235</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="25">
-        <v>46232</v>
-      </c>
-      <c r="B39" s="24">
-        <v>101.55832515</v>
+        <v>46233</v>
+      </c>
+      <c r="B39">
+        <v>466.33578662999997</v>
       </c>
       <c r="C39" s="30">
         <f t="shared" si="0"/>
-        <v>22.269067927747528</v>
+        <v>3.5918026507549188</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="25">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B40" s="24">
-        <v>4.3645205499999999</v>
+        <v>101.55832515</v>
       </c>
       <c r="C40" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98047278251084946</v>
+        <v>22.269067927747528</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="25">
-        <v>46108</v>
+        <v>46231</v>
       </c>
       <c r="B41" s="24">
-        <v>223.50959897000001</v>
+        <v>4.3645205499999999</v>
       </c>
       <c r="C41" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99220607504587943</v>
+        <v>-0.98047278251084946</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="25">
-        <v>46226</v>
+        <v>46108</v>
       </c>
       <c r="B42" s="24">
-        <v>28677.412251940001</v>
+        <v>223.50959897000001</v>
       </c>
       <c r="C42" s="30">
         <f t="shared" si="0"/>
-        <v>32.413800410299046</v>
+        <v>-0.99220607504587943</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="25">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B43" s="24">
-        <v>858.25054019000004</v>
+        <v>28677.412251940001</v>
       </c>
       <c r="C43" s="30">
         <f t="shared" si="0"/>
-        <v>41.77708649767068</v>
+        <v>32.413800410299046</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="25">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B44" s="24">
-        <v>20.063323860000001</v>
+        <v>858.25054019000004</v>
       </c>
       <c r="C44" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99734079323279778</v>
+        <v>41.77708649767068</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="25">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B45" s="24">
-        <v>7544.8528890099997</v>
+        <v>20.063323860000001</v>
       </c>
       <c r="C45" s="30">
         <f t="shared" si="0"/>
-        <v>-0.54491271467140989</v>
+        <v>-0.99734079323279778</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="25">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B46" s="24">
-        <v>16578.913830919999</v>
+        <v>7544.8528890099997</v>
       </c>
       <c r="C46" s="30">
         <f t="shared" si="0"/>
-        <v>1.1008050673763534</v>
+        <v>-0.54491271467140989</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="25">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B47" s="24">
-        <v>7891.6954687400003</v>
+        <v>16578.913830919999</v>
       </c>
       <c r="C47" s="30">
         <f t="shared" si="0"/>
-        <v>-0.79678113606112111</v>
+        <v>1.1008050673763534</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="25">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B48" s="24">
-        <v>38833.478919130001</v>
+        <v>7891.6954687400003</v>
       </c>
       <c r="C48" s="30">
         <f t="shared" si="0"/>
-        <v>-0.25771272667553924</v>
+        <v>-0.79678113606112111</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="25">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B49" s="24">
-        <v>52315.97026473</v>
+        <v>38833.478919130001</v>
       </c>
       <c r="C49" s="30">
         <f t="shared" si="0"/>
-        <v>-0.19048561913228002</v>
+        <v>-0.25771272667553924</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="25">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B50" s="24">
-        <v>64626.363040830001</v>
+        <v>52315.97026473</v>
       </c>
       <c r="C50" s="30">
         <f t="shared" si="0"/>
-        <v>1.2916911129109088</v>
+        <v>-0.19048561913228002</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="25">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B51" s="24">
-        <v>28200.29395617</v>
+        <v>64626.363040830001</v>
       </c>
       <c r="C51" s="30">
         <f t="shared" si="0"/>
-        <v>2.65997178100841</v>
+        <v>1.2916911129109088</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="25">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B52" s="24">
-        <v>7705.0577555</v>
+        <v>28200.29395617</v>
       </c>
       <c r="C52" s="30">
         <f t="shared" si="0"/>
-        <v>0.84099979813836301</v>
+        <v>2.65997178100841</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="25">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B53" s="24">
-        <v>4185.2572516800001</v>
+        <v>7705.0577555</v>
       </c>
       <c r="C53" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5358672604044985</v>
+        <v>0.84099979813836301</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="25">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B54" s="24">
-        <v>9017.3713134900008</v>
+        <v>4185.2572516800001</v>
       </c>
       <c r="C54" s="30">
         <f t="shared" si="0"/>
-        <v>-0.47344417767330416</v>
+        <v>-0.5358672604044985</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="25">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B55" s="24">
-        <v>17125.195337590001</v>
+        <v>9017.3713134900008</v>
       </c>
       <c r="C55" s="30">
         <f t="shared" si="0"/>
-        <v>-0.39167454677290181</v>
+        <v>-0.47344417767330416</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="25">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B56" s="24">
-        <v>28151.370695969999</v>
+        <v>17125.195337590001</v>
       </c>
       <c r="C56" s="30">
         <f t="shared" si="0"/>
-        <v>27.450841046685248</v>
+        <v>-0.39167454677290181</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="25">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B57" s="24">
-        <v>989.47411254999997</v>
+        <v>28151.370695969999</v>
       </c>
       <c r="C57" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82605795449481512</v>
+        <v>27.450841046685248</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="25">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B58" s="24">
-        <v>5688.5275189000004</v>
+        <v>989.47411254999997</v>
       </c>
       <c r="C58" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82035890094428965</v>
+        <v>-0.82605795449481512</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="25">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B59" s="24">
-        <v>31666.069450710002</v>
+        <v>5688.5275189000004</v>
       </c>
       <c r="C59" s="30">
         <f t="shared" si="0"/>
-        <v>12.096519032059602</v>
+        <v>-0.82035890094428965</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="25">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B60" s="24">
-        <v>2417.8997009200002</v>
+        <v>31666.069450710002</v>
       </c>
       <c r="C60" s="30">
         <f t="shared" si="0"/>
-        <v>0.40878477030033311</v>
+        <v>12.096519032059602</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="25">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B61" s="24">
-        <v>1716.30170335</v>
+        <v>2417.8997009200002</v>
       </c>
       <c r="C61" s="30">
         <f t="shared" si="0"/>
-        <v>103.40487339188886</v>
+        <v>0.40878477030033311</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="25">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B62" s="24">
-        <v>16.43890412</v>
+        <v>1716.30170335</v>
       </c>
       <c r="C62" s="30">
         <f t="shared" si="0"/>
-        <v>-0.93907248343987781</v>
+        <v>103.40487339188886</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="25">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B63" s="24">
-        <v>269.81083503999997</v>
+        <v>16.43890412</v>
       </c>
       <c r="C63" s="30">
         <f t="shared" si="0"/>
-        <v>-0.88259974628484428</v>
+        <v>-0.93907248343987781</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="25">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B64" s="24">
-        <v>2298.2133896800001</v>
+        <v>269.81083503999997</v>
       </c>
       <c r="C64" s="30">
         <f t="shared" si="0"/>
-        <v>0.90523755264044037</v>
+        <v>-0.88259974628484428</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="25">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B65" s="24">
-        <v>1206.260808</v>
+        <v>2298.2133896800001</v>
       </c>
       <c r="C65" s="30">
         <f t="shared" si="0"/>
-        <v>142.26137862232778</v>
+        <v>0.90523755264044037</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="25">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B66" s="24">
-        <v>8.42</v>
+        <v>1206.260808</v>
       </c>
       <c r="C66" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5604660313731078</v>
+        <v>142.26137862232778</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="25">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B67" s="24">
-        <v>19.156653639999998</v>
+        <v>8.42</v>
       </c>
       <c r="C67" s="30">
         <f t="shared" si="0"/>
-        <v>0.50703525245440206</v>
+        <v>-0.5604660313731078</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="25">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B68" s="24">
-        <v>12.711483429999999</v>
+        <v>19.156653639999998</v>
       </c>
       <c r="C68" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99943660659465605</v>
+        <v>0.50703525245440206</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="25">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B69" s="24">
-        <v>22562.357509739999</v>
+        <v>12.711483429999999</v>
       </c>
       <c r="C69" s="30">
-        <f t="shared" ref="C69:C110" si="1">+(B69-B70)/B70</f>
-        <v>5.2639483520141219</v>
+        <f t="shared" si="0"/>
+        <v>-0.99943660659465605</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B70" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C70" s="30">
+        <f t="shared" ref="C70:C111" si="1">+(B70-B71)/B71</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="25">
         <v>46182</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B71" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C71" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="25">
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
         <v>46178</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
         <v>46177</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
         <v>46176</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
         <v>46175</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>46174</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>46171</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>45074</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>46169</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>46168</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>46167</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>46164</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>46163</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46162</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46161</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46157</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46156</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46155</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="25">
         <v>46154</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="25">
+    <row r="90" spans="1:3">
+      <c r="A90" s="25">
         <v>46153</v>
       </c>
-      <c r="B89" s="24">
+      <c r="B90" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="25">
+    <row r="91" spans="1:3">
+      <c r="A91" s="25">
         <v>46150</v>
       </c>
-      <c r="B90" s="24">
+      <c r="B91" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="23">
+    <row r="92" spans="1:3">
+      <c r="A92" s="23">
         <v>46149</v>
       </c>
-      <c r="B91" s="22">
+      <c r="B92" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="18">
+    <row r="93" spans="1:3">
+      <c r="A93" s="18">
         <v>46148</v>
       </c>
-      <c r="B92" s="16">
+      <c r="B93" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="18">
+    <row r="94" spans="1:3">
+      <c r="A94" s="18">
         <v>46147</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B94" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="18">
+    <row r="95" spans="1:3">
+      <c r="A95" s="18">
         <v>46146</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B95" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="19">
+    <row r="96" spans="1:3">
+      <c r="A96" s="19">
         <v>46142</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B96" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="19">
+    <row r="97" spans="1:4">
+      <c r="A97" s="19">
         <v>46141</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B97" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="19">
+    <row r="98" spans="1:4">
+      <c r="A98" s="19">
         <v>46140</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="19">
+    <row r="99" spans="1:4">
+      <c r="A99" s="19">
         <v>46139</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="19">
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
         <v>46136</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46135</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46134</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46133</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+      <c r="D103" s="37"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46132</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
-      <c r="D103" s="37"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46129</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B105" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46128</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B106" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46127</v>
       </c>
-      <c r="B106" s="39">
+      <c r="B107" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46126</v>
       </c>
-      <c r="B107" s="39">
+      <c r="B108" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+      <c r="D108" s="36"/>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46125</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B109" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
-      <c r="D108" s="36"/>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="19">
         <v>46122</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B110" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C110" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="19">
+      <c r="D110" s="36"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="19">
         <v>46121</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B111" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C110" s="30">
+      <c r="C111" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
-      <c r="D110" s="36"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="19">
-        <v>46120</v>
-      </c>
-      <c r="B111" s="16">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C111" s="30">
-        <f>+(B111-B112)/B112</f>
-        <v>3.9632497533121036</v>
-      </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="19">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B112" s="16">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C112" s="30">
+        <f>+(B112-B113)/B113</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="19">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B113" s="16">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="19">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B114" s="16">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="19">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B115" s="16">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="19">
+        <v>46112</v>
+      </c>
+      <c r="B116" s="16">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="19">
         <v>46111</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B117" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7930,7 +7962,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9531,7 +9563,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:E104" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E105" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -10124,6 +10156,27 @@
       </c>
       <c r="F104" s="32">
         <v>3.26</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" s="25">
+        <v>46286</v>
+      </c>
+      <c r="B105" s="26">
+        <v>13272</v>
+      </c>
+      <c r="C105" s="24">
+        <v>3</v>
+      </c>
+      <c r="D105" s="26">
+        <v>13275</v>
+      </c>
+      <c r="E105" s="31">
+        <f t="shared" si="4"/>
+        <v>-4.7233468286099868E-3</v>
+      </c>
+      <c r="F105" s="32">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2989,7 +2989,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5379,6 +5379,26 @@
         <v>4.63</v>
       </c>
     </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="21">
+        <v>46288</v>
+      </c>
+      <c r="B124" s="17">
+        <v>8934.4187999999995</v>
+      </c>
+      <c r="C124" s="20"/>
+      <c r="D124" s="17">
+        <v>0.95</v>
+      </c>
+      <c r="E124" s="20"/>
+      <c r="F124" s="17">
+        <v>50</v>
+      </c>
+      <c r="G124" s="20"/>
+      <c r="H124" s="17">
+        <v>4.1399999999999997</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5387,7 +5407,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5416,14 +5436,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B2" s="24">
-        <v>146837.85895197999</v>
+        <v>174433.37119511</v>
       </c>
       <c r="C2" s="30">
-        <f t="shared" ref="C2:C69" si="0">+(B2-B3)/B3</f>
-        <v>6.7871692861553368E-2</v>
+        <f t="shared" ref="C2:C70" si="0">+(B2-B3)/B3</f>
+        <v>0.18793186198768058</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5434,14 +5454,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="25">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B3" s="24">
-        <v>137505.15153979001</v>
+        <v>146837.85895197999</v>
       </c>
       <c r="C3" s="30">
         <f t="shared" si="0"/>
-        <v>0.25618058698994745</v>
+        <v>6.7871692861553368E-2</v>
       </c>
       <c r="D3" s="24" t="s">
         <v>9</v>
@@ -5452,14 +5472,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="25">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B4" s="24">
-        <v>109462.8853239</v>
+        <v>137505.15153979001</v>
       </c>
       <c r="C4" s="30">
         <f t="shared" si="0"/>
-        <v>0.32349555871151542</v>
+        <v>0.25618058698994745</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>10</v>
@@ -5470,14 +5490,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="25">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B5" s="24">
-        <v>82707.40661228</v>
+        <v>109462.8853239</v>
       </c>
       <c r="C5" s="30">
         <f t="shared" si="0"/>
-        <v>28.486447660130633</v>
+        <v>0.32349555871151542</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>30</v>
@@ -5488,14 +5508,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="25">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B6" s="24">
-        <v>2804.9294905100001</v>
+        <v>82707.40661228</v>
       </c>
       <c r="C6" s="30">
         <f t="shared" si="0"/>
-        <v>54.85948274687906</v>
+        <v>28.486447660130633</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5506,14 +5526,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="25">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B7" s="24">
-        <v>50.214025489999997</v>
+        <v>2804.9294905100001</v>
       </c>
       <c r="C7" s="30">
         <f t="shared" si="0"/>
-        <v>0.37097114686342592</v>
+        <v>54.85948274687906</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -5524,14 +5544,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="25">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B8" s="24">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C8" s="30">
         <f t="shared" si="0"/>
-        <v>-0.67806849277578529</v>
+        <v>0.37097114686342592</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -5542,14 +5562,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="25">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B9" s="24">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C9" s="30">
         <f t="shared" si="0"/>
-        <v>18.560573043109468</v>
+        <v>-0.67806849277578529</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -5560,1283 +5580,1295 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="25">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B10" s="24">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C10" s="30">
         <f t="shared" si="0"/>
-        <v>0.64045278098882874</v>
+        <v>18.560573043109468</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="25">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B11" s="24">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C11" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <v>0.64045278098882874</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B12" s="24">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C12" s="30">
         <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <v>-0.82640880552358198</v>
       </c>
       <c r="E12" s="37"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="25">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B13" s="24">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C13" s="30">
         <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <v>2.4737529624349173</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="25">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B14" s="24">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C14" s="30">
         <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <v>-0.97953700801723442</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="25">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B15" s="24">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C15" s="30">
         <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <v>80.163058476193896</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="25">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B16" s="24">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C16" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <v>-0.77463732472189939</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B17" s="24">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C17" s="30">
         <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <v>-0.99727371031195</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B18" s="24">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C18" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <v>1028.4103166122507</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B19" s="24">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C19" s="30">
         <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <v>-0.98760095272084658</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B20" s="24">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C20" s="30">
         <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <v>98.812318362183703</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="25">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B21" s="24">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C21" s="30">
         <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <v>-0.9864837734804992</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="25">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B22" s="24">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C22" s="30">
         <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <v>74.639780601233326</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="25">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B23" s="24">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C23" s="30">
         <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="25">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B24" s="24">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C24" s="30">
         <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="25">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B25" s="24">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C25" s="30">
         <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="25">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B26" s="24">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C26" s="30">
         <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="25">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B27" s="24">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C27" s="30">
         <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="25">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B28" s="24">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C28" s="30">
         <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="25">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B29" s="24">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C29" s="30">
         <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="25">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B30" s="24">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C30" s="30">
         <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="25">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B31" s="24">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C31" s="30">
         <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="25">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B32" s="24">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C32" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="25">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B33" s="24">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C33" s="30">
         <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="25">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B34" s="24">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C34" s="30">
         <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="25">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B35" s="24">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C35" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="25">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B36" s="24">
-        <v>499.27660521000001</v>
+        <v>2.8086933300000001</v>
       </c>
       <c r="C36" s="30">
         <f t="shared" si="0"/>
-        <v>75.11816589074563</v>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="25">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B37" s="24">
-        <v>6.5592306300000001</v>
+        <v>499.27660521000001</v>
       </c>
       <c r="C37" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99966330474421161</v>
+        <v>75.11816589074563</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="25">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B38" s="24">
-        <v>19481.20894855</v>
+        <v>6.5592306300000001</v>
       </c>
       <c r="C38" s="30">
         <f t="shared" si="0"/>
-        <v>40.77506746658235</v>
+        <v>-0.99966330474421161</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="25">
-        <v>46233</v>
-      </c>
-      <c r="B39">
-        <v>466.33578662999997</v>
+        <v>46234</v>
+      </c>
+      <c r="B39" s="24">
+        <v>19481.20894855</v>
       </c>
       <c r="C39" s="30">
         <f t="shared" si="0"/>
-        <v>3.5918026507549188</v>
+        <v>40.77506746658235</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="25">
-        <v>46232</v>
-      </c>
-      <c r="B40" s="24">
-        <v>101.55832515</v>
+        <v>46233</v>
+      </c>
+      <c r="B40">
+        <v>466.33578662999997</v>
       </c>
       <c r="C40" s="30">
         <f t="shared" si="0"/>
-        <v>22.269067927747528</v>
+        <v>3.5918026507549188</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="25">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B41" s="24">
-        <v>4.3645205499999999</v>
+        <v>101.55832515</v>
       </c>
       <c r="C41" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98047278251084946</v>
+        <v>22.269067927747528</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="25">
-        <v>46108</v>
+        <v>46231</v>
       </c>
       <c r="B42" s="24">
-        <v>223.50959897000001</v>
+        <v>4.3645205499999999</v>
       </c>
       <c r="C42" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99220607504587943</v>
+        <v>-0.98047278251084946</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="25">
-        <v>46226</v>
+        <v>46108</v>
       </c>
       <c r="B43" s="24">
-        <v>28677.412251940001</v>
+        <v>223.50959897000001</v>
       </c>
       <c r="C43" s="30">
         <f t="shared" si="0"/>
-        <v>32.413800410299046</v>
+        <v>-0.99220607504587943</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="25">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B44" s="24">
-        <v>858.25054019000004</v>
+        <v>28677.412251940001</v>
       </c>
       <c r="C44" s="30">
         <f t="shared" si="0"/>
-        <v>41.77708649767068</v>
+        <v>32.413800410299046</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="25">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B45" s="24">
-        <v>20.063323860000001</v>
+        <v>858.25054019000004</v>
       </c>
       <c r="C45" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99734079323279778</v>
+        <v>41.77708649767068</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="25">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B46" s="24">
-        <v>7544.8528890099997</v>
+        <v>20.063323860000001</v>
       </c>
       <c r="C46" s="30">
         <f t="shared" si="0"/>
-        <v>-0.54491271467140989</v>
+        <v>-0.99734079323279778</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="25">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B47" s="24">
-        <v>16578.913830919999</v>
+        <v>7544.8528890099997</v>
       </c>
       <c r="C47" s="30">
         <f t="shared" si="0"/>
-        <v>1.1008050673763534</v>
+        <v>-0.54491271467140989</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="25">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B48" s="24">
-        <v>7891.6954687400003</v>
+        <v>16578.913830919999</v>
       </c>
       <c r="C48" s="30">
         <f t="shared" si="0"/>
-        <v>-0.79678113606112111</v>
+        <v>1.1008050673763534</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="25">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B49" s="24">
-        <v>38833.478919130001</v>
+        <v>7891.6954687400003</v>
       </c>
       <c r="C49" s="30">
         <f t="shared" si="0"/>
-        <v>-0.25771272667553924</v>
+        <v>-0.79678113606112111</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="25">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B50" s="24">
-        <v>52315.97026473</v>
+        <v>38833.478919130001</v>
       </c>
       <c r="C50" s="30">
         <f t="shared" si="0"/>
-        <v>-0.19048561913228002</v>
+        <v>-0.25771272667553924</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="25">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B51" s="24">
-        <v>64626.363040830001</v>
+        <v>52315.97026473</v>
       </c>
       <c r="C51" s="30">
         <f t="shared" si="0"/>
-        <v>1.2916911129109088</v>
+        <v>-0.19048561913228002</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="25">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B52" s="24">
-        <v>28200.29395617</v>
+        <v>64626.363040830001</v>
       </c>
       <c r="C52" s="30">
         <f t="shared" si="0"/>
-        <v>2.65997178100841</v>
+        <v>1.2916911129109088</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="25">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B53" s="24">
-        <v>7705.0577555</v>
+        <v>28200.29395617</v>
       </c>
       <c r="C53" s="30">
         <f t="shared" si="0"/>
-        <v>0.84099979813836301</v>
+        <v>2.65997178100841</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="25">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B54" s="24">
-        <v>4185.2572516800001</v>
+        <v>7705.0577555</v>
       </c>
       <c r="C54" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5358672604044985</v>
+        <v>0.84099979813836301</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="25">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B55" s="24">
-        <v>9017.3713134900008</v>
+        <v>4185.2572516800001</v>
       </c>
       <c r="C55" s="30">
         <f t="shared" si="0"/>
-        <v>-0.47344417767330416</v>
+        <v>-0.5358672604044985</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="25">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B56" s="24">
-        <v>17125.195337590001</v>
+        <v>9017.3713134900008</v>
       </c>
       <c r="C56" s="30">
         <f t="shared" si="0"/>
-        <v>-0.39167454677290181</v>
+        <v>-0.47344417767330416</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="25">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B57" s="24">
-        <v>28151.370695969999</v>
+        <v>17125.195337590001</v>
       </c>
       <c r="C57" s="30">
         <f t="shared" si="0"/>
-        <v>27.450841046685248</v>
+        <v>-0.39167454677290181</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="25">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B58" s="24">
-        <v>989.47411254999997</v>
+        <v>28151.370695969999</v>
       </c>
       <c r="C58" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82605795449481512</v>
+        <v>27.450841046685248</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="25">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B59" s="24">
-        <v>5688.5275189000004</v>
+        <v>989.47411254999997</v>
       </c>
       <c r="C59" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82035890094428965</v>
+        <v>-0.82605795449481512</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="25">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B60" s="24">
-        <v>31666.069450710002</v>
+        <v>5688.5275189000004</v>
       </c>
       <c r="C60" s="30">
         <f t="shared" si="0"/>
-        <v>12.096519032059602</v>
+        <v>-0.82035890094428965</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="25">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B61" s="24">
-        <v>2417.8997009200002</v>
+        <v>31666.069450710002</v>
       </c>
       <c r="C61" s="30">
         <f t="shared" si="0"/>
-        <v>0.40878477030033311</v>
+        <v>12.096519032059602</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="25">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B62" s="24">
-        <v>1716.30170335</v>
+        <v>2417.8997009200002</v>
       </c>
       <c r="C62" s="30">
         <f t="shared" si="0"/>
-        <v>103.40487339188886</v>
+        <v>0.40878477030033311</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="25">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B63" s="24">
-        <v>16.43890412</v>
+        <v>1716.30170335</v>
       </c>
       <c r="C63" s="30">
         <f t="shared" si="0"/>
-        <v>-0.93907248343987781</v>
+        <v>103.40487339188886</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="25">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B64" s="24">
-        <v>269.81083503999997</v>
+        <v>16.43890412</v>
       </c>
       <c r="C64" s="30">
         <f t="shared" si="0"/>
-        <v>-0.88259974628484428</v>
+        <v>-0.93907248343987781</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="25">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B65" s="24">
-        <v>2298.2133896800001</v>
+        <v>269.81083503999997</v>
       </c>
       <c r="C65" s="30">
         <f t="shared" si="0"/>
-        <v>0.90523755264044037</v>
+        <v>-0.88259974628484428</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="25">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B66" s="24">
-        <v>1206.260808</v>
+        <v>2298.2133896800001</v>
       </c>
       <c r="C66" s="30">
         <f t="shared" si="0"/>
-        <v>142.26137862232778</v>
+        <v>0.90523755264044037</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="25">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B67" s="24">
-        <v>8.42</v>
+        <v>1206.260808</v>
       </c>
       <c r="C67" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5604660313731078</v>
+        <v>142.26137862232778</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="25">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B68" s="24">
-        <v>19.156653639999998</v>
+        <v>8.42</v>
       </c>
       <c r="C68" s="30">
         <f t="shared" si="0"/>
-        <v>0.50703525245440206</v>
+        <v>-0.5604660313731078</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="25">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B69" s="24">
-        <v>12.711483429999999</v>
+        <v>19.156653639999998</v>
       </c>
       <c r="C69" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99943660659465605</v>
+        <v>0.50703525245440206</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="25">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B70" s="24">
-        <v>22562.357509739999</v>
+        <v>12.711483429999999</v>
       </c>
       <c r="C70" s="30">
-        <f t="shared" ref="C70:C111" si="1">+(B70-B71)/B71</f>
-        <v>5.2639483520141219</v>
+        <f t="shared" si="0"/>
+        <v>-0.99943660659465605</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B71" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C71" s="30">
+        <f t="shared" ref="C71:C112" si="1">+(B71-B72)/B72</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
         <v>46182</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
         <v>46178</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
         <v>46177</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
         <v>46176</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>46175</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>46174</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>46171</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>45074</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>46169</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>46168</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>46167</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>46164</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46163</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46162</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46161</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46157</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46156</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="25">
         <v>46155</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="25">
+    <row r="90" spans="1:3">
+      <c r="A90" s="25">
         <v>46154</v>
       </c>
-      <c r="B89" s="24">
+      <c r="B90" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="25">
+    <row r="91" spans="1:3">
+      <c r="A91" s="25">
         <v>46153</v>
       </c>
-      <c r="B90" s="24">
+      <c r="B91" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="25">
+    <row r="92" spans="1:3">
+      <c r="A92" s="25">
         <v>46150</v>
       </c>
-      <c r="B91" s="24">
+      <c r="B92" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="23">
+    <row r="93" spans="1:3">
+      <c r="A93" s="23">
         <v>46149</v>
       </c>
-      <c r="B92" s="22">
+      <c r="B93" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="18">
+    <row r="94" spans="1:3">
+      <c r="A94" s="18">
         <v>46148</v>
       </c>
-      <c r="B93" s="16">
+      <c r="B94" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="18">
+    <row r="95" spans="1:3">
+      <c r="A95" s="18">
         <v>46147</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B95" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="18">
+    <row r="96" spans="1:3">
+      <c r="A96" s="18">
         <v>46146</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B96" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="19">
+    <row r="97" spans="1:4">
+      <c r="A97" s="19">
         <v>46142</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B97" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="19">
+    <row r="98" spans="1:4">
+      <c r="A98" s="19">
         <v>46141</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="19">
+    <row r="99" spans="1:4">
+      <c r="A99" s="19">
         <v>46140</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="19">
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
         <v>46139</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46136</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46135</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46134</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+      <c r="D103" s="37"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46133</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
-      <c r="D103" s="37"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46132</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B105" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46129</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B106" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46128</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46127</v>
       </c>
-      <c r="B107" s="39">
+      <c r="B108" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+      <c r="D108" s="36"/>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46126</v>
       </c>
-      <c r="B108" s="39">
+      <c r="B109" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
-      <c r="D108" s="36"/>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="19">
         <v>46125</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B110" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C110" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="19">
+      <c r="D110" s="36"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="19">
         <v>46122</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B111" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C110" s="30">
+      <c r="C111" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
-      <c r="D110" s="36"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="19">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="19">
         <v>46121</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B112" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C111" s="30">
+      <c r="C112" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="19">
+    <row r="113" spans="1:3">
+      <c r="A113" s="19">
         <v>46120</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B113" s="16">
         <v>580.56056466999996</v>
       </c>
-      <c r="C112" s="30">
-        <f>+(B112-B113)/B113</f>
+      <c r="C113" s="30">
+        <f>+(B113-B114)/B114</f>
         <v>3.9632497533121036</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="19">
+    <row r="114" spans="1:3">
+      <c r="A114" s="19">
         <v>46119</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B114" s="16">
         <v>116.97186189</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="19">
+    <row r="115" spans="1:3">
+      <c r="A115" s="19">
         <v>46118</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B115" s="16">
         <v>6972.36861443</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="19">
+    <row r="116" spans="1:3">
+      <c r="A116" s="19">
         <v>46113</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B116" s="16">
         <v>540.00852741999995</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="19">
+    <row r="117" spans="1:3">
+      <c r="A117" s="19">
         <v>46112</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B117" s="16">
         <v>5262.3389565099997</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="19">
+    <row r="118" spans="1:3">
+      <c r="A118" s="19">
         <v>46111</v>
       </c>
-      <c r="B117" s="16">
+      <c r="B118" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7962,7 +7994,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9563,7 +9595,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:E105" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E106" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -10177,6 +10209,27 @@
       </c>
       <c r="F105" s="32">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" s="25">
+        <v>46287</v>
+      </c>
+      <c r="B106" s="26">
+        <v>13034</v>
+      </c>
+      <c r="C106" s="24">
+        <v>3</v>
+      </c>
+      <c r="D106" s="26">
+        <v>13037</v>
+      </c>
+      <c r="E106" s="31">
+        <f t="shared" si="4"/>
+        <v>-1.7928436911487759E-2</v>
+      </c>
+      <c r="F106" s="32">
+        <v>-1.79</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H124"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5399,6 +5399,26 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="21">
+        <v>46289</v>
+      </c>
+      <c r="B125" s="17">
+        <v>11795.6893</v>
+      </c>
+      <c r="C125" s="20"/>
+      <c r="D125" s="17">
+        <v>1</v>
+      </c>
+      <c r="E125" s="20"/>
+      <c r="F125" s="17">
+        <v>50</v>
+      </c>
+      <c r="G125" s="20"/>
+      <c r="H125" s="17">
+        <v>5.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5407,7 +5427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5436,14 +5456,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B2" s="24">
-        <v>174433.37119511</v>
+        <v>183559.87790473</v>
       </c>
       <c r="C2" s="30">
-        <f t="shared" ref="C2:C70" si="0">+(B2-B3)/B3</f>
-        <v>0.18793186198768058</v>
+        <f t="shared" ref="C2:C71" si="0">+(B2-B3)/B3</f>
+        <v>5.2320875570372835E-2</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5454,14 +5474,14 @@
     </row>
     <row r="3" spans="1:5" ht="17.25" customHeight="1">
       <c r="A3" s="25">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B3" s="24">
-        <v>146837.85895197999</v>
+        <v>174433.37119511</v>
       </c>
       <c r="C3" s="30">
         <f t="shared" si="0"/>
-        <v>6.7871692861553368E-2</v>
+        <v>0.18793186198768058</v>
       </c>
       <c r="D3" s="24" t="s">
         <v>9</v>
@@ -5472,14 +5492,14 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="25">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B4" s="24">
-        <v>137505.15153979001</v>
+        <v>146837.85895197999</v>
       </c>
       <c r="C4" s="30">
         <f t="shared" si="0"/>
-        <v>0.25618058698994745</v>
+        <v>6.7871692861553368E-2</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>10</v>
@@ -5490,14 +5510,14 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="25">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B5" s="24">
-        <v>109462.8853239</v>
+        <v>137505.15153979001</v>
       </c>
       <c r="C5" s="30">
         <f t="shared" si="0"/>
-        <v>0.32349555871151542</v>
+        <v>0.25618058698994745</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>30</v>
@@ -5508,14 +5528,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="25">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B6" s="24">
-        <v>82707.40661228</v>
+        <v>109462.8853239</v>
       </c>
       <c r="C6" s="30">
         <f t="shared" si="0"/>
-        <v>28.486447660130633</v>
+        <v>0.32349555871151542</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5526,14 +5546,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="25">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B7" s="24">
-        <v>2804.9294905100001</v>
+        <v>82707.40661228</v>
       </c>
       <c r="C7" s="30">
         <f t="shared" si="0"/>
-        <v>54.85948274687906</v>
+        <v>28.486447660130633</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -5544,14 +5564,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="25">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B8" s="24">
-        <v>50.214025489999997</v>
+        <v>2804.9294905100001</v>
       </c>
       <c r="C8" s="30">
         <f t="shared" si="0"/>
-        <v>0.37097114686342592</v>
+        <v>54.85948274687906</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -5562,14 +5582,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="25">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B9" s="24">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C9" s="30">
         <f t="shared" si="0"/>
-        <v>-0.67806849277578529</v>
+        <v>0.37097114686342592</v>
       </c>
       <c r="D9" t="s">
         <v>37</v>
@@ -5580,1295 +5600,1307 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="25">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B10" s="24">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C10" s="30">
         <f t="shared" si="0"/>
-        <v>18.560573043109468</v>
+        <v>-0.67806849277578529</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="25">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B11" s="24">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C11" s="30">
         <f t="shared" si="0"/>
-        <v>0.64045278098882874</v>
+        <v>18.560573043109468</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="25">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B12" s="24">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C12" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <v>0.64045278098882874</v>
       </c>
       <c r="E12" s="37"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="25">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B13" s="24">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C13" s="30">
         <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <v>-0.82640880552358198</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="25">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B14" s="24">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C14" s="30">
         <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <v>2.4737529624349173</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="25">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B15" s="24">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C15" s="30">
         <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <v>-0.97953700801723442</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="25">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B16" s="24">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C16" s="30">
         <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <v>80.163058476193896</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="25">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B17" s="24">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C17" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <v>-0.77463732472189939</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="25">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B18" s="24">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C18" s="30">
         <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <v>-0.99727371031195</v>
       </c>
       <c r="E18" s="7"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="25">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B19" s="24">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C19" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <v>1028.4103166122507</v>
       </c>
       <c r="E19" s="7"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="25">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B20" s="24">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C20" s="30">
         <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <v>-0.98760095272084658</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="25">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B21" s="24">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C21" s="30">
         <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <v>98.812318362183703</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="25">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B22" s="24">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C22" s="30">
         <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <v>-0.9864837734804992</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="25">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B23" s="24">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C23" s="30">
         <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <v>74.639780601233326</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="25">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B24" s="24">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C24" s="30">
         <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="25">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B25" s="24">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C25" s="30">
         <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="25">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B26" s="24">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C26" s="30">
         <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="25">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B27" s="24">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C27" s="30">
         <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="25">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B28" s="24">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C28" s="30">
         <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="25">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B29" s="24">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C29" s="30">
         <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="25">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B30" s="24">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C30" s="30">
         <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="25">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B31" s="24">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C31" s="30">
         <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="25">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B32" s="24">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C32" s="30">
         <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="25">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B33" s="24">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C33" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="25">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B34" s="24">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C34" s="30">
         <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="25">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B35" s="24">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C35" s="30">
         <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="25">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B36" s="24">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C36" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="25">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B37" s="24">
-        <v>499.27660521000001</v>
+        <v>2.8086933300000001</v>
       </c>
       <c r="C37" s="30">
         <f t="shared" si="0"/>
-        <v>75.11816589074563</v>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="25">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B38" s="24">
-        <v>6.5592306300000001</v>
+        <v>499.27660521000001</v>
       </c>
       <c r="C38" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99966330474421161</v>
+        <v>75.11816589074563</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="25">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B39" s="24">
-        <v>19481.20894855</v>
+        <v>6.5592306300000001</v>
       </c>
       <c r="C39" s="30">
         <f t="shared" si="0"/>
-        <v>40.77506746658235</v>
+        <v>-0.99966330474421161</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="25">
-        <v>46233</v>
-      </c>
-      <c r="B40">
-        <v>466.33578662999997</v>
+        <v>46234</v>
+      </c>
+      <c r="B40" s="24">
+        <v>19481.20894855</v>
       </c>
       <c r="C40" s="30">
         <f t="shared" si="0"/>
-        <v>3.5918026507549188</v>
+        <v>40.77506746658235</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="25">
-        <v>46232</v>
-      </c>
-      <c r="B41" s="24">
-        <v>101.55832515</v>
+        <v>46233</v>
+      </c>
+      <c r="B41">
+        <v>466.33578662999997</v>
       </c>
       <c r="C41" s="30">
         <f t="shared" si="0"/>
-        <v>22.269067927747528</v>
+        <v>3.5918026507549188</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="25">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B42" s="24">
-        <v>4.3645205499999999</v>
+        <v>101.55832515</v>
       </c>
       <c r="C42" s="30">
         <f t="shared" si="0"/>
-        <v>-0.98047278251084946</v>
+        <v>22.269067927747528</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="25">
-        <v>46108</v>
+        <v>46231</v>
       </c>
       <c r="B43" s="24">
-        <v>223.50959897000001</v>
+        <v>4.3645205499999999</v>
       </c>
       <c r="C43" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99220607504587943</v>
+        <v>-0.98047278251084946</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="25">
-        <v>46226</v>
+        <v>46108</v>
       </c>
       <c r="B44" s="24">
-        <v>28677.412251940001</v>
+        <v>223.50959897000001</v>
       </c>
       <c r="C44" s="30">
         <f t="shared" si="0"/>
-        <v>32.413800410299046</v>
+        <v>-0.99220607504587943</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="25">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B45" s="24">
-        <v>858.25054019000004</v>
+        <v>28677.412251940001</v>
       </c>
       <c r="C45" s="30">
         <f t="shared" si="0"/>
-        <v>41.77708649767068</v>
+        <v>32.413800410299046</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="25">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B46" s="24">
-        <v>20.063323860000001</v>
+        <v>858.25054019000004</v>
       </c>
       <c r="C46" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99734079323279778</v>
+        <v>41.77708649767068</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="25">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B47" s="24">
-        <v>7544.8528890099997</v>
+        <v>20.063323860000001</v>
       </c>
       <c r="C47" s="30">
         <f t="shared" si="0"/>
-        <v>-0.54491271467140989</v>
+        <v>-0.99734079323279778</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="25">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B48" s="24">
-        <v>16578.913830919999</v>
+        <v>7544.8528890099997</v>
       </c>
       <c r="C48" s="30">
         <f t="shared" si="0"/>
-        <v>1.1008050673763534</v>
+        <v>-0.54491271467140989</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="25">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B49" s="24">
-        <v>7891.6954687400003</v>
+        <v>16578.913830919999</v>
       </c>
       <c r="C49" s="30">
         <f t="shared" si="0"/>
-        <v>-0.79678113606112111</v>
+        <v>1.1008050673763534</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="25">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B50" s="24">
-        <v>38833.478919130001</v>
+        <v>7891.6954687400003</v>
       </c>
       <c r="C50" s="30">
         <f t="shared" si="0"/>
-        <v>-0.25771272667553924</v>
+        <v>-0.79678113606112111</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="25">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B51" s="24">
-        <v>52315.97026473</v>
+        <v>38833.478919130001</v>
       </c>
       <c r="C51" s="30">
         <f t="shared" si="0"/>
-        <v>-0.19048561913228002</v>
+        <v>-0.25771272667553924</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="25">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B52" s="24">
-        <v>64626.363040830001</v>
+        <v>52315.97026473</v>
       </c>
       <c r="C52" s="30">
         <f t="shared" si="0"/>
-        <v>1.2916911129109088</v>
+        <v>-0.19048561913228002</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="25">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B53" s="24">
-        <v>28200.29395617</v>
+        <v>64626.363040830001</v>
       </c>
       <c r="C53" s="30">
         <f t="shared" si="0"/>
-        <v>2.65997178100841</v>
+        <v>1.2916911129109088</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="25">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B54" s="24">
-        <v>7705.0577555</v>
+        <v>28200.29395617</v>
       </c>
       <c r="C54" s="30">
         <f t="shared" si="0"/>
-        <v>0.84099979813836301</v>
+        <v>2.65997178100841</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="25">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B55" s="24">
-        <v>4185.2572516800001</v>
+        <v>7705.0577555</v>
       </c>
       <c r="C55" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5358672604044985</v>
+        <v>0.84099979813836301</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="25">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B56" s="24">
-        <v>9017.3713134900008</v>
+        <v>4185.2572516800001</v>
       </c>
       <c r="C56" s="30">
         <f t="shared" si="0"/>
-        <v>-0.47344417767330416</v>
+        <v>-0.5358672604044985</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="25">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B57" s="24">
-        <v>17125.195337590001</v>
+        <v>9017.3713134900008</v>
       </c>
       <c r="C57" s="30">
         <f t="shared" si="0"/>
-        <v>-0.39167454677290181</v>
+        <v>-0.47344417767330416</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="25">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B58" s="24">
-        <v>28151.370695969999</v>
+        <v>17125.195337590001</v>
       </c>
       <c r="C58" s="30">
         <f t="shared" si="0"/>
-        <v>27.450841046685248</v>
+        <v>-0.39167454677290181</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="25">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B59" s="24">
-        <v>989.47411254999997</v>
+        <v>28151.370695969999</v>
       </c>
       <c r="C59" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82605795449481512</v>
+        <v>27.450841046685248</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="25">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B60" s="24">
-        <v>5688.5275189000004</v>
+        <v>989.47411254999997</v>
       </c>
       <c r="C60" s="30">
         <f t="shared" si="0"/>
-        <v>-0.82035890094428965</v>
+        <v>-0.82605795449481512</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="25">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B61" s="24">
-        <v>31666.069450710002</v>
+        <v>5688.5275189000004</v>
       </c>
       <c r="C61" s="30">
         <f t="shared" si="0"/>
-        <v>12.096519032059602</v>
+        <v>-0.82035890094428965</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="25">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B62" s="24">
-        <v>2417.8997009200002</v>
+        <v>31666.069450710002</v>
       </c>
       <c r="C62" s="30">
         <f t="shared" si="0"/>
-        <v>0.40878477030033311</v>
+        <v>12.096519032059602</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="25">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B63" s="24">
-        <v>1716.30170335</v>
+        <v>2417.8997009200002</v>
       </c>
       <c r="C63" s="30">
         <f t="shared" si="0"/>
-        <v>103.40487339188886</v>
+        <v>0.40878477030033311</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="25">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B64" s="24">
-        <v>16.43890412</v>
+        <v>1716.30170335</v>
       </c>
       <c r="C64" s="30">
         <f t="shared" si="0"/>
-        <v>-0.93907248343987781</v>
+        <v>103.40487339188886</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="25">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B65" s="24">
-        <v>269.81083503999997</v>
+        <v>16.43890412</v>
       </c>
       <c r="C65" s="30">
         <f t="shared" si="0"/>
-        <v>-0.88259974628484428</v>
+        <v>-0.93907248343987781</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="25">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B66" s="24">
-        <v>2298.2133896800001</v>
+        <v>269.81083503999997</v>
       </c>
       <c r="C66" s="30">
         <f t="shared" si="0"/>
-        <v>0.90523755264044037</v>
+        <v>-0.88259974628484428</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="25">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B67" s="24">
-        <v>1206.260808</v>
+        <v>2298.2133896800001</v>
       </c>
       <c r="C67" s="30">
         <f t="shared" si="0"/>
-        <v>142.26137862232778</v>
+        <v>0.90523755264044037</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="25">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B68" s="24">
-        <v>8.42</v>
+        <v>1206.260808</v>
       </c>
       <c r="C68" s="30">
         <f t="shared" si="0"/>
-        <v>-0.5604660313731078</v>
+        <v>142.26137862232778</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="25">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B69" s="24">
-        <v>19.156653639999998</v>
+        <v>8.42</v>
       </c>
       <c r="C69" s="30">
         <f t="shared" si="0"/>
-        <v>0.50703525245440206</v>
+        <v>-0.5604660313731078</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="25">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B70" s="24">
-        <v>12.711483429999999</v>
+        <v>19.156653639999998</v>
       </c>
       <c r="C70" s="30">
         <f t="shared" si="0"/>
-        <v>-0.99943660659465605</v>
+        <v>0.50703525245440206</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="25">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B71" s="24">
-        <v>22562.357509739999</v>
+        <v>12.711483429999999</v>
       </c>
       <c r="C71" s="30">
-        <f t="shared" ref="C71:C112" si="1">+(B71-B72)/B72</f>
-        <v>5.2639483520141219</v>
+        <f t="shared" si="0"/>
+        <v>-0.99943660659465605</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B72" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C72" s="30">
+        <f t="shared" ref="C72:C113" si="1">+(B72-B73)/B73</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
         <v>46182</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
         <v>46178</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
         <v>46177</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>46176</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>46175</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>46174</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>46171</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>45074</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>46169</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>46168</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>46167</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46164</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46163</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46162</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46161</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46157</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="25">
         <v>46156</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="25">
+    <row r="90" spans="1:3">
+      <c r="A90" s="25">
         <v>46155</v>
       </c>
-      <c r="B89" s="24">
+      <c r="B90" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="25">
+    <row r="91" spans="1:3">
+      <c r="A91" s="25">
         <v>46154</v>
       </c>
-      <c r="B90" s="24">
+      <c r="B91" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="25">
+    <row r="92" spans="1:3">
+      <c r="A92" s="25">
         <v>46153</v>
       </c>
-      <c r="B91" s="24">
+      <c r="B92" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="25">
+    <row r="93" spans="1:3">
+      <c r="A93" s="25">
         <v>46150</v>
       </c>
-      <c r="B92" s="24">
+      <c r="B93" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="23">
+    <row r="94" spans="1:3">
+      <c r="A94" s="23">
         <v>46149</v>
       </c>
-      <c r="B93" s="22">
+      <c r="B94" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="18">
+    <row r="95" spans="1:3">
+      <c r="A95" s="18">
         <v>46148</v>
       </c>
-      <c r="B94" s="16">
+      <c r="B95" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="18">
+    <row r="96" spans="1:3">
+      <c r="A96" s="18">
         <v>46147</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B96" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="18">
+    <row r="97" spans="1:4">
+      <c r="A97" s="18">
         <v>46146</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B97" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="19">
+    <row r="98" spans="1:4">
+      <c r="A98" s="19">
         <v>46142</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="19">
+    <row r="99" spans="1:4">
+      <c r="A99" s="19">
         <v>46141</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="19">
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
         <v>46140</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46139</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46136</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46135</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+      <c r="D103" s="37"/>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46134</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
-      <c r="D103" s="37"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46133</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B105" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46132</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B106" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46129</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46128</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B108" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+      <c r="D108" s="36"/>
+    </row>
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46127</v>
       </c>
-      <c r="B108" s="39">
+      <c r="B109" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
-      <c r="D108" s="36"/>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="19">
         <v>46126</v>
       </c>
-      <c r="B109" s="39">
+      <c r="B110" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C110" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="19">
+      <c r="D110" s="36"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="19">
         <v>46125</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B111" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C110" s="30">
+      <c r="C111" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
-      <c r="D110" s="36"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="19">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="19">
         <v>46122</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B112" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C111" s="30">
+      <c r="C112" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="19">
+    <row r="113" spans="1:3">
+      <c r="A113" s="19">
         <v>46121</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B113" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C112" s="30">
+      <c r="C113" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="19">
-        <v>46120</v>
-      </c>
-      <c r="B113" s="16">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C113" s="30">
-        <f>+(B113-B114)/B114</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="114" spans="1:3">
       <c r="A114" s="19">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B114" s="16">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C114" s="30">
+        <f>+(B114-B115)/B115</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="19">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B115" s="16">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="19">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B116" s="16">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="19">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B117" s="16">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="19">
+        <v>46112</v>
+      </c>
+      <c r="B118" s="16">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="19">
         <v>46111</v>
       </c>
-      <c r="B118" s="16">
+      <c r="B119" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7994,7 +8026,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G106"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9595,7 +9627,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:E106" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:F107" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -10230,6 +10262,27 @@
       </c>
       <c r="F106" s="32">
         <v>-1.79</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" s="25">
+        <v>46288</v>
+      </c>
+      <c r="B107" s="26">
+        <v>12909</v>
+      </c>
+      <c r="C107" s="24">
+        <v>3</v>
+      </c>
+      <c r="D107" s="26">
+        <v>12912</v>
+      </c>
+      <c r="E107" s="31">
+        <f t="shared" si="4"/>
+        <v>-9.5880954207256276E-3</v>
+      </c>
+      <c r="F107" s="31">
+        <v>-9.5999999999999992E-3</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -87,9 +87,6 @@
     <t>Monto E</t>
   </si>
   <si>
-    <t>mONTOf</t>
-  </si>
-  <si>
     <t>LIQUIDEZ</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>1.185.93</t>
+  </si>
+  <si>
+    <t>MONTO F</t>
   </si>
 </sst>
 </file>
@@ -2989,7 +2989,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5419,6 +5419,23 @@
         <v>5.18</v>
       </c>
     </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="21">
+        <v>46290</v>
+      </c>
+      <c r="B126">
+        <v>624.74</v>
+      </c>
+      <c r="D126" s="17">
+        <v>0.33</v>
+      </c>
+      <c r="F126" s="17">
+        <v>0.33</v>
+      </c>
+      <c r="H126" s="17">
+        <v>0.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5427,7 +5444,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5456,14 +5473,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B2" s="24">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C2" s="30">
-        <f t="shared" ref="C2:C71" si="0">+(B2-B3)/B3</f>
-        <v>5.2320875570372835E-2</v>
+        <f>+(B2-B3)/B3</f>
+        <v>0.55858664283872839</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5472,1435 +5489,1448 @@
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.25" customHeight="1">
+    <row r="3" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="25">
+        <v>46289</v>
+      </c>
+      <c r="B3" s="24">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C3" s="30">
+        <f t="shared" ref="C2:C72" si="0">+(B3-B4)/B4</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5">
+        <v>68497.757342013356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="17.25" customHeight="1">
+      <c r="A4" s="25">
         <v>46288</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B4" s="24">
         <v>174433.37119511</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C4" s="30">
         <f t="shared" si="0"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="D3" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5">
-        <v>68497.757342013356</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="25">
+      <c r="D4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
+        <v>85928.931135131905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="25">
         <v>46287</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B5" s="24">
         <v>146837.85895197999</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C5" s="30">
         <f t="shared" si="0"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6">
-        <v>85928.931135131905</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="25">
+      <c r="D5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="25">
         <v>46286</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B6" s="24">
         <v>137505.15153979001</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C6" s="30">
         <f t="shared" si="0"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D6" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="6">
-        <v>22227.4775024345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="25">
+      <c r="E6" s="6">
+        <v>24565.759999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="25">
         <v>46283</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B7" s="24">
         <v>109462.8853239</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C7" s="30">
         <f t="shared" si="0"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="6">
-        <v>24565.759999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="25">
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="25">
         <v>46282</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B8" s="24">
         <v>82707.40661228</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C8" s="30">
         <f t="shared" si="0"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="D7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="25">
+      <c r="D8" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="34">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="25">
         <v>46281</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B9" s="24">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C9" s="30">
         <f t="shared" si="0"/>
         <v>54.85948274687906</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D9" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="34">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="25">
+      <c r="E9" s="35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25">
         <v>46280</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B10" s="24">
         <v>50.214025489999997</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C10" s="30">
         <f t="shared" si="0"/>
         <v>0.37097114686342592</v>
       </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="25">
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="25">
         <v>46276</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B11" s="24">
         <v>36.626609979999998</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C11" s="30">
         <f t="shared" si="0"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="25">
+    <row r="12" spans="1:5">
+      <c r="A12" s="25">
         <v>46275</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B12" s="24">
         <v>113.77143633999999</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C12" s="30">
         <f t="shared" si="0"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="25">
+    <row r="13" spans="1:5">
+      <c r="A13" s="25">
         <v>46274</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B13" s="24">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C13" s="30">
         <f t="shared" si="0"/>
         <v>0.64045278098882874</v>
       </c>
-      <c r="E12" s="37"/>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="25">
+      <c r="E13" s="37"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="25">
         <v>46273</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B14" s="24">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C14" s="30">
         <f t="shared" si="0"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="25">
+    <row r="15" spans="1:5">
+      <c r="A15" s="25">
         <v>46272</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B15" s="24">
         <v>20.42491424</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C15" s="30">
         <f t="shared" si="0"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="25">
+    <row r="16" spans="1:5">
+      <c r="A16" s="25">
         <v>46269</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B16" s="24">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C16" s="30">
         <f t="shared" si="0"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="25">
+    <row r="17" spans="1:5">
+      <c r="A17" s="25">
         <v>46268</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B17" s="24">
         <v>287.33741307000003</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C17" s="30">
         <f t="shared" si="0"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="25">
+    <row r="18" spans="1:5">
+      <c r="A18" s="25">
         <v>46267</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B18" s="24">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C18" s="30">
         <f t="shared" si="0"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="25">
+    <row r="19" spans="1:5">
+      <c r="A19" s="25">
         <v>46266</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B19" s="24">
         <v>15.709117340000001</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C19" s="30">
         <f t="shared" si="0"/>
         <v>-0.99727371031195</v>
       </c>
-      <c r="E18" s="7"/>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="25">
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="25">
         <v>46265</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B20" s="24">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C20" s="30">
         <f t="shared" si="0"/>
         <v>1028.4103166122507</v>
       </c>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="25">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="25">
         <v>46262</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B21" s="24">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C21" s="30">
         <f t="shared" si="0"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="25">
+    <row r="22" spans="1:5">
+      <c r="A22" s="25">
         <v>46261</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B22" s="24">
         <v>451.44302815999998</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C22" s="30">
         <f t="shared" si="0"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="25">
+    <row r="23" spans="1:5">
+      <c r="A23" s="25">
         <v>46260</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B23" s="24">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="30">
         <f t="shared" si="0"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="25">
+    <row r="24" spans="1:5">
+      <c r="A24" s="25">
         <v>46259</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B24" s="24">
         <v>334.62882287999997</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C24" s="30">
         <f t="shared" si="0"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="25">
+    <row r="25" spans="1:5">
+      <c r="A25" s="25">
         <v>46256</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B25" s="24">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C25" s="30">
         <f t="shared" si="0"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="25">
+    <row r="26" spans="1:5">
+      <c r="A26" s="25">
         <v>46255</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B26" s="24">
         <v>126.21011864</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="30">
         <f t="shared" si="0"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="25">
+    <row r="27" spans="1:5">
+      <c r="A27" s="25">
         <v>46254</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B27" s="24">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C27" s="30">
         <f t="shared" si="0"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="25">
+    <row r="28" spans="1:5">
+      <c r="A28" s="25">
         <v>46253</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B28" s="24">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C28" s="30">
         <f t="shared" si="0"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="25">
+    <row r="29" spans="1:5">
+      <c r="A29" s="25">
         <v>46252</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B29" s="24">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C29" s="30">
         <f t="shared" si="0"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="25">
+    <row r="30" spans="1:5">
+      <c r="A30" s="25">
         <v>46251</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B30" s="24">
         <v>12.53018157</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C30" s="30">
         <f t="shared" si="0"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="25">
+    <row r="31" spans="1:5">
+      <c r="A31" s="25">
         <v>46248</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B31" s="24">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C31" s="30">
         <f t="shared" si="0"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="25">
+    <row r="32" spans="1:5">
+      <c r="A32" s="25">
         <v>46247</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B32" s="24">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C32" s="30">
         <f t="shared" si="0"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="25">
+    <row r="33" spans="1:3">
+      <c r="A33" s="25">
         <v>46246</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B33" s="24">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C33" s="30">
         <f t="shared" si="0"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="25">
+    <row r="34" spans="1:3">
+      <c r="A34" s="25">
         <v>46245</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B34" s="24">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C34" s="30">
         <f t="shared" si="0"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="25">
+    <row r="35" spans="1:3">
+      <c r="A35" s="25">
         <v>46244</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B35" s="24">
         <v>4.14256738</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C35" s="30">
         <f t="shared" si="0"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="25">
+    <row r="36" spans="1:3">
+      <c r="A36" s="25">
         <v>46241</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B36" s="24">
         <v>15624.152913600001</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C36" s="30">
         <f t="shared" si="0"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="25">
+    <row r="37" spans="1:3">
+      <c r="A37" s="25">
         <v>46240</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B37" s="24">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C37" s="30">
         <f t="shared" si="0"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="25">
+    <row r="38" spans="1:3">
+      <c r="A38" s="25">
         <v>46239</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B38" s="24">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C38" s="30">
         <f t="shared" si="0"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="25">
+    <row r="39" spans="1:3">
+      <c r="A39" s="25">
         <v>46238</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B39" s="24">
         <v>499.27660521000001</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C39" s="30">
         <f t="shared" si="0"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="25">
+    <row r="40" spans="1:3">
+      <c r="A40" s="25">
         <v>46237</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B40" s="24">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C40" s="30">
         <f t="shared" si="0"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="25">
+    <row r="41" spans="1:3">
+      <c r="A41" s="25">
         <v>46234</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B41" s="24">
         <v>19481.20894855</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C41" s="30">
         <f t="shared" si="0"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="25">
+    <row r="42" spans="1:3">
+      <c r="A42" s="25">
         <v>46233</v>
       </c>
-      <c r="B41">
+      <c r="B42">
         <v>466.33578662999997</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C42" s="30">
         <f t="shared" si="0"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="25">
+    <row r="43" spans="1:3">
+      <c r="A43" s="25">
         <v>46232</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B43" s="24">
         <v>101.55832515</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C43" s="30">
         <f t="shared" si="0"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="25">
+    <row r="44" spans="1:3">
+      <c r="A44" s="25">
         <v>46231</v>
       </c>
-      <c r="B43" s="24">
+      <c r="B44" s="24">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C44" s="30">
         <f t="shared" si="0"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="25">
+    <row r="45" spans="1:3">
+      <c r="A45" s="25">
         <v>46108</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B45" s="24">
         <v>223.50959897000001</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C45" s="30">
         <f t="shared" si="0"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="25">
+    <row r="46" spans="1:3">
+      <c r="A46" s="25">
         <v>46226</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B46" s="24">
         <v>28677.412251940001</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C46" s="30">
         <f t="shared" si="0"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="25">
+    <row r="47" spans="1:3">
+      <c r="A47" s="25">
         <v>46225</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B47" s="24">
         <v>858.25054019000004</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C47" s="30">
         <f t="shared" si="0"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="25">
+    <row r="48" spans="1:3">
+      <c r="A48" s="25">
         <v>46224</v>
       </c>
-      <c r="B47" s="24">
+      <c r="B48" s="24">
         <v>20.063323860000001</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C48" s="30">
         <f t="shared" si="0"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="25">
+    <row r="49" spans="1:3">
+      <c r="A49" s="25">
         <v>46220</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B49" s="24">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C49" s="30">
         <f t="shared" si="0"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="25">
+    <row r="50" spans="1:3">
+      <c r="A50" s="25">
         <v>46219</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B50" s="24">
         <v>16578.913830919999</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C50" s="30">
         <f t="shared" si="0"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="25">
+    <row r="51" spans="1:3">
+      <c r="A51" s="25">
         <v>46218</v>
       </c>
-      <c r="B50" s="24">
+      <c r="B51" s="24">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C51" s="30">
         <f t="shared" si="0"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="25">
+    <row r="52" spans="1:3">
+      <c r="A52" s="25">
         <v>46217</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B52" s="24">
         <v>38833.478919130001</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C52" s="30">
         <f t="shared" si="0"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="25">
+    <row r="53" spans="1:3">
+      <c r="A53" s="25">
         <v>46216</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B53" s="24">
         <v>52315.97026473</v>
       </c>
-      <c r="C52" s="30">
+      <c r="C53" s="30">
         <f t="shared" si="0"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="25">
+    <row r="54" spans="1:3">
+      <c r="A54" s="25">
         <v>46213</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B54" s="24">
         <v>64626.363040830001</v>
       </c>
-      <c r="C53" s="30">
+      <c r="C54" s="30">
         <f t="shared" si="0"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="25">
+    <row r="55" spans="1:3">
+      <c r="A55" s="25">
         <v>46212</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B55" s="24">
         <v>28200.29395617</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C55" s="30">
         <f t="shared" si="0"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="25">
+    <row r="56" spans="1:3">
+      <c r="A56" s="25">
         <v>46211</v>
       </c>
-      <c r="B55" s="24">
+      <c r="B56" s="24">
         <v>7705.0577555</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C56" s="30">
         <f t="shared" si="0"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="25">
+    <row r="57" spans="1:3">
+      <c r="A57" s="25">
         <v>46210</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B57" s="24">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C57" s="30">
         <f t="shared" si="0"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="25">
+    <row r="58" spans="1:3">
+      <c r="A58" s="25">
         <v>46209</v>
       </c>
-      <c r="B57" s="24">
+      <c r="B58" s="24">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C57" s="30">
+      <c r="C58" s="30">
         <f t="shared" si="0"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="25">
+    <row r="59" spans="1:3">
+      <c r="A59" s="25">
         <v>46206</v>
       </c>
-      <c r="B58" s="24">
+      <c r="B59" s="24">
         <v>17125.195337590001</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C59" s="30">
         <f t="shared" si="0"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="25">
+    <row r="60" spans="1:3">
+      <c r="A60" s="25">
         <v>46205</v>
       </c>
-      <c r="B59" s="24">
+      <c r="B60" s="24">
         <v>28151.370695969999</v>
       </c>
-      <c r="C59" s="30">
+      <c r="C60" s="30">
         <f t="shared" si="0"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="25">
+    <row r="61" spans="1:3">
+      <c r="A61" s="25">
         <v>46204</v>
       </c>
-      <c r="B60" s="24">
+      <c r="B61" s="24">
         <v>989.47411254999997</v>
       </c>
-      <c r="C60" s="30">
+      <c r="C61" s="30">
         <f t="shared" si="0"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="25">
+    <row r="62" spans="1:3">
+      <c r="A62" s="25">
         <v>46203</v>
       </c>
-      <c r="B61" s="24">
+      <c r="B62" s="24">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C62" s="30">
         <f t="shared" si="0"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="25">
+    <row r="63" spans="1:3">
+      <c r="A63" s="25">
         <v>46198</v>
       </c>
-      <c r="B62" s="24">
+      <c r="B63" s="24">
         <v>31666.069450710002</v>
       </c>
-      <c r="C62" s="30">
+      <c r="C63" s="30">
         <f t="shared" si="0"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="25">
+    <row r="64" spans="1:3">
+      <c r="A64" s="25">
         <v>46196</v>
       </c>
-      <c r="B63" s="24">
+      <c r="B64" s="24">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C63" s="30">
+      <c r="C64" s="30">
         <f t="shared" si="0"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="25">
+    <row r="65" spans="1:3">
+      <c r="A65" s="25">
         <v>46195</v>
       </c>
-      <c r="B64" s="24">
+      <c r="B65" s="24">
         <v>1716.30170335</v>
       </c>
-      <c r="C64" s="30">
+      <c r="C65" s="30">
         <f t="shared" si="0"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="25">
+    <row r="66" spans="1:3">
+      <c r="A66" s="25">
         <v>46192</v>
       </c>
-      <c r="B65" s="24">
+      <c r="B66" s="24">
         <v>16.43890412</v>
       </c>
-      <c r="C65" s="30">
+      <c r="C66" s="30">
         <f t="shared" si="0"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="25">
+    <row r="67" spans="1:3">
+      <c r="A67" s="25">
         <v>46191</v>
       </c>
-      <c r="B66" s="24">
+      <c r="B67" s="24">
         <v>269.81083503999997</v>
       </c>
-      <c r="C66" s="30">
+      <c r="C67" s="30">
         <f t="shared" si="0"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="25">
+    <row r="68" spans="1:3">
+      <c r="A68" s="25">
         <v>46190</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B68" s="24">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C67" s="30">
+      <c r="C68" s="30">
         <f t="shared" si="0"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="25">
+    <row r="69" spans="1:3">
+      <c r="A69" s="25">
         <v>46189</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B69" s="24">
         <v>1206.260808</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C69" s="30">
         <f t="shared" si="0"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="25">
+    <row r="70" spans="1:3">
+      <c r="A70" s="25">
         <v>46188</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B70" s="24">
         <v>8.42</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C70" s="30">
         <f t="shared" si="0"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="25">
+    <row r="71" spans="1:3">
+      <c r="A71" s="25">
         <v>46185</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B71" s="24">
         <v>19.156653639999998</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C71" s="30">
         <f t="shared" si="0"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="25">
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
         <v>46184</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="24">
         <v>12.711483429999999</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="30">
         <f t="shared" si="0"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
-        <v>46183</v>
-      </c>
-      <c r="B72" s="24">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C72" s="30">
-        <f t="shared" ref="C72:C113" si="1">+(B72-B73)/B73</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="73" spans="1:3">
       <c r="A73" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B73" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C73" s="30">
+        <f t="shared" ref="C73:C114" si="1">+(B73-B74)/B74</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
         <v>46182</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
         <v>46178</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>46177</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>46176</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>46175</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>46174</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>46171</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>45074</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>46169</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>46168</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46167</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46164</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46163</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46162</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46161</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="25">
         <v>46157</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="25">
+    <row r="90" spans="1:3">
+      <c r="A90" s="25">
         <v>46156</v>
       </c>
-      <c r="B89" s="24">
+      <c r="B90" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="25">
+    <row r="91" spans="1:3">
+      <c r="A91" s="25">
         <v>46155</v>
       </c>
-      <c r="B90" s="24">
+      <c r="B91" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="25">
+    <row r="92" spans="1:3">
+      <c r="A92" s="25">
         <v>46154</v>
       </c>
-      <c r="B91" s="24">
+      <c r="B92" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="25">
+    <row r="93" spans="1:3">
+      <c r="A93" s="25">
         <v>46153</v>
       </c>
-      <c r="B92" s="24">
+      <c r="B93" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="25">
+    <row r="94" spans="1:3">
+      <c r="A94" s="25">
         <v>46150</v>
       </c>
-      <c r="B93" s="24">
+      <c r="B94" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="23">
+    <row r="95" spans="1:3">
+      <c r="A95" s="23">
         <v>46149</v>
       </c>
-      <c r="B94" s="22">
+      <c r="B95" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="18">
+    <row r="96" spans="1:3">
+      <c r="A96" s="18">
         <v>46148</v>
       </c>
-      <c r="B95" s="16">
+      <c r="B96" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="18">
+    <row r="97" spans="1:4">
+      <c r="A97" s="18">
         <v>46147</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B97" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="18">
+    <row r="98" spans="1:4">
+      <c r="A98" s="18">
         <v>46146</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="19">
+    <row r="99" spans="1:4">
+      <c r="A99" s="19">
         <v>46142</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="19">
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
         <v>46141</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46140</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46139</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46136</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46135</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
-      <c r="D103" s="37"/>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+      <c r="D104" s="37"/>
+    </row>
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46134</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B105" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46133</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B106" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46132</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46129</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B108" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46128</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B109" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
-      <c r="D108" s="36"/>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
+      <c r="D109" s="36"/>
+    </row>
+    <row r="110" spans="1:4">
+      <c r="A110" s="19">
         <v>46127</v>
       </c>
-      <c r="B109" s="39">
+      <c r="B110" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C110" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="19">
+    <row r="111" spans="1:4">
+      <c r="A111" s="19">
         <v>46126</v>
       </c>
-      <c r="B110" s="39">
+      <c r="B111" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C110" s="30">
+      <c r="C111" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
-      <c r="D110" s="36"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="19">
+      <c r="D111" s="36"/>
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="19">
         <v>46125</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B112" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C111" s="30">
+      <c r="C112" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="19">
+    <row r="113" spans="1:3">
+      <c r="A113" s="19">
         <v>46122</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B113" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C112" s="30">
+      <c r="C113" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="19">
+    <row r="114" spans="1:3">
+      <c r="A114" s="19">
         <v>46121</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B114" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C113" s="30">
+      <c r="C114" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="19">
-        <v>46120</v>
-      </c>
-      <c r="B114" s="16">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C114" s="30">
-        <f>+(B114-B115)/B115</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="115" spans="1:3">
       <c r="A115" s="19">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B115" s="16">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C115" s="30">
+        <f>+(B115-B116)/B116</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="19">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B116" s="16">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="19">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B117" s="16">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="19">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B118" s="16">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="19">
+        <v>46112</v>
+      </c>
+      <c r="B119" s="16">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="19">
         <v>46111</v>
       </c>
-      <c r="B119" s="16">
+      <c r="B120" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -6937,7 +6967,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="17">
         <v>98931.490865999993</v>
@@ -6951,7 +6981,7 @@
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="17">
         <v>251306.31</v>
@@ -6963,12 +6993,12 @@
         <v>188.96</v>
       </c>
       <c r="G3" s="33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="17">
         <v>254788.61</v>
@@ -6980,12 +7010,12 @@
         <v>245.29</v>
       </c>
       <c r="G4" s="33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" s="24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="17">
         <v>40192.65</v>
@@ -6997,12 +7027,12 @@
         <v>81.88</v>
       </c>
       <c r="G5" s="33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="17">
         <v>10939.03</v>
@@ -7022,7 +7052,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -7227,7 +7257,7 @@
         <v>1452167458.20135</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" ref="C18:C25" si="0">+((B18-B17)/B17)*100</f>
+        <f t="shared" ref="C18:C28" si="0">+((B18-B17)/B17)*100</f>
         <v>0.77731466473397282</v>
       </c>
     </row>
@@ -7316,8 +7346,42 @@
       </c>
       <c r="E25" s="38"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" ht="15" thickBot="1">
+      <c r="A26" s="25">
+        <v>46269</v>
+      </c>
+      <c r="B26" s="17">
+        <v>1705456884.3822601</v>
+      </c>
+      <c r="C26" s="4">
+        <f t="shared" si="0"/>
+        <v>5.5202236947693484</v>
+      </c>
       <c r="E26" s="38"/>
+    </row>
+    <row r="27" spans="1:5" ht="15" thickBot="1">
+      <c r="A27" s="25">
+        <v>46276</v>
+      </c>
+      <c r="B27" s="17">
+        <v>1626323546.47457</v>
+      </c>
+      <c r="C27" s="4">
+        <f t="shared" si="0"/>
+        <v>-4.6400081193699148</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" thickBot="1">
+      <c r="A28" s="25">
+        <v>46283</v>
+      </c>
+      <c r="B28" s="17">
+        <v>1735040974.8817899</v>
+      </c>
+      <c r="C28" s="4">
+        <f t="shared" si="0"/>
+        <v>6.6848585352459482</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7326,7 +7390,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -7341,7 +7405,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>18</v>
@@ -7356,13 +7420,13 @@
         <v>21</v>
       </c>
       <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
         <v>22</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>23</v>
-      </c>
-      <c r="H1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -8018,6 +8082,46 @@
       <c r="H26" s="27">
         <v>-0.19229640741738052</v>
       </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="25">
+        <v>46283</v>
+      </c>
+      <c r="B27" s="17">
+        <v>79889194.534160003</v>
+      </c>
+      <c r="C27" s="17">
+        <v>2514501098.3346596</v>
+      </c>
+      <c r="D27" s="17">
+        <v>236888778.51269996</v>
+      </c>
+      <c r="E27" s="17">
+        <v>2831279071.3815198</v>
+      </c>
+      <c r="F27" s="17">
+        <v>7866916.1232899986</v>
+      </c>
+      <c r="G27" s="17">
+        <v>2839145987.5048099</v>
+      </c>
+      <c r="H27" s="27">
+        <v>3.3495872305050689</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8026,7 +8130,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -8039,22 +8143,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>27</v>
-      </c>
-      <c r="D1" t="s">
-        <v>28</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8070,10 +8174,7 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2" s="31" t="e">
-        <f t="shared" ref="E2:E17" si="0">+((D2-D1)/D1)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="E2" s="31"/>
       <c r="F2" s="32">
         <v>-0.03</v>
       </c>
@@ -8092,7 +8193,7 @@
         <v>13741</v>
       </c>
       <c r="E3" s="31">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E2:E17" si="0">+((D3-D2)/D2)</f>
         <v>4.8691139433717466E-2</v>
       </c>
       <c r="F3" s="32">
@@ -9627,7 +9728,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:F107" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:F108" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -10281,9 +10382,34 @@
         <f t="shared" si="4"/>
         <v>-9.5880954207256276E-3</v>
       </c>
-      <c r="F107" s="31">
-        <v>-9.5999999999999992E-3</v>
-      </c>
+      <c r="F107" s="32">
+        <v>-9.5880954207256276E-3</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" s="25">
+        <v>46289</v>
+      </c>
+      <c r="B108" s="26">
+        <v>12762</v>
+      </c>
+      <c r="C108" s="24">
+        <v>3</v>
+      </c>
+      <c r="D108" s="26">
+        <f t="shared" ref="D108" si="5">SUM(B108+C108)</f>
+        <v>12765</v>
+      </c>
+      <c r="E108" s="31">
+        <f t="shared" si="4"/>
+        <v>-1.1384758364312268E-2</v>
+      </c>
+      <c r="F108" s="32">
+        <v>-1.1384758364312268E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="E110" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2989,7 +2989,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5436,6 +5436,26 @@
         <v>0.33</v>
       </c>
     </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="21">
+        <v>46293</v>
+      </c>
+      <c r="B127" s="7">
+        <v>0</v>
+      </c>
+      <c r="C127" s="24"/>
+      <c r="D127" s="17">
+        <v>0</v>
+      </c>
+      <c r="E127" s="24"/>
+      <c r="F127" s="17">
+        <v>0</v>
+      </c>
+      <c r="G127" s="24"/>
+      <c r="H127" s="17">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5444,7 +5464,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5473,14 +5493,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B2" s="24">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C2" s="30">
         <f>+(B2-B3)/B3</f>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5491,14 +5511,14 @@
     </row>
     <row r="3" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="25">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B3" s="24">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C3" s="30">
-        <f t="shared" ref="C2:C72" si="0">+(B3-B4)/B4</f>
-        <v>5.2320875570372835E-2</v>
+        <f>+(B3-B4)/B4</f>
+        <v>0.55858664283872839</v>
       </c>
       <c r="D3" s="24" t="s">
         <v>9</v>
@@ -5507,1430 +5527,1444 @@
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="17.25" customHeight="1">
+    <row r="4" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="25">
+        <v>46289</v>
+      </c>
+      <c r="B4" s="24">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C4" s="30">
+        <f t="shared" ref="C4:C73" si="0">+(B4-B5)/B5</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
+        <v>85928.931135131905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" customHeight="1">
+      <c r="A5" s="25">
         <v>46288</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B5" s="24">
         <v>174433.37119511</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C5" s="30">
         <f t="shared" si="0"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="D4" s="24" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6">
-        <v>85928.931135131905</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="25">
+      <c r="D5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="25">
         <v>46287</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B6" s="24">
         <v>146837.85895197999</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C6" s="30">
         <f t="shared" si="0"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="6">
-        <v>22227.4775024345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="25">
+      <c r="D6" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="6">
+        <v>24565.759999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="25">
         <v>46286</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B7" s="24">
         <v>137505.15153979001</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C7" s="30">
         <f t="shared" si="0"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6">
-        <v>24565.759999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="25">
+      <c r="D7" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="25">
         <v>46283</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B8" s="24">
         <v>109462.8853239</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C8" s="30">
         <f t="shared" si="0"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="25">
+      <c r="D8" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="34">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="25">
         <v>46282</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B9" s="24">
         <v>82707.40661228</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C9" s="30">
         <f t="shared" si="0"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="34">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="25">
+      <c r="D9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25">
         <v>46281</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B10" s="24">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C10" s="30">
         <f t="shared" si="0"/>
         <v>54.85948274687906</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="25">
+      <c r="D10" s="24"/>
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="25">
         <v>46280</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B11" s="24">
         <v>50.214025489999997</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C11" s="30">
         <f t="shared" si="0"/>
         <v>0.37097114686342592</v>
       </c>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="25">
+      <c r="E11" s="35"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="25">
         <v>46276</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B12" s="24">
         <v>36.626609979999998</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C12" s="30">
         <f t="shared" si="0"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="25">
+    <row r="13" spans="1:5">
+      <c r="A13" s="25">
         <v>46275</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B13" s="24">
         <v>113.77143633999999</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C13" s="30">
         <f t="shared" si="0"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="25">
+    <row r="14" spans="1:5">
+      <c r="A14" s="25">
         <v>46274</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B14" s="24">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C14" s="30">
         <f t="shared" si="0"/>
         <v>0.64045278098882874</v>
       </c>
-      <c r="E13" s="37"/>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="25">
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="25">
         <v>46273</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B15" s="24">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C15" s="30">
         <f t="shared" si="0"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="25">
+    <row r="16" spans="1:5">
+      <c r="A16" s="25">
         <v>46272</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B16" s="24">
         <v>20.42491424</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C16" s="30">
         <f t="shared" si="0"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="25">
+    <row r="17" spans="1:5">
+      <c r="A17" s="25">
         <v>46269</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B17" s="24">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C17" s="30">
         <f t="shared" si="0"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="25">
+    <row r="18" spans="1:5">
+      <c r="A18" s="25">
         <v>46268</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B18" s="24">
         <v>287.33741307000003</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C18" s="30">
         <f t="shared" si="0"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="25">
+    <row r="19" spans="1:5">
+      <c r="A19" s="25">
         <v>46267</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B19" s="24">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C19" s="30">
         <f t="shared" si="0"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="25">
+    <row r="20" spans="1:5">
+      <c r="A20" s="25">
         <v>46266</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B20" s="24">
         <v>15.709117340000001</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C20" s="30">
         <f t="shared" si="0"/>
         <v>-0.99727371031195</v>
       </c>
-      <c r="E19" s="7"/>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="25">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="25">
         <v>46265</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B21" s="24">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C21" s="30">
         <f t="shared" si="0"/>
         <v>1028.4103166122507</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="25">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="25">
         <v>46262</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B22" s="24">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C22" s="30">
         <f t="shared" si="0"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="25">
+    <row r="23" spans="1:5">
+      <c r="A23" s="25">
         <v>46261</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B23" s="24">
         <v>451.44302815999998</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="30">
         <f t="shared" si="0"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="25">
+    <row r="24" spans="1:5">
+      <c r="A24" s="25">
         <v>46260</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B24" s="24">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C24" s="30">
         <f t="shared" si="0"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="25">
+    <row r="25" spans="1:5">
+      <c r="A25" s="25">
         <v>46259</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B25" s="24">
         <v>334.62882287999997</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C25" s="30">
         <f t="shared" si="0"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="25">
+    <row r="26" spans="1:5">
+      <c r="A26" s="25">
         <v>46256</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B26" s="24">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="30">
         <f t="shared" si="0"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="25">
+    <row r="27" spans="1:5">
+      <c r="A27" s="25">
         <v>46255</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B27" s="24">
         <v>126.21011864</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C27" s="30">
         <f t="shared" si="0"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="25">
+    <row r="28" spans="1:5">
+      <c r="A28" s="25">
         <v>46254</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B28" s="24">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C28" s="30">
         <f t="shared" si="0"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="25">
+    <row r="29" spans="1:5">
+      <c r="A29" s="25">
         <v>46253</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B29" s="24">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C29" s="30">
         <f t="shared" si="0"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="25">
+    <row r="30" spans="1:5">
+      <c r="A30" s="25">
         <v>46252</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B30" s="24">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C30" s="30">
         <f t="shared" si="0"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="25">
+    <row r="31" spans="1:5">
+      <c r="A31" s="25">
         <v>46251</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B31" s="24">
         <v>12.53018157</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C31" s="30">
         <f t="shared" si="0"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="25">
+    <row r="32" spans="1:5">
+      <c r="A32" s="25">
         <v>46248</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B32" s="24">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C32" s="30">
         <f t="shared" si="0"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="25">
+    <row r="33" spans="1:3">
+      <c r="A33" s="25">
         <v>46247</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B33" s="24">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C33" s="30">
         <f t="shared" si="0"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="25">
+    <row r="34" spans="1:3">
+      <c r="A34" s="25">
         <v>46246</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B34" s="24">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C34" s="30">
         <f t="shared" si="0"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="25">
+    <row r="35" spans="1:3">
+      <c r="A35" s="25">
         <v>46245</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B35" s="24">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C35" s="30">
         <f t="shared" si="0"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="25">
+    <row r="36" spans="1:3">
+      <c r="A36" s="25">
         <v>46244</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B36" s="24">
         <v>4.14256738</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C36" s="30">
         <f t="shared" si="0"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="25">
+    <row r="37" spans="1:3">
+      <c r="A37" s="25">
         <v>46241</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B37" s="24">
         <v>15624.152913600001</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C37" s="30">
         <f t="shared" si="0"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="25">
+    <row r="38" spans="1:3">
+      <c r="A38" s="25">
         <v>46240</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B38" s="24">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C38" s="30">
         <f t="shared" si="0"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="25">
+    <row r="39" spans="1:3">
+      <c r="A39" s="25">
         <v>46239</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B39" s="24">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C39" s="30">
         <f t="shared" si="0"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="25">
+    <row r="40" spans="1:3">
+      <c r="A40" s="25">
         <v>46238</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B40" s="24">
         <v>499.27660521000001</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C40" s="30">
         <f t="shared" si="0"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="25">
+    <row r="41" spans="1:3">
+      <c r="A41" s="25">
         <v>46237</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B41" s="24">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C41" s="30">
         <f t="shared" si="0"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="25">
+    <row r="42" spans="1:3">
+      <c r="A42" s="25">
         <v>46234</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B42" s="24">
         <v>19481.20894855</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C42" s="30">
         <f t="shared" si="0"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="25">
+    <row r="43" spans="1:3">
+      <c r="A43" s="25">
         <v>46233</v>
       </c>
-      <c r="B42">
+      <c r="B43">
         <v>466.33578662999997</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C43" s="30">
         <f t="shared" si="0"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="25">
+    <row r="44" spans="1:3">
+      <c r="A44" s="25">
         <v>46232</v>
       </c>
-      <c r="B43" s="24">
+      <c r="B44" s="24">
         <v>101.55832515</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C44" s="30">
         <f t="shared" si="0"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="25">
+    <row r="45" spans="1:3">
+      <c r="A45" s="25">
         <v>46231</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B45" s="24">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C45" s="30">
         <f t="shared" si="0"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="25">
+    <row r="46" spans="1:3">
+      <c r="A46" s="25">
         <v>46108</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B46" s="24">
         <v>223.50959897000001</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C46" s="30">
         <f t="shared" si="0"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="25">
+    <row r="47" spans="1:3">
+      <c r="A47" s="25">
         <v>46226</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B47" s="24">
         <v>28677.412251940001</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C47" s="30">
         <f t="shared" si="0"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="25">
+    <row r="48" spans="1:3">
+      <c r="A48" s="25">
         <v>46225</v>
       </c>
-      <c r="B47" s="24">
+      <c r="B48" s="24">
         <v>858.25054019000004</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C48" s="30">
         <f t="shared" si="0"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="25">
+    <row r="49" spans="1:3">
+      <c r="A49" s="25">
         <v>46224</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B49" s="24">
         <v>20.063323860000001</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C49" s="30">
         <f t="shared" si="0"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="25">
+    <row r="50" spans="1:3">
+      <c r="A50" s="25">
         <v>46220</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B50" s="24">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C50" s="30">
         <f t="shared" si="0"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="25">
+    <row r="51" spans="1:3">
+      <c r="A51" s="25">
         <v>46219</v>
       </c>
-      <c r="B50" s="24">
+      <c r="B51" s="24">
         <v>16578.913830919999</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C51" s="30">
         <f t="shared" si="0"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="25">
+    <row r="52" spans="1:3">
+      <c r="A52" s="25">
         <v>46218</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B52" s="24">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C52" s="30">
         <f t="shared" si="0"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="25">
+    <row r="53" spans="1:3">
+      <c r="A53" s="25">
         <v>46217</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B53" s="24">
         <v>38833.478919130001</v>
       </c>
-      <c r="C52" s="30">
+      <c r="C53" s="30">
         <f t="shared" si="0"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="25">
+    <row r="54" spans="1:3">
+      <c r="A54" s="25">
         <v>46216</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B54" s="24">
         <v>52315.97026473</v>
       </c>
-      <c r="C53" s="30">
+      <c r="C54" s="30">
         <f t="shared" si="0"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="25">
+    <row r="55" spans="1:3">
+      <c r="A55" s="25">
         <v>46213</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B55" s="24">
         <v>64626.363040830001</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C55" s="30">
         <f t="shared" si="0"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="25">
+    <row r="56" spans="1:3">
+      <c r="A56" s="25">
         <v>46212</v>
       </c>
-      <c r="B55" s="24">
+      <c r="B56" s="24">
         <v>28200.29395617</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C56" s="30">
         <f t="shared" si="0"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="25">
+    <row r="57" spans="1:3">
+      <c r="A57" s="25">
         <v>46211</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B57" s="24">
         <v>7705.0577555</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C57" s="30">
         <f t="shared" si="0"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="25">
+    <row r="58" spans="1:3">
+      <c r="A58" s="25">
         <v>46210</v>
       </c>
-      <c r="B57" s="24">
+      <c r="B58" s="24">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C57" s="30">
+      <c r="C58" s="30">
         <f t="shared" si="0"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="25">
+    <row r="59" spans="1:3">
+      <c r="A59" s="25">
         <v>46209</v>
       </c>
-      <c r="B58" s="24">
+      <c r="B59" s="24">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C59" s="30">
         <f t="shared" si="0"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="25">
+    <row r="60" spans="1:3">
+      <c r="A60" s="25">
         <v>46206</v>
       </c>
-      <c r="B59" s="24">
+      <c r="B60" s="24">
         <v>17125.195337590001</v>
       </c>
-      <c r="C59" s="30">
+      <c r="C60" s="30">
         <f t="shared" si="0"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="25">
+    <row r="61" spans="1:3">
+      <c r="A61" s="25">
         <v>46205</v>
       </c>
-      <c r="B60" s="24">
+      <c r="B61" s="24">
         <v>28151.370695969999</v>
       </c>
-      <c r="C60" s="30">
+      <c r="C61" s="30">
         <f t="shared" si="0"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="25">
+    <row r="62" spans="1:3">
+      <c r="A62" s="25">
         <v>46204</v>
       </c>
-      <c r="B61" s="24">
+      <c r="B62" s="24">
         <v>989.47411254999997</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C62" s="30">
         <f t="shared" si="0"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="25">
+    <row r="63" spans="1:3">
+      <c r="A63" s="25">
         <v>46203</v>
       </c>
-      <c r="B62" s="24">
+      <c r="B63" s="24">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C62" s="30">
+      <c r="C63" s="30">
         <f t="shared" si="0"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="25">
+    <row r="64" spans="1:3">
+      <c r="A64" s="25">
         <v>46198</v>
       </c>
-      <c r="B63" s="24">
+      <c r="B64" s="24">
         <v>31666.069450710002</v>
       </c>
-      <c r="C63" s="30">
+      <c r="C64" s="30">
         <f t="shared" si="0"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="25">
+    <row r="65" spans="1:3">
+      <c r="A65" s="25">
         <v>46196</v>
       </c>
-      <c r="B64" s="24">
+      <c r="B65" s="24">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C64" s="30">
+      <c r="C65" s="30">
         <f t="shared" si="0"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="25">
+    <row r="66" spans="1:3">
+      <c r="A66" s="25">
         <v>46195</v>
       </c>
-      <c r="B65" s="24">
+      <c r="B66" s="24">
         <v>1716.30170335</v>
       </c>
-      <c r="C65" s="30">
+      <c r="C66" s="30">
         <f t="shared" si="0"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="25">
+    <row r="67" spans="1:3">
+      <c r="A67" s="25">
         <v>46192</v>
       </c>
-      <c r="B66" s="24">
+      <c r="B67" s="24">
         <v>16.43890412</v>
       </c>
-      <c r="C66" s="30">
+      <c r="C67" s="30">
         <f t="shared" si="0"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="25">
+    <row r="68" spans="1:3">
+      <c r="A68" s="25">
         <v>46191</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B68" s="24">
         <v>269.81083503999997</v>
       </c>
-      <c r="C67" s="30">
+      <c r="C68" s="30">
         <f t="shared" si="0"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="25">
+    <row r="69" spans="1:3">
+      <c r="A69" s="25">
         <v>46190</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B69" s="24">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C69" s="30">
         <f t="shared" si="0"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="25">
+    <row r="70" spans="1:3">
+      <c r="A70" s="25">
         <v>46189</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B70" s="24">
         <v>1206.260808</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C70" s="30">
         <f t="shared" si="0"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="25">
+    <row r="71" spans="1:3">
+      <c r="A71" s="25">
         <v>46188</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B71" s="24">
         <v>8.42</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C71" s="30">
         <f t="shared" si="0"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="25">
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
         <v>46185</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="24">
         <v>19.156653639999998</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="30">
         <f t="shared" si="0"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
         <v>46184</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="24">
         <v>12.711483429999999</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="30">
         <f t="shared" si="0"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
-        <v>46183</v>
-      </c>
-      <c r="B73" s="24">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C73" s="30">
-        <f t="shared" ref="C73:C114" si="1">+(B73-B74)/B74</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="74" spans="1:3">
       <c r="A74" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B74" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C74" s="30">
+        <f t="shared" ref="C74:C115" si="1">+(B74-B75)/B75</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="25">
         <v>46182</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>46178</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>46177</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>46176</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>46175</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>46174</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>46171</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>45074</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>46169</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46168</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46167</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46164</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46163</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46162</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="25">
         <v>46161</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="25">
+    <row r="90" spans="1:3">
+      <c r="A90" s="25">
         <v>46157</v>
       </c>
-      <c r="B89" s="24">
+      <c r="B90" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="25">
+    <row r="91" spans="1:3">
+      <c r="A91" s="25">
         <v>46156</v>
       </c>
-      <c r="B90" s="24">
+      <c r="B91" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="25">
+    <row r="92" spans="1:3">
+      <c r="A92" s="25">
         <v>46155</v>
       </c>
-      <c r="B91" s="24">
+      <c r="B92" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="25">
+    <row r="93" spans="1:3">
+      <c r="A93" s="25">
         <v>46154</v>
       </c>
-      <c r="B92" s="24">
+      <c r="B93" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="25">
+    <row r="94" spans="1:3">
+      <c r="A94" s="25">
         <v>46153</v>
       </c>
-      <c r="B93" s="24">
+      <c r="B94" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="25">
+    <row r="95" spans="1:3">
+      <c r="A95" s="25">
         <v>46150</v>
       </c>
-      <c r="B94" s="24">
+      <c r="B95" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="23">
+    <row r="96" spans="1:3">
+      <c r="A96" s="23">
         <v>46149</v>
       </c>
-      <c r="B95" s="22">
+      <c r="B96" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="18">
+    <row r="97" spans="1:4">
+      <c r="A97" s="18">
         <v>46148</v>
       </c>
-      <c r="B96" s="16">
+      <c r="B97" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="18">
+    <row r="98" spans="1:4">
+      <c r="A98" s="18">
         <v>46147</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="18">
+    <row r="99" spans="1:4">
+      <c r="A99" s="18">
         <v>46146</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="19">
+    <row r="100" spans="1:4">
+      <c r="A100" s="19">
         <v>46142</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46141</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46140</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46139</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46136</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46135</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B105" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
-      <c r="D104" s="37"/>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+      <c r="D105" s="37"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46134</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B106" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46133</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46132</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B108" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46129</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B109" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
+    <row r="110" spans="1:4">
+      <c r="A110" s="19">
         <v>46128</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B110" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C110" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
-      <c r="D109" s="36"/>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="19">
+      <c r="D110" s="36"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="19">
         <v>46127</v>
       </c>
-      <c r="B110" s="39">
+      <c r="B111" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C110" s="30">
+      <c r="C111" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="19">
+    <row r="112" spans="1:4">
+      <c r="A112" s="19">
         <v>46126</v>
       </c>
-      <c r="B111" s="39">
+      <c r="B112" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C111" s="30">
+      <c r="C112" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
-      <c r="D111" s="36"/>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="19">
+      <c r="D112" s="36"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="19">
         <v>46125</v>
       </c>
-      <c r="B112" s="16">
+      <c r="B113" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C112" s="30">
+      <c r="C113" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="19">
+    <row r="114" spans="1:3">
+      <c r="A114" s="19">
         <v>46122</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B114" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C113" s="30">
+      <c r="C114" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="19">
+    <row r="115" spans="1:3">
+      <c r="A115" s="19">
         <v>46121</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B115" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C114" s="30">
+      <c r="C115" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="19">
-        <v>46120</v>
-      </c>
-      <c r="B115" s="16">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C115" s="30">
-        <f>+(B115-B116)/B116</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="116" spans="1:3">
       <c r="A116" s="19">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B116" s="16">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C116" s="30">
+        <f>+(B116-B117)/B117</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="19">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B117" s="16">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="19">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B118" s="16">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="19">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B119" s="16">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="19">
+        <v>46112</v>
+      </c>
+      <c r="B120" s="16">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="19">
         <v>46111</v>
       </c>
-      <c r="B120" s="16">
+      <c r="B121" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8193,7 +8227,7 @@
         <v>13741</v>
       </c>
       <c r="E3" s="31">
-        <f t="shared" ref="E2:E17" si="0">+((D3-D2)/D2)</f>
+        <f t="shared" ref="E3:E17" si="0">+((D3-D2)/D2)</f>
         <v>4.8691139433717466E-2</v>
       </c>
       <c r="F3" s="32">
@@ -9728,7 +9762,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:F108" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E109" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -10406,6 +10440,28 @@
       </c>
       <c r="F108" s="32">
         <v>-1.1384758364312268E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B109" s="26">
+        <v>12724</v>
+      </c>
+      <c r="C109" s="24">
+        <v>3</v>
+      </c>
+      <c r="D109" s="26">
+        <f t="shared" ref="D109" si="6">SUM(B109+C109)</f>
+        <v>12727</v>
+      </c>
+      <c r="E109" s="31">
+        <f t="shared" si="4"/>
+        <v>-2.9768899334116725E-3</v>
+      </c>
+      <c r="F109" s="32">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="110" spans="1:6">

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2989,7 +2989,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,7 +2997,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
@@ -5456,6 +5456,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="21">
+        <v>46294</v>
+      </c>
+      <c r="B128" s="17">
+        <v>48909.906707000002</v>
+      </c>
+      <c r="C128" s="20"/>
+      <c r="D128" s="17">
+        <v>5</v>
+      </c>
+      <c r="E128" s="20"/>
+      <c r="F128" s="17">
+        <v>20</v>
+      </c>
+      <c r="G128" s="20"/>
+      <c r="H128" s="17">
+        <v>8.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5464,7 +5484,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5493,14 +5513,14 @@
     </row>
     <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="25">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B2" s="24">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C2" s="30">
         <f>+(B2-B3)/B3</f>
-        <v>-0.49898704513189668</v>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="D2" s="24" t="s">
         <v>8</v>
@@ -5511,14 +5531,14 @@
     </row>
     <row r="3" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="25">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B3" s="24">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C3" s="30">
         <f>+(B3-B4)/B4</f>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="D3" s="24" t="s">
         <v>9</v>
@@ -5529,14 +5549,14 @@
     </row>
     <row r="4" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="25">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B4" s="24">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C4" s="30">
-        <f t="shared" ref="C4:C73" si="0">+(B4-B5)/B5</f>
-        <v>5.2320875570372835E-2</v>
+        <f>+(B4-B5)/B5</f>
+        <v>0.55858664283872839</v>
       </c>
       <c r="D4" s="24" t="s">
         <v>10</v>
@@ -5547,1424 +5567,1436 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="25">
+        <v>46289</v>
+      </c>
+      <c r="B5" s="24">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C5" s="30">
+        <f t="shared" ref="C5:C74" si="0">+(B5-B6)/B6</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="25">
         <v>46288</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B6" s="24">
         <v>174433.37119511</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C6" s="30">
         <f t="shared" si="0"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="6">
-        <v>22227.4775024345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="25">
+      <c r="D6" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="6">
+        <v>24565.759999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="25">
         <v>46287</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B7" s="24">
         <v>146837.85895197999</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C7" s="30">
         <f t="shared" si="0"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6">
-        <v>24565.759999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="25">
+      <c r="D7" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="25">
         <v>46286</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B8" s="24">
         <v>137505.15153979001</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C8" s="30">
         <f t="shared" si="0"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="25">
+      <c r="D8" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="34">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="25">
         <v>46283</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B9" s="24">
         <v>109462.8853239</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C9" s="30">
         <f t="shared" si="0"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="34">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="25">
+      <c r="D9" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="25">
         <v>46282</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B10" s="24">
         <v>82707.40661228</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C10" s="30">
         <f t="shared" si="0"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="25">
+      <c r="D10" s="24"/>
+      <c r="E10" s="35"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="25">
         <v>46281</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B11" s="24">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C11" s="30">
         <f t="shared" si="0"/>
         <v>54.85948274687906</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="25">
+      <c r="E11" s="35"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="25">
         <v>46280</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B12" s="24">
         <v>50.214025489999997</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C12" s="30">
         <f t="shared" si="0"/>
         <v>0.37097114686342592</v>
       </c>
-      <c r="E11" s="35"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="25">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="25">
         <v>46276</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B13" s="24">
         <v>36.626609979999998</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C13" s="30">
         <f t="shared" si="0"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="25">
+    <row r="14" spans="1:5">
+      <c r="A14" s="25">
         <v>46275</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B14" s="24">
         <v>113.77143633999999</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C14" s="30">
         <f t="shared" si="0"/>
         <v>18.560573043109468</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="25">
+      <c r="E14" s="37"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="25">
         <v>46274</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B15" s="24">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C15" s="30">
         <f t="shared" si="0"/>
         <v>0.64045278098882874</v>
       </c>
-      <c r="E14" s="37"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="25">
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="25">
         <v>46273</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B16" s="24">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C16" s="30">
         <f t="shared" si="0"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="25">
+    <row r="17" spans="1:5">
+      <c r="A17" s="25">
         <v>46272</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B17" s="24">
         <v>20.42491424</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C17" s="30">
         <f t="shared" si="0"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="25">
+    <row r="18" spans="1:5">
+      <c r="A18" s="25">
         <v>46269</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B18" s="24">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C18" s="30">
         <f t="shared" si="0"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="25">
+    <row r="19" spans="1:5">
+      <c r="A19" s="25">
         <v>46268</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B19" s="24">
         <v>287.33741307000003</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C19" s="30">
         <f t="shared" si="0"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="25">
+    <row r="20" spans="1:5">
+      <c r="A20" s="25">
         <v>46267</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B20" s="24">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C20" s="30">
         <f t="shared" si="0"/>
         <v>-0.77463732472189939</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="25">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="25">
         <v>46266</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B21" s="24">
         <v>15.709117340000001</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C21" s="30">
         <f t="shared" si="0"/>
         <v>-0.99727371031195</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="25">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="25">
         <v>46265</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B22" s="24">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C22" s="30">
         <f t="shared" si="0"/>
         <v>1028.4103166122507</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="25">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="25">
         <v>46262</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B23" s="24">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="30">
         <f t="shared" si="0"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="25">
+    <row r="24" spans="1:5">
+      <c r="A24" s="25">
         <v>46261</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B24" s="24">
         <v>451.44302815999998</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C24" s="30">
         <f t="shared" si="0"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="25">
+    <row r="25" spans="1:5">
+      <c r="A25" s="25">
         <v>46260</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B25" s="24">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C25" s="30">
         <f t="shared" si="0"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="25">
+    <row r="26" spans="1:5">
+      <c r="A26" s="25">
         <v>46259</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B26" s="24">
         <v>334.62882287999997</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="30">
         <f t="shared" si="0"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="25">
+    <row r="27" spans="1:5">
+      <c r="A27" s="25">
         <v>46256</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B27" s="24">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C27" s="30">
         <f t="shared" si="0"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="25">
+    <row r="28" spans="1:5">
+      <c r="A28" s="25">
         <v>46255</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B28" s="24">
         <v>126.21011864</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C28" s="30">
         <f t="shared" si="0"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="25">
+    <row r="29" spans="1:5">
+      <c r="A29" s="25">
         <v>46254</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B29" s="24">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C29" s="30">
         <f t="shared" si="0"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="25">
+    <row r="30" spans="1:5">
+      <c r="A30" s="25">
         <v>46253</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B30" s="24">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C30" s="30">
         <f t="shared" si="0"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="25">
+    <row r="31" spans="1:5">
+      <c r="A31" s="25">
         <v>46252</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B31" s="24">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C31" s="30">
         <f t="shared" si="0"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="25">
+    <row r="32" spans="1:5">
+      <c r="A32" s="25">
         <v>46251</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B32" s="24">
         <v>12.53018157</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C32" s="30">
         <f t="shared" si="0"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="25">
+    <row r="33" spans="1:3">
+      <c r="A33" s="25">
         <v>46248</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B33" s="24">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C33" s="30">
         <f t="shared" si="0"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="25">
+    <row r="34" spans="1:3">
+      <c r="A34" s="25">
         <v>46247</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B34" s="24">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C34" s="30">
         <f t="shared" si="0"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="25">
+    <row r="35" spans="1:3">
+      <c r="A35" s="25">
         <v>46246</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B35" s="24">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C35" s="30">
         <f t="shared" si="0"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="25">
+    <row r="36" spans="1:3">
+      <c r="A36" s="25">
         <v>46245</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B36" s="24">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C36" s="30">
         <f t="shared" si="0"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="25">
+    <row r="37" spans="1:3">
+      <c r="A37" s="25">
         <v>46244</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B37" s="24">
         <v>4.14256738</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C37" s="30">
         <f t="shared" si="0"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="25">
+    <row r="38" spans="1:3">
+      <c r="A38" s="25">
         <v>46241</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B38" s="24">
         <v>15624.152913600001</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C38" s="30">
         <f t="shared" si="0"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="25">
+    <row r="39" spans="1:3">
+      <c r="A39" s="25">
         <v>46240</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B39" s="24">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C39" s="30">
         <f t="shared" si="0"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="25">
+    <row r="40" spans="1:3">
+      <c r="A40" s="25">
         <v>46239</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B40" s="24">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C40" s="30">
         <f t="shared" si="0"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="25">
+    <row r="41" spans="1:3">
+      <c r="A41" s="25">
         <v>46238</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B41" s="24">
         <v>499.27660521000001</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C41" s="30">
         <f t="shared" si="0"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="25">
+    <row r="42" spans="1:3">
+      <c r="A42" s="25">
         <v>46237</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B42" s="24">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C42" s="30">
         <f t="shared" si="0"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="25">
+    <row r="43" spans="1:3">
+      <c r="A43" s="25">
         <v>46234</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B43" s="24">
         <v>19481.20894855</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C43" s="30">
         <f t="shared" si="0"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="25">
+    <row r="44" spans="1:3">
+      <c r="A44" s="25">
         <v>46233</v>
       </c>
-      <c r="B43">
+      <c r="B44">
         <v>466.33578662999997</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C44" s="30">
         <f t="shared" si="0"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="25">
+    <row r="45" spans="1:3">
+      <c r="A45" s="25">
         <v>46232</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B45" s="24">
         <v>101.55832515</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C45" s="30">
         <f t="shared" si="0"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="25">
+    <row r="46" spans="1:3">
+      <c r="A46" s="25">
         <v>46231</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B46" s="24">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C46" s="30">
         <f t="shared" si="0"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="25">
+    <row r="47" spans="1:3">
+      <c r="A47" s="25">
         <v>46108</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B47" s="24">
         <v>223.50959897000001</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C47" s="30">
         <f t="shared" si="0"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="25">
+    <row r="48" spans="1:3">
+      <c r="A48" s="25">
         <v>46226</v>
       </c>
-      <c r="B47" s="24">
+      <c r="B48" s="24">
         <v>28677.412251940001</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C48" s="30">
         <f t="shared" si="0"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="25">
+    <row r="49" spans="1:3">
+      <c r="A49" s="25">
         <v>46225</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B49" s="24">
         <v>858.25054019000004</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C49" s="30">
         <f t="shared" si="0"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="25">
+    <row r="50" spans="1:3">
+      <c r="A50" s="25">
         <v>46224</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B50" s="24">
         <v>20.063323860000001</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C50" s="30">
         <f t="shared" si="0"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="25">
+    <row r="51" spans="1:3">
+      <c r="A51" s="25">
         <v>46220</v>
       </c>
-      <c r="B50" s="24">
+      <c r="B51" s="24">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C51" s="30">
         <f t="shared" si="0"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="25">
+    <row r="52" spans="1:3">
+      <c r="A52" s="25">
         <v>46219</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B52" s="24">
         <v>16578.913830919999</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C52" s="30">
         <f t="shared" si="0"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="25">
+    <row r="53" spans="1:3">
+      <c r="A53" s="25">
         <v>46218</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B53" s="24">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C52" s="30">
+      <c r="C53" s="30">
         <f t="shared" si="0"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="25">
+    <row r="54" spans="1:3">
+      <c r="A54" s="25">
         <v>46217</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B54" s="24">
         <v>38833.478919130001</v>
       </c>
-      <c r="C53" s="30">
+      <c r="C54" s="30">
         <f t="shared" si="0"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="25">
+    <row r="55" spans="1:3">
+      <c r="A55" s="25">
         <v>46216</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B55" s="24">
         <v>52315.97026473</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C55" s="30">
         <f t="shared" si="0"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="25">
+    <row r="56" spans="1:3">
+      <c r="A56" s="25">
         <v>46213</v>
       </c>
-      <c r="B55" s="24">
+      <c r="B56" s="24">
         <v>64626.363040830001</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C56" s="30">
         <f t="shared" si="0"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="25">
+    <row r="57" spans="1:3">
+      <c r="A57" s="25">
         <v>46212</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B57" s="24">
         <v>28200.29395617</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C57" s="30">
         <f t="shared" si="0"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="25">
+    <row r="58" spans="1:3">
+      <c r="A58" s="25">
         <v>46211</v>
       </c>
-      <c r="B57" s="24">
+      <c r="B58" s="24">
         <v>7705.0577555</v>
       </c>
-      <c r="C57" s="30">
+      <c r="C58" s="30">
         <f t="shared" si="0"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="25">
+    <row r="59" spans="1:3">
+      <c r="A59" s="25">
         <v>46210</v>
       </c>
-      <c r="B58" s="24">
+      <c r="B59" s="24">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C59" s="30">
         <f t="shared" si="0"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="25">
+    <row r="60" spans="1:3">
+      <c r="A60" s="25">
         <v>46209</v>
       </c>
-      <c r="B59" s="24">
+      <c r="B60" s="24">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C59" s="30">
+      <c r="C60" s="30">
         <f t="shared" si="0"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="25">
+    <row r="61" spans="1:3">
+      <c r="A61" s="25">
         <v>46206</v>
       </c>
-      <c r="B60" s="24">
+      <c r="B61" s="24">
         <v>17125.195337590001</v>
       </c>
-      <c r="C60" s="30">
+      <c r="C61" s="30">
         <f t="shared" si="0"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="25">
+    <row r="62" spans="1:3">
+      <c r="A62" s="25">
         <v>46205</v>
       </c>
-      <c r="B61" s="24">
+      <c r="B62" s="24">
         <v>28151.370695969999</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C62" s="30">
         <f t="shared" si="0"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="25">
+    <row r="63" spans="1:3">
+      <c r="A63" s="25">
         <v>46204</v>
       </c>
-      <c r="B62" s="24">
+      <c r="B63" s="24">
         <v>989.47411254999997</v>
       </c>
-      <c r="C62" s="30">
+      <c r="C63" s="30">
         <f t="shared" si="0"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="25">
+    <row r="64" spans="1:3">
+      <c r="A64" s="25">
         <v>46203</v>
       </c>
-      <c r="B63" s="24">
+      <c r="B64" s="24">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C63" s="30">
+      <c r="C64" s="30">
         <f t="shared" si="0"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="25">
+    <row r="65" spans="1:3">
+      <c r="A65" s="25">
         <v>46198</v>
       </c>
-      <c r="B64" s="24">
+      <c r="B65" s="24">
         <v>31666.069450710002</v>
       </c>
-      <c r="C64" s="30">
+      <c r="C65" s="30">
         <f t="shared" si="0"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="25">
+    <row r="66" spans="1:3">
+      <c r="A66" s="25">
         <v>46196</v>
       </c>
-      <c r="B65" s="24">
+      <c r="B66" s="24">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C65" s="30">
+      <c r="C66" s="30">
         <f t="shared" si="0"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="25">
+    <row r="67" spans="1:3">
+      <c r="A67" s="25">
         <v>46195</v>
       </c>
-      <c r="B66" s="24">
+      <c r="B67" s="24">
         <v>1716.30170335</v>
       </c>
-      <c r="C66" s="30">
+      <c r="C67" s="30">
         <f t="shared" si="0"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="25">
+    <row r="68" spans="1:3">
+      <c r="A68" s="25">
         <v>46192</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B68" s="24">
         <v>16.43890412</v>
       </c>
-      <c r="C67" s="30">
+      <c r="C68" s="30">
         <f t="shared" si="0"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="25">
+    <row r="69" spans="1:3">
+      <c r="A69" s="25">
         <v>46191</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B69" s="24">
         <v>269.81083503999997</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C69" s="30">
         <f t="shared" si="0"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="25">
+    <row r="70" spans="1:3">
+      <c r="A70" s="25">
         <v>46190</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B70" s="24">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C70" s="30">
         <f t="shared" si="0"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="25">
+    <row r="71" spans="1:3">
+      <c r="A71" s="25">
         <v>46189</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B71" s="24">
         <v>1206.260808</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C71" s="30">
         <f t="shared" si="0"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="25">
+    <row r="72" spans="1:3">
+      <c r="A72" s="25">
         <v>46188</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="24">
         <v>8.42</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="30">
         <f t="shared" si="0"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
+    <row r="73" spans="1:3">
+      <c r="A73" s="25">
         <v>46185</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="24">
         <v>19.156653639999998</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="30">
         <f t="shared" si="0"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
+    <row r="74" spans="1:3">
+      <c r="A74" s="25">
         <v>46184</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="24">
         <v>12.711483429999999</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="30">
         <f t="shared" si="0"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
-        <v>46183</v>
-      </c>
-      <c r="B74" s="24">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C74" s="30">
-        <f t="shared" ref="C74:C115" si="1">+(B74-B75)/B75</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="75" spans="1:3">
       <c r="A75" s="25">
+        <v>46183</v>
+      </c>
+      <c r="B75" s="24">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C75" s="30">
+        <f t="shared" ref="C75:C116" si="1">+(B75-B76)/B76</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="25">
         <v>46182</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="24">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C75" s="30">
+      <c r="C76" s="30">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="25">
         <v>46178</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="24">
         <v>58292.928576159997</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="30">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="25">
         <v>46177</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="24">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="30">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="25">
         <v>46176</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="24">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="30">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="25">
         <v>46175</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="24">
         <v>29863.561946620001</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="30">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="25">
         <v>46174</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="24">
         <v>55.287064620000002</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="30">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="25">
         <v>46171</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="24">
         <v>33469.1560455</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="30">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="25">
         <v>45074</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="24">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="30">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="25">
         <v>46169</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="24">
         <v>21.673895040000001</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="30">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="25">
         <v>46168</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="24">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="30">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="25">
         <v>46167</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="24">
         <v>12500.80501835</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="30">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="25">
         <v>46164</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="24">
         <v>58837.242479</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="30">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="25">
         <v>46163</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="24">
         <v>55.256117230000001</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="30">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="25">
         <v>46162</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="24">
         <v>20356.468143580001</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="30">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="25">
+    <row r="90" spans="1:3">
+      <c r="A90" s="25">
         <v>46161</v>
       </c>
-      <c r="B89" s="24">
+      <c r="B90" s="24">
         <v>72301.933723569993</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="30">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="25">
+    <row r="91" spans="1:3">
+      <c r="A91" s="25">
         <v>46157</v>
       </c>
-      <c r="B90" s="24">
+      <c r="B91" s="24">
         <v>74209.813271849998</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="30">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="25">
+    <row r="92" spans="1:3">
+      <c r="A92" s="25">
         <v>46156</v>
       </c>
-      <c r="B91" s="24">
+      <c r="B92" s="24">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="30">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="25">
+    <row r="93" spans="1:3">
+      <c r="A93" s="25">
         <v>46155</v>
       </c>
-      <c r="B92" s="24">
+      <c r="B93" s="24">
         <v>24.614867159999999</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="30">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="25">
+    <row r="94" spans="1:3">
+      <c r="A94" s="25">
         <v>46154</v>
       </c>
-      <c r="B93" s="24">
+      <c r="B94" s="24">
         <v>673.01725538999995</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="30">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="25">
+    <row r="95" spans="1:3">
+      <c r="A95" s="25">
         <v>46153</v>
       </c>
-      <c r="B94" s="24">
+      <c r="B95" s="24">
         <v>16068.49495319</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="30">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="25">
+    <row r="96" spans="1:3">
+      <c r="A96" s="25">
         <v>46150</v>
       </c>
-      <c r="B95" s="24">
+      <c r="B96" s="24">
         <v>23652.710333340001</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="30">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="23">
+    <row r="97" spans="1:4">
+      <c r="A97" s="23">
         <v>46149</v>
       </c>
-      <c r="B96" s="22">
+      <c r="B97" s="22">
         <v>131.99794839</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="30">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="18">
+    <row r="98" spans="1:4">
+      <c r="A98" s="18">
         <v>46148</v>
       </c>
-      <c r="B97" s="16">
+      <c r="B98" s="16">
         <v>745.52443231999996</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="30">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="18">
+    <row r="99" spans="1:4">
+      <c r="A99" s="18">
         <v>46147</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="16">
         <v>84317.802960360001</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="30">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="18">
+    <row r="100" spans="1:4">
+      <c r="A100" s="18">
         <v>46146</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="16">
         <v>49567.396050169998</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="30">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="19">
+    <row r="101" spans="1:4">
+      <c r="A101" s="19">
         <v>46142</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="16">
         <v>87352.396084139997</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="30">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="19">
         <v>46141</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="16">
         <v>28385.438679769999</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="30">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="19">
         <v>46140</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="16">
         <v>70324.097718699995</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="30">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+    <row r="104" spans="1:4">
+      <c r="A104" s="19">
         <v>46139</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="16">
         <v>40338.944788629997</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="30">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    <row r="105" spans="1:4">
+      <c r="A105" s="19">
         <v>46136</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B105" s="16">
         <v>60973.651931649998</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="30">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+      <c r="D105" s="37"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="19">
         <v>46135</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B106" s="16">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="30">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
-      <c r="D105" s="37"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="19">
         <v>46134</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="16">
         <v>17251.00486529</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="30">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="19">
         <v>46133</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B108" s="16">
         <v>47981.781644150004</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="30">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+    <row r="109" spans="1:4">
+      <c r="A109" s="19">
         <v>46132</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B109" s="16">
         <v>51339.49161813</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="30">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
+    <row r="110" spans="1:4">
+      <c r="A110" s="19">
         <v>46129</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B110" s="16">
         <v>17216.492596060001</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C110" s="30">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="19">
+      <c r="D110" s="36"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="19">
         <v>46128</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B111" s="16">
         <v>18.890111640000001</v>
       </c>
-      <c r="C110" s="30">
+      <c r="C111" s="30">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
-      <c r="D110" s="36"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="19">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="19">
         <v>46127</v>
       </c>
-      <c r="B111" s="39">
+      <c r="B112" s="39">
         <v>15.79809785</v>
       </c>
-      <c r="C111" s="30">
+      <c r="C112" s="30">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="19">
+      <c r="D112" s="36"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="19">
         <v>46126</v>
       </c>
-      <c r="B112" s="39">
+      <c r="B113" s="39">
         <v>16.215898760000002</v>
       </c>
-      <c r="C112" s="30">
+      <c r="C113" s="30">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
-      <c r="D112" s="36"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="19">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="19">
         <v>46125</v>
       </c>
-      <c r="B113" s="16">
+      <c r="B114" s="16">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C113" s="30">
+      <c r="C114" s="30">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="19">
+    <row r="115" spans="1:3">
+      <c r="A115" s="19">
         <v>46122</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B115" s="16">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C114" s="30">
+      <c r="C115" s="30">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="19">
+    <row r="116" spans="1:3">
+      <c r="A116" s="19">
         <v>46121</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B116" s="16">
         <v>41.536584740000002</v>
       </c>
-      <c r="C115" s="30">
+      <c r="C116" s="30">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="19">
-        <v>46120</v>
-      </c>
-      <c r="B116" s="16">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C116" s="30">
-        <f>+(B116-B117)/B117</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="117" spans="1:3">
       <c r="A117" s="19">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B117" s="16">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C117" s="30">
+        <f>+(B117-B118)/B118</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="19">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B118" s="16">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="19">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B119" s="16">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="19">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B120" s="16">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="19">
+        <v>46112</v>
+      </c>
+      <c r="B121" s="16">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="19">
         <v>46111</v>
       </c>
-      <c r="B121" s="16">
+      <c r="B122" s="16">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -9762,7 +9794,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="31">
-        <f t="shared" ref="E76:E109" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E110" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="32">
@@ -10465,7 +10497,25 @@
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="E110" s="31"/>
+      <c r="A110" s="25">
+        <v>46293</v>
+      </c>
+      <c r="B110" s="26">
+        <v>12720</v>
+      </c>
+      <c r="C110" s="24">
+        <v>3</v>
+      </c>
+      <c r="D110" s="26">
+        <v>12723</v>
+      </c>
+      <c r="E110" s="31">
+        <f t="shared" si="4"/>
+        <v>-3.1429244912390981E-4</v>
+      </c>
+      <c r="F110" s="32">
+        <v>-0.3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>DÍA</t>
   </si>
@@ -137,19 +137,21 @@
   <si>
     <t>MONTO F</t>
   </si>
+  <si>
+    <t>SEPTIEMBRE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="15">
+  <numFmts count="14">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="General_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _B_s_-;\-* #,##0.00\ _B_s_-;_-* &quot;-&quot;??\ _B_s_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.00;[Red]0.00"/>
     <numFmt numFmtId="170" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="172" formatCode="#.##000"/>
@@ -1636,7 +1638,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1651,7 +1653,6 @@
     </xf>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2989,7 +2990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2997,10 +2998,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:H129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="26.625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
     <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
@@ -3008,7 +3009,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -3025,7 +3026,7 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="10">
+      <c r="A2" s="9">
         <v>46101</v>
       </c>
       <c r="B2" s="1">
@@ -3042,7 +3043,7 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="10">
+      <c r="A3" s="9">
         <v>46104</v>
       </c>
       <c r="B3" s="1">
@@ -3059,7 +3060,7 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="10">
+      <c r="A4" s="9">
         <v>46105</v>
       </c>
       <c r="B4" s="1">
@@ -3076,7 +3077,7 @@
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>46106</v>
       </c>
       <c r="B5" s="1">
@@ -3093,7 +3094,7 @@
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>46107</v>
       </c>
       <c r="B6" s="1">
@@ -3110,7 +3111,7 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>46108</v>
       </c>
       <c r="B7" s="1">
@@ -3127,7 +3128,7 @@
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>46111</v>
       </c>
       <c r="B8" s="1">
@@ -3144,7 +3145,7 @@
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="10">
+      <c r="A9" s="9">
         <v>46112</v>
       </c>
       <c r="B9" s="1">
@@ -3161,7 +3162,7 @@
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>46113</v>
       </c>
       <c r="B10" s="1">
@@ -3178,7 +3179,7 @@
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="10">
+      <c r="A11" s="9">
         <v>46118</v>
       </c>
       <c r="B11" s="1">
@@ -3195,7 +3196,7 @@
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>46119</v>
       </c>
       <c r="B12" s="1">
@@ -3212,7 +3213,7 @@
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>46120</v>
       </c>
       <c r="B13" s="1">
@@ -3229,7 +3230,7 @@
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="10">
+      <c r="A14" s="9">
         <v>46121</v>
       </c>
       <c r="B14" s="1">
@@ -3246,7 +3247,7 @@
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="10">
+      <c r="A15" s="9">
         <v>46122</v>
       </c>
       <c r="B15" s="1">
@@ -3263,7 +3264,7 @@
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="10">
+      <c r="A16" s="9">
         <v>46125</v>
       </c>
       <c r="B16" s="1">
@@ -3280,7 +3281,7 @@
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="10">
+      <c r="A17" s="9">
         <v>46126</v>
       </c>
       <c r="B17" s="1">
@@ -3297,7 +3298,7 @@
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="10">
+      <c r="A18" s="9">
         <v>46127</v>
       </c>
       <c r="B18" s="1">
@@ -3314,7 +3315,7 @@
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="10">
+      <c r="A19" s="9">
         <v>46128</v>
       </c>
       <c r="B19" s="1">
@@ -3331,7 +3332,7 @@
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="10">
+      <c r="A20" s="9">
         <v>46129</v>
       </c>
       <c r="B20" s="1">
@@ -3348,7 +3349,7 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="10">
+      <c r="A21" s="9">
         <v>46132</v>
       </c>
       <c r="B21" s="1">
@@ -3365,7 +3366,7 @@
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="10">
+      <c r="A22" s="9">
         <v>46133</v>
       </c>
       <c r="B22" s="1">
@@ -3382,7 +3383,7 @@
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="10">
+      <c r="A23" s="9">
         <v>46134</v>
       </c>
       <c r="B23" s="1">
@@ -3399,7 +3400,7 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="10">
+      <c r="A24" s="9">
         <v>46135</v>
       </c>
       <c r="B24" s="1">
@@ -3416,7 +3417,7 @@
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="10">
+      <c r="A25" s="9">
         <v>46136</v>
       </c>
       <c r="B25" s="1">
@@ -3433,7 +3434,7 @@
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="10">
+      <c r="A26" s="9">
         <v>46139</v>
       </c>
       <c r="B26" s="1">
@@ -3450,7 +3451,7 @@
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="10">
+      <c r="A27" s="9">
         <v>46140</v>
       </c>
       <c r="B27" s="1">
@@ -3467,7 +3468,7 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="10">
+      <c r="A28" s="9">
         <v>46141</v>
       </c>
       <c r="B28" s="1">
@@ -3484,7 +3485,7 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="10">
+      <c r="A29" s="9">
         <v>46142</v>
       </c>
       <c r="B29" s="1">
@@ -3504,1976 +3505,1996 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="10">
+      <c r="A30" s="9">
         <v>46146</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
-      <c r="C30" s="9"/>
+      <c r="C30" s="8"/>
       <c r="D30" s="1">
         <v>0</v>
       </c>
-      <c r="E30" s="9"/>
+      <c r="E30" s="8"/>
       <c r="F30" s="1">
         <v>0</v>
       </c>
-      <c r="G30" s="9"/>
+      <c r="G30" s="8"/>
       <c r="H30" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="10">
+      <c r="A31" s="9">
         <v>46147</v>
       </c>
       <c r="B31" s="1">
         <v>39236.082000000002</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="8"/>
       <c r="D31" s="1">
         <v>100</v>
       </c>
-      <c r="E31" s="9"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="1">
         <v>100</v>
       </c>
-      <c r="G31" s="9"/>
+      <c r="G31" s="8"/>
       <c r="H31" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="10">
+      <c r="A32" s="9">
         <v>46148</v>
       </c>
       <c r="B32" s="1">
         <v>1200</v>
       </c>
-      <c r="C32" s="9"/>
+      <c r="C32" s="8"/>
       <c r="D32" s="1">
         <v>100</v>
       </c>
-      <c r="E32" s="9"/>
+      <c r="E32" s="8"/>
       <c r="F32" s="1">
         <v>100</v>
       </c>
-      <c r="G32" s="9"/>
+      <c r="G32" s="8"/>
       <c r="H32" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="21">
+      <c r="A33" s="20">
         <v>46149</v>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="16">
         <v>32505.648000000001</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="17">
+      <c r="C33" s="19"/>
+      <c r="D33" s="16">
         <v>150</v>
       </c>
-      <c r="E33" s="20"/>
-      <c r="F33" s="17">
+      <c r="E33" s="19"/>
+      <c r="F33" s="16">
         <v>300</v>
       </c>
-      <c r="G33" s="20"/>
-      <c r="H33" s="17">
+      <c r="G33" s="19"/>
+      <c r="H33" s="16">
         <v>243.9</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="21">
+      <c r="A34" s="20">
         <v>46150</v>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="16">
         <v>8103.3360000000002</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="17">
+      <c r="C34" s="19"/>
+      <c r="D34" s="16">
         <v>100</v>
       </c>
-      <c r="E34" s="20"/>
-      <c r="F34" s="17">
+      <c r="E34" s="19"/>
+      <c r="F34" s="16">
         <v>100</v>
       </c>
-      <c r="G34" s="20"/>
-      <c r="H34" s="17">
+      <c r="G34" s="19"/>
+      <c r="H34" s="16">
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="21">
+      <c r="A35" s="20">
         <v>46153</v>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="16">
         <v>30219.955319000001</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="17">
+      <c r="C35" s="19"/>
+      <c r="D35" s="16">
         <v>100</v>
       </c>
-      <c r="E35" s="20"/>
-      <c r="F35" s="17">
+      <c r="E35" s="19"/>
+      <c r="F35" s="16">
         <v>110.06</v>
       </c>
-      <c r="G35" s="20"/>
-      <c r="H35" s="17">
+      <c r="G35" s="19"/>
+      <c r="H35" s="16">
         <v>109.71</v>
       </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="21">
+      <c r="A36" s="20">
         <v>46154</v>
       </c>
-      <c r="B36" s="17">
-        <v>0</v>
-      </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="17">
-        <v>0</v>
-      </c>
-      <c r="E36" s="20"/>
-      <c r="F36" s="17">
-        <v>0</v>
-      </c>
-      <c r="G36" s="20"/>
-      <c r="H36" s="17">
+      <c r="B36" s="16">
+        <v>0</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="16">
+        <v>0</v>
+      </c>
+      <c r="E36" s="19"/>
+      <c r="F36" s="16">
+        <v>0</v>
+      </c>
+      <c r="G36" s="19"/>
+      <c r="H36" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
-      <c r="A37" s="21">
+      <c r="A37" s="20">
         <v>46155</v>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="16">
         <v>200</v>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="17">
+      <c r="C37" s="19"/>
+      <c r="D37" s="16">
         <v>100</v>
       </c>
-      <c r="E37" s="20"/>
-      <c r="F37" s="17">
+      <c r="E37" s="19"/>
+      <c r="F37" s="16">
         <v>100</v>
       </c>
-      <c r="G37" s="20"/>
-      <c r="H37" s="17">
+      <c r="G37" s="19"/>
+      <c r="H37" s="16">
         <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="21">
+      <c r="A38" s="20">
         <v>46156</v>
       </c>
-      <c r="B38" s="17">
-        <v>0</v>
-      </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="17">
-        <v>0</v>
-      </c>
-      <c r="E38" s="20"/>
-      <c r="F38" s="17">
-        <v>0</v>
-      </c>
-      <c r="G38" s="20"/>
-      <c r="H38" s="17">
+      <c r="B38" s="16">
+        <v>0</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="16">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19"/>
+      <c r="F38" s="16">
+        <v>0</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="21">
+      <c r="A39" s="20">
         <v>46157</v>
       </c>
-      <c r="B39" s="17">
-        <v>0</v>
-      </c>
-      <c r="C39" s="28"/>
-      <c r="D39" s="17">
-        <v>0</v>
-      </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="17">
-        <v>0</v>
-      </c>
-      <c r="G39" s="29"/>
-      <c r="H39" s="17">
+      <c r="B39" s="16">
+        <v>0</v>
+      </c>
+      <c r="C39" s="27"/>
+      <c r="D39" s="16">
+        <v>0</v>
+      </c>
+      <c r="E39" s="28"/>
+      <c r="F39" s="16">
+        <v>0</v>
+      </c>
+      <c r="G39" s="28"/>
+      <c r="H39" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="21">
+      <c r="A40" s="20">
         <v>46161</v>
       </c>
-      <c r="B40" s="17">
-        <v>0</v>
-      </c>
-      <c r="D40" s="17">
-        <v>0</v>
-      </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="17">
-        <v>0</v>
-      </c>
-      <c r="G40" s="29"/>
-      <c r="H40" s="17">
+      <c r="B40" s="16">
+        <v>0</v>
+      </c>
+      <c r="D40" s="16">
+        <v>0</v>
+      </c>
+      <c r="E40" s="28"/>
+      <c r="F40" s="16">
+        <v>0</v>
+      </c>
+      <c r="G40" s="28"/>
+      <c r="H40" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="21">
+      <c r="A41" s="20">
         <v>46162</v>
       </c>
-      <c r="B41" s="17">
-        <v>0</v>
-      </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="17">
-        <v>0</v>
-      </c>
-      <c r="E41" s="24"/>
-      <c r="F41" s="17">
-        <v>0</v>
-      </c>
-      <c r="G41" s="24"/>
-      <c r="H41" s="17">
+      <c r="B41" s="16">
+        <v>0</v>
+      </c>
+      <c r="C41" s="23"/>
+      <c r="D41" s="16">
+        <v>0</v>
+      </c>
+      <c r="E41" s="23"/>
+      <c r="F41" s="16">
+        <v>0</v>
+      </c>
+      <c r="G41" s="23"/>
+      <c r="H41" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="A42" s="21">
+      <c r="A42" s="20">
         <v>46163</v>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="16">
         <v>5006.6000000000004</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="17">
+      <c r="C42" s="19"/>
+      <c r="D42" s="16">
         <v>120</v>
       </c>
-      <c r="E42" s="20"/>
-      <c r="F42" s="17">
+      <c r="E42" s="19"/>
+      <c r="F42" s="16">
         <v>120</v>
       </c>
-      <c r="G42" s="20"/>
-      <c r="H42" s="17">
+      <c r="G42" s="19"/>
+      <c r="H42" s="16">
         <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="21">
+      <c r="A43" s="20">
         <v>46164</v>
       </c>
-      <c r="B43" s="17">
-        <v>0</v>
-      </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="17">
-        <v>0</v>
-      </c>
-      <c r="E43" s="20"/>
-      <c r="F43" s="17">
-        <v>0</v>
-      </c>
-      <c r="G43" s="20"/>
-      <c r="H43" s="17">
+      <c r="B43" s="16">
+        <v>0</v>
+      </c>
+      <c r="C43" s="19"/>
+      <c r="D43" s="16">
+        <v>0</v>
+      </c>
+      <c r="E43" s="19"/>
+      <c r="F43" s="16">
+        <v>0</v>
+      </c>
+      <c r="G43" s="19"/>
+      <c r="H43" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="21">
+      <c r="A44" s="20">
         <v>46167</v>
       </c>
-      <c r="B44" s="17">
-        <v>0</v>
-      </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="17">
-        <v>0</v>
-      </c>
-      <c r="E44" s="20"/>
-      <c r="F44" s="17">
-        <v>0</v>
-      </c>
-      <c r="G44" s="20"/>
-      <c r="H44" s="17">
+      <c r="B44" s="16">
+        <v>0</v>
+      </c>
+      <c r="C44" s="19"/>
+      <c r="D44" s="16">
+        <v>0</v>
+      </c>
+      <c r="E44" s="19"/>
+      <c r="F44" s="16">
+        <v>0</v>
+      </c>
+      <c r="G44" s="19"/>
+      <c r="H44" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="21">
+      <c r="A45" s="20">
         <v>46168</v>
       </c>
-      <c r="B45" s="17">
-        <v>0</v>
-      </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="17">
-        <v>0</v>
-      </c>
-      <c r="E45" s="20"/>
-      <c r="F45" s="17">
-        <v>0</v>
-      </c>
-      <c r="G45" s="20"/>
-      <c r="H45" s="17">
+      <c r="B45" s="16">
+        <v>0</v>
+      </c>
+      <c r="C45" s="19"/>
+      <c r="D45" s="16">
+        <v>0</v>
+      </c>
+      <c r="E45" s="19"/>
+      <c r="F45" s="16">
+        <v>0</v>
+      </c>
+      <c r="G45" s="19"/>
+      <c r="H45" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="21">
+      <c r="A46" s="20">
         <v>46169</v>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="16">
         <v>51256.235569999997</v>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="17">
+      <c r="C46" s="19"/>
+      <c r="D46" s="16">
         <v>250</v>
       </c>
-      <c r="E46" s="20"/>
-      <c r="F46" s="17">
+      <c r="E46" s="19"/>
+      <c r="F46" s="16">
         <v>300.02</v>
       </c>
-      <c r="G46" s="20"/>
-      <c r="H46" s="17">
+      <c r="G46" s="19"/>
+      <c r="H46" s="16">
         <v>273.24</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="A47" s="21">
+      <c r="A47" s="20">
         <v>46170</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="16">
         <v>38032.045118000002</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="17">
+      <c r="C47" s="19"/>
+      <c r="D47" s="16">
         <v>300</v>
       </c>
-      <c r="E47" s="20"/>
-      <c r="F47" s="17">
+      <c r="E47" s="19"/>
+      <c r="F47" s="16">
         <v>330</v>
       </c>
-      <c r="G47" s="20"/>
-      <c r="H47" s="17">
+      <c r="G47" s="19"/>
+      <c r="H47" s="16">
         <v>311.49</v>
       </c>
     </row>
     <row r="48" spans="1:8">
-      <c r="A48" s="21">
+      <c r="A48" s="20">
         <v>46171</v>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="16">
         <v>45546.404509</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="17">
+      <c r="C48" s="19"/>
+      <c r="D48" s="16">
         <v>100</v>
       </c>
-      <c r="E48" s="20"/>
-      <c r="F48" s="17">
+      <c r="E48" s="19"/>
+      <c r="F48" s="16">
         <v>120</v>
       </c>
-      <c r="G48" s="20"/>
-      <c r="H48" s="17">
+      <c r="G48" s="19"/>
+      <c r="H48" s="16">
         <v>107.95</v>
       </c>
     </row>
     <row r="49" spans="1:8">
-      <c r="A49" s="21">
+      <c r="A49" s="20">
         <v>46174</v>
       </c>
-      <c r="B49" s="17">
-        <v>0</v>
-      </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="17">
-        <v>0</v>
-      </c>
-      <c r="E49" s="20"/>
-      <c r="F49" s="17">
-        <v>0</v>
-      </c>
-      <c r="G49" s="20"/>
-      <c r="H49" s="17">
+      <c r="B49" s="16">
+        <v>0</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="16">
+        <v>0</v>
+      </c>
+      <c r="E49" s="19"/>
+      <c r="F49" s="16">
+        <v>0</v>
+      </c>
+      <c r="G49" s="19"/>
+      <c r="H49" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="21">
+      <c r="A50" s="20">
         <v>46175</v>
       </c>
-      <c r="B50" s="17">
-        <v>0</v>
-      </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="17">
-        <v>0</v>
-      </c>
-      <c r="E50" s="20"/>
-      <c r="F50" s="17">
-        <v>0</v>
-      </c>
-      <c r="G50" s="20"/>
-      <c r="H50" s="17">
+      <c r="B50" s="16">
+        <v>0</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" s="16">
+        <v>0</v>
+      </c>
+      <c r="E50" s="19"/>
+      <c r="F50" s="16">
+        <v>0</v>
+      </c>
+      <c r="G50" s="19"/>
+      <c r="H50" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:8">
-      <c r="A51" s="21">
+      <c r="A51" s="20">
         <v>46176</v>
       </c>
-      <c r="B51" s="17">
-        <v>0</v>
-      </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="17">
-        <v>0</v>
-      </c>
-      <c r="E51" s="20"/>
-      <c r="F51" s="17">
-        <v>0</v>
-      </c>
-      <c r="G51" s="20"/>
-      <c r="H51" s="17">
+      <c r="B51" s="16">
+        <v>0</v>
+      </c>
+      <c r="C51" s="19"/>
+      <c r="D51" s="16">
+        <v>0</v>
+      </c>
+      <c r="E51" s="19"/>
+      <c r="F51" s="16">
+        <v>0</v>
+      </c>
+      <c r="G51" s="19"/>
+      <c r="H51" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="21">
+      <c r="A52" s="20">
         <v>46177</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="16">
         <v>200</v>
       </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="17">
+      <c r="C52" s="19"/>
+      <c r="D52" s="16">
         <v>150</v>
       </c>
-      <c r="E52" s="20"/>
-      <c r="F52" s="17">
+      <c r="E52" s="19"/>
+      <c r="F52" s="16">
         <v>150</v>
       </c>
-      <c r="G52" s="20"/>
-      <c r="H52" s="17">
+      <c r="G52" s="19"/>
+      <c r="H52" s="16">
         <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="21">
+      <c r="A53" s="20">
         <v>46178</v>
       </c>
-      <c r="B53" s="17">
+      <c r="B53" s="16">
         <v>10878.022664</v>
       </c>
-      <c r="C53" s="20"/>
-      <c r="D53" s="17">
+      <c r="C53" s="19"/>
+      <c r="D53" s="16">
         <v>50</v>
       </c>
-      <c r="E53" s="20"/>
-      <c r="F53" s="17">
+      <c r="E53" s="19"/>
+      <c r="F53" s="16">
         <v>50</v>
       </c>
-      <c r="G53" s="20"/>
-      <c r="H53" s="17">
+      <c r="G53" s="19"/>
+      <c r="H53" s="16">
         <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:8">
-      <c r="A54" s="21">
+      <c r="A54" s="20">
         <v>46182</v>
       </c>
-      <c r="B54" s="17">
-        <v>0</v>
-      </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="17">
-        <v>0</v>
-      </c>
-      <c r="E54" s="20"/>
-      <c r="F54" s="17">
-        <v>0</v>
-      </c>
-      <c r="G54" s="20"/>
-      <c r="H54" s="17">
+      <c r="B54" s="16">
+        <v>0</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="16">
+        <v>0</v>
+      </c>
+      <c r="E54" s="19"/>
+      <c r="F54" s="16">
+        <v>0</v>
+      </c>
+      <c r="G54" s="19"/>
+      <c r="H54" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:8">
-      <c r="A55" s="21">
+      <c r="A55" s="20">
         <v>46183</v>
       </c>
-      <c r="B55" s="17">
+      <c r="B55" s="16">
         <v>67565.465119999993</v>
       </c>
-      <c r="C55" s="20"/>
-      <c r="D55" s="17">
+      <c r="C55" s="19"/>
+      <c r="D55" s="16">
         <v>250</v>
       </c>
-      <c r="E55" s="20"/>
-      <c r="F55" s="17">
+      <c r="E55" s="19"/>
+      <c r="F55" s="16">
         <v>320</v>
       </c>
-      <c r="G55" s="20"/>
-      <c r="H55" s="17">
+      <c r="G55" s="19"/>
+      <c r="H55" s="16">
         <v>294.99</v>
       </c>
     </row>
     <row r="56" spans="1:8">
-      <c r="A56" s="21">
+      <c r="A56" s="20">
         <v>46184</v>
       </c>
-      <c r="B56" s="17">
-        <v>0</v>
-      </c>
-      <c r="C56" s="20"/>
-      <c r="D56" s="17">
-        <v>0</v>
-      </c>
-      <c r="E56" s="20"/>
-      <c r="F56" s="17">
-        <v>0</v>
-      </c>
-      <c r="G56" s="20"/>
-      <c r="H56" s="17">
+      <c r="B56" s="16">
+        <v>0</v>
+      </c>
+      <c r="C56" s="19"/>
+      <c r="D56" s="16">
+        <v>0</v>
+      </c>
+      <c r="E56" s="19"/>
+      <c r="F56" s="16">
+        <v>0</v>
+      </c>
+      <c r="G56" s="19"/>
+      <c r="H56" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:8">
-      <c r="A57" s="21">
+      <c r="A57" s="20">
         <v>46185</v>
       </c>
-      <c r="B57" s="17">
+      <c r="B57" s="16">
         <v>40962.766997999999</v>
       </c>
-      <c r="C57" s="20"/>
-      <c r="D57" s="17">
+      <c r="C57" s="19"/>
+      <c r="D57" s="16">
         <v>110</v>
       </c>
-      <c r="E57" s="20"/>
-      <c r="F57" s="17">
+      <c r="E57" s="19"/>
+      <c r="F57" s="16">
         <v>120</v>
       </c>
-      <c r="G57" s="20"/>
-      <c r="H57" s="17">
+      <c r="G57" s="19"/>
+      <c r="H57" s="16">
         <v>110.87</v>
       </c>
     </row>
     <row r="58" spans="1:8">
-      <c r="A58" s="21">
+      <c r="A58" s="20">
         <v>46188</v>
       </c>
-      <c r="B58" s="17">
+      <c r="B58" s="16">
         <v>13248.755665999999</v>
       </c>
-      <c r="C58" s="20"/>
-      <c r="D58" s="17">
+      <c r="C58" s="19"/>
+      <c r="D58" s="16">
         <v>290</v>
       </c>
-      <c r="E58" s="20"/>
-      <c r="F58" s="17">
+      <c r="E58" s="19"/>
+      <c r="F58" s="16">
         <v>330</v>
       </c>
-      <c r="G58" s="20"/>
-      <c r="H58" s="17">
+      <c r="G58" s="19"/>
+      <c r="H58" s="16">
         <v>300.5</v>
       </c>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="21">
+      <c r="A59" s="20">
         <v>46189</v>
       </c>
-      <c r="B59" s="17">
+      <c r="B59" s="16">
         <v>15884.312540000001</v>
       </c>
-      <c r="C59" s="20"/>
-      <c r="D59" s="17">
+      <c r="C59" s="19"/>
+      <c r="D59" s="16">
         <v>335</v>
       </c>
-      <c r="E59" s="20"/>
-      <c r="F59" s="17">
+      <c r="E59" s="19"/>
+      <c r="F59" s="16">
         <v>340</v>
       </c>
-      <c r="G59" s="20"/>
-      <c r="H59" s="17">
+      <c r="G59" s="19"/>
+      <c r="H59" s="16">
         <v>335.1</v>
       </c>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="21">
+      <c r="A60" s="20">
         <v>46190</v>
       </c>
-      <c r="B60" s="17">
+      <c r="B60" s="16">
         <v>51428.024998000001</v>
       </c>
-      <c r="C60" s="20"/>
-      <c r="D60" s="17">
+      <c r="C60" s="19"/>
+      <c r="D60" s="16">
         <v>300</v>
       </c>
-      <c r="E60" s="20"/>
-      <c r="F60" s="17">
+      <c r="E60" s="19"/>
+      <c r="F60" s="16">
         <v>340</v>
       </c>
-      <c r="G60" s="20"/>
-      <c r="H60" s="17">
+      <c r="G60" s="19"/>
+      <c r="H60" s="16">
         <v>314.18</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="21">
+      <c r="A61" s="20">
         <v>46191</v>
       </c>
-      <c r="B61" s="17">
+      <c r="B61" s="16">
         <v>21477.350433</v>
       </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="17">
+      <c r="C61" s="19"/>
+      <c r="D61" s="16">
         <v>350</v>
       </c>
-      <c r="E61" s="20"/>
-      <c r="F61" s="17">
+      <c r="E61" s="19"/>
+      <c r="F61" s="16">
         <v>390</v>
       </c>
-      <c r="G61" s="20"/>
-      <c r="H61" s="17">
+      <c r="G61" s="19"/>
+      <c r="H61" s="16">
         <v>354.17</v>
       </c>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="21">
+      <c r="A62" s="20">
         <v>46192</v>
       </c>
-      <c r="B62" s="17">
+      <c r="B62" s="16">
         <v>19544.702092</v>
       </c>
-      <c r="C62" s="20"/>
-      <c r="D62" s="17">
+      <c r="C62" s="19"/>
+      <c r="D62" s="16">
         <v>120</v>
       </c>
-      <c r="E62" s="20"/>
-      <c r="F62" s="17">
+      <c r="E62" s="19"/>
+      <c r="F62" s="16">
         <v>125.02</v>
       </c>
-      <c r="G62" s="20"/>
-      <c r="H62" s="17">
+      <c r="G62" s="19"/>
+      <c r="H62" s="16">
         <v>121.88</v>
       </c>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="21">
+      <c r="A63" s="20">
         <v>46195</v>
       </c>
-      <c r="B63" s="17">
+      <c r="B63" s="16">
         <v>1676.4307650000001</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="17">
+      <c r="C63" s="19"/>
+      <c r="D63" s="16">
         <v>350</v>
       </c>
-      <c r="E63" s="20"/>
-      <c r="F63" s="17">
+      <c r="E63" s="19"/>
+      <c r="F63" s="16">
         <v>360</v>
       </c>
-      <c r="G63" s="20"/>
-      <c r="H63" s="17">
+      <c r="G63" s="19"/>
+      <c r="H63" s="16">
         <v>351.2</v>
       </c>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="21">
+      <c r="A64" s="20">
         <v>46196</v>
       </c>
-      <c r="B64" s="17">
+      <c r="B64" s="16">
         <v>4776.4754999999996</v>
       </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="17">
+      <c r="C64" s="19"/>
+      <c r="D64" s="16">
         <v>140</v>
       </c>
-      <c r="E64" s="20"/>
-      <c r="F64" s="17">
+      <c r="E64" s="19"/>
+      <c r="F64" s="16">
         <v>350</v>
       </c>
-      <c r="G64" s="20"/>
-      <c r="H64" s="17">
+      <c r="G64" s="19"/>
+      <c r="H64" s="16">
         <v>184.42</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="21">
+      <c r="A65" s="20">
         <v>46198</v>
       </c>
-      <c r="B65" s="17">
+      <c r="B65" s="16">
         <v>1740</v>
       </c>
-      <c r="C65" s="20"/>
-      <c r="D65" s="17">
+      <c r="C65" s="19"/>
+      <c r="D65" s="16">
         <v>120</v>
       </c>
-      <c r="E65" s="20"/>
-      <c r="F65" s="17">
+      <c r="E65" s="19"/>
+      <c r="F65" s="16">
         <v>300</v>
       </c>
-      <c r="G65" s="20"/>
-      <c r="H65" s="17">
+      <c r="G65" s="19"/>
+      <c r="H65" s="16">
         <v>282.06896551724139</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="21">
+      <c r="A66" s="20">
         <v>46203</v>
       </c>
-      <c r="B66" s="17">
+      <c r="B66" s="16">
         <v>1904.22222222</v>
       </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="17">
+      <c r="C66" s="19"/>
+      <c r="D66" s="16">
         <v>0.01</v>
       </c>
-      <c r="E66" s="20"/>
-      <c r="F66" s="17">
+      <c r="E66" s="19"/>
+      <c r="F66" s="16">
         <v>0.01</v>
       </c>
-      <c r="G66" s="20"/>
-      <c r="H66" s="17">
+      <c r="G66" s="19"/>
+      <c r="H66" s="16">
         <v>0.01</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="21">
+      <c r="A67" s="20">
         <v>46204</v>
       </c>
-      <c r="B67" s="17">
-        <v>0</v>
-      </c>
-      <c r="C67" s="20"/>
-      <c r="D67" s="17">
-        <v>0</v>
-      </c>
-      <c r="E67" s="20"/>
-      <c r="F67" s="17">
-        <v>0</v>
-      </c>
-      <c r="G67" s="20"/>
-      <c r="H67" s="17">
+      <c r="B67" s="16">
+        <v>0</v>
+      </c>
+      <c r="C67" s="19"/>
+      <c r="D67" s="16">
+        <v>0</v>
+      </c>
+      <c r="E67" s="19"/>
+      <c r="F67" s="16">
+        <v>0</v>
+      </c>
+      <c r="G67" s="19"/>
+      <c r="H67" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="21">
+      <c r="A68" s="20">
         <v>46205</v>
       </c>
-      <c r="B68" s="17">
+      <c r="B68" s="16">
         <v>2461.9</v>
       </c>
-      <c r="C68" s="20"/>
-      <c r="D68" s="17">
+      <c r="C68" s="19"/>
+      <c r="D68" s="16">
         <v>110</v>
       </c>
-      <c r="E68" s="20"/>
-      <c r="F68" s="17">
+      <c r="E68" s="19"/>
+      <c r="F68" s="16">
         <v>135</v>
       </c>
-      <c r="G68" s="20"/>
-      <c r="H68" s="17">
+      <c r="G68" s="19"/>
+      <c r="H68" s="16">
         <v>131.66</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="21">
+      <c r="A69" s="20">
         <v>46206</v>
       </c>
-      <c r="B69" s="17">
+      <c r="B69" s="16">
         <v>279.5</v>
       </c>
-      <c r="C69" s="20"/>
-      <c r="D69" s="17">
+      <c r="C69" s="19"/>
+      <c r="D69" s="16">
         <v>5</v>
       </c>
-      <c r="E69" s="20"/>
-      <c r="F69" s="17">
+      <c r="E69" s="19"/>
+      <c r="F69" s="16">
         <v>60</v>
       </c>
-      <c r="G69" s="20"/>
-      <c r="H69" s="17">
+      <c r="G69" s="19"/>
+      <c r="H69" s="16">
         <v>54.19</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="21">
+      <c r="A70" s="20">
         <v>46209</v>
       </c>
-      <c r="B70" s="17">
-        <v>0</v>
-      </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="17">
-        <v>0</v>
-      </c>
-      <c r="E70" s="20"/>
-      <c r="F70" s="17">
-        <v>0</v>
-      </c>
-      <c r="G70" s="20"/>
-      <c r="H70" s="17">
+      <c r="B70" s="16">
+        <v>0</v>
+      </c>
+      <c r="C70" s="19"/>
+      <c r="D70" s="16">
+        <v>0</v>
+      </c>
+      <c r="E70" s="19"/>
+      <c r="F70" s="16">
+        <v>0</v>
+      </c>
+      <c r="G70" s="19"/>
+      <c r="H70" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="21">
+      <c r="A71" s="20">
         <v>46210</v>
       </c>
-      <c r="B71" s="17">
-        <v>0</v>
-      </c>
-      <c r="C71" s="20"/>
-      <c r="D71" s="17">
-        <v>0</v>
-      </c>
-      <c r="E71" s="20"/>
-      <c r="F71" s="17">
-        <v>0</v>
-      </c>
-      <c r="G71" s="20"/>
-      <c r="H71" s="17">
+      <c r="B71" s="16">
+        <v>0</v>
+      </c>
+      <c r="C71" s="19"/>
+      <c r="D71" s="16">
+        <v>0</v>
+      </c>
+      <c r="E71" s="19"/>
+      <c r="F71" s="16">
+        <v>0</v>
+      </c>
+      <c r="G71" s="19"/>
+      <c r="H71" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="21">
+      <c r="A72" s="20">
         <v>46211</v>
       </c>
-      <c r="B72" s="17">
-        <v>0</v>
-      </c>
-      <c r="C72" s="20"/>
-      <c r="D72" s="17">
-        <v>0</v>
-      </c>
-      <c r="E72" s="20"/>
-      <c r="F72" s="17">
-        <v>0</v>
-      </c>
-      <c r="G72" s="20"/>
-      <c r="H72" s="17">
+      <c r="B72" s="16">
+        <v>0</v>
+      </c>
+      <c r="C72" s="19"/>
+      <c r="D72" s="16">
+        <v>0</v>
+      </c>
+      <c r="E72" s="19"/>
+      <c r="F72" s="16">
+        <v>0</v>
+      </c>
+      <c r="G72" s="19"/>
+      <c r="H72" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="21">
+      <c r="A73" s="20">
         <v>46212</v>
       </c>
-      <c r="B73" s="17">
+      <c r="B73" s="16">
         <v>3000</v>
       </c>
-      <c r="C73" s="20"/>
-      <c r="D73" s="17">
+      <c r="C73" s="19"/>
+      <c r="D73" s="16">
         <v>1</v>
       </c>
-      <c r="E73" s="20"/>
-      <c r="F73" s="17">
+      <c r="E73" s="19"/>
+      <c r="F73" s="16">
         <v>1</v>
       </c>
-      <c r="G73" s="20"/>
-      <c r="H73" s="17">
+      <c r="G73" s="19"/>
+      <c r="H73" s="16">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="21">
+      <c r="A74" s="20">
         <v>46213</v>
       </c>
-      <c r="B74" s="17">
-        <v>0</v>
-      </c>
-      <c r="C74" s="20"/>
-      <c r="D74" s="17">
-        <v>0</v>
-      </c>
-      <c r="E74" s="20"/>
-      <c r="F74" s="17">
-        <v>0</v>
-      </c>
-      <c r="G74" s="20"/>
-      <c r="H74" s="17">
+      <c r="B74" s="16">
+        <v>0</v>
+      </c>
+      <c r="C74" s="19"/>
+      <c r="D74" s="16">
+        <v>0</v>
+      </c>
+      <c r="E74" s="19"/>
+      <c r="F74" s="16">
+        <v>0</v>
+      </c>
+      <c r="G74" s="19"/>
+      <c r="H74" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="21">
+      <c r="A75" s="20">
         <v>46216</v>
       </c>
-      <c r="B75" s="17">
-        <v>0</v>
-      </c>
-      <c r="C75" s="20"/>
-      <c r="D75" s="17">
-        <v>0</v>
-      </c>
-      <c r="E75" s="20"/>
-      <c r="F75" s="17">
-        <v>0</v>
-      </c>
-      <c r="G75" s="20"/>
-      <c r="H75" s="17">
+      <c r="B75" s="16">
+        <v>0</v>
+      </c>
+      <c r="C75" s="19"/>
+      <c r="D75" s="16">
+        <v>0</v>
+      </c>
+      <c r="E75" s="19"/>
+      <c r="F75" s="16">
+        <v>0</v>
+      </c>
+      <c r="G75" s="19"/>
+      <c r="H75" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="21">
+      <c r="A76" s="20">
         <v>46217</v>
       </c>
-      <c r="B76" s="17">
-        <v>0</v>
-      </c>
-      <c r="C76" s="20"/>
-      <c r="D76" s="17">
-        <v>0</v>
-      </c>
-      <c r="E76" s="20"/>
-      <c r="F76" s="17">
-        <v>0</v>
-      </c>
-      <c r="G76" s="20"/>
-      <c r="H76" s="17">
+      <c r="B76" s="16">
+        <v>0</v>
+      </c>
+      <c r="C76" s="19"/>
+      <c r="D76" s="16">
+        <v>0</v>
+      </c>
+      <c r="E76" s="19"/>
+      <c r="F76" s="16">
+        <v>0</v>
+      </c>
+      <c r="G76" s="19"/>
+      <c r="H76" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="21">
+      <c r="A77" s="20">
         <v>46218</v>
       </c>
-      <c r="B77" s="17">
+      <c r="B77" s="16">
         <v>217.41</v>
       </c>
-      <c r="C77" s="20"/>
-      <c r="D77" s="17">
+      <c r="C77" s="19"/>
+      <c r="D77" s="16">
         <v>50</v>
       </c>
-      <c r="E77" s="20"/>
-      <c r="F77" s="17">
+      <c r="E77" s="19"/>
+      <c r="F77" s="16">
         <v>200</v>
       </c>
-      <c r="G77" s="20"/>
-      <c r="H77" s="17">
+      <c r="G77" s="19"/>
+      <c r="H77" s="16">
         <v>165.7</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="21">
+      <c r="A78" s="20">
         <v>46219</v>
       </c>
-      <c r="B78" s="17">
+      <c r="B78" s="16">
         <v>517.9</v>
       </c>
-      <c r="C78" s="20"/>
-      <c r="D78" s="17">
+      <c r="C78" s="19"/>
+      <c r="D78" s="16">
         <v>50</v>
       </c>
-      <c r="E78" s="20"/>
-      <c r="F78" s="17">
+      <c r="E78" s="19"/>
+      <c r="F78" s="16">
         <v>120</v>
       </c>
-      <c r="G78" s="20"/>
-      <c r="H78" s="17">
+      <c r="G78" s="19"/>
+      <c r="H78" s="16">
         <v>119.03</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="21">
+      <c r="A79" s="20">
         <v>46190</v>
       </c>
-      <c r="B79" s="17">
+      <c r="B79" s="16">
         <v>31613.569407999999</v>
       </c>
-      <c r="C79" s="20"/>
-      <c r="D79" s="17">
+      <c r="C79" s="19"/>
+      <c r="D79" s="16">
         <v>25</v>
       </c>
-      <c r="E79" s="20"/>
-      <c r="F79" s="17">
+      <c r="E79" s="19"/>
+      <c r="F79" s="16">
         <v>85</v>
       </c>
-      <c r="G79" s="20"/>
-      <c r="H79" s="17">
+      <c r="G79" s="19"/>
+      <c r="H79" s="16">
         <v>80.14</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="21">
+      <c r="A80" s="20">
         <v>46224</v>
       </c>
-      <c r="B80" s="17">
+      <c r="B80" s="16">
         <v>880</v>
       </c>
-      <c r="C80" s="20"/>
-      <c r="D80" s="17">
+      <c r="C80" s="19"/>
+      <c r="D80" s="16">
         <v>150</v>
       </c>
-      <c r="E80" s="20"/>
-      <c r="F80" s="17">
+      <c r="E80" s="19"/>
+      <c r="F80" s="16">
         <v>200</v>
       </c>
-      <c r="G80" s="20"/>
-      <c r="H80" s="17">
+      <c r="G80" s="19"/>
+      <c r="H80" s="16">
         <v>184.77</v>
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="21">
+      <c r="A81" s="20">
         <v>46225</v>
       </c>
-      <c r="B81" s="17">
-        <v>0</v>
-      </c>
-      <c r="C81" s="20"/>
-      <c r="D81" s="17">
-        <v>0</v>
-      </c>
-      <c r="E81" s="20"/>
-      <c r="F81" s="17">
-        <v>0</v>
-      </c>
-      <c r="G81" s="20"/>
-      <c r="H81" s="17">
+      <c r="B81" s="16">
+        <v>0</v>
+      </c>
+      <c r="C81" s="19"/>
+      <c r="D81" s="16">
+        <v>0</v>
+      </c>
+      <c r="E81" s="19"/>
+      <c r="F81" s="16">
+        <v>0</v>
+      </c>
+      <c r="G81" s="19"/>
+      <c r="H81" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:8">
-      <c r="A82" s="21">
+      <c r="A82" s="20">
         <v>46226</v>
       </c>
-      <c r="B82" s="17">
-        <v>0</v>
-      </c>
-      <c r="C82" s="20"/>
-      <c r="D82" s="17">
-        <v>0</v>
-      </c>
-      <c r="E82" s="20"/>
-      <c r="F82" s="17">
-        <v>0</v>
-      </c>
-      <c r="G82" s="20"/>
-      <c r="H82" s="17">
+      <c r="B82" s="16">
+        <v>0</v>
+      </c>
+      <c r="C82" s="19"/>
+      <c r="D82" s="16">
+        <v>0</v>
+      </c>
+      <c r="E82" s="19"/>
+      <c r="F82" s="16">
+        <v>0</v>
+      </c>
+      <c r="G82" s="19"/>
+      <c r="H82" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:8">
-      <c r="A83" s="21">
+      <c r="A83" s="20">
         <v>46230</v>
       </c>
-      <c r="B83" s="17">
-        <v>0</v>
-      </c>
-      <c r="C83" s="20"/>
-      <c r="D83" s="17">
-        <v>0</v>
-      </c>
-      <c r="E83" s="20"/>
-      <c r="F83" s="17">
-        <v>0</v>
-      </c>
-      <c r="G83" s="20"/>
-      <c r="H83" s="17">
+      <c r="B83" s="16">
+        <v>0</v>
+      </c>
+      <c r="C83" s="19"/>
+      <c r="D83" s="16">
+        <v>0</v>
+      </c>
+      <c r="E83" s="19"/>
+      <c r="F83" s="16">
+        <v>0</v>
+      </c>
+      <c r="G83" s="19"/>
+      <c r="H83" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:8">
-      <c r="A84" s="21">
+      <c r="A84" s="20">
         <v>46231</v>
       </c>
-      <c r="B84" s="17">
+      <c r="B84" s="16">
         <v>230</v>
       </c>
-      <c r="C84" s="20"/>
-      <c r="D84" s="17">
+      <c r="C84" s="19"/>
+      <c r="D84" s="16">
         <v>90</v>
       </c>
-      <c r="E84" s="20"/>
-      <c r="F84" s="17">
+      <c r="E84" s="19"/>
+      <c r="F84" s="16">
         <v>100</v>
       </c>
-      <c r="G84" s="20"/>
-      <c r="H84" s="17">
+      <c r="G84" s="19"/>
+      <c r="H84" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="85" spans="1:8">
-      <c r="A85" s="21">
+      <c r="A85" s="20">
         <v>46232</v>
       </c>
-      <c r="B85" s="17">
+      <c r="B85" s="16">
         <v>20</v>
       </c>
-      <c r="C85" s="20"/>
-      <c r="D85" s="17">
+      <c r="C85" s="19"/>
+      <c r="D85" s="16">
         <v>100</v>
       </c>
-      <c r="E85" s="20"/>
-      <c r="F85" s="17">
+      <c r="E85" s="19"/>
+      <c r="F85" s="16">
         <v>100</v>
       </c>
-      <c r="G85" s="20"/>
-      <c r="H85" s="17">
+      <c r="G85" s="19"/>
+      <c r="H85" s="16">
         <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:8">
-      <c r="A86" s="21">
+      <c r="A86" s="20">
         <v>46233</v>
       </c>
-      <c r="B86" s="17">
+      <c r="B86" s="16">
         <v>280</v>
       </c>
-      <c r="C86" s="20"/>
-      <c r="D86" s="17">
+      <c r="C86" s="19"/>
+      <c r="D86" s="16">
         <v>40</v>
       </c>
-      <c r="E86" s="20"/>
-      <c r="F86" s="17">
+      <c r="E86" s="19"/>
+      <c r="F86" s="16">
         <v>100</v>
       </c>
-      <c r="G86" s="20"/>
-      <c r="H86" s="17">
+      <c r="G86" s="19"/>
+      <c r="H86" s="16">
         <v>66.430000000000007</v>
       </c>
     </row>
     <row r="87" spans="1:8">
-      <c r="A87" s="21">
+      <c r="A87" s="20">
         <v>46234</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B87" s="16">
         <v>60</v>
       </c>
-      <c r="C87" s="20"/>
-      <c r="D87" s="17">
+      <c r="C87" s="19"/>
+      <c r="D87" s="16">
         <v>40</v>
       </c>
-      <c r="E87" s="20"/>
-      <c r="F87" s="17">
+      <c r="E87" s="19"/>
+      <c r="F87" s="16">
         <v>40</v>
       </c>
-      <c r="G87" s="20"/>
-      <c r="H87" s="17">
+      <c r="G87" s="19"/>
+      <c r="H87" s="16">
         <v>40</v>
       </c>
     </row>
     <row r="88" spans="1:8">
-      <c r="A88" s="21">
+      <c r="A88" s="20">
         <v>46237</v>
       </c>
-      <c r="B88" s="17">
+      <c r="B88" s="16">
         <v>1500</v>
       </c>
-      <c r="C88" s="20"/>
-      <c r="D88" s="17">
+      <c r="C88" s="19"/>
+      <c r="D88" s="16">
         <v>110</v>
       </c>
-      <c r="E88" s="20"/>
-      <c r="F88" s="17">
+      <c r="E88" s="19"/>
+      <c r="F88" s="16">
         <v>110</v>
       </c>
-      <c r="G88" s="20"/>
-      <c r="H88" s="17">
+      <c r="G88" s="19"/>
+      <c r="H88" s="16">
         <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:8">
-      <c r="A89" s="21">
+      <c r="A89" s="20">
         <v>46238</v>
       </c>
-      <c r="B89" s="17">
-        <v>0</v>
-      </c>
-      <c r="C89" s="20"/>
-      <c r="D89" s="17">
-        <v>0</v>
-      </c>
-      <c r="E89" s="20"/>
-      <c r="F89" s="17">
-        <v>0</v>
-      </c>
-      <c r="G89" s="20"/>
-      <c r="H89" s="17">
+      <c r="B89" s="16">
+        <v>0</v>
+      </c>
+      <c r="C89" s="19"/>
+      <c r="D89" s="16">
+        <v>0</v>
+      </c>
+      <c r="E89" s="19"/>
+      <c r="F89" s="16">
+        <v>0</v>
+      </c>
+      <c r="G89" s="19"/>
+      <c r="H89" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:8">
-      <c r="A90" s="21">
+      <c r="A90" s="20">
         <v>46239</v>
       </c>
-      <c r="B90" s="17">
-        <v>0</v>
-      </c>
-      <c r="C90" s="20"/>
-      <c r="D90" s="17">
-        <v>0</v>
-      </c>
-      <c r="E90" s="20"/>
-      <c r="F90" s="17">
-        <v>0</v>
-      </c>
-      <c r="G90" s="20"/>
-      <c r="H90" s="17">
+      <c r="B90" s="16">
+        <v>0</v>
+      </c>
+      <c r="C90" s="19"/>
+      <c r="D90" s="16">
+        <v>0</v>
+      </c>
+      <c r="E90" s="19"/>
+      <c r="F90" s="16">
+        <v>0</v>
+      </c>
+      <c r="G90" s="19"/>
+      <c r="H90" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:8">
-      <c r="A91" s="21">
+      <c r="A91" s="20">
         <v>46240</v>
       </c>
-      <c r="B91" s="17">
-        <v>0</v>
-      </c>
-      <c r="C91" s="20"/>
-      <c r="D91" s="17">
-        <v>0</v>
-      </c>
-      <c r="E91" s="20"/>
-      <c r="F91" s="17">
-        <v>0</v>
-      </c>
-      <c r="G91" s="20"/>
-      <c r="H91" s="17">
+      <c r="B91" s="16">
+        <v>0</v>
+      </c>
+      <c r="C91" s="19"/>
+      <c r="D91" s="16">
+        <v>0</v>
+      </c>
+      <c r="E91" s="19"/>
+      <c r="F91" s="16">
+        <v>0</v>
+      </c>
+      <c r="G91" s="19"/>
+      <c r="H91" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:8">
-      <c r="A92" s="21">
+      <c r="A92" s="20">
         <v>46241</v>
       </c>
-      <c r="B92" s="17">
+      <c r="B92" s="16">
         <v>100</v>
       </c>
-      <c r="C92" s="20"/>
-      <c r="D92" s="17">
+      <c r="C92" s="19"/>
+      <c r="D92" s="16">
         <v>90</v>
       </c>
-      <c r="E92" s="20"/>
-      <c r="F92" s="17">
+      <c r="E92" s="19"/>
+      <c r="F92" s="16">
         <v>100</v>
       </c>
-      <c r="G92" s="20"/>
-      <c r="H92" s="17">
+      <c r="G92" s="19"/>
+      <c r="H92" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="93" spans="1:8">
-      <c r="A93" s="21">
+      <c r="A93" s="20">
         <v>46244</v>
       </c>
-      <c r="B93" s="17">
-        <v>0</v>
-      </c>
-      <c r="C93" s="20"/>
-      <c r="D93" s="17">
-        <v>0</v>
-      </c>
-      <c r="E93" s="20"/>
-      <c r="F93" s="17">
-        <v>0</v>
-      </c>
-      <c r="G93" s="20"/>
-      <c r="H93" s="17">
+      <c r="B93" s="16">
+        <v>0</v>
+      </c>
+      <c r="C93" s="19"/>
+      <c r="D93" s="16">
+        <v>0</v>
+      </c>
+      <c r="E93" s="19"/>
+      <c r="F93" s="16">
+        <v>0</v>
+      </c>
+      <c r="G93" s="19"/>
+      <c r="H93" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:8">
-      <c r="A94" s="21">
+      <c r="A94" s="20">
         <v>46245</v>
       </c>
-      <c r="B94" s="17">
+      <c r="B94" s="16">
         <v>100</v>
       </c>
-      <c r="D94" s="17">
+      <c r="D94" s="16">
         <v>90</v>
       </c>
-      <c r="F94" s="17">
+      <c r="F94" s="16">
         <v>100</v>
       </c>
-      <c r="H94" s="17">
+      <c r="H94" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:8">
-      <c r="A95" s="21">
+      <c r="A95" s="20">
         <v>46246</v>
       </c>
-      <c r="B95" s="17">
+      <c r="B95" s="16">
         <v>2710.8615399999999</v>
       </c>
-      <c r="C95" s="20"/>
-      <c r="D95" s="17">
+      <c r="C95" s="19"/>
+      <c r="D95" s="16">
         <v>90</v>
       </c>
-      <c r="E95" s="20"/>
-      <c r="F95" s="17">
+      <c r="E95" s="19"/>
+      <c r="F95" s="16">
         <v>160</v>
       </c>
-      <c r="G95" s="20"/>
-      <c r="H95" s="17">
+      <c r="G95" s="19"/>
+      <c r="H95" s="16">
         <v>143.79</v>
       </c>
     </row>
     <row r="96" spans="1:8">
-      <c r="A96" s="21">
+      <c r="A96" s="20">
         <v>46247</v>
       </c>
-      <c r="B96" s="17">
+      <c r="B96" s="16">
         <v>480</v>
       </c>
-      <c r="C96" s="20"/>
-      <c r="D96" s="17">
+      <c r="C96" s="19"/>
+      <c r="D96" s="16">
         <v>90</v>
       </c>
-      <c r="E96" s="20"/>
-      <c r="F96" s="17">
+      <c r="E96" s="19"/>
+      <c r="F96" s="16">
         <v>100</v>
       </c>
-      <c r="G96" s="20"/>
-      <c r="H96" s="17">
+      <c r="G96" s="19"/>
+      <c r="H96" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="97" spans="1:8">
-      <c r="A97" s="21">
+      <c r="A97" s="20">
         <v>46248</v>
       </c>
-      <c r="B97" s="17">
+      <c r="B97" s="16">
         <v>4514.1648089999999</v>
       </c>
-      <c r="C97" s="20"/>
-      <c r="D97" s="17">
+      <c r="C97" s="19"/>
+      <c r="D97" s="16">
         <v>70</v>
       </c>
-      <c r="E97" s="20"/>
-      <c r="F97" s="17">
+      <c r="E97" s="19"/>
+      <c r="F97" s="16">
         <v>70</v>
       </c>
-      <c r="G97" s="20"/>
-      <c r="H97" s="17">
+      <c r="G97" s="19"/>
+      <c r="H97" s="16">
         <v>70</v>
       </c>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="21">
+      <c r="A98" s="20">
         <v>46251</v>
       </c>
-      <c r="B98" s="17">
-        <v>0</v>
-      </c>
-      <c r="C98" s="20"/>
-      <c r="D98" s="17">
-        <v>0</v>
-      </c>
-      <c r="E98" s="20"/>
-      <c r="F98" s="17">
-        <v>0</v>
-      </c>
-      <c r="G98" s="20"/>
-      <c r="H98" s="17">
+      <c r="B98" s="16">
+        <v>0</v>
+      </c>
+      <c r="C98" s="19"/>
+      <c r="D98" s="16">
+        <v>0</v>
+      </c>
+      <c r="E98" s="19"/>
+      <c r="F98" s="16">
+        <v>0</v>
+      </c>
+      <c r="G98" s="19"/>
+      <c r="H98" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:8">
-      <c r="A99" s="21">
+      <c r="A99" s="20">
         <v>46252</v>
       </c>
-      <c r="B99" s="17">
+      <c r="B99" s="16">
         <v>120</v>
       </c>
-      <c r="C99" s="20"/>
-      <c r="D99" s="17">
+      <c r="C99" s="19"/>
+      <c r="D99" s="16">
         <v>90</v>
       </c>
-      <c r="E99" s="20"/>
-      <c r="F99" s="17">
+      <c r="E99" s="19"/>
+      <c r="F99" s="16">
         <v>100</v>
       </c>
-      <c r="G99" s="20"/>
-      <c r="H99" s="17">
+      <c r="G99" s="19"/>
+      <c r="H99" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:8">
-      <c r="A100" s="21">
+      <c r="A100" s="20">
         <v>46253</v>
       </c>
-      <c r="B100" s="17">
-        <v>0</v>
-      </c>
-      <c r="C100" s="20"/>
-      <c r="D100" s="17">
-        <v>0</v>
-      </c>
-      <c r="E100" s="20"/>
-      <c r="F100" s="17">
-        <v>0</v>
-      </c>
-      <c r="G100" s="20"/>
-      <c r="H100" s="17">
+      <c r="B100" s="16">
+        <v>0</v>
+      </c>
+      <c r="C100" s="19"/>
+      <c r="D100" s="16">
+        <v>0</v>
+      </c>
+      <c r="E100" s="19"/>
+      <c r="F100" s="16">
+        <v>0</v>
+      </c>
+      <c r="G100" s="19"/>
+      <c r="H100" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:8">
-      <c r="A101" s="21">
+      <c r="A101" s="20">
         <v>46254</v>
       </c>
-      <c r="B101" s="17">
-        <v>0</v>
-      </c>
-      <c r="C101" s="20"/>
-      <c r="D101" s="17">
-        <v>0</v>
-      </c>
-      <c r="E101" s="20"/>
-      <c r="F101" s="17">
-        <v>0</v>
-      </c>
-      <c r="G101" s="20"/>
-      <c r="H101" s="17">
+      <c r="B101" s="16">
+        <v>0</v>
+      </c>
+      <c r="C101" s="19"/>
+      <c r="D101" s="16">
+        <v>0</v>
+      </c>
+      <c r="E101" s="19"/>
+      <c r="F101" s="16">
+        <v>0</v>
+      </c>
+      <c r="G101" s="19"/>
+      <c r="H101" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:8">
-      <c r="A102" s="21">
+      <c r="A102" s="20">
         <v>46255</v>
       </c>
-      <c r="B102" s="17">
-        <v>0</v>
-      </c>
-      <c r="C102" s="20"/>
-      <c r="D102" s="17">
-        <v>0</v>
-      </c>
-      <c r="E102" s="20"/>
-      <c r="F102" s="17">
-        <v>0</v>
-      </c>
-      <c r="G102" s="20"/>
-      <c r="H102" s="17">
+      <c r="B102" s="16">
+        <v>0</v>
+      </c>
+      <c r="C102" s="19"/>
+      <c r="D102" s="16">
+        <v>0</v>
+      </c>
+      <c r="E102" s="19"/>
+      <c r="F102" s="16">
+        <v>0</v>
+      </c>
+      <c r="G102" s="19"/>
+      <c r="H102" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:8">
-      <c r="A103" s="21">
+      <c r="A103" s="20">
         <v>46256</v>
       </c>
-      <c r="B103" s="17">
+      <c r="B103" s="16">
         <v>60</v>
       </c>
-      <c r="C103" s="20"/>
-      <c r="D103" s="17">
+      <c r="C103" s="19"/>
+      <c r="D103" s="16">
         <v>90</v>
       </c>
-      <c r="E103" s="20"/>
-      <c r="F103" s="17">
+      <c r="E103" s="19"/>
+      <c r="F103" s="16">
         <v>100</v>
       </c>
-      <c r="G103" s="20"/>
-      <c r="H103" s="17">
+      <c r="G103" s="19"/>
+      <c r="H103" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:8">
-      <c r="A104" s="21">
+      <c r="A104" s="20">
         <v>46259</v>
       </c>
-      <c r="B104" s="17">
+      <c r="B104" s="16">
         <v>53</v>
       </c>
-      <c r="C104" s="20"/>
-      <c r="D104" s="17">
+      <c r="C104" s="19"/>
+      <c r="D104" s="16">
         <v>250</v>
       </c>
-      <c r="E104" s="20"/>
-      <c r="F104" s="17">
+      <c r="E104" s="19"/>
+      <c r="F104" s="16">
         <v>250</v>
       </c>
-      <c r="G104" s="20"/>
-      <c r="H104" s="17">
+      <c r="G104" s="19"/>
+      <c r="H104" s="16">
         <v>250</v>
       </c>
     </row>
     <row r="105" spans="1:8">
-      <c r="A105" s="21">
+      <c r="A105" s="20">
         <v>46260</v>
       </c>
-      <c r="B105" s="17">
+      <c r="B105" s="16">
         <v>266</v>
       </c>
-      <c r="C105" s="20"/>
-      <c r="D105" s="17">
+      <c r="C105" s="19"/>
+      <c r="D105" s="16">
         <v>120</v>
       </c>
-      <c r="E105" s="20"/>
-      <c r="F105" s="17">
+      <c r="E105" s="19"/>
+      <c r="F105" s="16">
         <v>250</v>
       </c>
-      <c r="G105" s="20"/>
-      <c r="H105" s="17">
+      <c r="G105" s="19"/>
+      <c r="H105" s="16">
         <v>183.16</v>
       </c>
     </row>
     <row r="106" spans="1:8">
-      <c r="A106" s="21">
+      <c r="A106" s="20">
         <v>46261</v>
       </c>
-      <c r="B106" s="17">
+      <c r="B106" s="16">
         <v>175</v>
       </c>
-      <c r="C106" s="20"/>
-      <c r="D106" s="17">
+      <c r="C106" s="19"/>
+      <c r="D106" s="16">
         <v>90</v>
       </c>
-      <c r="E106" s="20"/>
-      <c r="F106" s="17">
+      <c r="E106" s="19"/>
+      <c r="F106" s="16">
         <v>100</v>
       </c>
-      <c r="G106" s="20"/>
-      <c r="H106" s="17">
+      <c r="G106" s="19"/>
+      <c r="H106" s="16">
         <v>96</v>
       </c>
     </row>
     <row r="107" spans="1:8">
-      <c r="A107" s="21">
+      <c r="A107" s="20">
         <v>46262</v>
       </c>
-      <c r="B107" s="17">
+      <c r="B107" s="16">
         <v>800</v>
       </c>
-      <c r="C107" s="20"/>
-      <c r="D107" s="17">
+      <c r="C107" s="19"/>
+      <c r="D107" s="16">
         <v>50</v>
       </c>
-      <c r="E107" s="20"/>
-      <c r="F107" s="17">
+      <c r="E107" s="19"/>
+      <c r="F107" s="16">
         <v>500</v>
       </c>
-      <c r="G107" s="20"/>
-      <c r="H107" s="17">
+      <c r="G107" s="19"/>
+      <c r="H107" s="16">
         <v>275</v>
       </c>
     </row>
     <row r="108" spans="1:8">
-      <c r="A108" s="21">
+      <c r="A108" s="20">
         <v>46265</v>
       </c>
-      <c r="B108" s="17">
+      <c r="B108" s="16">
         <v>60</v>
       </c>
-      <c r="C108" s="20"/>
-      <c r="D108" s="17">
+      <c r="C108" s="19"/>
+      <c r="D108" s="16">
         <v>40</v>
       </c>
-      <c r="E108" s="20"/>
-      <c r="F108" s="17">
+      <c r="E108" s="19"/>
+      <c r="F108" s="16">
         <v>40</v>
       </c>
-      <c r="G108" s="20"/>
-      <c r="H108" s="17">
+      <c r="G108" s="19"/>
+      <c r="H108" s="16">
         <v>40</v>
       </c>
     </row>
     <row r="109" spans="1:8">
-      <c r="A109" s="21">
+      <c r="A109" s="20">
         <v>46266</v>
       </c>
-      <c r="B109" s="17">
-        <v>0</v>
-      </c>
-      <c r="C109" s="20"/>
-      <c r="D109" s="17">
-        <v>0</v>
-      </c>
-      <c r="E109" s="20"/>
-      <c r="F109" s="17">
-        <v>0</v>
-      </c>
-      <c r="G109" s="20"/>
-      <c r="H109" s="17">
+      <c r="B109" s="16">
+        <v>0</v>
+      </c>
+      <c r="C109" s="19"/>
+      <c r="D109" s="16">
+        <v>0</v>
+      </c>
+      <c r="E109" s="19"/>
+      <c r="F109" s="16">
+        <v>0</v>
+      </c>
+      <c r="G109" s="19"/>
+      <c r="H109" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:8">
-      <c r="A110" s="21">
+      <c r="A110" s="20">
         <v>46267</v>
       </c>
-      <c r="B110" s="17">
+      <c r="B110" s="16">
         <v>700</v>
       </c>
-      <c r="C110" s="20"/>
-      <c r="D110" s="17">
+      <c r="C110" s="19"/>
+      <c r="D110" s="16">
         <v>90</v>
       </c>
-      <c r="E110" s="20"/>
-      <c r="F110" s="17">
+      <c r="E110" s="19"/>
+      <c r="F110" s="16">
         <v>100</v>
       </c>
-      <c r="G110" s="20"/>
-      <c r="H110" s="17">
+      <c r="G110" s="19"/>
+      <c r="H110" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="111" spans="1:8">
-      <c r="A111" s="21">
+      <c r="A111" s="20">
         <v>46268</v>
       </c>
-      <c r="B111" s="17">
+      <c r="B111" s="16">
         <v>420</v>
       </c>
-      <c r="C111" s="20"/>
-      <c r="D111" s="17">
+      <c r="C111" s="19"/>
+      <c r="D111" s="16">
         <v>80</v>
       </c>
-      <c r="E111" s="20"/>
-      <c r="F111" s="17">
+      <c r="E111" s="19"/>
+      <c r="F111" s="16">
         <v>100</v>
       </c>
-      <c r="G111" s="20"/>
-      <c r="H111" s="17">
+      <c r="G111" s="19"/>
+      <c r="H111" s="16">
         <v>91.19</v>
       </c>
     </row>
     <row r="112" spans="1:8">
-      <c r="A112" s="21">
+      <c r="A112" s="20">
         <v>46269</v>
       </c>
-      <c r="B112" s="17">
+      <c r="B112" s="16">
         <v>604</v>
       </c>
-      <c r="C112" s="20"/>
-      <c r="D112" s="17">
+      <c r="C112" s="19"/>
+      <c r="D112" s="16">
         <v>20</v>
       </c>
-      <c r="E112" s="20"/>
-      <c r="F112" s="17">
+      <c r="E112" s="19"/>
+      <c r="F112" s="16">
         <v>30</v>
       </c>
-      <c r="G112" s="20"/>
-      <c r="H112" s="17">
+      <c r="G112" s="19"/>
+      <c r="H112" s="16">
         <v>26.75</v>
       </c>
     </row>
     <row r="113" spans="1:8">
-      <c r="A113" s="21">
+      <c r="A113" s="20">
         <v>46272</v>
       </c>
-      <c r="B113" s="17">
+      <c r="B113" s="16">
         <v>1389.4680000000001</v>
       </c>
-      <c r="C113" s="20"/>
-      <c r="D113" s="17">
+      <c r="C113" s="19"/>
+      <c r="D113" s="16">
         <v>90</v>
       </c>
-      <c r="E113" s="20"/>
-      <c r="F113" s="17">
+      <c r="E113" s="19"/>
+      <c r="F113" s="16">
         <v>300</v>
       </c>
-      <c r="G113" s="20"/>
-      <c r="H113" s="17">
+      <c r="G113" s="19"/>
+      <c r="H113" s="16">
         <v>171.07</v>
       </c>
     </row>
     <row r="114" spans="1:8">
-      <c r="A114" s="21">
+      <c r="A114" s="20">
         <v>46273</v>
       </c>
-      <c r="B114" s="17">
+      <c r="B114" s="16">
         <v>1000</v>
       </c>
-      <c r="C114" s="20"/>
-      <c r="D114" s="17">
+      <c r="C114" s="19"/>
+      <c r="D114" s="16">
         <v>90</v>
       </c>
-      <c r="E114" s="20"/>
-      <c r="F114" s="17">
+      <c r="E114" s="19"/>
+      <c r="F114" s="16">
         <v>100</v>
       </c>
-      <c r="G114" s="20"/>
-      <c r="H114" s="17">
+      <c r="G114" s="19"/>
+      <c r="H114" s="16">
         <v>95</v>
       </c>
     </row>
     <row r="115" spans="1:8">
-      <c r="A115" s="21">
+      <c r="A115" s="20">
         <v>47370</v>
       </c>
-      <c r="B115" s="17">
+      <c r="B115" s="16">
         <v>386</v>
       </c>
-      <c r="C115" s="20"/>
-      <c r="D115" s="17">
+      <c r="C115" s="19"/>
+      <c r="D115" s="16">
         <v>60</v>
       </c>
-      <c r="E115" s="20"/>
-      <c r="F115" s="17">
+      <c r="E115" s="19"/>
+      <c r="F115" s="16">
         <v>100</v>
       </c>
-      <c r="G115" s="20"/>
-      <c r="H115" s="17">
+      <c r="G115" s="19"/>
+      <c r="H115" s="16">
         <v>80</v>
       </c>
     </row>
     <row r="116" spans="1:8">
-      <c r="A116" s="21">
+      <c r="A116" s="20">
         <v>46275</v>
       </c>
-      <c r="B116" s="17">
+      <c r="B116" s="16">
         <v>300</v>
       </c>
-      <c r="C116" s="20"/>
-      <c r="D116" s="17">
+      <c r="C116" s="19"/>
+      <c r="D116" s="16">
         <v>60</v>
       </c>
-      <c r="E116" s="20"/>
-      <c r="F116" s="17">
+      <c r="E116" s="19"/>
+      <c r="F116" s="16">
         <v>100</v>
       </c>
-      <c r="G116" s="20"/>
-      <c r="H116" s="17">
+      <c r="G116" s="19"/>
+      <c r="H116" s="16">
         <v>80</v>
       </c>
     </row>
     <row r="117" spans="1:8">
-      <c r="A117" s="21">
+      <c r="A117" s="20">
         <v>46276</v>
       </c>
-      <c r="B117" s="17">
+      <c r="B117" s="16">
         <v>108</v>
       </c>
-      <c r="C117" s="20"/>
-      <c r="D117" s="17">
+      <c r="C117" s="19"/>
+      <c r="D117" s="16">
         <v>60</v>
       </c>
-      <c r="E117" s="20"/>
-      <c r="F117" s="17">
+      <c r="E117" s="19"/>
+      <c r="F117" s="16">
         <v>100</v>
       </c>
-      <c r="G117" s="20"/>
-      <c r="H117" s="17">
+      <c r="G117" s="19"/>
+      <c r="H117" s="16">
         <v>80</v>
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="21">
+      <c r="A118" s="20">
         <v>46280</v>
       </c>
-      <c r="B118" s="17">
+      <c r="B118" s="16">
         <v>2571.288</v>
       </c>
-      <c r="C118" s="20"/>
-      <c r="D118" s="17">
+      <c r="C118" s="19"/>
+      <c r="D118" s="16">
         <v>100</v>
       </c>
-      <c r="E118" s="20"/>
-      <c r="F118" s="17">
+      <c r="E118" s="19"/>
+      <c r="F118" s="16">
         <v>150</v>
       </c>
-      <c r="G118" s="20"/>
-      <c r="H118" s="17">
+      <c r="G118" s="19"/>
+      <c r="H118" s="16">
         <v>110.92</v>
       </c>
     </row>
     <row r="119" spans="1:8">
-      <c r="A119" s="21">
+      <c r="A119" s="20">
         <v>46281</v>
       </c>
-      <c r="B119" s="17">
+      <c r="B119" s="16">
         <v>10800</v>
       </c>
-      <c r="C119" s="20"/>
-      <c r="D119" s="17">
+      <c r="C119" s="19"/>
+      <c r="D119" s="16">
         <v>200</v>
       </c>
-      <c r="E119" s="20"/>
-      <c r="F119" s="17">
+      <c r="E119" s="19"/>
+      <c r="F119" s="16">
         <v>200</v>
       </c>
-      <c r="G119" s="20"/>
-      <c r="H119" s="17">
+      <c r="G119" s="19"/>
+      <c r="H119" s="16">
         <v>200</v>
       </c>
     </row>
     <row r="120" spans="1:8">
-      <c r="A120" s="21">
+      <c r="A120" s="20">
         <v>46282</v>
       </c>
-      <c r="B120" s="17">
+      <c r="B120" s="16">
         <v>3168.1590000000001</v>
       </c>
-      <c r="C120" s="20"/>
-      <c r="D120" s="17">
+      <c r="C120" s="19"/>
+      <c r="D120" s="16">
         <v>90</v>
       </c>
-      <c r="E120" s="20"/>
-      <c r="F120" s="17">
+      <c r="E120" s="19"/>
+      <c r="F120" s="16">
         <v>250</v>
       </c>
-      <c r="G120" s="20"/>
-      <c r="H120" s="17">
+      <c r="G120" s="19"/>
+      <c r="H120" s="16">
         <v>247.55</v>
       </c>
     </row>
     <row r="121" spans="1:8">
-      <c r="A121" s="21">
+      <c r="A121" s="20">
         <v>46283</v>
       </c>
-      <c r="B121" s="17">
+      <c r="B121" s="16">
         <v>820</v>
       </c>
-      <c r="C121" s="20"/>
-      <c r="D121" s="17">
+      <c r="C121" s="19"/>
+      <c r="D121" s="16">
         <v>25</v>
       </c>
-      <c r="E121" s="20"/>
-      <c r="F121" s="17">
+      <c r="E121" s="19"/>
+      <c r="F121" s="16">
         <v>30</v>
       </c>
-      <c r="G121" s="20"/>
-      <c r="H121" s="17">
+      <c r="G121" s="19"/>
+      <c r="H121" s="16">
         <v>27.5</v>
       </c>
     </row>
     <row r="122" spans="1:8">
-      <c r="A122" s="21">
+      <c r="A122" s="20">
         <v>46286</v>
       </c>
-      <c r="B122" s="17">
+      <c r="B122" s="16">
         <v>20888.307000000001</v>
       </c>
-      <c r="C122" s="20"/>
-      <c r="D122" s="17">
+      <c r="C122" s="19"/>
+      <c r="D122" s="16">
         <v>1</v>
       </c>
-      <c r="E122" s="20"/>
-      <c r="F122" s="17">
+      <c r="E122" s="19"/>
+      <c r="F122" s="16">
         <v>100</v>
       </c>
-      <c r="G122" s="20"/>
-      <c r="H122" s="17">
+      <c r="G122" s="19"/>
+      <c r="H122" s="16">
         <v>23.39</v>
       </c>
     </row>
     <row r="123" spans="1:8">
-      <c r="A123" s="21">
+      <c r="A123" s="20">
         <v>46287</v>
       </c>
-      <c r="B123" s="17">
+      <c r="B123" s="16">
         <v>17245.765071999998</v>
       </c>
-      <c r="C123" s="20"/>
-      <c r="D123" s="17">
+      <c r="C123" s="19"/>
+      <c r="D123" s="16">
         <v>1.5</v>
       </c>
-      <c r="E123" s="20"/>
-      <c r="F123" s="17">
+      <c r="E123" s="19"/>
+      <c r="F123" s="16">
         <v>100</v>
       </c>
-      <c r="G123" s="20"/>
-      <c r="H123" s="17">
+      <c r="G123" s="19"/>
+      <c r="H123" s="16">
         <v>4.63</v>
       </c>
     </row>
     <row r="124" spans="1:8">
-      <c r="A124" s="21">
+      <c r="A124" s="20">
         <v>46288</v>
       </c>
-      <c r="B124" s="17">
+      <c r="B124" s="16">
         <v>8934.4187999999995</v>
       </c>
-      <c r="C124" s="20"/>
-      <c r="D124" s="17">
+      <c r="C124" s="19"/>
+      <c r="D124" s="16">
         <v>0.95</v>
       </c>
-      <c r="E124" s="20"/>
-      <c r="F124" s="17">
+      <c r="E124" s="19"/>
+      <c r="F124" s="16">
         <v>50</v>
       </c>
-      <c r="G124" s="20"/>
-      <c r="H124" s="17">
+      <c r="G124" s="19"/>
+      <c r="H124" s="16">
         <v>4.1399999999999997</v>
       </c>
     </row>
     <row r="125" spans="1:8">
-      <c r="A125" s="21">
+      <c r="A125" s="20">
         <v>46289</v>
       </c>
-      <c r="B125" s="17">
+      <c r="B125" s="16">
         <v>11795.6893</v>
       </c>
-      <c r="C125" s="20"/>
-      <c r="D125" s="17">
+      <c r="C125" s="19"/>
+      <c r="D125" s="16">
         <v>1</v>
       </c>
-      <c r="E125" s="20"/>
-      <c r="F125" s="17">
+      <c r="E125" s="19"/>
+      <c r="F125" s="16">
         <v>50</v>
       </c>
-      <c r="G125" s="20"/>
-      <c r="H125" s="17">
+      <c r="G125" s="19"/>
+      <c r="H125" s="16">
         <v>5.18</v>
       </c>
     </row>
     <row r="126" spans="1:8">
-      <c r="A126" s="21">
+      <c r="A126" s="20">
         <v>46290</v>
       </c>
       <c r="B126">
         <v>624.74</v>
       </c>
-      <c r="D126" s="17">
+      <c r="D126" s="16">
         <v>0.33</v>
       </c>
-      <c r="F126" s="17">
+      <c r="F126" s="16">
         <v>0.33</v>
       </c>
-      <c r="H126" s="17">
+      <c r="H126" s="16">
         <v>0.33</v>
       </c>
     </row>
     <row r="127" spans="1:8">
-      <c r="A127" s="21">
+      <c r="A127" s="20">
         <v>46293</v>
       </c>
       <c r="B127" s="7">
         <v>0</v>
       </c>
-      <c r="C127" s="24"/>
-      <c r="D127" s="17">
-        <v>0</v>
-      </c>
-      <c r="E127" s="24"/>
-      <c r="F127" s="17">
-        <v>0</v>
-      </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="17">
+      <c r="C127" s="23"/>
+      <c r="D127" s="16">
+        <v>0</v>
+      </c>
+      <c r="E127" s="23"/>
+      <c r="F127" s="16">
+        <v>0</v>
+      </c>
+      <c r="G127" s="23"/>
+      <c r="H127" s="16">
         <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:8">
-      <c r="A128" s="21">
+      <c r="A128" s="20">
         <v>46294</v>
       </c>
-      <c r="B128" s="17">
+      <c r="B128" s="16">
         <v>48909.906707000002</v>
       </c>
-      <c r="C128" s="20"/>
-      <c r="D128" s="17">
+      <c r="C128" s="19"/>
+      <c r="D128" s="16">
         <v>5</v>
       </c>
-      <c r="E128" s="20"/>
-      <c r="F128" s="17">
+      <c r="E128" s="19"/>
+      <c r="F128" s="16">
         <v>20</v>
       </c>
-      <c r="G128" s="20"/>
-      <c r="H128" s="17">
+      <c r="G128" s="19"/>
+      <c r="H128" s="16">
         <v>8.58</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="20">
+        <v>47391</v>
+      </c>
+      <c r="B129" s="16">
+        <v>25151.44958</v>
+      </c>
+      <c r="C129" s="19"/>
+      <c r="D129" s="16">
+        <v>20</v>
+      </c>
+      <c r="E129" s="19"/>
+      <c r="F129" s="16">
+        <v>60</v>
+      </c>
+      <c r="G129" s="19"/>
+      <c r="H129" s="16">
+        <v>58.03</v>
       </c>
     </row>
   </sheetData>
@@ -5484,12 +5505,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.75" customWidth="1"/>
-    <col min="3" max="3" width="14" style="13" customWidth="1"/>
+    <col min="3" max="3" width="14" style="12" customWidth="1"/>
     <col min="4" max="4" width="17.375" customWidth="1"/>
     <col min="5" max="5" width="24.625" bestFit="1" customWidth="1"/>
   </cols>
@@ -5501,7 +5522,7 @@
       <c r="B1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D1" t="s">
@@ -5511,54 +5532,54 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="25">
-        <v>46294</v>
-      </c>
-      <c r="B2" s="24">
-        <v>20524.128823380001</v>
-      </c>
-      <c r="C2" s="30">
+    <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
+      <c r="A2" s="24">
+        <v>46295</v>
+      </c>
+      <c r="B2" s="23">
+        <v>201687.34548826001</v>
+      </c>
+      <c r="C2" s="29">
         <f>+(B2-B3)/B3</f>
-        <v>-0.85681185394119452</v>
-      </c>
-      <c r="D2" s="24" t="s">
+        <v>8.8268407504102413</v>
+      </c>
+      <c r="D2" s="23" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="5">
         <v>42155.425069182624</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="25">
-        <v>46293</v>
-      </c>
-      <c r="B3" s="24">
-        <v>143336.78721526999</v>
-      </c>
-      <c r="C3" s="30">
+    <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
+      <c r="A3" s="24">
+        <v>46294</v>
+      </c>
+      <c r="B3" s="23">
+        <v>20524.128823380001</v>
+      </c>
+      <c r="C3" s="29">
         <f>+(B3-B4)/B4</f>
-        <v>-0.49898704513189668</v>
-      </c>
-      <c r="D3" s="24" t="s">
+        <v>-0.85681185394119452</v>
+      </c>
+      <c r="D3" s="23" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="5">
         <v>68497.757342013356</v>
       </c>
     </row>
-    <row r="4" spans="1:5" s="24" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="25">
-        <v>46290</v>
-      </c>
-      <c r="B4" s="24">
-        <v>286093.97386342002</v>
-      </c>
-      <c r="C4" s="30">
+    <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
+      <c r="A4" s="24">
+        <v>46293</v>
+      </c>
+      <c r="B4" s="23">
+        <v>143336.78721526999</v>
+      </c>
+      <c r="C4" s="29">
         <f>+(B4-B5)/B5</f>
-        <v>0.55858664283872839</v>
-      </c>
-      <c r="D4" s="24" t="s">
+        <v>-0.49898704513189668</v>
+      </c>
+      <c r="D4" s="23" t="s">
         <v>10</v>
       </c>
       <c r="E4" s="6">
@@ -5566,17 +5587,17 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A5" s="25">
-        <v>46289</v>
-      </c>
-      <c r="B5" s="24">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C5" s="30">
-        <f t="shared" ref="C5:C74" si="0">+(B5-B6)/B6</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
-      <c r="D5" s="24" t="s">
+      <c r="A5" s="24">
+        <v>46290</v>
+      </c>
+      <c r="B5" s="23">
+        <v>286093.97386342002</v>
+      </c>
+      <c r="C5" s="29">
+        <f>+(B5-B6)/B6</f>
+        <v>0.55858664283872839</v>
+      </c>
+      <c r="D5" s="23" t="s">
         <v>29</v>
       </c>
       <c r="E5" s="6">
@@ -5584,1419 +5605,1432 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="25">
+      <c r="A6" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C6" s="29">
+        <f t="shared" ref="C6:C75" si="0">+(B6-B7)/B7</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="6">
+        <v>24565.759999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24">
         <v>46288</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B7" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C7" s="29">
         <f t="shared" si="0"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="D6" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6">
-        <v>24565.759999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="25">
+      <c r="D7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24">
         <v>46287</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B8" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C8" s="29">
         <f t="shared" si="0"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="D7" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="25">
+      <c r="D8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="33">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24">
         <v>46286</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B9" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="34">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="25">
+      <c r="D9" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24">
         <v>46283</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B10" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="D9" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="25">
+      <c r="D10" s="23"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46282</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B11" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="35"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="25">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46281</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B12" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>54.85948274687906</v>
       </c>
-      <c r="E11" s="35"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="25">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46280</v>
       </c>
-      <c r="B12" s="24">
+      <c r="B13" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="25">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46276</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B14" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>-0.67806849277578529</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="25">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46275</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B15" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C15" s="29">
         <f t="shared" si="0"/>
         <v>18.560573043109468</v>
       </c>
-      <c r="E14" s="37"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="25">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46274</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B16" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C16" s="29">
         <f t="shared" si="0"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="25">
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46273</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B17" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C17" s="29">
         <f t="shared" si="0"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="25">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46272</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B18" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C18" s="29">
         <f t="shared" si="0"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="25">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46269</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B19" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C19" s="29">
         <f t="shared" si="0"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="25">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46268</v>
       </c>
-      <c r="B19" s="24">
+      <c r="B20" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C20" s="29">
         <f t="shared" si="0"/>
         <v>80.163058476193896</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="25">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46267</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B21" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C21" s="29">
         <f t="shared" si="0"/>
         <v>-0.77463732472189939</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="25">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46266</v>
       </c>
-      <c r="B21" s="24">
+      <c r="B22" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C22" s="29">
         <f t="shared" si="0"/>
         <v>-0.99727371031195</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="25">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46265</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B23" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C23" s="29">
         <f t="shared" si="0"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="25">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46262</v>
       </c>
-      <c r="B23" s="24">
+      <c r="B24" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C24" s="29">
         <f t="shared" si="0"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="25">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46261</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B25" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C25" s="29">
         <f t="shared" si="0"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="25">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46260</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B26" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C26" s="29">
         <f t="shared" si="0"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="25">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46259</v>
       </c>
-      <c r="B26" s="24">
+      <c r="B27" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C27" s="29">
         <f t="shared" si="0"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="25">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46256</v>
       </c>
-      <c r="B27" s="24">
+      <c r="B28" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C28" s="29">
         <f t="shared" si="0"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="25">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46255</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B29" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C28" s="30">
+      <c r="C29" s="29">
         <f t="shared" si="0"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="25">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46254</v>
       </c>
-      <c r="B29" s="24">
+      <c r="B30" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C30" s="29">
         <f t="shared" si="0"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="25">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46253</v>
       </c>
-      <c r="B30" s="24">
+      <c r="B31" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C31" s="29">
         <f t="shared" si="0"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="25">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46252</v>
       </c>
-      <c r="B31" s="24">
+      <c r="B32" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C32" s="29">
         <f t="shared" si="0"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="25">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46251</v>
       </c>
-      <c r="B32" s="24">
+      <c r="B33" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C33" s="29">
         <f t="shared" si="0"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="25">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46248</v>
       </c>
-      <c r="B33" s="24">
+      <c r="B34" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C34" s="29">
         <f t="shared" si="0"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="25">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46247</v>
       </c>
-      <c r="B34" s="24">
+      <c r="B35" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C35" s="29">
         <f t="shared" si="0"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="25">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46246</v>
       </c>
-      <c r="B35" s="24">
+      <c r="B36" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C36" s="29">
         <f t="shared" si="0"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="25">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46245</v>
       </c>
-      <c r="B36" s="24">
+      <c r="B37" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C37" s="29">
         <f t="shared" si="0"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="25">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46244</v>
       </c>
-      <c r="B37" s="24">
+      <c r="B38" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C38" s="29">
         <f t="shared" si="0"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="25">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46241</v>
       </c>
-      <c r="B38" s="24">
+      <c r="B39" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C39" s="29">
         <f t="shared" si="0"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="25">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46240</v>
       </c>
-      <c r="B39" s="24">
+      <c r="B40" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C40" s="29">
         <f t="shared" si="0"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="25">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46239</v>
       </c>
-      <c r="B40" s="24">
+      <c r="B41" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C40" s="30">
+      <c r="C41" s="29">
         <f t="shared" si="0"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="25">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46238</v>
       </c>
-      <c r="B41" s="24">
+      <c r="B42" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C42" s="29">
         <f t="shared" si="0"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="25">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46237</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B43" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C43" s="29">
         <f t="shared" si="0"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="25">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46234</v>
       </c>
-      <c r="B43" s="24">
+      <c r="B44" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C44" s="29">
         <f t="shared" si="0"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="25">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46233</v>
       </c>
-      <c r="B44">
+      <c r="B45">
         <v>466.33578662999997</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C45" s="29">
         <f t="shared" si="0"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="25">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46232</v>
       </c>
-      <c r="B45" s="24">
+      <c r="B46" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C45" s="30">
+      <c r="C46" s="29">
         <f t="shared" si="0"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="25">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46231</v>
       </c>
-      <c r="B46" s="24">
+      <c r="B47" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C46" s="30">
+      <c r="C47" s="29">
         <f t="shared" si="0"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="25">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46108</v>
       </c>
-      <c r="B47" s="24">
+      <c r="B48" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C47" s="30">
+      <c r="C48" s="29">
         <f t="shared" si="0"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="25">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46226</v>
       </c>
-      <c r="B48" s="24">
+      <c r="B49" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C48" s="30">
+      <c r="C49" s="29">
         <f t="shared" si="0"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="25">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46225</v>
       </c>
-      <c r="B49" s="24">
+      <c r="B50" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C49" s="30">
+      <c r="C50" s="29">
         <f t="shared" si="0"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="25">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46224</v>
       </c>
-      <c r="B50" s="24">
+      <c r="B51" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C50" s="30">
+      <c r="C51" s="29">
         <f t="shared" si="0"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="25">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46220</v>
       </c>
-      <c r="B51" s="24">
+      <c r="B52" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C51" s="30">
+      <c r="C52" s="29">
         <f t="shared" si="0"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="25">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46219</v>
       </c>
-      <c r="B52" s="24">
+      <c r="B53" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C52" s="30">
+      <c r="C53" s="29">
         <f t="shared" si="0"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="25">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46218</v>
       </c>
-      <c r="B53" s="24">
+      <c r="B54" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C53" s="30">
+      <c r="C54" s="29">
         <f t="shared" si="0"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="25">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46217</v>
       </c>
-      <c r="B54" s="24">
+      <c r="B55" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C54" s="30">
+      <c r="C55" s="29">
         <f t="shared" si="0"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="25">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46216</v>
       </c>
-      <c r="B55" s="24">
+      <c r="B56" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C55" s="30">
+      <c r="C56" s="29">
         <f t="shared" si="0"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="25">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46213</v>
       </c>
-      <c r="B56" s="24">
+      <c r="B57" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C56" s="30">
+      <c r="C57" s="29">
         <f t="shared" si="0"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="25">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46212</v>
       </c>
-      <c r="B57" s="24">
+      <c r="B58" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C57" s="30">
+      <c r="C58" s="29">
         <f t="shared" si="0"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="25">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46211</v>
       </c>
-      <c r="B58" s="24">
+      <c r="B59" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C58" s="30">
+      <c r="C59" s="29">
         <f t="shared" si="0"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="25">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46210</v>
       </c>
-      <c r="B59" s="24">
+      <c r="B60" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C59" s="30">
+      <c r="C60" s="29">
         <f t="shared" si="0"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="25">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46209</v>
       </c>
-      <c r="B60" s="24">
+      <c r="B61" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C60" s="30">
+      <c r="C61" s="29">
         <f t="shared" si="0"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="25">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46206</v>
       </c>
-      <c r="B61" s="24">
+      <c r="B62" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C61" s="30">
+      <c r="C62" s="29">
         <f t="shared" si="0"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="25">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46205</v>
       </c>
-      <c r="B62" s="24">
+      <c r="B63" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C62" s="30">
+      <c r="C63" s="29">
         <f t="shared" si="0"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="25">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46204</v>
       </c>
-      <c r="B63" s="24">
+      <c r="B64" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C63" s="30">
+      <c r="C64" s="29">
         <f t="shared" si="0"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="25">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46203</v>
       </c>
-      <c r="B64" s="24">
+      <c r="B65" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C64" s="30">
+      <c r="C65" s="29">
         <f t="shared" si="0"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="25">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46198</v>
       </c>
-      <c r="B65" s="24">
+      <c r="B66" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C65" s="30">
+      <c r="C66" s="29">
         <f t="shared" si="0"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="25">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46196</v>
       </c>
-      <c r="B66" s="24">
+      <c r="B67" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C66" s="30">
+      <c r="C67" s="29">
         <f t="shared" si="0"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="25">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46195</v>
       </c>
-      <c r="B67" s="24">
+      <c r="B68" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C67" s="30">
+      <c r="C68" s="29">
         <f t="shared" si="0"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="25">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46192</v>
       </c>
-      <c r="B68" s="24">
+      <c r="B69" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C69" s="29">
         <f t="shared" si="0"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="25">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46191</v>
       </c>
-      <c r="B69" s="24">
+      <c r="B70" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C69" s="30">
+      <c r="C70" s="29">
         <f t="shared" si="0"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="25">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46190</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B71" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C70" s="30">
+      <c r="C71" s="29">
         <f t="shared" si="0"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="25">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46189</v>
       </c>
-      <c r="B71" s="24">
+      <c r="B72" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C71" s="30">
+      <c r="C72" s="29">
         <f t="shared" si="0"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="25">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46188</v>
       </c>
-      <c r="B72" s="24">
+      <c r="B73" s="23">
         <v>8.42</v>
       </c>
-      <c r="C72" s="30">
+      <c r="C73" s="29">
         <f t="shared" si="0"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="25">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46185</v>
       </c>
-      <c r="B73" s="24">
+      <c r="B74" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C73" s="30">
+      <c r="C74" s="29">
         <f t="shared" si="0"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="25">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46184</v>
       </c>
-      <c r="B74" s="24">
+      <c r="B75" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C74" s="30">
+      <c r="C75" s="29">
         <f t="shared" si="0"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="25">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46183</v>
       </c>
-      <c r="B75" s="24">
+      <c r="B76" s="23">
         <v>22562.357509739999</v>
       </c>
-      <c r="C75" s="30">
-        <f t="shared" ref="C75:C116" si="1">+(B75-B76)/B76</f>
+      <c r="C76" s="29">
+        <f t="shared" ref="C76:C117" si="1">+(B76-B77)/B77</f>
         <v>5.2639483520141219</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="25">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46182</v>
       </c>
-      <c r="B76" s="24">
+      <c r="B77" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C76" s="30">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="25">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46178</v>
       </c>
-      <c r="B77" s="24">
+      <c r="B78" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C77" s="30">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="25">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46177</v>
       </c>
-      <c r="B78" s="24">
+      <c r="B79" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C78" s="30">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="25">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46176</v>
       </c>
-      <c r="B79" s="24">
+      <c r="B80" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C79" s="30">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="25">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46175</v>
       </c>
-      <c r="B80" s="24">
+      <c r="B81" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C80" s="30">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="25">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46174</v>
       </c>
-      <c r="B81" s="24">
+      <c r="B82" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C81" s="30">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="25">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46171</v>
       </c>
-      <c r="B82" s="24">
+      <c r="B83" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C82" s="30">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="25">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>45074</v>
       </c>
-      <c r="B83" s="24">
+      <c r="B84" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C83" s="30">
+      <c r="C84" s="29">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="25">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46169</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B85" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C84" s="30">
+      <c r="C85" s="29">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="25">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46168</v>
       </c>
-      <c r="B85" s="24">
+      <c r="B86" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C85" s="30">
+      <c r="C86" s="29">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="25">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46167</v>
       </c>
-      <c r="B86" s="24">
+      <c r="B87" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C86" s="30">
+      <c r="C87" s="29">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="25">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46164</v>
       </c>
-      <c r="B87" s="24">
+      <c r="B88" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C87" s="30">
+      <c r="C88" s="29">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="25">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46163</v>
       </c>
-      <c r="B88" s="24">
+      <c r="B89" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C88" s="30">
+      <c r="C89" s="29">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="25">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46162</v>
       </c>
-      <c r="B89" s="24">
+      <c r="B90" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C89" s="30">
+      <c r="C90" s="29">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="25">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46161</v>
       </c>
-      <c r="B90" s="24">
+      <c r="B91" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C91" s="29">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="25">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46157</v>
       </c>
-      <c r="B91" s="24">
+      <c r="B92" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C91" s="30">
+      <c r="C92" s="29">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="25">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46156</v>
       </c>
-      <c r="B92" s="24">
+      <c r="B93" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C93" s="29">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="25">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46155</v>
       </c>
-      <c r="B93" s="24">
+      <c r="B94" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C93" s="30">
+      <c r="C94" s="29">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="25">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46154</v>
       </c>
-      <c r="B94" s="24">
+      <c r="B95" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C94" s="30">
+      <c r="C95" s="29">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="25">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46153</v>
       </c>
-      <c r="B95" s="24">
+      <c r="B96" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C95" s="30">
+      <c r="C96" s="29">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="25">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46150</v>
       </c>
-      <c r="B96" s="24">
+      <c r="B97" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C96" s="30">
+      <c r="C97" s="29">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="23">
+    <row r="98" spans="1:4">
+      <c r="A98" s="22">
         <v>46149</v>
       </c>
-      <c r="B97" s="22">
+      <c r="B98" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C97" s="30">
+      <c r="C98" s="29">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="18">
+    <row r="99" spans="1:4">
+      <c r="A99" s="17">
         <v>46148</v>
       </c>
-      <c r="B98" s="16">
+      <c r="B99" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C98" s="30">
+      <c r="C99" s="29">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="18">
+    <row r="100" spans="1:4">
+      <c r="A100" s="17">
         <v>46147</v>
       </c>
-      <c r="B99" s="16">
+      <c r="B100" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C99" s="30">
+      <c r="C100" s="29">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="18">
+    <row r="101" spans="1:4">
+      <c r="A101" s="17">
         <v>46146</v>
       </c>
-      <c r="B100" s="16">
+      <c r="B101" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C101" s="29">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="19">
+    <row r="102" spans="1:4">
+      <c r="A102" s="18">
         <v>46142</v>
       </c>
-      <c r="B101" s="16">
+      <c r="B102" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C102" s="29">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="19">
+    <row r="103" spans="1:4">
+      <c r="A103" s="18">
         <v>46141</v>
       </c>
-      <c r="B102" s="16">
+      <c r="B103" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C102" s="30">
+      <c r="C103" s="29">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="19">
+    <row r="104" spans="1:4">
+      <c r="A104" s="18">
         <v>46140</v>
       </c>
-      <c r="B103" s="16">
+      <c r="B104" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C103" s="30">
+      <c r="C104" s="29">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="19">
+    <row r="105" spans="1:4">
+      <c r="A105" s="18">
         <v>46139</v>
       </c>
-      <c r="B104" s="16">
+      <c r="B105" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C104" s="30">
+      <c r="C105" s="29">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="19">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="18">
         <v>46136</v>
       </c>
-      <c r="B105" s="16">
+      <c r="B106" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C105" s="30">
+      <c r="C106" s="29">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
-      <c r="D105" s="37"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="19">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="18">
         <v>46135</v>
       </c>
-      <c r="B106" s="16">
+      <c r="B107" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C106" s="30">
+      <c r="C107" s="29">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="19">
+    <row r="108" spans="1:4">
+      <c r="A108" s="18">
         <v>46134</v>
       </c>
-      <c r="B107" s="16">
+      <c r="B108" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C107" s="30">
+      <c r="C108" s="29">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="19">
+    <row r="109" spans="1:4">
+      <c r="A109" s="18">
         <v>46133</v>
       </c>
-      <c r="B108" s="16">
+      <c r="B109" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C108" s="30">
+      <c r="C109" s="29">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="19">
+    <row r="110" spans="1:4">
+      <c r="A110" s="18">
         <v>46132</v>
       </c>
-      <c r="B109" s="16">
+      <c r="B110" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C109" s="30">
+      <c r="C110" s="29">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="19">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46129</v>
       </c>
-      <c r="B110" s="16">
+      <c r="B111" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C110" s="30">
+      <c r="C111" s="29">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
-      <c r="D110" s="36"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="19">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46128</v>
       </c>
-      <c r="B111" s="16">
+      <c r="B112" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C111" s="30">
+      <c r="C112" s="29">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="19">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46127</v>
       </c>
-      <c r="B112" s="39">
+      <c r="B113" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C112" s="30">
+      <c r="C113" s="29">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
-      <c r="D112" s="36"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="19">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46126</v>
       </c>
-      <c r="B113" s="39">
+      <c r="B114" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C113" s="30">
+      <c r="C114" s="29">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="19">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46125</v>
       </c>
-      <c r="B114" s="16">
+      <c r="B115" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C114" s="30">
+      <c r="C115" s="29">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="19">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46122</v>
       </c>
-      <c r="B115" s="16">
+      <c r="B116" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C115" s="30">
+      <c r="C116" s="29">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="19">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46121</v>
       </c>
-      <c r="B116" s="16">
+      <c r="B117" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C116" s="30">
+      <c r="C117" s="29">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="19">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46120</v>
       </c>
-      <c r="B117" s="16">
+      <c r="B118" s="15">
         <v>580.56056466999996</v>
       </c>
-      <c r="C117" s="30">
-        <f>+(B117-B118)/B118</f>
+      <c r="C118" s="29">
+        <f>+(B118-B119)/B119</f>
         <v>3.9632497533121036</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="19">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46119</v>
       </c>
-      <c r="B118" s="16">
+      <c r="B119" s="15">
         <v>116.97186189</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="19">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46118</v>
       </c>
-      <c r="B119" s="16">
+      <c r="B120" s="15">
         <v>6972.36861443</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="19">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46113</v>
       </c>
-      <c r="B120" s="16">
+      <c r="B121" s="15">
         <v>540.00852741999995</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="19">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46112</v>
       </c>
-      <c r="B121" s="16">
+      <c r="B122" s="15">
         <v>5262.3389565099997</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="19">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46111</v>
       </c>
-      <c r="B122" s="16">
+      <c r="B123" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7032,82 +7066,82 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="17">
-        <v>98931.490865999993</v>
-      </c>
-      <c r="C2" s="1">
-        <v>4946.5745432999993</v>
-      </c>
-      <c r="D2" s="8">
-        <v>64.09</v>
+      <c r="A2" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="16">
+        <v>251306.31</v>
+      </c>
+      <c r="C2" s="16">
+        <v>13226.65</v>
+      </c>
+      <c r="D2" s="23">
+        <v>188.96</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
-      <c r="A3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="17">
-        <v>251306.31</v>
-      </c>
-      <c r="C3" s="17">
-        <v>13226.65</v>
-      </c>
-      <c r="D3">
-        <v>188.96</v>
-      </c>
-      <c r="G3" s="33" t="s">
+      <c r="A3" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="16">
+        <v>254788.61</v>
+      </c>
+      <c r="C3" s="16">
+        <v>13409.93</v>
+      </c>
+      <c r="D3" s="7">
+        <v>245.29</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15">
-      <c r="A4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="17">
-        <v>254788.61</v>
-      </c>
-      <c r="C4" s="17">
-        <v>13409.93</v>
+      <c r="A4" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="16">
+        <v>40192.65</v>
+      </c>
+      <c r="C4" s="16">
+        <v>1826.94</v>
       </c>
       <c r="D4" s="7">
-        <v>245.29</v>
-      </c>
-      <c r="G4" s="33" t="s">
+        <v>81.88</v>
+      </c>
+      <c r="G4" s="32" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
-      <c r="A5" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="17">
-        <v>40192.65</v>
-      </c>
-      <c r="C5" s="17">
-        <v>1826.94</v>
+      <c r="A5" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="16">
+        <v>10939.03</v>
+      </c>
+      <c r="C5" s="7">
+        <v>520.91</v>
       </c>
       <c r="D5" s="7">
-        <v>81.88</v>
-      </c>
-      <c r="G5" s="33" t="s">
+        <v>114.6</v>
+      </c>
+      <c r="G5" s="32" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="17">
-        <v>10939.03</v>
-      </c>
-      <c r="C6" s="7">
-        <v>520.91</v>
-      </c>
-      <c r="D6" s="7">
-        <v>114.6</v>
+        <v>39</v>
+      </c>
+      <c r="B6" s="16">
+        <v>155817.19145900002</v>
+      </c>
+      <c r="C6" s="16">
+        <v>7419.8662599523823</v>
+      </c>
+      <c r="D6" s="16">
+        <v>40.529003233410926</v>
       </c>
     </row>
   </sheetData>
@@ -7292,10 +7326,10 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>46136</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="16">
         <v>1206629034.17156</v>
       </c>
       <c r="C16" s="4">
@@ -7304,10 +7338,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" thickBot="1">
-      <c r="A17" s="25">
+      <c r="A17" s="24">
         <v>46164</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="16">
         <v>1440966613.4014599</v>
       </c>
       <c r="C17" s="4">
@@ -7316,10 +7350,10 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" thickBot="1">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <v>46171</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="16">
         <v>1452167458.20135</v>
       </c>
       <c r="C18" s="4">
@@ -7328,10 +7362,10 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" thickBot="1">
-      <c r="A19" s="25">
+      <c r="A19" s="24">
         <v>46178</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="16">
         <v>1583302878.3216901</v>
       </c>
       <c r="C19" s="4">
@@ -7340,10 +7374,10 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" thickBot="1">
-      <c r="A20" s="25">
+      <c r="A20" s="24">
         <v>46185</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="16">
         <v>1491369041.2082701</v>
       </c>
       <c r="C20" s="4">
@@ -7352,10 +7386,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" thickBot="1">
-      <c r="A21" s="25">
+      <c r="A21" s="24">
         <v>46192</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="16">
         <v>1486232648.3692801</v>
       </c>
       <c r="C21" s="4">
@@ -7364,10 +7398,10 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" thickBot="1">
-      <c r="A22" s="25">
+      <c r="A22" s="24">
         <v>46199</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="16">
         <v>1396607027.6049099</v>
       </c>
       <c r="C22" s="4">
@@ -7376,10 +7410,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" thickBot="1">
-      <c r="A23" s="25">
+      <c r="A23" s="24">
         <v>46227</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="16">
         <v>1468051657.5950301</v>
       </c>
       <c r="C23" s="4">
@@ -7388,10 +7422,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" thickBot="1">
-      <c r="A24" s="25">
+      <c r="A24" s="24">
         <v>46255</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="16">
         <v>1588746455.7100201</v>
       </c>
       <c r="C24" s="4">
@@ -7400,36 +7434,36 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" thickBot="1">
-      <c r="A25" s="25">
+      <c r="A25" s="24">
         <v>46262</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="16">
         <v>1616236987.2485399</v>
       </c>
       <c r="C25" s="4">
         <f t="shared" si="0"/>
         <v>1.730328425893116</v>
       </c>
-      <c r="E25" s="38"/>
+      <c r="E25" s="37"/>
     </row>
     <row r="26" spans="1:5" ht="15" thickBot="1">
-      <c r="A26" s="25">
+      <c r="A26" s="24">
         <v>46269</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <v>1705456884.3822601</v>
       </c>
       <c r="C26" s="4">
         <f t="shared" si="0"/>
         <v>5.5202236947693484</v>
       </c>
-      <c r="E26" s="38"/>
+      <c r="E26" s="37"/>
     </row>
     <row r="27" spans="1:5" ht="15" thickBot="1">
-      <c r="A27" s="25">
+      <c r="A27" s="24">
         <v>46276</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <v>1626323546.47457</v>
       </c>
       <c r="C27" s="4">
@@ -7438,10 +7472,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" thickBot="1">
-      <c r="A28" s="25">
+      <c r="A28" s="24">
         <v>46283</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="16">
         <v>1735040974.8817899</v>
       </c>
       <c r="C28" s="4">
@@ -7517,7 +7551,7 @@
       <c r="G2" s="1">
         <v>1519806353.6243293</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="14">
         <v>0</v>
       </c>
     </row>
@@ -7543,7 +7577,7 @@
       <c r="G3" s="1">
         <v>1498426560.28052</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="14">
         <f>+((G3-G2)/G2)*100</f>
         <v>-1.4067445693212368</v>
       </c>
@@ -7570,7 +7604,7 @@
       <c r="G4" s="1">
         <v>1513046615.0035896</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="14">
         <f>+((G4-G3)/G3)*100</f>
         <v>0.9756937784346702</v>
       </c>
@@ -7597,7 +7631,7 @@
       <c r="G5" s="1">
         <v>1565623499.8385897</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="14">
         <f>+((G5-G4)/G4)*100</f>
         <v>3.4749018512476764</v>
       </c>
@@ -7624,570 +7658,572 @@
       <c r="G6" s="1">
         <v>1612822155.3327496</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <f>+((G6-G5)/G5)*100</f>
         <v>3.0146874710954426</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="25">
+      <c r="A7" s="24">
         <v>46143</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="16">
         <v>56289349.634710021</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>1572208957.4513197</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="16">
         <v>131632832.49728999</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="16">
         <v>1760131139.5833197</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="16">
         <v>1480052.1803799996</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>1761611191.7636998</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="26">
         <v>9.2253839605925378</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>46150</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="16">
         <v>56976115.061530016</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>1583444536.3055906</v>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="16">
         <v>120943453.33754002</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="16">
         <v>1761364104.7046607</v>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="16">
         <v>1443633.0552200002</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="16">
         <v>1762807737.7598805</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="26">
         <v>6.7923387508850297E-2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="25">
+      <c r="A9" s="24">
         <v>46157</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="16">
         <v>57191389.678870022</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="16">
         <v>1736713788.0136802</v>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="16">
         <v>154232219.13352999</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="16">
         <v>1948137396.8260801</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="16">
         <v>1517284.0840200002</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="16">
         <v>1949654680.9101</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="26">
         <v>10.599394315551303</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="25">
+      <c r="A10" s="24">
         <v>46164</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>59297253.722750016</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>1756395281.4472902</v>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="16">
         <v>146574089.18363994</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="16">
         <v>1962266624.3536801</v>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="16">
         <v>1598030.6558000003</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="16">
         <v>1963864655.0094802</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="26">
         <v>0.72884568936828487</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="25">
+      <c r="A11" s="24">
         <v>46202</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="16">
         <v>61835356.210640013</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>1886607672.3299406</v>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="16">
         <v>163572012.59929004</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="16">
         <v>2112015041.1398706</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="16">
         <v>1706770.0237499999</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <v>2113721811.1636207</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="26">
         <v>7.6307272892701832</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="25">
+      <c r="A12" s="24">
         <v>46178</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="16">
         <v>63931654.937720016</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="16">
         <v>1957457867.6445699</v>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="16">
         <v>149657684.68581003</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="16">
         <v>2171047207.2680998</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="16">
         <v>1753411.3252600001</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="16">
         <v>2172800618.5933599</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="26">
         <v>2.7950133796091023</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="25">
+      <c r="A13" s="24">
         <v>46185</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="16">
         <v>63611606.013210006</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="16">
         <v>1879421568.1788502</v>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="16">
         <v>133033132.39342</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="16">
         <v>2076066306.5854802</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="16">
         <v>1714526.8965600003</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="16">
         <v>2077780833.4820399</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="26">
         <v>-4.3731479224649092</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="25">
+      <c r="A14" s="24">
         <v>46192</v>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="16">
         <v>65860434.967950001</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="16">
         <v>1914988346.0565095</v>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="16">
         <v>162309932.49878004</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <v>2143158713.5232396</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="16">
         <v>1705432.2701800002</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="16">
         <v>2144864145.7934194</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="26">
         <v>3.2286038657387337</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="25">
+      <c r="A15" s="24">
         <v>46199</v>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="16">
         <v>66643069.210480012</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="16">
         <v>1865343448.3990905</v>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="16">
         <v>172370820.8464765</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="16">
         <v>2104357338.4560471</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="16">
         <v>1885890.7660000003</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="16">
         <v>2106243229.2220471</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="26">
         <v>-1.8006229740525441</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>46206</v>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="16">
         <v>68376322.198670015</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="16">
         <v>1874824600.7037601</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="16">
         <v>187900609.12325659</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>2131101532.0256867</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="16">
         <v>2089309.7912699997</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="16">
         <v>2133190841.8169568</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="26">
         <v>1.2794159867691519</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="25">
+      <c r="A17" s="24">
         <v>46213</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="16">
         <v>68487199.928740025</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="16">
         <v>1899748731.1160312</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="16">
         <v>162301220.45412648</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="16">
         <v>2130537151.4988976</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="16">
         <v>2464039.5699600005</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="16">
         <v>2133001191.0688577</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="26">
         <v>-8.8904726375744758E-3</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <v>46220</v>
       </c>
-      <c r="B18" s="17">
+      <c r="B18" s="16">
         <v>69757899.158520013</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="16">
         <v>2038826282.5316811</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="16">
         <v>217968687.7986365</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="16">
         <v>2326552869.4888377</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="16">
         <v>2029339.0808599996</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="16">
         <v>2328582208.5696979</v>
       </c>
-      <c r="H18" s="27">
+      <c r="H18" s="26">
         <v>9.1692877772296697</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="25">
+      <c r="A19" s="24">
         <v>46227</v>
       </c>
-      <c r="B19" s="17">
+      <c r="B19" s="16">
         <v>71935096.137300014</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="16">
         <v>2094704967.8231509</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="16">
         <v>222110560.74773642</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="16">
         <v>2388750624.7081876</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="16">
         <v>2133572.8824000005</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="16">
         <v>2390884197.5905876</v>
       </c>
-      <c r="H19" s="27">
+      <c r="H19" s="26">
         <v>2.6755331545351737</v>
       </c>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="25">
+      <c r="A20" s="24">
         <v>46234</v>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="16">
         <v>73562982.041420013</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="16">
         <v>2158280622.777401</v>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="16">
         <v>232842453.77054653</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="16">
         <v>2464686058.5893674</v>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="16">
         <v>2259648.3903599996</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="16">
         <v>2466945706.9797273</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="26">
         <v>3.1813129831127327</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="25">
+      <c r="A21" s="24">
         <v>46241</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="16">
         <v>74588465.34969002</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="16">
         <v>2167193538.7617316</v>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="16">
         <v>198439181.48875651</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="16">
         <v>2440221185.6001782</v>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="16">
         <v>2971243.6223900001</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="16">
         <v>2443192429.222568</v>
       </c>
-      <c r="H21" s="27">
+      <c r="H21" s="26">
         <v>-0.96286179667246508</v>
       </c>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="25">
+      <c r="A22" s="24">
         <v>46248</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="16">
         <v>74239926.334400013</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="16">
         <v>2163040890.6203313</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="16">
         <v>208734334.00143653</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="16">
         <v>2446015150.9561682</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="16">
         <v>2159689.0630499991</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="16">
         <v>2448174840.0192175</v>
       </c>
-      <c r="H22" s="27">
+      <c r="H22" s="26">
         <v>0.2039303469123297</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="25">
+      <c r="A23" s="24">
         <v>46255</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="16">
         <v>76026162.824400008</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="16">
         <v>2297157294.4069014</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <v>212317214.11852658</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>2585500671.3498278</v>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="16">
         <v>2182911.8923299997</v>
       </c>
-      <c r="G23" s="17">
+      <c r="G23" s="16">
         <v>2587683583.2421579</v>
       </c>
-      <c r="H23" s="27">
+      <c r="H23" s="26">
         <v>5.6984795751697845</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="25">
+      <c r="A24" s="24">
         <v>46262</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="16">
         <v>78436320.980450019</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="16">
         <v>2368853653.2673907</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <v>221939034.59143993</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>2669229008.8392806</v>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="16">
         <v>2363869.91811</v>
       </c>
-      <c r="G24" s="17">
+      <c r="G24" s="16">
         <v>2671592878.7573905</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="26">
         <v>3.2456431709609603</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="25">
+      <c r="A25" s="24">
         <v>46269</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="16">
         <v>79934788.226620004</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="16">
         <v>2449226669.3992906</v>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="16">
         <v>220761212.62711993</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="16">
         <v>2749922670.2530308</v>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="16">
         <v>2498658.4271799996</v>
       </c>
-      <c r="G25" s="17">
+      <c r="G25" s="16">
         <v>2752421328.6802111</v>
       </c>
-      <c r="H25" s="27">
+      <c r="H25" s="26">
         <v>3.0254778175788317</v>
       </c>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="25">
+      <c r="A26" s="24">
         <v>46276</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <v>79385922.735550016</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="16">
         <v>2467050597.1357689</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="16">
         <v>198171308.14264002</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="16">
         <v>2744607828.0139589</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="16">
         <v>2520693.33421</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="16">
         <v>2747128521.3481688</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="26">
         <v>-0.19229640741738052</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="25">
+      <c r="A27" s="24">
         <v>46283</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <v>79889194.534160003</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="16">
         <v>2514501098.3346596</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="16">
         <v>236888778.51269996</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="16">
         <v>2831279071.3815198</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="16">
         <v>7866916.1232899986</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="16">
         <v>2839145987.5048099</v>
       </c>
-      <c r="H27" s="27">
+      <c r="H27" s="26">
         <v>3.3495872305050689</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="26"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8196,14 +8232,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
     <col min="2" max="2" width="10.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.875" style="14" customWidth="1"/>
+    <col min="5" max="5" width="21.875" style="13" customWidth="1"/>
     <col min="9" max="9" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8220,7 +8256,7 @@
       <c r="D1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>17</v>
       </c>
       <c r="F1" t="s">
@@ -8240,8 +8276,8 @@
       <c r="D2">
         <v>13103</v>
       </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="32">
+      <c r="E2" s="30"/>
+      <c r="F2" s="31">
         <v>-0.03</v>
       </c>
     </row>
@@ -8258,11 +8294,11 @@
       <c r="D3">
         <v>13741</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="30">
         <f t="shared" ref="E3:E17" si="0">+((D3-D2)/D2)</f>
         <v>4.8691139433717466E-2</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="31">
         <v>0.05</v>
       </c>
     </row>
@@ -8279,11 +8315,11 @@
       <c r="D4">
         <v>13589</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="30">
         <f t="shared" si="0"/>
         <v>-1.1061785896222982E-2</v>
       </c>
-      <c r="F4" s="32">
+      <c r="F4" s="31">
         <v>-0.01</v>
       </c>
     </row>
@@ -8300,11 +8336,11 @@
       <c r="D5">
         <v>13674</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <f t="shared" si="0"/>
         <v>6.2550592390904405E-3</v>
       </c>
-      <c r="F5" s="32">
+      <c r="F5" s="31">
         <v>0.01</v>
       </c>
     </row>
@@ -8321,11 +8357,11 @@
       <c r="D6">
         <v>13484</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <f t="shared" si="0"/>
         <v>-1.3894983179757204E-2</v>
       </c>
-      <c r="F6" s="32">
+      <c r="F6" s="31">
         <v>-0.01</v>
       </c>
     </row>
@@ -8342,11 +8378,11 @@
       <c r="D7">
         <v>13460</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <f t="shared" si="0"/>
         <v>-1.7798872738059924E-3</v>
       </c>
-      <c r="F7" s="32">
+      <c r="F7" s="31">
         <v>-0.01</v>
       </c>
     </row>
@@ -8363,11 +8399,11 @@
       <c r="D8">
         <v>13253</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <f t="shared" si="0"/>
         <v>-1.5378900445765229E-2</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="31">
         <v>-0.01</v>
       </c>
     </row>
@@ -8384,11 +8420,11 @@
       <c r="D9">
         <v>13187</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <f t="shared" si="0"/>
         <v>-4.9800045272768434E-3</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="31">
         <v>-0.01</v>
       </c>
     </row>
@@ -8405,11 +8441,11 @@
       <c r="D10">
         <v>13280</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <f t="shared" si="0"/>
         <v>7.0524000909987106E-3</v>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="31">
         <v>-0.01</v>
       </c>
       <c r="G10" s="7"/>
@@ -8427,11 +8463,11 @@
       <c r="D11">
         <v>14061</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <f t="shared" si="0"/>
         <v>5.8810240963855419E-2</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="31">
         <v>-0.01</v>
       </c>
     </row>
@@ -8439,2082 +8475,2103 @@
       <c r="A12" s="2">
         <v>46147</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <v>13869</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <v>13872</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <f t="shared" si="0"/>
         <v>-1.3441433752933647E-2</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="31">
         <v>-0.01</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="25">
+      <c r="A13" s="24">
         <v>46148</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="25">
         <v>13411</v>
       </c>
-      <c r="C13" s="24">
-        <v>3</v>
-      </c>
-      <c r="D13" s="26">
+      <c r="C13" s="23">
+        <v>3</v>
+      </c>
+      <c r="D13" s="25">
         <v>13414</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <f t="shared" si="0"/>
         <v>-3.3016147635524795E-2</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="31">
         <v>-0.123456</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="25">
+      <c r="A14" s="24">
         <v>46149</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="25">
         <v>13460</v>
       </c>
-      <c r="C14" s="24">
-        <v>3</v>
-      </c>
-      <c r="D14" s="26">
+      <c r="C14" s="23">
+        <v>3</v>
+      </c>
+      <c r="D14" s="25">
         <v>13463</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <f t="shared" si="0"/>
         <v>3.6528999552706129E-3</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="31">
         <v>0.37123455999999999</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="25">
+      <c r="A15" s="24">
         <v>46150</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="25">
         <v>13398</v>
       </c>
-      <c r="C15" s="24">
-        <v>3</v>
-      </c>
-      <c r="D15" s="26">
+      <c r="C15" s="23">
+        <v>3</v>
+      </c>
+      <c r="D15" s="25">
         <v>13401</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <f t="shared" si="0"/>
         <v>-4.6052142910198322E-3</v>
       </c>
-      <c r="F15" s="32">
+      <c r="F15" s="31">
         <v>-0.46123456000000002</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="25">
+      <c r="A16" s="24">
         <v>46153</v>
       </c>
-      <c r="B16" s="26">
+      <c r="B16" s="25">
         <v>13309</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="25">
         <v>13312</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <f t="shared" si="0"/>
         <v>-6.6412954257144986E-3</v>
       </c>
-      <c r="F16" s="32">
+      <c r="F16" s="31">
         <v>-0.66123456000000003</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="25">
+      <c r="A17" s="24">
         <v>46154</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="25">
         <v>13300</v>
       </c>
-      <c r="C17" s="24">
-        <v>3</v>
-      </c>
-      <c r="D17" s="26">
+      <c r="C17" s="23">
+        <v>3</v>
+      </c>
+      <c r="D17" s="25">
         <v>13303</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <f t="shared" si="0"/>
         <v>-6.7608173076923075E-4</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="31">
         <v>-7.1234560000000002E-2</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="25">
+      <c r="A18" s="24">
         <v>46155</v>
       </c>
-      <c r="B18" s="26">
+      <c r="B18" s="25">
         <v>13277</v>
       </c>
-      <c r="C18" s="24">
-        <v>3</v>
-      </c>
-      <c r="D18" s="26">
+      <c r="C18" s="23">
+        <v>3</v>
+      </c>
+      <c r="D18" s="25">
         <v>13280</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <f>+((D18-D17)/D17)</f>
         <v>-1.7289333233105315E-3</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="31">
         <v>-0.17123456000000001</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="25">
+      <c r="A19" s="24">
         <v>46156</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="25">
         <v>13282</v>
       </c>
-      <c r="C19" s="24">
-        <v>3</v>
-      </c>
-      <c r="D19" s="26">
+      <c r="C19" s="23">
+        <v>3</v>
+      </c>
+      <c r="D19" s="25">
         <f t="shared" ref="D19" si="1">SUM(B19+C19)</f>
         <v>13285</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="30">
         <f>+((D19-D18)/D18)</f>
         <v>3.7650602409638556E-4</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="31">
         <v>4.1234560000000003E-2</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="25">
+      <c r="A20" s="24">
         <v>46157</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="25">
         <v>13015</v>
       </c>
-      <c r="C20" s="24">
-        <v>3</v>
-      </c>
-      <c r="D20" s="26">
+      <c r="C20" s="23">
+        <v>3</v>
+      </c>
+      <c r="D20" s="25">
         <v>13018</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="30">
         <f>+((D20-D19)/D19)</f>
         <v>-2.0097854723372225E-2</v>
       </c>
-      <c r="F20" s="32">
+      <c r="F20" s="31">
         <v>-2.0112345600000001</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="25">
+      <c r="A21" s="24">
         <v>46161</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="25">
         <v>12992</v>
       </c>
-      <c r="C21" s="24">
-        <v>3</v>
-      </c>
-      <c r="D21" s="26">
+      <c r="C21" s="23">
+        <v>3</v>
+      </c>
+      <c r="D21" s="25">
         <v>12995</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="30">
         <f>+((D21-D20)/D20)</f>
         <v>-1.7667844522968198E-3</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="31">
         <v>-0.18123455999999999</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="25">
+      <c r="A22" s="24">
         <v>46162</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="25">
         <v>12888</v>
       </c>
-      <c r="C22" s="24">
-        <v>3</v>
-      </c>
-      <c r="D22" s="26">
+      <c r="C22" s="23">
+        <v>3</v>
+      </c>
+      <c r="D22" s="25">
         <v>12891</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="30">
         <f>+((D22-D21)/D21)</f>
         <v>-8.0030781069642173E-3</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="31">
         <v>-0.80123456000000004</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="25">
+      <c r="A23" s="24">
         <v>46163</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="25">
         <v>14686</v>
       </c>
-      <c r="C23" s="24">
-        <v>3</v>
-      </c>
-      <c r="D23" s="26">
+      <c r="C23" s="23">
+        <v>3</v>
+      </c>
+      <c r="D23" s="25">
         <v>14689</v>
       </c>
-      <c r="E23" s="31">
+      <c r="E23" s="30">
         <f t="shared" ref="E23:E24" si="2">+((D23-D22)/D22)</f>
         <v>0.13947715460398727</v>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="31">
         <v>13.95123456</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="25">
+      <c r="A24" s="24">
         <v>46164</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="25">
         <v>14649</v>
       </c>
-      <c r="C24" s="24">
-        <v>3</v>
-      </c>
-      <c r="D24" s="26">
+      <c r="C24" s="23">
+        <v>3</v>
+      </c>
+      <c r="D24" s="25">
         <v>14652</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="30">
         <f t="shared" si="2"/>
         <v>-2.5188916876574307E-3</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="31">
         <v>-0.25123456</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="25">
+      <c r="A25" s="24">
         <v>46167</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="25">
         <v>12949</v>
       </c>
-      <c r="C25" s="24">
-        <v>3</v>
-      </c>
-      <c r="D25" s="26">
+      <c r="C25" s="23">
+        <v>3</v>
+      </c>
+      <c r="D25" s="25">
         <v>12952</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="30">
         <f t="shared" ref="E25:E75" si="3">+((D25-D24)/D24)</f>
         <v>-0.11602511602511603</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="31">
         <v>-11.60123456</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="25">
+      <c r="A26" s="24">
         <v>46168</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="25">
         <v>12961</v>
       </c>
-      <c r="C26" s="24">
-        <v>3</v>
-      </c>
-      <c r="D26" s="26">
+      <c r="C26" s="23">
+        <v>3</v>
+      </c>
+      <c r="D26" s="25">
         <v>12964</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="30">
         <f t="shared" si="3"/>
         <v>9.2649783817171094E-4</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="31">
         <v>9.1234560000000006E-2</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="25">
+      <c r="A27" s="24">
         <v>46169</v>
       </c>
-      <c r="B27" s="26">
+      <c r="B27" s="25">
         <v>12914</v>
       </c>
-      <c r="C27" s="24">
-        <v>3</v>
-      </c>
-      <c r="D27" s="26">
+      <c r="C27" s="23">
+        <v>3</v>
+      </c>
+      <c r="D27" s="25">
         <v>12917</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="30">
         <f t="shared" si="3"/>
         <v>-3.625424251774144E-3</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="31">
         <v>-0.36</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="25">
+      <c r="A28" s="24">
         <v>46170</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="25">
         <v>12758</v>
       </c>
-      <c r="C28" s="24">
-        <v>3</v>
-      </c>
-      <c r="D28" s="26">
+      <c r="C28" s="23">
+        <v>3</v>
+      </c>
+      <c r="D28" s="25">
         <v>12761</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="30">
         <f t="shared" si="3"/>
         <v>-1.2077107687543547E-2</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="31">
         <v>-1.21</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="25">
+      <c r="A29" s="24">
         <v>46171</v>
       </c>
-      <c r="B29" s="26">
+      <c r="B29" s="25">
         <v>12968</v>
       </c>
-      <c r="C29" s="24">
-        <v>3</v>
-      </c>
-      <c r="D29" s="26">
+      <c r="C29" s="23">
+        <v>3</v>
+      </c>
+      <c r="D29" s="25">
         <v>12971</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="30">
         <f t="shared" si="3"/>
         <v>1.6456390565002744E-2</v>
       </c>
-      <c r="F29" s="32">
+      <c r="F29" s="31">
         <v>1.65</v>
       </c>
     </row>
     <row r="30" spans="1:6">
-      <c r="A30" s="25">
+      <c r="A30" s="24">
         <v>46174</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="25">
         <v>12916</v>
       </c>
-      <c r="C30" s="24">
-        <v>3</v>
-      </c>
-      <c r="D30" s="26">
+      <c r="C30" s="23">
+        <v>3</v>
+      </c>
+      <c r="D30" s="25">
         <v>12919</v>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="30">
         <f t="shared" si="3"/>
         <v>-4.0089430267519852E-3</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="31">
         <v>-0.4</v>
       </c>
     </row>
     <row r="31" spans="1:6">
-      <c r="A31" s="25">
+      <c r="A31" s="24">
         <v>46175</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="25">
         <v>12982</v>
       </c>
-      <c r="C31" s="24">
-        <v>3</v>
-      </c>
-      <c r="D31" s="26">
+      <c r="C31" s="23">
+        <v>3</v>
+      </c>
+      <c r="D31" s="25">
         <v>12985</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="30">
         <f t="shared" si="3"/>
         <v>5.1087545475656014E-3</v>
       </c>
-      <c r="F31" s="32">
+      <c r="F31" s="31">
         <v>0.51</v>
       </c>
     </row>
     <row r="32" spans="1:6">
-      <c r="A32" s="25">
+      <c r="A32" s="24">
         <v>46176</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="25">
         <v>12852</v>
       </c>
-      <c r="C32" s="24">
-        <v>3</v>
-      </c>
-      <c r="D32" s="26">
+      <c r="C32" s="23">
+        <v>3</v>
+      </c>
+      <c r="D32" s="25">
         <v>12855</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="30">
         <f t="shared" si="3"/>
         <v>-1.0011551790527531E-2</v>
       </c>
-      <c r="F32" s="32">
+      <c r="F32" s="31">
         <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="25">
+      <c r="A33" s="24">
         <v>46177</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="25">
         <v>12861</v>
       </c>
-      <c r="C33" s="24">
-        <v>3</v>
-      </c>
-      <c r="D33" s="26">
+      <c r="C33" s="23">
+        <v>3</v>
+      </c>
+      <c r="D33" s="25">
         <v>12864</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="30">
         <f t="shared" si="3"/>
         <v>7.0011668611435238E-4</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="31">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="34" spans="1:6">
-      <c r="A34" s="25">
+      <c r="A34" s="24">
         <v>46178</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="25">
         <v>12861</v>
       </c>
-      <c r="C34" s="24">
-        <v>3</v>
-      </c>
-      <c r="D34" s="26">
+      <c r="C34" s="23">
+        <v>3</v>
+      </c>
+      <c r="D34" s="25">
         <v>12864</v>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="31">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:6">
-      <c r="A35" s="25">
+      <c r="A35" s="24">
         <v>46182</v>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="25">
         <v>12645</v>
       </c>
-      <c r="C35" s="24">
-        <v>3</v>
-      </c>
-      <c r="D35" s="26">
+      <c r="C35" s="23">
+        <v>3</v>
+      </c>
+      <c r="D35" s="25">
         <v>12648</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="30">
         <f t="shared" si="3"/>
         <v>-1.6791044776119403E-2</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="31">
         <v>-1.68</v>
       </c>
     </row>
     <row r="36" spans="1:6">
-      <c r="A36" s="25">
+      <c r="A36" s="24">
         <v>46183</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="25">
         <v>12401</v>
       </c>
-      <c r="C36" s="24">
-        <v>3</v>
-      </c>
-      <c r="D36" s="26">
+      <c r="C36" s="23">
+        <v>3</v>
+      </c>
+      <c r="D36" s="25">
         <v>12404</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="30">
         <f t="shared" si="3"/>
         <v>-1.9291587602783048E-2</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="31">
         <v>-1.93</v>
       </c>
     </row>
     <row r="37" spans="1:6">
-      <c r="A37" s="25">
+      <c r="A37" s="24">
         <v>46184</v>
       </c>
-      <c r="B37" s="26">
+      <c r="B37" s="25">
         <v>12260</v>
       </c>
-      <c r="C37" s="24">
-        <v>3</v>
-      </c>
-      <c r="D37" s="26">
+      <c r="C37" s="23">
+        <v>3</v>
+      </c>
+      <c r="D37" s="25">
         <v>12263</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="30">
         <f t="shared" si="3"/>
         <v>-1.1367300870686875E-2</v>
       </c>
-      <c r="F37" s="32">
+      <c r="F37" s="31">
         <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:6">
-      <c r="A38" s="25">
+      <c r="A38" s="24">
         <v>46185</v>
       </c>
-      <c r="B38" s="26">
+      <c r="B38" s="25">
         <v>13444</v>
       </c>
-      <c r="C38" s="24">
-        <v>3</v>
-      </c>
-      <c r="D38" s="26">
+      <c r="C38" s="23">
+        <v>3</v>
+      </c>
+      <c r="D38" s="25">
         <v>13447</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="30">
         <f t="shared" si="3"/>
         <v>9.6550599363940309E-2</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="31">
         <v>9.66</v>
       </c>
     </row>
     <row r="39" spans="1:6">
-      <c r="A39" s="25">
+      <c r="A39" s="24">
         <v>46188</v>
       </c>
-      <c r="B39" s="26">
+      <c r="B39" s="25">
         <v>13557</v>
       </c>
-      <c r="C39" s="24">
-        <v>3</v>
-      </c>
-      <c r="D39" s="26">
+      <c r="C39" s="23">
+        <v>3</v>
+      </c>
+      <c r="D39" s="25">
         <v>13560</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="30">
         <f t="shared" si="3"/>
         <v>8.4033613445378148E-3</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="31">
         <v>0.84</v>
       </c>
     </row>
     <row r="40" spans="1:6">
-      <c r="A40" s="25">
+      <c r="A40" s="24">
         <v>46189</v>
       </c>
-      <c r="B40" s="26">
+      <c r="B40" s="25">
         <v>13566</v>
       </c>
-      <c r="C40" s="24">
-        <v>3</v>
-      </c>
-      <c r="D40" s="26">
+      <c r="C40" s="23">
+        <v>3</v>
+      </c>
+      <c r="D40" s="25">
         <v>13569</v>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="30">
         <f t="shared" si="3"/>
         <v>6.6371681415929203E-4</v>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="31">
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="41" spans="1:6">
-      <c r="A41" s="25">
+      <c r="A41" s="24">
         <v>46190</v>
       </c>
-      <c r="B41" s="26">
+      <c r="B41" s="25">
         <v>13567</v>
       </c>
-      <c r="C41" s="24">
-        <v>3</v>
-      </c>
-      <c r="D41" s="26">
+      <c r="C41" s="23">
+        <v>3</v>
+      </c>
+      <c r="D41" s="25">
         <v>13570</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="30">
         <f t="shared" si="3"/>
         <v>7.3697398481833586E-5</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="31">
         <v>0.01</v>
       </c>
     </row>
     <row r="42" spans="1:6">
-      <c r="A42" s="25">
+      <c r="A42" s="24">
         <v>46191</v>
       </c>
-      <c r="B42" s="26">
+      <c r="B42" s="25">
         <v>13443</v>
       </c>
-      <c r="C42" s="24">
-        <v>3</v>
-      </c>
-      <c r="D42" s="26">
+      <c r="C42" s="23">
+        <v>3</v>
+      </c>
+      <c r="D42" s="25">
         <v>13446</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="30">
         <f t="shared" si="3"/>
         <v>-9.1378039793662495E-3</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="31">
         <v>-0.91</v>
       </c>
     </row>
     <row r="43" spans="1:6">
-      <c r="A43" s="25">
+      <c r="A43" s="24">
         <v>46192</v>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="25">
         <v>12812</v>
       </c>
-      <c r="C43" s="24">
-        <v>3</v>
-      </c>
-      <c r="D43" s="26">
+      <c r="C43" s="23">
+        <v>3</v>
+      </c>
+      <c r="D43" s="25">
         <v>12815</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="30">
         <f t="shared" si="3"/>
         <v>-4.6928454558976644E-2</v>
       </c>
-      <c r="F43" s="32">
+      <c r="F43" s="31">
         <v>-4.6900000000000004</v>
       </c>
     </row>
     <row r="44" spans="1:6">
-      <c r="A44" s="25">
+      <c r="A44" s="24">
         <v>46195</v>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="25">
         <v>14632</v>
       </c>
-      <c r="C44" s="24">
-        <v>3</v>
-      </c>
-      <c r="D44" s="26">
+      <c r="C44" s="23">
+        <v>3</v>
+      </c>
+      <c r="D44" s="25">
         <v>14635</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="30">
         <f t="shared" si="3"/>
         <v>0.14202106905969566</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="31">
         <v>14.2</v>
       </c>
     </row>
     <row r="45" spans="1:6">
-      <c r="A45" s="25">
+      <c r="A45" s="24">
         <v>46196</v>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="25">
         <v>14497</v>
       </c>
-      <c r="C45" s="24">
-        <v>3</v>
-      </c>
-      <c r="D45" s="26">
+      <c r="C45" s="23">
+        <v>3</v>
+      </c>
+      <c r="D45" s="25">
         <v>14500</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="30">
         <f t="shared" si="3"/>
         <v>-9.2244619063887937E-3</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="31">
         <v>-0.92</v>
       </c>
     </row>
     <row r="46" spans="1:6">
-      <c r="A46" s="25">
+      <c r="A46" s="24">
         <v>46198</v>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="25">
         <v>14307</v>
       </c>
-      <c r="C46" s="24">
-        <v>3</v>
-      </c>
-      <c r="D46" s="26">
+      <c r="C46" s="23">
+        <v>3</v>
+      </c>
+      <c r="D46" s="25">
         <v>14310</v>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="30">
         <f t="shared" si="3"/>
         <v>-1.3103448275862069E-2</v>
       </c>
-      <c r="F46" s="32">
+      <c r="F46" s="31">
         <v>-1.31</v>
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="A47" s="25">
+      <c r="A47" s="24">
         <v>46199</v>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="25">
         <v>13995</v>
       </c>
-      <c r="C47" s="24">
-        <v>3</v>
-      </c>
-      <c r="D47" s="26">
+      <c r="C47" s="23">
+        <v>3</v>
+      </c>
+      <c r="D47" s="25">
         <v>13998</v>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="30">
         <f t="shared" si="3"/>
         <v>-2.180293501048218E-2</v>
       </c>
-      <c r="F47" s="32">
+      <c r="F47" s="31">
         <v>-2.1800000000000002</v>
       </c>
     </row>
     <row r="48" spans="1:6">
-      <c r="A48" s="25">
+      <c r="A48" s="24">
         <v>46203</v>
       </c>
-      <c r="B48" s="26">
+      <c r="B48" s="25">
         <v>13908</v>
       </c>
-      <c r="C48" s="24">
-        <v>3</v>
-      </c>
-      <c r="D48" s="26">
+      <c r="C48" s="23">
+        <v>3</v>
+      </c>
+      <c r="D48" s="25">
         <v>13911</v>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="30">
         <f t="shared" si="3"/>
         <v>-6.2151735962280323E-3</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="31">
         <v>-0.62</v>
       </c>
     </row>
     <row r="49" spans="1:6">
-      <c r="A49" s="25">
+      <c r="A49" s="24">
         <v>46204</v>
       </c>
-      <c r="B49" s="26">
+      <c r="B49" s="25">
         <v>13749</v>
       </c>
-      <c r="C49" s="24">
-        <v>3</v>
-      </c>
-      <c r="D49" s="26">
+      <c r="C49" s="23">
+        <v>3</v>
+      </c>
+      <c r="D49" s="25">
         <v>13752</v>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="30">
         <f t="shared" si="3"/>
         <v>-1.1429803752426138E-2</v>
       </c>
-      <c r="F49" s="32">
+      <c r="F49" s="31">
         <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="A50" s="25">
+      <c r="A50" s="24">
         <v>46205</v>
       </c>
-      <c r="B50" s="26">
+      <c r="B50" s="25">
         <v>13869</v>
       </c>
-      <c r="C50" s="24">
-        <v>3</v>
-      </c>
-      <c r="D50" s="26">
+      <c r="C50" s="23">
+        <v>3</v>
+      </c>
+      <c r="D50" s="25">
         <v>13872</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="30">
         <f t="shared" si="3"/>
         <v>8.7260034904013961E-3</v>
       </c>
-      <c r="F50" s="32">
+      <c r="F50" s="31">
         <v>0.87</v>
       </c>
     </row>
     <row r="51" spans="1:6">
-      <c r="A51" s="25">
+      <c r="A51" s="24">
         <v>46206</v>
       </c>
-      <c r="B51" s="26">
+      <c r="B51" s="25">
         <v>13495</v>
       </c>
-      <c r="C51" s="24">
-        <v>3</v>
-      </c>
-      <c r="D51" s="26">
+      <c r="C51" s="23">
+        <v>3</v>
+      </c>
+      <c r="D51" s="25">
         <v>13498</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="30">
         <f t="shared" si="3"/>
         <v>-2.6960784313725492E-2</v>
       </c>
-      <c r="F51" s="32">
+      <c r="F51" s="31">
         <v>-2.7</v>
       </c>
     </row>
     <row r="52" spans="1:6">
-      <c r="A52" s="25">
+      <c r="A52" s="24">
         <v>46209</v>
       </c>
-      <c r="B52" s="26">
+      <c r="B52" s="25">
         <v>13393</v>
       </c>
-      <c r="C52" s="24">
-        <v>3</v>
-      </c>
-      <c r="D52" s="26">
+      <c r="C52" s="23">
+        <v>3</v>
+      </c>
+      <c r="D52" s="25">
         <v>13396</v>
       </c>
-      <c r="E52" s="31">
+      <c r="E52" s="30">
         <f t="shared" si="3"/>
         <v>-7.556675062972292E-3</v>
       </c>
-      <c r="F52" s="32">
+      <c r="F52" s="31">
         <v>-0.76</v>
       </c>
     </row>
     <row r="53" spans="1:6">
-      <c r="A53" s="25">
+      <c r="A53" s="24">
         <v>46210</v>
       </c>
-      <c r="B53" s="26">
+      <c r="B53" s="25">
         <v>13475</v>
       </c>
-      <c r="C53" s="24">
-        <v>3</v>
-      </c>
-      <c r="D53" s="26">
+      <c r="C53" s="23">
+        <v>3</v>
+      </c>
+      <c r="D53" s="25">
         <v>13478</v>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="30">
         <f t="shared" si="3"/>
         <v>6.1212302179755153E-3</v>
       </c>
-      <c r="F53" s="32">
+      <c r="F53" s="31">
         <v>0.61</v>
       </c>
     </row>
     <row r="54" spans="1:6">
-      <c r="A54" s="25">
+      <c r="A54" s="24">
         <v>46211</v>
       </c>
-      <c r="B54" s="26">
+      <c r="B54" s="25">
         <v>13365</v>
       </c>
-      <c r="C54" s="24">
-        <v>3</v>
-      </c>
-      <c r="D54" s="26">
+      <c r="C54" s="23">
+        <v>3</v>
+      </c>
+      <c r="D54" s="25">
         <v>13368</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="30">
         <f t="shared" si="3"/>
         <v>-8.1614482860958605E-3</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="31">
         <v>-0.82</v>
       </c>
     </row>
     <row r="55" spans="1:6">
-      <c r="A55" s="25">
+      <c r="A55" s="24">
         <v>46212</v>
       </c>
-      <c r="B55" s="26">
+      <c r="B55" s="25">
         <v>13447</v>
       </c>
-      <c r="C55" s="24">
-        <v>3</v>
-      </c>
-      <c r="D55" s="26">
+      <c r="C55" s="23">
+        <v>3</v>
+      </c>
+      <c r="D55" s="25">
         <v>13450</v>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="30">
         <f t="shared" si="3"/>
         <v>6.1340514661879118E-3</v>
       </c>
-      <c r="F55" s="32">
+      <c r="F55" s="31">
         <v>0.61</v>
       </c>
     </row>
     <row r="56" spans="1:6">
-      <c r="A56" s="25">
+      <c r="A56" s="24">
         <v>46213</v>
       </c>
-      <c r="B56" s="26">
+      <c r="B56" s="25">
         <v>13286</v>
       </c>
-      <c r="C56" s="24">
-        <v>3</v>
-      </c>
-      <c r="D56" s="26">
+      <c r="C56" s="23">
+        <v>3</v>
+      </c>
+      <c r="D56" s="25">
         <v>13289</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="30">
         <f t="shared" si="3"/>
         <v>-1.1970260223048328E-2</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="31">
         <v>-1.2</v>
       </c>
     </row>
     <row r="57" spans="1:6">
-      <c r="A57" s="25">
+      <c r="A57" s="24">
         <v>46216</v>
       </c>
-      <c r="B57" s="26">
+      <c r="B57" s="25">
         <v>13313</v>
       </c>
-      <c r="C57" s="24">
-        <v>3</v>
-      </c>
-      <c r="D57" s="26">
+      <c r="C57" s="23">
+        <v>3</v>
+      </c>
+      <c r="D57" s="25">
         <v>13316</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="30">
         <f t="shared" si="3"/>
         <v>2.0317555873278653E-3</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="31">
         <v>0.2</v>
       </c>
     </row>
     <row r="58" spans="1:6">
-      <c r="A58" s="25">
+      <c r="A58" s="24">
         <v>46217</v>
       </c>
-      <c r="B58" s="26">
+      <c r="B58" s="25">
         <v>13191</v>
       </c>
-      <c r="C58" s="24">
-        <v>3</v>
-      </c>
-      <c r="D58" s="26">
+      <c r="C58" s="23">
+        <v>3</v>
+      </c>
+      <c r="D58" s="25">
         <v>13194</v>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="30">
         <f t="shared" si="3"/>
         <v>-9.1619104836287175E-3</v>
       </c>
-      <c r="F58" s="32">
+      <c r="F58" s="31">
         <v>-0.92</v>
       </c>
     </row>
     <row r="59" spans="1:6">
-      <c r="A59" s="25">
+      <c r="A59" s="24">
         <v>46218</v>
       </c>
-      <c r="B59" s="26">
+      <c r="B59" s="25">
         <v>13192</v>
       </c>
-      <c r="C59" s="24">
-        <v>3</v>
-      </c>
-      <c r="D59" s="26">
+      <c r="C59" s="23">
+        <v>3</v>
+      </c>
+      <c r="D59" s="25">
         <v>13195</v>
       </c>
-      <c r="E59" s="31">
+      <c r="E59" s="30">
         <f t="shared" si="3"/>
         <v>7.5792026678793393E-5</v>
       </c>
-      <c r="F59" s="32">
+      <c r="F59" s="31">
         <v>0.01</v>
       </c>
     </row>
     <row r="60" spans="1:6">
-      <c r="A60" s="25">
+      <c r="A60" s="24">
         <v>46219</v>
       </c>
-      <c r="B60" s="26">
+      <c r="B60" s="25">
         <v>13206</v>
       </c>
-      <c r="C60" s="24">
-        <v>3</v>
-      </c>
-      <c r="D60" s="26">
+      <c r="C60" s="23">
+        <v>3</v>
+      </c>
+      <c r="D60" s="25">
         <v>13209</v>
       </c>
-      <c r="E60" s="31">
+      <c r="E60" s="30">
         <f t="shared" si="3"/>
         <v>1.0610079575596816E-3</v>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="31">
         <v>0.11</v>
       </c>
     </row>
     <row r="61" spans="1:6">
-      <c r="A61" s="25">
+      <c r="A61" s="24">
         <v>46220</v>
       </c>
-      <c r="B61" s="26">
+      <c r="B61" s="25">
         <v>13769</v>
       </c>
-      <c r="C61" s="24">
-        <v>3</v>
-      </c>
-      <c r="D61" s="26">
+      <c r="C61" s="23">
+        <v>3</v>
+      </c>
+      <c r="D61" s="25">
         <v>13772</v>
       </c>
-      <c r="E61" s="31">
+      <c r="E61" s="30">
         <f t="shared" si="3"/>
         <v>4.2622454387160266E-2</v>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="31">
         <v>4.26</v>
       </c>
     </row>
     <row r="62" spans="1:6">
-      <c r="A62" s="25">
+      <c r="A62" s="24">
         <v>46223</v>
       </c>
-      <c r="B62" s="26">
+      <c r="B62" s="25">
         <v>13591</v>
       </c>
-      <c r="C62" s="24">
-        <v>3</v>
-      </c>
-      <c r="D62" s="26">
+      <c r="C62" s="23">
+        <v>3</v>
+      </c>
+      <c r="D62" s="25">
         <v>13594</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="30">
         <f t="shared" si="3"/>
         <v>-1.2924774905605577E-2</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="31">
         <v>-1.26</v>
       </c>
     </row>
     <row r="63" spans="1:6">
-      <c r="A63" s="25">
+      <c r="A63" s="24">
         <v>46224</v>
       </c>
-      <c r="B63" s="26">
+      <c r="B63" s="25">
         <v>13510</v>
       </c>
-      <c r="C63" s="24">
-        <v>3</v>
-      </c>
-      <c r="D63" s="26">
+      <c r="C63" s="23">
+        <v>3</v>
+      </c>
+      <c r="D63" s="25">
         <v>13513</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="30">
         <f t="shared" si="3"/>
         <v>-5.9585111078416944E-3</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="31">
         <v>-0.6</v>
       </c>
     </row>
     <row r="64" spans="1:6">
-      <c r="A64" s="25">
+      <c r="A64" s="24">
         <v>46225</v>
       </c>
-      <c r="B64" s="26">
+      <c r="B64" s="25">
         <v>13589</v>
       </c>
-      <c r="C64" s="24">
-        <v>3</v>
-      </c>
-      <c r="D64" s="26">
+      <c r="C64" s="23">
+        <v>3</v>
+      </c>
+      <c r="D64" s="25">
         <v>13592</v>
       </c>
-      <c r="E64" s="31">
+      <c r="E64" s="30">
         <f t="shared" si="3"/>
         <v>5.8462221564419452E-3</v>
       </c>
-      <c r="F64" s="32">
+      <c r="F64" s="31">
         <v>0.57999999999999996</v>
       </c>
     </row>
     <row r="65" spans="1:6">
-      <c r="A65" s="25">
+      <c r="A65" s="24">
         <v>46226</v>
       </c>
-      <c r="B65" s="26">
+      <c r="B65" s="25">
         <v>13361</v>
       </c>
-      <c r="C65" s="24">
-        <v>3</v>
-      </c>
-      <c r="D65" s="26">
+      <c r="C65" s="23">
+        <v>3</v>
+      </c>
+      <c r="D65" s="25">
         <v>13364</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="30">
         <f t="shared" si="3"/>
         <v>-1.6774573278399058E-2</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="31">
         <v>-1.58</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="25">
+      <c r="A66" s="24">
         <v>46230</v>
       </c>
-      <c r="B66" s="26">
+      <c r="B66" s="25">
         <v>13208</v>
       </c>
-      <c r="C66" s="24">
-        <v>3</v>
-      </c>
-      <c r="D66" s="26">
+      <c r="C66" s="23">
+        <v>3</v>
+      </c>
+      <c r="D66" s="25">
         <v>13211</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="30">
         <f t="shared" si="3"/>
         <v>-1.1448668063454055E-2</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="31">
         <v>-1.1399999999999999</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="25">
+      <c r="A67" s="24">
         <v>46231</v>
       </c>
-      <c r="B67" s="26">
+      <c r="B67" s="25">
         <v>13105</v>
       </c>
-      <c r="C67" s="24">
-        <v>3</v>
-      </c>
-      <c r="D67" s="26">
+      <c r="C67" s="23">
+        <v>3</v>
+      </c>
+      <c r="D67" s="25">
         <v>13108</v>
       </c>
-      <c r="E67" s="31">
+      <c r="E67" s="30">
         <f t="shared" si="3"/>
         <v>-7.7965331920369389E-3</v>
       </c>
-      <c r="F67" s="32">
+      <c r="F67" s="31">
         <v>-0.78</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="25">
+      <c r="A68" s="24">
         <v>46232</v>
       </c>
-      <c r="B68" s="26">
+      <c r="B68" s="25">
         <v>12971</v>
       </c>
-      <c r="C68" s="24">
-        <v>3</v>
-      </c>
-      <c r="D68" s="26">
+      <c r="C68" s="23">
+        <v>3</v>
+      </c>
+      <c r="D68" s="25">
         <v>12974</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="30">
         <f t="shared" si="3"/>
         <v>-1.0222764723832774E-2</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="31">
         <v>-1.02</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="25">
+      <c r="A69" s="24">
         <v>46233</v>
       </c>
-      <c r="B69" s="26">
+      <c r="B69" s="25">
         <v>13004</v>
       </c>
-      <c r="C69" s="24">
-        <v>3</v>
-      </c>
-      <c r="D69" s="26">
+      <c r="C69" s="23">
+        <v>3</v>
+      </c>
+      <c r="D69" s="25">
         <v>13007</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="30">
         <f t="shared" si="3"/>
         <v>2.5435486357330045E-3</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="31">
         <v>0.25</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="25">
+      <c r="A70" s="24">
         <v>46234</v>
       </c>
-      <c r="B70" s="26">
+      <c r="B70" s="25">
         <v>12822</v>
       </c>
-      <c r="C70" s="24">
-        <v>3</v>
-      </c>
-      <c r="D70" s="26">
+      <c r="C70" s="23">
+        <v>3</v>
+      </c>
+      <c r="D70" s="25">
         <v>12825</v>
       </c>
-      <c r="E70" s="31">
+      <c r="E70" s="30">
         <f t="shared" si="3"/>
         <v>-1.3992465595448604E-2</v>
       </c>
-      <c r="F70" s="32">
+      <c r="F70" s="31">
         <v>-1.4</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="25">
+      <c r="A71" s="24">
         <v>46237</v>
       </c>
-      <c r="B71" s="26">
+      <c r="B71" s="25">
         <v>13167</v>
       </c>
-      <c r="C71" s="24">
-        <v>3</v>
-      </c>
-      <c r="D71" s="26">
+      <c r="C71" s="23">
+        <v>3</v>
+      </c>
+      <c r="D71" s="25">
         <v>13170</v>
       </c>
-      <c r="E71" s="31">
+      <c r="E71" s="30">
         <f t="shared" si="3"/>
         <v>2.6900584795321637E-2</v>
       </c>
-      <c r="F71" s="32">
+      <c r="F71" s="31">
         <v>2.69</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="25">
+      <c r="A72" s="24">
         <v>46238</v>
       </c>
-      <c r="B72" s="26">
+      <c r="B72" s="25">
         <v>13114</v>
       </c>
-      <c r="C72" s="24">
-        <v>3</v>
-      </c>
-      <c r="D72" s="26">
+      <c r="C72" s="23">
+        <v>3</v>
+      </c>
+      <c r="D72" s="25">
         <v>13117</v>
       </c>
-      <c r="E72" s="31">
+      <c r="E72" s="30">
         <f t="shared" si="3"/>
         <v>-4.0242976461655278E-3</v>
       </c>
-      <c r="F72" s="32">
+      <c r="F72" s="31">
         <v>-4.4000000000000004</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="25">
+      <c r="A73" s="24">
         <v>46239</v>
       </c>
-      <c r="B73" s="26">
+      <c r="B73" s="25">
         <v>13146</v>
       </c>
-      <c r="C73" s="24">
-        <v>3</v>
-      </c>
-      <c r="D73" s="26">
+      <c r="C73" s="23">
+        <v>3</v>
+      </c>
+      <c r="D73" s="25">
         <v>13149</v>
       </c>
-      <c r="E73" s="31">
+      <c r="E73" s="30">
         <f t="shared" si="3"/>
         <v>2.4395822215445605E-3</v>
       </c>
-      <c r="F73" s="32">
+      <c r="F73" s="31">
         <v>0.24</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" s="25">
+      <c r="A74" s="24">
         <v>46240</v>
       </c>
-      <c r="B74" s="26">
+      <c r="B74" s="25">
         <v>13234</v>
       </c>
-      <c r="C74" s="24">
-        <v>3</v>
-      </c>
-      <c r="D74" s="26">
+      <c r="C74" s="23">
+        <v>3</v>
+      </c>
+      <c r="D74" s="25">
         <v>13237</v>
       </c>
-      <c r="E74" s="31">
+      <c r="E74" s="30">
         <f t="shared" si="3"/>
         <v>6.6925241463229139E-3</v>
       </c>
-      <c r="F74" s="32">
+      <c r="F74" s="31">
         <v>0.67</v>
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="25">
+      <c r="A75" s="24">
         <v>46241</v>
       </c>
-      <c r="B75" s="26">
+      <c r="B75" s="25">
         <v>13266</v>
       </c>
-      <c r="C75" s="24">
-        <v>3</v>
-      </c>
-      <c r="D75" s="26">
+      <c r="C75" s="23">
+        <v>3</v>
+      </c>
+      <c r="D75" s="25">
         <v>13269</v>
       </c>
-      <c r="E75" s="31">
+      <c r="E75" s="30">
         <f t="shared" si="3"/>
         <v>2.4174661932462038E-3</v>
       </c>
-      <c r="F75" s="32">
+      <c r="F75" s="31">
         <v>0.24</v>
       </c>
     </row>
     <row r="76" spans="1:6">
-      <c r="A76" s="25">
+      <c r="A76" s="24">
         <v>46244</v>
       </c>
-      <c r="B76" s="26">
+      <c r="B76" s="25">
         <v>13237</v>
       </c>
-      <c r="C76" s="24">
-        <v>3</v>
-      </c>
-      <c r="D76" s="26">
+      <c r="C76" s="23">
+        <v>3</v>
+      </c>
+      <c r="D76" s="25">
         <v>13240</v>
       </c>
-      <c r="E76" s="31">
-        <f t="shared" ref="E76:E110" si="4">+((D76-D75)/D75)</f>
+      <c r="E76" s="30">
+        <f t="shared" ref="E76:E111" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
-      <c r="F76" s="32">
+      <c r="F76" s="31">
         <v>0.22</v>
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="A77" s="25">
+      <c r="A77" s="24">
         <v>46245</v>
       </c>
-      <c r="B77" s="26">
+      <c r="B77" s="25">
         <v>13220</v>
       </c>
-      <c r="C77" s="24">
-        <v>3</v>
-      </c>
-      <c r="D77" s="26">
+      <c r="C77" s="23">
+        <v>3</v>
+      </c>
+      <c r="D77" s="25">
         <v>13223</v>
       </c>
-      <c r="E77" s="31">
+      <c r="E77" s="30">
         <f t="shared" si="4"/>
         <v>-1.2839879154078551E-3</v>
       </c>
-      <c r="F77" s="32">
+      <c r="F77" s="31">
         <v>-0.13</v>
       </c>
     </row>
     <row r="78" spans="1:6">
-      <c r="A78" s="25">
+      <c r="A78" s="24">
         <v>46246</v>
       </c>
-      <c r="B78" s="26">
+      <c r="B78" s="25">
         <v>13231</v>
       </c>
-      <c r="C78" s="24">
-        <v>3</v>
-      </c>
-      <c r="D78" s="26">
+      <c r="C78" s="23">
+        <v>3</v>
+      </c>
+      <c r="D78" s="25">
         <v>13234</v>
       </c>
-      <c r="E78" s="31">
+      <c r="E78" s="30">
         <f t="shared" si="4"/>
         <v>8.3188383876578692E-4</v>
       </c>
-      <c r="F78" s="32">
+      <c r="F78" s="31">
         <v>0.08</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="25">
+      <c r="A79" s="24">
         <v>46247</v>
       </c>
-      <c r="B79" s="26">
+      <c r="B79" s="25">
         <v>13147</v>
       </c>
-      <c r="C79" s="24">
-        <v>3</v>
-      </c>
-      <c r="D79" s="26">
+      <c r="C79" s="23">
+        <v>3</v>
+      </c>
+      <c r="D79" s="25">
         <v>13150</v>
       </c>
-      <c r="E79" s="31">
+      <c r="E79" s="30">
         <f t="shared" si="4"/>
         <v>-6.3472872903128303E-3</v>
       </c>
-      <c r="F79" s="32">
+      <c r="F79" s="31">
         <v>-0.63</v>
       </c>
     </row>
     <row r="80" spans="1:6">
-      <c r="A80" s="25">
+      <c r="A80" s="24">
         <v>46248</v>
       </c>
-      <c r="B80" s="26">
+      <c r="B80" s="25">
         <v>13019</v>
       </c>
-      <c r="C80" s="24">
-        <v>3</v>
-      </c>
-      <c r="D80" s="26">
+      <c r="C80" s="23">
+        <v>3</v>
+      </c>
+      <c r="D80" s="25">
         <v>13022</v>
       </c>
-      <c r="E80" s="31">
+      <c r="E80" s="30">
         <f t="shared" si="4"/>
         <v>-9.7338403041825096E-3</v>
       </c>
-      <c r="F80" s="32">
+      <c r="F80" s="31">
         <v>-97</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="25">
+      <c r="A81" s="24">
         <v>46251</v>
       </c>
-      <c r="B81" s="26">
+      <c r="B81" s="25">
         <v>13022</v>
       </c>
-      <c r="C81" s="24">
-        <v>3</v>
-      </c>
-      <c r="D81" s="26">
+      <c r="C81" s="23">
+        <v>3</v>
+      </c>
+      <c r="D81" s="25">
         <v>13025</v>
       </c>
-      <c r="E81" s="31">
+      <c r="E81" s="30">
         <f t="shared" si="4"/>
         <v>2.3037935800952235E-4</v>
       </c>
-      <c r="F81" s="32">
+      <c r="F81" s="31">
         <v>0.02</v>
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="25">
+      <c r="A82" s="24">
         <v>46252</v>
       </c>
-      <c r="B82" s="26">
+      <c r="B82" s="25">
         <v>13431</v>
       </c>
-      <c r="C82" s="24">
-        <v>3</v>
-      </c>
-      <c r="D82" s="26">
+      <c r="C82" s="23">
+        <v>3</v>
+      </c>
+      <c r="D82" s="25">
         <v>13434</v>
       </c>
-      <c r="E82" s="31">
+      <c r="E82" s="30">
         <f t="shared" si="4"/>
         <v>3.1401151631477928E-2</v>
       </c>
-      <c r="F82" s="32">
+      <c r="F82" s="31">
         <v>3.14</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="25">
+      <c r="A83" s="24">
         <v>46253</v>
       </c>
-      <c r="B83" s="26">
+      <c r="B83" s="25">
         <v>13323</v>
       </c>
-      <c r="C83" s="24">
-        <v>3</v>
-      </c>
-      <c r="D83" s="26">
+      <c r="C83" s="23">
+        <v>3</v>
+      </c>
+      <c r="D83" s="25">
         <v>13326</v>
       </c>
-      <c r="E83" s="31">
+      <c r="E83" s="30">
         <f t="shared" si="4"/>
         <v>-8.0393032603841008E-3</v>
       </c>
-      <c r="F83" s="32">
+      <c r="F83" s="31">
         <v>-0.8</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="25">
+      <c r="A84" s="24">
         <v>46254</v>
       </c>
-      <c r="B84" s="26">
+      <c r="B84" s="25">
         <v>13436</v>
       </c>
-      <c r="C84" s="24">
-        <v>3</v>
-      </c>
-      <c r="D84" s="26">
+      <c r="C84" s="23">
+        <v>3</v>
+      </c>
+      <c r="D84" s="25">
         <v>13439</v>
       </c>
-      <c r="E84" s="31">
+      <c r="E84" s="30">
         <f t="shared" si="4"/>
         <v>8.4796638150983032E-3</v>
       </c>
-      <c r="F84" s="32">
+      <c r="F84" s="31">
         <v>85</v>
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="25">
+      <c r="A85" s="24">
         <v>46255</v>
       </c>
-      <c r="B85" s="26">
+      <c r="B85" s="25">
         <v>13379</v>
       </c>
-      <c r="C85" s="24">
-        <v>3</v>
-      </c>
-      <c r="D85" s="26">
+      <c r="C85" s="23">
+        <v>3</v>
+      </c>
+      <c r="D85" s="25">
         <v>13382</v>
       </c>
-      <c r="E85" s="31">
+      <c r="E85" s="30">
         <f t="shared" si="4"/>
         <v>-4.2413870079619021E-3</v>
       </c>
-      <c r="F85" s="32">
+      <c r="F85" s="31">
         <v>-0.42</v>
       </c>
     </row>
     <row r="86" spans="1:6">
-      <c r="A86" s="25">
+      <c r="A86" s="24">
         <v>46258</v>
       </c>
-      <c r="B86" s="26">
+      <c r="B86" s="25">
         <v>13352</v>
       </c>
-      <c r="C86" s="24">
-        <v>3</v>
-      </c>
-      <c r="D86" s="26">
+      <c r="C86" s="23">
+        <v>3</v>
+      </c>
+      <c r="D86" s="25">
         <v>13355</v>
       </c>
-      <c r="E86" s="31">
+      <c r="E86" s="30">
         <f t="shared" si="4"/>
         <v>-2.01763562995068E-3</v>
       </c>
-      <c r="F86" s="32">
+      <c r="F86" s="31">
         <v>-0.20300000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:6">
-      <c r="A87" s="25">
+      <c r="A87" s="24">
         <v>46259</v>
       </c>
-      <c r="B87" s="26">
+      <c r="B87" s="25">
         <v>13205</v>
       </c>
-      <c r="C87" s="24">
-        <v>3</v>
-      </c>
-      <c r="D87" s="26">
+      <c r="C87" s="23">
+        <v>3</v>
+      </c>
+      <c r="D87" s="25">
         <v>13208</v>
       </c>
-      <c r="E87" s="31">
+      <c r="E87" s="30">
         <f t="shared" si="4"/>
         <v>-1.1007113440658928E-2</v>
       </c>
-      <c r="F87" s="32">
+      <c r="F87" s="31">
         <v>-1.1000000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:6">
-      <c r="A88" s="25">
+      <c r="A88" s="24">
         <v>46260</v>
       </c>
-      <c r="B88" s="26">
+      <c r="B88" s="25">
         <v>13147</v>
       </c>
-      <c r="C88" s="24">
-        <v>3</v>
-      </c>
-      <c r="D88" s="26">
+      <c r="C88" s="23">
+        <v>3</v>
+      </c>
+      <c r="D88" s="25">
         <v>13150</v>
       </c>
-      <c r="E88" s="31">
+      <c r="E88" s="30">
         <f t="shared" si="4"/>
         <v>-4.3912780133252578E-3</v>
       </c>
-      <c r="F88" s="32">
+      <c r="F88" s="31">
         <v>-4.4400000000000004</v>
       </c>
     </row>
     <row r="89" spans="1:6">
-      <c r="A89" s="25">
+      <c r="A89" s="24">
         <v>46261</v>
       </c>
-      <c r="B89" s="26">
+      <c r="B89" s="25">
         <v>13053</v>
       </c>
-      <c r="C89" s="24">
-        <v>3</v>
-      </c>
-      <c r="D89" s="26">
+      <c r="C89" s="23">
+        <v>3</v>
+      </c>
+      <c r="D89" s="25">
         <v>13056</v>
       </c>
-      <c r="E89" s="31">
+      <c r="E89" s="30">
         <f t="shared" si="4"/>
         <v>-7.1482889733840305E-3</v>
       </c>
-      <c r="F89" s="32">
+      <c r="F89" s="31">
         <v>-0.71</v>
       </c>
     </row>
     <row r="90" spans="1:6">
-      <c r="A90" s="25">
+      <c r="A90" s="24">
         <v>46262</v>
       </c>
-      <c r="B90" s="26">
+      <c r="B90" s="25">
         <v>13360</v>
       </c>
-      <c r="C90" s="24">
-        <v>3</v>
-      </c>
-      <c r="D90" s="26">
+      <c r="C90" s="23">
+        <v>3</v>
+      </c>
+      <c r="D90" s="25">
         <v>13363</v>
       </c>
-      <c r="E90" s="31">
+      <c r="E90" s="30">
         <f t="shared" si="4"/>
         <v>2.3514093137254902E-2</v>
       </c>
-      <c r="F90" s="32">
+      <c r="F90" s="31">
         <v>2.35</v>
       </c>
     </row>
     <row r="91" spans="1:6">
-      <c r="A91" s="25">
+      <c r="A91" s="24">
         <v>46265</v>
       </c>
-      <c r="B91" s="26">
+      <c r="B91" s="25">
         <v>13285</v>
       </c>
-      <c r="C91" s="24">
-        <v>3</v>
-      </c>
-      <c r="D91" s="26">
+      <c r="C91" s="23">
+        <v>3</v>
+      </c>
+      <c r="D91" s="25">
         <v>13288</v>
       </c>
-      <c r="E91" s="31">
+      <c r="E91" s="30">
         <f t="shared" si="4"/>
         <v>-5.612512160443014E-3</v>
       </c>
-      <c r="F91" s="32">
+      <c r="F91" s="31">
         <v>-0.56000000000000005</v>
       </c>
     </row>
     <row r="92" spans="1:6">
-      <c r="A92" s="25">
+      <c r="A92" s="24">
         <v>46266</v>
       </c>
-      <c r="B92" s="26">
+      <c r="B92" s="25">
         <v>12895</v>
       </c>
-      <c r="C92" s="24">
-        <v>3</v>
-      </c>
-      <c r="D92" s="26">
+      <c r="C92" s="23">
+        <v>3</v>
+      </c>
+      <c r="D92" s="25">
         <v>12898</v>
       </c>
-      <c r="E92" s="31">
+      <c r="E92" s="30">
         <f t="shared" si="4"/>
         <v>-2.9349789283564118E-2</v>
       </c>
-      <c r="F92" s="32">
+      <c r="F92" s="31">
         <v>-2.93</v>
       </c>
     </row>
     <row r="93" spans="1:6">
-      <c r="A93" s="25">
+      <c r="A93" s="24">
         <v>46267</v>
       </c>
-      <c r="B93" s="26">
+      <c r="B93" s="25">
         <v>12709</v>
       </c>
-      <c r="C93" s="24">
-        <v>3</v>
-      </c>
-      <c r="D93" s="26">
+      <c r="C93" s="23">
+        <v>3</v>
+      </c>
+      <c r="D93" s="25">
         <v>12712</v>
       </c>
-      <c r="E93" s="31">
+      <c r="E93" s="30">
         <f t="shared" si="4"/>
         <v>-1.4420840440378353E-2</v>
       </c>
-      <c r="F93" s="32">
+      <c r="F93" s="31">
         <v>-1.44</v>
       </c>
     </row>
     <row r="94" spans="1:6">
-      <c r="A94" s="25">
+      <c r="A94" s="24">
         <v>46268</v>
       </c>
-      <c r="B94" s="26">
+      <c r="B94" s="25">
         <v>12864</v>
       </c>
-      <c r="C94" s="24">
-        <v>3</v>
-      </c>
-      <c r="D94" s="26">
+      <c r="C94" s="23">
+        <v>3</v>
+      </c>
+      <c r="D94" s="25">
         <v>12867</v>
       </c>
-      <c r="E94" s="31">
+      <c r="E94" s="30">
         <f t="shared" si="4"/>
         <v>1.2193203272498426E-2</v>
       </c>
-      <c r="F94" s="32">
+      <c r="F94" s="31">
         <v>1.22</v>
       </c>
     </row>
     <row r="95" spans="1:6">
-      <c r="A95" s="25">
+      <c r="A95" s="24">
         <v>46269</v>
       </c>
-      <c r="B95" s="26">
+      <c r="B95" s="25">
         <v>12801</v>
       </c>
-      <c r="C95" s="24">
-        <v>3</v>
-      </c>
-      <c r="D95" s="26">
+      <c r="C95" s="23">
+        <v>3</v>
+      </c>
+      <c r="D95" s="25">
         <v>12804</v>
       </c>
-      <c r="E95" s="31">
+      <c r="E95" s="30">
         <f t="shared" si="4"/>
         <v>-4.8962462112380504E-3</v>
       </c>
-      <c r="F95" s="32">
+      <c r="F95" s="31">
         <v>-0.49</v>
       </c>
     </row>
     <row r="96" spans="1:6">
-      <c r="A96" s="25">
+      <c r="A96" s="24">
         <v>46272</v>
       </c>
-      <c r="B96" s="26">
+      <c r="B96" s="25">
         <v>12979</v>
       </c>
-      <c r="C96" s="24">
-        <v>3</v>
-      </c>
-      <c r="D96" s="26">
+      <c r="C96" s="23">
+        <v>3</v>
+      </c>
+      <c r="D96" s="25">
         <v>12982</v>
       </c>
-      <c r="E96" s="31">
+      <c r="E96" s="30">
         <f t="shared" si="4"/>
         <v>1.3901905654482974E-2</v>
       </c>
-      <c r="F96" s="32">
+      <c r="F96" s="31">
         <v>1.39</v>
       </c>
     </row>
     <row r="97" spans="1:6">
-      <c r="A97" s="25">
+      <c r="A97" s="24">
         <v>46273</v>
       </c>
-      <c r="B97" s="26">
+      <c r="B97" s="25">
         <v>12912</v>
       </c>
-      <c r="C97" s="24">
-        <v>3</v>
-      </c>
-      <c r="D97" s="26">
+      <c r="C97" s="23">
+        <v>3</v>
+      </c>
+      <c r="D97" s="25">
         <v>12915</v>
       </c>
-      <c r="E97" s="31">
+      <c r="E97" s="30">
         <f t="shared" si="4"/>
         <v>-5.1609921429671855E-3</v>
       </c>
-      <c r="F97" s="32">
+      <c r="F97" s="31">
         <v>-0.52</v>
       </c>
     </row>
     <row r="98" spans="1:6">
-      <c r="A98" s="25">
+      <c r="A98" s="24">
         <v>46274</v>
       </c>
-      <c r="B98" s="26">
+      <c r="B98" s="25">
         <v>12898</v>
       </c>
-      <c r="C98" s="24">
-        <v>3</v>
-      </c>
-      <c r="D98" s="26">
+      <c r="C98" s="23">
+        <v>3</v>
+      </c>
+      <c r="D98" s="25">
         <v>12901</v>
       </c>
-      <c r="E98" s="31">
+      <c r="E98" s="30">
         <f t="shared" si="4"/>
         <v>-1.0840108401084011E-3</v>
       </c>
-      <c r="F98" s="32">
+      <c r="F98" s="31">
         <v>-0.11</v>
       </c>
     </row>
     <row r="99" spans="1:6">
-      <c r="A99" s="25">
+      <c r="A99" s="24">
         <v>46275</v>
       </c>
-      <c r="B99" s="26">
+      <c r="B99" s="25">
         <v>12855</v>
       </c>
-      <c r="C99" s="24">
-        <v>3</v>
-      </c>
-      <c r="D99" s="26">
+      <c r="C99" s="23">
+        <v>3</v>
+      </c>
+      <c r="D99" s="25">
         <v>12858</v>
       </c>
-      <c r="E99" s="31">
+      <c r="E99" s="30">
         <f t="shared" si="4"/>
         <v>-3.3330749554298118E-3</v>
       </c>
-      <c r="F99" s="32">
+      <c r="F99" s="31">
         <v>-0.33</v>
       </c>
     </row>
     <row r="100" spans="1:6">
-      <c r="A100" s="25">
+      <c r="A100" s="24">
         <v>46276</v>
       </c>
-      <c r="B100" s="26">
+      <c r="B100" s="25">
         <v>13098</v>
       </c>
-      <c r="C100" s="24">
-        <v>3</v>
-      </c>
-      <c r="D100" s="26">
+      <c r="C100" s="23">
+        <v>3</v>
+      </c>
+      <c r="D100" s="25">
         <v>13101</v>
       </c>
-      <c r="E100" s="31">
+      <c r="E100" s="30">
         <f t="shared" si="4"/>
         <v>1.8898740083994399E-2</v>
       </c>
-      <c r="F100" s="32">
+      <c r="F100" s="31">
         <v>1.89</v>
       </c>
     </row>
     <row r="101" spans="1:6">
-      <c r="A101" s="25">
+      <c r="A101" s="24">
         <v>46280</v>
       </c>
-      <c r="B101" s="26">
+      <c r="B101" s="25">
         <v>12938</v>
       </c>
-      <c r="C101" s="24">
-        <v>3</v>
-      </c>
-      <c r="D101" s="26">
+      <c r="C101" s="23">
+        <v>3</v>
+      </c>
+      <c r="D101" s="25">
         <v>12941</v>
       </c>
-      <c r="E101" s="31">
+      <c r="E101" s="30">
         <f t="shared" si="4"/>
         <v>-1.2212808182581482E-2</v>
       </c>
-      <c r="F101" s="32">
+      <c r="F101" s="31">
         <v>-1.22</v>
       </c>
     </row>
     <row r="102" spans="1:6">
-      <c r="A102" s="25">
+      <c r="A102" s="24">
         <v>46281</v>
       </c>
-      <c r="B102" s="26">
+      <c r="B102" s="25">
         <v>12985</v>
       </c>
-      <c r="C102" s="24">
-        <v>3</v>
-      </c>
-      <c r="D102" s="26">
+      <c r="C102" s="23">
+        <v>3</v>
+      </c>
+      <c r="D102" s="25">
         <v>12988</v>
       </c>
-      <c r="E102" s="31">
+      <c r="E102" s="30">
         <f t="shared" si="4"/>
         <v>3.6318677072869174E-3</v>
       </c>
-      <c r="F102" s="32">
+      <c r="F102" s="31">
         <v>0.36</v>
       </c>
     </row>
     <row r="103" spans="1:6">
-      <c r="A103" s="25">
+      <c r="A103" s="24">
         <v>46282</v>
       </c>
-      <c r="B103" s="26">
+      <c r="B103" s="25">
         <v>12914</v>
       </c>
-      <c r="C103" s="24">
-        <v>3</v>
-      </c>
-      <c r="D103" s="26">
+      <c r="C103" s="23">
+        <v>3</v>
+      </c>
+      <c r="D103" s="25">
         <v>12917</v>
       </c>
-      <c r="E103" s="31">
+      <c r="E103" s="30">
         <f t="shared" si="4"/>
         <v>-5.4665845395749924E-3</v>
       </c>
-      <c r="F103" s="32">
+      <c r="F103" s="31">
         <v>-0.55000000000000004</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="A104" s="25">
+      <c r="A104" s="24">
         <v>46283</v>
       </c>
-      <c r="B104" s="26">
+      <c r="B104" s="25">
         <v>13335</v>
       </c>
-      <c r="C104" s="24">
-        <v>3</v>
-      </c>
-      <c r="D104" s="26">
+      <c r="C104" s="23">
+        <v>3</v>
+      </c>
+      <c r="D104" s="25">
         <v>13338</v>
       </c>
-      <c r="E104" s="31">
+      <c r="E104" s="30">
         <f t="shared" si="4"/>
         <v>3.2592707284973294E-2</v>
       </c>
-      <c r="F104" s="32">
+      <c r="F104" s="31">
         <v>3.26</v>
       </c>
     </row>
     <row r="105" spans="1:6">
-      <c r="A105" s="25">
+      <c r="A105" s="24">
         <v>46286</v>
       </c>
-      <c r="B105" s="26">
+      <c r="B105" s="25">
         <v>13272</v>
       </c>
-      <c r="C105" s="24">
-        <v>3</v>
-      </c>
-      <c r="D105" s="26">
+      <c r="C105" s="23">
+        <v>3</v>
+      </c>
+      <c r="D105" s="25">
         <v>13275</v>
       </c>
-      <c r="E105" s="31">
+      <c r="E105" s="30">
         <f t="shared" si="4"/>
         <v>-4.7233468286099868E-3</v>
       </c>
-      <c r="F105" s="32">
+      <c r="F105" s="31">
         <v>-0.47</v>
       </c>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="25">
+      <c r="A106" s="24">
         <v>46287</v>
       </c>
-      <c r="B106" s="26">
+      <c r="B106" s="25">
         <v>13034</v>
       </c>
-      <c r="C106" s="24">
-        <v>3</v>
-      </c>
-      <c r="D106" s="26">
+      <c r="C106" s="23">
+        <v>3</v>
+      </c>
+      <c r="D106" s="25">
         <v>13037</v>
       </c>
-      <c r="E106" s="31">
+      <c r="E106" s="30">
         <f t="shared" si="4"/>
         <v>-1.7928436911487759E-2</v>
       </c>
-      <c r="F106" s="32">
+      <c r="F106" s="31">
         <v>-1.79</v>
       </c>
     </row>
     <row r="107" spans="1:6">
-      <c r="A107" s="25">
+      <c r="A107" s="24">
         <v>46288</v>
       </c>
-      <c r="B107" s="26">
+      <c r="B107" s="25">
         <v>12909</v>
       </c>
-      <c r="C107" s="24">
-        <v>3</v>
-      </c>
-      <c r="D107" s="26">
+      <c r="C107" s="23">
+        <v>3</v>
+      </c>
+      <c r="D107" s="25">
         <v>12912</v>
       </c>
-      <c r="E107" s="31">
+      <c r="E107" s="30">
         <f t="shared" si="4"/>
         <v>-9.5880954207256276E-3</v>
       </c>
-      <c r="F107" s="32">
+      <c r="F107" s="31">
         <v>-9.5880954207256276E-3</v>
       </c>
     </row>
     <row r="108" spans="1:6">
-      <c r="A108" s="25">
+      <c r="A108" s="24">
         <v>46289</v>
       </c>
-      <c r="B108" s="26">
+      <c r="B108" s="25">
         <v>12762</v>
       </c>
-      <c r="C108" s="24">
-        <v>3</v>
-      </c>
-      <c r="D108" s="26">
+      <c r="C108" s="23">
+        <v>3</v>
+      </c>
+      <c r="D108" s="25">
         <f t="shared" ref="D108" si="5">SUM(B108+C108)</f>
         <v>12765</v>
       </c>
-      <c r="E108" s="31">
+      <c r="E108" s="30">
         <f t="shared" si="4"/>
         <v>-1.1384758364312268E-2</v>
       </c>
-      <c r="F108" s="32">
+      <c r="F108" s="31">
         <v>-1.1384758364312268E-2</v>
       </c>
     </row>
     <row r="109" spans="1:6">
-      <c r="A109" s="25">
+      <c r="A109" s="24">
         <v>46290</v>
       </c>
-      <c r="B109" s="26">
+      <c r="B109" s="25">
         <v>12724</v>
       </c>
-      <c r="C109" s="24">
-        <v>3</v>
-      </c>
-      <c r="D109" s="26">
+      <c r="C109" s="23">
+        <v>3</v>
+      </c>
+      <c r="D109" s="25">
         <f t="shared" ref="D109" si="6">SUM(B109+C109)</f>
         <v>12727</v>
       </c>
-      <c r="E109" s="31">
+      <c r="E109" s="30">
         <f t="shared" si="4"/>
         <v>-2.9768899334116725E-3</v>
       </c>
-      <c r="F109" s="32">
+      <c r="F109" s="31">
         <v>-0.3</v>
       </c>
     </row>
     <row r="110" spans="1:6">
-      <c r="A110" s="25">
+      <c r="A110" s="24">
         <v>46293</v>
       </c>
-      <c r="B110" s="26">
+      <c r="B110" s="25">
         <v>12720</v>
       </c>
-      <c r="C110" s="24">
-        <v>3</v>
-      </c>
-      <c r="D110" s="26">
+      <c r="C110" s="23">
+        <v>3</v>
+      </c>
+      <c r="D110" s="25">
         <v>12723</v>
       </c>
-      <c r="E110" s="31">
+      <c r="E110" s="30">
         <f t="shared" si="4"/>
         <v>-3.1429244912390981E-4</v>
       </c>
-      <c r="F110" s="32">
+      <c r="F110" s="31">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" s="24">
+        <v>46294</v>
+      </c>
+      <c r="B111" s="25">
+        <v>12666</v>
+      </c>
+      <c r="C111" s="23">
+        <v>3</v>
+      </c>
+      <c r="D111" s="25">
+        <v>12669</v>
+      </c>
+      <c r="E111" s="30">
+        <f t="shared" si="4"/>
+        <v>-4.2442820089601506E-3</v>
+      </c>
+      <c r="F111" s="31">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="2"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -152,14 +152,14 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _B_s_-;\-* #,##0.00\ _B_s_-;_-* &quot;-&quot;??\ _B_s_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_([$€-2]\ * #,##0.00_);_([$€-2]\ * \(#,##0.00\);_([$€-2]\ * &quot;-&quot;??_)"/>
     <numFmt numFmtId="168" formatCode="_([$€]* #,##0.00_);_([$€]* \(#,##0.00\);_([$€]* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="172" formatCode="#.##000"/>
-    <numFmt numFmtId="173" formatCode="\$#,#00"/>
-    <numFmt numFmtId="174" formatCode="#,#00"/>
-    <numFmt numFmtId="175" formatCode="#.##0,"/>
-    <numFmt numFmtId="176" formatCode="\$#,"/>
-    <numFmt numFmtId="177" formatCode="_-[$€]* #,##0.00_-;\-[$€]* #,##0.00_-;_-[$€]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="171" formatCode="#.##000"/>
+    <numFmt numFmtId="172" formatCode="\$#,#00"/>
+    <numFmt numFmtId="173" formatCode="#,#00"/>
+    <numFmt numFmtId="174" formatCode="#.##0,"/>
+    <numFmt numFmtId="175" formatCode="\$#,"/>
+    <numFmt numFmtId="176" formatCode="_-[$€]* #,##0.00_-;\-[$€]* #,##0.00_-;_-[$€]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -1609,29 +1609,29 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="177" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="174" fontId="26" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="173" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="172" fontId="26" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="172" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="171" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0">
+    <xf numFmtId="174" fontId="26" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="13">
@@ -2990,7 +2990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2998,7 +2998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5497,6 +5497,26 @@
         <v>58.03</v>
       </c>
     </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="20">
+        <v>46296</v>
+      </c>
+      <c r="B130" s="16">
+        <v>23187.184927999999</v>
+      </c>
+      <c r="C130" s="19"/>
+      <c r="D130" s="16">
+        <v>1</v>
+      </c>
+      <c r="E130" s="19"/>
+      <c r="F130" s="16">
+        <v>5</v>
+      </c>
+      <c r="G130" s="19"/>
+      <c r="H130" s="16">
+        <v>1.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5505,7 +5525,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5534,14 +5554,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B2" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C2" s="29">
         <f>+(B2-B3)/B3</f>
-        <v>8.8268407504102413</v>
+        <v>0.35910087116479922</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5552,14 +5572,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B3" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C3" s="29">
         <f>+(B3-B4)/B4</f>
-        <v>-0.85681185394119452</v>
+        <v>8.8268407504102413</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5570,14 +5590,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B4" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C4" s="29">
         <f>+(B4-B5)/B5</f>
-        <v>-0.49898704513189668</v>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5588,14 +5608,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B5" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C5" s="29">
         <f>+(B5-B6)/B6</f>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5606,14 +5626,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B6" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C6" s="29">
-        <f t="shared" ref="C6:C75" si="0">+(B6-B7)/B7</f>
-        <v>5.2320875570372835E-2</v>
+        <f>+(B6-B7)/B7</f>
+        <v>0.55858664283872839</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5624,1413 +5644,1425 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B7" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C7" s="29">
+        <f t="shared" ref="C7:C76" si="0">+(B7-B8)/B8</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24">
         <v>46288</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B8" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C8" s="29">
         <f t="shared" si="0"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="24">
+      <c r="D8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="33">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24">
         <v>46287</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B9" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="33">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="24">
+      <c r="D9" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24">
         <v>46286</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B10" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="24">
+      <c r="D10" s="23"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46283</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="34"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46282</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46281</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46280</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>0.37097114686342592</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46276</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="0"/>
         <v>-0.67806849277578529</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46275</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="0"/>
         <v>18.560573043109468</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46274</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="0"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46273</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="0"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46272</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="0"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46269</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="0"/>
         <v>-0.97953700801723442</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46268</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="0"/>
         <v>80.163058476193896</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46267</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="0"/>
         <v>-0.77463732472189939</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46266</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="0"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46265</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="0"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46262</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="0"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46261</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="0"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46260</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="0"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46259</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="0"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46256</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="0"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46255</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="0"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46254</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="0"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46253</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="0"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46252</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="0"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46251</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="0"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46248</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="0"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46247</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="0"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46246</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="0"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46245</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="0"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46244</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="0"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46241</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="0"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46240</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="0"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46239</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="0"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46238</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="0"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46237</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="0"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46234</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="0"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46233</v>
       </c>
-      <c r="B45">
+      <c r="B46">
         <v>466.33578662999997</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="0"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46232</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="0"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46231</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="0"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46108</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="0"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46226</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="0"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46225</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="0"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46224</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="0"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46220</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="0"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46219</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="0"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46218</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="0"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46217</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="0"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46216</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="0"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46213</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="0"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46212</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="0"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46211</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="0"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46210</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="0"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46209</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="0"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46206</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="0"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46205</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="0"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46204</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="0"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46203</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="0"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46198</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="0"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46196</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="0"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46195</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="0"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46192</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="0"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46191</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="0"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46190</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="0"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46189</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="0"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46188</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>8.42</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="0"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46185</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="0"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46184</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="0"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B76" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C76" s="29">
-        <f t="shared" ref="C76:C117" si="1">+(B76-B77)/B77</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="77" spans="1:3">
       <c r="A77" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B77" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C77" s="29">
+        <f t="shared" ref="C77:C118" si="1">+(B77-B78)/B78</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46182</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46178</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46177</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46176</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46175</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46174</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46171</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>45074</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46169</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46168</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46167</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46164</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46163</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46162</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46161</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46157</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46156</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46155</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46154</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46153</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46150</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="22">
+    <row r="99" spans="1:4">
+      <c r="A99" s="22">
         <v>46149</v>
       </c>
-      <c r="B98" s="21">
+      <c r="B99" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="17">
+    <row r="100" spans="1:4">
+      <c r="A100" s="17">
         <v>46148</v>
       </c>
-      <c r="B99" s="15">
+      <c r="B100" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="17">
+    <row r="101" spans="1:4">
+      <c r="A101" s="17">
         <v>46147</v>
       </c>
-      <c r="B100" s="15">
+      <c r="B101" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="17">
+    <row r="102" spans="1:4">
+      <c r="A102" s="17">
         <v>46146</v>
       </c>
-      <c r="B101" s="15">
+      <c r="B102" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="18">
+    <row r="103" spans="1:4">
+      <c r="A103" s="18">
         <v>46142</v>
       </c>
-      <c r="B102" s="15">
+      <c r="B103" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="18">
+    <row r="104" spans="1:4">
+      <c r="A104" s="18">
         <v>46141</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B104" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="18">
+    <row r="105" spans="1:4">
+      <c r="A105" s="18">
         <v>46140</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B105" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="18">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="18">
         <v>46139</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B106" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="18">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="18">
         <v>46136</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B107" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="18">
+    <row r="108" spans="1:4">
+      <c r="A108" s="18">
         <v>46135</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B108" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="18">
+    <row r="109" spans="1:4">
+      <c r="A109" s="18">
         <v>46134</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="18">
+    <row r="110" spans="1:4">
+      <c r="A110" s="18">
         <v>46133</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="18">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46132</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46129</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46128</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46127</v>
       </c>
-      <c r="B113" s="38">
+      <c r="B114" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46126</v>
       </c>
-      <c r="B114" s="38">
+      <c r="B115" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46125</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46122</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46121</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B118" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C118" s="29">
-        <f>+(B118-B119)/B119</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="119" spans="1:3">
       <c r="A119" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B119" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C119" s="29">
+        <f>+(B119-B120)/B120</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B120" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B121" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B122" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B123" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46111</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8232,7 +8264,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9830,7 +9862,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E111" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E112" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -10572,6 +10604,27 @@
       </c>
       <c r="F111" s="31">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" s="24">
+        <v>46295</v>
+      </c>
+      <c r="B112" s="25">
+        <v>12798</v>
+      </c>
+      <c r="C112" s="23">
+        <v>3</v>
+      </c>
+      <c r="D112" s="25">
+        <v>12801</v>
+      </c>
+      <c r="E112" s="30">
+        <f t="shared" si="4"/>
+        <v>1.0419133317546767E-2</v>
+      </c>
+      <c r="F112" s="31">
+        <v>1.04</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2990,7 +2990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7173,7 +7173,7 @@
         <v>7419.8662599523823</v>
       </c>
       <c r="D6" s="16">
-        <v>40.529003233410926</v>
+        <v>40.520000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="2"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2990,7 +2990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2998,7 +2998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5517,6 +5517,26 @@
         <v>1.56</v>
       </c>
     </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="20">
+        <v>46297</v>
+      </c>
+      <c r="B131" s="16">
+        <v>4500</v>
+      </c>
+      <c r="C131" s="19"/>
+      <c r="D131" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="E131" s="19"/>
+      <c r="F131" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G131" s="19"/>
+      <c r="H131" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5525,7 +5545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5554,14 +5574,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B2" s="23">
-        <v>274113.44695601001</v>
+        <v>346430.12939344998</v>
       </c>
       <c r="C2" s="29">
         <f>+(B2-B3)/B3</f>
-        <v>0.35910087116479922</v>
+        <v>0.2638202658078479</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5572,14 +5592,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B3" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C3" s="29">
         <f>+(B3-B4)/B4</f>
-        <v>8.8268407504102413</v>
+        <v>0.35910087116479922</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5590,14 +5610,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B4" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C4" s="29">
         <f>+(B4-B5)/B5</f>
-        <v>-0.85681185394119452</v>
+        <v>8.8268407504102413</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5608,14 +5628,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B5" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C5" s="29">
         <f>+(B5-B6)/B6</f>
-        <v>-0.49898704513189668</v>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5626,14 +5646,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B6" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C6" s="29">
         <f>+(B6-B7)/B7</f>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5644,14 +5664,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B7" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C7" s="29">
-        <f t="shared" ref="C7:C76" si="0">+(B7-B8)/B8</f>
-        <v>5.2320875570372835E-2</v>
+        <f>+(B7-B8)/B8</f>
+        <v>0.55858664283872839</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5662,1407 +5682,1419 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B8" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C8" s="29">
+        <f t="shared" ref="C8:C77" si="0">+(B8-B9)/B9</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="33">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24">
         <v>46288</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B9" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="33">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="24">
+      <c r="D9" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24">
         <v>46287</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B10" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="24">
+      <c r="D10" s="23"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46286</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="34"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46283</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46282</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46281</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>54.85948274687906</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46280</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="0"/>
         <v>0.37097114686342592</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46276</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="0"/>
         <v>-0.67806849277578529</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46275</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="0"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46274</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="0"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46273</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="0"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46272</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="0"/>
         <v>2.4737529624349173</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46269</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="0"/>
         <v>-0.97953700801723442</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46268</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="0"/>
         <v>80.163058476193896</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46267</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="0"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46266</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="0"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46265</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="0"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46262</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="0"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46261</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="0"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46260</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="0"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46259</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="0"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46256</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="0"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46255</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="0"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46254</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="0"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46253</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="0"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46252</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="0"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46251</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="0"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46248</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="0"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46247</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="0"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46246</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="0"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46245</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="0"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46244</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="0"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46241</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="0"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46240</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="0"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46239</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="0"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46238</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="0"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46237</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="0"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46234</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="0"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46233</v>
       </c>
-      <c r="B46">
+      <c r="B47">
         <v>466.33578662999997</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="0"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46232</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="0"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46231</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="0"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46108</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="0"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46226</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="0"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46225</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="0"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46224</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="0"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46220</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="0"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46219</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="0"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46218</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="0"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46217</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="0"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46216</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="0"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46213</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="0"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46212</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="0"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46211</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="0"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46210</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="0"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46209</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="0"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46206</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="0"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46205</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="0"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46204</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="0"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46203</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="0"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46198</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="0"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46196</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="0"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46195</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="0"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46192</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="0"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46191</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="0"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46190</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="0"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46189</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="0"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46188</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>8.42</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="0"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46185</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="0"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46184</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="0"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B77" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C77" s="29">
-        <f t="shared" ref="C77:C118" si="1">+(B77-B78)/B78</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="78" spans="1:3">
       <c r="A78" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B78" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C78" s="29">
+        <f t="shared" ref="C78:C119" si="1">+(B78-B79)/B79</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46182</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46178</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46177</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46176</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46175</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46174</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="1"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46171</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="1"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>45074</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="1"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46169</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="1"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46168</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="1"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46167</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="1"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46164</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="1"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46163</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="1"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46162</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="1"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46161</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="1"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46157</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="1"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46156</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="1"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46155</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="1"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46154</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="1"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46153</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="1"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46150</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="1"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="22">
+    <row r="100" spans="1:4">
+      <c r="A100" s="22">
         <v>46149</v>
       </c>
-      <c r="B99" s="21">
+      <c r="B100" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="1"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="17">
+    <row r="101" spans="1:4">
+      <c r="A101" s="17">
         <v>46148</v>
       </c>
-      <c r="B100" s="15">
+      <c r="B101" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="1"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="17">
+    <row r="102" spans="1:4">
+      <c r="A102" s="17">
         <v>46147</v>
       </c>
-      <c r="B101" s="15">
+      <c r="B102" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="1"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="17">
+    <row r="103" spans="1:4">
+      <c r="A103" s="17">
         <v>46146</v>
       </c>
-      <c r="B102" s="15">
+      <c r="B103" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="1"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="18">
+    <row r="104" spans="1:4">
+      <c r="A104" s="18">
         <v>46142</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B104" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="1"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="18">
+    <row r="105" spans="1:4">
+      <c r="A105" s="18">
         <v>46141</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B105" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="1"/>
         <v>-0.59636256133262866</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="18">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="18">
         <v>46140</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B106" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="1"/>
         <v>0.74333012643706198</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="18">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="18">
         <v>46139</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B107" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="1"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="18">
+    <row r="108" spans="1:4">
+      <c r="A108" s="18">
         <v>46136</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B108" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="1"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="18">
+    <row r="109" spans="1:4">
+      <c r="A109" s="18">
         <v>46135</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="1"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="18">
+    <row r="110" spans="1:4">
+      <c r="A110" s="18">
         <v>46134</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="1"/>
         <v>-0.64046760511667533</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="18">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46133</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="1"/>
         <v>-6.5402088492716129E-2</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46132</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="1"/>
         <v>1.9819948129202027</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46129</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="1"/>
         <v>910.40237411852581</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46128</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="1"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46127</v>
       </c>
-      <c r="B114" s="38">
+      <c r="B115" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="1"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46126</v>
       </c>
-      <c r="B115" s="38">
+      <c r="B116" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="1"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46125</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="1"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46122</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="1"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46121</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="1"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B119" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C119" s="29">
-        <f>+(B119-B120)/B120</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="120" spans="1:3">
       <c r="A120" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B120" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C120" s="29">
+        <f>+(B120-B121)/B121</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B121" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B122" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B123" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B124" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46111</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B125" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7184,7 +7216,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -7389,7 +7421,7 @@
         <v>1452167458.20135</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" ref="C18:C28" si="0">+((B18-B17)/B17)*100</f>
+        <f t="shared" ref="C18:C29" si="0">+((B18-B17)/B17)*100</f>
         <v>0.77731466473397282</v>
       </c>
     </row>
@@ -7513,6 +7545,18 @@
       <c r="C28" s="4">
         <f t="shared" si="0"/>
         <v>6.6848585352459482</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" thickBot="1">
+      <c r="A29" s="24">
+        <v>46290</v>
+      </c>
+      <c r="B29" s="16">
+        <v>1840960656.3900001</v>
+      </c>
+      <c r="C29" s="4">
+        <f t="shared" si="0"/>
+        <v>6.1047366051644163</v>
       </c>
     </row>
   </sheetData>
@@ -8242,13 +8286,30 @@
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="26"/>
+      <c r="A28" s="24">
+        <v>46290</v>
+      </c>
+      <c r="B28" s="16">
+        <v>82724239.333660007</v>
+      </c>
+      <c r="C28" s="16">
+        <v>2636631655.8762808</v>
+      </c>
+      <c r="D28" s="16">
+        <v>232397280.81039</v>
+      </c>
+      <c r="E28" s="16">
+        <v>2951753176.0203309</v>
+      </c>
+      <c r="F28" s="16">
+        <v>18233253.49667</v>
+      </c>
+      <c r="G28" s="16">
+        <v>2969986429.5170007</v>
+      </c>
+      <c r="H28" s="26">
+        <v>4.6084436160741538</v>
+      </c>
     </row>
     <row r="29" spans="1:8">
       <c r="B29" s="16"/>
@@ -8264,7 +8325,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G112"/>
+  <dimension ref="A1:G113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9862,7 +9923,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E112" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E113" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -10625,6 +10686,27 @@
       </c>
       <c r="F112" s="31">
         <v>1.04</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" s="24">
+        <v>46296</v>
+      </c>
+      <c r="B113" s="25">
+        <v>12719</v>
+      </c>
+      <c r="C113" s="23">
+        <v>3</v>
+      </c>
+      <c r="D113" s="25">
+        <v>12722</v>
+      </c>
+      <c r="E113" s="30">
+        <f t="shared" si="4"/>
+        <v>-6.171392859932818E-3</v>
+      </c>
+      <c r="F113" s="31">
+        <v>-0.62</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2990,7 +2990,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2998,7 +2998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5537,6 +5537,26 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="20">
+        <v>46300</v>
+      </c>
+      <c r="B132" s="7">
+        <v>0</v>
+      </c>
+      <c r="C132" s="23"/>
+      <c r="D132" s="16">
+        <v>0</v>
+      </c>
+      <c r="E132" s="23"/>
+      <c r="F132" s="16">
+        <v>0</v>
+      </c>
+      <c r="G132" s="23"/>
+      <c r="H132" s="16">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5545,7 +5565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5574,14 +5594,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B2" s="23">
-        <v>346430.12939344998</v>
+        <v>298642.62637141999</v>
       </c>
       <c r="C2" s="29">
-        <f>+(B2-B3)/B3</f>
-        <v>0.2638202658078479</v>
+        <f t="shared" ref="C2:C8" si="0">+(B2-B3)/B3</f>
+        <v>-0.13794268733409284</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5592,14 +5612,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B3" s="23">
-        <v>274113.44695601001</v>
+        <v>346430.12939344998</v>
       </c>
       <c r="C3" s="29">
-        <f>+(B3-B4)/B4</f>
-        <v>0.35910087116479922</v>
+        <f t="shared" si="0"/>
+        <v>0.2638202658078479</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5610,14 +5630,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B4" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C4" s="29">
-        <f>+(B4-B5)/B5</f>
-        <v>8.8268407504102413</v>
+        <f t="shared" si="0"/>
+        <v>0.35910087116479922</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5628,14 +5648,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B5" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C5" s="29">
-        <f>+(B5-B6)/B6</f>
-        <v>-0.85681185394119452</v>
+        <f t="shared" si="0"/>
+        <v>8.8268407504102413</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5646,14 +5666,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B6" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C6" s="29">
-        <f>+(B6-B7)/B7</f>
-        <v>-0.49898704513189668</v>
+        <f t="shared" si="0"/>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5664,14 +5684,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B7" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C7" s="29">
-        <f>+(B7-B8)/B8</f>
-        <v>0.55858664283872839</v>
+        <f t="shared" si="0"/>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5682,14 +5702,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B8" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C8" s="29">
-        <f t="shared" ref="C8:C77" si="0">+(B8-B9)/B9</f>
-        <v>5.2320875570372835E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.55858664283872839</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5700,14 +5720,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B9" s="23">
-        <v>174433.37119511</v>
+        <v>183559.87790473</v>
       </c>
       <c r="C9" s="29">
-        <f t="shared" si="0"/>
-        <v>0.18793186198768058</v>
+        <f t="shared" ref="C9:C78" si="1">+(B9-B10)/B10</f>
+        <v>5.2320875570372835E-2</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5718,1383 +5738,1395 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B10" s="23">
-        <v>146837.85895197999</v>
+        <v>174433.37119511</v>
       </c>
       <c r="C10" s="29">
-        <f t="shared" si="0"/>
-        <v>6.7871692861553368E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.18793186198768058</v>
       </c>
       <c r="D10" s="23"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B11" s="23">
-        <v>137505.15153979001</v>
+        <v>146837.85895197999</v>
       </c>
       <c r="C11" s="29">
-        <f t="shared" si="0"/>
-        <v>0.25618058698994745</v>
+        <f t="shared" si="1"/>
+        <v>6.7871692861553368E-2</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B12" s="23">
-        <v>109462.8853239</v>
+        <v>137505.15153979001</v>
       </c>
       <c r="C12" s="29">
-        <f t="shared" si="0"/>
-        <v>0.32349555871151542</v>
+        <f t="shared" si="1"/>
+        <v>0.25618058698994745</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="24">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B13" s="23">
-        <v>82707.40661228</v>
+        <v>109462.8853239</v>
       </c>
       <c r="C13" s="29">
-        <f t="shared" si="0"/>
-        <v>28.486447660130633</v>
+        <f t="shared" si="1"/>
+        <v>0.32349555871151542</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="24">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B14" s="23">
-        <v>2804.9294905100001</v>
+        <v>82707.40661228</v>
       </c>
       <c r="C14" s="29">
-        <f t="shared" si="0"/>
-        <v>54.85948274687906</v>
+        <f t="shared" si="1"/>
+        <v>28.486447660130633</v>
       </c>
       <c r="E14" s="35"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="24">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B15" s="23">
-        <v>50.214025489999997</v>
+        <v>2804.9294905100001</v>
       </c>
       <c r="C15" s="29">
-        <f t="shared" si="0"/>
-        <v>0.37097114686342592</v>
+        <f t="shared" si="1"/>
+        <v>54.85948274687906</v>
       </c>
       <c r="E15" s="35"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="24">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B16" s="23">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C16" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.67806849277578529</v>
+        <f t="shared" si="1"/>
+        <v>0.37097114686342592</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="24">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B17" s="23">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C17" s="29">
-        <f t="shared" si="0"/>
-        <v>18.560573043109468</v>
+        <f t="shared" si="1"/>
+        <v>-0.67806849277578529</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="24">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B18" s="23">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C18" s="29">
-        <f t="shared" si="0"/>
-        <v>0.64045278098882874</v>
+        <f t="shared" si="1"/>
+        <v>18.560573043109468</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="24">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B19" s="23">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C19" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.82640880552358198</v>
+        <f t="shared" si="1"/>
+        <v>0.64045278098882874</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="24">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B20" s="23">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C20" s="29">
-        <f t="shared" si="0"/>
-        <v>2.4737529624349173</v>
+        <f t="shared" si="1"/>
+        <v>-0.82640880552358198</v>
       </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="24">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B21" s="23">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C21" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.97953700801723442</v>
+        <f t="shared" si="1"/>
+        <v>2.4737529624349173</v>
       </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="24">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B22" s="23">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C22" s="29">
-        <f t="shared" si="0"/>
-        <v>80.163058476193896</v>
+        <f t="shared" si="1"/>
+        <v>-0.97953700801723442</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="24">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="23">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C23" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.77463732472189939</v>
+        <f t="shared" si="1"/>
+        <v>80.163058476193896</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="24">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B24" s="23">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C24" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.99727371031195</v>
+        <f t="shared" si="1"/>
+        <v>-0.77463732472189939</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="24">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B25" s="23">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C25" s="29">
-        <f t="shared" si="0"/>
-        <v>1028.4103166122507</v>
+        <f t="shared" si="1"/>
+        <v>-0.99727371031195</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="24">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B26" s="23">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C26" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.98760095272084658</v>
+        <f t="shared" si="1"/>
+        <v>1028.4103166122507</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="24">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B27" s="23">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C27" s="29">
-        <f t="shared" si="0"/>
-        <v>98.812318362183703</v>
+        <f t="shared" si="1"/>
+        <v>-0.98760095272084658</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="24">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B28" s="23">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C28" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.9864837734804992</v>
+        <f t="shared" si="1"/>
+        <v>98.812318362183703</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="24">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B29" s="23">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C29" s="29">
-        <f t="shared" si="0"/>
-        <v>74.639780601233326</v>
+        <f t="shared" si="1"/>
+        <v>-0.9864837734804992</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="24">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B30" s="23">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C30" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.96494750708048294</v>
+        <f t="shared" si="1"/>
+        <v>74.639780601233326</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="24">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B31" s="23">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C31" s="29">
-        <f t="shared" si="0"/>
-        <v>71.190985743560688</v>
+        <f t="shared" si="1"/>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="24">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B32" s="23">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C32" s="29">
-        <f t="shared" si="0"/>
-        <v>-5.8184422793468707E-2</v>
+        <f t="shared" si="1"/>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="24">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B33" s="23">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C33" s="29">
-        <f t="shared" si="0"/>
-        <v>2.7977445325652688E-3</v>
+        <f t="shared" si="1"/>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="24">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B34" s="23">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C34" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.85226798513183877</v>
+        <f t="shared" si="1"/>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="24">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B35" s="23">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C35" s="29">
-        <f t="shared" si="0"/>
-        <v>1.9051656117130662</v>
+        <f t="shared" si="1"/>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="24">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B36" s="23">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C36" s="29">
-        <f t="shared" si="0"/>
-        <v>0.67644958648237985</v>
+        <f t="shared" si="1"/>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="24">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B37" s="23">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C37" s="29">
-        <f t="shared" si="0"/>
-        <v>7.9800987331472867E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="24">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B38" s="23">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C38" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.998836660607344</v>
+        <f t="shared" si="1"/>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="24">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B39" s="23">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C39" s="29">
-        <f t="shared" si="0"/>
-        <v>493.39746561225513</v>
+        <f t="shared" si="1"/>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="24">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B40" s="23">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C40" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.99973486131357592</v>
+        <f t="shared" si="1"/>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="24">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B41" s="23">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C41" s="29">
-        <f t="shared" si="0"/>
-        <v>4796.873754983676</v>
+        <f t="shared" si="1"/>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="24">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B42" s="23">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C42" s="29">
-        <f t="shared" si="0"/>
-        <v>0.15942681787904545</v>
+        <f t="shared" si="1"/>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="24">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B43" s="23">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C43" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.99437447438816284</v>
+        <f t="shared" si="1"/>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="24">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B44" s="23">
-        <v>499.27660521000001</v>
+        <v>2.8086933300000001</v>
       </c>
       <c r="C44" s="29">
-        <f t="shared" si="0"/>
-        <v>75.11816589074563</v>
+        <f t="shared" si="1"/>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="24">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B45" s="23">
-        <v>6.5592306300000001</v>
+        <v>499.27660521000001</v>
       </c>
       <c r="C45" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.99966330474421161</v>
+        <f t="shared" si="1"/>
+        <v>75.11816589074563</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="24">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B46" s="23">
-        <v>19481.20894855</v>
+        <v>6.5592306300000001</v>
       </c>
       <c r="C46" s="29">
-        <f t="shared" si="0"/>
-        <v>40.77506746658235</v>
+        <f t="shared" si="1"/>
+        <v>-0.99966330474421161</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="24">
-        <v>46233</v>
-      </c>
-      <c r="B47">
-        <v>466.33578662999997</v>
+        <v>46234</v>
+      </c>
+      <c r="B47" s="23">
+        <v>19481.20894855</v>
       </c>
       <c r="C47" s="29">
-        <f t="shared" si="0"/>
-        <v>3.5918026507549188</v>
+        <f t="shared" si="1"/>
+        <v>40.77506746658235</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="24">
-        <v>46232</v>
-      </c>
-      <c r="B48" s="23">
-        <v>101.55832515</v>
+        <v>46233</v>
+      </c>
+      <c r="B48">
+        <v>466.33578662999997</v>
       </c>
       <c r="C48" s="29">
-        <f t="shared" si="0"/>
-        <v>22.269067927747528</v>
+        <f t="shared" si="1"/>
+        <v>3.5918026507549188</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="24">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B49" s="23">
-        <v>4.3645205499999999</v>
+        <v>101.55832515</v>
       </c>
       <c r="C49" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.98047278251084946</v>
+        <f t="shared" si="1"/>
+        <v>22.269067927747528</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="24">
-        <v>46108</v>
+        <v>46231</v>
       </c>
       <c r="B50" s="23">
-        <v>223.50959897000001</v>
+        <v>4.3645205499999999</v>
       </c>
       <c r="C50" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.99220607504587943</v>
+        <f t="shared" si="1"/>
+        <v>-0.98047278251084946</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="24">
-        <v>46226</v>
+        <v>46108</v>
       </c>
       <c r="B51" s="23">
-        <v>28677.412251940001</v>
+        <v>223.50959897000001</v>
       </c>
       <c r="C51" s="29">
-        <f t="shared" si="0"/>
-        <v>32.413800410299046</v>
+        <f t="shared" si="1"/>
+        <v>-0.99220607504587943</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="24">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B52" s="23">
-        <v>858.25054019000004</v>
+        <v>28677.412251940001</v>
       </c>
       <c r="C52" s="29">
-        <f t="shared" si="0"/>
-        <v>41.77708649767068</v>
+        <f t="shared" si="1"/>
+        <v>32.413800410299046</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="24">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B53" s="23">
-        <v>20.063323860000001</v>
+        <v>858.25054019000004</v>
       </c>
       <c r="C53" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.99734079323279778</v>
+        <f t="shared" si="1"/>
+        <v>41.77708649767068</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="24">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B54" s="23">
-        <v>7544.8528890099997</v>
+        <v>20.063323860000001</v>
       </c>
       <c r="C54" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.54491271467140989</v>
+        <f t="shared" si="1"/>
+        <v>-0.99734079323279778</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="24">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B55" s="23">
-        <v>16578.913830919999</v>
+        <v>7544.8528890099997</v>
       </c>
       <c r="C55" s="29">
-        <f t="shared" si="0"/>
-        <v>1.1008050673763534</v>
+        <f t="shared" si="1"/>
+        <v>-0.54491271467140989</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="24">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B56" s="23">
-        <v>7891.6954687400003</v>
+        <v>16578.913830919999</v>
       </c>
       <c r="C56" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.79678113606112111</v>
+        <f t="shared" si="1"/>
+        <v>1.1008050673763534</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="24">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B57" s="23">
-        <v>38833.478919130001</v>
+        <v>7891.6954687400003</v>
       </c>
       <c r="C57" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.25771272667553924</v>
+        <f t="shared" si="1"/>
+        <v>-0.79678113606112111</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="24">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B58" s="23">
-        <v>52315.97026473</v>
+        <v>38833.478919130001</v>
       </c>
       <c r="C58" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.19048561913228002</v>
+        <f t="shared" si="1"/>
+        <v>-0.25771272667553924</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="24">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B59" s="23">
-        <v>64626.363040830001</v>
+        <v>52315.97026473</v>
       </c>
       <c r="C59" s="29">
-        <f t="shared" si="0"/>
-        <v>1.2916911129109088</v>
+        <f t="shared" si="1"/>
+        <v>-0.19048561913228002</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="24">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B60" s="23">
-        <v>28200.29395617</v>
+        <v>64626.363040830001</v>
       </c>
       <c r="C60" s="29">
-        <f t="shared" si="0"/>
-        <v>2.65997178100841</v>
+        <f t="shared" si="1"/>
+        <v>1.2916911129109088</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="24">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B61" s="23">
-        <v>7705.0577555</v>
+        <v>28200.29395617</v>
       </c>
       <c r="C61" s="29">
-        <f t="shared" si="0"/>
-        <v>0.84099979813836301</v>
+        <f t="shared" si="1"/>
+        <v>2.65997178100841</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="24">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B62" s="23">
-        <v>4185.2572516800001</v>
+        <v>7705.0577555</v>
       </c>
       <c r="C62" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.5358672604044985</v>
+        <f t="shared" si="1"/>
+        <v>0.84099979813836301</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="24">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B63" s="23">
-        <v>9017.3713134900008</v>
+        <v>4185.2572516800001</v>
       </c>
       <c r="C63" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.47344417767330416</v>
+        <f t="shared" si="1"/>
+        <v>-0.5358672604044985</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="24">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B64" s="23">
-        <v>17125.195337590001</v>
+        <v>9017.3713134900008</v>
       </c>
       <c r="C64" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.39167454677290181</v>
+        <f t="shared" si="1"/>
+        <v>-0.47344417767330416</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="24">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B65" s="23">
-        <v>28151.370695969999</v>
+        <v>17125.195337590001</v>
       </c>
       <c r="C65" s="29">
-        <f t="shared" si="0"/>
-        <v>27.450841046685248</v>
+        <f t="shared" si="1"/>
+        <v>-0.39167454677290181</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="24">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B66" s="23">
-        <v>989.47411254999997</v>
+        <v>28151.370695969999</v>
       </c>
       <c r="C66" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.82605795449481512</v>
+        <f t="shared" si="1"/>
+        <v>27.450841046685248</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="24">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B67" s="23">
-        <v>5688.5275189000004</v>
+        <v>989.47411254999997</v>
       </c>
       <c r="C67" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.82035890094428965</v>
+        <f t="shared" si="1"/>
+        <v>-0.82605795449481512</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="24">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B68" s="23">
-        <v>31666.069450710002</v>
+        <v>5688.5275189000004</v>
       </c>
       <c r="C68" s="29">
-        <f t="shared" si="0"/>
-        <v>12.096519032059602</v>
+        <f t="shared" si="1"/>
+        <v>-0.82035890094428965</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="24">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B69" s="23">
-        <v>2417.8997009200002</v>
+        <v>31666.069450710002</v>
       </c>
       <c r="C69" s="29">
-        <f t="shared" si="0"/>
-        <v>0.40878477030033311</v>
+        <f t="shared" si="1"/>
+        <v>12.096519032059602</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="24">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B70" s="23">
-        <v>1716.30170335</v>
+        <v>2417.8997009200002</v>
       </c>
       <c r="C70" s="29">
-        <f t="shared" si="0"/>
-        <v>103.40487339188886</v>
+        <f t="shared" si="1"/>
+        <v>0.40878477030033311</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="24">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B71" s="23">
-        <v>16.43890412</v>
+        <v>1716.30170335</v>
       </c>
       <c r="C71" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.93907248343987781</v>
+        <f t="shared" si="1"/>
+        <v>103.40487339188886</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="24">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B72" s="23">
-        <v>269.81083503999997</v>
+        <v>16.43890412</v>
       </c>
       <c r="C72" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.88259974628484428</v>
+        <f t="shared" si="1"/>
+        <v>-0.93907248343987781</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="24">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B73" s="23">
-        <v>2298.2133896800001</v>
+        <v>269.81083503999997</v>
       </c>
       <c r="C73" s="29">
-        <f t="shared" si="0"/>
-        <v>0.90523755264044037</v>
+        <f t="shared" si="1"/>
+        <v>-0.88259974628484428</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="24">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B74" s="23">
-        <v>1206.260808</v>
+        <v>2298.2133896800001</v>
       </c>
       <c r="C74" s="29">
-        <f t="shared" si="0"/>
-        <v>142.26137862232778</v>
+        <f t="shared" si="1"/>
+        <v>0.90523755264044037</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="24">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B75" s="23">
-        <v>8.42</v>
+        <v>1206.260808</v>
       </c>
       <c r="C75" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.5604660313731078</v>
+        <f t="shared" si="1"/>
+        <v>142.26137862232778</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="24">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B76" s="23">
-        <v>19.156653639999998</v>
+        <v>8.42</v>
       </c>
       <c r="C76" s="29">
-        <f t="shared" si="0"/>
-        <v>0.50703525245440206</v>
+        <f t="shared" si="1"/>
+        <v>-0.5604660313731078</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="24">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B77" s="23">
-        <v>12.711483429999999</v>
+        <v>19.156653639999998</v>
       </c>
       <c r="C77" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.99943660659465605</v>
+        <f t="shared" si="1"/>
+        <v>0.50703525245440206</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="24">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B78" s="23">
-        <v>22562.357509739999</v>
+        <v>12.711483429999999</v>
       </c>
       <c r="C78" s="29">
-        <f t="shared" ref="C78:C119" si="1">+(B78-B79)/B79</f>
-        <v>5.2639483520141219</v>
+        <f t="shared" si="1"/>
+        <v>-0.99943660659465605</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="24">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B79" s="23">
-        <v>3601.9386242999999</v>
+        <v>22562.357509739999</v>
       </c>
       <c r="C79" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.93820968147801931</v>
+        <f t="shared" ref="C79:C120" si="2">+(B79-B80)/B80</f>
+        <v>5.2639483520141219</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="24">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B80" s="23">
-        <v>58292.928576159997</v>
+        <v>3601.9386242999999</v>
       </c>
       <c r="C80" s="29">
-        <f t="shared" si="1"/>
-        <v>5.2345136037951523</v>
+        <f t="shared" si="2"/>
+        <v>-0.93820968147801931</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="24">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B81" s="23">
-        <v>9350.0363108799993</v>
+        <v>58292.928576159997</v>
       </c>
       <c r="C81" s="29">
-        <f t="shared" si="1"/>
-        <v>1.8327551324816331</v>
+        <f t="shared" si="2"/>
+        <v>5.2345136037951523</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="24">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B82" s="23">
-        <v>3300.6863896099999</v>
+        <v>9350.0363108799993</v>
       </c>
       <c r="C82" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.88947445735006914</v>
+        <f t="shared" si="2"/>
+        <v>1.8327551324816331</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="24">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B83" s="23">
-        <v>29863.561946620001</v>
+        <v>3300.6863896099999</v>
       </c>
       <c r="C83" s="29">
-        <f t="shared" si="1"/>
-        <v>539.15459406063144</v>
+        <f t="shared" si="2"/>
+        <v>-0.88947445735006914</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="24">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B84" s="23">
-        <v>55.287064620000002</v>
+        <v>29863.561946620001</v>
       </c>
       <c r="C84" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99834811895033015</v>
+        <f t="shared" si="2"/>
+        <v>539.15459406063144</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="24">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B85" s="23">
-        <v>33469.1560455</v>
+        <v>55.287064620000002</v>
       </c>
       <c r="C85" s="29">
-        <f t="shared" si="1"/>
-        <v>2.616728100871637</v>
+        <f t="shared" si="2"/>
+        <v>-0.99834811895033015</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="24">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B86" s="23">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C86" s="29">
-        <f t="shared" si="1"/>
-        <v>425.96466507526281</v>
+        <f t="shared" si="2"/>
+        <v>2.616728100871637</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="24">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B87" s="23">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C87" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99745431244335425</v>
+        <f t="shared" si="2"/>
+        <v>425.96466507526281</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="24">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B88" s="23">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C88" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="2"/>
+        <v>-0.99745431244335425</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="24">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B89" s="23">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C89" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.78753584478722383</v>
+        <f t="shared" si="2"/>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="24">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B90" s="23">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C90" s="29">
-        <f t="shared" si="1"/>
-        <v>1063.8095709311931</v>
+        <f t="shared" si="2"/>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="24">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B91" s="23">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C91" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99728557445032884</v>
+        <f t="shared" si="2"/>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="24">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B92" s="23">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C92" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.71845195425328001</v>
+        <f t="shared" si="2"/>
+        <v>-0.99728557445032884</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="24">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B93" s="23">
-        <v>72301.933723569993</v>
+        <v>20356.468143580001</v>
       </c>
       <c r="C93" s="29">
-        <f t="shared" si="1"/>
-        <v>-2.5709262214296945E-2</v>
+        <f t="shared" si="2"/>
+        <v>-0.71845195425328001</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="24">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B94" s="23">
-        <v>74209.813271849998</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C94" s="29">
-        <f t="shared" si="1"/>
-        <v>35.243819791014161</v>
+        <f t="shared" si="2"/>
+        <v>-2.5709262214296945E-2</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="24">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B95" s="23">
-        <v>2047.5163407099999</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C95" s="29">
-        <f t="shared" si="1"/>
-        <v>82.182099964255912</v>
+        <f t="shared" si="2"/>
+        <v>35.243819791014161</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="24">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B96" s="23">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C96" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.96342609797465562</v>
+        <f t="shared" si="2"/>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="24">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B97" s="23">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C97" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.95811572537747924</v>
+        <f t="shared" si="2"/>
+        <v>-0.96342609797465562</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="24">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B98" s="23">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C98" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.32064889280191988</v>
+        <f t="shared" si="2"/>
+        <v>-0.95811572537747924</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="24">
+        <v>46153</v>
+      </c>
+      <c r="B99" s="23">
+        <v>16068.49495319</v>
+      </c>
+      <c r="C99" s="29">
+        <f t="shared" si="2"/>
+        <v>-0.32064889280191988</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46150</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C99" s="29">
-        <f t="shared" si="1"/>
+      <c r="C100" s="29">
+        <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="22">
+    <row r="101" spans="1:4">
+      <c r="A101" s="22">
         <v>46149</v>
       </c>
-      <c r="B100" s="21">
+      <c r="B101" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C100" s="29">
-        <f t="shared" si="1"/>
+      <c r="C101" s="29">
+        <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="17">
-        <v>46148</v>
-      </c>
-      <c r="B101" s="15">
-        <v>745.52443231999996</v>
-      </c>
-      <c r="C101" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99115816107458954</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="17">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B102" s="15">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C102" s="29">
-        <f t="shared" si="1"/>
-        <v>0.70107388483787059</v>
+        <f t="shared" si="2"/>
+        <v>-0.99115816107458954</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="17">
+        <v>46147</v>
+      </c>
+      <c r="B103" s="15">
+        <v>84317.802960360001</v>
+      </c>
+      <c r="C103" s="29">
+        <f t="shared" si="2"/>
+        <v>0.70107388483787059</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4">
+      <c r="A104" s="17">
         <v>46146</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B104" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C103" s="29">
-        <f t="shared" si="1"/>
+      <c r="C104" s="29">
+        <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="18">
-        <v>46142</v>
-      </c>
-      <c r="B104" s="15">
-        <v>87352.396084139997</v>
-      </c>
-      <c r="C104" s="29">
-        <f t="shared" si="1"/>
-        <v>2.0773664296544805</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="18">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B105" s="15">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C105" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.59636256133262866</v>
+        <f t="shared" si="2"/>
+        <v>2.0773664296544805</v>
       </c>
       <c r="D105" s="36"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="18">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B106" s="15">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C106" s="29">
-        <f t="shared" si="1"/>
-        <v>0.74333012643706198</v>
+        <f t="shared" si="2"/>
+        <v>-0.59636256133262866</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="18">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B107" s="15">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C107" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.33842006324553126</v>
+        <f t="shared" si="2"/>
+        <v>0.74333012643706198</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="18">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B108" s="15">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C108" s="29">
-        <f t="shared" si="1"/>
-        <v>12.106463903543759</v>
+        <f t="shared" si="2"/>
+        <v>-0.33842006324553126</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="18">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B109" s="15">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C109" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.73032401489373799</v>
+        <f t="shared" si="2"/>
+        <v>12.106463903543759</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="18">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B110" s="15">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C110" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.64046760511667533</v>
+        <f t="shared" si="2"/>
+        <v>-0.73032401489373799</v>
       </c>
       <c r="D110" s="35"/>
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="18">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B111" s="15">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C111" s="29">
-        <f t="shared" si="1"/>
-        <v>-6.5402088492716129E-2</v>
+        <f t="shared" si="2"/>
+        <v>-0.64046760511667533</v>
       </c>
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="18">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B112" s="15">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C112" s="29">
-        <f t="shared" si="1"/>
-        <v>1.9819948129202027</v>
+        <f t="shared" si="2"/>
+        <v>-6.5402088492716129E-2</v>
       </c>
       <c r="D112" s="35"/>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="18">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B113" s="15">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C113" s="29">
-        <f t="shared" si="1"/>
-        <v>910.40237411852581</v>
+        <f t="shared" si="2"/>
+        <v>1.9819948129202027</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="18">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B114" s="15">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C114" s="29">
-        <f t="shared" si="1"/>
-        <v>0.19572063797541306</v>
+        <f t="shared" si="2"/>
+        <v>910.40237411852581</v>
       </c>
     </row>
     <row r="115" spans="1:3">
       <c r="A115" s="18">
-        <v>46127</v>
-      </c>
-      <c r="B115" s="38">
-        <v>15.79809785</v>
+        <v>46128</v>
+      </c>
+      <c r="B115" s="15">
+        <v>18.890111640000001</v>
       </c>
       <c r="C115" s="29">
-        <f t="shared" si="1"/>
-        <v>-2.5764893835585476E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.19572063797541306</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="18">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B116" s="38">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C116" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99344926580920656</v>
+        <f t="shared" si="2"/>
+        <v>-2.5764893835585476E-2</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="18">
-        <v>46125</v>
-      </c>
-      <c r="B117" s="15">
-        <v>2475.4322626600001</v>
+        <v>46126</v>
+      </c>
+      <c r="B117" s="38">
+        <v>16.215898760000002</v>
       </c>
       <c r="C117" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.68887087467151309</v>
+        <f t="shared" si="2"/>
+        <v>-0.99344926580920656</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="18">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B118" s="15">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C118" s="29">
-        <f t="shared" si="1"/>
-        <v>190.54886991293833</v>
+        <f t="shared" si="2"/>
+        <v>-0.68887087467151309</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="18">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B119" s="15">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C119" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.92845434694034024</v>
+        <f t="shared" si="2"/>
+        <v>190.54886991293833</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="18">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B120" s="15">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C120" s="29">
-        <f>+(B120-B121)/B121</f>
-        <v>3.9632497533121036</v>
+        <f t="shared" si="2"/>
+        <v>-0.92845434694034024</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B121" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C121" s="29">
+        <f>+(B121-B122)/B122</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B122" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B123" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B124" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B125" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46111</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B126" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8325,7 +8357,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9923,7 +9955,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E113" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E114" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -10707,6 +10739,27 @@
       </c>
       <c r="F113" s="31">
         <v>-0.62</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" s="24">
+        <v>46297</v>
+      </c>
+      <c r="B114" s="25">
+        <v>12671</v>
+      </c>
+      <c r="C114" s="23">
+        <v>3</v>
+      </c>
+      <c r="D114" s="25">
+        <v>12674</v>
+      </c>
+      <c r="E114" s="30">
+        <f t="shared" si="4"/>
+        <v>-3.7729916679767332E-3</v>
+      </c>
+      <c r="F114" s="31">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>DÍA</t>
   </si>
@@ -1638,7 +1638,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1712,6 +1712,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="956">
     <cellStyle name="=C:\WINNT\SYSTEM32\COMMAND.COM" xfId="936"/>
@@ -2990,7 +2993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2998,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5557,6 +5560,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="20">
+        <v>46301</v>
+      </c>
+      <c r="B133" s="16">
+        <v>19790.829399999999</v>
+      </c>
+      <c r="C133" s="19"/>
+      <c r="D133" s="16">
+        <v>1</v>
+      </c>
+      <c r="E133" s="19"/>
+      <c r="F133" s="16">
+        <v>1</v>
+      </c>
+      <c r="G133" s="19"/>
+      <c r="H133" s="16">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5565,7 +5588,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5594,14 +5617,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B2" s="23">
-        <v>298642.62637141999</v>
+        <v>289696.54104963999</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C8" si="0">+(B2-B3)/B3</f>
-        <v>-0.13794268733409284</v>
+        <f t="shared" ref="C2:C9" si="0">+(B2-B3)/B3</f>
+        <v>-2.9955821881414251E-2</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5612,14 +5635,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B3" s="23">
-        <v>346430.12939344998</v>
+        <v>298642.62637141999</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>0.2638202658078479</v>
+        <v>-0.13794268733409284</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5630,14 +5653,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B4" s="23">
-        <v>274113.44695601001</v>
+        <v>346430.12939344998</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>0.35910087116479922</v>
+        <v>0.2638202658078479</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5648,14 +5671,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B5" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>8.8268407504102413</v>
+        <v>0.35910087116479922</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5666,14 +5689,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B6" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>-0.85681185394119452</v>
+        <v>8.8268407504102413</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5684,14 +5707,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B7" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>-0.49898704513189668</v>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5702,14 +5725,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B8" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5720,14 +5743,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B9" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C9" s="29">
-        <f t="shared" ref="C9:C78" si="1">+(B9-B10)/B10</f>
-        <v>5.2320875570372835E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.55858664283872839</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5738,1395 +5761,1411 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B10" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C10" s="29">
+        <f t="shared" ref="C10:C79" si="1">+(B10-B11)/B11</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="39">
+        <v>70928.40866225904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46288</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="34"/>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46287</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46286</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46283</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46282</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46281</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46280</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46276</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46275</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46274</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46273</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46272</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46269</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46268</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46267</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46266</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46265</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46262</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46261</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46260</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46259</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46256</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46255</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46254</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46253</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46252</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46251</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46248</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46247</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46246</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46245</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46244</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46241</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46240</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46239</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46238</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46237</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46234</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46233</v>
       </c>
-      <c r="B48">
+      <c r="B49">
         <v>466.33578662999997</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46232</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46231</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46108</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46226</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46225</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46224</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46220</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46219</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46218</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46217</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46216</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46213</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46212</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46211</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46210</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46209</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46206</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46205</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46204</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46203</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46198</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46196</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46195</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46192</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46191</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46190</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46189</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46188</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>8.42</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46185</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46184</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B79" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C79" s="29">
-        <f t="shared" ref="C79:C120" si="2">+(B79-B80)/B80</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="80" spans="1:3">
       <c r="A80" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B80" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C80" s="29">
+        <f t="shared" ref="C80:C121" si="2">+(B80-B81)/B81</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46182</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46178</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46177</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46176</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46175</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46174</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46171</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>45074</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46169</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46168</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46167</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46164</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46163</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46162</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46161</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46157</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46156</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46155</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46154</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46153</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46150</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="22">
+    <row r="102" spans="1:4">
+      <c r="A102" s="22">
         <v>46149</v>
       </c>
-      <c r="B101" s="21">
+      <c r="B102" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="17">
+    <row r="103" spans="1:4">
+      <c r="A103" s="17">
         <v>46148</v>
       </c>
-      <c r="B102" s="15">
+      <c r="B103" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="17">
+    <row r="104" spans="1:4">
+      <c r="A104" s="17">
         <v>46147</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B104" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="17">
+    <row r="105" spans="1:4">
+      <c r="A105" s="17">
         <v>46146</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B105" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="18">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="18">
         <v>46142</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B106" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="18">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="18">
         <v>46141</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B107" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="18">
+    <row r="108" spans="1:4">
+      <c r="A108" s="18">
         <v>46140</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B108" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="18">
+    <row r="109" spans="1:4">
+      <c r="A109" s="18">
         <v>46139</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="18">
+    <row r="110" spans="1:4">
+      <c r="A110" s="18">
         <v>46136</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="18">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46135</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46134</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46133</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46132</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46129</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46128</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46127</v>
       </c>
-      <c r="B116" s="38">
+      <c r="B117" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46126</v>
       </c>
-      <c r="B117" s="38">
+      <c r="B118" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46125</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46122</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46121</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B121" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C121" s="29">
-        <f>+(B121-B122)/B122</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="122" spans="1:3">
       <c r="A122" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B122" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C122" s="29">
+        <f>+(B122-B123)/B123</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B123" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B124" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B125" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B126" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" s="18">
         <v>46111</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B127" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8357,7 +8396,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9955,7 +9994,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E114" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E115" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -10760,6 +10799,27 @@
       </c>
       <c r="F114" s="31">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" s="24">
+        <v>46300</v>
+      </c>
+      <c r="B115" s="25">
+        <v>12892</v>
+      </c>
+      <c r="C115" s="23">
+        <v>3</v>
+      </c>
+      <c r="D115" s="25">
+        <v>12895</v>
+      </c>
+      <c r="E115" s="30">
+        <f t="shared" si="4"/>
+        <v>1.7437273157645573E-2</v>
+      </c>
+      <c r="F115" s="31">
+        <v>1.74</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -3001,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5580,6 +5580,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="20">
+        <v>46302</v>
+      </c>
+      <c r="B134" s="16">
+        <v>18028.403399999999</v>
+      </c>
+      <c r="C134" s="19"/>
+      <c r="D134" s="16">
+        <v>1</v>
+      </c>
+      <c r="E134" s="19"/>
+      <c r="F134" s="16">
+        <v>1</v>
+      </c>
+      <c r="G134" s="19"/>
+      <c r="H134" s="16">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5588,7 +5608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5617,14 +5637,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B2" s="23">
-        <v>289696.54104963999</v>
+        <v>290836.70931037999</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C9" si="0">+(B2-B3)/B3</f>
-        <v>-2.9955821881414251E-2</v>
+        <f t="shared" ref="C2:C10" si="0">+(B2-B3)/B3</f>
+        <v>3.9357330833461011E-3</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5635,14 +5655,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B3" s="23">
-        <v>298642.62637141999</v>
+        <v>289696.54104963999</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>-0.13794268733409284</v>
+        <v>-2.9955821881414251E-2</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5653,14 +5673,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B4" s="23">
-        <v>346430.12939344998</v>
+        <v>298642.62637141999</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>0.2638202658078479</v>
+        <v>-0.13794268733409284</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5671,14 +5691,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B5" s="23">
-        <v>274113.44695601001</v>
+        <v>346430.12939344998</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>0.35910087116479922</v>
+        <v>0.2638202658078479</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5689,14 +5709,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B6" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>8.8268407504102413</v>
+        <v>0.35910087116479922</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5707,14 +5727,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B7" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>-0.85681185394119452</v>
+        <v>8.8268407504102413</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5725,14 +5745,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B8" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>-0.49898704513189668</v>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5743,14 +5763,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B9" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C9" s="29">
         <f t="shared" si="0"/>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5761,14 +5781,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B10" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C10" s="29">
-        <f t="shared" ref="C10:C79" si="1">+(B10-B11)/B11</f>
-        <v>5.2320875570372835E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.55858664283872839</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>39</v>
@@ -5779,1393 +5799,1405 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B11" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C11" s="29">
+        <f t="shared" ref="C11:C80" si="1">+(B11-B12)/B12</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46288</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46287</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46286</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46283</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46282</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46281</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46280</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46276</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46275</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46274</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46273</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46272</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46269</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46268</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46267</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46266</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46265</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46262</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46261</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46260</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46259</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46256</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46255</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46254</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46253</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46252</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46251</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46248</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46247</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46246</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46245</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46244</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46241</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46240</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46239</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46238</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46237</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46234</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46233</v>
       </c>
-      <c r="B49">
+      <c r="B50">
         <v>466.33578662999997</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46232</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46231</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46108</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46226</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46225</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46224</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46220</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46219</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46218</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46217</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46216</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46213</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46212</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46211</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46210</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46209</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46206</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46205</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46204</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46203</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46198</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46196</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46195</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46192</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46191</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46190</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46189</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46188</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>8.42</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46185</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46184</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B80" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C80" s="29">
-        <f t="shared" ref="C80:C121" si="2">+(B80-B81)/B81</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="81" spans="1:3">
       <c r="A81" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B81" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C81" s="29">
+        <f t="shared" ref="C81:C122" si="2">+(B81-B82)/B82</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46182</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46178</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46177</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46176</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46175</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46174</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46171</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>45074</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46169</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46168</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46167</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46164</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46163</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46162</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46161</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46157</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46156</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46155</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46154</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46153</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46150</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="22">
+    <row r="103" spans="1:4">
+      <c r="A103" s="22">
         <v>46149</v>
       </c>
-      <c r="B102" s="21">
+      <c r="B103" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="17">
+    <row r="104" spans="1:4">
+      <c r="A104" s="17">
         <v>46148</v>
       </c>
-      <c r="B103" s="15">
+      <c r="B104" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="17">
+    <row r="105" spans="1:4">
+      <c r="A105" s="17">
         <v>46147</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B105" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="17">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="17">
         <v>46146</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B106" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="18">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="18">
         <v>46142</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B107" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="18">
+    <row r="108" spans="1:4">
+      <c r="A108" s="18">
         <v>46141</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B108" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="18">
+    <row r="109" spans="1:4">
+      <c r="A109" s="18">
         <v>46140</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="18">
+    <row r="110" spans="1:4">
+      <c r="A110" s="18">
         <v>46139</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="18">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46136</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46135</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46134</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46133</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46132</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46129</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46128</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46127</v>
       </c>
-      <c r="B117" s="38">
+      <c r="B118" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46126</v>
       </c>
-      <c r="B118" s="38">
+      <c r="B119" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46125</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46122</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46121</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B122" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C122" s="29">
-        <f>+(B122-B123)/B123</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="123" spans="1:3">
       <c r="A123" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B123" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C123" s="29">
+        <f>+(B123-B124)/B124</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B124" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B125" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B126" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B127" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" s="18">
         <v>46111</v>
       </c>
-      <c r="B127" s="15">
+      <c r="B128" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8396,7 +8428,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -9994,7 +10026,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E115" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E116" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -10820,6 +10852,27 @@
       </c>
       <c r="F115" s="31">
         <v>1.74</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" s="24">
+        <v>46301</v>
+      </c>
+      <c r="B116" s="25">
+        <v>12844</v>
+      </c>
+      <c r="C116" s="23">
+        <v>3</v>
+      </c>
+      <c r="D116" s="25">
+        <v>12847</v>
+      </c>
+      <c r="E116" s="30">
+        <f t="shared" si="4"/>
+        <v>-3.7223730127956571E-3</v>
+      </c>
+      <c r="F116" s="31">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2993,7 +2993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3001,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H134"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5600,6 +5600,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="20">
+        <v>46303</v>
+      </c>
+      <c r="B135" s="16">
+        <v>13681.624299999999</v>
+      </c>
+      <c r="C135" s="19"/>
+      <c r="D135" s="16">
+        <v>1</v>
+      </c>
+      <c r="E135" s="19"/>
+      <c r="F135" s="16">
+        <v>1</v>
+      </c>
+      <c r="G135" s="19"/>
+      <c r="H135" s="16">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5608,7 +5628,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5637,14 +5657,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2" s="23">
-        <v>290836.70931037999</v>
+        <v>280223.23481502</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C10" si="0">+(B2-B3)/B3</f>
-        <v>3.9357330833461011E-3</v>
+        <f t="shared" ref="C2:C11" si="0">+(B2-B3)/B3</f>
+        <v>-3.649289843956157E-2</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5655,14 +5675,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B3" s="23">
-        <v>289696.54104963999</v>
+        <v>290836.70931037999</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>-2.9955821881414251E-2</v>
+        <v>3.9357330833461011E-3</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5673,14 +5693,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B4" s="23">
-        <v>298642.62637141999</v>
+        <v>289696.54104963999</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>-0.13794268733409284</v>
+        <v>-2.9955821881414251E-2</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5691,14 +5711,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B5" s="23">
-        <v>346430.12939344998</v>
+        <v>298642.62637141999</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>0.2638202658078479</v>
+        <v>-0.13794268733409284</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5709,14 +5729,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B6" s="23">
-        <v>274113.44695601001</v>
+        <v>346430.12939344998</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>0.35910087116479922</v>
+        <v>0.2638202658078479</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5727,14 +5747,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B7" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>8.8268407504102413</v>
+        <v>0.35910087116479922</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5745,14 +5765,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B8" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>-0.85681185394119452</v>
+        <v>8.8268407504102413</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5763,14 +5783,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B9" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C9" s="29">
         <f t="shared" si="0"/>
-        <v>-0.49898704513189668</v>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5781,14 +5801,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B10" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C10" s="29">
         <f t="shared" si="0"/>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>39</v>
@@ -5799,1405 +5819,1417 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B11" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C11" s="29">
-        <f t="shared" ref="C11:C80" si="1">+(B11-B12)/B12</f>
-        <v>5.2320875570372835E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.55858664283872839</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B12" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C12" s="29">
+        <f t="shared" ref="C12:C81" si="1">+(B12-B13)/B13</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46288</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46287</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46286</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46283</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46282</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46281</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46280</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46276</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46275</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46274</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46273</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46272</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46269</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46268</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46267</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46266</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46265</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46262</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46261</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46260</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46259</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46256</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46255</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46254</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46253</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46252</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46251</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46248</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46247</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46246</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46245</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46244</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46241</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46240</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46239</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46238</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46237</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46234</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46233</v>
       </c>
-      <c r="B50">
+      <c r="B51">
         <v>466.33578662999997</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46232</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46231</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46108</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46226</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46225</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46224</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46220</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46219</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46218</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46217</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46216</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46213</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46212</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46211</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46210</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46209</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46206</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46205</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46204</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46203</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46198</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46196</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46195</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46192</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46191</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46190</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46189</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46188</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>8.42</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46185</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46184</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B81" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C81" s="29">
-        <f t="shared" ref="C81:C122" si="2">+(B81-B82)/B82</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="82" spans="1:3">
       <c r="A82" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B82" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C82" s="29">
+        <f t="shared" ref="C82:C123" si="2">+(B82-B83)/B83</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46182</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46178</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46177</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46176</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46175</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46174</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46171</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>45074</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46169</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46168</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46167</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46164</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46163</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46162</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46161</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46157</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46156</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46155</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46154</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46153</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46150</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="22">
+    <row r="104" spans="1:4">
+      <c r="A104" s="22">
         <v>46149</v>
       </c>
-      <c r="B103" s="21">
+      <c r="B104" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="17">
+    <row r="105" spans="1:4">
+      <c r="A105" s="17">
         <v>46148</v>
       </c>
-      <c r="B104" s="15">
+      <c r="B105" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="17">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="17">
         <v>46147</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B106" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="17">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="17">
         <v>46146</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B107" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="18">
+    <row r="108" spans="1:4">
+      <c r="A108" s="18">
         <v>46142</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B108" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="18">
+    <row r="109" spans="1:4">
+      <c r="A109" s="18">
         <v>46141</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="18">
+    <row r="110" spans="1:4">
+      <c r="A110" s="18">
         <v>46140</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="18">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46139</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46136</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46135</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46134</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46133</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46132</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46129</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46128</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46127</v>
       </c>
-      <c r="B118" s="38">
+      <c r="B119" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46126</v>
       </c>
-      <c r="B119" s="38">
+      <c r="B120" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46125</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46122</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46121</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B123" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C123" s="29">
-        <f>+(B123-B124)/B124</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="124" spans="1:3">
       <c r="A124" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B124" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C124" s="29">
+        <f>+(B124-B125)/B125</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B125" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B126" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B127" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B128" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="18">
         <v>46111</v>
       </c>
-      <c r="B128" s="15">
+      <c r="B129" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8428,7 +8460,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10026,7 +10058,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E116" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E117" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -10873,6 +10905,27 @@
       </c>
       <c r="F116" s="31">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" s="24">
+        <v>46302</v>
+      </c>
+      <c r="B117" s="25">
+        <v>12756</v>
+      </c>
+      <c r="C117" s="23">
+        <v>3</v>
+      </c>
+      <c r="D117" s="25">
+        <v>12759</v>
+      </c>
+      <c r="E117" s="30">
+        <f t="shared" si="4"/>
+        <v>-6.8498482135907219E-3</v>
+      </c>
+      <c r="F117" s="31">
+        <v>-0.68</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2993,7 +2993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3001,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5620,6 +5620,26 @@
         <v>1</v>
       </c>
     </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="20">
+        <v>46304</v>
+      </c>
+      <c r="B136" s="16">
+        <v>3612.7458999999999</v>
+      </c>
+      <c r="C136" s="19"/>
+      <c r="D136" s="16">
+        <v>0.25</v>
+      </c>
+      <c r="E136" s="19"/>
+      <c r="F136" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G136" s="19"/>
+      <c r="H136" s="16">
+        <v>0.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5628,7 +5648,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5657,14 +5677,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B2" s="23">
-        <v>280223.23481502</v>
+        <v>306385.59906737</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C11" si="0">+(B2-B3)/B3</f>
-        <v>-3.649289843956157E-2</v>
+        <f t="shared" ref="C2:C12" si="0">+(B2-B3)/B3</f>
+        <v>9.336258026433894E-2</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5675,14 +5695,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B3" s="23">
-        <v>290836.70931037999</v>
+        <v>280223.23481502</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>3.9357330833461011E-3</v>
+        <v>-3.649289843956157E-2</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5693,14 +5713,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B4" s="23">
-        <v>289696.54104963999</v>
+        <v>290836.70931037999</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>-2.9955821881414251E-2</v>
+        <v>3.9357330833461011E-3</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5711,14 +5731,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B5" s="23">
-        <v>298642.62637141999</v>
+        <v>289696.54104963999</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>-0.13794268733409284</v>
+        <v>-2.9955821881414251E-2</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5729,14 +5749,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B6" s="23">
-        <v>346430.12939344998</v>
+        <v>298642.62637141999</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>0.2638202658078479</v>
+        <v>-0.13794268733409284</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5747,14 +5767,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B7" s="23">
-        <v>274113.44695601001</v>
+        <v>346430.12939344998</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>0.35910087116479922</v>
+        <v>0.2638202658078479</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5765,14 +5785,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B8" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>8.8268407504102413</v>
+        <v>0.35910087116479922</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5783,14 +5803,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B9" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C9" s="29">
         <f t="shared" si="0"/>
-        <v>-0.85681185394119452</v>
+        <v>8.8268407504102413</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5801,14 +5821,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B10" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C10" s="29">
         <f t="shared" si="0"/>
-        <v>-0.49898704513189668</v>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>39</v>
@@ -5819,1417 +5839,1429 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B11" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C11" s="29">
         <f t="shared" si="0"/>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B12" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C12" s="29">
-        <f t="shared" ref="C12:C81" si="1">+(B12-B13)/B13</f>
-        <v>5.2320875570372835E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.55858664283872839</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B13" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C13" s="29">
+        <f t="shared" ref="C13:C82" si="1">+(B13-B14)/B14</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46288</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46287</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46286</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46283</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46282</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46281</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46280</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46276</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46275</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46274</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46273</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46272</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46269</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46268</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46267</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46266</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46265</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46262</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46261</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46260</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46259</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46256</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46255</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46254</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46253</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46252</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46251</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46248</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46247</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46246</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46245</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46244</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46241</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46240</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46239</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46238</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46237</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46234</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46233</v>
       </c>
-      <c r="B51">
+      <c r="B52">
         <v>466.33578662999997</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46232</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46231</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46108</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46226</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46225</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46224</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46220</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46219</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46218</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46217</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46216</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46213</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46212</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46211</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46210</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46209</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46206</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46205</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46204</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46203</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46198</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46196</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46195</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46192</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46191</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46190</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46189</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46188</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>8.42</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46185</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46184</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B82" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C82" s="29">
-        <f t="shared" ref="C82:C123" si="2">+(B82-B83)/B83</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="83" spans="1:3">
       <c r="A83" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B83" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C83" s="29">
+        <f t="shared" ref="C83:C124" si="2">+(B83-B84)/B84</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46182</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46178</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46177</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46176</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46175</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46174</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46171</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>45074</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46169</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46168</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46167</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46164</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46163</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46162</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46161</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46157</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46156</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46155</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46154</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46153</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46150</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="22">
+    <row r="105" spans="1:4">
+      <c r="A105" s="22">
         <v>46149</v>
       </c>
-      <c r="B104" s="21">
+      <c r="B105" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="17">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="17">
         <v>46148</v>
       </c>
-      <c r="B105" s="15">
+      <c r="B106" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="17">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="17">
         <v>46147</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B107" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="17">
+    <row r="108" spans="1:4">
+      <c r="A108" s="17">
         <v>46146</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B108" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="18">
+    <row r="109" spans="1:4">
+      <c r="A109" s="18">
         <v>46142</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="18">
+    <row r="110" spans="1:4">
+      <c r="A110" s="18">
         <v>46141</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="18">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46140</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46139</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46136</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46135</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46134</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46133</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46132</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46129</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46128</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46127</v>
       </c>
-      <c r="B119" s="38">
+      <c r="B120" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46126</v>
       </c>
-      <c r="B120" s="38">
+      <c r="B121" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46125</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46122</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46121</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B124" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C124" s="29">
-        <f>+(B124-B125)/B125</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="125" spans="1:3">
       <c r="A125" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B125" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C125" s="29">
+        <f>+(B125-B126)/B126</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B126" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B127" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B128" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B129" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="18">
         <v>46111</v>
       </c>
-      <c r="B129" s="15">
+      <c r="B130" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8447,11 +8479,30 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="A29" s="24">
+        <v>46297</v>
+      </c>
+      <c r="B29" s="16">
+        <v>84421385.438590005</v>
+      </c>
+      <c r="C29" s="16">
+        <v>2742425809.1924901</v>
+      </c>
+      <c r="D29" s="16">
+        <v>255682015.32416996</v>
+      </c>
+      <c r="E29" s="16">
+        <v>3082529209.9552503</v>
+      </c>
+      <c r="F29" s="16">
+        <v>31910068.605470002</v>
+      </c>
+      <c r="G29" s="16">
+        <v>3114439278.5607204</v>
+      </c>
+      <c r="H29" s="26">
+        <v>4.8637545144343264</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8460,7 +8511,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10058,7 +10109,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E117" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E118" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -10926,6 +10977,27 @@
       </c>
       <c r="F117" s="31">
         <v>-0.68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" s="24">
+        <v>46303</v>
+      </c>
+      <c r="B118" s="25">
+        <v>12703</v>
+      </c>
+      <c r="C118" s="23">
+        <v>3</v>
+      </c>
+      <c r="D118" s="25">
+        <v>12706</v>
+      </c>
+      <c r="E118" s="30">
+        <f t="shared" si="4"/>
+        <v>-4.1539305588212247E-3</v>
+      </c>
+      <c r="F118" s="31">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2993,7 +2993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3001,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5640,6 +5640,26 @@
         <v>0.49</v>
       </c>
     </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="20">
+        <v>46308</v>
+      </c>
+      <c r="B137" s="16">
+        <v>35938.443534999999</v>
+      </c>
+      <c r="C137" s="19"/>
+      <c r="D137" s="16">
+        <v>18</v>
+      </c>
+      <c r="E137" s="19"/>
+      <c r="F137" s="16">
+        <v>20</v>
+      </c>
+      <c r="G137" s="19"/>
+      <c r="H137" s="16">
+        <v>19.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5648,7 +5668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5677,14 +5697,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B2" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C12" si="0">+(B2-B3)/B3</f>
-        <v>9.336258026433894E-2</v>
+        <f t="shared" ref="C2:C13" si="0">+(B2-B3)/B3</f>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5695,14 +5715,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B3" s="23">
-        <v>280223.23481502</v>
+        <v>306385.59906737</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>-3.649289843956157E-2</v>
+        <v>9.336258026433894E-2</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5713,14 +5733,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B4" s="23">
-        <v>290836.70931037999</v>
+        <v>280223.23481502</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>3.9357330833461011E-3</v>
+        <v>-3.649289843956157E-2</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5731,14 +5751,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B5" s="23">
-        <v>289696.54104963999</v>
+        <v>290836.70931037999</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>-2.9955821881414251E-2</v>
+        <v>3.9357330833461011E-3</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5749,14 +5769,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B6" s="23">
-        <v>298642.62637141999</v>
+        <v>289696.54104963999</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>-0.13794268733409284</v>
+        <v>-2.9955821881414251E-2</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5767,14 +5787,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B7" s="23">
-        <v>346430.12939344998</v>
+        <v>298642.62637141999</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>0.2638202658078479</v>
+        <v>-0.13794268733409284</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5785,14 +5805,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B8" s="23">
-        <v>274113.44695601001</v>
+        <v>346430.12939344998</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>0.35910087116479922</v>
+        <v>0.2638202658078479</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5803,14 +5823,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B9" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C9" s="29">
         <f t="shared" si="0"/>
-        <v>8.8268407504102413</v>
+        <v>0.35910087116479922</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5821,14 +5841,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B10" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C10" s="29">
         <f t="shared" si="0"/>
-        <v>-0.85681185394119452</v>
+        <v>8.8268407504102413</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>39</v>
@@ -5839,1429 +5859,1441 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B11" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C11" s="29">
         <f t="shared" si="0"/>
-        <v>-0.49898704513189668</v>
+        <v>-0.85681185394119452</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B12" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C12" s="29">
         <f t="shared" si="0"/>
-        <v>0.55858664283872839</v>
+        <v>-0.49898704513189668</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B13" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C13" s="29">
-        <f t="shared" ref="C13:C82" si="1">+(B13-B14)/B14</f>
-        <v>5.2320875570372835E-2</v>
+        <f t="shared" si="0"/>
+        <v>0.55858664283872839</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B14" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C14" s="29">
+        <f t="shared" ref="C14:C83" si="1">+(B14-B15)/B15</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46288</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46287</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46286</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46283</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46282</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46281</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46280</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46276</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46275</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46274</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46273</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46272</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46269</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46268</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46267</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46266</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46265</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46262</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46261</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46260</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46259</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46256</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46255</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46254</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46253</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46252</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46251</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46248</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46247</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46246</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46245</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46244</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46241</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46240</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46239</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46238</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46237</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46234</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46233</v>
       </c>
-      <c r="B52">
+      <c r="B53">
         <v>466.33578662999997</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46232</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46231</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46108</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46226</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46225</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46224</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46220</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46219</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46218</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46217</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46216</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46213</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46212</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46211</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46210</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46209</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46206</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46205</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46204</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46203</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46198</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46196</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46195</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46192</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46191</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46190</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46189</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46188</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>8.42</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46185</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46184</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B83" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C83" s="29">
-        <f t="shared" ref="C83:C124" si="2">+(B83-B84)/B84</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="84" spans="1:3">
       <c r="A84" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B84" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C84" s="29">
+        <f t="shared" ref="C84:C125" si="2">+(B84-B85)/B85</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46182</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46178</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46177</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46176</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46175</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46174</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46171</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>45074</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46169</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46168</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46167</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46164</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46163</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46162</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46161</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46157</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46156</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46155</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46154</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46153</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46150</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="22">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="22">
         <v>46149</v>
       </c>
-      <c r="B105" s="21">
+      <c r="B106" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="17">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="17">
         <v>46148</v>
       </c>
-      <c r="B106" s="15">
+      <c r="B107" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="17">
+    <row r="108" spans="1:4">
+      <c r="A108" s="17">
         <v>46147</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B108" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="17">
+    <row r="109" spans="1:4">
+      <c r="A109" s="17">
         <v>46146</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="18">
+    <row r="110" spans="1:4">
+      <c r="A110" s="18">
         <v>46142</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="18">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46141</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46140</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46139</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46136</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46135</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46134</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46133</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46132</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46129</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46128</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46127</v>
       </c>
-      <c r="B120" s="38">
+      <c r="B121" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46126</v>
       </c>
-      <c r="B121" s="38">
+      <c r="B122" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46125</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46122</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46121</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B125" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B125" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C125" s="29">
-        <f>+(B125-B126)/B126</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="126" spans="1:3">
       <c r="A126" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B126" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C126" s="29">
+        <f>+(B126-B127)/B127</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B127" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B128" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B129" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B130" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="18">
         <v>46111</v>
       </c>
-      <c r="B130" s="15">
+      <c r="B131" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8511,7 +8543,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10109,7 +10141,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E118" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E119" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -10998,6 +11030,27 @@
       </c>
       <c r="F118" s="31">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B119" s="25">
+        <v>12684</v>
+      </c>
+      <c r="C119" s="23">
+        <v>3</v>
+      </c>
+      <c r="D119" s="25">
+        <v>12687</v>
+      </c>
+      <c r="E119" s="30">
+        <f t="shared" si="4"/>
+        <v>-1.4953565244766253E-3</v>
+      </c>
+      <c r="F119" s="31">
+        <v>-0.15</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2993,7 +2993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3001,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H137"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5660,6 +5660,26 @@
         <v>19.8</v>
       </c>
     </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="20">
+        <v>46309</v>
+      </c>
+      <c r="B138" s="16">
+        <v>34727.03</v>
+      </c>
+      <c r="C138" s="19"/>
+      <c r="D138" s="16">
+        <v>2</v>
+      </c>
+      <c r="E138" s="19"/>
+      <c r="F138" s="16">
+        <v>20</v>
+      </c>
+      <c r="G138" s="19"/>
+      <c r="H138" s="16">
+        <v>5.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5668,7 +5688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5697,14 +5717,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C13" si="0">+(B2-B3)/B3</f>
-        <v>-0.6788555314993624</v>
+        <f>+(B2-B3)/B3</f>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5715,14 +5735,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B3" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C3" s="29">
-        <f t="shared" si="0"/>
-        <v>9.336258026433894E-2</v>
+        <f>+(B3-B4)/B4</f>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5733,1567 +5753,1579 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B4" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C4" s="29">
+        <f t="shared" ref="C3:C14" si="0">+(B4-B5)/B5</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6">
+        <v>85928.931135131905</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="17.25" customHeight="1">
+      <c r="A5" s="24">
         <v>46303</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B5" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C4" s="29">
+      <c r="C5" s="29">
         <f t="shared" si="0"/>
         <v>-3.649289843956157E-2</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6">
-        <v>85928.931135131905</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A5" s="24">
+      <c r="D5" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="24">
         <v>46302</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B6" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C6" s="29">
         <f t="shared" si="0"/>
         <v>3.9357330833461011E-3</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="6">
-        <v>22227.4775024345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="24">
+      <c r="D6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="6">
+        <v>24565.759999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24">
         <v>46301</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B7" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C7" s="29">
         <f t="shared" si="0"/>
         <v>-2.9955821881414251E-2</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6">
-        <v>24565.759999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="24">
+      <c r="D7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24">
         <v>46300</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B8" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C8" s="29">
         <f t="shared" si="0"/>
         <v>-0.13794268733409284</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="24">
+      <c r="D8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="33">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24">
         <v>46297</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B9" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>0.2638202658078479</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="33">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="24">
+      <c r="D9" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24">
         <v>46296</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B10" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>0.35910087116479922</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="24">
+      <c r="D10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="39">
+        <v>70928.40866225904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46295</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>8.8268407504102413</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="39">
-        <v>70928.40866225904</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46294</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>-0.85681185394119452</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46293</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>-0.49898704513189668</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46290</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>0.55858664283872839</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B14" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C14" s="29">
-        <f t="shared" ref="C14:C83" si="1">+(B14-B15)/B15</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
       <c r="E14" s="35"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B15" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C15" s="29">
+        <f t="shared" ref="C15:C84" si="1">+(B15-B16)/B16</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46288</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46287</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46286</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46283</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46282</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46281</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46280</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46276</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46275</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46274</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46273</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46272</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46269</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46268</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46267</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46266</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46265</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46262</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46261</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46260</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46259</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46256</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46255</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46254</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46253</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46252</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46251</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46248</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46247</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46246</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46245</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46244</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46241</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46240</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46239</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46238</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46237</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46234</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46233</v>
       </c>
-      <c r="B53">
+      <c r="B54">
         <v>466.33578662999997</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46232</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46231</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46108</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46226</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46225</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46224</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46220</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46219</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46218</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46217</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46216</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46213</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46212</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46211</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46210</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46209</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46206</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46205</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46204</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46203</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46198</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46196</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46195</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46192</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46191</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46190</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46189</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46188</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>8.42</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46185</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46184</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B84" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C84" s="29">
-        <f t="shared" ref="C84:C125" si="2">+(B84-B85)/B85</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="85" spans="1:3">
       <c r="A85" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B85" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C85" s="29">
+        <f t="shared" ref="C85:C126" si="2">+(B85-B86)/B86</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46182</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46178</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46177</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46176</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46175</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46174</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46171</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>45074</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46169</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46168</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46167</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46164</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46163</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46162</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46161</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46157</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46156</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46155</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46154</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46153</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46150</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="22">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="22">
         <v>46149</v>
       </c>
-      <c r="B106" s="21">
+      <c r="B107" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="17">
+    <row r="108" spans="1:4">
+      <c r="A108" s="17">
         <v>46148</v>
       </c>
-      <c r="B107" s="15">
+      <c r="B108" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="17">
+    <row r="109" spans="1:4">
+      <c r="A109" s="17">
         <v>46147</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="17">
+    <row r="110" spans="1:4">
+      <c r="A110" s="17">
         <v>46146</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="18">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="18">
         <v>46142</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46141</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46140</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46139</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46136</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46135</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46134</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46133</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46132</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46129</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46128</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46127</v>
       </c>
-      <c r="B121" s="38">
+      <c r="B122" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46126</v>
       </c>
-      <c r="B122" s="38">
+      <c r="B123" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46125</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46122</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B125" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46121</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B126" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C126" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B126" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C126" s="29">
-        <f>+(B126-B127)/B127</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="127" spans="1:3">
       <c r="A127" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B127" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C127" s="29">
+        <f>+(B127-B128)/B128</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B128" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B129" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B130" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B131" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="18">
         <v>46111</v>
       </c>
-      <c r="B131" s="15">
+      <c r="B132" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8543,7 +8575,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10141,7 +10173,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E119" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E120" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11051,6 +11083,27 @@
       </c>
       <c r="F119" s="31">
         <v>-0.15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" s="24">
+        <v>46308</v>
+      </c>
+      <c r="B120" s="25">
+        <v>13084</v>
+      </c>
+      <c r="C120" s="23">
+        <v>3</v>
+      </c>
+      <c r="D120" s="25">
+        <v>13087</v>
+      </c>
+      <c r="E120" s="30">
+        <f t="shared" si="4"/>
+        <v>3.1528336092062743E-2</v>
+      </c>
+      <c r="F120" s="31">
+        <v>3.15</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2993,7 +2993,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3001,7 +3001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H138"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5680,6 +5680,26 @@
         <v>5.16</v>
       </c>
     </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="20">
+        <v>46310</v>
+      </c>
+      <c r="B139" s="16">
+        <v>32955</v>
+      </c>
+      <c r="C139" s="19"/>
+      <c r="D139" s="16">
+        <v>70</v>
+      </c>
+      <c r="E139" s="19"/>
+      <c r="F139" s="16">
+        <v>80</v>
+      </c>
+      <c r="G139" s="19"/>
+      <c r="H139" s="16">
+        <v>77.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5688,7 +5708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5717,14 +5737,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B2" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C2" s="29">
         <f>+(B2-B3)/B3</f>
-        <v>-0.88352658705352882</v>
+        <v>11.24948691206232</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5735,14 +5755,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B3" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C3" s="29">
         <f>+(B3-B4)/B4</f>
-        <v>-0.6788555314993624</v>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5753,14 +5773,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B4" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C4" s="29">
-        <f t="shared" ref="C3:C14" si="0">+(B4-B5)/B5</f>
-        <v>9.336258026433894E-2</v>
+        <f>+(B4-B5)/B5</f>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5771,1561 +5791,1573 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B5" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C5" s="29">
+        <f t="shared" ref="C5:C15" si="0">+(B5-B6)/B6</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="6">
+        <v>22227.4775024345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="24">
         <v>46303</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B6" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C6" s="29">
         <f t="shared" si="0"/>
         <v>-3.649289843956157E-2</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="6">
-        <v>22227.4775024345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="24">
+      <c r="D6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="6">
+        <v>24565.759999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24">
         <v>46302</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B7" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C7" s="29">
         <f t="shared" si="0"/>
         <v>3.9357330833461011E-3</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6">
-        <v>24565.759999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="24">
+      <c r="D7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24">
         <v>46301</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B8" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C8" s="29">
         <f t="shared" si="0"/>
         <v>-2.9955821881414251E-2</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="24">
+      <c r="D8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="33">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24">
         <v>46300</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B9" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>-0.13794268733409284</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="33">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="24">
+      <c r="D9" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24">
         <v>46297</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B10" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>0.2638202658078479</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="24">
+      <c r="D10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="39">
+        <v>70928.40866225904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46296</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>0.35910087116479922</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="39">
-        <v>70928.40866225904</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46295</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>8.8268407504102413</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46294</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>-0.85681185394119452</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46293</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>-0.49898704513189668</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46290</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="0"/>
         <v>0.55858664283872839</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B15" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C15" s="29">
-        <f t="shared" ref="C15:C84" si="1">+(B15-B16)/B16</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
       <c r="E15" s="35"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B16" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C16" s="29">
+        <f t="shared" ref="C16:C85" si="1">+(B16-B17)/B17</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46288</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46287</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46286</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46283</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46282</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46281</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46280</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46276</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46275</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46274</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46273</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46272</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46269</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46268</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46267</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46266</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46265</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46262</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46261</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46260</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46259</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46256</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46255</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46254</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46253</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46252</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46251</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46248</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46247</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46246</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46245</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46244</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46241</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46240</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46239</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46238</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46237</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46234</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46233</v>
       </c>
-      <c r="B54">
+      <c r="B55">
         <v>466.33578662999997</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46232</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46231</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46108</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46226</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46225</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46224</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46220</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46219</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46218</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46217</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46216</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46213</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46212</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46211</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46210</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46209</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46206</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46205</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46204</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46203</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46198</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46196</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46195</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46192</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46191</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46190</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46189</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46188</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>8.42</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46185</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46184</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B85" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C85" s="29">
-        <f t="shared" ref="C85:C126" si="2">+(B85-B86)/B86</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="86" spans="1:3">
       <c r="A86" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B86" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C86" s="29">
+        <f t="shared" ref="C86:C127" si="2">+(B86-B87)/B87</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46182</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46178</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46177</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46176</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46175</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46174</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46171</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>45074</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46169</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46168</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46167</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46164</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46163</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46162</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46161</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46157</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46156</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46155</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46154</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46153</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="24">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="24">
         <v>46150</v>
       </c>
-      <c r="B106" s="23">
+      <c r="B107" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="22">
+    <row r="108" spans="1:4">
+      <c r="A108" s="22">
         <v>46149</v>
       </c>
-      <c r="B107" s="21">
+      <c r="B108" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="17">
+    <row r="109" spans="1:4">
+      <c r="A109" s="17">
         <v>46148</v>
       </c>
-      <c r="B108" s="15">
+      <c r="B109" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="17">
+    <row r="110" spans="1:4">
+      <c r="A110" s="17">
         <v>46147</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="17">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="17">
         <v>46146</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="18">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="18">
         <v>46142</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46141</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46140</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46139</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46136</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46135</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46134</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46133</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46132</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46129</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46128</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46127</v>
       </c>
-      <c r="B122" s="38">
+      <c r="B123" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46126</v>
       </c>
-      <c r="B123" s="38">
+      <c r="B124" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46125</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B125" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46122</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B126" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C126" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="18">
+    <row r="127" spans="1:3">
+      <c r="A127" s="18">
         <v>46121</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B127" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C126" s="29">
+      <c r="C127" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B127" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C127" s="29">
-        <f>+(B127-B128)/B128</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="128" spans="1:3">
       <c r="A128" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B128" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C128" s="29">
+        <f>+(B128-B129)/B129</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B129" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B130" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B131" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B132" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="18">
         <v>46111</v>
       </c>
-      <c r="B132" s="15">
+      <c r="B133" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8575,7 +8607,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10173,7 +10205,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E120" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E121" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11104,6 +11136,27 @@
       </c>
       <c r="F120" s="31">
         <v>3.15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" s="24">
+        <v>46309</v>
+      </c>
+      <c r="B121" s="25">
+        <v>12998</v>
+      </c>
+      <c r="C121" s="23">
+        <v>3</v>
+      </c>
+      <c r="D121" s="25">
+        <v>13001</v>
+      </c>
+      <c r="E121" s="30">
+        <f t="shared" si="4"/>
+        <v>-6.571406739512493E-3</v>
+      </c>
+      <c r="F121" s="31">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="10785" yWindow="-15" windowWidth="10830" windowHeight="10140" tabRatio="819"/>
+    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10125" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
   <si>
     <t>DÍA</t>
   </si>
@@ -139,6 +139,9 @@
   </si>
   <si>
     <t>SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>16/10/206</t>
   </si>
 </sst>
 </file>
@@ -3001,7 +3004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H140"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5700,6 +5703,26 @@
         <v>77.33</v>
       </c>
     </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="20">
+        <v>46311</v>
+      </c>
+      <c r="B140" s="16">
+        <v>32821.478965000002</v>
+      </c>
+      <c r="C140" s="19"/>
+      <c r="D140" s="16">
+        <v>2</v>
+      </c>
+      <c r="E140" s="19"/>
+      <c r="F140" s="16">
+        <v>5</v>
+      </c>
+      <c r="G140" s="19"/>
+      <c r="H140" s="16">
+        <v>3.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5708,7 +5731,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5736,15 +5759,15 @@
       </c>
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="24">
-        <v>46310</v>
+      <c r="A2" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B2" s="23">
-        <v>140382.66863150999</v>
+        <v>195620.76542108</v>
       </c>
       <c r="C2" s="29">
         <f>+(B2-B3)/B3</f>
-        <v>11.24948691206232</v>
+        <v>0.39348231037382758</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5755,14 +5778,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B3" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C3" s="29">
         <f>+(B3-B4)/B4</f>
-        <v>-0.88352658705352882</v>
+        <v>11.24948691206232</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5773,14 +5796,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B4" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C4" s="29">
         <f>+(B4-B5)/B5</f>
-        <v>-0.6788555314993624</v>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5791,14 +5814,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B5" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C5" s="29">
-        <f t="shared" ref="C5:C15" si="0">+(B5-B6)/B6</f>
-        <v>9.336258026433894E-2</v>
+        <f>+(B5-B6)/B6</f>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5809,1555 +5832,1567 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B6" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C6" s="29">
+        <f t="shared" ref="C6:C16" si="0">+(B6-B7)/B7</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="6">
+        <v>24565.759999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24">
         <v>46303</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B7" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C7" s="29">
         <f t="shared" si="0"/>
         <v>-3.649289843956157E-2</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6">
-        <v>24565.759999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="24">
+      <c r="D7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24">
         <v>46302</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B8" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C8" s="29">
         <f t="shared" si="0"/>
         <v>3.9357330833461011E-3</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="24">
+      <c r="D8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="33">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24">
         <v>46301</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B9" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>-2.9955821881414251E-2</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="33">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="24">
+      <c r="D9" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24">
         <v>46300</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B10" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>-0.13794268733409284</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="24">
+      <c r="D10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="39">
+        <v>70928.40866225904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46297</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>0.2638202658078479</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="39">
-        <v>70928.40866225904</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46296</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>0.35910087116479922</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46295</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>8.8268407504102413</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46294</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>-0.85681185394119452</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46293</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="0"/>
         <v>-0.49898704513189668</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46290</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="0"/>
         <v>0.55858664283872839</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B16" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C16" s="29">
-        <f t="shared" ref="C16:C85" si="1">+(B16-B17)/B17</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B17" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C17" s="29">
+        <f t="shared" ref="C17:C86" si="1">+(B17-B18)/B18</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46288</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46287</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46286</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46283</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46282</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46281</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46280</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46276</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46275</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46274</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46273</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46272</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46269</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46268</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46267</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46266</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46265</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46262</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46261</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46260</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46259</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46256</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46255</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46254</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46253</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46252</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46251</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46248</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46247</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46246</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46245</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46244</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46241</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46240</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46239</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46238</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46237</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46234</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46233</v>
       </c>
-      <c r="B55">
+      <c r="B56">
         <v>466.33578662999997</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46232</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46231</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46108</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46226</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46225</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46224</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46220</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46219</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46218</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46217</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46216</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46213</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46212</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46211</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46210</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46209</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46206</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46205</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46204</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46203</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46198</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46196</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46195</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46192</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46191</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46190</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46189</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46188</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>8.42</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46185</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46184</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B86" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C86" s="29">
-        <f t="shared" ref="C86:C127" si="2">+(B86-B87)/B87</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="87" spans="1:3">
       <c r="A87" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B87" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C87" s="29">
+        <f t="shared" ref="C87:C128" si="2">+(B87-B88)/B88</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46182</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46178</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46177</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46176</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46175</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46174</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46171</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>45074</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46169</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46168</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46167</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46164</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46163</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46162</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46161</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46157</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46156</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46155</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46154</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="24">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="24">
         <v>46153</v>
       </c>
-      <c r="B106" s="23">
+      <c r="B107" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="24">
+    <row r="108" spans="1:4">
+      <c r="A108" s="24">
         <v>46150</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B108" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="22">
+    <row r="109" spans="1:4">
+      <c r="A109" s="22">
         <v>46149</v>
       </c>
-      <c r="B108" s="21">
+      <c r="B109" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="17">
+    <row r="110" spans="1:4">
+      <c r="A110" s="17">
         <v>46148</v>
       </c>
-      <c r="B109" s="15">
+      <c r="B110" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="17">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="17">
         <v>46147</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="17">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="17">
         <v>46146</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="18">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="18">
         <v>46142</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46141</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46140</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46139</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46136</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46135</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46134</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46133</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46132</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46129</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46128</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46127</v>
       </c>
-      <c r="B123" s="38">
+      <c r="B124" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46126</v>
       </c>
-      <c r="B124" s="38">
+      <c r="B125" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46125</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B126" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C126" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="18">
+    <row r="127" spans="1:3">
+      <c r="A127" s="18">
         <v>46122</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B127" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C126" s="29">
+      <c r="C127" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="18">
+    <row r="128" spans="1:3">
+      <c r="A128" s="18">
         <v>46121</v>
       </c>
-      <c r="B127" s="15">
+      <c r="B128" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C127" s="29">
+      <c r="C128" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="18">
+    <row r="129" spans="1:3">
+      <c r="A129" s="18">
         <v>46120</v>
       </c>
-      <c r="B128" s="15">
+      <c r="B129" s="15">
         <v>580.56056466999996</v>
       </c>
-      <c r="C128" s="29">
-        <f>+(B128-B129)/B129</f>
+      <c r="C129" s="29">
+        <f>+(B129-B130)/B130</f>
         <v>3.9632497533121036</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
-      <c r="A129" s="18">
+    <row r="130" spans="1:3">
+      <c r="A130" s="18">
         <v>46119</v>
       </c>
-      <c r="B129" s="15">
+      <c r="B130" s="15">
         <v>116.97186189</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
-      <c r="A130" s="18">
+    <row r="131" spans="1:3">
+      <c r="A131" s="18">
         <v>46118</v>
       </c>
-      <c r="B130" s="15">
+      <c r="B131" s="15">
         <v>6972.36861443</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
-      <c r="A131" s="18">
+    <row r="132" spans="1:3">
+      <c r="A132" s="18">
         <v>46113</v>
       </c>
-      <c r="B131" s="15">
+      <c r="B132" s="15">
         <v>540.00852741999995</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="18">
+    <row r="133" spans="1:3">
+      <c r="A133" s="18">
         <v>46112</v>
       </c>
-      <c r="B132" s="15">
+      <c r="B133" s="15">
         <v>5262.3389565099997</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="18">
+    <row r="134" spans="1:3">
+      <c r="A134" s="18">
         <v>46111</v>
       </c>
-      <c r="B133" s="15">
+      <c r="B134" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7829,7 +7864,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -8600,6 +8635,32 @@
         <v>4.8637545144343264</v>
       </c>
     </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B30" s="16">
+        <v>84394676.288930014</v>
+      </c>
+      <c r="C30" s="16">
+        <v>2750338997.4745512</v>
+      </c>
+      <c r="D30" s="16">
+        <v>222739165.56059</v>
+      </c>
+      <c r="E30" s="16">
+        <v>3057472839.3240709</v>
+      </c>
+      <c r="F30" s="16">
+        <v>41787376.816790007</v>
+      </c>
+      <c r="G30" s="16">
+        <v>3099260216.140861</v>
+      </c>
+      <c r="H30" s="26">
+        <v>-0.48737705449418689</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8607,7 +8668,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G121"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10205,7 +10266,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E121" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E122" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11157,6 +11218,27 @@
       </c>
       <c r="F121" s="31">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" s="24">
+        <v>46310</v>
+      </c>
+      <c r="B122" s="25">
+        <v>12991</v>
+      </c>
+      <c r="C122" s="23">
+        <v>3</v>
+      </c>
+      <c r="D122" s="25">
+        <v>12994</v>
+      </c>
+      <c r="E122" s="30">
+        <f t="shared" si="4"/>
+        <v>-5.3842012152911312E-4</v>
+      </c>
+      <c r="F122" s="31">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10125" tabRatio="819"/>
+    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10125" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2996,7 +2996,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3004,7 +3004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:H141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5723,6 +5723,26 @@
         <v>3.71</v>
       </c>
     </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="20">
+        <v>46314</v>
+      </c>
+      <c r="B141" s="16">
+        <v>0</v>
+      </c>
+      <c r="C141" s="19"/>
+      <c r="D141" s="16">
+        <v>0</v>
+      </c>
+      <c r="E141" s="19"/>
+      <c r="F141" s="16">
+        <v>0</v>
+      </c>
+      <c r="G141" s="19"/>
+      <c r="H141" s="16">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5731,7 +5751,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5759,15 +5779,15 @@
       </c>
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="23" t="s">
-        <v>40</v>
+      <c r="A2" s="24">
+        <v>46314</v>
       </c>
       <c r="B2" s="23">
-        <v>195620.76542108</v>
+        <v>159658.86505789001</v>
       </c>
       <c r="C2" s="29">
         <f>+(B2-B3)/B3</f>
-        <v>0.39348231037382758</v>
+        <v>-0.18383477994159175</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5777,15 +5797,15 @@
       </c>
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="24">
-        <v>46310</v>
+      <c r="A3" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B3" s="23">
-        <v>140382.66863150999</v>
+        <v>195620.76542108</v>
       </c>
       <c r="C3" s="29">
         <f>+(B3-B4)/B4</f>
-        <v>11.24948691206232</v>
+        <v>0.39348231037382758</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5796,14 +5816,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B4" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C4" s="29">
         <f>+(B4-B5)/B5</f>
-        <v>-0.88352658705352882</v>
+        <v>11.24948691206232</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5814,14 +5834,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B5" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C5" s="29">
         <f>+(B5-B6)/B6</f>
-        <v>-0.6788555314993624</v>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5832,14 +5852,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B6" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C6" s="29">
-        <f t="shared" ref="C6:C16" si="0">+(B6-B7)/B7</f>
-        <v>9.336258026433894E-2</v>
+        <f>+(B6-B7)/B7</f>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5850,1549 +5870,1561 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B7" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C7" s="29">
+        <f t="shared" ref="C7:C17" si="0">+(B7-B8)/B8</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>10177.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24">
         <v>46303</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B8" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C8" s="29">
         <f t="shared" si="0"/>
         <v>-3.649289843956157E-2</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="6">
-        <v>10177.18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="24">
+      <c r="D8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="33">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24">
         <v>46302</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B9" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>3.9357330833461011E-3</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="33">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="24">
+      <c r="D9" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24">
         <v>46301</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B10" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>-2.9955821881414251E-2</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="24">
+      <c r="D10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="39">
+        <v>70928.40866225904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46300</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>-0.13794268733409284</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="39">
-        <v>70928.40866225904</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46297</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>0.2638202658078479</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46296</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>0.35910087116479922</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46295</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>8.8268407504102413</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46294</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="0"/>
         <v>-0.85681185394119452</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46293</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="0"/>
         <v>-0.49898704513189668</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46290</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="0"/>
         <v>0.55858664283872839</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B17" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C17" s="29">
-        <f t="shared" ref="C17:C86" si="1">+(B17-B18)/B18</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
-    </row>
     <row r="18" spans="1:5">
       <c r="A18" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B18" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C18" s="29">
+        <f t="shared" ref="C18:C87" si="1">+(B18-B19)/B19</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46288</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46287</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46286</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46283</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46282</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46281</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46280</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46276</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46275</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46274</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46273</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46272</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46269</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46268</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46267</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46266</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46265</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46262</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46261</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46260</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46259</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46256</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46255</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46254</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46253</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46252</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46251</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46248</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46247</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46246</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46245</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46244</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46241</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46240</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46239</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46238</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46237</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46234</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46233</v>
       </c>
-      <c r="B56">
+      <c r="B57">
         <v>466.33578662999997</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46232</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46231</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46108</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46226</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46225</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46224</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46220</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46219</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46218</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46217</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46216</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46213</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46212</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46211</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46210</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46209</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46206</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46205</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46204</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46203</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46198</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46196</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46195</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46192</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46191</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46190</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46189</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46188</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>8.42</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46185</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46184</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B87" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C87" s="29">
-        <f t="shared" ref="C87:C128" si="2">+(B87-B88)/B88</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="88" spans="1:3">
       <c r="A88" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B88" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C88" s="29">
+        <f t="shared" ref="C88:C129" si="2">+(B88-B89)/B89</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46182</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46178</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46177</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46176</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46175</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46174</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46171</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>45074</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46169</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46168</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46167</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46164</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46163</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46162</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46161</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46157</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46156</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46155</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="24">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="24">
         <v>46154</v>
       </c>
-      <c r="B106" s="23">
+      <c r="B107" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="24">
+    <row r="108" spans="1:4">
+      <c r="A108" s="24">
         <v>46153</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B108" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="24">
+    <row r="109" spans="1:4">
+      <c r="A109" s="24">
         <v>46150</v>
       </c>
-      <c r="B108" s="23">
+      <c r="B109" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="22">
+    <row r="110" spans="1:4">
+      <c r="A110" s="22">
         <v>46149</v>
       </c>
-      <c r="B109" s="21">
+      <c r="B110" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="17">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="17">
         <v>46148</v>
       </c>
-      <c r="B110" s="15">
+      <c r="B111" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="17">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="17">
         <v>46147</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="17">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="17">
         <v>46146</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="18">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="18">
         <v>46142</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46141</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46140</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46139</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46136</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46135</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46134</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46133</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46132</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46129</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46128</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46127</v>
       </c>
-      <c r="B124" s="38">
+      <c r="B125" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46126</v>
       </c>
-      <c r="B125" s="38">
+      <c r="B126" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C126" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="18">
+    <row r="127" spans="1:3">
+      <c r="A127" s="18">
         <v>46125</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B127" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C126" s="29">
+      <c r="C127" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="18">
+    <row r="128" spans="1:3">
+      <c r="A128" s="18">
         <v>46122</v>
       </c>
-      <c r="B127" s="15">
+      <c r="B128" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C127" s="29">
+      <c r="C128" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="18">
+    <row r="129" spans="1:3">
+      <c r="A129" s="18">
         <v>46121</v>
       </c>
-      <c r="B128" s="15">
+      <c r="B129" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C128" s="29">
+      <c r="C129" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B129" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C129" s="29">
-        <f>+(B129-B130)/B130</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="130" spans="1:3">
       <c r="A130" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B130" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C130" s="29">
+        <f>+(B130-B131)/B131</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B131" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B132" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B133" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B134" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" s="18">
         <v>46111</v>
       </c>
-      <c r="B134" s="15">
+      <c r="B135" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8668,7 +8700,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10266,7 +10298,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E122" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E123" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11239,6 +11271,27 @@
       </c>
       <c r="F122" s="31">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" s="24">
+        <v>46311</v>
+      </c>
+      <c r="B123" s="25">
+        <v>13375</v>
+      </c>
+      <c r="C123" s="23">
+        <v>3</v>
+      </c>
+      <c r="D123" s="25">
+        <v>13378</v>
+      </c>
+      <c r="E123" s="30">
+        <f t="shared" si="4"/>
+        <v>2.9552100969678315E-2</v>
+      </c>
+      <c r="F123" s="31">
+        <v>2.96</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10125" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10140" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2996,7 +2996,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3004,7 +3004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5743,6 +5743,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="20">
+        <v>46315</v>
+      </c>
+      <c r="B142" s="16">
+        <v>0</v>
+      </c>
+      <c r="C142" s="19"/>
+      <c r="D142" s="16">
+        <v>0</v>
+      </c>
+      <c r="E142" s="19"/>
+      <c r="F142" s="16">
+        <v>0</v>
+      </c>
+      <c r="G142" s="19"/>
+      <c r="H142" s="16">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5751,7 +5771,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5780,14 +5800,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B2" s="23">
-        <v>159658.86505789001</v>
+        <v>78030.063477150004</v>
       </c>
       <c r="C2" s="29">
         <f>+(B2-B3)/B3</f>
-        <v>-0.18383477994159175</v>
+        <v>-0.51127008544838759</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5797,15 +5817,15 @@
       </c>
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="23" t="s">
-        <v>40</v>
+      <c r="A3" s="24">
+        <v>46314</v>
       </c>
       <c r="B3" s="23">
-        <v>195620.76542108</v>
+        <v>159658.86505789001</v>
       </c>
       <c r="C3" s="29">
         <f>+(B3-B4)/B4</f>
-        <v>0.39348231037382758</v>
+        <v>-0.18383477994159175</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5815,15 +5835,15 @@
       </c>
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="24">
-        <v>46310</v>
+      <c r="A4" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B4" s="23">
-        <v>140382.66863150999</v>
+        <v>195620.76542108</v>
       </c>
       <c r="C4" s="29">
         <f>+(B4-B5)/B5</f>
-        <v>11.24948691206232</v>
+        <v>0.39348231037382758</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5834,14 +5854,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B5" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C5" s="29">
         <f>+(B5-B6)/B6</f>
-        <v>-0.88352658705352882</v>
+        <v>11.24948691206232</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5852,14 +5872,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B6" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C6" s="29">
         <f>+(B6-B7)/B7</f>
-        <v>-0.6788555314993624</v>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5870,14 +5890,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B7" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C7" s="29">
-        <f t="shared" ref="C7:C17" si="0">+(B7-B8)/B8</f>
-        <v>9.336258026433894E-2</v>
+        <f>+(B7-B8)/B8</f>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5888,1543 +5908,1555 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B8" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C8" s="29">
+        <f t="shared" ref="C8:C18" si="0">+(B8-B9)/B9</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="33">
+        <v>15136.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24">
         <v>46303</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B9" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C9" s="29">
         <f t="shared" si="0"/>
         <v>-3.649289843956157E-2</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="33">
-        <v>15136.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="24">
+      <c r="D9" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24">
         <v>46302</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B10" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C10" s="29">
         <f t="shared" si="0"/>
         <v>3.9357330833461011E-3</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="24">
+      <c r="D10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="39">
+        <v>70928.40866225904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46301</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="0"/>
         <v>-2.9955821881414251E-2</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="39">
-        <v>70928.40866225904</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46300</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="0"/>
         <v>-0.13794268733409284</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46297</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="0"/>
         <v>0.2638202658078479</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46296</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="0"/>
         <v>0.35910087116479922</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46295</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="0"/>
         <v>8.8268407504102413</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46294</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="0"/>
         <v>-0.85681185394119452</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46293</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="0"/>
         <v>-0.49898704513189668</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46290</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="0"/>
         <v>0.55858664283872839</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B18" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C18" s="29">
-        <f t="shared" ref="C18:C87" si="1">+(B18-B19)/B19</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
-    </row>
     <row r="19" spans="1:5">
       <c r="A19" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B19" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C19" s="29">
+        <f t="shared" ref="C19:C88" si="1">+(B19-B20)/B20</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46288</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>0.18793186198768058</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46287</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>6.7871692861553368E-2</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46286</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>0.25618058698994745</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46283</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>0.32349555871151542</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46282</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="1"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46281</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="1"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46280</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="1"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46276</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="1"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46275</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="1"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46274</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="1"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46273</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="1"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46272</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="1"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46269</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="1"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46268</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="1"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46267</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="1"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46266</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="1"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46265</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="1"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46262</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="1"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46261</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="1"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46260</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="1"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46259</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="1"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46256</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="1"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46255</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="1"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46254</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="1"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46253</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="1"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46252</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="1"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46251</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="1"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46248</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="1"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46247</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="1"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46246</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="1"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46245</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="1"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46244</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="1"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46241</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="1"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46240</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="1"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46239</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="1"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46238</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="1"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46237</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="1"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46234</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="1"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46233</v>
       </c>
-      <c r="B57">
+      <c r="B58">
         <v>466.33578662999997</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="1"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46232</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="1"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46231</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="1"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46108</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="1"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46226</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="1"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46225</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="1"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46224</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="1"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46220</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="1"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46219</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="1"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46218</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="1"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46217</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="1"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46216</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="1"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46213</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="1"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46212</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="1"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46211</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="1"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46210</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="1"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46209</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="1"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46206</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="1"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46205</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="1"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46204</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="1"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46203</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="1"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46198</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="1"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46196</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="1"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46195</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="1"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46192</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="1"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46191</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="1"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46190</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="1"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46189</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="1"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46188</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>8.42</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="1"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46185</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="1"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46184</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="1"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B88" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C88" s="29">
-        <f t="shared" ref="C88:C129" si="2">+(B88-B89)/B89</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="89" spans="1:3">
       <c r="A89" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B89" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C89" s="29">
+        <f t="shared" ref="C89:C130" si="2">+(B89-B90)/B90</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46182</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46178</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46177</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46176</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46175</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="2"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46174</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="2"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46171</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="2"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>45074</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="2"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46169</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="2"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46168</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="2"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46167</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="2"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46164</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="2"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46163</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="2"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46162</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="2"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46161</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="2"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46157</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="2"/>
         <v>35.243819791014161</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46156</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="2"/>
         <v>82.182099964255912</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="24">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="24">
         <v>46155</v>
       </c>
-      <c r="B106" s="23">
+      <c r="B107" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="2"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="24">
+    <row r="108" spans="1:4">
+      <c r="A108" s="24">
         <v>46154</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B108" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="2"/>
         <v>-0.95811572537747924</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="24">
+    <row r="109" spans="1:4">
+      <c r="A109" s="24">
         <v>46153</v>
       </c>
-      <c r="B108" s="23">
+      <c r="B109" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="2"/>
         <v>-0.32064889280191988</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="24">
+    <row r="110" spans="1:4">
+      <c r="A110" s="24">
         <v>46150</v>
       </c>
-      <c r="B109" s="23">
+      <c r="B110" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="2"/>
         <v>178.18998455533497</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="22">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="22">
         <v>46149</v>
       </c>
-      <c r="B110" s="21">
+      <c r="B111" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="2"/>
         <v>-0.82294618034282907</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="17">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="17">
         <v>46148</v>
       </c>
-      <c r="B111" s="15">
+      <c r="B112" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="2"/>
         <v>-0.99115816107458954</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="17">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="17">
         <v>46147</v>
       </c>
-      <c r="B112" s="15">
+      <c r="B113" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="2"/>
         <v>0.70107388483787059</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="17">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="17">
         <v>46146</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="2"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="18">
+    <row r="115" spans="1:3">
+      <c r="A115" s="18">
         <v>46142</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="2"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
+    <row r="116" spans="1:3">
+      <c r="A116" s="18">
         <v>46141</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="2"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46140</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="2"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46139</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="2"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46136</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="2"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46135</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="2"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46134</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="2"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46133</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="2"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46132</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="2"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46129</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="2"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46128</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B125" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="2"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46127</v>
       </c>
-      <c r="B125" s="38">
+      <c r="B126" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C126" s="29">
         <f t="shared" si="2"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="18">
+    <row r="127" spans="1:3">
+      <c r="A127" s="18">
         <v>46126</v>
       </c>
-      <c r="B126" s="38">
+      <c r="B127" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C126" s="29">
+      <c r="C127" s="29">
         <f t="shared" si="2"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="18">
+    <row r="128" spans="1:3">
+      <c r="A128" s="18">
         <v>46125</v>
       </c>
-      <c r="B127" s="15">
+      <c r="B128" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C127" s="29">
+      <c r="C128" s="29">
         <f t="shared" si="2"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="18">
+    <row r="129" spans="1:3">
+      <c r="A129" s="18">
         <v>46122</v>
       </c>
-      <c r="B128" s="15">
+      <c r="B129" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C128" s="29">
+      <c r="C129" s="29">
         <f t="shared" si="2"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="18">
+    <row r="130" spans="1:3">
+      <c r="A130" s="18">
         <v>46121</v>
       </c>
-      <c r="B129" s="15">
+      <c r="B130" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C129" s="29">
+      <c r="C130" s="29">
         <f t="shared" si="2"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B130" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C130" s="29">
-        <f>+(B130-B131)/B131</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="131" spans="1:3">
       <c r="A131" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B131" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C131" s="29">
+        <f>+(B131-B132)/B132</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B132" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B133" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B134" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B135" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" s="18">
         <v>46111</v>
       </c>
-      <c r="B135" s="15">
+      <c r="B136" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8700,7 +8732,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G123"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10298,7 +10330,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E123" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E124" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11292,6 +11324,27 @@
       </c>
       <c r="F123" s="31">
         <v>2.96</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" s="24">
+        <v>46314</v>
+      </c>
+      <c r="B124" s="25">
+        <v>13280</v>
+      </c>
+      <c r="C124" s="23">
+        <v>3</v>
+      </c>
+      <c r="D124" s="25">
+        <v>13283</v>
+      </c>
+      <c r="E124" s="30">
+        <f t="shared" si="4"/>
+        <v>-7.1012109433398118E-3</v>
+      </c>
+      <c r="F124" s="31">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10140" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10140" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -2996,7 +2996,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3004,7 +3004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H142"/>
+  <dimension ref="A1:H143"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5763,6 +5763,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="20">
+        <v>46316</v>
+      </c>
+      <c r="B143" s="16">
+        <v>500</v>
+      </c>
+      <c r="C143" s="19"/>
+      <c r="D143" s="16">
+        <v>50</v>
+      </c>
+      <c r="E143" s="19"/>
+      <c r="F143" s="16">
+        <v>50</v>
+      </c>
+      <c r="G143" s="19"/>
+      <c r="H143" s="16">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5771,7 +5791,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5800,14 +5820,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B2" s="23">
-        <v>78030.063477150004</v>
+        <v>50526.509366320002</v>
       </c>
       <c r="C2" s="29">
-        <f>+(B2-B3)/B3</f>
-        <v>-0.51127008544838759</v>
+        <f t="shared" ref="C2:C8" si="0">+(B2-B3)/B3</f>
+        <v>-0.35247381438929659</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5818,14 +5838,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B3" s="23">
-        <v>159658.86505789001</v>
+        <v>78030.063477150004</v>
       </c>
       <c r="C3" s="29">
-        <f>+(B3-B4)/B4</f>
-        <v>-0.18383477994159175</v>
+        <f t="shared" si="0"/>
+        <v>-0.51127008544838759</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5835,15 +5855,15 @@
       </c>
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A4" s="23" t="s">
-        <v>40</v>
+      <c r="A4" s="24">
+        <v>46314</v>
       </c>
       <c r="B4" s="23">
-        <v>195620.76542108</v>
+        <v>159658.86505789001</v>
       </c>
       <c r="C4" s="29">
-        <f>+(B4-B5)/B5</f>
-        <v>0.39348231037382758</v>
+        <f t="shared" si="0"/>
+        <v>-0.18383477994159175</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5853,15 +5873,15 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A5" s="24">
-        <v>46310</v>
+      <c r="A5" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B5" s="23">
-        <v>140382.66863150999</v>
+        <v>195620.76542108</v>
       </c>
       <c r="C5" s="29">
-        <f>+(B5-B6)/B6</f>
-        <v>11.24948691206232</v>
+        <f t="shared" si="0"/>
+        <v>0.39348231037382758</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5872,14 +5892,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B6" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C6" s="29">
-        <f>+(B6-B7)/B7</f>
-        <v>-0.88352658705352882</v>
+        <f t="shared" si="0"/>
+        <v>11.24948691206232</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5890,14 +5910,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B7" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C7" s="29">
-        <f>+(B7-B8)/B8</f>
-        <v>-0.6788555314993624</v>
+        <f t="shared" si="0"/>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5908,14 +5928,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B8" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C8" s="29">
-        <f t="shared" ref="C8:C18" si="0">+(B8-B9)/B9</f>
-        <v>9.336258026433894E-2</v>
+        <f t="shared" si="0"/>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5926,14 +5946,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B9" s="23">
-        <v>280223.23481502</v>
+        <v>306385.59906737</v>
       </c>
       <c r="C9" s="29">
-        <f t="shared" si="0"/>
-        <v>-3.649289843956157E-2</v>
+        <f t="shared" ref="C9:C19" si="1">+(B9-B10)/B10</f>
+        <v>9.336258026433894E-2</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5944,14 +5964,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B10" s="23">
-        <v>290836.70931037999</v>
+        <v>280223.23481502</v>
       </c>
       <c r="C10" s="29">
-        <f t="shared" si="0"/>
-        <v>3.9357330833461011E-3</v>
+        <f t="shared" si="1"/>
+        <v>-3.649289843956157E-2</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>39</v>
@@ -5962,1501 +5982,1513 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B11" s="23">
-        <v>289696.54104963999</v>
+        <v>290836.70931037999</v>
       </c>
       <c r="C11" s="29">
-        <f t="shared" si="0"/>
-        <v>-2.9955821881414251E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.9357330833461011E-3</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B12" s="23">
-        <v>298642.62637141999</v>
+        <v>289696.54104963999</v>
       </c>
       <c r="C12" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.13794268733409284</v>
+        <f t="shared" si="1"/>
+        <v>-2.9955821881414251E-2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="24">
-        <v>46297</v>
+        <v>46300</v>
       </c>
       <c r="B13" s="23">
-        <v>346430.12939344998</v>
+        <v>298642.62637141999</v>
       </c>
       <c r="C13" s="29">
-        <f t="shared" si="0"/>
-        <v>0.2638202658078479</v>
+        <f t="shared" si="1"/>
+        <v>-0.13794268733409284</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="24">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B14" s="23">
-        <v>274113.44695601001</v>
+        <v>346430.12939344998</v>
       </c>
       <c r="C14" s="29">
-        <f t="shared" si="0"/>
-        <v>0.35910087116479922</v>
+        <f t="shared" si="1"/>
+        <v>0.2638202658078479</v>
       </c>
       <c r="E14" s="35"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="24">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B15" s="23">
-        <v>201687.34548826001</v>
+        <v>274113.44695601001</v>
       </c>
       <c r="C15" s="29">
-        <f t="shared" si="0"/>
-        <v>8.8268407504102413</v>
+        <f t="shared" si="1"/>
+        <v>0.35910087116479922</v>
       </c>
       <c r="E15" s="35"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="24">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B16" s="23">
-        <v>20524.128823380001</v>
+        <v>201687.34548826001</v>
       </c>
       <c r="C16" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.85681185394119452</v>
+        <f t="shared" si="1"/>
+        <v>8.8268407504102413</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="24">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B17" s="23">
-        <v>143336.78721526999</v>
+        <v>20524.128823380001</v>
       </c>
       <c r="C17" s="29">
-        <f t="shared" si="0"/>
-        <v>-0.49898704513189668</v>
+        <f t="shared" si="1"/>
+        <v>-0.85681185394119452</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="24">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="B18" s="23">
-        <v>286093.97386342002</v>
+        <v>143336.78721526999</v>
       </c>
       <c r="C18" s="29">
-        <f t="shared" si="0"/>
-        <v>0.55858664283872839</v>
+        <f t="shared" si="1"/>
+        <v>-0.49898704513189668</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="24">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B19" s="23">
-        <v>183559.87790473</v>
+        <v>286093.97386342002</v>
       </c>
       <c r="C19" s="29">
-        <f t="shared" ref="C19:C88" si="1">+(B19-B20)/B20</f>
-        <v>5.2320875570372835E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.55858664283872839</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="24">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="B20" s="23">
-        <v>174433.37119511</v>
+        <v>183559.87790473</v>
       </c>
       <c r="C20" s="29">
-        <f t="shared" si="1"/>
-        <v>0.18793186198768058</v>
+        <f t="shared" ref="C20:C89" si="2">+(B20-B21)/B21</f>
+        <v>5.2320875570372835E-2</v>
       </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="24">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="B21" s="23">
-        <v>146837.85895197999</v>
+        <v>174433.37119511</v>
       </c>
       <c r="C21" s="29">
-        <f t="shared" si="1"/>
-        <v>6.7871692861553368E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.18793186198768058</v>
       </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="24">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B22" s="23">
-        <v>137505.15153979001</v>
+        <v>146837.85895197999</v>
       </c>
       <c r="C22" s="29">
-        <f t="shared" si="1"/>
-        <v>0.25618058698994745</v>
+        <f t="shared" si="2"/>
+        <v>6.7871692861553368E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="24">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="B23" s="23">
-        <v>109462.8853239</v>
+        <v>137505.15153979001</v>
       </c>
       <c r="C23" s="29">
-        <f t="shared" si="1"/>
-        <v>0.32349555871151542</v>
+        <f t="shared" si="2"/>
+        <v>0.25618058698994745</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="24">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B24" s="23">
-        <v>82707.40661228</v>
+        <v>109462.8853239</v>
       </c>
       <c r="C24" s="29">
-        <f t="shared" si="1"/>
-        <v>28.486447660130633</v>
+        <f t="shared" si="2"/>
+        <v>0.32349555871151542</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="24">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B25" s="23">
-        <v>2804.9294905100001</v>
+        <v>82707.40661228</v>
       </c>
       <c r="C25" s="29">
-        <f t="shared" si="1"/>
-        <v>54.85948274687906</v>
+        <f t="shared" si="2"/>
+        <v>28.486447660130633</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="24">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B26" s="23">
-        <v>50.214025489999997</v>
+        <v>2804.9294905100001</v>
       </c>
       <c r="C26" s="29">
-        <f t="shared" si="1"/>
-        <v>0.37097114686342592</v>
+        <f t="shared" si="2"/>
+        <v>54.85948274687906</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="24">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B27" s="23">
-        <v>36.626609979999998</v>
+        <v>50.214025489999997</v>
       </c>
       <c r="C27" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.67806849277578529</v>
+        <f t="shared" si="2"/>
+        <v>0.37097114686342592</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="24">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B28" s="23">
-        <v>113.77143633999999</v>
+        <v>36.626609979999998</v>
       </c>
       <c r="C28" s="29">
-        <f t="shared" si="1"/>
-        <v>18.560573043109468</v>
+        <f t="shared" si="2"/>
+        <v>-0.67806849277578529</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="24">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B29" s="23">
-        <v>5.8163651999999999</v>
+        <v>113.77143633999999</v>
       </c>
       <c r="C29" s="29">
-        <f t="shared" si="1"/>
-        <v>0.64045278098882874</v>
+        <f t="shared" si="2"/>
+        <v>18.560573043109468</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="24">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B30" s="23">
-        <v>3.5455852600000002</v>
+        <v>5.8163651999999999</v>
       </c>
       <c r="C30" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.82640880552358198</v>
+        <f t="shared" si="2"/>
+        <v>0.64045278098882874</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="24">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B31" s="23">
-        <v>20.42491424</v>
+        <v>3.5455852600000002</v>
       </c>
       <c r="C31" s="29">
-        <f t="shared" si="1"/>
-        <v>2.4737529624349173</v>
+        <f t="shared" si="2"/>
+        <v>-0.82640880552358198</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="24">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B32" s="23">
-        <v>5.8797831800000004</v>
+        <v>20.42491424</v>
       </c>
       <c r="C32" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.97953700801723442</v>
+        <f t="shared" si="2"/>
+        <v>2.4737529624349173</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="24">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B33" s="23">
-        <v>287.33741307000003</v>
+        <v>5.8797831800000004</v>
       </c>
       <c r="C33" s="29">
-        <f t="shared" si="1"/>
-        <v>80.163058476193896</v>
+        <f t="shared" si="2"/>
+        <v>-0.97953700801723442</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="24">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B34" s="23">
-        <v>3.5402487100000002</v>
+        <v>287.33741307000003</v>
       </c>
       <c r="C34" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.77463732472189939</v>
+        <f t="shared" si="2"/>
+        <v>80.163058476193896</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="24">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B35" s="23">
-        <v>15.709117340000001</v>
+        <v>3.5402487100000002</v>
       </c>
       <c r="C35" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99727371031195</v>
+        <f t="shared" si="2"/>
+        <v>-0.77463732472189939</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="24">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B36" s="23">
-        <v>5762.0866222900004</v>
+        <v>15.709117340000001</v>
       </c>
       <c r="C36" s="29">
-        <f t="shared" si="1"/>
-        <v>1028.4103166122507</v>
+        <f t="shared" si="2"/>
+        <v>-0.99727371031195</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="24">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B37" s="23">
-        <v>5.5974634500000002</v>
+        <v>5762.0866222900004</v>
       </c>
       <c r="C37" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.98760095272084658</v>
+        <f t="shared" si="2"/>
+        <v>1028.4103166122507</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="24">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B38" s="23">
-        <v>451.44302815999998</v>
+        <v>5.5974634500000002</v>
       </c>
       <c r="C38" s="29">
-        <f t="shared" si="1"/>
-        <v>98.812318362183703</v>
+        <f t="shared" si="2"/>
+        <v>-0.98760095272084658</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" s="24">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B39" s="23">
-        <v>4.5229189700000001</v>
+        <v>451.44302815999998</v>
       </c>
       <c r="C39" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.9864837734804992</v>
+        <f t="shared" si="2"/>
+        <v>98.812318362183703</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" s="24">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B40" s="23">
-        <v>334.62882287999997</v>
+        <v>4.5229189700000001</v>
       </c>
       <c r="C40" s="29">
-        <f t="shared" si="1"/>
-        <v>74.639780601233326</v>
+        <f t="shared" si="2"/>
+        <v>-0.9864837734804992</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="24">
-        <v>46256</v>
+        <v>46259</v>
       </c>
       <c r="B41" s="23">
-        <v>4.4239792900000001</v>
+        <v>334.62882287999997</v>
       </c>
       <c r="C41" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.96494750708048294</v>
+        <f t="shared" si="2"/>
+        <v>74.639780601233326</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" s="24">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B42" s="23">
-        <v>126.21011864</v>
+        <v>4.4239792900000001</v>
       </c>
       <c r="C42" s="29">
-        <f t="shared" si="1"/>
-        <v>71.190985743560688</v>
+        <f t="shared" si="2"/>
+        <v>-0.96494750708048294</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" s="24">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B43" s="23">
-        <v>1.7482808599999999</v>
+        <v>126.21011864</v>
       </c>
       <c r="C43" s="29">
-        <f t="shared" si="1"/>
-        <v>-5.8184422793468707E-2</v>
+        <f t="shared" si="2"/>
+        <v>71.190985743560688</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" s="24">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B44" s="23">
-        <v>1.8562879000000001</v>
+        <v>1.7482808599999999</v>
       </c>
       <c r="C44" s="29">
-        <f t="shared" si="1"/>
-        <v>2.7977445325652688E-3</v>
+        <f t="shared" si="2"/>
+        <v>-5.8184422793468707E-2</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="24">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B45" s="23">
-        <v>1.8511089700000001</v>
+        <v>1.8562879000000001</v>
       </c>
       <c r="C45" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.85226798513183877</v>
+        <f t="shared" si="2"/>
+        <v>2.7977445325652688E-3</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" s="24">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B46" s="23">
-        <v>12.53018157</v>
+        <v>1.8511089700000001</v>
       </c>
       <c r="C46" s="29">
-        <f t="shared" si="1"/>
-        <v>1.9051656117130662</v>
+        <f t="shared" si="2"/>
+        <v>-0.85226798513183877</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" s="24">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B47" s="23">
-        <v>4.3130696300000002</v>
+        <v>12.53018157</v>
       </c>
       <c r="C47" s="29">
-        <f t="shared" si="1"/>
-        <v>0.67644958648237985</v>
+        <f t="shared" si="2"/>
+        <v>1.9051656117130662</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" s="24">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B48" s="23">
-        <v>2.5727404300000001</v>
+        <v>4.3130696300000002</v>
       </c>
       <c r="C48" s="29">
-        <f t="shared" si="1"/>
-        <v>7.9800987331472867E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.67644958648237985</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="24">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B49" s="23">
-        <v>2.3826061100000002</v>
+        <v>2.5727404300000001</v>
       </c>
       <c r="C49" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.998836660607344</v>
+        <f t="shared" si="2"/>
+        <v>7.9800987331472867E-2</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" s="24">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B50" s="23">
-        <v>2048.0748137999999</v>
+        <v>2.3826061100000002</v>
       </c>
       <c r="C50" s="29">
-        <f t="shared" si="1"/>
-        <v>493.39746561225513</v>
+        <f t="shared" si="2"/>
+        <v>-0.998836660607344</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" s="24">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B51" s="23">
-        <v>4.14256738</v>
+        <v>2048.0748137999999</v>
       </c>
       <c r="C51" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99973486131357592</v>
+        <f t="shared" si="2"/>
+        <v>493.39746561225513</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="24">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B52" s="23">
-        <v>15624.152913600001</v>
+        <v>4.14256738</v>
       </c>
       <c r="C52" s="29">
-        <f t="shared" si="1"/>
-        <v>4796.873754983676</v>
+        <f t="shared" si="2"/>
+        <v>-0.99973486131357592</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="24">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B53" s="23">
-        <v>3.2564743699999998</v>
+        <v>15624.152913600001</v>
       </c>
       <c r="C53" s="29">
-        <f t="shared" si="1"/>
-        <v>0.15942681787904545</v>
+        <f t="shared" si="2"/>
+        <v>4796.873754983676</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="24">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B54" s="23">
-        <v>2.8086933300000001</v>
+        <v>3.2564743699999998</v>
       </c>
       <c r="C54" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99437447438816284</v>
+        <f t="shared" si="2"/>
+        <v>0.15942681787904545</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" s="24">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B55" s="23">
-        <v>499.27660521000001</v>
+        <v>2.8086933300000001</v>
       </c>
       <c r="C55" s="29">
-        <f t="shared" si="1"/>
-        <v>75.11816589074563</v>
+        <f t="shared" si="2"/>
+        <v>-0.99437447438816284</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="24">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B56" s="23">
-        <v>6.5592306300000001</v>
+        <v>499.27660521000001</v>
       </c>
       <c r="C56" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99966330474421161</v>
+        <f t="shared" si="2"/>
+        <v>75.11816589074563</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="24">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B57" s="23">
-        <v>19481.20894855</v>
+        <v>6.5592306300000001</v>
       </c>
       <c r="C57" s="29">
-        <f t="shared" si="1"/>
-        <v>40.77506746658235</v>
+        <f t="shared" si="2"/>
+        <v>-0.99966330474421161</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" s="24">
-        <v>46233</v>
-      </c>
-      <c r="B58">
-        <v>466.33578662999997</v>
+        <v>46234</v>
+      </c>
+      <c r="B58" s="23">
+        <v>19481.20894855</v>
       </c>
       <c r="C58" s="29">
-        <f t="shared" si="1"/>
-        <v>3.5918026507549188</v>
+        <f t="shared" si="2"/>
+        <v>40.77506746658235</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" s="24">
-        <v>46232</v>
-      </c>
-      <c r="B59" s="23">
-        <v>101.55832515</v>
+        <v>46233</v>
+      </c>
+      <c r="B59">
+        <v>466.33578662999997</v>
       </c>
       <c r="C59" s="29">
-        <f t="shared" si="1"/>
-        <v>22.269067927747528</v>
+        <f t="shared" si="2"/>
+        <v>3.5918026507549188</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" s="24">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B60" s="23">
-        <v>4.3645205499999999</v>
+        <v>101.55832515</v>
       </c>
       <c r="C60" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.98047278251084946</v>
+        <f t="shared" si="2"/>
+        <v>22.269067927747528</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="24">
-        <v>46108</v>
+        <v>46231</v>
       </c>
       <c r="B61" s="23">
-        <v>223.50959897000001</v>
+        <v>4.3645205499999999</v>
       </c>
       <c r="C61" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99220607504587943</v>
+        <f t="shared" si="2"/>
+        <v>-0.98047278251084946</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="24">
-        <v>46226</v>
+        <v>46108</v>
       </c>
       <c r="B62" s="23">
-        <v>28677.412251940001</v>
+        <v>223.50959897000001</v>
       </c>
       <c r="C62" s="29">
-        <f t="shared" si="1"/>
-        <v>32.413800410299046</v>
+        <f t="shared" si="2"/>
+        <v>-0.99220607504587943</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" s="24">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B63" s="23">
-        <v>858.25054019000004</v>
+        <v>28677.412251940001</v>
       </c>
       <c r="C63" s="29">
-        <f t="shared" si="1"/>
-        <v>41.77708649767068</v>
+        <f t="shared" si="2"/>
+        <v>32.413800410299046</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="24">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B64" s="23">
-        <v>20.063323860000001</v>
+        <v>858.25054019000004</v>
       </c>
       <c r="C64" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99734079323279778</v>
+        <f t="shared" si="2"/>
+        <v>41.77708649767068</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="24">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B65" s="23">
-        <v>7544.8528890099997</v>
+        <v>20.063323860000001</v>
       </c>
       <c r="C65" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.54491271467140989</v>
+        <f t="shared" si="2"/>
+        <v>-0.99734079323279778</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="24">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B66" s="23">
-        <v>16578.913830919999</v>
+        <v>7544.8528890099997</v>
       </c>
       <c r="C66" s="29">
-        <f t="shared" si="1"/>
-        <v>1.1008050673763534</v>
+        <f t="shared" si="2"/>
+        <v>-0.54491271467140989</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="24">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B67" s="23">
-        <v>7891.6954687400003</v>
+        <v>16578.913830919999</v>
       </c>
       <c r="C67" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.79678113606112111</v>
+        <f t="shared" si="2"/>
+        <v>1.1008050673763534</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="24">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B68" s="23">
-        <v>38833.478919130001</v>
+        <v>7891.6954687400003</v>
       </c>
       <c r="C68" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.25771272667553924</v>
+        <f t="shared" si="2"/>
+        <v>-0.79678113606112111</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="24">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B69" s="23">
-        <v>52315.97026473</v>
+        <v>38833.478919130001</v>
       </c>
       <c r="C69" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.19048561913228002</v>
+        <f t="shared" si="2"/>
+        <v>-0.25771272667553924</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="24">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B70" s="23">
-        <v>64626.363040830001</v>
+        <v>52315.97026473</v>
       </c>
       <c r="C70" s="29">
-        <f t="shared" si="1"/>
-        <v>1.2916911129109088</v>
+        <f t="shared" si="2"/>
+        <v>-0.19048561913228002</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="24">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B71" s="23">
-        <v>28200.29395617</v>
+        <v>64626.363040830001</v>
       </c>
       <c r="C71" s="29">
-        <f t="shared" si="1"/>
-        <v>2.65997178100841</v>
+        <f t="shared" si="2"/>
+        <v>1.2916911129109088</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="24">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B72" s="23">
-        <v>7705.0577555</v>
+        <v>28200.29395617</v>
       </c>
       <c r="C72" s="29">
-        <f t="shared" si="1"/>
-        <v>0.84099979813836301</v>
+        <f t="shared" si="2"/>
+        <v>2.65997178100841</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="24">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B73" s="23">
-        <v>4185.2572516800001</v>
+        <v>7705.0577555</v>
       </c>
       <c r="C73" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.5358672604044985</v>
+        <f t="shared" si="2"/>
+        <v>0.84099979813836301</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="24">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B74" s="23">
-        <v>9017.3713134900008</v>
+        <v>4185.2572516800001</v>
       </c>
       <c r="C74" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.47344417767330416</v>
+        <f t="shared" si="2"/>
+        <v>-0.5358672604044985</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="24">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B75" s="23">
-        <v>17125.195337590001</v>
+        <v>9017.3713134900008</v>
       </c>
       <c r="C75" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.39167454677290181</v>
+        <f t="shared" si="2"/>
+        <v>-0.47344417767330416</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="24">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B76" s="23">
-        <v>28151.370695969999</v>
+        <v>17125.195337590001</v>
       </c>
       <c r="C76" s="29">
-        <f t="shared" si="1"/>
-        <v>27.450841046685248</v>
+        <f t="shared" si="2"/>
+        <v>-0.39167454677290181</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="24">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B77" s="23">
-        <v>989.47411254999997</v>
+        <v>28151.370695969999</v>
       </c>
       <c r="C77" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.82605795449481512</v>
+        <f t="shared" si="2"/>
+        <v>27.450841046685248</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="24">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B78" s="23">
-        <v>5688.5275189000004</v>
+        <v>989.47411254999997</v>
       </c>
       <c r="C78" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.82035890094428965</v>
+        <f t="shared" si="2"/>
+        <v>-0.82605795449481512</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="24">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="B79" s="23">
-        <v>31666.069450710002</v>
+        <v>5688.5275189000004</v>
       </c>
       <c r="C79" s="29">
-        <f t="shared" si="1"/>
-        <v>12.096519032059602</v>
+        <f t="shared" si="2"/>
+        <v>-0.82035890094428965</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="24">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B80" s="23">
-        <v>2417.8997009200002</v>
+        <v>31666.069450710002</v>
       </c>
       <c r="C80" s="29">
-        <f t="shared" si="1"/>
-        <v>0.40878477030033311</v>
+        <f t="shared" si="2"/>
+        <v>12.096519032059602</v>
       </c>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="24">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B81" s="23">
-        <v>1716.30170335</v>
+        <v>2417.8997009200002</v>
       </c>
       <c r="C81" s="29">
-        <f t="shared" si="1"/>
-        <v>103.40487339188886</v>
+        <f t="shared" si="2"/>
+        <v>0.40878477030033311</v>
       </c>
     </row>
     <row r="82" spans="1:3">
       <c r="A82" s="24">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="B82" s="23">
-        <v>16.43890412</v>
+        <v>1716.30170335</v>
       </c>
       <c r="C82" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.93907248343987781</v>
+        <f t="shared" si="2"/>
+        <v>103.40487339188886</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="A83" s="24">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B83" s="23">
-        <v>269.81083503999997</v>
+        <v>16.43890412</v>
       </c>
       <c r="C83" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.88259974628484428</v>
+        <f t="shared" si="2"/>
+        <v>-0.93907248343987781</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="24">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B84" s="23">
-        <v>2298.2133896800001</v>
+        <v>269.81083503999997</v>
       </c>
       <c r="C84" s="29">
-        <f t="shared" si="1"/>
-        <v>0.90523755264044037</v>
+        <f t="shared" si="2"/>
+        <v>-0.88259974628484428</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="24">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B85" s="23">
-        <v>1206.260808</v>
+        <v>2298.2133896800001</v>
       </c>
       <c r="C85" s="29">
-        <f t="shared" si="1"/>
-        <v>142.26137862232778</v>
+        <f t="shared" si="2"/>
+        <v>0.90523755264044037</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="24">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B86" s="23">
-        <v>8.42</v>
+        <v>1206.260808</v>
       </c>
       <c r="C86" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.5604660313731078</v>
+        <f t="shared" si="2"/>
+        <v>142.26137862232778</v>
       </c>
     </row>
     <row r="87" spans="1:3">
       <c r="A87" s="24">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B87" s="23">
-        <v>19.156653639999998</v>
+        <v>8.42</v>
       </c>
       <c r="C87" s="29">
-        <f t="shared" si="1"/>
-        <v>0.50703525245440206</v>
+        <f t="shared" si="2"/>
+        <v>-0.5604660313731078</v>
       </c>
     </row>
     <row r="88" spans="1:3">
       <c r="A88" s="24">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B88" s="23">
-        <v>12.711483429999999</v>
+        <v>19.156653639999998</v>
       </c>
       <c r="C88" s="29">
-        <f t="shared" si="1"/>
-        <v>-0.99943660659465605</v>
+        <f t="shared" si="2"/>
+        <v>0.50703525245440206</v>
       </c>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="24">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B89" s="23">
-        <v>22562.357509739999</v>
+        <v>12.711483429999999</v>
       </c>
       <c r="C89" s="29">
-        <f t="shared" ref="C89:C130" si="2">+(B89-B90)/B90</f>
-        <v>5.2639483520141219</v>
+        <f t="shared" si="2"/>
+        <v>-0.99943660659465605</v>
       </c>
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="24">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B90" s="23">
-        <v>3601.9386242999999</v>
+        <v>22562.357509739999</v>
       </c>
       <c r="C90" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.93820968147801931</v>
+        <f t="shared" ref="C90:C131" si="3">+(B90-B91)/B91</f>
+        <v>5.2639483520141219</v>
       </c>
     </row>
     <row r="91" spans="1:3">
       <c r="A91" s="24">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B91" s="23">
-        <v>58292.928576159997</v>
+        <v>3601.9386242999999</v>
       </c>
       <c r="C91" s="29">
-        <f t="shared" si="2"/>
-        <v>5.2345136037951523</v>
+        <f t="shared" si="3"/>
+        <v>-0.93820968147801931</v>
       </c>
     </row>
     <row r="92" spans="1:3">
       <c r="A92" s="24">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B92" s="23">
-        <v>9350.0363108799993</v>
+        <v>58292.928576159997</v>
       </c>
       <c r="C92" s="29">
-        <f t="shared" si="2"/>
-        <v>1.8327551324816331</v>
+        <f t="shared" si="3"/>
+        <v>5.2345136037951523</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="24">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B93" s="23">
-        <v>3300.6863896099999</v>
+        <v>9350.0363108799993</v>
       </c>
       <c r="C93" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.88947445735006914</v>
+        <f t="shared" si="3"/>
+        <v>1.8327551324816331</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="24">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B94" s="23">
-        <v>29863.561946620001</v>
+        <v>3300.6863896099999</v>
       </c>
       <c r="C94" s="29">
-        <f t="shared" si="2"/>
-        <v>539.15459406063144</v>
+        <f t="shared" si="3"/>
+        <v>-0.88947445735006914</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="24">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B95" s="23">
-        <v>55.287064620000002</v>
+        <v>29863.561946620001</v>
       </c>
       <c r="C95" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.99834811895033015</v>
+        <f t="shared" si="3"/>
+        <v>539.15459406063144</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="24">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B96" s="23">
-        <v>33469.1560455</v>
+        <v>55.287064620000002</v>
       </c>
       <c r="C96" s="29">
-        <f t="shared" si="2"/>
-        <v>2.616728100871637</v>
+        <f t="shared" si="3"/>
+        <v>-0.99834811895033015</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="24">
-        <v>45074</v>
+        <v>46171</v>
       </c>
       <c r="B97" s="23">
-        <v>9253.9873366299998</v>
+        <v>33469.1560455</v>
       </c>
       <c r="C97" s="29">
-        <f t="shared" si="2"/>
-        <v>425.96466507526281</v>
+        <f t="shared" si="3"/>
+        <v>2.616728100871637</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="24">
-        <v>46169</v>
+        <v>45074</v>
       </c>
       <c r="B98" s="23">
-        <v>21.673895040000001</v>
+        <v>9253.9873366299998</v>
       </c>
       <c r="C98" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.99745431244335425</v>
+        <f t="shared" si="3"/>
+        <v>425.96466507526281</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="24">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B99" s="23">
-        <v>8513.9651106900001</v>
+        <v>21.673895040000001</v>
       </c>
       <c r="C99" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.31892665326814518</v>
+        <f t="shared" si="3"/>
+        <v>-0.99745431244335425</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="24">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B100" s="23">
-        <v>12500.80501835</v>
+        <v>8513.9651106900001</v>
       </c>
       <c r="C100" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.78753584478722383</v>
+        <f t="shared" si="3"/>
+        <v>-0.31892665326814518</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="24">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="B101" s="23">
-        <v>58837.242479</v>
+        <v>12500.80501835</v>
       </c>
       <c r="C101" s="29">
-        <f t="shared" si="2"/>
-        <v>1063.8095709311931</v>
+        <f t="shared" si="3"/>
+        <v>-0.78753584478722383</v>
       </c>
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="24">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B102" s="23">
-        <v>55.256117230000001</v>
+        <v>58837.242479</v>
       </c>
       <c r="C102" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.99728557445032884</v>
+        <f t="shared" si="3"/>
+        <v>1063.8095709311931</v>
       </c>
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="24">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B103" s="23">
-        <v>20356.468143580001</v>
+        <v>55.256117230000001</v>
       </c>
       <c r="C103" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.71845195425328001</v>
+        <f t="shared" si="3"/>
+        <v>-0.99728557445032884</v>
       </c>
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="24">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B104" s="23">
-        <v>72301.933723569993</v>
+        <v>20356.468143580001</v>
       </c>
       <c r="C104" s="29">
-        <f t="shared" si="2"/>
-        <v>-2.5709262214296945E-2</v>
+        <f t="shared" si="3"/>
+        <v>-0.71845195425328001</v>
       </c>
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="24">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B105" s="23">
-        <v>74209.813271849998</v>
+        <v>72301.933723569993</v>
       </c>
       <c r="C105" s="29">
-        <f t="shared" si="2"/>
-        <v>35.243819791014161</v>
+        <f t="shared" si="3"/>
+        <v>-2.5709262214296945E-2</v>
       </c>
       <c r="D105" s="36"/>
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="24">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B106" s="23">
-        <v>2047.5163407099999</v>
+        <v>74209.813271849998</v>
       </c>
       <c r="C106" s="29">
-        <f t="shared" si="2"/>
-        <v>82.182099964255912</v>
+        <f t="shared" si="3"/>
+        <v>35.243819791014161</v>
       </c>
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="24">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B107" s="23">
-        <v>24.614867159999999</v>
+        <v>2047.5163407099999</v>
       </c>
       <c r="C107" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.96342609797465562</v>
+        <f t="shared" si="3"/>
+        <v>82.182099964255912</v>
       </c>
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="24">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B108" s="23">
-        <v>673.01725538999995</v>
+        <v>24.614867159999999</v>
       </c>
       <c r="C108" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.95811572537747924</v>
+        <f t="shared" si="3"/>
+        <v>-0.96342609797465562</v>
       </c>
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="24">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B109" s="23">
-        <v>16068.49495319</v>
+        <v>673.01725538999995</v>
       </c>
       <c r="C109" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.32064889280191988</v>
+        <f t="shared" si="3"/>
+        <v>-0.95811572537747924</v>
       </c>
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="24">
+        <v>46153</v>
+      </c>
+      <c r="B110" s="23">
+        <v>16068.49495319</v>
+      </c>
+      <c r="C110" s="29">
+        <f t="shared" si="3"/>
+        <v>-0.32064889280191988</v>
+      </c>
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="24">
         <v>46150</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B111" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C110" s="29">
-        <f t="shared" si="2"/>
+      <c r="C111" s="29">
+        <f t="shared" si="3"/>
         <v>178.18998455533497</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="22">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="22">
         <v>46149</v>
       </c>
-      <c r="B111" s="21">
+      <c r="B112" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C111" s="29">
-        <f t="shared" si="2"/>
+      <c r="C112" s="29">
+        <f t="shared" si="3"/>
         <v>-0.82294618034282907</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="17">
-        <v>46148</v>
-      </c>
-      <c r="B112" s="15">
-        <v>745.52443231999996</v>
-      </c>
-      <c r="C112" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.99115816107458954</v>
       </c>
       <c r="D112" s="35"/>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="17">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B113" s="15">
-        <v>84317.802960360001</v>
+        <v>745.52443231999996</v>
       </c>
       <c r="C113" s="29">
-        <f t="shared" si="2"/>
-        <v>0.70107388483787059</v>
+        <f t="shared" si="3"/>
+        <v>-0.99115816107458954</v>
       </c>
     </row>
     <row r="114" spans="1:3">
       <c r="A114" s="17">
+        <v>46147</v>
+      </c>
+      <c r="B114" s="15">
+        <v>84317.802960360001</v>
+      </c>
+      <c r="C114" s="29">
+        <f t="shared" si="3"/>
+        <v>0.70107388483787059</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="17">
         <v>46146</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C114" s="29">
-        <f t="shared" si="2"/>
+      <c r="C115" s="29">
+        <f t="shared" si="3"/>
         <v>-0.43255825515735763</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="18">
-        <v>46142</v>
-      </c>
-      <c r="B115" s="15">
-        <v>87352.396084139997</v>
-      </c>
-      <c r="C115" s="29">
-        <f t="shared" si="2"/>
-        <v>2.0773664296544805</v>
       </c>
     </row>
     <row r="116" spans="1:3">
       <c r="A116" s="18">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B116" s="15">
-        <v>28385.438679769999</v>
+        <v>87352.396084139997</v>
       </c>
       <c r="C116" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.59636256133262866</v>
+        <f t="shared" si="3"/>
+        <v>2.0773664296544805</v>
       </c>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="18">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B117" s="15">
-        <v>70324.097718699995</v>
+        <v>28385.438679769999</v>
       </c>
       <c r="C117" s="29">
-        <f t="shared" si="2"/>
-        <v>0.74333012643706198</v>
+        <f t="shared" si="3"/>
+        <v>-0.59636256133262866</v>
       </c>
     </row>
     <row r="118" spans="1:3">
       <c r="A118" s="18">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B118" s="15">
-        <v>40338.944788629997</v>
+        <v>70324.097718699995</v>
       </c>
       <c r="C118" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.33842006324553126</v>
+        <f t="shared" si="3"/>
+        <v>0.74333012643706198</v>
       </c>
     </row>
     <row r="119" spans="1:3">
       <c r="A119" s="18">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B119" s="15">
-        <v>60973.651931649998</v>
+        <v>40338.944788629997</v>
       </c>
       <c r="C119" s="29">
-        <f t="shared" si="2"/>
-        <v>12.106463903543759</v>
+        <f t="shared" si="3"/>
+        <v>-0.33842006324553126</v>
       </c>
     </row>
     <row r="120" spans="1:3">
       <c r="A120" s="18">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B120" s="15">
-        <v>4652.1817311200002</v>
+        <v>60973.651931649998</v>
       </c>
       <c r="C120" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.73032401489373799</v>
+        <f t="shared" si="3"/>
+        <v>12.106463903543759</v>
       </c>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="18">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B121" s="15">
-        <v>17251.00486529</v>
+        <v>4652.1817311200002</v>
       </c>
       <c r="C121" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.64046760511667533</v>
+        <f t="shared" si="3"/>
+        <v>-0.73032401489373799</v>
       </c>
     </row>
     <row r="122" spans="1:3">
       <c r="A122" s="18">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B122" s="15">
-        <v>47981.781644150004</v>
+        <v>17251.00486529</v>
       </c>
       <c r="C122" s="29">
-        <f t="shared" si="2"/>
-        <v>-6.5402088492716129E-2</v>
+        <f t="shared" si="3"/>
+        <v>-0.64046760511667533</v>
       </c>
     </row>
     <row r="123" spans="1:3">
       <c r="A123" s="18">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B123" s="15">
-        <v>51339.49161813</v>
+        <v>47981.781644150004</v>
       </c>
       <c r="C123" s="29">
-        <f t="shared" si="2"/>
-        <v>1.9819948129202027</v>
+        <f t="shared" si="3"/>
+        <v>-6.5402088492716129E-2</v>
       </c>
     </row>
     <row r="124" spans="1:3">
       <c r="A124" s="18">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B124" s="15">
-        <v>17216.492596060001</v>
+        <v>51339.49161813</v>
       </c>
       <c r="C124" s="29">
-        <f t="shared" si="2"/>
-        <v>910.40237411852581</v>
+        <f t="shared" si="3"/>
+        <v>1.9819948129202027</v>
       </c>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="18">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B125" s="15">
-        <v>18.890111640000001</v>
+        <v>17216.492596060001</v>
       </c>
       <c r="C125" s="29">
-        <f t="shared" si="2"/>
-        <v>0.19572063797541306</v>
+        <f t="shared" si="3"/>
+        <v>910.40237411852581</v>
       </c>
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="18">
-        <v>46127</v>
-      </c>
-      <c r="B126" s="38">
-        <v>15.79809785</v>
+        <v>46128</v>
+      </c>
+      <c r="B126" s="15">
+        <v>18.890111640000001</v>
       </c>
       <c r="C126" s="29">
-        <f t="shared" si="2"/>
-        <v>-2.5764893835585476E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.19572063797541306</v>
       </c>
     </row>
     <row r="127" spans="1:3">
       <c r="A127" s="18">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B127" s="38">
-        <v>16.215898760000002</v>
+        <v>15.79809785</v>
       </c>
       <c r="C127" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.99344926580920656</v>
+        <f t="shared" si="3"/>
+        <v>-2.5764893835585476E-2</v>
       </c>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="18">
-        <v>46125</v>
-      </c>
-      <c r="B128" s="15">
-        <v>2475.4322626600001</v>
+        <v>46126</v>
+      </c>
+      <c r="B128" s="38">
+        <v>16.215898760000002</v>
       </c>
       <c r="C128" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.68887087467151309</v>
+        <f t="shared" si="3"/>
+        <v>-0.99344926580920656</v>
       </c>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="18">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B129" s="15">
-        <v>7956.2858669899997</v>
+        <v>2475.4322626600001</v>
       </c>
       <c r="C129" s="29">
-        <f t="shared" si="2"/>
-        <v>190.54886991293833</v>
+        <f t="shared" si="3"/>
+        <v>-0.68887087467151309</v>
       </c>
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="18">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B130" s="15">
-        <v>41.536584740000002</v>
+        <v>7956.2858669899997</v>
       </c>
       <c r="C130" s="29">
-        <f t="shared" si="2"/>
-        <v>-0.92845434694034024</v>
+        <f t="shared" si="3"/>
+        <v>190.54886991293833</v>
       </c>
     </row>
     <row r="131" spans="1:3">
       <c r="A131" s="18">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B131" s="15">
-        <v>580.56056466999996</v>
+        <v>41.536584740000002</v>
       </c>
       <c r="C131" s="29">
-        <f>+(B131-B132)/B132</f>
-        <v>3.9632497533121036</v>
+        <f t="shared" si="3"/>
+        <v>-0.92845434694034024</v>
       </c>
     </row>
     <row r="132" spans="1:3">
       <c r="A132" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B132" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C132" s="29">
+        <f>+(B132-B133)/B133</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B133" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B134" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B135" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B136" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" s="18">
         <v>46111</v>
       </c>
-      <c r="B136" s="15">
+      <c r="B137" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8732,7 +8764,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:H125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10330,7 +10362,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E124" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E125" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11095,7 +11127,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:8">
       <c r="A113" s="24">
         <v>46296</v>
       </c>
@@ -11116,7 +11148,7 @@
         <v>-0.62</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:8">
       <c r="A114" s="24">
         <v>46297</v>
       </c>
@@ -11137,7 +11169,7 @@
         <v>-0.38</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:8">
       <c r="A115" s="24">
         <v>46300</v>
       </c>
@@ -11158,7 +11190,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:8">
       <c r="A116" s="24">
         <v>46301</v>
       </c>
@@ -11179,7 +11211,7 @@
         <v>-0.37</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:8">
       <c r="A117" s="24">
         <v>46302</v>
       </c>
@@ -11200,7 +11232,7 @@
         <v>-0.68</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:8">
       <c r="A118" s="24">
         <v>46303</v>
       </c>
@@ -11221,7 +11253,7 @@
         <v>-0.42</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:8">
       <c r="A119" s="24">
         <v>46304</v>
       </c>
@@ -11242,7 +11274,7 @@
         <v>-0.15</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:8">
       <c r="A120" s="24">
         <v>46308</v>
       </c>
@@ -11263,7 +11295,7 @@
         <v>3.15</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:8">
       <c r="A121" s="24">
         <v>46309</v>
       </c>
@@ -11284,7 +11316,7 @@
         <v>-0.66</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:8">
       <c r="A122" s="24">
         <v>46310</v>
       </c>
@@ -11305,7 +11337,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:8">
       <c r="A123" s="24">
         <v>46311</v>
       </c>
@@ -11326,7 +11358,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:8">
       <c r="A124" s="24">
         <v>46314</v>
       </c>
@@ -11346,6 +11378,29 @@
       <c r="F124" s="31">
         <v>-0.71</v>
       </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="24">
+        <v>46315</v>
+      </c>
+      <c r="B125" s="25">
+        <v>13080</v>
+      </c>
+      <c r="C125" s="23">
+        <v>3</v>
+      </c>
+      <c r="D125" s="25">
+        <v>13083</v>
+      </c>
+      <c r="E125" s="30">
+        <f t="shared" si="4"/>
+        <v>-1.5056839569374389E-2</v>
+      </c>
+      <c r="F125" s="16">
+        <v>-1.51</v>
+      </c>
+      <c r="G125" s="19"/>
+      <c r="H125" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2996,7 +2996,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5791,7 +5791,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5820,14 +5820,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B2" s="23">
-        <v>50526.509366320002</v>
+        <v>12243.93331552</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C8" si="0">+(B2-B3)/B3</f>
-        <v>-0.35247381438929659</v>
+        <f t="shared" ref="C2:C9" si="0">+(B2-B3)/B3</f>
+        <v>-0.75767308153526292</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5838,14 +5838,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B3" s="23">
-        <v>78030.063477150004</v>
+        <v>50526.509366320002</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>-0.51127008544838759</v>
+        <v>-0.35247381438929659</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5856,14 +5856,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B4" s="23">
-        <v>159658.86505789001</v>
+        <v>78030.063477150004</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>-0.18383477994159175</v>
+        <v>-0.51127008544838759</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5873,15 +5873,15 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
-      <c r="A5" s="23" t="s">
-        <v>40</v>
+      <c r="A5" s="24">
+        <v>46314</v>
       </c>
       <c r="B5" s="23">
-        <v>195620.76542108</v>
+        <v>159658.86505789001</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>0.39348231037382758</v>
+        <v>-0.18383477994159175</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5891,15 +5891,15 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="24">
-        <v>46310</v>
+      <c r="A6" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B6" s="23">
-        <v>140382.66863150999</v>
+        <v>195620.76542108</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>11.24948691206232</v>
+        <v>0.39348231037382758</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5910,14 +5910,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B7" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>-0.88352658705352882</v>
+        <v>11.24948691206232</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5928,14 +5928,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B8" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>-0.6788555314993624</v>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5946,14 +5946,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B9" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C9" s="29">
-        <f t="shared" ref="C9:C19" si="1">+(B9-B10)/B10</f>
-        <v>9.336258026433894E-2</v>
+        <f t="shared" si="0"/>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5964,1531 +5964,1543 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B10" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C10" s="29">
+        <f t="shared" ref="C10:C20" si="1">+(B10-B11)/B11</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="39">
+        <v>70928.40866225904</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24">
         <v>46303</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B11" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C11" s="29">
         <f t="shared" si="1"/>
         <v>-3.649289843956157E-2</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="39">
-        <v>70928.40866225904</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="24">
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46302</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="1"/>
         <v>3.9357330833461011E-3</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46301</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="1"/>
         <v>-2.9955821881414251E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46300</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>-0.13794268733409284</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46297</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>0.2638202658078479</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46296</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>0.35910087116479922</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46295</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>8.8268407504102413</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46294</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>-0.85681185394119452</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46293</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>-0.49898704513189668</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46290</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>0.55858664283872839</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B20" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C20" s="29">
-        <f t="shared" ref="C20:C89" si="2">+(B20-B21)/B21</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
       <c r="E20" s="7"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B21" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C21" s="29">
+        <f t="shared" ref="C21:C90" si="2">+(B21-B22)/B22</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46288</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="2"/>
         <v>0.18793186198768058</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46287</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="2"/>
         <v>6.7871692861553368E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46286</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="2"/>
         <v>0.25618058698994745</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46283</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="2"/>
         <v>0.32349555871151542</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46282</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="2"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46281</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="2"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46280</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="2"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46276</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="2"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46275</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="2"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46274</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="2"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46273</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="2"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46272</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="2"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46269</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="2"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46268</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="2"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46267</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="2"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46266</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="2"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46265</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="2"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46262</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="2"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46261</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="2"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46260</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="2"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46259</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="2"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46256</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="2"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46255</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="2"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46254</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="2"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46253</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="2"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46252</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="2"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46251</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="2"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46248</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="2"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46247</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="2"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46246</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="2"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46245</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="2"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46244</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="2"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46241</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="2"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46240</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="2"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46239</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="2"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46238</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="2"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46237</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="2"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46234</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="2"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46233</v>
       </c>
-      <c r="B59">
+      <c r="B60">
         <v>466.33578662999997</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="2"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46232</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="2"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46231</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="2"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46108</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="2"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46226</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="2"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46225</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="2"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46224</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="2"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46220</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="2"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46219</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="2"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46218</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="2"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46217</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="2"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46216</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="2"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46213</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="2"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46212</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="2"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46211</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="2"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46210</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="2"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46209</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="2"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46206</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="2"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46205</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="2"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46204</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="2"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46203</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="2"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46198</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="2"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46196</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="2"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46195</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="2"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46192</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46191</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46190</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46189</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46188</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>8.42</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46185</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46184</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B90" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C90" s="29">
-        <f t="shared" ref="C90:C131" si="3">+(B90-B91)/B91</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="91" spans="1:3">
       <c r="A91" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B91" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C91" s="29">
+        <f t="shared" ref="C91:C132" si="3">+(B91-B92)/B92</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46182</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="3"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46178</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="3"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46177</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="3"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46176</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="3"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46175</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="3"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46174</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="3"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46171</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="3"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>45074</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="3"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46169</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="3"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46168</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="3"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46167</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="3"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46164</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="3"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46163</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="3"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46162</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="3"/>
         <v>-0.71845195425328001</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46161</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="3"/>
         <v>-2.5709262214296945E-2</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="24">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="24">
         <v>46157</v>
       </c>
-      <c r="B106" s="23">
+      <c r="B107" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="3"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="24">
+    <row r="108" spans="1:4">
+      <c r="A108" s="24">
         <v>46156</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B108" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="3"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="24">
+    <row r="109" spans="1:4">
+      <c r="A109" s="24">
         <v>46155</v>
       </c>
-      <c r="B108" s="23">
+      <c r="B109" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="3"/>
         <v>-0.96342609797465562</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="24">
+    <row r="110" spans="1:4">
+      <c r="A110" s="24">
         <v>46154</v>
       </c>
-      <c r="B109" s="23">
+      <c r="B110" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="3"/>
         <v>-0.95811572537747924</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="24">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="24">
         <v>46153</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B111" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="3"/>
         <v>-0.32064889280191988</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="24">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="24">
         <v>46150</v>
       </c>
-      <c r="B111" s="23">
+      <c r="B112" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="3"/>
         <v>178.18998455533497</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="22">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="22">
         <v>46149</v>
       </c>
-      <c r="B112" s="21">
+      <c r="B113" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="3"/>
         <v>-0.82294618034282907</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="17">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="17">
         <v>46148</v>
       </c>
-      <c r="B113" s="15">
+      <c r="B114" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="3"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="17">
+    <row r="115" spans="1:3">
+      <c r="A115" s="17">
         <v>46147</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="3"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="17">
+    <row r="116" spans="1:3">
+      <c r="A116" s="17">
         <v>46146</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="3"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="18">
+    <row r="117" spans="1:3">
+      <c r="A117" s="18">
         <v>46142</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="3"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46141</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="3"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46140</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="3"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46139</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="3"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46136</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="3"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46135</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="3"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46134</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="3"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46133</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="3"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46132</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B125" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="3"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46129</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B126" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C126" s="29">
         <f t="shared" si="3"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="18">
+    <row r="127" spans="1:3">
+      <c r="A127" s="18">
         <v>46128</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B127" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C126" s="29">
+      <c r="C127" s="29">
         <f t="shared" si="3"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="18">
+    <row r="128" spans="1:3">
+      <c r="A128" s="18">
         <v>46127</v>
       </c>
-      <c r="B127" s="38">
+      <c r="B128" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C127" s="29">
+      <c r="C128" s="29">
         <f t="shared" si="3"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="18">
+    <row r="129" spans="1:3">
+      <c r="A129" s="18">
         <v>46126</v>
       </c>
-      <c r="B128" s="38">
+      <c r="B129" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C128" s="29">
+      <c r="C129" s="29">
         <f t="shared" si="3"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="18">
+    <row r="130" spans="1:3">
+      <c r="A130" s="18">
         <v>46125</v>
       </c>
-      <c r="B129" s="15">
+      <c r="B130" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C129" s="29">
+      <c r="C130" s="29">
         <f t="shared" si="3"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="18">
+    <row r="131" spans="1:3">
+      <c r="A131" s="18">
         <v>46122</v>
       </c>
-      <c r="B130" s="15">
+      <c r="B131" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C130" s="29">
+      <c r="C131" s="29">
         <f t="shared" si="3"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="18">
+    <row r="132" spans="1:3">
+      <c r="A132" s="18">
         <v>46121</v>
       </c>
-      <c r="B131" s="15">
+      <c r="B132" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C131" s="29">
+      <c r="C132" s="29">
         <f t="shared" si="3"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B132" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C132" s="29">
-        <f>+(B132-B133)/B133</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="133" spans="1:3">
       <c r="A133" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B133" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C133" s="29">
+        <f>+(B133-B134)/B134</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="134" spans="1:3">
       <c r="A134" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B134" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B135" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B136" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B137" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3">
+      <c r="A138" s="18">
         <v>46111</v>
       </c>
-      <c r="B137" s="15">
+      <c r="B138" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8764,7 +8776,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10362,7 +10374,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E125" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E126" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11401,6 +11413,27 @@
       </c>
       <c r="G125" s="19"/>
       <c r="H125" s="16"/>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="24">
+        <v>46316</v>
+      </c>
+      <c r="B126" s="25">
+        <v>13088</v>
+      </c>
+      <c r="C126" s="23">
+        <v>3</v>
+      </c>
+      <c r="D126" s="25">
+        <v>13091</v>
+      </c>
+      <c r="E126" s="30">
+        <f t="shared" si="4"/>
+        <v>6.114805472750898E-4</v>
+      </c>
+      <c r="F126" s="31">
+        <v>0.06</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10140" tabRatio="819"/>
+    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10140" tabRatio="819" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -3004,7 +3004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H143"/>
+  <dimension ref="A1:H144"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5783,6 +5783,26 @@
         <v>50</v>
       </c>
     </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="20">
+        <v>46318</v>
+      </c>
+      <c r="B144" s="16">
+        <v>0</v>
+      </c>
+      <c r="C144" s="19"/>
+      <c r="D144" s="16">
+        <v>0</v>
+      </c>
+      <c r="E144" s="19"/>
+      <c r="F144" s="16">
+        <v>0</v>
+      </c>
+      <c r="G144" s="19"/>
+      <c r="H144" s="16">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5791,7 +5811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5820,14 +5840,14 @@
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A2" s="24">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B2" s="23">
-        <v>12243.93331552</v>
+        <v>189892.13945995999</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C9" si="0">+(B2-B3)/B3</f>
-        <v>-0.75767308153526292</v>
+        <f t="shared" ref="C2:C10" si="0">+(B2-B3)/B3</f>
+        <v>14.509079849304559</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5838,14 +5858,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B3" s="23">
-        <v>50526.509366320002</v>
+        <v>12243.93331552</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>-0.35247381438929659</v>
+        <v>-0.75767308153526292</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5856,14 +5876,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B4" s="23">
-        <v>78030.063477150004</v>
+        <v>50526.509366320002</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>-0.51127008544838759</v>
+        <v>-0.35247381438929659</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5874,14 +5894,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B5" s="23">
-        <v>159658.86505789001</v>
+        <v>78030.063477150004</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>-0.18383477994159175</v>
+        <v>-0.51127008544838759</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5891,15 +5911,15 @@
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="23" t="s">
-        <v>40</v>
+      <c r="A6" s="24">
+        <v>46314</v>
       </c>
       <c r="B6" s="23">
-        <v>195620.76542108</v>
+        <v>159658.86505789001</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>0.39348231037382758</v>
+        <v>-0.18383477994159175</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5909,15 +5929,15 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="24">
-        <v>46310</v>
+      <c r="A7" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B7" s="23">
-        <v>140382.66863150999</v>
+        <v>195620.76542108</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>11.24948691206232</v>
+        <v>0.39348231037382758</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5928,14 +5948,14 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B8" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>-0.88352658705352882</v>
+        <v>11.24948691206232</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5946,14 +5966,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B9" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C9" s="29">
         <f t="shared" si="0"/>
-        <v>-0.6788555314993624</v>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5964,14 +5984,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B10" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C10" s="29">
-        <f t="shared" ref="C10:C20" si="1">+(B10-B11)/B11</f>
-        <v>9.336258026433894E-2</v>
+        <f t="shared" si="0"/>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>39</v>
@@ -5982,1525 +6002,1537 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B11" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C11" s="29">
+        <f t="shared" ref="C11:C21" si="1">+(B11-B12)/B12</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24">
         <v>46303</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B12" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C12" s="29">
         <f t="shared" si="1"/>
         <v>-3.649289843956157E-2</v>
       </c>
-      <c r="E11" s="34"/>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="24">
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46302</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="1"/>
         <v>3.9357330833461011E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46301</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>-2.9955821881414251E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46300</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>-0.13794268733409284</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46297</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>0.2638202658078479</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46296</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>0.35910087116479922</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46295</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>8.8268407504102413</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46294</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>-0.85681185394119452</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46293</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>-0.49898704513189668</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46290</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>0.55858664283872839</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B21" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C21" s="29">
-        <f t="shared" ref="C21:C90" si="2">+(B21-B22)/B22</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
       <c r="E21" s="7"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B22" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C22" s="29">
+        <f t="shared" ref="C22:C91" si="2">+(B22-B23)/B23</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46288</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="2"/>
         <v>0.18793186198768058</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46287</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="2"/>
         <v>6.7871692861553368E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46286</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="2"/>
         <v>0.25618058698994745</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46283</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="2"/>
         <v>0.32349555871151542</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46282</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="2"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46281</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="2"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46280</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="2"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46276</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="2"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46275</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="2"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46274</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="2"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46273</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="2"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46272</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="2"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46269</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="2"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46268</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="2"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46267</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="2"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46266</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="2"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46265</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="2"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46262</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="2"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46261</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="2"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46260</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="2"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46259</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="2"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46256</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="2"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46255</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="2"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46254</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="2"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46253</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="2"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46252</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="2"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46251</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="2"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46248</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="2"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46247</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="2"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46246</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="2"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46245</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="2"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46244</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="2"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46241</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="2"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46240</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="2"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46239</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="2"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46238</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="2"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46237</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="2"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46234</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="2"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46233</v>
       </c>
-      <c r="B60">
+      <c r="B61">
         <v>466.33578662999997</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="2"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46232</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="2"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46231</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="2"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46108</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="2"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46226</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="2"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46225</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="2"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46224</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="2"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46220</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="2"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46219</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="2"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46218</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="2"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46217</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="2"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46216</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="2"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46213</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="2"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46212</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="2"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46211</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="2"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46210</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="2"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46209</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="2"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46206</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="2"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46205</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="2"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46204</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="2"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46203</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="2"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46198</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="2"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46196</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="2"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46195</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46192</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46191</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46190</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46189</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46188</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>8.42</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46185</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46184</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B91" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C91" s="29">
-        <f t="shared" ref="C91:C132" si="3">+(B91-B92)/B92</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="92" spans="1:3">
       <c r="A92" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B92" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C92" s="29">
+        <f t="shared" ref="C92:C133" si="3">+(B92-B93)/B93</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46182</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="3"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46178</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="3"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46177</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="3"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46176</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="3"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46175</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="3"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46174</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="3"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46171</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="3"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>45074</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="3"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46169</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="3"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46168</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="3"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46167</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="3"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46164</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="3"/>
         <v>1063.8095709311931</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46163</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="3"/>
         <v>-0.99728557445032884</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46162</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="3"/>
         <v>-0.71845195425328001</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="24">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="24">
         <v>46161</v>
       </c>
-      <c r="B106" s="23">
+      <c r="B107" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="3"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="24">
+    <row r="108" spans="1:4">
+      <c r="A108" s="24">
         <v>46157</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B108" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="3"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="24">
+    <row r="109" spans="1:4">
+      <c r="A109" s="24">
         <v>46156</v>
       </c>
-      <c r="B108" s="23">
+      <c r="B109" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="3"/>
         <v>82.182099964255912</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="24">
+    <row r="110" spans="1:4">
+      <c r="A110" s="24">
         <v>46155</v>
       </c>
-      <c r="B109" s="23">
+      <c r="B110" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="3"/>
         <v>-0.96342609797465562</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="24">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="24">
         <v>46154</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B111" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="3"/>
         <v>-0.95811572537747924</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="24">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="24">
         <v>46153</v>
       </c>
-      <c r="B111" s="23">
+      <c r="B112" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="3"/>
         <v>-0.32064889280191988</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="24">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="24">
         <v>46150</v>
       </c>
-      <c r="B112" s="23">
+      <c r="B113" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="3"/>
         <v>178.18998455533497</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="22">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="22">
         <v>46149</v>
       </c>
-      <c r="B113" s="21">
+      <c r="B114" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="3"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="17">
+    <row r="115" spans="1:3">
+      <c r="A115" s="17">
         <v>46148</v>
       </c>
-      <c r="B114" s="15">
+      <c r="B115" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="3"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="17">
+    <row r="116" spans="1:3">
+      <c r="A116" s="17">
         <v>46147</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="3"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="17">
+    <row r="117" spans="1:3">
+      <c r="A117" s="17">
         <v>46146</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="3"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="18">
+    <row r="118" spans="1:3">
+      <c r="A118" s="18">
         <v>46142</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="3"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46141</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="3"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46140</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="3"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46139</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="3"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46136</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="3"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46135</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="3"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46134</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="3"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46133</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B125" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="3"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46132</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B126" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C126" s="29">
         <f t="shared" si="3"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="18">
+    <row r="127" spans="1:3">
+      <c r="A127" s="18">
         <v>46129</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B127" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C126" s="29">
+      <c r="C127" s="29">
         <f t="shared" si="3"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="18">
+    <row r="128" spans="1:3">
+      <c r="A128" s="18">
         <v>46128</v>
       </c>
-      <c r="B127" s="15">
+      <c r="B128" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C127" s="29">
+      <c r="C128" s="29">
         <f t="shared" si="3"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="18">
+    <row r="129" spans="1:3">
+      <c r="A129" s="18">
         <v>46127</v>
       </c>
-      <c r="B128" s="38">
+      <c r="B129" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C128" s="29">
+      <c r="C129" s="29">
         <f t="shared" si="3"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="18">
+    <row r="130" spans="1:3">
+      <c r="A130" s="18">
         <v>46126</v>
       </c>
-      <c r="B129" s="38">
+      <c r="B130" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C129" s="29">
+      <c r="C130" s="29">
         <f t="shared" si="3"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="18">
+    <row r="131" spans="1:3">
+      <c r="A131" s="18">
         <v>46125</v>
       </c>
-      <c r="B130" s="15">
+      <c r="B131" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C130" s="29">
+      <c r="C131" s="29">
         <f t="shared" si="3"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="18">
+    <row r="132" spans="1:3">
+      <c r="A132" s="18">
         <v>46122</v>
       </c>
-      <c r="B131" s="15">
+      <c r="B132" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C131" s="29">
+      <c r="C132" s="29">
         <f t="shared" si="3"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="18">
+    <row r="133" spans="1:3">
+      <c r="A133" s="18">
         <v>46121</v>
       </c>
-      <c r="B132" s="15">
+      <c r="B133" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C132" s="29">
+      <c r="C133" s="29">
         <f t="shared" si="3"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B133" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C133" s="29">
-        <f>+(B133-B134)/B134</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="134" spans="1:3">
       <c r="A134" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B134" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C134" s="29">
+        <f>+(B134-B135)/B135</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="135" spans="1:3">
       <c r="A135" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B135" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B136" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B137" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B138" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3">
+      <c r="A139" s="18">
         <v>46111</v>
       </c>
-      <c r="B138" s="15">
+      <c r="B139" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -7622,7 +7654,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -7827,7 +7859,7 @@
         <v>1452167458.20135</v>
       </c>
       <c r="C18" s="4">
-        <f t="shared" ref="C18:C29" si="0">+((B18-B17)/B17)*100</f>
+        <f t="shared" ref="C18:C32" si="0">+((B18-B17)/B17)*100</f>
         <v>0.77731466473397282</v>
       </c>
     </row>
@@ -7963,6 +7995,42 @@
       <c r="C29" s="4">
         <f t="shared" si="0"/>
         <v>6.1047366051644163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" thickBot="1">
+      <c r="A30" s="24">
+        <v>46297</v>
+      </c>
+      <c r="B30" s="16">
+        <v>1989759558.6563499</v>
+      </c>
+      <c r="C30" s="4">
+        <f t="shared" si="0"/>
+        <v>8.0826769301053076</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" thickBot="1">
+      <c r="A31" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B31" s="16">
+        <v>1923670752.90625</v>
+      </c>
+      <c r="C31" s="4">
+        <f t="shared" si="0"/>
+        <v>-3.3214468282151901</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" thickBot="1">
+      <c r="A32" s="24">
+        <v>46311</v>
+      </c>
+      <c r="B32" s="16">
+        <v>1972453207.41008</v>
+      </c>
+      <c r="C32" s="4">
+        <f t="shared" si="0"/>
+        <v>2.5359045683950971</v>
       </c>
     </row>
   </sheetData>
@@ -7972,7 +8040,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -8769,6 +8837,32 @@
         <v>-0.48737705449418689</v>
       </c>
     </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="24">
+        <v>46311</v>
+      </c>
+      <c r="B31" s="16">
+        <v>84594237.019020006</v>
+      </c>
+      <c r="C31" s="16">
+        <v>2857222795.5366302</v>
+      </c>
+      <c r="D31" s="16">
+        <v>261796468.60564005</v>
+      </c>
+      <c r="E31" s="16">
+        <v>3203613501.1612902</v>
+      </c>
+      <c r="F31" s="16">
+        <v>57789336.13893</v>
+      </c>
+      <c r="G31" s="16">
+        <v>3261402837.30022</v>
+      </c>
+      <c r="H31" s="26">
+        <v>5.231655616231401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8776,7 +8870,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10374,7 +10468,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E126" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E127" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11433,6 +11527,27 @@
       </c>
       <c r="F126" s="31">
         <v>0.06</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="24">
+        <v>46317</v>
+      </c>
+      <c r="B127" s="25">
+        <v>12910</v>
+      </c>
+      <c r="C127" s="23">
+        <v>3</v>
+      </c>
+      <c r="D127" s="25">
+        <v>12913</v>
+      </c>
+      <c r="E127" s="30">
+        <f t="shared" si="4"/>
+        <v>-1.3597127797723627E-2</v>
+      </c>
+      <c r="F127" s="31">
+        <v>-1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10140" tabRatio="819" activeTab="5"/>
+    <workbookView xWindow="-15" yWindow="-15" windowWidth="10800" windowHeight="10140" tabRatio="819"/>
   </bookViews>
   <sheets>
     <sheet name="Tasa Overnight Diaria" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>DÍA</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>16/10/206</t>
+  </si>
+  <si>
+    <t>27/10/1026</t>
   </si>
 </sst>
 </file>
@@ -2996,7 +2999,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3004,7 +3007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H144"/>
+  <dimension ref="A1:H145"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5803,6 +5806,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="20">
+        <v>46322</v>
+      </c>
+      <c r="B145" s="16">
+        <v>0</v>
+      </c>
+      <c r="C145" s="19"/>
+      <c r="D145" s="16">
+        <v>0</v>
+      </c>
+      <c r="E145" s="19"/>
+      <c r="F145" s="16">
+        <v>0</v>
+      </c>
+      <c r="G145" s="19"/>
+      <c r="H145" s="16">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5811,7 +5834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5839,15 +5862,15 @@
       </c>
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="24">
-        <v>46318</v>
+      <c r="A2" s="23" t="s">
+        <v>41</v>
       </c>
       <c r="B2" s="23">
-        <v>189892.13945995999</v>
+        <v>87037.177886279998</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C10" si="0">+(B2-B3)/B3</f>
-        <v>14.509079849304559</v>
+        <f t="shared" ref="C2:C11" si="0">+(B2-B3)/B3</f>
+        <v>-0.54164939036545867</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5858,14 +5881,14 @@
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="24">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B3" s="23">
-        <v>12243.93331552</v>
+        <v>189892.13945995999</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>-0.75767308153526292</v>
+        <v>14.509079849304559</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5876,14 +5899,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B4" s="23">
-        <v>50526.509366320002</v>
+        <v>12243.93331552</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>-0.35247381438929659</v>
+        <v>-0.75767308153526292</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5894,14 +5917,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B5" s="23">
-        <v>78030.063477150004</v>
+        <v>50526.509366320002</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>-0.51127008544838759</v>
+        <v>-0.35247381438929659</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5912,14 +5935,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B6" s="23">
-        <v>159658.86505789001</v>
+        <v>78030.063477150004</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>-0.18383477994159175</v>
+        <v>-0.51127008544838759</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5929,15 +5952,15 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="23" t="s">
-        <v>40</v>
+      <c r="A7" s="24">
+        <v>46314</v>
       </c>
       <c r="B7" s="23">
-        <v>195620.76542108</v>
+        <v>159658.86505789001</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>0.39348231037382758</v>
+        <v>-0.18383477994159175</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5947,15 +5970,15 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="24">
-        <v>46310</v>
+      <c r="A8" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B8" s="23">
-        <v>140382.66863150999</v>
+        <v>195620.76542108</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>11.24948691206232</v>
+        <v>0.39348231037382758</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5966,14 +5989,14 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B9" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C9" s="29">
         <f t="shared" si="0"/>
-        <v>-0.88352658705352882</v>
+        <v>11.24948691206232</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -5984,14 +6007,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B10" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C10" s="29">
         <f t="shared" si="0"/>
-        <v>-0.6788555314993624</v>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>39</v>
@@ -6002,1537 +6025,1549 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B11" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C11" s="29">
-        <f t="shared" ref="C11:C21" si="1">+(B11-B12)/B12</f>
-        <v>9.336258026433894E-2</v>
+        <f t="shared" si="0"/>
+        <v>-0.6788555314993624</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B12" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C12" s="29">
+        <f t="shared" ref="C12:C22" si="1">+(B12-B13)/B13</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24">
         <v>46303</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B13" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C13" s="29">
         <f t="shared" si="1"/>
         <v>-3.649289843956157E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="24">
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46302</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>3.9357330833461011E-3</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46301</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>-2.9955821881414251E-2</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46300</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>-0.13794268733409284</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46297</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>0.2638202658078479</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46296</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>0.35910087116479922</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46295</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>8.8268407504102413</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46294</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>-0.85681185394119452</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46293</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>-0.49898704513189668</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46290</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>0.55858664283872839</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B22" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C22" s="29">
-        <f t="shared" ref="C22:C91" si="2">+(B22-B23)/B23</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B23" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C23" s="29">
+        <f t="shared" ref="C23:C92" si="2">+(B23-B24)/B24</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="24">
         <v>46288</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B24" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C23" s="29">
+      <c r="C24" s="29">
         <f t="shared" si="2"/>
         <v>0.18793186198768058</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="24">
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46287</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="2"/>
         <v>6.7871692861553368E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46286</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="2"/>
         <v>0.25618058698994745</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46283</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="2"/>
         <v>0.32349555871151542</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46282</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="2"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46281</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="2"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46280</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="2"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46276</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="2"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46275</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="2"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46274</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="2"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46273</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="2"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46272</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="2"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46269</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="2"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46268</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="2"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46267</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="2"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46266</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="2"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46265</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="2"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46262</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="2"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46261</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="2"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46260</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="2"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46259</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="2"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46256</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="2"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46255</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="2"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46254</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="2"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46253</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="2"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46252</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="2"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46251</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="2"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46248</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="2"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46247</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="2"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46246</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="2"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46245</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="2"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46244</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="2"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46241</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="2"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46240</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="2"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46239</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="2"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46238</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="2"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46237</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="2"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46234</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="2"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46233</v>
       </c>
-      <c r="B61">
+      <c r="B62">
         <v>466.33578662999997</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="2"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46232</v>
       </c>
-      <c r="B62" s="23">
+      <c r="B63" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="2"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46231</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="2"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46108</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="2"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46226</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="2"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46225</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="2"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46224</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="2"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46220</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="2"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46219</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="2"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46218</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="2"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46217</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="2"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46216</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="2"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46213</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="2"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46212</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="2"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46211</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="2"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46210</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="2"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46209</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="2"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46206</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="2"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46205</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="2"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46204</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="2"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46203</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="2"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46198</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="2"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46196</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46195</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46192</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46191</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46190</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46189</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46188</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>8.42</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46185</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46184</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B92" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C92" s="29">
-        <f t="shared" ref="C92:C133" si="3">+(B92-B93)/B93</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="93" spans="1:3">
       <c r="A93" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B93" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C93" s="29">
+        <f t="shared" ref="C93:C134" si="3">+(B93-B94)/B94</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="24">
         <v>46182</v>
       </c>
-      <c r="B93" s="23">
+      <c r="B94" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C93" s="29">
+      <c r="C94" s="29">
         <f t="shared" si="3"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="24">
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46178</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="3"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46177</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="3"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46176</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="3"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46175</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="3"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46174</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="3"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46171</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="3"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>45074</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="3"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>46169</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="3"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46168</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="3"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46167</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="3"/>
         <v>-0.78753584478722383</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46164</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="3"/>
         <v>1063.8095709311931</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46163</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="3"/>
         <v>-0.99728557445032884</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="24">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="24">
         <v>46162</v>
       </c>
-      <c r="B106" s="23">
+      <c r="B107" s="23">
         <v>20356.468143580001</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="3"/>
         <v>-0.71845195425328001</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="24">
+    <row r="108" spans="1:4">
+      <c r="A108" s="24">
         <v>46161</v>
       </c>
-      <c r="B107" s="23">
+      <c r="B108" s="23">
         <v>72301.933723569993</v>
       </c>
-      <c r="C107" s="29">
+      <c r="C108" s="29">
         <f t="shared" si="3"/>
         <v>-2.5709262214296945E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="24">
+    <row r="109" spans="1:4">
+      <c r="A109" s="24">
         <v>46157</v>
       </c>
-      <c r="B108" s="23">
+      <c r="B109" s="23">
         <v>74209.813271849998</v>
       </c>
-      <c r="C108" s="29">
+      <c r="C109" s="29">
         <f t="shared" si="3"/>
         <v>35.243819791014161</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="24">
+    <row r="110" spans="1:4">
+      <c r="A110" s="24">
         <v>46156</v>
       </c>
-      <c r="B109" s="23">
+      <c r="B110" s="23">
         <v>2047.5163407099999</v>
       </c>
-      <c r="C109" s="29">
+      <c r="C110" s="29">
         <f t="shared" si="3"/>
         <v>82.182099964255912</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="24">
+      <c r="D110" s="35"/>
+    </row>
+    <row r="111" spans="1:4">
+      <c r="A111" s="24">
         <v>46155</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B111" s="23">
         <v>24.614867159999999</v>
       </c>
-      <c r="C110" s="29">
+      <c r="C111" s="29">
         <f t="shared" si="3"/>
         <v>-0.96342609797465562</v>
       </c>
-      <c r="D110" s="35"/>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="24">
+    </row>
+    <row r="112" spans="1:4">
+      <c r="A112" s="24">
         <v>46154</v>
       </c>
-      <c r="B111" s="23">
+      <c r="B112" s="23">
         <v>673.01725538999995</v>
       </c>
-      <c r="C111" s="29">
+      <c r="C112" s="29">
         <f t="shared" si="3"/>
         <v>-0.95811572537747924</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="24">
+      <c r="D112" s="35"/>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="24">
         <v>46153</v>
       </c>
-      <c r="B112" s="23">
+      <c r="B113" s="23">
         <v>16068.49495319</v>
       </c>
-      <c r="C112" s="29">
+      <c r="C113" s="29">
         <f t="shared" si="3"/>
         <v>-0.32064889280191988</v>
       </c>
-      <c r="D112" s="35"/>
-    </row>
-    <row r="113" spans="1:3">
-      <c r="A113" s="24">
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="24">
         <v>46150</v>
       </c>
-      <c r="B113" s="23">
+      <c r="B114" s="23">
         <v>23652.710333340001</v>
       </c>
-      <c r="C113" s="29">
+      <c r="C114" s="29">
         <f t="shared" si="3"/>
         <v>178.18998455533497</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
-      <c r="A114" s="22">
+    <row r="115" spans="1:3">
+      <c r="A115" s="22">
         <v>46149</v>
       </c>
-      <c r="B114" s="21">
+      <c r="B115" s="21">
         <v>131.99794839</v>
       </c>
-      <c r="C114" s="29">
+      <c r="C115" s="29">
         <f t="shared" si="3"/>
         <v>-0.82294618034282907</v>
       </c>
     </row>
-    <row r="115" spans="1:3">
-      <c r="A115" s="17">
+    <row r="116" spans="1:3">
+      <c r="A116" s="17">
         <v>46148</v>
       </c>
-      <c r="B115" s="15">
+      <c r="B116" s="15">
         <v>745.52443231999996</v>
       </c>
-      <c r="C115" s="29">
+      <c r="C116" s="29">
         <f t="shared" si="3"/>
         <v>-0.99115816107458954</v>
       </c>
     </row>
-    <row r="116" spans="1:3">
-      <c r="A116" s="17">
+    <row r="117" spans="1:3">
+      <c r="A117" s="17">
         <v>46147</v>
       </c>
-      <c r="B116" s="15">
+      <c r="B117" s="15">
         <v>84317.802960360001</v>
       </c>
-      <c r="C116" s="29">
+      <c r="C117" s="29">
         <f t="shared" si="3"/>
         <v>0.70107388483787059</v>
       </c>
     </row>
-    <row r="117" spans="1:3">
-      <c r="A117" s="17">
+    <row r="118" spans="1:3">
+      <c r="A118" s="17">
         <v>46146</v>
       </c>
-      <c r="B117" s="15">
+      <c r="B118" s="15">
         <v>49567.396050169998</v>
       </c>
-      <c r="C117" s="29">
+      <c r="C118" s="29">
         <f t="shared" si="3"/>
         <v>-0.43255825515735763</v>
       </c>
     </row>
-    <row r="118" spans="1:3">
-      <c r="A118" s="18">
+    <row r="119" spans="1:3">
+      <c r="A119" s="18">
         <v>46142</v>
       </c>
-      <c r="B118" s="15">
+      <c r="B119" s="15">
         <v>87352.396084139997</v>
       </c>
-      <c r="C118" s="29">
+      <c r="C119" s="29">
         <f t="shared" si="3"/>
         <v>2.0773664296544805</v>
       </c>
     </row>
-    <row r="119" spans="1:3">
-      <c r="A119" s="18">
+    <row r="120" spans="1:3">
+      <c r="A120" s="18">
         <v>46141</v>
       </c>
-      <c r="B119" s="15">
+      <c r="B120" s="15">
         <v>28385.438679769999</v>
       </c>
-      <c r="C119" s="29">
+      <c r="C120" s="29">
         <f t="shared" si="3"/>
         <v>-0.59636256133262866</v>
       </c>
     </row>
-    <row r="120" spans="1:3">
-      <c r="A120" s="18">
+    <row r="121" spans="1:3">
+      <c r="A121" s="18">
         <v>46140</v>
       </c>
-      <c r="B120" s="15">
+      <c r="B121" s="15">
         <v>70324.097718699995</v>
       </c>
-      <c r="C120" s="29">
+      <c r="C121" s="29">
         <f t="shared" si="3"/>
         <v>0.74333012643706198</v>
       </c>
     </row>
-    <row r="121" spans="1:3">
-      <c r="A121" s="18">
+    <row r="122" spans="1:3">
+      <c r="A122" s="18">
         <v>46139</v>
       </c>
-      <c r="B121" s="15">
+      <c r="B122" s="15">
         <v>40338.944788629997</v>
       </c>
-      <c r="C121" s="29">
+      <c r="C122" s="29">
         <f t="shared" si="3"/>
         <v>-0.33842006324553126</v>
       </c>
     </row>
-    <row r="122" spans="1:3">
-      <c r="A122" s="18">
+    <row r="123" spans="1:3">
+      <c r="A123" s="18">
         <v>46136</v>
       </c>
-      <c r="B122" s="15">
+      <c r="B123" s="15">
         <v>60973.651931649998</v>
       </c>
-      <c r="C122" s="29">
+      <c r="C123" s="29">
         <f t="shared" si="3"/>
         <v>12.106463903543759</v>
       </c>
     </row>
-    <row r="123" spans="1:3">
-      <c r="A123" s="18">
+    <row r="124" spans="1:3">
+      <c r="A124" s="18">
         <v>46135</v>
       </c>
-      <c r="B123" s="15">
+      <c r="B124" s="15">
         <v>4652.1817311200002</v>
       </c>
-      <c r="C123" s="29">
+      <c r="C124" s="29">
         <f t="shared" si="3"/>
         <v>-0.73032401489373799</v>
       </c>
     </row>
-    <row r="124" spans="1:3">
-      <c r="A124" s="18">
+    <row r="125" spans="1:3">
+      <c r="A125" s="18">
         <v>46134</v>
       </c>
-      <c r="B124" s="15">
+      <c r="B125" s="15">
         <v>17251.00486529</v>
       </c>
-      <c r="C124" s="29">
+      <c r="C125" s="29">
         <f t="shared" si="3"/>
         <v>-0.64046760511667533</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
-      <c r="A125" s="18">
+    <row r="126" spans="1:3">
+      <c r="A126" s="18">
         <v>46133</v>
       </c>
-      <c r="B125" s="15">
+      <c r="B126" s="15">
         <v>47981.781644150004</v>
       </c>
-      <c r="C125" s="29">
+      <c r="C126" s="29">
         <f t="shared" si="3"/>
         <v>-6.5402088492716129E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:3">
-      <c r="A126" s="18">
+    <row r="127" spans="1:3">
+      <c r="A127" s="18">
         <v>46132</v>
       </c>
-      <c r="B126" s="15">
+      <c r="B127" s="15">
         <v>51339.49161813</v>
       </c>
-      <c r="C126" s="29">
+      <c r="C127" s="29">
         <f t="shared" si="3"/>
         <v>1.9819948129202027</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
-      <c r="A127" s="18">
+    <row r="128" spans="1:3">
+      <c r="A128" s="18">
         <v>46129</v>
       </c>
-      <c r="B127" s="15">
+      <c r="B128" s="15">
         <v>17216.492596060001</v>
       </c>
-      <c r="C127" s="29">
+      <c r="C128" s="29">
         <f t="shared" si="3"/>
         <v>910.40237411852581</v>
       </c>
     </row>
-    <row r="128" spans="1:3">
-      <c r="A128" s="18">
+    <row r="129" spans="1:3">
+      <c r="A129" s="18">
         <v>46128</v>
       </c>
-      <c r="B128" s="15">
+      <c r="B129" s="15">
         <v>18.890111640000001</v>
       </c>
-      <c r="C128" s="29">
+      <c r="C129" s="29">
         <f t="shared" si="3"/>
         <v>0.19572063797541306</v>
       </c>
     </row>
-    <row r="129" spans="1:3">
-      <c r="A129" s="18">
+    <row r="130" spans="1:3">
+      <c r="A130" s="18">
         <v>46127</v>
       </c>
-      <c r="B129" s="38">
+      <c r="B130" s="38">
         <v>15.79809785</v>
       </c>
-      <c r="C129" s="29">
+      <c r="C130" s="29">
         <f t="shared" si="3"/>
         <v>-2.5764893835585476E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
-      <c r="A130" s="18">
+    <row r="131" spans="1:3">
+      <c r="A131" s="18">
         <v>46126</v>
       </c>
-      <c r="B130" s="38">
+      <c r="B131" s="38">
         <v>16.215898760000002</v>
       </c>
-      <c r="C130" s="29">
+      <c r="C131" s="29">
         <f t="shared" si="3"/>
         <v>-0.99344926580920656</v>
       </c>
     </row>
-    <row r="131" spans="1:3">
-      <c r="A131" s="18">
+    <row r="132" spans="1:3">
+      <c r="A132" s="18">
         <v>46125</v>
       </c>
-      <c r="B131" s="15">
+      <c r="B132" s="15">
         <v>2475.4322626600001</v>
       </c>
-      <c r="C131" s="29">
+      <c r="C132" s="29">
         <f t="shared" si="3"/>
         <v>-0.68887087467151309</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
-      <c r="A132" s="18">
+    <row r="133" spans="1:3">
+      <c r="A133" s="18">
         <v>46122</v>
       </c>
-      <c r="B132" s="15">
+      <c r="B133" s="15">
         <v>7956.2858669899997</v>
       </c>
-      <c r="C132" s="29">
+      <c r="C133" s="29">
         <f t="shared" si="3"/>
         <v>190.54886991293833</v>
       </c>
     </row>
-    <row r="133" spans="1:3">
-      <c r="A133" s="18">
+    <row r="134" spans="1:3">
+      <c r="A134" s="18">
         <v>46121</v>
       </c>
-      <c r="B133" s="15">
+      <c r="B134" s="15">
         <v>41.536584740000002</v>
       </c>
-      <c r="C133" s="29">
+      <c r="C134" s="29">
         <f t="shared" si="3"/>
         <v>-0.92845434694034024</v>
       </c>
     </row>
-    <row r="134" spans="1:3">
-      <c r="A134" s="18">
-        <v>46120</v>
-      </c>
-      <c r="B134" s="15">
-        <v>580.56056466999996</v>
-      </c>
-      <c r="C134" s="29">
-        <f>+(B134-B135)/B135</f>
-        <v>3.9632497533121036</v>
-      </c>
-    </row>
     <row r="135" spans="1:3">
       <c r="A135" s="18">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B135" s="15">
-        <v>116.97186189</v>
+        <v>580.56056466999996</v>
+      </c>
+      <c r="C135" s="29">
+        <f>+(B135-B136)/B136</f>
+        <v>3.9632497533121036</v>
       </c>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="18">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B136" s="15">
-        <v>6972.36861443</v>
+        <v>116.97186189</v>
       </c>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="18">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B137" s="15">
-        <v>540.00852741999995</v>
+        <v>6972.36861443</v>
       </c>
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="18">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B138" s="15">
-        <v>5262.3389565099997</v>
+        <v>540.00852741999995</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="18">
+        <v>46112</v>
+      </c>
+      <c r="B139" s="15">
+        <v>5262.3389565099997</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3">
+      <c r="A140" s="18">
         <v>46111</v>
       </c>
-      <c r="B139" s="15">
+      <c r="B140" s="15">
         <v>22969.58967849</v>
       </c>
     </row>
@@ -8870,7 +8905,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="13.125" customWidth="1"/>
@@ -10468,7 +10503,7 @@
         <v>13240</v>
       </c>
       <c r="E76" s="30">
-        <f t="shared" ref="E76:E127" si="4">+((D76-D75)/D75)</f>
+        <f t="shared" ref="E76:E128" si="4">+((D76-D75)/D75)</f>
         <v>-2.185545255859522E-3</v>
       </c>
       <c r="F76" s="31">
@@ -11548,6 +11583,27 @@
       </c>
       <c r="F127" s="31">
         <v>-1.36</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="24">
+        <v>46318</v>
+      </c>
+      <c r="B128" s="25">
+        <v>12745</v>
+      </c>
+      <c r="C128" s="23">
+        <v>3</v>
+      </c>
+      <c r="D128" s="25">
+        <v>12748</v>
+      </c>
+      <c r="E128" s="30">
+        <f t="shared" si="4"/>
+        <v>-1.2777820800743437E-2</v>
+      </c>
+      <c r="F128" s="31">
+        <v>-1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Datos_Macroeconomicos.xlsx
+++ b/Datos_Macroeconomicos.xlsx
@@ -2999,7 +2999,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3007,7 +3007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H145"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="26.625" style="10" customWidth="1"/>
@@ -5826,6 +5826,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="20">
+        <v>46323</v>
+      </c>
+      <c r="B146" s="16">
+        <v>0</v>
+      </c>
+      <c r="C146" s="19"/>
+      <c r="D146" s="16">
+        <v>0</v>
+      </c>
+      <c r="E146" s="19"/>
+      <c r="F146" s="16">
+        <v>0</v>
+      </c>
+      <c r="G146" s="19"/>
+      <c r="H146" s="16">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5834,7 +5854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.875" bestFit="1" customWidth="1"/>
@@ -5862,15 +5882,15 @@
       </c>
     </row>
     <row r="2" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A2" s="23" t="s">
-        <v>41</v>
+      <c r="A2" s="24">
+        <v>46323</v>
       </c>
       <c r="B2" s="23">
-        <v>87037.177886279998</v>
+        <v>59915.570356620003</v>
       </c>
       <c r="C2" s="29">
-        <f t="shared" ref="C2:C11" si="0">+(B2-B3)/B3</f>
-        <v>-0.54164939036545867</v>
+        <f t="shared" ref="C2:C12" si="0">+(B2-B3)/B3</f>
+        <v>-0.31160945458383571</v>
       </c>
       <c r="D2" s="23" t="s">
         <v>8</v>
@@ -5880,15 +5900,15 @@
       </c>
     </row>
     <row r="3" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="24">
-        <v>46318</v>
+      <c r="A3" s="23" t="s">
+        <v>41</v>
       </c>
       <c r="B3" s="23">
-        <v>189892.13945995999</v>
+        <v>87037.177886279998</v>
       </c>
       <c r="C3" s="29">
         <f t="shared" si="0"/>
-        <v>14.509079849304559</v>
+        <v>-0.54164939036545867</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>9</v>
@@ -5899,14 +5919,14 @@
     </row>
     <row r="4" spans="1:5" s="23" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="24">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="B4" s="23">
-        <v>12243.93331552</v>
+        <v>189892.13945995999</v>
       </c>
       <c r="C4" s="29">
         <f t="shared" si="0"/>
-        <v>-0.75767308153526292</v>
+        <v>14.509079849304559</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>10</v>
@@ -5917,14 +5937,14 @@
     </row>
     <row r="5" spans="1:5" ht="17.25" customHeight="1">
       <c r="A5" s="24">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B5" s="23">
-        <v>50526.509366320002</v>
+        <v>12243.93331552</v>
       </c>
       <c r="C5" s="29">
         <f t="shared" si="0"/>
-        <v>-0.35247381438929659</v>
+        <v>-0.75767308153526292</v>
       </c>
       <c r="D5" s="23" t="s">
         <v>29</v>
@@ -5935,14 +5955,14 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="24">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="B6" s="23">
-        <v>78030.063477150004</v>
+        <v>50526.509366320002</v>
       </c>
       <c r="C6" s="29">
         <f t="shared" si="0"/>
-        <v>-0.51127008544838759</v>
+        <v>-0.35247381438929659</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>30</v>
@@ -5953,14 +5973,14 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="24">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="B7" s="23">
-        <v>159658.86505789001</v>
+        <v>78030.063477150004</v>
       </c>
       <c r="C7" s="29">
         <f t="shared" si="0"/>
-        <v>-0.18383477994159175</v>
+        <v>-0.51127008544838759</v>
       </c>
       <c r="D7" s="23" t="s">
         <v>31</v>
@@ -5970,15 +5990,15 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="23" t="s">
-        <v>40</v>
+      <c r="A8" s="24">
+        <v>46314</v>
       </c>
       <c r="B8" s="23">
-        <v>195620.76542108</v>
+        <v>159658.86505789001</v>
       </c>
       <c r="C8" s="29">
         <f t="shared" si="0"/>
-        <v>0.39348231037382758</v>
+        <v>-0.18383477994159175</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>35</v>
@@ -5988,15 +6008,15 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="24">
-        <v>46310</v>
+      <c r="A9" s="23" t="s">
+        <v>40</v>
       </c>
       <c r="B9" s="23">
-        <v>140382.66863150999</v>
+        <v>195620.76542108</v>
       </c>
       <c r="C9" s="29">
         <f t="shared" si="0"/>
-        <v>11.24948691206232</v>
+        <v>0.39348231037382758</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>36</v>
@@ -6007,14 +6027,14 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="24">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="B10" s="23">
-        <v>11460.28969534</v>
+        <v>140382.66863150999</v>
       </c>
       <c r="C10" s="29">
         <f t="shared" si="0"/>
-        <v>-0.88352658705352882</v>
+        <v>11.24948691206232</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>39</v>
@@ -6025,1549 +6045,1561 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="24">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B11" s="23">
-        <v>98394.040368739996</v>
+        <v>11460.28969534</v>
       </c>
       <c r="C11" s="29">
         <f t="shared" si="0"/>
-        <v>-0.6788555314993624</v>
+        <v>-0.88352658705352882</v>
       </c>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="24">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="B12" s="23">
-        <v>306385.59906737</v>
+        <v>98394.040368739996</v>
       </c>
       <c r="C12" s="29">
-        <f t="shared" ref="C12:C22" si="1">+(B12-B13)/B13</f>
-        <v>9.336258026433894E-2</v>
+        <f t="shared" si="0"/>
+        <v>-0.6788555314993624</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="24">
+        <v>46304</v>
+      </c>
+      <c r="B13" s="23">
+        <v>306385.59906737</v>
+      </c>
+      <c r="C13" s="29">
+        <f t="shared" ref="C13:C23" si="1">+(B13-B14)/B14</f>
+        <v>9.336258026433894E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="24">
         <v>46303</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B14" s="23">
         <v>280223.23481502</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C14" s="29">
         <f t="shared" si="1"/>
         <v>-3.649289843956157E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="24">
+      <c r="E14" s="35"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24">
         <v>46302</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B15" s="23">
         <v>290836.70931037999</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C15" s="29">
         <f t="shared" si="1"/>
         <v>3.9357330833461011E-3</v>
       </c>
-      <c r="E14" s="35"/>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="24">
+      <c r="E15" s="35"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24">
         <v>46301</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B16" s="23">
         <v>289696.54104963999</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C16" s="29">
         <f t="shared" si="1"/>
         <v>-2.9955821881414251E-2</v>
       </c>
-      <c r="E15" s="35"/>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="24">
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24">
         <v>46300</v>
       </c>
-      <c r="B16" s="23">
+      <c r="B17" s="23">
         <v>298642.62637141999</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C17" s="29">
         <f t="shared" si="1"/>
         <v>-0.13794268733409284</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="24">
+    <row r="18" spans="1:5">
+      <c r="A18" s="24">
         <v>46297</v>
       </c>
-      <c r="B17" s="23">
+      <c r="B18" s="23">
         <v>346430.12939344998</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C18" s="29">
         <f t="shared" si="1"/>
         <v>0.2638202658078479</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="24">
+    <row r="19" spans="1:5">
+      <c r="A19" s="24">
         <v>46296</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B19" s="23">
         <v>274113.44695601001</v>
       </c>
-      <c r="C18" s="29">
+      <c r="C19" s="29">
         <f t="shared" si="1"/>
         <v>0.35910087116479922</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="24">
+    <row r="20" spans="1:5">
+      <c r="A20" s="24">
         <v>46295</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B20" s="23">
         <v>201687.34548826001</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C20" s="29">
         <f t="shared" si="1"/>
         <v>8.8268407504102413</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="24">
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24">
         <v>46294</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B21" s="23">
         <v>20524.128823380001</v>
       </c>
-      <c r="C20" s="29">
+      <c r="C21" s="29">
         <f t="shared" si="1"/>
         <v>-0.85681185394119452</v>
       </c>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="24">
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24">
         <v>46293</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B22" s="23">
         <v>143336.78721526999</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C22" s="29">
         <f t="shared" si="1"/>
         <v>-0.49898704513189668</v>
       </c>
-      <c r="E21" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="24">
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24">
         <v>46290</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B23" s="23">
         <v>286093.97386342002</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C23" s="29">
         <f t="shared" si="1"/>
         <v>0.55858664283872839</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="24">
-        <v>46289</v>
-      </c>
-      <c r="B23" s="23">
-        <v>183559.87790473</v>
-      </c>
-      <c r="C23" s="29">
-        <f t="shared" ref="C23:C92" si="2">+(B23-B24)/B24</f>
-        <v>5.2320875570372835E-2</v>
-      </c>
-    </row>
     <row r="24" spans="1:5">
       <c r="A24" s="24">
+        <v>46289</v>
+      </c>
+      <c r="B24" s="23">
+        <v>183559.87790473</v>
+      </c>
+      <c r="C24" s="29">
+        <f t="shared" ref="C24:C93" si="2">+(B24-B25)/B25</f>
+        <v>5.2320875570372835E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="24">
         <v>46288</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B25" s="23">
         <v>174433.37119511</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C25" s="29">
         <f t="shared" si="2"/>
         <v>0.18793186198768058</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="24">
+    <row r="26" spans="1:5">
+      <c r="A26" s="24">
         <v>46287</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B26" s="23">
         <v>146837.85895197999</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C26" s="29">
         <f t="shared" si="2"/>
         <v>6.7871692861553368E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="24">
+    <row r="27" spans="1:5">
+      <c r="A27" s="24">
         <v>46286</v>
       </c>
-      <c r="B26" s="23">
+      <c r="B27" s="23">
         <v>137505.15153979001</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C27" s="29">
         <f t="shared" si="2"/>
         <v>0.25618058698994745</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="24">
+    <row r="28" spans="1:5">
+      <c r="A28" s="24">
         <v>46283</v>
       </c>
-      <c r="B27" s="23">
+      <c r="B28" s="23">
         <v>109462.8853239</v>
       </c>
-      <c r="C27" s="29">
+      <c r="C28" s="29">
         <f t="shared" si="2"/>
         <v>0.32349555871151542</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="24">
+    <row r="29" spans="1:5">
+      <c r="A29" s="24">
         <v>46282</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B29" s="23">
         <v>82707.40661228</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C29" s="29">
         <f t="shared" si="2"/>
         <v>28.486447660130633</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="24">
+    <row r="30" spans="1:5">
+      <c r="A30" s="24">
         <v>46281</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B30" s="23">
         <v>2804.9294905100001</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C30" s="29">
         <f t="shared" si="2"/>
         <v>54.85948274687906</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="24">
+    <row r="31" spans="1:5">
+      <c r="A31" s="24">
         <v>46280</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B31" s="23">
         <v>50.214025489999997</v>
       </c>
-      <c r="C30" s="29">
+      <c r="C31" s="29">
         <f t="shared" si="2"/>
         <v>0.37097114686342592</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="24">
+    <row r="32" spans="1:5">
+      <c r="A32" s="24">
         <v>46276</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B32" s="23">
         <v>36.626609979999998</v>
       </c>
-      <c r="C31" s="29">
+      <c r="C32" s="29">
         <f t="shared" si="2"/>
         <v>-0.67806849277578529</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="24">
+    <row r="33" spans="1:3">
+      <c r="A33" s="24">
         <v>46275</v>
       </c>
-      <c r="B32" s="23">
+      <c r="B33" s="23">
         <v>113.77143633999999</v>
       </c>
-      <c r="C32" s="29">
+      <c r="C33" s="29">
         <f t="shared" si="2"/>
         <v>18.560573043109468</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="24">
+    <row r="34" spans="1:3">
+      <c r="A34" s="24">
         <v>46274</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B34" s="23">
         <v>5.8163651999999999</v>
       </c>
-      <c r="C33" s="29">
+      <c r="C34" s="29">
         <f t="shared" si="2"/>
         <v>0.64045278098882874</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="24">
+    <row r="35" spans="1:3">
+      <c r="A35" s="24">
         <v>46273</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B35" s="23">
         <v>3.5455852600000002</v>
       </c>
-      <c r="C34" s="29">
+      <c r="C35" s="29">
         <f t="shared" si="2"/>
         <v>-0.82640880552358198</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="24">
+    <row r="36" spans="1:3">
+      <c r="A36" s="24">
         <v>46272</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B36" s="23">
         <v>20.42491424</v>
       </c>
-      <c r="C35" s="29">
+      <c r="C36" s="29">
         <f t="shared" si="2"/>
         <v>2.4737529624349173</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="24">
+    <row r="37" spans="1:3">
+      <c r="A37" s="24">
         <v>46269</v>
       </c>
-      <c r="B36" s="23">
+      <c r="B37" s="23">
         <v>5.8797831800000004</v>
       </c>
-      <c r="C36" s="29">
+      <c r="C37" s="29">
         <f t="shared" si="2"/>
         <v>-0.97953700801723442</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="24">
+    <row r="38" spans="1:3">
+      <c r="A38" s="24">
         <v>46268</v>
       </c>
-      <c r="B37" s="23">
+      <c r="B38" s="23">
         <v>287.33741307000003</v>
       </c>
-      <c r="C37" s="29">
+      <c r="C38" s="29">
         <f t="shared" si="2"/>
         <v>80.163058476193896</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="24">
+    <row r="39" spans="1:3">
+      <c r="A39" s="24">
         <v>46267</v>
       </c>
-      <c r="B38" s="23">
+      <c r="B39" s="23">
         <v>3.5402487100000002</v>
       </c>
-      <c r="C38" s="29">
+      <c r="C39" s="29">
         <f t="shared" si="2"/>
         <v>-0.77463732472189939</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="24">
+    <row r="40" spans="1:3">
+      <c r="A40" s="24">
         <v>46266</v>
       </c>
-      <c r="B39" s="23">
+      <c r="B40" s="23">
         <v>15.709117340000001</v>
       </c>
-      <c r="C39" s="29">
+      <c r="C40" s="29">
         <f t="shared" si="2"/>
         <v>-0.99727371031195</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="24">
+    <row r="41" spans="1:3">
+      <c r="A41" s="24">
         <v>46265</v>
       </c>
-      <c r="B40" s="23">
+      <c r="B41" s="23">
         <v>5762.0866222900004</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C41" s="29">
         <f t="shared" si="2"/>
         <v>1028.4103166122507</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="24">
+    <row r="42" spans="1:3">
+      <c r="A42" s="24">
         <v>46262</v>
       </c>
-      <c r="B41" s="23">
+      <c r="B42" s="23">
         <v>5.5974634500000002</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C42" s="29">
         <f t="shared" si="2"/>
         <v>-0.98760095272084658</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="24">
+    <row r="43" spans="1:3">
+      <c r="A43" s="24">
         <v>46261</v>
       </c>
-      <c r="B42" s="23">
+      <c r="B43" s="23">
         <v>451.44302815999998</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C43" s="29">
         <f t="shared" si="2"/>
         <v>98.812318362183703</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="24">
+    <row r="44" spans="1:3">
+      <c r="A44" s="24">
         <v>46260</v>
       </c>
-      <c r="B43" s="23">
+      <c r="B44" s="23">
         <v>4.5229189700000001</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C44" s="29">
         <f t="shared" si="2"/>
         <v>-0.9864837734804992</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="24">
+    <row r="45" spans="1:3">
+      <c r="A45" s="24">
         <v>46259</v>
       </c>
-      <c r="B44" s="23">
+      <c r="B45" s="23">
         <v>334.62882287999997</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C45" s="29">
         <f t="shared" si="2"/>
         <v>74.639780601233326</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="24">
+    <row r="46" spans="1:3">
+      <c r="A46" s="24">
         <v>46256</v>
       </c>
-      <c r="B45" s="23">
+      <c r="B46" s="23">
         <v>4.4239792900000001</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C46" s="29">
         <f t="shared" si="2"/>
         <v>-0.96494750708048294</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="24">
+    <row r="47" spans="1:3">
+      <c r="A47" s="24">
         <v>46255</v>
       </c>
-      <c r="B46" s="23">
+      <c r="B47" s="23">
         <v>126.21011864</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C47" s="29">
         <f t="shared" si="2"/>
         <v>71.190985743560688</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
-      <c r="A47" s="24">
+    <row r="48" spans="1:3">
+      <c r="A48" s="24">
         <v>46254</v>
       </c>
-      <c r="B47" s="23">
+      <c r="B48" s="23">
         <v>1.7482808599999999</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C48" s="29">
         <f t="shared" si="2"/>
         <v>-5.8184422793468707E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
-      <c r="A48" s="24">
+    <row r="49" spans="1:3">
+      <c r="A49" s="24">
         <v>46253</v>
       </c>
-      <c r="B48" s="23">
+      <c r="B49" s="23">
         <v>1.8562879000000001</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C49" s="29">
         <f t="shared" si="2"/>
         <v>2.7977445325652688E-3</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="24">
+    <row r="50" spans="1:3">
+      <c r="A50" s="24">
         <v>46252</v>
       </c>
-      <c r="B49" s="23">
+      <c r="B50" s="23">
         <v>1.8511089700000001</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C50" s="29">
         <f t="shared" si="2"/>
         <v>-0.85226798513183877</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="24">
+    <row r="51" spans="1:3">
+      <c r="A51" s="24">
         <v>46251</v>
       </c>
-      <c r="B50" s="23">
+      <c r="B51" s="23">
         <v>12.53018157</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C51" s="29">
         <f t="shared" si="2"/>
         <v>1.9051656117130662</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="24">
+    <row r="52" spans="1:3">
+      <c r="A52" s="24">
         <v>46248</v>
       </c>
-      <c r="B51" s="23">
+      <c r="B52" s="23">
         <v>4.3130696300000002</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C52" s="29">
         <f t="shared" si="2"/>
         <v>0.67644958648237985</v>
       </c>
     </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="24">
+    <row r="53" spans="1:3">
+      <c r="A53" s="24">
         <v>46247</v>
       </c>
-      <c r="B52" s="23">
+      <c r="B53" s="23">
         <v>2.5727404300000001</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C53" s="29">
         <f t="shared" si="2"/>
         <v>7.9800987331472867E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="A53" s="24">
+    <row r="54" spans="1:3">
+      <c r="A54" s="24">
         <v>46246</v>
       </c>
-      <c r="B53" s="23">
+      <c r="B54" s="23">
         <v>2.3826061100000002</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C54" s="29">
         <f t="shared" si="2"/>
         <v>-0.998836660607344</v>
       </c>
     </row>
-    <row r="54" spans="1:3">
-      <c r="A54" s="24">
+    <row r="55" spans="1:3">
+      <c r="A55" s="24">
         <v>46245</v>
       </c>
-      <c r="B54" s="23">
+      <c r="B55" s="23">
         <v>2048.0748137999999</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C55" s="29">
         <f t="shared" si="2"/>
         <v>493.39746561225513</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
-      <c r="A55" s="24">
+    <row r="56" spans="1:3">
+      <c r="A56" s="24">
         <v>46244</v>
       </c>
-      <c r="B55" s="23">
+      <c r="B56" s="23">
         <v>4.14256738</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C56" s="29">
         <f t="shared" si="2"/>
         <v>-0.99973486131357592</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="24">
+    <row r="57" spans="1:3">
+      <c r="A57" s="24">
         <v>46241</v>
       </c>
-      <c r="B56" s="23">
+      <c r="B57" s="23">
         <v>15624.152913600001</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C57" s="29">
         <f t="shared" si="2"/>
         <v>4796.873754983676</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="24">
+    <row r="58" spans="1:3">
+      <c r="A58" s="24">
         <v>46240</v>
       </c>
-      <c r="B57" s="23">
+      <c r="B58" s="23">
         <v>3.2564743699999998</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C58" s="29">
         <f t="shared" si="2"/>
         <v>0.15942681787904545</v>
       </c>
     </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="24">
+    <row r="59" spans="1:3">
+      <c r="A59" s="24">
         <v>46239</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B59" s="23">
         <v>2.8086933300000001</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C59" s="29">
         <f t="shared" si="2"/>
         <v>-0.99437447438816284</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="24">
+    <row r="60" spans="1:3">
+      <c r="A60" s="24">
         <v>46238</v>
       </c>
-      <c r="B59" s="23">
+      <c r="B60" s="23">
         <v>499.27660521000001</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C60" s="29">
         <f t="shared" si="2"/>
         <v>75.11816589074563</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="24">
+    <row r="61" spans="1:3">
+      <c r="A61" s="24">
         <v>46237</v>
       </c>
-      <c r="B60" s="23">
+      <c r="B61" s="23">
         <v>6.5592306300000001</v>
       </c>
-      <c r="C60" s="29">
+      <c r="C61" s="29">
         <f t="shared" si="2"/>
         <v>-0.99966330474421161</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
-      <c r="A61" s="24">
+    <row r="62" spans="1:3">
+      <c r="A62" s="24">
         <v>46234</v>
       </c>
-      <c r="B61" s="23">
+      <c r="B62" s="23">
         <v>19481.20894855</v>
       </c>
-      <c r="C61" s="29">
+      <c r="C62" s="29">
         <f t="shared" si="2"/>
         <v>40.77506746658235</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
-      <c r="A62" s="24">
+    <row r="63" spans="1:3">
+      <c r="A63" s="24">
         <v>46233</v>
       </c>
-      <c r="B62">
+      <c r="B63">
         <v>466.33578662999997</v>
       </c>
-      <c r="C62" s="29">
+      <c r="C63" s="29">
         <f t="shared" si="2"/>
         <v>3.5918026507549188</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
-      <c r="A63" s="24">
+    <row r="64" spans="1:3">
+      <c r="A64" s="24">
         <v>46232</v>
       </c>
-      <c r="B63" s="23">
+      <c r="B64" s="23">
         <v>101.55832515</v>
       </c>
-      <c r="C63" s="29">
+      <c r="C64" s="29">
         <f t="shared" si="2"/>
         <v>22.269067927747528</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="24">
+    <row r="65" spans="1:3">
+      <c r="A65" s="24">
         <v>46231</v>
       </c>
-      <c r="B64" s="23">
+      <c r="B65" s="23">
         <v>4.3645205499999999</v>
       </c>
-      <c r="C64" s="29">
+      <c r="C65" s="29">
         <f t="shared" si="2"/>
         <v>-0.98047278251084946</v>
       </c>
     </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="24">
+    <row r="66" spans="1:3">
+      <c r="A66" s="24">
         <v>46108</v>
       </c>
-      <c r="B65" s="23">
+      <c r="B66" s="23">
         <v>223.50959897000001</v>
       </c>
-      <c r="C65" s="29">
+      <c r="C66" s="29">
         <f t="shared" si="2"/>
         <v>-0.99220607504587943</v>
       </c>
     </row>
-    <row r="66" spans="1:3">
-      <c r="A66" s="24">
+    <row r="67" spans="1:3">
+      <c r="A67" s="24">
         <v>46226</v>
       </c>
-      <c r="B66" s="23">
+      <c r="B67" s="23">
         <v>28677.412251940001</v>
       </c>
-      <c r="C66" s="29">
+      <c r="C67" s="29">
         <f t="shared" si="2"/>
         <v>32.413800410299046</v>
       </c>
     </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="24">
+    <row r="68" spans="1:3">
+      <c r="A68" s="24">
         <v>46225</v>
       </c>
-      <c r="B67" s="23">
+      <c r="B68" s="23">
         <v>858.25054019000004</v>
       </c>
-      <c r="C67" s="29">
+      <c r="C68" s="29">
         <f t="shared" si="2"/>
         <v>41.77708649767068</v>
       </c>
     </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="24">
+    <row r="69" spans="1:3">
+      <c r="A69" s="24">
         <v>46224</v>
       </c>
-      <c r="B68" s="23">
+      <c r="B69" s="23">
         <v>20.063323860000001</v>
       </c>
-      <c r="C68" s="29">
+      <c r="C69" s="29">
         <f t="shared" si="2"/>
         <v>-0.99734079323279778</v>
       </c>
     </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="24">
+    <row r="70" spans="1:3">
+      <c r="A70" s="24">
         <v>46220</v>
       </c>
-      <c r="B69" s="23">
+      <c r="B70" s="23">
         <v>7544.8528890099997</v>
       </c>
-      <c r="C69" s="29">
+      <c r="C70" s="29">
         <f t="shared" si="2"/>
         <v>-0.54491271467140989</v>
       </c>
     </row>
-    <row r="70" spans="1:3">
-      <c r="A70" s="24">
+    <row r="71" spans="1:3">
+      <c r="A71" s="24">
         <v>46219</v>
       </c>
-      <c r="B70" s="23">
+      <c r="B71" s="23">
         <v>16578.913830919999</v>
       </c>
-      <c r="C70" s="29">
+      <c r="C71" s="29">
         <f t="shared" si="2"/>
         <v>1.1008050673763534</v>
       </c>
     </row>
-    <row r="71" spans="1:3">
-      <c r="A71" s="24">
+    <row r="72" spans="1:3">
+      <c r="A72" s="24">
         <v>46218</v>
       </c>
-      <c r="B71" s="23">
+      <c r="B72" s="23">
         <v>7891.6954687400003</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C72" s="29">
         <f t="shared" si="2"/>
         <v>-0.79678113606112111</v>
       </c>
     </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="24">
+    <row r="73" spans="1:3">
+      <c r="A73" s="24">
         <v>46217</v>
       </c>
-      <c r="B72" s="23">
+      <c r="B73" s="23">
         <v>38833.478919130001</v>
       </c>
-      <c r="C72" s="29">
+      <c r="C73" s="29">
         <f t="shared" si="2"/>
         <v>-0.25771272667553924</v>
       </c>
     </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="24">
+    <row r="74" spans="1:3">
+      <c r="A74" s="24">
         <v>46216</v>
       </c>
-      <c r="B73" s="23">
+      <c r="B74" s="23">
         <v>52315.97026473</v>
       </c>
-      <c r="C73" s="29">
+      <c r="C74" s="29">
         <f t="shared" si="2"/>
         <v>-0.19048561913228002</v>
       </c>
     </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="24">
+    <row r="75" spans="1:3">
+      <c r="A75" s="24">
         <v>46213</v>
       </c>
-      <c r="B74" s="23">
+      <c r="B75" s="23">
         <v>64626.363040830001</v>
       </c>
-      <c r="C74" s="29">
+      <c r="C75" s="29">
         <f t="shared" si="2"/>
         <v>1.2916911129109088</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
-      <c r="A75" s="24">
+    <row r="76" spans="1:3">
+      <c r="A76" s="24">
         <v>46212</v>
       </c>
-      <c r="B75" s="23">
+      <c r="B76" s="23">
         <v>28200.29395617</v>
       </c>
-      <c r="C75" s="29">
+      <c r="C76" s="29">
         <f t="shared" si="2"/>
         <v>2.65997178100841</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="24">
+    <row r="77" spans="1:3">
+      <c r="A77" s="24">
         <v>46211</v>
       </c>
-      <c r="B76" s="23">
+      <c r="B77" s="23">
         <v>7705.0577555</v>
       </c>
-      <c r="C76" s="29">
+      <c r="C77" s="29">
         <f t="shared" si="2"/>
         <v>0.84099979813836301</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
-      <c r="A77" s="24">
+    <row r="78" spans="1:3">
+      <c r="A78" s="24">
         <v>46210</v>
       </c>
-      <c r="B77" s="23">
+      <c r="B78" s="23">
         <v>4185.2572516800001</v>
       </c>
-      <c r="C77" s="29">
+      <c r="C78" s="29">
         <f t="shared" si="2"/>
         <v>-0.5358672604044985</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
-      <c r="A78" s="24">
+    <row r="79" spans="1:3">
+      <c r="A79" s="24">
         <v>46209</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B79" s="23">
         <v>9017.3713134900008</v>
       </c>
-      <c r="C78" s="29">
+      <c r="C79" s="29">
         <f t="shared" si="2"/>
         <v>-0.47344417767330416</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
-      <c r="A79" s="24">
+    <row r="80" spans="1:3">
+      <c r="A80" s="24">
         <v>46206</v>
       </c>
-      <c r="B79" s="23">
+      <c r="B80" s="23">
         <v>17125.195337590001</v>
       </c>
-      <c r="C79" s="29">
+      <c r="C80" s="29">
         <f t="shared" si="2"/>
         <v>-0.39167454677290181</v>
       </c>
     </row>
-    <row r="80" spans="1:3">
-      <c r="A80" s="24">
+    <row r="81" spans="1:3">
+      <c r="A81" s="24">
         <v>46205</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B81" s="23">
         <v>28151.370695969999</v>
       </c>
-      <c r="C80" s="29">
+      <c r="C81" s="29">
         <f t="shared" si="2"/>
         <v>27.450841046685248</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
-      <c r="A81" s="24">
+    <row r="82" spans="1:3">
+      <c r="A82" s="24">
         <v>46204</v>
       </c>
-      <c r="B81" s="23">
+      <c r="B82" s="23">
         <v>989.47411254999997</v>
       </c>
-      <c r="C81" s="29">
+      <c r="C82" s="29">
         <f t="shared" si="2"/>
         <v>-0.82605795449481512</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
-      <c r="A82" s="24">
+    <row r="83" spans="1:3">
+      <c r="A83" s="24">
         <v>46203</v>
       </c>
-      <c r="B82" s="23">
+      <c r="B83" s="23">
         <v>5688.5275189000004</v>
       </c>
-      <c r="C82" s="29">
+      <c r="C83" s="29">
         <f t="shared" si="2"/>
         <v>-0.82035890094428965</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
-      <c r="A83" s="24">
+    <row r="84" spans="1:3">
+      <c r="A84" s="24">
         <v>46198</v>
       </c>
-      <c r="B83" s="23">
+      <c r="B84" s="23">
         <v>31666.069450710002</v>
       </c>
-      <c r="C83" s="29">
+      <c r="C84" s="29">
         <f t="shared" si="2"/>
         <v>12.096519032059602</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
-      <c r="A84" s="24">
+    <row r="85" spans="1:3">
+      <c r="A85" s="24">
         <v>46196</v>
       </c>
-      <c r="B84" s="23">
+      <c r="B85" s="23">
         <v>2417.8997009200002</v>
       </c>
-      <c r="C84" s="29">
+      <c r="C85" s="29">
         <f t="shared" si="2"/>
         <v>0.40878477030033311</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
-      <c r="A85" s="24">
+    <row r="86" spans="1:3">
+      <c r="A86" s="24">
         <v>46195</v>
       </c>
-      <c r="B85" s="23">
+      <c r="B86" s="23">
         <v>1716.30170335</v>
       </c>
-      <c r="C85" s="29">
+      <c r="C86" s="29">
         <f t="shared" si="2"/>
         <v>103.40487339188886</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
-      <c r="A86" s="24">
+    <row r="87" spans="1:3">
+      <c r="A87" s="24">
         <v>46192</v>
       </c>
-      <c r="B86" s="23">
+      <c r="B87" s="23">
         <v>16.43890412</v>
       </c>
-      <c r="C86" s="29">
+      <c r="C87" s="29">
         <f t="shared" si="2"/>
         <v>-0.93907248343987781</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
-      <c r="A87" s="24">
+    <row r="88" spans="1:3">
+      <c r="A88" s="24">
         <v>46191</v>
       </c>
-      <c r="B87" s="23">
+      <c r="B88" s="23">
         <v>269.81083503999997</v>
       </c>
-      <c r="C87" s="29">
+      <c r="C88" s="29">
         <f t="shared" si="2"/>
         <v>-0.88259974628484428</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
-      <c r="A88" s="24">
+    <row r="89" spans="1:3">
+      <c r="A89" s="24">
         <v>46190</v>
       </c>
-      <c r="B88" s="23">
+      <c r="B89" s="23">
         <v>2298.2133896800001</v>
       </c>
-      <c r="C88" s="29">
+      <c r="C89" s="29">
         <f t="shared" si="2"/>
         <v>0.90523755264044037</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="24">
+    <row r="90" spans="1:3">
+      <c r="A90" s="24">
         <v>46189</v>
       </c>
-      <c r="B89" s="23">
+      <c r="B90" s="23">
         <v>1206.260808</v>
       </c>
-      <c r="C89" s="29">
+      <c r="C90" s="29">
         <f t="shared" si="2"/>
         <v>142.26137862232778</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24">
+    <row r="91" spans="1:3">
+      <c r="A91" s="24">
         <v>46188</v>
       </c>
-      <c r="B90" s="23">
+      <c r="B91" s="23">
         <v>8.42</v>
       </c>
-      <c r="C90" s="29">
+      <c r="C91" s="29">
         <f t="shared" si="2"/>
         <v>-0.5604660313731078</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
-      <c r="A91" s="24">
+    <row r="92" spans="1:3">
+      <c r="A92" s="24">
         <v>46185</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B92" s="23">
         <v>19.156653639999998</v>
       </c>
-      <c r="C91" s="29">
+      <c r="C92" s="29">
         <f t="shared" si="2"/>
         <v>0.50703525245440206</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
-      <c r="A92" s="24">
+    <row r="93" spans="1:3">
+      <c r="A93" s="24">
         <v>46184</v>
       </c>
-      <c r="B92" s="23">
+      <c r="B93" s="23">
         <v>12.711483429999999</v>
       </c>
-      <c r="C92" s="29">
+      <c r="C93" s="29">
         <f t="shared" si="2"/>
         <v>-0.99943660659465605</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="24">
-        <v>46183</v>
-      </c>
-      <c r="B93" s="23">
-        <v>22562.357509739999</v>
-      </c>
-      <c r="C93" s="29">
-        <f t="shared" ref="C93:C134" si="3">+(B93-B94)/B94</f>
-        <v>5.2639483520141219</v>
-      </c>
-    </row>
     <row r="94" spans="1:3">
       <c r="A94" s="24">
+        <v>46183</v>
+      </c>
+      <c r="B94" s="23">
+        <v>22562.357509739999</v>
+      </c>
+      <c r="C94" s="29">
+        <f t="shared" ref="C94:C135" si="3">+(B94-B95)/B95</f>
+        <v>5.2639483520141219</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="24">
         <v>46182</v>
       </c>
-      <c r="B94" s="23">
+      <c r="B95" s="23">
         <v>3601.9386242999999</v>
       </c>
-      <c r="C94" s="29">
+      <c r="C95" s="29">
         <f t="shared" si="3"/>
         <v>-0.93820968147801931</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="24">
+    <row r="96" spans="1:3">
+      <c r="A96" s="24">
         <v>46178</v>
       </c>
-      <c r="B95" s="23">
+      <c r="B96" s="23">
         <v>58292.928576159997</v>
       </c>
-      <c r="C95" s="29">
+      <c r="C96" s="29">
         <f t="shared" si="3"/>
         <v>5.2345136037951523</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
-      <c r="A96" s="24">
+    <row r="97" spans="1:4">
+      <c r="A97" s="24">
         <v>46177</v>
       </c>
-      <c r="B96" s="23">
+      <c r="B97" s="23">
         <v>9350.0363108799993</v>
       </c>
-      <c r="C96" s="29">
+      <c r="C97" s="29">
         <f t="shared" si="3"/>
         <v>1.8327551324816331</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="24">
+    <row r="98" spans="1:4">
+      <c r="A98" s="24">
         <v>46176</v>
       </c>
-      <c r="B97" s="23">
+      <c r="B98" s="23">
         <v>3300.6863896099999</v>
       </c>
-      <c r="C97" s="29">
+      <c r="C98" s="29">
         <f t="shared" si="3"/>
         <v>-0.88947445735006914</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="24">
+    <row r="99" spans="1:4">
+      <c r="A99" s="24">
         <v>46175</v>
       </c>
-      <c r="B98" s="23">
+      <c r="B99" s="23">
         <v>29863.561946620001</v>
       </c>
-      <c r="C98" s="29">
+      <c r="C99" s="29">
         <f t="shared" si="3"/>
         <v>539.15459406063144</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="24">
+    <row r="100" spans="1:4">
+      <c r="A100" s="24">
         <v>46174</v>
       </c>
-      <c r="B99" s="23">
+      <c r="B100" s="23">
         <v>55.287064620000002</v>
       </c>
-      <c r="C99" s="29">
+      <c r="C100" s="29">
         <f t="shared" si="3"/>
         <v>-0.99834811895033015</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="24">
+    <row r="101" spans="1:4">
+      <c r="A101" s="24">
         <v>46171</v>
       </c>
-      <c r="B100" s="23">
+      <c r="B101" s="23">
         <v>33469.1560455</v>
       </c>
-      <c r="C100" s="29">
+      <c r="C101" s="29">
         <f t="shared" si="3"/>
         <v>2.616728100871637</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="24">
+    <row r="102" spans="1:4">
+      <c r="A102" s="24">
         <v>45074</v>
       </c>
-      <c r="B101" s="23">
+      <c r="B102" s="23">
         <v>9253.9873366299998</v>
       </c>
-      <c r="C101" s="29">
+      <c r="C102" s="29">
         <f t="shared" si="3"/>
         <v>425.96466507526281</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="24">
+    <row r="103" spans="1:4">
+      <c r="A103" s="24">
         <v>46169</v>
       </c>
-      <c r="B102" s="23">
+      <c r="B103" s="23">
         <v>21.673895040000001</v>
       </c>
-      <c r="C102" s="29">
+      <c r="C103" s="29">
         <f t="shared" si="3"/>
         <v>-0.99745431244335425</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="24">
+    <row r="104" spans="1:4">
+      <c r="A104" s="24">
         <v>46168</v>
       </c>
-      <c r="B103" s="23">
+      <c r="B104" s="23">
         <v>8513.9651106900001</v>
       </c>
-      <c r="C103" s="29">
+      <c r="C104" s="29">
         <f t="shared" si="3"/>
         <v>-0.31892665326814518</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="24">
+    <row r="105" spans="1:4">
+      <c r="A105" s="24">
         <v>46167</v>
       </c>
-      <c r="B104" s="23">
+      <c r="B105" s="23">
         <v>12500.80501835</v>
       </c>
-      <c r="C104" s="29">
+      <c r="C105" s="29">
         <f t="shared" si="3"/>
         <v>-0.78753584478722383</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="24">
+      <c r="D105" s="36"/>
+    </row>
+    <row r="106" spans="1:4">
+      <c r="A106" s="24">
         <v>46164</v>
       </c>
-      <c r="B105" s="23">
+      <c r="B106" s="23">
         <v>58837.242479</v>
       </c>
-      <c r="C105" s="29">
+      <c r="C106" s="29">
         <f t="shared" si="3"/>
         <v>1063.8095709311931</v>
       </c>
-      <c r="D105" s="36"/>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="24">
+    </row>
+    <row r="107" spans="1:4">
+      <c r="A107" s="24">
         <v>46163</v>
       </c>
-      <c r="B106" s="23">
+      <c r="B107" s="23">
         <v>55.256117230000001</v>
       </c>
-      <c r="C106" s="29">
+      <c r="C107" s="29">
         <f t="shared" si="3"/>
         <v>-0.99728557445032884</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="24">
+    <row r="108" spans="1:4">
+      <c r="A108" s="24">
         <v>46162</v>
       </c>
-      <c r="B107" s="23">
+   